--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -62868,7 +62868,7 @@
         <v>46276.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>12772922</v>
+        <v>12906682</v>
       </c>
       <c r="C2718" t="n">
         <v>4.39099979400635</v>
@@ -62883,6 +62883,29 @@
         <v>4.31300020217896</v>
       </c>
       <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>21690629</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>4.3289999961853</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>4.13000011444092</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>4.31300020217896</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>4.15700006484985</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>11988771</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>4.25099992752075</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>4.13399982452393</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>4.22200012207031</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>15575259</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>4.36299991607666</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>4.25099992752075</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>4.25099992752075</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>4.2810001373291</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>14706077</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>4.3899998664856</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>4.27299976348877</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>4.28700017929077</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>4.33300018310547</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>13370095</v>
+        <v>8883873</v>
       </c>
       <c r="C2715" t="n">
-        <v>4.40000009536743</v>
+        <v>4.43300008773804</v>
       </c>
       <c r="D2715" t="n">
-        <v>4.33799982070923</v>
+        <v>4.32600021362305</v>
       </c>
       <c r="E2715" t="n">
-        <v>4.34999990463257</v>
+        <v>4.375</v>
       </c>
       <c r="F2715" t="n">
-        <v>4.36299991607666</v>
+        <v>4.33199977874756</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>14093539</v>
+        <v>13370095</v>
       </c>
       <c r="C2716" t="n">
-        <v>4.39699983596802</v>
+        <v>4.40000009536743</v>
       </c>
       <c r="D2716" t="n">
-        <v>4.31300020217896</v>
+        <v>4.33799982070923</v>
       </c>
       <c r="E2716" t="n">
-        <v>4.3600001335144</v>
+        <v>4.34999990463257</v>
       </c>
       <c r="F2716" t="n">
-        <v>4.37799978256226</v>
+        <v>4.36299991607666</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>15550448</v>
+        <v>14093539</v>
       </c>
       <c r="C2717" t="n">
-        <v>4.42399978637695</v>
+        <v>4.39699983596802</v>
       </c>
       <c r="D2717" t="n">
-        <v>4.31400012969971</v>
+        <v>4.31300020217896</v>
       </c>
       <c r="E2717" t="n">
-        <v>4.3730001449585</v>
+        <v>4.3600001335144</v>
       </c>
       <c r="F2717" t="n">
-        <v>4.36700010299683</v>
+        <v>4.37799978256226</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>12906682</v>
+        <v>15550448</v>
       </c>
       <c r="C2718" t="n">
-        <v>4.39099979400635</v>
+        <v>4.42399978637695</v>
       </c>
       <c r="D2718" t="n">
-        <v>4.29099988937378</v>
+        <v>4.31400012969971</v>
       </c>
       <c r="E2718" t="n">
-        <v>4.38800001144409</v>
+        <v>4.3730001449585</v>
       </c>
       <c r="F2718" t="n">
-        <v>4.31300020217896</v>
+        <v>4.36700010299683</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>21690629</v>
+        <v>12906682</v>
       </c>
       <c r="C2719" t="n">
-        <v>4.3289999961853</v>
+        <v>4.39099979400635</v>
       </c>
       <c r="D2719" t="n">
-        <v>4.13000011444092</v>
+        <v>4.29099988937378</v>
       </c>
       <c r="E2719" t="n">
+        <v>4.38800001144409</v>
+      </c>
+      <c r="F2719" t="n">
         <v>4.31300020217896</v>
-      </c>
-      <c r="F2719" t="n">
-        <v>4.15700006484985</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>11988771</v>
+        <v>21690629</v>
       </c>
       <c r="C2720" t="n">
-        <v>4.25099992752075</v>
+        <v>4.3289999961853</v>
       </c>
       <c r="D2720" t="n">
-        <v>4.13399982452393</v>
+        <v>4.13000011444092</v>
       </c>
       <c r="E2720" t="n">
-        <v>4.15999984741211</v>
+        <v>4.31300020217896</v>
       </c>
       <c r="F2720" t="n">
-        <v>4.22200012207031</v>
+        <v>4.15700006484985</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>15575259</v>
+        <v>11988771</v>
       </c>
       <c r="C2721" t="n">
-        <v>4.36299991607666</v>
+        <v>4.25099992752075</v>
       </c>
       <c r="D2721" t="n">
-        <v>4.25099992752075</v>
+        <v>4.13399982452393</v>
       </c>
       <c r="E2721" t="n">
-        <v>4.25099992752075</v>
+        <v>4.15999984741211</v>
       </c>
       <c r="F2721" t="n">
-        <v>4.2810001373291</v>
+        <v>4.22200012207031</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>14706077</v>
+        <v>15575259</v>
       </c>
       <c r="C2722" t="n">
-        <v>4.3899998664856</v>
+        <v>4.36299991607666</v>
       </c>
       <c r="D2722" t="n">
-        <v>4.27299976348877</v>
+        <v>4.25099992752075</v>
       </c>
       <c r="E2722" t="n">
-        <v>4.28700017929077</v>
+        <v>4.25099992752075</v>
       </c>
       <c r="F2722" t="n">
-        <v>4.33300018310547</v>
+        <v>4.2810001373291</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>28904473</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>4.34100008010864</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>4.24100017547607</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>4.34100008010864</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>4.2649998664856</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -499,7 +499,7 @@
         <v>21.9295864105225</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4443855285645</v>
+        <v>19.4443836212158</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>22.1665782928467</v>
       </c>
       <c r="G9" t="n">
-        <v>19.65452003479</v>
+        <v>19.6545181274414</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460279464722</v>
+        <v>15.7460289001465</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>13.2778282165527</v>
       </c>
       <c r="G16" t="n">
-        <v>11.773099899292</v>
+        <v>11.7730989456177</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087112426758</v>
+        <v>12.6087121963501</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.8813648223877</v>
       </c>
       <c r="G23" t="n">
-        <v>12.3082399368286</v>
+        <v>12.3082389831543</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.0530023574829</v>
       </c>
       <c r="G26" t="n">
-        <v>11.5737524032593</v>
+        <v>11.573751449585</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393558502197</v>
+        <v>6.74393510818481</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.87747955322266</v>
+        <v>6.8774790763855</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243982315063</v>
+        <v>7.91243934631348</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218820571899</v>
+        <v>7.75218772888184</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.83838844299316</v>
       </c>
       <c r="G63" t="n">
-        <v>7.8367657661438</v>
+        <v>7.83676528930664</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G65" t="n">
-        <v>7.32262372970581</v>
+        <v>7.32262420654297</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.93220806121826</v>
       </c>
       <c r="G67" t="n">
-        <v>7.03327894210815</v>
+        <v>7.03327941894531</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.8634729385376</v>
+        <v>7.86347389221191</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86569976806641</v>
+        <v>7.86570024490356</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.25006008148193</v>
       </c>
       <c r="G79" t="n">
-        <v>8.20178318023682</v>
+        <v>8.20178413391113</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.39816093444824</v>
       </c>
       <c r="G80" t="n">
-        <v>8.33310031890869</v>
+        <v>8.33310127258301</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G86" t="n">
-        <v>8.54009246826172</v>
+        <v>8.54009342193604</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G88" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G89" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G97" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.92875480651855</v>
       </c>
       <c r="G100" t="n">
-        <v>7.9168906211853</v>
+        <v>7.91689109802246</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.04924392700195</v>
       </c>
       <c r="G108" t="n">
-        <v>8.02372455596924</v>
+        <v>8.02372550964355</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889585494995</v>
+        <v>7.77889633178711</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325277328491</v>
+        <v>7.72325325012207</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660755157471</v>
+        <v>7.73660659790039</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76488971710205</v>
+        <v>8.76489067077637</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G123" t="n">
-        <v>9.00749397277832</v>
+        <v>9.00749492645264</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933570861816</v>
+        <v>8.05933666229248</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.59193658828735</v>
+        <v>7.5919361114502</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78557395935059</v>
+        <v>7.78557348251343</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.86349010467529</v>
       </c>
       <c r="G127" t="n">
-        <v>7.85902261734009</v>
+        <v>7.85902214050293</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.60650730133057</v>
       </c>
       <c r="G130" t="n">
-        <v>8.51783657073975</v>
+        <v>8.51783561706543</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G132" t="n">
-        <v>7.823410987854</v>
+        <v>7.82341051101685</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.04171371459961</v>
       </c>
       <c r="G133" t="n">
-        <v>8.01704883575439</v>
+        <v>8.01704788208008</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.71147346496582</v>
+        <v>8.7114725112915</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420448303223</v>
+        <v>9.03420352935791</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G137" t="n">
-        <v>9.25454902648926</v>
+        <v>9.25454998016357</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>10.3771362304688</v>
       </c>
       <c r="G139" t="n">
-        <v>9.20113182067871</v>
+        <v>9.20113277435303</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>10.5679111480713</v>
       </c>
       <c r="G140" t="n">
-        <v>9.37028789520264</v>
+        <v>9.37028694152832</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>10.977071762085</v>
       </c>
       <c r="G142" t="n">
-        <v>9.73307800292969</v>
+        <v>9.733078956604</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>10.359564781189</v>
       </c>
       <c r="G145" t="n">
-        <v>9.18555164337158</v>
+        <v>9.1855525970459</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>10.6934204101562</v>
       </c>
       <c r="G146" t="n">
-        <v>9.48157215118408</v>
+        <v>9.4815731048584</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427124023438</v>
+        <v>9.78427219390869</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G149" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.3881196975708</v>
       </c>
       <c r="G152" t="n">
-        <v>8.32419776916504</v>
+        <v>8.32419681549072</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.37807941436768</v>
       </c>
       <c r="G153" t="n">
-        <v>8.31529426574707</v>
+        <v>8.31529521942139</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228736877441</v>
+        <v>8.52228832244873</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.90019989013672</v>
       </c>
       <c r="G155" t="n">
-        <v>8.77824592590332</v>
+        <v>8.778244972229</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.98303604125977</v>
       </c>
       <c r="G164" t="n">
-        <v>8.85169410705566</v>
+        <v>8.85169315338135</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122665405273</v>
+        <v>9.26122570037842</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G170" t="n">
-        <v>9.16997241973877</v>
+        <v>9.16997337341309</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.27235412597656</v>
+        <v>9.27235507965088</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G175" t="n">
-        <v>9.16997241973877</v>
+        <v>9.16997337341309</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G177" t="n">
-        <v>9.23451805114746</v>
+        <v>9.23451900482178</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.44836521148682</v>
       </c>
       <c r="G180" t="n">
-        <v>8.37761497497559</v>
+        <v>8.3776159286499</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G182" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.07936668395996</v>
       </c>
       <c r="G184" t="n">
-        <v>8.05043411254883</v>
+        <v>8.05043315887451</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.79225015640259</v>
+        <v>7.7922511100769</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463424682617</v>
+        <v>7.89463329315186</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.28771305084229</v>
       </c>
       <c r="G188" t="n">
-        <v>8.23516845703125</v>
+        <v>8.23516941070557</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798759460449</v>
+        <v>7.90798711776733</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G193" t="n">
-        <v>8.38429164886475</v>
+        <v>8.38429260253906</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10.3696060180664</v>
       </c>
       <c r="G204" t="n">
-        <v>9.19445610046387</v>
+        <v>9.19445514678955</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G219" t="n">
-        <v>8.38429164886475</v>
+        <v>8.38429260253906</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G220" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G221" t="n">
-        <v>8.73373031616211</v>
+        <v>8.73373126983643</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.1185855865479</v>
       </c>
       <c r="G229" t="n">
-        <v>8.97188186645508</v>
+        <v>8.97188091278076</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G234" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.71193504333496</v>
       </c>
       <c r="G235" t="n">
-        <v>8.61131477355957</v>
+        <v>8.61131572723389</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.6457271575928</v>
       </c>
       <c r="G236" t="n">
-        <v>9.43928527832031</v>
+        <v>9.439284324646</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.6507472991943</v>
       </c>
       <c r="G238" t="n">
-        <v>9.44373607635498</v>
+        <v>9.4437370300293</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.4088249206543</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1159038543701</v>
+        <v>10.1159029006958</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.9218482971191</v>
       </c>
       <c r="G243" t="n">
-        <v>9.68411445617676</v>
+        <v>9.68411350250244</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.2406415939331</v>
       </c>
       <c r="G244" t="n">
-        <v>9.96677875518799</v>
+        <v>9.9667797088623</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G246" t="n">
-        <v>10.5721769332886</v>
+        <v>10.5721759796143</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12.8019819259644</v>
       </c>
       <c r="G250" t="n">
-        <v>11.3511800765991</v>
+        <v>11.3511791229248</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G251" t="n">
-        <v>10.9883871078491</v>
+        <v>10.9883861541748</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195251464844</v>
+        <v>12.4195261001587</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858253479004</v>
+        <v>12.1858243942261</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>12.7392282485962</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2955369949341</v>
+        <v>11.2955360412598</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>12.8647365570068</v>
       </c>
       <c r="G267" t="n">
-        <v>11.4068212509155</v>
+        <v>11.4068222045898</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.2999439239502</v>
       </c>
       <c r="G268" t="n">
-        <v>10.9060344696045</v>
+        <v>10.9060354232788</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.5635137557983</v>
       </c>
       <c r="G269" t="n">
-        <v>11.1397342681885</v>
+        <v>11.1397352218628</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>12.6011667251587</v>
       </c>
       <c r="G272" t="n">
-        <v>11.1731204986572</v>
+        <v>11.1731214523315</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>13.1283073425293</v>
       </c>
       <c r="G276" t="n">
-        <v>11.6405220031738</v>
+        <v>11.6405229568481</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.1995363235474</v>
       </c>
       <c r="G278" t="n">
-        <v>10.817006111145</v>
+        <v>10.8170070648193</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.2516717910767</v>
+        <v>10.251672744751</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.3711729049683</v>
       </c>
       <c r="G285" t="n">
-        <v>10.0825185775757</v>
+        <v>10.0825176239014</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.707537651062</v>
       </c>
       <c r="G287" t="n">
-        <v>10.3807640075684</v>
+        <v>10.3807649612427</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.0213117599487</v>
       </c>
       <c r="G288" t="n">
-        <v>10.6589784622192</v>
+        <v>10.6589794158936</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651847839355</v>
+        <v>10.3651857376099</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>11.3787031173706</v>
       </c>
       <c r="G290" t="n">
-        <v>10.0891952514648</v>
+        <v>10.0891962051392</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939605712891</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>11.6372528076172</v>
       </c>
       <c r="G293" t="n">
-        <v>10.3184432983398</v>
+        <v>10.3184442520142</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.6874570846558</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3629589080811</v>
+        <v>10.3629579544067</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G297" t="n">
-        <v>9.36360931396484</v>
+        <v>9.36361026763916</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486450195312</v>
+        <v>9.45486354827881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G305" t="n">
-        <v>9.25454902648926</v>
+        <v>9.25454998016357</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G306" t="n">
-        <v>9.00749397277832</v>
+        <v>9.00749492645264</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10.1386680603027</v>
       </c>
       <c r="G307" t="n">
-        <v>8.98968887329102</v>
+        <v>8.9896879196167</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520519256592</v>
+        <v>8.96520614624023</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10.218994140625</v>
       </c>
       <c r="G310" t="n">
-        <v>9.06091117858887</v>
+        <v>9.06091213226318</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539485931396</v>
+        <v>9.08539390563965</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10.1562385559082</v>
       </c>
       <c r="G317" t="n">
-        <v>9.00526809692383</v>
+        <v>9.00526714324951</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>10.8164196014404</v>
       </c>
       <c r="G321" t="n">
-        <v>9.59063243865967</v>
+        <v>9.59063339233398</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77982044219971</v>
+        <v>9.77981948852539</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>10.0106477737427</v>
       </c>
       <c r="G332" t="n">
-        <v>8.87617683410645</v>
+        <v>8.87617588043213</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.7671594619751</v>
       </c>
       <c r="G335" t="n">
-        <v>8.66028213500977</v>
+        <v>8.66028118133545</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.2033576965332</v>
+        <v>9.20335865020752</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G344" t="n">
-        <v>8.87840175628662</v>
+        <v>8.87840270996094</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>10.0332403182983</v>
       </c>
       <c r="G345" t="n">
-        <v>8.89620780944824</v>
+        <v>8.89620876312256</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G346" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G347" t="n">
-        <v>8.87840175628662</v>
+        <v>8.87840270996094</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G353" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.80481243133545</v>
       </c>
       <c r="G354" t="n">
-        <v>8.69366836547852</v>
+        <v>8.6936674118042</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G355" t="n">
-        <v>8.86282253265381</v>
+        <v>8.86282348632812</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G357" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G361" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G362" t="n">
-        <v>8.0348539352417</v>
+        <v>8.03485298156738</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033880233765</v>
+        <v>7.99033975601196</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>8.97142791748047</v>
       </c>
       <c r="G364" t="n">
-        <v>7.95472764968872</v>
+        <v>7.95472812652588</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G366" t="n">
-        <v>7.66093349456787</v>
+        <v>7.66093301773071</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215675354004</v>
+        <v>7.73215627670288</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.88106060028076</v>
       </c>
       <c r="G372" t="n">
-        <v>7.8746018409729</v>
+        <v>7.87460136413574</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G374" t="n">
-        <v>7.32262372970581</v>
+        <v>7.32262420654297</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G376" t="n">
-        <v>7.19798278808594</v>
+        <v>7.1979832649231</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G378" t="n">
-        <v>7.18017673492432</v>
+        <v>7.18017721176147</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.07779979705811</v>
       </c>
       <c r="G380" t="n">
-        <v>7.16237115859985</v>
+        <v>7.16237163543701</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G384" t="n">
-        <v>7.19798278808594</v>
+        <v>7.1979832649231</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055463790894</v>
+        <v>7.42055511474609</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.44428825378418</v>
       </c>
       <c r="G387" t="n">
-        <v>7.48732662200928</v>
+        <v>7.48732709884644</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G389" t="n">
-        <v>7.32262372970581</v>
+        <v>7.32262420654297</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8.4242057800293</v>
       </c>
       <c r="G390" t="n">
-        <v>7.46952104568481</v>
+        <v>7.46952056884766</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390941619873</v>
+        <v>7.43390893936157</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.85679721832275</v>
+        <v>7.8567967414856</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>8.52461433410645</v>
       </c>
       <c r="G397" t="n">
-        <v>7.55854988098145</v>
+        <v>7.5585503578186</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>8.6953067779541</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70989847183228</v>
+        <v>7.70989894866943</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G405" t="n">
-        <v>7.70099544525146</v>
+        <v>7.70099496841431</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757823944092</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.5748176574707</v>
       </c>
       <c r="G411" t="n">
-        <v>7.60306406021118</v>
+        <v>7.60306358337402</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>8.53967475891113</v>
       </c>
       <c r="G412" t="n">
-        <v>7.57190418243408</v>
+        <v>7.57190370559692</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G413" t="n">
-        <v>7.50513219833374</v>
+        <v>7.50513172149658</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249744415283</v>
+        <v>7.24249792098999</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G416" t="n">
-        <v>7.26475477218628</v>
+        <v>7.26475429534912</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.15812587738037</v>
       </c>
       <c r="G417" t="n">
-        <v>7.23359441757202</v>
+        <v>7.23359489440918</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7.93220806121826</v>
       </c>
       <c r="G420" t="n">
-        <v>7.03327894210815</v>
+        <v>7.03327941894531</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.61592388153076</v>
       </c>
       <c r="G422" t="n">
-        <v>6.75283861160278</v>
+        <v>6.75283813476562</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.40004777908325</v>
       </c>
       <c r="G426" t="n">
-        <v>6.56142663955688</v>
+        <v>6.56142616271973</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.9397988319397</v>
+        <v>6.93979835510254</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857604980469</v>
+        <v>6.86857557296753</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.00751399993896</v>
       </c>
       <c r="G430" t="n">
-        <v>7.1000509262085</v>
+        <v>7.10005044937134</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591464996338</v>
+        <v>7.29591417312622</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.66538381576538</v>
+        <v>7.66538429260254</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G442" t="n">
-        <v>7.70099544525146</v>
+        <v>7.70099496841431</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491683959961</v>
+        <v>8.07491779327393</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.10195827484131</v>
       </c>
       <c r="G445" t="n">
-        <v>8.07046508789062</v>
+        <v>8.07046604156494</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.09693813323975</v>
       </c>
       <c r="G446" t="n">
-        <v>8.06601524353027</v>
+        <v>8.06601428985596</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G447" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692302703857</v>
+        <v>7.93692350387573</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.82081699371338</v>
       </c>
       <c r="G456" t="n">
-        <v>7.82118511199951</v>
+        <v>7.82118463516235</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G457" t="n">
-        <v>7.77221870422363</v>
+        <v>7.77221775054932</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.85093879699707</v>
       </c>
       <c r="G458" t="n">
-        <v>7.84789323806763</v>
+        <v>7.84789371490479</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.92122364044189</v>
       </c>
       <c r="G459" t="n">
-        <v>7.91021347045898</v>
+        <v>7.91021251678467</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.4294581413269</v>
+        <v>7.42945766448975</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.66538381576538</v>
+        <v>7.66538429260254</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G468" t="n">
-        <v>7.64312696456909</v>
+        <v>7.64312648773193</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.49354839324951</v>
       </c>
       <c r="G478" t="n">
-        <v>8.4176778793335</v>
+        <v>8.41767883300781</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.44836521148682</v>
       </c>
       <c r="G479" t="n">
-        <v>8.37761497497559</v>
+        <v>8.3776159286499</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G480" t="n">
-        <v>7.78557395935059</v>
+        <v>7.78557348251343</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757823944092</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>8.60494041442871</v>
       </c>
       <c r="G488" t="n">
-        <v>7.62977266311646</v>
+        <v>7.62977313995361</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G492" t="n">
-        <v>7.50513219833374</v>
+        <v>7.50513172149658</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G493" t="n">
-        <v>7.64312696456909</v>
+        <v>7.64312648773193</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>8.44930839538574</v>
       </c>
       <c r="G497" t="n">
-        <v>7.4917778968811</v>
+        <v>7.49177837371826</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>8.39910411834717</v>
       </c>
       <c r="G498" t="n">
-        <v>7.44726371765137</v>
+        <v>7.44726324081421</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G500" t="n">
-        <v>7.77221870422363</v>
+        <v>7.77221775054932</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>8.39910411834717</v>
       </c>
       <c r="G502" t="n">
-        <v>7.44726371765137</v>
+        <v>7.44726324081421</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>8.34889984130859</v>
       </c>
       <c r="G503" t="n">
-        <v>7.40274810791016</v>
+        <v>7.40274858474731</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.7499623298645</v>
+        <v>7.74996185302734</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G507" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.34795665740967</v>
       </c>
       <c r="G508" t="n">
-        <v>8.28858661651611</v>
+        <v>8.2885856628418</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.61403846740723</v>
       </c>
       <c r="G510" t="n">
-        <v>8.52451324462891</v>
+        <v>8.52451419830322</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670719146729</v>
+        <v>8.5067081451416</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G514" t="n">
-        <v>8.73373031616211</v>
+        <v>8.73373126983643</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805721282959</v>
+        <v>8.65805625915527</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.1813411712646</v>
       </c>
       <c r="G524" t="n">
-        <v>9.02752590179443</v>
+        <v>9.02752685546875</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G527" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G537" t="n">
-        <v>7.823410987854</v>
+        <v>7.82341051101685</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G538" t="n">
-        <v>8.0348539352417</v>
+        <v>8.03485298156738</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660755157471</v>
+        <v>7.73660659790039</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519510269165</v>
+        <v>7.54519557952881</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G545" t="n">
-        <v>7.66093349456787</v>
+        <v>7.66093301773071</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.5229377746582</v>
+        <v>7.52293825149536</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.56979656219482</v>
       </c>
       <c r="G558" t="n">
-        <v>7.59861183166504</v>
+        <v>7.5986123085022</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663900375366</v>
+        <v>7.7566385269165</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218820571899</v>
+        <v>7.75218772888184</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>8.32379913330078</v>
       </c>
       <c r="G563" t="n">
-        <v>7.38049173355103</v>
+        <v>7.38049268722534</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613433837891</v>
+        <v>7.43613481521606</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585174560547</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826681137085</v>
+        <v>7.37826633453369</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>8.43173694610596</v>
       </c>
       <c r="G568" t="n">
-        <v>7.47619819641113</v>
+        <v>7.47619867324829</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.17820739746094</v>
       </c>
       <c r="G570" t="n">
-        <v>7.25139999389648</v>
+        <v>7.25140047073364</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.03512573242188</v>
       </c>
       <c r="G571" t="n">
-        <v>7.12453365325928</v>
+        <v>7.12453317642212</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.79163789749146</v>
       </c>
       <c r="G576" t="n">
-        <v>6.90863943099976</v>
+        <v>6.9086389541626</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G578" t="n">
-        <v>6.98876571655273</v>
+        <v>6.98876523971558</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744762420654</v>
+        <v>6.85744714736938</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G585" t="n">
-        <v>7.18017673492432</v>
+        <v>7.18017721176147</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G586" t="n">
-        <v>7.48064947128296</v>
+        <v>7.4806489944458</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610383987427</v>
+        <v>7.41610431671143</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G589" t="n">
-        <v>7.48064947128296</v>
+        <v>7.4806489944458</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G590" t="n">
-        <v>7.26475477218628</v>
+        <v>7.26475429534912</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G591" t="n">
-        <v>6.98876571655273</v>
+        <v>6.98876523971558</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.06022834777832</v>
       </c>
       <c r="G599" t="n">
-        <v>7.14679098129272</v>
+        <v>7.14679145812988</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.83242416381836</v>
       </c>
       <c r="G605" t="n">
-        <v>8.71815013885498</v>
+        <v>8.7181510925293</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G607" t="n">
-        <v>8.54009246826172</v>
+        <v>8.54009342193604</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37539005279541</v>
+        <v>8.37538909912109</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.85250568389893</v>
       </c>
       <c r="G623" t="n">
-        <v>8.73595523834229</v>
+        <v>8.7359561920166</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902694702148</v>
+        <v>8.56902599334717</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G629" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G633" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G634" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.90019989013672</v>
       </c>
       <c r="G637" t="n">
-        <v>8.77824592590332</v>
+        <v>8.778244972229</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.86254692077637</v>
       </c>
       <c r="G639" t="n">
-        <v>8.74485969543457</v>
+        <v>8.74485874176025</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G640" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.71147346496582</v>
+        <v>8.7114725112915</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.2767276763916</v>
       </c>
       <c r="G643" t="n">
-        <v>9.11210155487061</v>
+        <v>9.11210250854492</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G644" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009822845459</v>
+        <v>9.25009727478027</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.4649925231934</v>
       </c>
       <c r="G647" t="n">
-        <v>9.27903270721436</v>
+        <v>9.27903175354004</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>10.0608520507812</v>
       </c>
       <c r="G649" t="n">
-        <v>8.92069149017334</v>
+        <v>8.92069053649902</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>11.401294708252</v>
       </c>
       <c r="G658" t="n">
-        <v>10.1092262268066</v>
+        <v>10.109227180481</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G660" t="n">
-        <v>9.84659099578857</v>
+        <v>9.84659194946289</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G667" t="n">
-        <v>9.87107467651367</v>
+        <v>9.87107372283936</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>11.200478553772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.93116760253906</v>
+        <v>9.93116855621338</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>11.5167636871338</v>
       </c>
       <c r="G675" t="n">
-        <v>10.2116088867188</v>
+        <v>10.2116098403931</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939605712891</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>11.3711729049683</v>
       </c>
       <c r="G679" t="n">
-        <v>10.0825185775757</v>
+        <v>10.0825176239014</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>11.4665603637695</v>
       </c>
       <c r="G680" t="n">
-        <v>10.1670961380005</v>
+        <v>10.1670951843262</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>11.9259252548218</v>
       </c>
       <c r="G689" t="n">
-        <v>10.5744018554688</v>
+        <v>10.5744028091431</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>12.0238227844238</v>
       </c>
       <c r="G696" t="n">
-        <v>10.661205291748</v>
+        <v>10.6612062454224</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>13.233736038208</v>
       </c>
       <c r="G700" t="n">
-        <v>11.7340040206909</v>
+        <v>11.7340030670166</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856666564941</v>
+        <v>12.0856676101685</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>12.7618188858032</v>
       </c>
       <c r="G709" t="n">
-        <v>11.3155670166016</v>
+        <v>11.3155660629272</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395774841309</v>
+        <v>11.0395765304565</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>12.7065954208374</v>
       </c>
       <c r="G712" t="n">
-        <v>11.2666025161743</v>
+        <v>11.2666015625</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G719" t="n">
-        <v>10.5499200820923</v>
+        <v>10.549919128418</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G720" t="n">
-        <v>10.5721769332886</v>
+        <v>10.5721759796143</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G722" t="n">
-        <v>10.5721769332886</v>
+        <v>10.5721759796143</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006381988525</v>
+        <v>10.3006391525269</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>11.1251735687256</v>
       </c>
       <c r="G731" t="n">
-        <v>9.8643970489502</v>
+        <v>9.86439800262451</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G736" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G737" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G738" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889585494995</v>
+        <v>7.77889633178711</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>9.65169143676758</v>
       </c>
       <c r="G742" t="n">
-        <v>8.55789947509766</v>
+        <v>8.55790042877197</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>10.0307302474976</v>
       </c>
       <c r="G748" t="n">
-        <v>8.89398288726807</v>
+        <v>8.89398384094238</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G749" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>9.33540630340576</v>
       </c>
       <c r="G753" t="n">
-        <v>8.27745819091797</v>
+        <v>8.27745723724365</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466474533081</v>
+        <v>7.91466569900513</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.81228160858154</v>
+        <v>7.8122820854187</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>8.12800407409668</v>
       </c>
       <c r="G761" t="n">
-        <v>7.20688581466675</v>
+        <v>7.20688629150391</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>8.19577884674072</v>
       </c>
       <c r="G763" t="n">
-        <v>7.26698017120361</v>
+        <v>7.26698064804077</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096927642822</v>
+        <v>8.39096832275391</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>9.71193504333496</v>
       </c>
       <c r="G780" t="n">
-        <v>8.61131477355957</v>
+        <v>8.61131572723389</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G782" t="n">
-        <v>8.86282253265381</v>
+        <v>8.86282348632812</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>10.4298496246338</v>
       </c>
       <c r="G789" t="n">
-        <v>9.2478723526001</v>
+        <v>9.24787139892578</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>9.79477119445801</v>
       </c>
       <c r="G790" t="n">
-        <v>8.68476390838623</v>
+        <v>8.68476486206055</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>9.75711917877197</v>
       </c>
       <c r="G791" t="n">
-        <v>8.6513786315918</v>
+        <v>8.65137958526611</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>10.7963380813599</v>
       </c>
       <c r="G797" t="n">
-        <v>9.57282638549805</v>
+        <v>9.57282733917236</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>10.6557683944702</v>
       </c>
       <c r="G800" t="n">
-        <v>9.44818782806396</v>
+        <v>9.44818878173828</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>10.6833801269531</v>
       </c>
       <c r="G801" t="n">
-        <v>9.47267055511475</v>
+        <v>9.47266960144043</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>10.8440322875977</v>
       </c>
       <c r="G803" t="n">
-        <v>9.61511707305908</v>
+        <v>9.61511611938477</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>11.5167636871338</v>
       </c>
       <c r="G807" t="n">
-        <v>10.2116088867188</v>
+        <v>10.2116098403931</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.3150053024292</v>
       </c>
       <c r="G815" t="n">
-        <v>10.9193897247314</v>
+        <v>10.9193887710571</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>12.2145967483521</v>
       </c>
       <c r="G817" t="n">
-        <v>10.8303604125977</v>
+        <v>10.8303594589233</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371957778931</v>
+        <v>10.9371948242188</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G819" t="n">
-        <v>10.9883871078491</v>
+        <v>10.9883861541748</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>11.5970897674561</v>
       </c>
       <c r="G821" t="n">
-        <v>10.2828321456909</v>
+        <v>10.2828330993652</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147802352905</v>
+        <v>10.8147792816162</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G842" t="n">
-        <v>10.5499200820923</v>
+        <v>10.549919128418</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>11.8154773712158</v>
       </c>
       <c r="G843" t="n">
-        <v>10.4764719009399</v>
+        <v>10.4764709472656</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>11.3912544250488</v>
       </c>
       <c r="G844" t="n">
-        <v>10.1003246307373</v>
+        <v>10.100323677063</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>10.977071762085</v>
       </c>
       <c r="G848" t="n">
-        <v>9.73307800292969</v>
+        <v>9.733078956604</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G851" t="n">
-        <v>9.33912658691406</v>
+        <v>9.33912754058838</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>10.1411781311035</v>
       </c>
       <c r="G852" t="n">
-        <v>8.99191379547119</v>
+        <v>8.99191474914551</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>10.4072589874268</v>
       </c>
       <c r="G856" t="n">
-        <v>9.22784233093262</v>
+        <v>9.2278413772583</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G858" t="n">
-        <v>9.27012920379639</v>
+        <v>9.2701301574707</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>10.5101757049561</v>
       </c>
       <c r="G860" t="n">
-        <v>9.31909561157227</v>
+        <v>9.31909465789795</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G861" t="n">
-        <v>9.25232315063477</v>
+        <v>9.25232410430908</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G871" t="n">
-        <v>9.07203960418701</v>
+        <v>9.07204055786133</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G876" t="n">
-        <v>9.23451805114746</v>
+        <v>9.23451900482178</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G877" t="n">
-        <v>9.33912658691406</v>
+        <v>9.33912754058838</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G878" t="n">
-        <v>9.27012920379639</v>
+        <v>9.2701301574707</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>10.9218482971191</v>
       </c>
       <c r="G886" t="n">
-        <v>9.68411445617676</v>
+        <v>9.68411350250244</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0498676300049</v>
       </c>
       <c r="G887" t="n">
-        <v>9.79762554168701</v>
+        <v>9.7976245880127</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>11.2130298614502</v>
       </c>
       <c r="G894" t="n">
-        <v>9.94229698181152</v>
+        <v>9.94229602813721</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070003509521</v>
+        <v>10.1070013046265</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>11.2381324768066</v>
       </c>
       <c r="G899" t="n">
-        <v>9.96455478668213</v>
+        <v>9.96455574035645</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.4715795516968</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1715459823608</v>
+        <v>10.1715469360352</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>11.1603164672852</v>
       </c>
       <c r="G901" t="n">
-        <v>9.89555740356445</v>
+        <v>9.89555835723877</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G910" t="n">
-        <v>9.75088500976562</v>
+        <v>9.75088596343994</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.1829080581665</v>
       </c>
       <c r="G912" t="n">
-        <v>9.91558837890625</v>
+        <v>9.91558933258057</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G919" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>9.84497547149658</v>
       </c>
       <c r="G921" t="n">
-        <v>8.72927951812744</v>
+        <v>8.72927856445312</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.4474220275879</v>
       </c>
       <c r="G925" t="n">
-        <v>9.26345348358154</v>
+        <v>9.26345252990723</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>10.7586851119995</v>
       </c>
       <c r="G930" t="n">
-        <v>9.53944110870361</v>
+        <v>9.53944206237793</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.9067869186401</v>
       </c>
       <c r="G933" t="n">
-        <v>9.6707592010498</v>
+        <v>9.67076015472412</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>11.4665603637695</v>
       </c>
       <c r="G939" t="n">
-        <v>10.1670961380005</v>
+        <v>10.1670951843262</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403865814209</v>
+        <v>10.1403875350952</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230537414551</v>
+        <v>10.4230527877808</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>11.2155408859253</v>
       </c>
       <c r="G944" t="n">
-        <v>9.94452285766602</v>
+        <v>9.94452381134033</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G946" t="n">
-        <v>9.87107467651367</v>
+        <v>9.87107372283936</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G947" t="n">
-        <v>9.84659099578857</v>
+        <v>9.84659194946289</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392574310303</v>
+        <v>9.56392478942871</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G950" t="n">
-        <v>9.36360931396484</v>
+        <v>9.36361026763916</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>10.0332403182983</v>
       </c>
       <c r="G956" t="n">
-        <v>8.89620780944824</v>
+        <v>8.89620876312256</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00971984863281</v>
+        <v>9.00972080230713</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G961" t="n">
-        <v>9.16997241973877</v>
+        <v>9.16997337341309</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>10.6557683944702</v>
       </c>
       <c r="G971" t="n">
-        <v>9.44818782806396</v>
+        <v>9.44818878173828</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>10.3219118118286</v>
       </c>
       <c r="G975" t="n">
-        <v>9.15216541290283</v>
+        <v>9.15216636657715</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>11.1904392242432</v>
       </c>
       <c r="G979" t="n">
-        <v>9.92226696014404</v>
+        <v>9.92226600646973</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>11.2306022644043</v>
       </c>
       <c r="G981" t="n">
-        <v>9.95787811279297</v>
+        <v>9.95787715911865</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>10.8164196014404</v>
       </c>
       <c r="G993" t="n">
-        <v>9.59063243865967</v>
+        <v>9.59063339233398</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>10.7135019302368</v>
       </c>
       <c r="G996" t="n">
-        <v>9.4993782043457</v>
+        <v>9.49937915802002</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G997" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G998" t="n">
-        <v>9.07203960418701</v>
+        <v>9.07204055786133</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.25232315063477</v>
+        <v>9.25232410430908</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>10.427339553833</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.24564647674561</v>
+        <v>9.24564552307129</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G1004" t="n">
-        <v>9.36360931396484</v>
+        <v>9.36361026763916</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G1014" t="n">
-        <v>9.75088500976562</v>
+        <v>9.75088596343994</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>10.934398651123</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.6952428817749</v>
+        <v>9.69524192810059</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G1016" t="n">
-        <v>9.75088500976562</v>
+        <v>9.75088596343994</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>11.1728668212891</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.9066858291626</v>
+        <v>9.90668487548828</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>11.1251735687256</v>
       </c>
       <c r="G1028" t="n">
-        <v>9.8643970489502</v>
+        <v>9.86439800262451</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G1031" t="n">
-        <v>9.25454902648926</v>
+        <v>9.25454998016357</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>9.63411903381348</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.54231834411621</v>
+        <v>8.54231929779053</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>9.55630302429199</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.47332096099854</v>
+        <v>8.47332191467285</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>9.41573238372803</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.34868049621582</v>
+        <v>8.34868144989014</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.4354829788208</v>
+        <v>8.43548393249512</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>9.42577266693115</v>
       </c>
       <c r="G1052" t="n">
-        <v>8.35758399963379</v>
+        <v>8.35758304595947</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657657623291</v>
+        <v>7.71657609939575</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754774093628</v>
+        <v>7.62754726409912</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585174560547</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.89613008499146</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.34126901626587</v>
+        <v>4.34126949310303</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.95009994506836</v>
       </c>
       <c r="G1068" t="n">
-        <v>4.38912296295166</v>
+        <v>4.3891224861145</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.88991022109985</v>
+        <v>4.8899097442627</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>5.8261570930481</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.1658992767334</v>
+        <v>5.16589975357056</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.06713485717773</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.37956809997559</v>
+        <v>5.37956762313843</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386259078979</v>
+        <v>5.28386211395264</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950519561768</v>
+        <v>5.33950567245483</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.29276561737061</v>
+        <v>5.29276514053345</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>5.28395509719849</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.68514347076416</v>
+        <v>4.685142993927</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445537567139</v>
+        <v>4.95445489883423</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>5.73328018188477</v>
       </c>
       <c r="G1100" t="n">
-        <v>5.08354806900024</v>
+        <v>5.08354759216309</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>5.62032079696655</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.98338937759399</v>
+        <v>4.98338985443115</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470794677734</v>
+        <v>5.11470746994019</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.92329549789429</v>
+        <v>4.92329597473145</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>5.59521913528442</v>
       </c>
       <c r="G1108" t="n">
-        <v>4.96113300323486</v>
+        <v>4.96113252639771</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.79800081253052</v>
+        <v>4.79800033569336</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>5.46217918395996</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.865074634552</v>
+        <v>4.86507511138916</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>5.30905723571777</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.72869110107422</v>
+        <v>4.72869157791138</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>5.79854488372803</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.16466999053955</v>
+        <v>5.16467046737671</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>6.46876621246338</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.76162576675415</v>
+        <v>5.76162528991699</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>6.59176588058472</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.87117910385132</v>
+        <v>5.87117958068848</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>6.41354179382324</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.71243762969971</v>
+        <v>5.71243810653687</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>5.99182987213135</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33682584762573</v>
+        <v>5.33682632446289</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>5.98680877685547</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.3323540687561</v>
+        <v>5.33235359191895</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.0841817855835</v>
+        <v>5.08418226242065</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>5.61530113220215</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.00145816802979</v>
+        <v>5.00145769119263</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.97686338424683</v>
+        <v>4.97686290740967</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>5.68558597564697</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.06405973434448</v>
+        <v>5.06405925750732</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>5.27642488479614</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.69962596893311</v>
+        <v>4.69962644577026</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>5.28897619247437</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.71080541610718</v>
+        <v>4.71080589294434</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>5.36679220199585</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.78011465072632</v>
+        <v>4.78011512756348</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.47724008560181</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.87848949432373</v>
+        <v>4.87848901748657</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>4.92123222351074</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.38326215744019</v>
+        <v>4.38326168060303</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.57357120513916</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.07360553741455</v>
+        <v>4.07360601425171</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.96892595291138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.42574214935303</v>
+        <v>4.42574167251587</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1174" t="n">
-        <v>4.34189987182617</v>
+        <v>4.34190034866333</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.66895818710327</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.15856552124023</v>
+        <v>4.15856599807739</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.50579500198364</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.01323843002319</v>
+        <v>4.01323890686035</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.39032697677612</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.91039347648621</v>
+        <v>3.91039323806763</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.29242897033691</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.82319736480713</v>
+        <v>3.82319688796997</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.19327592849731</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.73488283157349</v>
+        <v>3.73488306999207</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.07906293869019</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.63315534591675</v>
+        <v>3.63315558433533</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.22465419769287</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.76283097267151</v>
+        <v>3.76283121109009</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.56321811676025</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.17370080947876</v>
+        <v>3.17370057106018</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.86444091796875</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.4419949054718</v>
+        <v>3.44199514389038</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.79415607452393</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.3793933391571</v>
+        <v>3.37939357757568</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.65609502792358</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.25642466545105</v>
+        <v>3.25642490386963</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>3.59585094451904</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.20276641845703</v>
+        <v>3.20276618003845</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.62597298622131</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.22959566116333</v>
+        <v>3.22959542274475</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.68496203422546</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.28213620185852</v>
+        <v>3.28213596343994</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>3.78411507606506</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.37045001983643</v>
+        <v>3.370450258255</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.6940598487854</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.18092346191406</v>
+        <v>4.1809229850769</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>4.89487504959106</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.35978651046753</v>
+        <v>4.35978603363037</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.27706241607666</v>
+        <v>4.2770619392395</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.47157573699951</v>
+        <v>4.47157526016235</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>5.42201614379883</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.8293023109436</v>
+        <v>4.82930183410645</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>5.30654716491699</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.72645568847656</v>
+        <v>4.72645616531372</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>5.1333441734314</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.5721869468689</v>
+        <v>4.57218647003174</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.62584495544434</v>
+        <v>4.62584447860718</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>5.35675096511841</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.77117109298706</v>
+        <v>4.77117156982422</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>5.37683200836182</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.78905773162842</v>
+        <v>4.78905725479126</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>5.46719884872437</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.86954593658447</v>
+        <v>4.86954545974731</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.86060285568237</v>
+        <v>4.86060237884521</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>5.82364702224731</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.18702840805054</v>
+        <v>5.18702793121338</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>6.17256307601929</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.49780178070068</v>
+        <v>5.49780225753784</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>6.10729789733887</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.43967151641846</v>
+        <v>5.4396710395813</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>6.08721685409546</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.42178583145142</v>
+        <v>5.42178535461426</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>6.00689077377319</v>
       </c>
       <c r="G1279" t="n">
-        <v>5.35024070739746</v>
+        <v>5.3502402305603</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.85878896713257</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.21832895278931</v>
+        <v>5.21832847595215</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>5.34169006347656</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.75775718688965</v>
+        <v>4.75775671005249</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>5.59019899368286</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.9790997505188</v>
+        <v>4.97910022735596</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>5.98178911209106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.32788276672363</v>
+        <v>5.32788324356079</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>6.55160188674927</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.83540630340576</v>
+        <v>5.8354058265686</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>6.3457670211792</v>
       </c>
       <c r="G1303" t="n">
-        <v>5.65207195281982</v>
+        <v>5.65207242965698</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>6.35078716278076</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.65654373168945</v>
+        <v>5.65654325485229</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>6.40852212905884</v>
       </c>
       <c r="G1305" t="n">
-        <v>5.70796728134155</v>
+        <v>5.70796680450439</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>6.63192892074585</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.90695142745972</v>
+        <v>5.90695190429688</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>6.00940084457397</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.35247659683228</v>
+        <v>5.35247611999512</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.0841817855835</v>
+        <v>5.08418226242065</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1312" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>5.91652393341064</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.26975250244141</v>
+        <v>5.26975202560425</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>6.07215595245361</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.40837097167969</v>
+        <v>5.40837144851685</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>6.07717609405518</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.41284275054932</v>
+        <v>5.41284227371216</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>6.12486982345581</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.45532274246216</v>
+        <v>5.455322265625</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>5.97174787521362</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.31893920898438</v>
+        <v>5.31893968582153</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.31670379638672</v>
+        <v>5.31670331954956</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>5.69060611724854</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.06853055953979</v>
+        <v>5.06853103637695</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>5.87887096405029</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.23621559143066</v>
+        <v>5.23621511459351</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>5.83870792388916</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.20044231414795</v>
+        <v>5.20044279098511</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.97686338424683</v>
+        <v>4.97686290740967</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.94556283950806</v>
+        <v>4.94556331634521</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.87855911254883</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.34525346755981</v>
+        <v>4.34525394439697</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.82333517074585</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.29606676101685</v>
+        <v>4.29606628417969</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>5.06054782867432</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.50734806060791</v>
+        <v>4.50734853744507</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.69068288803101</v>
+        <v>4.69068336486816</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>5.1383638381958</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.57665729522705</v>
+        <v>4.57665777206421</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>5.12832307815552</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.56771421432495</v>
+        <v>4.56771469116211</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>5.11828184127808</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.55877065658569</v>
+        <v>4.55877113342285</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>5.3793420791626</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.79129266738892</v>
+        <v>4.79129314422607</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>5.56760692596436</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.95897769927979</v>
+        <v>4.95897722244263</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.72422027587891</v>
+        <v>4.72421979904175</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.72422027587891</v>
+        <v>4.72421979904175</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>5.29901599884033</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.71974754333496</v>
+        <v>4.71974802017212</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1396" t="n">
-        <v>4.56324338912964</v>
+        <v>4.56324291229248</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>5.22873115539551</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.65714597702026</v>
+        <v>4.65714645385742</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>5.21868991851807</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.64820241928101</v>
+        <v>4.64820289611816</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.90617084503174</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.3698468208313</v>
+        <v>4.36984729766846</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.97143602371216</v>
       </c>
       <c r="G1403" t="n">
-        <v>4.42797756195068</v>
+        <v>4.42797803878784</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>4.88483476638794</v>
       </c>
       <c r="G1405" t="n">
-        <v>4.35084295272827</v>
+        <v>4.35084342956543</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.90240621566772</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.36649417877197</v>
+        <v>4.36649370193481</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.75681495666504</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.23681783676147</v>
+        <v>4.23681831359863</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1417" t="n">
-        <v>4.5297064781189</v>
+        <v>4.52970600128174</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>4.91119194030762</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.37431955337524</v>
+        <v>4.37431907653809</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.92499780654907</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.38661575317383</v>
+        <v>4.38661623001099</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.56324338912964</v>
+        <v>4.56324291229248</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>5.16597604751587</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.60125160217285</v>
+        <v>4.60125112533569</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>4.98147678375244</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.43692064285278</v>
+        <v>4.43692111968994</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.27706241607666</v>
+        <v>4.2770619392395</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.47157573699951</v>
+        <v>4.47157526016235</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>4.96139478683472</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41903400421143</v>
+        <v>4.41903448104858</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.01662015914917</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.46822214126587</v>
+        <v>4.46822261810303</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.62584495544434</v>
+        <v>4.62584447860718</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.5297064781189</v>
+        <v>4.52970600128174</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.99151802062988</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.4458646774292</v>
+        <v>4.44586420059204</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>4.91244697570801</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.37543725967407</v>
+        <v>4.37543678283691</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>5.07058906555176</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.51629161834717</v>
+        <v>4.51629209518433</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>5.55003595352173</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.9433274269104</v>
+        <v>4.94332695007324</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.69068288803101</v>
+        <v>4.69068336486816</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.79800081253052</v>
+        <v>4.79800033569336</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.91202640533447</v>
+        <v>4.91202592849731</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.94556283950806</v>
+        <v>4.94556331634521</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.87353897094727</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.3407826423645</v>
+        <v>4.34078216552734</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.81203889846802</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.28600549697876</v>
+        <v>4.2860050201416</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.34189987182617</v>
+        <v>4.34190034866333</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.39220523834229</v>
+        <v>4.39220476150513</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>4.46563196182251</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.97746610641479</v>
+        <v>3.97746634483337</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>4.50328493118286</v>
       </c>
       <c r="G1504" t="n">
-        <v>4.0110034942627</v>
+        <v>4.01100301742554</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>4.42170381546021</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.93834018707275</v>
+        <v>3.93833994865417</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>4.59365177154541</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.09149169921875</v>
+        <v>4.09149122238159</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>4.56729507446289</v>
       </c>
       <c r="G1511" t="n">
-        <v>4.06801605224609</v>
+        <v>4.06801557540894</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>4.41040802001953</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.92827916145325</v>
+        <v>3.92827892303467</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.4455509185791</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.95958018302917</v>
+        <v>3.95958042144775</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>4.37275505065918</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.89474248886108</v>
+        <v>3.89474201202393</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.55097913742065</v>
       </c>
       <c r="G1522" t="n">
-        <v>4.05348348617554</v>
+        <v>4.0534839630127</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>4.78317213058472</v>
       </c>
       <c r="G1527" t="n">
-        <v>4.26029443740845</v>
+        <v>4.26029396057129</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>4.91495704650879</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.37767267227173</v>
+        <v>4.37767314910889</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.03042602539062</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.48051929473877</v>
+        <v>4.48051881790161</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.39220523834229</v>
+        <v>4.39220476150513</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>5.01410913467407</v>
       </c>
       <c r="G1541" t="n">
-        <v>4.46598625183105</v>
+        <v>4.4659857749939</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>2.99591493606567</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.66841292381287</v>
+        <v>2.66841316223145</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3.02854704856873</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.69747805595398</v>
+        <v>2.6974778175354</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.8616189956665</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.54879784584045</v>
+        <v>2.54879760742188</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.56221222877502</v>
+        <v>2.5622124671936</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.51521301269531</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.24025964736938</v>
+        <v>2.24025940895081</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.56165099143982</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.28162121772766</v>
+        <v>2.28162097930908</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.56792688369751</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.28721117973328</v>
+        <v>2.2872109413147</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>2.37715196609497</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.11729097366333</v>
+        <v>2.11729073524475</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.58047795295715</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.29838991165161</v>
+        <v>2.29839015007019</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>2.46450710296631</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.19509673118591</v>
+        <v>2.19509649276733</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>2.67335510253906</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.38111400604248</v>
+        <v>2.38111424446106</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>2.86287403106689</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.54991555213928</v>
+        <v>2.54991579055786</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.56221222877502</v>
+        <v>2.5622124671936</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>2.93943500518799</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.61810731887817</v>
+        <v>2.61810708045959</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>2.87919092178345</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.564448595047</v>
+        <v>2.56444883346558</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>2.84404802322388</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.53314781188965</v>
+        <v>2.53314757347107</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.77878308296204</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.47501730918884</v>
+        <v>2.47501707077026</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>2.80262994766235</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.49625730514526</v>
+        <v>2.49625706672668</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>2.79384398460388</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.48843169212341</v>
+        <v>2.48843145370483</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2.75744605064392</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.45601272583008</v>
+        <v>2.4560124874115</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.43700885772705</v>
+        <v>2.43700909614563</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.84028291702271</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.52979397773743</v>
+        <v>2.52979421615601</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>2.92437410354614</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.6046929359436</v>
+        <v>2.60469269752502</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.43700885772705</v>
+        <v>2.43700909614563</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.48509001731873</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.21342945098877</v>
+        <v>2.21342968940735</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>2.53780388832092</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.26038098335266</v>
+        <v>2.26038074493408</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>2.68841600418091</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.39452886581421</v>
+        <v>2.39452862739563</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.90680289268494</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.58904242515564</v>
+        <v>2.58904218673706</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>2.97517991065979</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.6499445438385</v>
+        <v>2.64994478225708</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>2.72426104545593</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.42645525932312</v>
+        <v>2.4264554977417</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>2.37423992156982</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.11469721794128</v>
+        <v>2.11469697952271</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.96649694442749</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.75152707099915</v>
+        <v>1.75152695178986</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>2.01657509803772</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.79613077640533</v>
+        <v>1.79613089561462</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>2.21557092666626</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.97337329387665</v>
+        <v>1.97337317466736</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>1.73798203468323</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.54799246788025</v>
+        <v>1.54799258708954</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.59776198863983</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.42310070991516</v>
+        <v>1.42310082912445</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>1.24932205677032</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.11275100708008</v>
+        <v>1.11275088787079</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98913478851318</v>
+        <v>2.98913502693176</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.73594284057617</v>
+        <v>1.73594272136688</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.985986948013306</v>
+        <v>0.98598700761795</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.04209995269775</v>
+        <v>1.04210007190704</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.730360686779022</v>
+        <v>0.730360746383667</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>0.71340000629425</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.635413825511932</v>
+        <v>0.635413885116577</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.659106075763702</v>
+        <v>0.659106016159058</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.692061364650726</v>
+        <v>0.692061305046082</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.751737177371979</v>
+        <v>0.751737117767334</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>0.833599984645844</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.74247407913208</v>
+        <v>0.742474019527435</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>0.821799993515015</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.731963992118835</v>
+        <v>0.731963932514191</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>0.762199997901917</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.678879261016846</v>
+        <v>0.678879201412201</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.716400027275085</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.638085901737213</v>
+        <v>0.638085961341858</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>0.674600005149841</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.60085529088974</v>
+        <v>0.600855350494385</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>0.697399973869324</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.621162891387939</v>
+        <v>0.621162831783295</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>0.683200001716614</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.608515202999115</v>
+        <v>0.60851514339447</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>0.662199974060059</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589810848236084</v>
+        <v>0.589810788631439</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>0.64300000667572</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.572709739208221</v>
+        <v>0.572709679603577</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.540645062923431</v>
+        <v>0.540645122528076</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>0.584800004959106</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.520871937274933</v>
+        <v>0.520871877670288</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.59280002117157</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.527997374534607</v>
+        <v>0.527997434139252</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>0.597199976444244</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.531916320323944</v>
+        <v>0.531916379928589</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>0.637600004673004</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.567900002002716</v>
+        <v>0.567900061607361</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.72759997844696</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.648061513900757</v>
+        <v>0.648061573505402</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.620806694030762</v>
+        <v>0.620806634426117</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.658215343952179</v>
+        <v>0.658215403556824</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>0.758199989795685</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.675316452980042</v>
+        <v>0.675316512584686</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>0.828599989414215</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.738020598888397</v>
+        <v>0.738020658493042</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>0.958599984645844</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.853809535503387</v>
+        <v>0.853809475898743</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.8764328956604</v>
+        <v>0.876432955265045</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.87376081943512</v>
+        <v>0.873760879039764</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.882667660713196</v>
+        <v>0.882667720317841</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.919185698032379</v>
+        <v>0.919185638427734</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.957485198974609</v>
+        <v>0.957485139369965</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>1.09650003910065</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.976634860038757</v>
+        <v>0.976634919643402</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>1.03250002861023</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.919631063938141</v>
+        <v>0.919631123542786</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.921857714653015</v>
+        <v>0.92185777425766</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>1.04649996757507</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.932100653648376</v>
+        <v>0.932100594043732</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.926311135292053</v>
+        <v>0.926311194896698</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>1.04750001430511</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.93299126625061</v>
+        <v>0.932991325855255</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.912950873374939</v>
+        <v>0.912950932979584</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>1.01950001716614</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.908052146434784</v>
+        <v>0.908052206039429</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>1.04449999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.93031919002533</v>
+        <v>0.930319249629974</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>1.00650000572205</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.896473228931427</v>
+        <v>0.896473288536072</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.04949998855591</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.934772729873657</v>
+        <v>0.934772670269012</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.10950005054474</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.988213777542114</v>
+        <v>0.988213717937469</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.977970957756042</v>
+        <v>0.977970898151398</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>1.12750005722046</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.00424599647522</v>
+        <v>1.00424611568451</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.05456960201263</v>
+        <v>1.05456972122192</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>1.31149995326996</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.16813182830811</v>
+        <v>1.16813170909882</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.25141072273254</v>
+        <v>1.25141084194183</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.2309250831604</v>
+        <v>1.23092496395111</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.21845555305481</v>
+        <v>1.21845543384552</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.25586414337158</v>
+        <v>1.25586426258087</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.24962949752808</v>
+        <v>1.24962937831879</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.3146493434906</v>
+        <v>1.31464922428131</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.35116744041443</v>
+        <v>1.35116732120514</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.53450000286102</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.36675429344177</v>
+        <v>1.36675441265106</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.31643068790436</v>
+        <v>1.31643080711365</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.35749995708466</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.20910334587097</v>
+        <v>1.20910322666168</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>1.26549994945526</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.12716031074524</v>
+        <v>1.12716042995453</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>1.14049994945526</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.01582491397858</v>
+        <v>1.01582479476929</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>1.23450005054474</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.09954929351807</v>
+        <v>1.09954917430878</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.32550001144409</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.18060147762299</v>
+        <v>1.1806013584137</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.14007532596588</v>
+        <v>1.14007520675659</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23181581497192</v>
+        <v>1.23181569576263</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>1.25049996376038</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.11380004882812</v>
+        <v>1.11380016803741</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.15076351165771</v>
+        <v>1.150763630867</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.13473129272461</v>
+        <v>1.13473117351532</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.12048017978668</v>
+        <v>1.12048029899597</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.15788900852203</v>
+        <v>1.15788888931274</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.25750005245209</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.1200350522995</v>
+        <v>1.12003493309021</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.12226164340973</v>
+        <v>1.12226152420044</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.07416474819183</v>
+        <v>1.07416462898254</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.13473129272461</v>
+        <v>1.13473117351532</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>1.25450003147125</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.11736297607422</v>
+        <v>1.11736285686493</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.08663427829742</v>
+        <v>1.08663439750671</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>1.16250002384186</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.03541994094849</v>
+        <v>1.03542006015778</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.04833495616913</v>
+        <v>1.04833483695984</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.07772743701935</v>
+        <v>1.07772755622864</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.30039846897125</v>
+        <v>1.30039834976196</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.3110865354538</v>
+        <v>1.31108665466309</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.32266557216644</v>
+        <v>1.32266545295715</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>1.43949997425079</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.28213942050934</v>
+        <v>1.28213930130005</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>1.43250000476837</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.27590453624725</v>
+        <v>1.27590465545654</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.30039846897125</v>
+        <v>1.30039834976196</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.328009724617</v>
+        <v>1.32800960540771</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1930" t="n">
-        <v>1.29683566093445</v>
+        <v>1.29683554172516</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.29327285289764</v>
+        <v>1.29327297210693</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.25586414337158</v>
+        <v>1.25586426258087</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.24339461326599</v>
+        <v>1.24339473247528</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.30485188961029</v>
+        <v>1.304851770401</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.33869779109955</v>
+        <v>1.33869791030884</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.32266557216644</v>
+        <v>1.32266545295715</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1951" t="n">
-        <v>1.4019364118576</v>
+        <v>1.40193629264832</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.328009724617</v>
+        <v>1.32800960540771</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.37566113471985</v>
+        <v>1.37566125392914</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.41975009441376</v>
+        <v>1.41974997520447</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>1.60950005054474</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.43355572223663</v>
+        <v>1.43355560302734</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.40104568004608</v>
+        <v>1.40104556083679</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>1.46249997615814</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.30262517929077</v>
+        <v>1.30262506008148</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.27679538726807</v>
+        <v>1.27679526805878</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.29683566093445</v>
+        <v>1.29683554172516</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>1.41849994659424</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.26343500614166</v>
+        <v>1.26343488693237</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>1.5275000333786</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.36051964759827</v>
+        <v>1.36051952838898</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52031,7 +52031,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.37566113471985</v>
+        <v>1.37566125392914</v>
       </c>
       <c r="H1987" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.29015564918518</v>
+        <v>1.29015552997589</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.41449999809265</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.25987231731415</v>
+        <v>1.25987219810486</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.23626923561096</v>
+        <v>1.23626911640167</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.23805046081543</v>
+        <v>1.23805058002472</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>1.44749999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>1.28926479816437</v>
+        <v>1.28926491737366</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>1.46150004863739</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.30173444747925</v>
+        <v>1.30173456668854</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.24784803390503</v>
+        <v>1.24784815311432</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.24784803390503</v>
+        <v>1.24784815311432</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.22647166252136</v>
+        <v>1.22647154331207</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>1.42050004005432</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.26521635055542</v>
+        <v>1.26521646976471</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.29015564918518</v>
+        <v>1.29015552997589</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>1.44649994373322</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.28837406635284</v>
+        <v>1.28837418556213</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.3208841085434</v>
+        <v>1.32088422775269</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.30930531024933</v>
+        <v>1.30930519104004</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.32622814178467</v>
+        <v>1.32622826099396</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>1.50650000572205</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.34181523323059</v>
+        <v>1.3418151140213</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.27679538726807</v>
+        <v>1.27679526805878</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31643068790436</v>
+        <v>1.31643080711365</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.34315121173859</v>
+        <v>1.34315133094788</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>1.375</v>
       </c>
       <c r="G2070" t="n">
-        <v>1.22469019889832</v>
+        <v>1.2246903181076</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>1.38100004196167</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.23003435134888</v>
+        <v>1.23003447055817</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.32979094982147</v>
+        <v>1.32979106903076</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>1.82149994373322</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.6223806142807</v>
+        <v>1.62238049507141</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.72347319126129</v>
+        <v>1.723473072052</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>1.97650003433228</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.76043665409088</v>
+        <v>1.76043653488159</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.87488961219788</v>
+        <v>1.87488949298859</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.88112413883209</v>
+        <v>1.88112425804138</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>2.08699989318848</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.85885715484619</v>
+        <v>1.8588570356369</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.91318881511688</v>
+        <v>1.91318893432617</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.98889696598053</v>
+        <v>1.98889708518982</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2104" t="n">
-        <v>2.00760126113892</v>
+        <v>2.0076014995575</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G2105" t="n">
-        <v>2.00849199295044</v>
+        <v>2.00849223136902</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.06994915008545</v>
+        <v>2.06994891166687</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>2.3970000743866</v>
       </c>
       <c r="G2109" t="n">
-        <v>2.13496923446655</v>
+        <v>2.13496899604797</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2110" t="n">
-        <v>2.08419990539551</v>
+        <v>2.08420014381409</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.99513185024261</v>
+        <v>1.99513173103333</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.94258141517639</v>
+        <v>1.94258153438568</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.97197389602661</v>
+        <v>1.9719740152359</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.9523788690567</v>
+        <v>1.95237898826599</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.94080007076263</v>
+        <v>1.94079983234406</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2126" t="n">
-        <v>1.91318881511688</v>
+        <v>1.91318893432617</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55697,7 +55697,7 @@
         <v>2.13100004196167</v>
       </c>
       <c r="G2128" t="n">
-        <v>1.8980473279953</v>
+        <v>1.89804720878601</v>
       </c>
       <c r="H2128" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G2131" t="n">
-        <v>1.97019255161285</v>
+        <v>1.97019267082214</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2132" t="n">
-        <v>2.02541494369507</v>
+        <v>2.02541518211365</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55853,7 +55853,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2134" t="n">
-        <v>2.11359286308289</v>
+        <v>2.11359262466431</v>
       </c>
       <c r="H2134" t="s">
         <v>8</v>
@@ -55957,7 +55957,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2138" t="n">
-        <v>2.12160897254944</v>
+        <v>2.12160873413086</v>
       </c>
       <c r="H2138" t="s">
         <v>8</v>
@@ -55983,7 +55983,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2139" t="n">
-        <v>2.11359286308289</v>
+        <v>2.11359262466431</v>
       </c>
       <c r="H2139" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2141" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2143" t="n">
-        <v>1.98889696598053</v>
+        <v>1.98889708518982</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56139,7 +56139,7 @@
         <v>2.15300011634827</v>
       </c>
       <c r="G2145" t="n">
-        <v>1.91764235496521</v>
+        <v>1.9176424741745</v>
       </c>
       <c r="H2145" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.9203143119812</v>
+        <v>1.92031419277191</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.93367457389832</v>
+        <v>1.9336746931076</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.83926212787628</v>
+        <v>1.83926224708557</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.86152911186218</v>
+        <v>1.86152923107147</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.86152911186218</v>
+        <v>1.86152923107147</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56425,7 +56425,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2156" t="n">
-        <v>1.89626574516296</v>
+        <v>1.89626586437225</v>
       </c>
       <c r="H2156" t="s">
         <v>8</v>
@@ -56451,7 +56451,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2157" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>2.15899991989136</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.92298626899719</v>
+        <v>1.92298638820648</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56503,7 +56503,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.99245965480804</v>
+        <v>1.99245977401733</v>
       </c>
       <c r="H2159" t="s">
         <v>8</v>
@@ -56607,7 +56607,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.1358597278595</v>
+        <v>2.13585996627808</v>
       </c>
       <c r="H2163" t="s">
         <v>8</v>
@@ -56711,7 +56711,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2167" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2167" t="s">
         <v>8</v>
@@ -56789,7 +56789,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G2170" t="n">
-        <v>2.07351183891296</v>
+        <v>2.07351207733154</v>
       </c>
       <c r="H2170" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.06371426582336</v>
+        <v>2.06371450424194</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56841,7 +56841,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G2172" t="n">
-        <v>2.09666991233826</v>
+        <v>2.09666967391968</v>
       </c>
       <c r="H2172" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2174" t="n">
-        <v>2.10913920402527</v>
+        <v>2.10913944244385</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.12339043617249</v>
+        <v>2.12339019775391</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -56945,7 +56945,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.14476656913757</v>
+        <v>2.14476680755615</v>
       </c>
       <c r="H2176" t="s">
         <v>8</v>
@@ -57023,7 +57023,7 @@
         <v>2.41899991035461</v>
       </c>
       <c r="G2179" t="n">
-        <v>2.15456390380859</v>
+        <v>2.15456414222717</v>
       </c>
       <c r="H2179" t="s">
         <v>8</v>
@@ -57075,7 +57075,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2181" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2181" t="s">
         <v>8</v>
@@ -57101,7 +57101,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G2182" t="n">
-        <v>1.98444354534149</v>
+        <v>1.9844434261322</v>
       </c>
       <c r="H2182" t="s">
         <v>8</v>
@@ -57153,7 +57153,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.9461442232132</v>
+        <v>1.94614410400391</v>
       </c>
       <c r="H2184" t="s">
         <v>8</v>
@@ -57179,7 +57179,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2185" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2185" t="s">
         <v>8</v>
@@ -57205,7 +57205,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.94080007076263</v>
+        <v>1.94079983234406</v>
       </c>
       <c r="H2186" t="s">
         <v>8</v>
@@ -57309,7 +57309,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G2190" t="n">
-        <v>1.79294645786285</v>
+        <v>1.79294657707214</v>
       </c>
       <c r="H2190" t="s">
         <v>8</v>
@@ -57413,7 +57413,7 @@
         <v>1.98450005054474</v>
       </c>
       <c r="G2194" t="n">
-        <v>1.76756203174591</v>
+        <v>1.7675621509552</v>
       </c>
       <c r="H2194" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G2199" t="n">
-        <v>1.84282493591309</v>
+        <v>1.8428248167038</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57621,7 +57621,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.84549701213837</v>
+        <v>1.84549689292908</v>
       </c>
       <c r="H2202" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.81521379947662</v>
+        <v>1.81521368026733</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57725,7 +57725,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2206" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2207" t="n">
-        <v>1.80185341835022</v>
+        <v>1.80185329914093</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57777,7 +57777,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.67448556423187</v>
+        <v>1.67448568344116</v>
       </c>
       <c r="H2208" t="s">
         <v>8</v>
@@ -57803,7 +57803,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.71189427375793</v>
+        <v>1.71189439296722</v>
       </c>
       <c r="H2209" t="s">
         <v>8</v>
@@ -57907,7 +57907,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G2213" t="n">
-        <v>1.60055887699127</v>
+        <v>1.60055899620056</v>
       </c>
       <c r="H2213" t="s">
         <v>8</v>
@@ -57933,7 +57933,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.6272794008255</v>
+        <v>1.62727928161621</v>
       </c>
       <c r="H2214" t="s">
         <v>8</v>
@@ -58193,7 +58193,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.81343221664429</v>
+        <v>1.81343233585358</v>
       </c>
       <c r="H2224" t="s">
         <v>8</v>
@@ -58401,7 +58401,7 @@
         <v>2.05699992179871</v>
       </c>
       <c r="G2232" t="n">
-        <v>1.83213663101196</v>
+        <v>1.83213651180267</v>
       </c>
       <c r="H2232" t="s">
         <v>8</v>
@@ -58453,7 +58453,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2234" t="n">
-        <v>1.79027438163757</v>
+        <v>1.79027450084686</v>
       </c>
       <c r="H2234" t="s">
         <v>8</v>
@@ -58479,7 +58479,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.80185341835022</v>
+        <v>1.80185329914093</v>
       </c>
       <c r="H2235" t="s">
         <v>8</v>
@@ -58635,7 +58635,7 @@
         <v>1.99150002002716</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.773796916008</v>
+        <v>1.77379679679871</v>
       </c>
       <c r="H2241" t="s">
         <v>8</v>
@@ -58687,7 +58687,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2243" t="n">
-        <v>1.83926212787628</v>
+        <v>1.83926224708557</v>
       </c>
       <c r="H2243" t="s">
         <v>8</v>
@@ -58713,7 +58713,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G2244" t="n">
-        <v>1.80630695819855</v>
+        <v>1.80630683898926</v>
       </c>
       <c r="H2244" t="s">
         <v>8</v>
@@ -58739,7 +58739,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G2245" t="n">
-        <v>1.89003121852875</v>
+        <v>1.89003109931946</v>
       </c>
       <c r="H2245" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.94970679283142</v>
+        <v>1.94970667362213</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58817,7 +58817,7 @@
         <v>2.16300010681152</v>
       </c>
       <c r="G2248" t="n">
-        <v>1.92654919624329</v>
+        <v>1.92654931545258</v>
       </c>
       <c r="H2248" t="s">
         <v>8</v>
@@ -58843,7 +58843,7 @@
         <v>2.16700005531311</v>
       </c>
       <c r="G2249" t="n">
-        <v>1.93011200428009</v>
+        <v>1.9301118850708</v>
       </c>
       <c r="H2249" t="s">
         <v>8</v>
@@ -58869,7 +58869,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2250" t="n">
-        <v>1.94525361061096</v>
+        <v>1.94525349140167</v>
       </c>
       <c r="H2250" t="s">
         <v>8</v>
@@ -58895,7 +58895,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2251" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2251" t="s">
         <v>8</v>
@@ -58921,7 +58921,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2252" t="s">
         <v>8</v>
@@ -58973,7 +58973,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2254" t="n">
-        <v>2.00314784049988</v>
+        <v>2.00314807891846</v>
       </c>
       <c r="H2254" t="s">
         <v>8</v>
@@ -59025,7 +59025,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2256" t="n">
-        <v>2.06994915008545</v>
+        <v>2.06994891166687</v>
       </c>
       <c r="H2256" t="s">
         <v>8</v>
@@ -59103,7 +59103,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2259" t="n">
-        <v>2.05302619934082</v>
+        <v>2.0530264377594</v>
       </c>
       <c r="H2259" t="s">
         <v>8</v>
@@ -59129,7 +59129,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2260" t="n">
-        <v>2.06371426582336</v>
+        <v>2.06371450424194</v>
       </c>
       <c r="H2260" t="s">
         <v>8</v>
@@ -59155,7 +59155,7 @@
         <v>2.33299994468689</v>
       </c>
       <c r="G2261" t="n">
-        <v>2.07796549797058</v>
+        <v>2.077965259552</v>
       </c>
       <c r="H2261" t="s">
         <v>8</v>
@@ -59181,7 +59181,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2262" t="n">
-        <v>2.10913920402527</v>
+        <v>2.10913944244385</v>
       </c>
       <c r="H2262" t="s">
         <v>8</v>
@@ -59363,7 +59363,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G2269" t="n">
-        <v>2.16525220870972</v>
+        <v>2.1652524471283</v>
       </c>
       <c r="H2269" t="s">
         <v>8</v>
@@ -59493,7 +59493,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G2274" t="n">
-        <v>2.26768088340759</v>
+        <v>2.26768112182617</v>
       </c>
       <c r="H2274" t="s">
         <v>8</v>
@@ -59597,7 +59597,7 @@
         <v>2.48699998855591</v>
       </c>
       <c r="G2278" t="n">
-        <v>2.21513080596924</v>
+        <v>2.21513056755066</v>
       </c>
       <c r="H2278" t="s">
         <v>8</v>
@@ -59675,7 +59675,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2281" t="n">
-        <v>2.29261994361877</v>
+        <v>2.29262018203735</v>
       </c>
       <c r="H2281" t="s">
         <v>8</v>
@@ -59701,7 +59701,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2282" t="n">
-        <v>2.31577801704407</v>
+        <v>2.31577777862549</v>
       </c>
       <c r="H2282" t="s">
         <v>8</v>
@@ -59779,7 +59779,7 @@
         <v>2.64299988746643</v>
       </c>
       <c r="G2285" t="n">
-        <v>2.35407733917236</v>
+        <v>2.35407710075378</v>
       </c>
       <c r="H2285" t="s">
         <v>8</v>
@@ -59857,7 +59857,7 @@
         <v>2.51099991798401</v>
       </c>
       <c r="G2288" t="n">
-        <v>2.23650693893433</v>
+        <v>2.23650717735291</v>
       </c>
       <c r="H2288" t="s">
         <v>8</v>
@@ -59883,7 +59883,7 @@
         <v>2.5090000629425</v>
       </c>
       <c r="G2289" t="n">
-        <v>2.23472595214844</v>
+        <v>2.23472571372986</v>
       </c>
       <c r="H2289" t="s">
         <v>8</v>
@@ -60039,7 +60039,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G2295" t="n">
-        <v>2.45294332504272</v>
+        <v>2.45294308662415</v>
       </c>
       <c r="H2295" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G2299" t="n">
-        <v>2.31221508979797</v>
+        <v>2.31221532821655</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60195,7 +60195,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G2301" t="n">
-        <v>2.27658772468567</v>
+        <v>2.27658796310425</v>
       </c>
       <c r="H2301" t="s">
         <v>8</v>
@@ -60221,7 +60221,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G2302" t="n">
-        <v>2.25164866447449</v>
+        <v>2.25164890289307</v>
       </c>
       <c r="H2302" t="s">
         <v>8</v>
@@ -60247,7 +60247,7 @@
         <v>2.51300001144409</v>
       </c>
       <c r="G2303" t="n">
-        <v>2.23828840255737</v>
+        <v>2.23828864097595</v>
       </c>
       <c r="H2303" t="s">
         <v>8</v>
@@ -60299,7 +60299,7 @@
         <v>2.48300004005432</v>
       </c>
       <c r="G2305" t="n">
-        <v>2.21156787872314</v>
+        <v>2.21156811714172</v>
       </c>
       <c r="H2305" t="s">
         <v>8</v>
@@ -60325,7 +60325,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G2306" t="n">
-        <v>2.14832949638367</v>
+        <v>2.14832925796509</v>
       </c>
       <c r="H2306" t="s">
         <v>8</v>
@@ -60351,7 +60351,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2307" t="n">
-        <v>2.12160897254944</v>
+        <v>2.12160873413086</v>
       </c>
       <c r="H2307" t="s">
         <v>8</v>
@@ -60559,7 +60559,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2315" t="n">
-        <v>2.04411935806274</v>
+        <v>2.04411959648132</v>
       </c>
       <c r="H2315" t="s">
         <v>8</v>
@@ -60611,7 +60611,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G2317" t="n">
-        <v>2.04768228530884</v>
+        <v>2.04768204689026</v>
       </c>
       <c r="H2317" t="s">
         <v>8</v>
@@ -60741,7 +60741,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G2322" t="n">
-        <v>2.05658912658691</v>
+        <v>2.05658888816833</v>
       </c>
       <c r="H2322" t="s">
         <v>8</v>
@@ -60819,7 +60819,7 @@
         <v>2.28099989891052</v>
       </c>
       <c r="G2325" t="n">
-        <v>2.03164982795715</v>
+        <v>2.03164958953857</v>
       </c>
       <c r="H2325" t="s">
         <v>8</v>
@@ -60845,7 +60845,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G2326" t="n">
-        <v>2.0681676864624</v>
+        <v>2.06816792488098</v>
       </c>
       <c r="H2326" t="s">
         <v>8</v>
@@ -60923,7 +60923,7 @@
         <v>2.20300006866455</v>
       </c>
       <c r="G2329" t="n">
-        <v>1.9621764421463</v>
+        <v>1.96217656135559</v>
       </c>
       <c r="H2329" t="s">
         <v>8</v>
@@ -60949,7 +60949,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2330" t="n">
-        <v>2.00314784049988</v>
+        <v>2.00314807891846</v>
       </c>
       <c r="H2330" t="s">
         <v>8</v>
@@ -61001,7 +61001,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2332" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2332" t="s">
         <v>8</v>
@@ -61053,7 +61053,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2334" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2334" t="s">
         <v>8</v>
@@ -61183,7 +61183,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G2339" t="n">
-        <v>1.85440385341644</v>
+        <v>1.85440373420715</v>
       </c>
       <c r="H2339" t="s">
         <v>8</v>
@@ -61261,7 +61261,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2342" t="n">
-        <v>1.89626574516296</v>
+        <v>1.89626586437225</v>
       </c>
       <c r="H2342" t="s">
         <v>8</v>
@@ -61287,7 +61287,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.93278396129608</v>
+        <v>1.93278384208679</v>
       </c>
       <c r="H2343" t="s">
         <v>8</v>
@@ -61313,7 +61313,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2344" t="s">
         <v>8</v>
@@ -61391,7 +61391,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2347" t="n">
-        <v>1.96841132640839</v>
+        <v>1.9684112071991</v>
       </c>
       <c r="H2347" t="s">
         <v>8</v>
@@ -61417,7 +61417,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2348" t="n">
-        <v>1.94525361061096</v>
+        <v>1.94525349140167</v>
       </c>
       <c r="H2348" t="s">
         <v>8</v>
@@ -61469,7 +61469,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G2350" t="n">
-        <v>1.9586136341095</v>
+        <v>1.95861351490021</v>
       </c>
       <c r="H2350" t="s">
         <v>8</v>
@@ -61495,7 +61495,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2351" t="n">
-        <v>1.93367457389832</v>
+        <v>1.9336746931076</v>
       </c>
       <c r="H2351" t="s">
         <v>8</v>
@@ -61573,7 +61573,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2354" t="n">
-        <v>1.89537537097931</v>
+        <v>1.89537525177002</v>
       </c>
       <c r="H2354" t="s">
         <v>8</v>
@@ -61599,7 +61599,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.72436380386353</v>
+        <v>1.72436392307281</v>
       </c>
       <c r="H2355" t="s">
         <v>8</v>
@@ -61755,7 +61755,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G2361" t="n">
-        <v>1.52128803730011</v>
+        <v>1.52128791809082</v>
       </c>
       <c r="H2361" t="s">
         <v>8</v>
@@ -61781,7 +61781,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G2362" t="n">
-        <v>1.56493139266968</v>
+        <v>1.56493151187897</v>
       </c>
       <c r="H2362" t="s">
         <v>8</v>
@@ -61937,7 +61937,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G2368" t="n">
-        <v>1.74930310249329</v>
+        <v>1.749302983284</v>
       </c>
       <c r="H2368" t="s">
         <v>8</v>
@@ -62015,7 +62015,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.82590174674988</v>
+        <v>1.82590186595917</v>
       </c>
       <c r="H2371" t="s">
         <v>8</v>
@@ -62067,7 +62067,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2373" t="n">
-        <v>1.85262227058411</v>
+        <v>1.8526223897934</v>
       </c>
       <c r="H2373" t="s">
         <v>8</v>
@@ -62093,7 +62093,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G2374" t="n">
-        <v>1.83302748203278</v>
+        <v>1.83302736282349</v>
       </c>
       <c r="H2374" t="s">
         <v>8</v>
@@ -62119,7 +62119,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G2375" t="n">
-        <v>1.82768332958221</v>
+        <v>1.82768321037292</v>
       </c>
       <c r="H2375" t="s">
         <v>8</v>
@@ -62145,7 +62145,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G2376" t="n">
-        <v>1.83837139606476</v>
+        <v>1.83837127685547</v>
       </c>
       <c r="H2376" t="s">
         <v>8</v>
@@ -62197,7 +62197,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G2378" t="n">
-        <v>1.9399094581604</v>
+        <v>1.93990933895111</v>
       </c>
       <c r="H2378" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>4.33500003814697</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>15239567</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>4.35400009155273</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>4.33799982070923</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>4.33799982070923</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -71251,6 +71251,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>12012904</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>4.37200021743774</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>4.32000017166138</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>4.36299991607666</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>4.36299991607666</v>
+      </c>
+      <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>23.2093391418457</v>
       </c>
       <c r="G3" t="n">
-        <v>20.5791053771973</v>
+        <v>20.5791072845459</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540729522705</v>
+        <v>18.9540748596191</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.8786602020264</v>
+        <v>19.878662109375</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>22.1665782928467</v>
       </c>
       <c r="G9" t="n">
-        <v>19.6545181274414</v>
+        <v>19.65452003479</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811958312988</v>
+        <v>17.5811977386475</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460289001465</v>
+        <v>15.7460269927979</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.8214406967163</v>
+        <v>14.821439743042</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552736282349</v>
+        <v>13.9552726745605</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.806058883667</v>
       </c>
       <c r="G19" t="n">
-        <v>12.2414674758911</v>
+        <v>12.2414665222168</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087121963501</v>
+        <v>12.6087112426758</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G21" t="n">
-        <v>12.6977405548096</v>
+        <v>12.6977415084839</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.358302116394</v>
       </c>
       <c r="G22" t="n">
-        <v>12.7311267852783</v>
+        <v>12.7311277389526</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.8813648223877</v>
       </c>
       <c r="G23" t="n">
-        <v>12.3082389831543</v>
+        <v>12.30823802948</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>13.5048360824585</v>
       </c>
       <c r="G24" t="n">
-        <v>11.9743804931641</v>
+        <v>11.9743814468384</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G29" t="n">
-        <v>8.0571117401123</v>
+        <v>8.05711078643799</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393510818481</v>
+        <v>6.74393558502197</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.8774790763855</v>
+        <v>6.87747859954834</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51180982589722</v>
+        <v>7.51181030273438</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36045980453491</v>
+        <v>7.36046028137207</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.67679214477539</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58015537261963</v>
+        <v>8.58015632629395</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.96546459197998</v>
       </c>
       <c r="G46" t="n">
-        <v>8.83611392974854</v>
+        <v>8.83611297607422</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.07714366912842</v>
+        <v>8.0771427154541</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811340332031</v>
+        <v>7.98811292648315</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683395385742</v>
+        <v>8.58683300018311</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G53" t="n">
-        <v>8.29526329040527</v>
+        <v>8.29526424407959</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.3175220489502</v>
+        <v>8.31752109527588</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G57" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218772888184</v>
+        <v>7.75218820571899</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.34488010406494</v>
+        <v>7.34487962722778</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.93628597259521</v>
       </c>
       <c r="G62" t="n">
-        <v>7.92356824874878</v>
+        <v>7.92356872558594</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870809555054</v>
+        <v>7.65870761871338</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973592758179</v>
+        <v>6.89973640441895</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.93220806121826</v>
       </c>
       <c r="G67" t="n">
-        <v>7.03327941894531</v>
+        <v>7.03327894210815</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365732192993</v>
+        <v>7.27365779876709</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.86347389221191</v>
+        <v>7.86347341537476</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09939956665039</v>
+        <v>8.09940052032471</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86570024490356</v>
+        <v>7.86569976806641</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G75" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.55128288269043</v>
       </c>
       <c r="G81" t="n">
-        <v>8.46886920928955</v>
+        <v>8.46887016296387</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912178039551</v>
+        <v>8.62912082672119</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G83" t="n">
-        <v>9.68188762664795</v>
+        <v>9.68188858032227</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G86" t="n">
-        <v>8.54009342193604</v>
+        <v>8.54009246826172</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.20487594604492</v>
       </c>
       <c r="G91" t="n">
-        <v>8.16172027587891</v>
+        <v>8.16171932220459</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.2685546875</v>
+        <v>8.26855373382568</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542007446289</v>
+        <v>8.39542102813721</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G96" t="n">
-        <v>8.31974601745605</v>
+        <v>8.31974697113037</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588800430298</v>
+        <v>7.98588752746582</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701738357544</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.14212131500244</v>
       </c>
       <c r="G101" t="n">
-        <v>8.10607814788818</v>
+        <v>8.10607719421387</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.3303861618042</v>
       </c>
       <c r="G105" t="n">
-        <v>8.27300643920898</v>
+        <v>8.27300548553467</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G106" t="n">
-        <v>8.18842887878418</v>
+        <v>8.1884298324585</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889633178711</v>
+        <v>7.77889537811279</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701738357544</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.5261812210083</v>
       </c>
       <c r="G111" t="n">
-        <v>8.44661331176758</v>
+        <v>8.44661235809326</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837268829346</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.28018188476562</v>
       </c>
       <c r="G114" t="n">
-        <v>8.22849178314209</v>
+        <v>8.22849273681641</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325325012207</v>
+        <v>7.72325372695923</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660659790039</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808242797852</v>
+        <v>7.96808195114136</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G118" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76489067077637</v>
+        <v>8.76488971710205</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G123" t="n">
-        <v>9.00749492645264</v>
+        <v>9.00749397277832</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.5919361114502</v>
+        <v>7.59193563461304</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G131" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.44083404541016</v>
       </c>
       <c r="G134" t="n">
-        <v>8.37093734741211</v>
+        <v>8.37093830108643</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.7114725112915</v>
+        <v>8.71147346496582</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420352935791</v>
+        <v>9.03420257568359</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G137" t="n">
-        <v>9.25454998016357</v>
+        <v>9.25454902648926</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G138" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856620788574</v>
+        <v>9.68856430053711</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>10.6934204101562</v>
       </c>
       <c r="G146" t="n">
-        <v>9.4815731048584</v>
+        <v>9.48157215118408</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427219390869</v>
+        <v>9.78427124023438</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G151" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.3881196975708</v>
       </c>
       <c r="G152" t="n">
-        <v>8.32419681549072</v>
+        <v>8.32419776916504</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228832244873</v>
+        <v>8.52228736877441</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.0056276321411</v>
       </c>
       <c r="G156" t="n">
-        <v>8.87172508239746</v>
+        <v>8.87172603607178</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G157" t="n">
-        <v>8.7760181427002</v>
+        <v>8.77601909637451</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>10.3269319534302</v>
       </c>
       <c r="G159" t="n">
-        <v>9.15661716461182</v>
+        <v>9.15661811828613</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.98303604125977</v>
       </c>
       <c r="G164" t="n">
-        <v>8.85169315338135</v>
+        <v>8.85169410705566</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122570037842</v>
+        <v>9.26122665405273</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G169" t="n">
-        <v>9.08094310760498</v>
+        <v>9.0809440612793</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548778533936</v>
+        <v>9.14548873901367</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G176" t="n">
-        <v>9.2078104019165</v>
+        <v>9.20780944824219</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G179" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359874725342</v>
+        <v>7.94359827041626</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.07936668395996</v>
       </c>
       <c r="G184" t="n">
-        <v>8.05043315887451</v>
+        <v>8.05043411254883</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.7922511100769</v>
+        <v>7.79224967956543</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798711776733</v>
+        <v>7.90798759460449</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.73883295059204</v>
+        <v>7.7388334274292</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G192" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G197" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473293304443</v>
+        <v>8.66473388671875</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G199" t="n">
-        <v>8.94294929504395</v>
+        <v>8.94294834136963</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.063362121582</v>
       </c>
       <c r="G200" t="n">
-        <v>8.92291736602783</v>
+        <v>8.92291641235352</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.1662797927856</v>
       </c>
       <c r="G202" t="n">
-        <v>9.0141716003418</v>
+        <v>9.01417064666748</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.8139095306396</v>
       </c>
       <c r="G206" t="n">
-        <v>9.58840847015381</v>
+        <v>9.58840751647949</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856620788574</v>
+        <v>9.68856430053711</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.9519701004028</v>
       </c>
       <c r="G208" t="n">
-        <v>9.71082210540771</v>
+        <v>9.71082305908203</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G209" t="n">
-        <v>9.68188762664795</v>
+        <v>9.68188858032227</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G212" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.34645557403564</v>
+        <v>8.34645462036133</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.22244834899902</v>
       </c>
       <c r="G216" t="n">
-        <v>8.17730140686035</v>
+        <v>8.17730045318604</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G220" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G221" t="n">
-        <v>8.73373126983643</v>
+        <v>8.73373031616211</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.2240142822266</v>
       </c>
       <c r="G225" t="n">
-        <v>9.06536293029785</v>
+        <v>9.06536388397217</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072246551514</v>
+        <v>8.94072341918945</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.1185855865479</v>
       </c>
       <c r="G229" t="n">
-        <v>8.97188091278076</v>
+        <v>8.97188186645508</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.2215042114258</v>
       </c>
       <c r="G231" t="n">
-        <v>9.06313800811768</v>
+        <v>9.06313705444336</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.6457271575928</v>
       </c>
       <c r="G236" t="n">
-        <v>9.439284324646</v>
+        <v>9.43928527832031</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640228271484</v>
+        <v>9.72640323638916</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.6507472991943</v>
       </c>
       <c r="G238" t="n">
-        <v>9.4437370300293</v>
+        <v>9.44373607635498</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.182674407959</v>
+        <v>10.1826753616333</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.6347427368164</v>
       </c>
       <c r="G241" t="n">
-        <v>10.316219329834</v>
+        <v>10.3162183761597</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.4088249206543</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1159029006958</v>
+        <v>10.1159038543701</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G246" t="n">
-        <v>10.5721759796143</v>
+        <v>10.5721769332886</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788536071777</v>
+        <v>10.5788545608521</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12.8019819259644</v>
       </c>
       <c r="G250" t="n">
-        <v>11.3511791229248</v>
+        <v>11.3511781692505</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.0906553268433</v>
       </c>
       <c r="G254" t="n">
-        <v>11.6071376800537</v>
+        <v>11.607138633728</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295513153076</v>
+        <v>11.7295522689819</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076099395752</v>
+        <v>11.9076108932495</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.0319766998291</v>
       </c>
       <c r="G258" t="n">
-        <v>12.4417819976807</v>
+        <v>12.441782951355</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G259" t="n">
-        <v>12.6977405548096</v>
+        <v>12.6977415084839</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195261001587</v>
+        <v>12.4195251464844</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858243942261</v>
+        <v>12.1858253479004</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.3165721893311</v>
       </c>
       <c r="G263" t="n">
-        <v>11.8074531555176</v>
+        <v>11.8074522018433</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>12.7517786026001</v>
       </c>
       <c r="G264" t="n">
-        <v>11.3066654205322</v>
+        <v>11.3066644668579</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>12.7392282485962</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2955360412598</v>
+        <v>11.2955369949341</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351257324219</v>
+        <v>11.0351266860962</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.5007591247559</v>
       </c>
       <c r="G274" t="n">
-        <v>11.0840921401978</v>
+        <v>11.0840930938721</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963228225708</v>
+        <v>11.7963237762451</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960083007812</v>
+        <v>11.5960092544556</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.1995363235474</v>
       </c>
       <c r="G278" t="n">
-        <v>10.8170070648193</v>
+        <v>10.817006111145</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G280" t="n">
-        <v>10.5276622772217</v>
+        <v>10.5276613235474</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141492843628</v>
+        <v>10.4141502380371</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.251672744751</v>
+        <v>10.2516717910767</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.3711729049683</v>
       </c>
       <c r="G285" t="n">
-        <v>10.0825176239014</v>
+        <v>10.0825185775757</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.39857006073</v>
+        <v>10.3985710144043</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651857376099</v>
+        <v>10.3651847839355</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>11.3787031173706</v>
       </c>
       <c r="G290" t="n">
-        <v>10.0891962051392</v>
+        <v>10.0891952514648</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939605712891</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.6874570846558</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3629579544067</v>
+        <v>10.3629589080811</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G297" t="n">
-        <v>9.36361026763916</v>
+        <v>9.36360931396484</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486354827881</v>
+        <v>9.45486450195312</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5428085327148</v>
       </c>
       <c r="G303" t="n">
-        <v>9.34803009033203</v>
+        <v>9.34802913665771</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G305" t="n">
-        <v>9.25454998016357</v>
+        <v>9.25454902648926</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G306" t="n">
-        <v>9.00749492645264</v>
+        <v>9.00749397277832</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.2491159439087</v>
       </c>
       <c r="G308" t="n">
-        <v>9.08762073516846</v>
+        <v>9.08761978149414</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520614624023</v>
+        <v>8.96520709991455</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.3244218826294</v>
       </c>
       <c r="G311" t="n">
-        <v>9.15439224243164</v>
+        <v>9.15439128875732</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539390563965</v>
+        <v>9.08539485931396</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10.6808700561523</v>
       </c>
       <c r="G322" t="n">
-        <v>9.47044467926025</v>
+        <v>9.47044563293457</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981948852539</v>
+        <v>9.77981853485107</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>10.2691984176636</v>
       </c>
       <c r="G331" t="n">
-        <v>9.10542678833008</v>
+        <v>9.10542583465576</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>10.0106477737427</v>
       </c>
       <c r="G332" t="n">
-        <v>8.87617588043213</v>
+        <v>8.87617683410645</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10.0784225463867</v>
       </c>
       <c r="G333" t="n">
-        <v>8.93626976013184</v>
+        <v>8.93627071380615</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.7671594619751</v>
       </c>
       <c r="G335" t="n">
-        <v>8.66028118133545</v>
+        <v>8.66028213500977</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.20335865020752</v>
+        <v>9.2033576965332</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G339" t="n">
-        <v>8.94294929504395</v>
+        <v>8.94294834136963</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837268829346</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G346" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10.003116607666</v>
       </c>
       <c r="G349" t="n">
-        <v>8.86949920654297</v>
+        <v>8.86949825286865</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.80481243133545</v>
       </c>
       <c r="G354" t="n">
-        <v>8.6936674118042</v>
+        <v>8.69366836547852</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.36301803588867</v>
       </c>
       <c r="G359" t="n">
-        <v>8.30194091796875</v>
+        <v>8.30193996429443</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G362" t="n">
-        <v>8.03485298156738</v>
+        <v>8.03485488891602</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033975601196</v>
+        <v>7.9903392791748</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>8.97142791748047</v>
       </c>
       <c r="G364" t="n">
-        <v>7.95472812652588</v>
+        <v>7.95472764968872</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G365" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G366" t="n">
-        <v>7.66093301773071</v>
+        <v>7.66093397140503</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G370" t="n">
-        <v>8.0571117401123</v>
+        <v>8.05711078643799</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133756637573</v>
+        <v>7.21133661270142</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G378" t="n">
-        <v>7.18017721176147</v>
+        <v>7.18017673492432</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.07779979705811</v>
       </c>
       <c r="G380" t="n">
-        <v>7.16237163543701</v>
+        <v>7.16237115859985</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914218902588</v>
+        <v>7.22914266586304</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817197799683</v>
+        <v>7.31817245483398</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390893936157</v>
+        <v>7.43390846252441</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842359542847</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757871627808</v>
+        <v>7.64757919311523</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G408" t="n">
-        <v>7.58525800704956</v>
+        <v>7.5852575302124</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428731918335</v>
+        <v>7.67428636550903</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.5748176574707</v>
       </c>
       <c r="G411" t="n">
-        <v>7.60306358337402</v>
+        <v>7.60306453704834</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>8.53967475891113</v>
       </c>
       <c r="G412" t="n">
-        <v>7.57190370559692</v>
+        <v>7.57190418243408</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701162338257</v>
+        <v>7.28701210021973</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G416" t="n">
-        <v>7.26475429534912</v>
+        <v>7.26475477218628</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.15812587738037</v>
       </c>
       <c r="G417" t="n">
-        <v>7.23359489440918</v>
+        <v>7.23359441757202</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7.93220806121826</v>
       </c>
       <c r="G420" t="n">
-        <v>7.03327941894531</v>
+        <v>7.03327894210815</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.61592388153076</v>
       </c>
       <c r="G422" t="n">
-        <v>6.75283813476562</v>
+        <v>6.75283861160278</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.40004777908325</v>
       </c>
       <c r="G426" t="n">
-        <v>6.56142616271973</v>
+        <v>6.56142663955688</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.93979835510254</v>
+        <v>6.9397988319397</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.76151514053345</v>
       </c>
       <c r="G429" t="n">
-        <v>6.88192987442017</v>
+        <v>6.88193035125732</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.00751399993896</v>
       </c>
       <c r="G430" t="n">
-        <v>7.10005044937134</v>
+        <v>7.1000509262085</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591417312622</v>
+        <v>7.29591369628906</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409908294678</v>
+        <v>7.55409860610962</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G439" t="n">
-        <v>7.58525800704956</v>
+        <v>7.5852575302124</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.66538429260254</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491779327393</v>
+        <v>8.07491683959961</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.10195827484131</v>
       </c>
       <c r="G445" t="n">
-        <v>8.07046604156494</v>
+        <v>8.07046508789062</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G449" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692350387573</v>
+        <v>7.93692302703857</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504264831543</v>
+        <v>8.15504360198975</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.15216159820557</v>
       </c>
       <c r="G455" t="n">
-        <v>8.1149787902832</v>
+        <v>8.11497974395752</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.82081699371338</v>
       </c>
       <c r="G456" t="n">
-        <v>7.82118463516235</v>
+        <v>7.82118511199951</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G457" t="n">
-        <v>7.77221775054932</v>
+        <v>7.77221822738647</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.85093879699707</v>
       </c>
       <c r="G458" t="n">
-        <v>7.84789371490479</v>
+        <v>7.84789323806763</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.92122364044189</v>
       </c>
       <c r="G459" t="n">
-        <v>7.91021251678467</v>
+        <v>7.91021299362183</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G460" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939523696899</v>
+        <v>7.38939476013184</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.04673385620117</v>
       </c>
       <c r="G465" t="n">
-        <v>8.02150058746338</v>
+        <v>8.02149963378906</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.66538429260254</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479150772095</v>
+        <v>7.99479103088379</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G470" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.54677104949951</v>
+        <v>8.5467700958252</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.49354839324951</v>
       </c>
       <c r="G478" t="n">
-        <v>8.41767883300781</v>
+        <v>8.4176778793335</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757871627808</v>
+        <v>7.64757919311523</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576314926147</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344148635864</v>
+        <v>7.84344244003296</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>8.60494041442871</v>
       </c>
       <c r="G488" t="n">
-        <v>7.62977313995361</v>
+        <v>7.62977266311646</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>8.44930839538574</v>
       </c>
       <c r="G497" t="n">
-        <v>7.49177837371826</v>
+        <v>7.4917778968811</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G500" t="n">
-        <v>7.77221775054932</v>
+        <v>7.77221822738647</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996185302734</v>
+        <v>7.74996280670166</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G505" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.11199855804443</v>
       </c>
       <c r="G506" t="n">
-        <v>8.07936763763428</v>
+        <v>8.07936859130859</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.34795665740967</v>
       </c>
       <c r="G508" t="n">
-        <v>8.2885856628418</v>
+        <v>8.28858661651611</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.61403846740723</v>
       </c>
       <c r="G510" t="n">
-        <v>8.52451419830322</v>
+        <v>8.52451324462891</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109508514404</v>
+        <v>8.47109603881836</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.5067081451416</v>
+        <v>8.50670719146729</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.5022554397583</v>
+        <v>8.50225639343262</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G514" t="n">
-        <v>8.73373126983643</v>
+        <v>8.73373031616211</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.1813411712646</v>
       </c>
       <c r="G524" t="n">
-        <v>9.02752685546875</v>
+        <v>9.02752590179443</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G529" t="n">
-        <v>9.04087924957275</v>
+        <v>9.04088020324707</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G530" t="n">
-        <v>9.04087924957275</v>
+        <v>9.04088020324707</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833980560303</v>
+        <v>8.83833885192871</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.60399723052979</v>
       </c>
       <c r="G532" t="n">
-        <v>8.51560974121094</v>
+        <v>8.51561069488525</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.24852466583252</v>
+        <v>8.2485237121582</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G538" t="n">
-        <v>8.03485298156738</v>
+        <v>8.03485488891602</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660659790039</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G545" t="n">
-        <v>7.66093301773071</v>
+        <v>7.66093397140503</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083818435669</v>
+        <v>7.60083913803101</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.76331663131714</v>
+        <v>7.76331615447998</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368877410889</v>
+        <v>7.29368829727173</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.56979656219482</v>
       </c>
       <c r="G558" t="n">
-        <v>7.5986123085022</v>
+        <v>7.59861183166504</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.7566385269165</v>
+        <v>7.75663900375366</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218772888184</v>
+        <v>7.75218820571899</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936330795288</v>
+        <v>7.36936378479004</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585079193115</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>8.43173694610596</v>
       </c>
       <c r="G568" t="n">
-        <v>7.47619867324829</v>
+        <v>7.47619771957397</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>8.16063594818115</v>
       </c>
       <c r="G569" t="n">
-        <v>7.23582029342651</v>
+        <v>7.23581981658936</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.17820739746094</v>
       </c>
       <c r="G570" t="n">
-        <v>7.25140047073364</v>
+        <v>7.25139999389648</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.03512573242188</v>
       </c>
       <c r="G571" t="n">
-        <v>7.12453317642212</v>
+        <v>7.12453365325928</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G578" t="n">
-        <v>6.98876523971558</v>
+        <v>6.98876571655273</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G585" t="n">
-        <v>7.18017721176147</v>
+        <v>7.18017673492432</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842359542847</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610431671143</v>
+        <v>7.41610383987427</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G590" t="n">
-        <v>7.26475429534912</v>
+        <v>7.26475477218628</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G591" t="n">
-        <v>6.98876523971558</v>
+        <v>6.98876571655273</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766778945923</v>
+        <v>6.99766731262207</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443929672241</v>
+        <v>7.06443881988525</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.06022834777832</v>
       </c>
       <c r="G599" t="n">
-        <v>7.14679145812988</v>
+        <v>7.14679098129272</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939523696899</v>
+        <v>7.38939476013184</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.55222606658936</v>
       </c>
       <c r="G603" t="n">
-        <v>7.58303260803223</v>
+        <v>7.58303213119507</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.83242416381836</v>
       </c>
       <c r="G605" t="n">
-        <v>8.7181510925293</v>
+        <v>8.71815013885498</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G607" t="n">
-        <v>8.54009342193604</v>
+        <v>8.54009246826172</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37538909912109</v>
+        <v>8.37539005279541</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065380096436</v>
+        <v>8.19065475463867</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.85250568389893</v>
       </c>
       <c r="G623" t="n">
-        <v>8.7359561920166</v>
+        <v>8.73595523834229</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902599334717</v>
+        <v>8.56902694702148</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G627" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G629" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>9.36552906036377</v>
       </c>
       <c r="G630" t="n">
-        <v>8.30416679382324</v>
+        <v>8.30416774749756</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G636" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.7114725112915</v>
+        <v>8.71147346496582</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>10.0608520507812</v>
       </c>
       <c r="G649" t="n">
-        <v>8.92069053649902</v>
+        <v>8.92069149017334</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G651" t="n">
-        <v>9.0564603805542</v>
+        <v>9.05646133422852</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100601196289</v>
+        <v>9.12100505828857</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>11.401294708252</v>
       </c>
       <c r="G658" t="n">
-        <v>10.109227180481</v>
+        <v>10.1092262268066</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G661" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>11.2331123352051</v>
       </c>
       <c r="G666" t="n">
-        <v>9.96010398864746</v>
+        <v>9.96010303497314</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>11.200478553772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.93116855621338</v>
+        <v>9.93116760253906</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139925003052</v>
+        <v>10.3139934539795</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G671" t="n">
-        <v>9.80652809143066</v>
+        <v>9.80652904510498</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.6648645401001</v>
       </c>
       <c r="G674" t="n">
-        <v>10.3429260253906</v>
+        <v>10.3429269790649</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939605712891</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>11.3711729049683</v>
       </c>
       <c r="G679" t="n">
-        <v>10.0825176239014</v>
+        <v>10.0825185775757</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>11.700008392334</v>
       </c>
       <c r="G683" t="n">
-        <v>10.3740873336792</v>
+        <v>10.3740882873535</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G684" t="n">
-        <v>10.3340244293213</v>
+        <v>10.334023475647</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99348926544189</v>
+        <v>9.99349021911621</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694797515869</v>
+        <v>10.2694787979126</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>11.5017032623291</v>
       </c>
       <c r="G688" t="n">
-        <v>10.1982555389404</v>
+        <v>10.1982564926147</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>11.9259252548218</v>
       </c>
       <c r="G689" t="n">
-        <v>10.5744028091431</v>
+        <v>10.5744018554688</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>11.328498840332</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0446805953979</v>
+        <v>10.0446796417236</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>12.0489253997803</v>
       </c>
       <c r="G692" t="n">
-        <v>10.6834630966187</v>
+        <v>10.683464050293</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G693" t="n">
-        <v>10.8259086608887</v>
+        <v>10.8259077072144</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.756911277771</v>
+        <v>10.7569122314453</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>12.0238227844238</v>
       </c>
       <c r="G696" t="n">
-        <v>10.6612062454224</v>
+        <v>10.661205291748</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>12.4580860137939</v>
       </c>
       <c r="G697" t="n">
-        <v>11.0462560653687</v>
+        <v>11.0462551116943</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.1232872009277</v>
       </c>
       <c r="G698" t="n">
-        <v>11.6360712051392</v>
+        <v>11.6360721588135</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>13.233736038208</v>
       </c>
       <c r="G700" t="n">
-        <v>11.7340030670166</v>
+        <v>11.7340040206909</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>13.7558555603027</v>
       </c>
       <c r="G704" t="n">
-        <v>12.1969528198242</v>
+        <v>12.1969537734985</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856676101685</v>
+        <v>12.0856685638428</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.032919883728</v>
       </c>
       <c r="G706" t="n">
-        <v>11.555944442749</v>
+        <v>11.5559453964233</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>12.7618188858032</v>
       </c>
       <c r="G709" t="n">
-        <v>11.3155660629272</v>
+        <v>11.3155679702759</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395765304565</v>
+        <v>11.0395784378052</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>12.7065954208374</v>
       </c>
       <c r="G712" t="n">
-        <v>11.2666015625</v>
+        <v>11.2666025161743</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349679946899</v>
+        <v>10.9349699020386</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>11.8004150390625</v>
       </c>
       <c r="G715" t="n">
-        <v>10.4631156921387</v>
+        <v>10.463116645813</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364080429077</v>
+        <v>10.4364070892334</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G719" t="n">
-        <v>10.549919128418</v>
+        <v>10.5499200820923</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G720" t="n">
-        <v>10.5721759796143</v>
+        <v>10.5721769332886</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G722" t="n">
-        <v>10.5721759796143</v>
+        <v>10.5721769332886</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>11.7025184631348</v>
       </c>
       <c r="G727" t="n">
-        <v>10.3763132095337</v>
+        <v>10.376314163208</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006391525269</v>
+        <v>10.3006381988525</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>11.1251735687256</v>
       </c>
       <c r="G731" t="n">
-        <v>9.86439800262451</v>
+        <v>9.8643970489502</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>11.1377248764038</v>
       </c>
       <c r="G732" t="n">
-        <v>9.87552547454834</v>
+        <v>9.87552642822266</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580421447754</v>
+        <v>9.34580516815186</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G737" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G738" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081058502197</v>
+        <v>8.29081249237061</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889633178711</v>
+        <v>7.77889537811279</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>9.65169143676758</v>
       </c>
       <c r="G742" t="n">
-        <v>8.55790042877197</v>
+        <v>8.55789947509766</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219253540039</v>
+        <v>8.46219158172607</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.65922069549561</v>
       </c>
       <c r="G745" t="n">
-        <v>8.5645751953125</v>
+        <v>8.56457614898682</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>10.0307302474976</v>
       </c>
       <c r="G748" t="n">
-        <v>8.89398384094238</v>
+        <v>8.89398288726807</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G750" t="n">
-        <v>8.18842887878418</v>
+        <v>8.1884298324585</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G754" t="n">
-        <v>8.29526329040527</v>
+        <v>8.29526424407959</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.8122820854187</v>
+        <v>7.81228256225586</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.25602340698242</v>
       </c>
       <c r="G758" t="n">
-        <v>7.32039737701416</v>
+        <v>7.32039785385132</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>8.17318725585938</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24694871902466</v>
+        <v>7.24694919586182</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>8.12800407409668</v>
       </c>
       <c r="G761" t="n">
-        <v>7.20688629150391</v>
+        <v>7.20688581466675</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873378753662</v>
+        <v>6.96873331069946</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>8.19577884674072</v>
       </c>
       <c r="G763" t="n">
-        <v>7.26698064804077</v>
+        <v>7.26698017120361</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.37400245666504</v>
       </c>
       <c r="G765" t="n">
-        <v>7.42500638961792</v>
+        <v>7.42500686645508</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576314926147</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9.12957000732422</v>
       </c>
       <c r="G767" t="n">
-        <v>8.09494781494141</v>
+        <v>8.09494876861572</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096832275391</v>
+        <v>8.39096927642822</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G778" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G779" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>10.3445043563843</v>
       </c>
       <c r="G787" t="n">
-        <v>9.17219829559326</v>
+        <v>9.17219924926758</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G788" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>10.4298496246338</v>
       </c>
       <c r="G789" t="n">
-        <v>9.24787139892578</v>
+        <v>9.2478723526001</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G795" t="n">
-        <v>9.08094310760498</v>
+        <v>9.0809440612793</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G796" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>10.7963380813599</v>
       </c>
       <c r="G797" t="n">
-        <v>9.57282733917236</v>
+        <v>9.57282638549805</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>10.6557683944702</v>
       </c>
       <c r="G800" t="n">
-        <v>9.44818878173828</v>
+        <v>9.44818782806396</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>10.6833801269531</v>
       </c>
       <c r="G801" t="n">
-        <v>9.47266960144043</v>
+        <v>9.47267055511475</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>10.8440322875977</v>
       </c>
       <c r="G803" t="n">
-        <v>9.61511611938477</v>
+        <v>9.61511707305908</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746685028076</v>
+        <v>9.69746875762939</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232891082764</v>
+        <v>9.96232986450195</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496055603027</v>
+        <v>10.3496036529541</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>11.8882722854614</v>
       </c>
       <c r="G809" t="n">
-        <v>10.5410165786743</v>
+        <v>10.541015625</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G812" t="n">
-        <v>10.5276622772217</v>
+        <v>10.5276613235474</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.2572708129883</v>
       </c>
       <c r="G814" t="n">
-        <v>10.8681983947754</v>
+        <v>10.8681974411011</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.3150053024292</v>
       </c>
       <c r="G815" t="n">
-        <v>10.9193887710571</v>
+        <v>10.9193897247314</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371948242188</v>
+        <v>10.9371957778931</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G820" t="n">
-        <v>10.8259086608887</v>
+        <v>10.8259077072144</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>11.5368452072144</v>
       </c>
       <c r="G822" t="n">
-        <v>10.2294158935547</v>
+        <v>10.2294149398804</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G825" t="n">
-        <v>10.3340244293213</v>
+        <v>10.334023475647</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147792816162</v>
+        <v>10.8147811889648</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295736312866</v>
+        <v>10.3295726776123</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.0564546585083</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6901397705078</v>
+        <v>10.6901388168335</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G842" t="n">
-        <v>10.549919128418</v>
+        <v>10.5499200820923</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>11.8154773712158</v>
       </c>
       <c r="G843" t="n">
-        <v>10.4764709472656</v>
+        <v>10.4764719009399</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>11.3912544250488</v>
       </c>
       <c r="G844" t="n">
-        <v>10.100323677063</v>
+        <v>10.1003246307373</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>11.3385400772095</v>
       </c>
       <c r="G846" t="n">
-        <v>10.0535831451416</v>
+        <v>10.0535840988159</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>10.203932762146</v>
       </c>
       <c r="G854" t="n">
-        <v>9.04755783081055</v>
+        <v>9.04755687713623</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G855" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G858" t="n">
-        <v>9.2701301574707</v>
+        <v>9.27012920379639</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G863" t="n">
-        <v>8.7760181427002</v>
+        <v>8.77601909637451</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>9.62156772613525</v>
       </c>
       <c r="G868" t="n">
-        <v>8.53118896484375</v>
+        <v>8.53118991851807</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>10.768726348877</v>
       </c>
       <c r="G874" t="n">
-        <v>9.5483455657959</v>
+        <v>9.54834461212158</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395671844482</v>
+        <v>9.58395576477051</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G878" t="n">
-        <v>9.2701301574707</v>
+        <v>9.27012920379639</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079208374023</v>
+        <v>9.69079113006592</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0498676300049</v>
       </c>
       <c r="G887" t="n">
-        <v>9.7976245880127</v>
+        <v>9.79762649536133</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.2431526184082</v>
       </c>
       <c r="G889" t="n">
-        <v>9.96900653839111</v>
+        <v>9.9690055847168</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746685028076</v>
+        <v>9.69746875762939</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>11.2130298614502</v>
       </c>
       <c r="G894" t="n">
-        <v>9.94229602813721</v>
+        <v>9.94229698181152</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070013046265</v>
+        <v>10.1070003509521</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>11.2381324768066</v>
       </c>
       <c r="G899" t="n">
-        <v>9.96455574035645</v>
+        <v>9.96455478668213</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>11.1603164672852</v>
       </c>
       <c r="G901" t="n">
-        <v>9.89555835723877</v>
+        <v>9.89555740356445</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304798126221</v>
+        <v>9.71304893493652</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>11.0423374176025</v>
       </c>
       <c r="G905" t="n">
-        <v>9.79094886779785</v>
+        <v>9.79094791412354</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G910" t="n">
-        <v>9.75088596343994</v>
+        <v>9.75088500976562</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794006347656</v>
+        <v>9.99794101715088</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.1829080581665</v>
       </c>
       <c r="G912" t="n">
-        <v>9.91558933258057</v>
+        <v>9.91558837890625</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G914" t="n">
-        <v>9.2078104019165</v>
+        <v>9.20780944824219</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>10.3721160888672</v>
       </c>
       <c r="G917" t="n">
-        <v>9.19668006896973</v>
+        <v>9.19668102264404</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G919" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>9.84497547149658</v>
       </c>
       <c r="G921" t="n">
-        <v>8.72927856445312</v>
+        <v>8.72927951812744</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.95185089111328</v>
+        <v>8.9518518447876</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.4474220275879</v>
       </c>
       <c r="G925" t="n">
-        <v>9.26345252990723</v>
+        <v>9.26345348358154</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>10.7586851119995</v>
       </c>
       <c r="G930" t="n">
-        <v>9.53944206237793</v>
+        <v>9.53944110870361</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.9067869186401</v>
       </c>
       <c r="G933" t="n">
-        <v>9.67076015472412</v>
+        <v>9.6707592010498</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G934" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G937" t="n">
-        <v>9.80652809143066</v>
+        <v>9.80652904510498</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.104775428772</v>
+        <v>10.1047744750977</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136770248413</v>
+        <v>10.1136779785156</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403875350952</v>
+        <v>10.1403865814209</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>11.2155408859253</v>
       </c>
       <c r="G944" t="n">
-        <v>9.94452381134033</v>
+        <v>9.94452285766602</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>11.1854181289673</v>
       </c>
       <c r="G945" t="n">
-        <v>9.91781425476074</v>
+        <v>9.91781520843506</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.881685256958</v>
       </c>
       <c r="G948" t="n">
-        <v>9.64850234985352</v>
+        <v>9.64850330352783</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G950" t="n">
-        <v>9.36361026763916</v>
+        <v>9.36360931396484</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.92736911773682</v>
+        <v>8.92736721038818</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00972080230713</v>
+        <v>9.00971984863281</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G962" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G964" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>10.6557683944702</v>
       </c>
       <c r="G971" t="n">
-        <v>9.44818878173828</v>
+        <v>9.44818782806396</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65963077545166</v>
+        <v>9.65962982177734</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>11.1904392242432</v>
       </c>
       <c r="G979" t="n">
-        <v>9.92226600646973</v>
+        <v>9.92226696014404</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812492370605</v>
+        <v>9.40812397003174</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G999" t="n">
-        <v>9.0564603805542</v>
+        <v>9.05646133422852</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>10.427339553833</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.24564552307129</v>
+        <v>9.24564647674561</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G1004" t="n">
-        <v>9.36361026763916</v>
+        <v>9.36360931396484</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467578887939</v>
+        <v>9.33467674255371</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.5616979598999</v>
+        <v>9.56169891357422</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G1014" t="n">
-        <v>9.75088596343994</v>
+        <v>9.75088500976562</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G1016" t="n">
-        <v>9.75088596343994</v>
+        <v>9.75088500976562</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>11.1728668212891</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.90668487548828</v>
+        <v>9.9066858291626</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>11.1678466796875</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.90223407745361</v>
+        <v>9.90223503112793</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>11.1251735687256</v>
       </c>
       <c r="G1028" t="n">
-        <v>9.86439800262451</v>
+        <v>9.8643970489502</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G1031" t="n">
-        <v>9.25454998016357</v>
+        <v>9.25454902648926</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.31974601745605</v>
+        <v>8.31974697113037</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>9.75962924957275</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.65360546112061</v>
+        <v>8.65360450744629</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.34645557403564</v>
+        <v>8.34645462036133</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>9.63411903381348</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.54231929779053</v>
+        <v>8.54231834411621</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657609939575</v>
+        <v>7.71657657623291</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083818435669</v>
+        <v>7.60083913803101</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>8.3037166595459</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.36268615722656</v>
+        <v>7.36268663406372</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585079193115</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.89613008499146</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.34126949310303</v>
+        <v>4.34126901626587</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.16346597671509</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.57830858230591</v>
+        <v>4.57830905914307</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.18605804443359</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.59834003448486</v>
+        <v>4.59834051132202</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342130661011</v>
+        <v>5.00342178344727</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.8899097442627</v>
+        <v>4.88990926742554</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>5.8261570930481</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.16589975357056</v>
+        <v>5.1658992767334</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.06713485717773</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.37956762313843</v>
+        <v>5.37956809997559</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386211395264</v>
+        <v>5.28386259078979</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445489883423</v>
+        <v>4.95445537567139</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>5.67303514480591</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.03013038635254</v>
+        <v>5.03012990951538</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928503036499</v>
+        <v>5.19928550720215</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041393280029</v>
+        <v>5.21041345596313</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470746994019</v>
+        <v>5.11470699310303</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>5.80858516693115</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15031909942627</v>
+        <v>5.15031862258911</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248207092285</v>
+        <v>5.11248159408569</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>5.59521913528442</v>
       </c>
       <c r="G1108" t="n">
-        <v>4.96113252639771</v>
+        <v>4.96113300323486</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>5.57513809204102</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.9433274269104</v>
+        <v>4.94332695007324</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>4.36299991607666</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>10583147</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>4.38299989700317</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>4.31899976730347</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>4.35400009155273</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>4.36100006103516</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>4.36100006103516</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>23.2093391418457</v>
       </c>
       <c r="G3" t="n">
-        <v>20.5791072845459</v>
+        <v>20.5791053771973</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540748596191</v>
+        <v>18.9540729522705</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.878662109375</v>
+        <v>19.8786602020264</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>22.1665782928467</v>
       </c>
       <c r="G9" t="n">
-        <v>19.65452003479</v>
+        <v>19.6545181274414</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811977386475</v>
+        <v>17.5811958312988</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460269927979</v>
+        <v>15.7460289001465</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.821439743042</v>
+        <v>14.8214406967163</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552726745605</v>
+        <v>13.9552736282349</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.806058883667</v>
       </c>
       <c r="G19" t="n">
-        <v>12.2414665222168</v>
+        <v>12.2414674758911</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087112426758</v>
+        <v>12.6087121963501</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G21" t="n">
-        <v>12.6977415084839</v>
+        <v>12.6977405548096</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.358302116394</v>
       </c>
       <c r="G22" t="n">
-        <v>12.7311277389526</v>
+        <v>12.7311267852783</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.8813648223877</v>
       </c>
       <c r="G23" t="n">
-        <v>12.30823802948</v>
+        <v>12.3082389831543</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>13.5048360824585</v>
       </c>
       <c r="G24" t="n">
-        <v>11.9743814468384</v>
+        <v>11.9743804931641</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G29" t="n">
-        <v>8.05711078643799</v>
+        <v>8.0571117401123</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393558502197</v>
+        <v>6.74393510818481</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.87747859954834</v>
+        <v>6.8774790763855</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51181030273438</v>
+        <v>7.51180982589722</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36046028137207</v>
+        <v>7.36045980453491</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.67679214477539</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58015632629395</v>
+        <v>8.58015537261963</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.96546459197998</v>
       </c>
       <c r="G46" t="n">
-        <v>8.83611297607422</v>
+        <v>8.83611392974854</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.0771427154541</v>
+        <v>8.07714366912842</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811292648315</v>
+        <v>7.98811340332031</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683300018311</v>
+        <v>8.58683395385742</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G53" t="n">
-        <v>8.29526424407959</v>
+        <v>8.29526329040527</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.31752109527588</v>
+        <v>8.3175220489502</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G57" t="n">
-        <v>8.15726852416992</v>
+        <v>8.15726947784424</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218820571899</v>
+        <v>7.75218772888184</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.34487962722778</v>
+        <v>7.34488010406494</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.93628597259521</v>
       </c>
       <c r="G62" t="n">
-        <v>7.92356872558594</v>
+        <v>7.92356824874878</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870761871338</v>
+        <v>7.65870809555054</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973640441895</v>
+        <v>6.89973592758179</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.93220806121826</v>
       </c>
       <c r="G67" t="n">
-        <v>7.03327894210815</v>
+        <v>7.03327941894531</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365779876709</v>
+        <v>7.27365732192993</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.86347341537476</v>
+        <v>7.86347389221191</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09940052032471</v>
+        <v>8.09939956665039</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86569976806641</v>
+        <v>7.86570024490356</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G75" t="n">
-        <v>8.27523231506348</v>
+        <v>8.27523136138916</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.55128288269043</v>
       </c>
       <c r="G81" t="n">
-        <v>8.46887016296387</v>
+        <v>8.46886920928955</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912082672119</v>
+        <v>8.62912178039551</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G83" t="n">
-        <v>9.68188858032227</v>
+        <v>9.68188762664795</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G86" t="n">
-        <v>8.54009246826172</v>
+        <v>8.54009342193604</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.20487594604492</v>
       </c>
       <c r="G91" t="n">
-        <v>8.16171932220459</v>
+        <v>8.16172027587891</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.26855373382568</v>
+        <v>8.2685546875</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542102813721</v>
+        <v>8.39542007446289</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G96" t="n">
-        <v>8.31974697113037</v>
+        <v>8.31974601745605</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588752746582</v>
+        <v>7.98588800430298</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701738357544</v>
+        <v>7.99701690673828</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.14212131500244</v>
       </c>
       <c r="G101" t="n">
-        <v>8.10607719421387</v>
+        <v>8.10607814788818</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.3303861618042</v>
       </c>
       <c r="G105" t="n">
-        <v>8.27300548553467</v>
+        <v>8.27300643920898</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G106" t="n">
-        <v>8.1884298324585</v>
+        <v>8.18842887878418</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889537811279</v>
+        <v>7.77889633178711</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701738357544</v>
+        <v>7.99701690673828</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.5261812210083</v>
       </c>
       <c r="G111" t="n">
-        <v>8.44661235809326</v>
+        <v>8.44661331176758</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837268829346</v>
+        <v>8.85837173461914</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.28018188476562</v>
       </c>
       <c r="G114" t="n">
-        <v>8.22849273681641</v>
+        <v>8.22849178314209</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325372695923</v>
+        <v>7.72325325012207</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660659790039</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808195114136</v>
+        <v>7.96808242797852</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G118" t="n">
-        <v>7.78112173080444</v>
+        <v>7.78112125396729</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76488971710205</v>
+        <v>8.76489067077637</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G123" t="n">
-        <v>9.00749397277832</v>
+        <v>9.00749492645264</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.59193563461304</v>
+        <v>7.5919361114502</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G131" t="n">
-        <v>8.15726852416992</v>
+        <v>8.15726947784424</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.44083404541016</v>
       </c>
       <c r="G134" t="n">
-        <v>8.37093830108643</v>
+        <v>8.37093734741211</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.71147346496582</v>
+        <v>8.7114725112915</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420257568359</v>
+        <v>9.03420352935791</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G137" t="n">
-        <v>9.25454902648926</v>
+        <v>9.25454998016357</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G138" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856430053711</v>
+        <v>9.68856620788574</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>10.6934204101562</v>
       </c>
       <c r="G146" t="n">
-        <v>9.48157215118408</v>
+        <v>9.4815731048584</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427124023438</v>
+        <v>9.78427219390869</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G151" t="n">
-        <v>8.27523231506348</v>
+        <v>8.27523136138916</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.3881196975708</v>
       </c>
       <c r="G152" t="n">
-        <v>8.32419776916504</v>
+        <v>8.32419681549072</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228736877441</v>
+        <v>8.52228832244873</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.0056276321411</v>
       </c>
       <c r="G156" t="n">
-        <v>8.87172603607178</v>
+        <v>8.87172508239746</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G157" t="n">
-        <v>8.77601909637451</v>
+        <v>8.7760181427002</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>10.3269319534302</v>
       </c>
       <c r="G159" t="n">
-        <v>9.15661811828613</v>
+        <v>9.15661716461182</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.98303604125977</v>
       </c>
       <c r="G164" t="n">
-        <v>8.85169410705566</v>
+        <v>8.85169315338135</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122665405273</v>
+        <v>9.26122570037842</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G169" t="n">
-        <v>9.0809440612793</v>
+        <v>9.08094310760498</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548873901367</v>
+        <v>9.14548778533936</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G176" t="n">
-        <v>9.20780944824219</v>
+        <v>9.2078104019165</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G179" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359827041626</v>
+        <v>7.94359874725342</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.07936668395996</v>
       </c>
       <c r="G184" t="n">
-        <v>8.05043411254883</v>
+        <v>8.05043315887451</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.79224967956543</v>
+        <v>7.7922511100769</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798759460449</v>
+        <v>7.90798711776733</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.7388334274292</v>
+        <v>7.73883295059204</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G192" t="n">
-        <v>8.15726852416992</v>
+        <v>8.15726947784424</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G197" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473388671875</v>
+        <v>8.66473293304443</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G199" t="n">
-        <v>8.94294834136963</v>
+        <v>8.94294929504395</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.063362121582</v>
       </c>
       <c r="G200" t="n">
-        <v>8.92291641235352</v>
+        <v>8.92291736602783</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.1662797927856</v>
       </c>
       <c r="G202" t="n">
-        <v>9.01417064666748</v>
+        <v>9.0141716003418</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.8139095306396</v>
       </c>
       <c r="G206" t="n">
-        <v>9.58840751647949</v>
+        <v>9.58840847015381</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856430053711</v>
+        <v>9.68856620788574</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.9519701004028</v>
       </c>
       <c r="G208" t="n">
-        <v>9.71082305908203</v>
+        <v>9.71082210540771</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G209" t="n">
-        <v>9.68188858032227</v>
+        <v>9.68188762664795</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G212" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.34645462036133</v>
+        <v>8.34645557403564</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.22244834899902</v>
       </c>
       <c r="G216" t="n">
-        <v>8.17730045318604</v>
+        <v>8.17730140686035</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G220" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G221" t="n">
-        <v>8.73373031616211</v>
+        <v>8.73373126983643</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.2240142822266</v>
       </c>
       <c r="G225" t="n">
-        <v>9.06536388397217</v>
+        <v>9.06536293029785</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072341918945</v>
+        <v>8.94072246551514</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.1185855865479</v>
       </c>
       <c r="G229" t="n">
-        <v>8.97188186645508</v>
+        <v>8.97188091278076</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.2215042114258</v>
       </c>
       <c r="G231" t="n">
-        <v>9.06313705444336</v>
+        <v>9.06313800811768</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.6457271575928</v>
       </c>
       <c r="G236" t="n">
-        <v>9.43928527832031</v>
+        <v>9.439284324646</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640323638916</v>
+        <v>9.72640228271484</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.6507472991943</v>
       </c>
       <c r="G238" t="n">
-        <v>9.44373607635498</v>
+        <v>9.4437370300293</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1826753616333</v>
+        <v>10.182674407959</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.6347427368164</v>
       </c>
       <c r="G241" t="n">
-        <v>10.3162183761597</v>
+        <v>10.316219329834</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.4088249206543</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1159038543701</v>
+        <v>10.1159029006958</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G246" t="n">
-        <v>10.5721769332886</v>
+        <v>10.5721759796143</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788545608521</v>
+        <v>10.5788536071777</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12.8019819259644</v>
       </c>
       <c r="G250" t="n">
-        <v>11.3511781692505</v>
+        <v>11.3511791229248</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.0906553268433</v>
       </c>
       <c r="G254" t="n">
-        <v>11.607138633728</v>
+        <v>11.6071376800537</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295522689819</v>
+        <v>11.7295513153076</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076108932495</v>
+        <v>11.9076099395752</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.0319766998291</v>
       </c>
       <c r="G258" t="n">
-        <v>12.441782951355</v>
+        <v>12.4417819976807</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G259" t="n">
-        <v>12.6977415084839</v>
+        <v>12.6977405548096</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195251464844</v>
+        <v>12.4195261001587</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858253479004</v>
+        <v>12.1858243942261</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.3165721893311</v>
       </c>
       <c r="G263" t="n">
-        <v>11.8074522018433</v>
+        <v>11.8074531555176</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>12.7517786026001</v>
       </c>
       <c r="G264" t="n">
-        <v>11.3066644668579</v>
+        <v>11.3066654205322</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>12.7392282485962</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2955369949341</v>
+        <v>11.2955360412598</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351266860962</v>
+        <v>11.0351257324219</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.5007591247559</v>
       </c>
       <c r="G274" t="n">
-        <v>11.0840930938721</v>
+        <v>11.0840921401978</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963237762451</v>
+        <v>11.7963228225708</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960092544556</v>
+        <v>11.5960083007812</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.1995363235474</v>
       </c>
       <c r="G278" t="n">
-        <v>10.817006111145</v>
+        <v>10.8170070648193</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G280" t="n">
-        <v>10.5276613235474</v>
+        <v>10.5276622772217</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141502380371</v>
+        <v>10.4141492843628</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.2516717910767</v>
+        <v>10.251672744751</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.3711729049683</v>
       </c>
       <c r="G285" t="n">
-        <v>10.0825185775757</v>
+        <v>10.0825176239014</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.3985710144043</v>
+        <v>10.39857006073</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651847839355</v>
+        <v>10.3651857376099</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>11.3787031173706</v>
       </c>
       <c r="G290" t="n">
-        <v>10.0891952514648</v>
+        <v>10.0891962051392</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939605712891</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.6874570846558</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3629589080811</v>
+        <v>10.3629579544067</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G297" t="n">
-        <v>9.36360931396484</v>
+        <v>9.36361026763916</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486450195312</v>
+        <v>9.45486354827881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5428085327148</v>
       </c>
       <c r="G303" t="n">
-        <v>9.34802913665771</v>
+        <v>9.34803009033203</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G305" t="n">
-        <v>9.25454902648926</v>
+        <v>9.25454998016357</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G306" t="n">
-        <v>9.00749397277832</v>
+        <v>9.00749492645264</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.2491159439087</v>
       </c>
       <c r="G308" t="n">
-        <v>9.08761978149414</v>
+        <v>9.08762073516846</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520709991455</v>
+        <v>8.96520614624023</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.3244218826294</v>
       </c>
       <c r="G311" t="n">
-        <v>9.15439128875732</v>
+        <v>9.15439224243164</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539485931396</v>
+        <v>9.08539390563965</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10.6808700561523</v>
       </c>
       <c r="G322" t="n">
-        <v>9.47044563293457</v>
+        <v>9.47044467926025</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981853485107</v>
+        <v>9.77981948852539</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>10.2691984176636</v>
       </c>
       <c r="G331" t="n">
-        <v>9.10542583465576</v>
+        <v>9.10542678833008</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>10.0106477737427</v>
       </c>
       <c r="G332" t="n">
-        <v>8.87617683410645</v>
+        <v>8.87617588043213</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10.0784225463867</v>
       </c>
       <c r="G333" t="n">
-        <v>8.93627071380615</v>
+        <v>8.93626976013184</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.7671594619751</v>
       </c>
       <c r="G335" t="n">
-        <v>8.66028213500977</v>
+        <v>8.66028118133545</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.2033576965332</v>
+        <v>9.20335865020752</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G339" t="n">
-        <v>8.94294834136963</v>
+        <v>8.94294929504395</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837268829346</v>
+        <v>8.85837173461914</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G346" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10.003116607666</v>
       </c>
       <c r="G349" t="n">
-        <v>8.86949825286865</v>
+        <v>8.86949920654297</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.80481243133545</v>
       </c>
       <c r="G354" t="n">
-        <v>8.69366836547852</v>
+        <v>8.6936674118042</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.36301803588867</v>
       </c>
       <c r="G359" t="n">
-        <v>8.30193996429443</v>
+        <v>8.30194091796875</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G362" t="n">
-        <v>8.03485488891602</v>
+        <v>8.03485298156738</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.9903392791748</v>
+        <v>7.99033975601196</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>8.97142791748047</v>
       </c>
       <c r="G364" t="n">
-        <v>7.95472764968872</v>
+        <v>7.95472812652588</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G365" t="n">
-        <v>7.78112173080444</v>
+        <v>7.78112125396729</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G366" t="n">
-        <v>7.66093397140503</v>
+        <v>7.66093301773071</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G370" t="n">
-        <v>8.05711078643799</v>
+        <v>8.0571117401123</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133661270142</v>
+        <v>7.21133756637573</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G378" t="n">
-        <v>7.18017673492432</v>
+        <v>7.18017721176147</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.07779979705811</v>
       </c>
       <c r="G380" t="n">
-        <v>7.16237115859985</v>
+        <v>7.16237163543701</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914266586304</v>
+        <v>7.22914218902588</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817245483398</v>
+        <v>7.31817197799683</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804521560669</v>
+        <v>7.23804569244385</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390846252441</v>
+        <v>7.43390893936157</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842359542847</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757919311523</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G408" t="n">
-        <v>7.5852575302124</v>
+        <v>7.58525800704956</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428636550903</v>
+        <v>7.67428731918335</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.5748176574707</v>
       </c>
       <c r="G411" t="n">
-        <v>7.60306453704834</v>
+        <v>7.60306358337402</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>8.53967475891113</v>
       </c>
       <c r="G412" t="n">
-        <v>7.57190418243408</v>
+        <v>7.57190370559692</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701210021973</v>
+        <v>7.28701162338257</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G416" t="n">
-        <v>7.26475477218628</v>
+        <v>7.26475429534912</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.15812587738037</v>
       </c>
       <c r="G417" t="n">
-        <v>7.23359441757202</v>
+        <v>7.23359489440918</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7.93220806121826</v>
       </c>
       <c r="G420" t="n">
-        <v>7.03327894210815</v>
+        <v>7.03327941894531</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.61592388153076</v>
       </c>
       <c r="G422" t="n">
-        <v>6.75283861160278</v>
+        <v>6.75283813476562</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.40004777908325</v>
       </c>
       <c r="G426" t="n">
-        <v>6.56142663955688</v>
+        <v>6.56142616271973</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.9397988319397</v>
+        <v>6.93979835510254</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.76151514053345</v>
       </c>
       <c r="G429" t="n">
-        <v>6.88193035125732</v>
+        <v>6.88192987442017</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.00751399993896</v>
       </c>
       <c r="G430" t="n">
-        <v>7.1000509262085</v>
+        <v>7.10005044937134</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591369628906</v>
+        <v>7.29591417312622</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409860610962</v>
+        <v>7.55409908294678</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G439" t="n">
-        <v>7.5852575302124</v>
+        <v>7.58525800704956</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538429260254</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491683959961</v>
+        <v>8.07491779327393</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.10195827484131</v>
       </c>
       <c r="G445" t="n">
-        <v>8.07046508789062</v>
+        <v>8.07046604156494</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G449" t="n">
-        <v>8.03040313720703</v>
+        <v>8.03040218353271</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692302703857</v>
+        <v>7.93692350387573</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504360198975</v>
+        <v>8.15504264831543</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.15216159820557</v>
       </c>
       <c r="G455" t="n">
-        <v>8.11497974395752</v>
+        <v>8.1149787902832</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.82081699371338</v>
       </c>
       <c r="G456" t="n">
-        <v>7.82118511199951</v>
+        <v>7.82118463516235</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G457" t="n">
-        <v>7.77221822738647</v>
+        <v>7.77221775054932</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.85093879699707</v>
       </c>
       <c r="G458" t="n">
-        <v>7.84789323806763</v>
+        <v>7.84789371490479</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.92122364044189</v>
       </c>
       <c r="G459" t="n">
-        <v>7.91021299362183</v>
+        <v>7.91021251678467</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G460" t="n">
-        <v>7.78112173080444</v>
+        <v>7.78112125396729</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804521560669</v>
+        <v>7.23804569244385</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.04673385620117</v>
       </c>
       <c r="G465" t="n">
-        <v>8.02149963378906</v>
+        <v>8.02150058746338</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538429260254</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479103088379</v>
+        <v>7.99479150772095</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G470" t="n">
-        <v>8.03040313720703</v>
+        <v>8.03040218353271</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.5467700958252</v>
+        <v>8.54677104949951</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.49354839324951</v>
       </c>
       <c r="G478" t="n">
-        <v>8.4176778793335</v>
+        <v>8.41767883300781</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757919311523</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576314926147</v>
+        <v>7.90576267242432</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344244003296</v>
+        <v>7.84344148635864</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>8.60494041442871</v>
       </c>
       <c r="G488" t="n">
-        <v>7.62977266311646</v>
+        <v>7.62977313995361</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>8.44930839538574</v>
       </c>
       <c r="G497" t="n">
-        <v>7.4917778968811</v>
+        <v>7.49177837371826</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G500" t="n">
-        <v>7.77221822738647</v>
+        <v>7.77221775054932</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996280670166</v>
+        <v>7.74996185302734</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G505" t="n">
-        <v>8.03040313720703</v>
+        <v>8.03040218353271</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.11199855804443</v>
       </c>
       <c r="G506" t="n">
-        <v>8.07936859130859</v>
+        <v>8.07936763763428</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.34795665740967</v>
       </c>
       <c r="G508" t="n">
-        <v>8.28858661651611</v>
+        <v>8.2885856628418</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.61403846740723</v>
       </c>
       <c r="G510" t="n">
-        <v>8.52451324462891</v>
+        <v>8.52451419830322</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109603881836</v>
+        <v>8.47109508514404</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670719146729</v>
+        <v>8.5067081451416</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.50225639343262</v>
+        <v>8.5022554397583</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G514" t="n">
-        <v>8.73373031616211</v>
+        <v>8.73373126983643</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.1813411712646</v>
       </c>
       <c r="G524" t="n">
-        <v>9.02752590179443</v>
+        <v>9.02752685546875</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G529" t="n">
-        <v>9.04088020324707</v>
+        <v>9.04087924957275</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G530" t="n">
-        <v>9.04088020324707</v>
+        <v>9.04087924957275</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833885192871</v>
+        <v>8.83833980560303</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.60399723052979</v>
       </c>
       <c r="G532" t="n">
-        <v>8.51561069488525</v>
+        <v>8.51560974121094</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.2485237121582</v>
+        <v>8.24852466583252</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G538" t="n">
-        <v>8.03485488891602</v>
+        <v>8.03485298156738</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660659790039</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G545" t="n">
-        <v>7.66093397140503</v>
+        <v>7.66093301773071</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083913803101</v>
+        <v>7.60083818435669</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.76331615447998</v>
+        <v>7.76331663131714</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368829727173</v>
+        <v>7.29368877410889</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.56979656219482</v>
       </c>
       <c r="G558" t="n">
-        <v>7.59861183166504</v>
+        <v>7.5986123085022</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663900375366</v>
+        <v>7.7566385269165</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218820571899</v>
+        <v>7.75218772888184</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936378479004</v>
+        <v>7.36936330795288</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585079193115</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>8.43173694610596</v>
       </c>
       <c r="G568" t="n">
-        <v>7.47619771957397</v>
+        <v>7.47619867324829</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>8.16063594818115</v>
       </c>
       <c r="G569" t="n">
-        <v>7.23581981658936</v>
+        <v>7.23582029342651</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.17820739746094</v>
       </c>
       <c r="G570" t="n">
-        <v>7.25139999389648</v>
+        <v>7.25140047073364</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.03512573242188</v>
       </c>
       <c r="G571" t="n">
-        <v>7.12453365325928</v>
+        <v>7.12453317642212</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G578" t="n">
-        <v>6.98876571655273</v>
+        <v>6.98876523971558</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G585" t="n">
-        <v>7.18017673492432</v>
+        <v>7.18017721176147</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842359542847</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610383987427</v>
+        <v>7.41610431671143</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G590" t="n">
-        <v>7.26475477218628</v>
+        <v>7.26475429534912</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G591" t="n">
-        <v>6.98876571655273</v>
+        <v>6.98876523971558</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766731262207</v>
+        <v>6.99766778945923</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443881988525</v>
+        <v>7.06443929672241</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.06022834777832</v>
       </c>
       <c r="G599" t="n">
-        <v>7.14679098129272</v>
+        <v>7.14679145812988</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.55222606658936</v>
       </c>
       <c r="G603" t="n">
-        <v>7.58303213119507</v>
+        <v>7.58303260803223</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.83242416381836</v>
       </c>
       <c r="G605" t="n">
-        <v>8.71815013885498</v>
+        <v>8.7181510925293</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G607" t="n">
-        <v>8.54009246826172</v>
+        <v>8.54009342193604</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37539005279541</v>
+        <v>8.37538909912109</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065475463867</v>
+        <v>8.19065380096436</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.85250568389893</v>
       </c>
       <c r="G623" t="n">
-        <v>8.73595523834229</v>
+        <v>8.7359561920166</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902694702148</v>
+        <v>8.56902599334717</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G627" t="n">
-        <v>8.27523231506348</v>
+        <v>8.27523136138916</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G629" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>9.36552906036377</v>
       </c>
       <c r="G630" t="n">
-        <v>8.30416774749756</v>
+        <v>8.30416679382324</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G636" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.71147346496582</v>
+        <v>8.7114725112915</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>10.0608520507812</v>
       </c>
       <c r="G649" t="n">
-        <v>8.92069149017334</v>
+        <v>8.92069053649902</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G651" t="n">
-        <v>9.05646133422852</v>
+        <v>9.0564603805542</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100505828857</v>
+        <v>9.12100601196289</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>11.401294708252</v>
       </c>
       <c r="G658" t="n">
-        <v>10.1092262268066</v>
+        <v>10.109227180481</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G661" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686973571777</v>
+        <v>9.31686878204346</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317378997803</v>
+        <v>9.79317283630371</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>11.2331123352051</v>
       </c>
       <c r="G666" t="n">
-        <v>9.96010303497314</v>
+        <v>9.96010398864746</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>11.200478553772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.93116760253906</v>
+        <v>9.93116855621338</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139934539795</v>
+        <v>10.3139925003052</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G671" t="n">
-        <v>9.80652904510498</v>
+        <v>9.80652809143066</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.6648645401001</v>
       </c>
       <c r="G674" t="n">
-        <v>10.3429269790649</v>
+        <v>10.3429260253906</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939605712891</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>11.3711729049683</v>
       </c>
       <c r="G679" t="n">
-        <v>10.0825185775757</v>
+        <v>10.0825176239014</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>11.700008392334</v>
       </c>
       <c r="G683" t="n">
-        <v>10.3740882873535</v>
+        <v>10.3740873336792</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G684" t="n">
-        <v>10.334023475647</v>
+        <v>10.3340244293213</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99349021911621</v>
+        <v>9.99348926544189</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694787979126</v>
+        <v>10.2694797515869</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>11.5017032623291</v>
       </c>
       <c r="G688" t="n">
-        <v>10.1982564926147</v>
+        <v>10.1982555389404</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>11.9259252548218</v>
       </c>
       <c r="G689" t="n">
-        <v>10.5744018554688</v>
+        <v>10.5744028091431</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>11.328498840332</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0446796417236</v>
+        <v>10.0446805953979</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.3941192626953</v>
+        <v>10.394118309021</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>12.0489253997803</v>
       </c>
       <c r="G692" t="n">
-        <v>10.683464050293</v>
+        <v>10.6834630966187</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G693" t="n">
-        <v>10.8259077072144</v>
+        <v>10.8259086608887</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.7569122314453</v>
+        <v>10.756911277771</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>12.0238227844238</v>
       </c>
       <c r="G696" t="n">
-        <v>10.661205291748</v>
+        <v>10.6612062454224</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>12.4580860137939</v>
       </c>
       <c r="G697" t="n">
-        <v>11.0462551116943</v>
+        <v>11.0462560653687</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.1232872009277</v>
       </c>
       <c r="G698" t="n">
-        <v>11.6360721588135</v>
+        <v>11.6360712051392</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>13.233736038208</v>
       </c>
       <c r="G700" t="n">
-        <v>11.7340040206909</v>
+        <v>11.7340030670166</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>13.7558555603027</v>
       </c>
       <c r="G704" t="n">
-        <v>12.1969537734985</v>
+        <v>12.1969528198242</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856685638428</v>
+        <v>12.0856676101685</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.032919883728</v>
       </c>
       <c r="G706" t="n">
-        <v>11.5559453964233</v>
+        <v>11.555944442749</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>12.7618188858032</v>
       </c>
       <c r="G709" t="n">
-        <v>11.3155679702759</v>
+        <v>11.3155660629272</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395784378052</v>
+        <v>11.0395765304565</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>12.7065954208374</v>
       </c>
       <c r="G712" t="n">
-        <v>11.2666025161743</v>
+        <v>11.2666015625</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349699020386</v>
+        <v>10.9349679946899</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>11.8004150390625</v>
       </c>
       <c r="G715" t="n">
-        <v>10.463116645813</v>
+        <v>10.4631156921387</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364070892334</v>
+        <v>10.4364080429077</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G719" t="n">
-        <v>10.5499200820923</v>
+        <v>10.549919128418</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G720" t="n">
-        <v>10.5721769332886</v>
+        <v>10.5721759796143</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G722" t="n">
-        <v>10.5721769332886</v>
+        <v>10.5721759796143</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.3941192626953</v>
+        <v>10.394118309021</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>11.7025184631348</v>
       </c>
       <c r="G727" t="n">
-        <v>10.376314163208</v>
+        <v>10.3763132095337</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006381988525</v>
+        <v>10.3006391525269</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>11.1251735687256</v>
       </c>
       <c r="G731" t="n">
-        <v>9.8643970489502</v>
+        <v>9.86439800262451</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>11.1377248764038</v>
       </c>
       <c r="G732" t="n">
-        <v>9.87552642822266</v>
+        <v>9.87552547454834</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580516815186</v>
+        <v>9.34580421447754</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G737" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G738" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081249237061</v>
+        <v>8.29081058502197</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889537811279</v>
+        <v>7.77889633178711</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>9.65169143676758</v>
       </c>
       <c r="G742" t="n">
-        <v>8.55789947509766</v>
+        <v>8.55790042877197</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219158172607</v>
+        <v>8.46219253540039</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.65922069549561</v>
       </c>
       <c r="G745" t="n">
-        <v>8.56457614898682</v>
+        <v>8.5645751953125</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>10.0307302474976</v>
       </c>
       <c r="G748" t="n">
-        <v>8.89398288726807</v>
+        <v>8.89398384094238</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G750" t="n">
-        <v>8.1884298324585</v>
+        <v>8.18842887878418</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G754" t="n">
-        <v>8.29526424407959</v>
+        <v>8.29526329040527</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.81228256225586</v>
+        <v>7.8122820854187</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.25602340698242</v>
       </c>
       <c r="G758" t="n">
-        <v>7.32039785385132</v>
+        <v>7.32039737701416</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>8.17318725585938</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24694919586182</v>
+        <v>7.24694871902466</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>8.12800407409668</v>
       </c>
       <c r="G761" t="n">
-        <v>7.20688581466675</v>
+        <v>7.20688629150391</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873331069946</v>
+        <v>6.96873378753662</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>8.19577884674072</v>
       </c>
       <c r="G763" t="n">
-        <v>7.26698017120361</v>
+        <v>7.26698064804077</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.37400245666504</v>
       </c>
       <c r="G765" t="n">
-        <v>7.42500686645508</v>
+        <v>7.42500638961792</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576314926147</v>
+        <v>7.90576267242432</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9.12957000732422</v>
       </c>
       <c r="G767" t="n">
-        <v>8.09494876861572</v>
+        <v>8.09494781494141</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096927642822</v>
+        <v>8.39096832275391</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G778" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G779" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>10.3445043563843</v>
       </c>
       <c r="G787" t="n">
-        <v>9.17219924926758</v>
+        <v>9.17219829559326</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G788" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>10.4298496246338</v>
       </c>
       <c r="G789" t="n">
-        <v>9.2478723526001</v>
+        <v>9.24787139892578</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G795" t="n">
-        <v>9.0809440612793</v>
+        <v>9.08094310760498</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G796" t="n">
-        <v>9.43705940246582</v>
+        <v>9.4370584487915</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>10.7963380813599</v>
       </c>
       <c r="G797" t="n">
-        <v>9.57282638549805</v>
+        <v>9.57282733917236</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>10.6557683944702</v>
       </c>
       <c r="G800" t="n">
-        <v>9.44818782806396</v>
+        <v>9.44818878173828</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>10.6833801269531</v>
       </c>
       <c r="G801" t="n">
-        <v>9.47267055511475</v>
+        <v>9.47266960144043</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>10.8440322875977</v>
       </c>
       <c r="G803" t="n">
-        <v>9.61511707305908</v>
+        <v>9.61511611938477</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746875762939</v>
+        <v>9.69746685028076</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232986450195</v>
+        <v>9.96232891082764</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496036529541</v>
+        <v>10.3496055603027</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>11.8882722854614</v>
       </c>
       <c r="G809" t="n">
-        <v>10.541015625</v>
+        <v>10.5410165786743</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G812" t="n">
-        <v>10.5276613235474</v>
+        <v>10.5276622772217</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.2572708129883</v>
       </c>
       <c r="G814" t="n">
-        <v>10.8681974411011</v>
+        <v>10.8681983947754</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.3150053024292</v>
       </c>
       <c r="G815" t="n">
-        <v>10.9193897247314</v>
+        <v>10.9193887710571</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371957778931</v>
+        <v>10.9371948242188</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G820" t="n">
-        <v>10.8259077072144</v>
+        <v>10.8259086608887</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>11.5368452072144</v>
       </c>
       <c r="G822" t="n">
-        <v>10.2294149398804</v>
+        <v>10.2294158935547</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G825" t="n">
-        <v>10.334023475647</v>
+        <v>10.3340244293213</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147811889648</v>
+        <v>10.8147792816162</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295726776123</v>
+        <v>10.3295736312866</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.0564546585083</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6901388168335</v>
+        <v>10.6901397705078</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G842" t="n">
-        <v>10.5499200820923</v>
+        <v>10.549919128418</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>11.8154773712158</v>
       </c>
       <c r="G843" t="n">
-        <v>10.4764719009399</v>
+        <v>10.4764709472656</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>11.3912544250488</v>
       </c>
       <c r="G844" t="n">
-        <v>10.1003246307373</v>
+        <v>10.100323677063</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>11.3385400772095</v>
       </c>
       <c r="G846" t="n">
-        <v>10.0535840988159</v>
+        <v>10.0535831451416</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>10.203932762146</v>
       </c>
       <c r="G854" t="n">
-        <v>9.04755687713623</v>
+        <v>9.04755783081055</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G855" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G858" t="n">
-        <v>9.27012920379639</v>
+        <v>9.2701301574707</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G863" t="n">
-        <v>8.77601909637451</v>
+        <v>8.7760181427002</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>9.62156772613525</v>
       </c>
       <c r="G868" t="n">
-        <v>8.53118991851807</v>
+        <v>8.53118896484375</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>10.768726348877</v>
       </c>
       <c r="G874" t="n">
-        <v>9.54834461212158</v>
+        <v>9.5483455657959</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395576477051</v>
+        <v>9.58395671844482</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G878" t="n">
-        <v>9.27012920379639</v>
+        <v>9.2701301574707</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079113006592</v>
+        <v>9.69079208374023</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0498676300049</v>
       </c>
       <c r="G887" t="n">
-        <v>9.79762649536133</v>
+        <v>9.7976245880127</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.2431526184082</v>
       </c>
       <c r="G889" t="n">
-        <v>9.9690055847168</v>
+        <v>9.96900653839111</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746875762939</v>
+        <v>9.69746685028076</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>11.2130298614502</v>
       </c>
       <c r="G894" t="n">
-        <v>9.94229698181152</v>
+        <v>9.94229602813721</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070003509521</v>
+        <v>10.1070013046265</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>11.2381324768066</v>
       </c>
       <c r="G899" t="n">
-        <v>9.96455478668213</v>
+        <v>9.96455574035645</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>11.1603164672852</v>
       </c>
       <c r="G901" t="n">
-        <v>9.89555740356445</v>
+        <v>9.89555835723877</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304893493652</v>
+        <v>9.71304798126221</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>11.0423374176025</v>
       </c>
       <c r="G905" t="n">
-        <v>9.79094791412354</v>
+        <v>9.79094886779785</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G910" t="n">
-        <v>9.75088500976562</v>
+        <v>9.75088596343994</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794101715088</v>
+        <v>9.99794006347656</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.1829080581665</v>
       </c>
       <c r="G912" t="n">
-        <v>9.91558837890625</v>
+        <v>9.91558933258057</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G914" t="n">
-        <v>9.20780944824219</v>
+        <v>9.2078104019165</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>10.3721160888672</v>
       </c>
       <c r="G917" t="n">
-        <v>9.19668102264404</v>
+        <v>9.19668006896973</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G919" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>9.84497547149658</v>
       </c>
       <c r="G921" t="n">
-        <v>8.72927951812744</v>
+        <v>8.72927856445312</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.9518518447876</v>
+        <v>8.95185089111328</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.4474220275879</v>
       </c>
       <c r="G925" t="n">
-        <v>9.26345348358154</v>
+        <v>9.26345252990723</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>10.7586851119995</v>
       </c>
       <c r="G930" t="n">
-        <v>9.53944110870361</v>
+        <v>9.53944206237793</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.9067869186401</v>
       </c>
       <c r="G933" t="n">
-        <v>9.6707592010498</v>
+        <v>9.67076015472412</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G934" t="n">
-        <v>9.43705940246582</v>
+        <v>9.4370584487915</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G937" t="n">
-        <v>9.80652904510498</v>
+        <v>9.80652809143066</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.1047744750977</v>
+        <v>10.104775428772</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136779785156</v>
+        <v>10.1136770248413</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403865814209</v>
+        <v>10.1403875350952</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>11.2155408859253</v>
       </c>
       <c r="G944" t="n">
-        <v>9.94452285766602</v>
+        <v>9.94452381134033</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>11.1854181289673</v>
       </c>
       <c r="G945" t="n">
-        <v>9.91781520843506</v>
+        <v>9.91781425476074</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.881685256958</v>
       </c>
       <c r="G948" t="n">
-        <v>9.64850330352783</v>
+        <v>9.64850234985352</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G950" t="n">
-        <v>9.36360931396484</v>
+        <v>9.36361026763916</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.92736721038818</v>
+        <v>8.92736911773682</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00971984863281</v>
+        <v>9.00972080230713</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G962" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G964" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686973571777</v>
+        <v>9.31686878204346</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>10.6557683944702</v>
       </c>
       <c r="G971" t="n">
-        <v>9.44818782806396</v>
+        <v>9.44818878173828</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65962982177734</v>
+        <v>9.65963077545166</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>11.1904392242432</v>
       </c>
       <c r="G979" t="n">
-        <v>9.92226696014404</v>
+        <v>9.92226600646973</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812397003174</v>
+        <v>9.40812492370605</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G999" t="n">
-        <v>9.05646133422852</v>
+        <v>9.0564603805542</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>10.427339553833</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.24564647674561</v>
+        <v>9.24564552307129</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G1004" t="n">
-        <v>9.36360931396484</v>
+        <v>9.36361026763916</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467674255371</v>
+        <v>9.33467578887939</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.56169891357422</v>
+        <v>9.5616979598999</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G1014" t="n">
-        <v>9.75088500976562</v>
+        <v>9.75088596343994</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G1016" t="n">
-        <v>9.75088500976562</v>
+        <v>9.75088596343994</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>11.1728668212891</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.9066858291626</v>
+        <v>9.90668487548828</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>11.1678466796875</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.90223503112793</v>
+        <v>9.90223407745361</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317378997803</v>
+        <v>9.79317283630371</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>11.1251735687256</v>
       </c>
       <c r="G1028" t="n">
-        <v>9.8643970489502</v>
+        <v>9.86439800262451</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G1031" t="n">
-        <v>9.25454902648926</v>
+        <v>9.25454998016357</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.31974697113037</v>
+        <v>8.31974601745605</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>9.75962924957275</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.65360450744629</v>
+        <v>8.65360546112061</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.34645462036133</v>
+        <v>8.34645557403564</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>9.63411903381348</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.54231834411621</v>
+        <v>8.54231929779053</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657657623291</v>
+        <v>7.71657609939575</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083913803101</v>
+        <v>7.60083818435669</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>8.3037166595459</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.36268663406372</v>
+        <v>7.36268615722656</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585079193115</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.89613008499146</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.34126901626587</v>
+        <v>4.34126949310303</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.16346597671509</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.57830905914307</v>
+        <v>4.57830858230591</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.18605804443359</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.59834051132202</v>
+        <v>4.59834003448486</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342178344727</v>
+        <v>5.00342130661011</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.88990926742554</v>
+        <v>4.8899097442627</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>5.8261570930481</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.1658992767334</v>
+        <v>5.16589975357056</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.06713485717773</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.37956809997559</v>
+        <v>5.37956762313843</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386259078979</v>
+        <v>5.28386211395264</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445537567139</v>
+        <v>4.95445489883423</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>5.67303514480591</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.03012990951538</v>
+        <v>5.03013038635254</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928550720215</v>
+        <v>5.19928503036499</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041345596313</v>
+        <v>5.21041393280029</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470699310303</v>
+        <v>5.11470746994019</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>5.80858516693115</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15031862258911</v>
+        <v>5.15031909942627</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248159408569</v>
+        <v>5.11248207092285</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>5.59521913528442</v>
       </c>
       <c r="G1108" t="n">
-        <v>4.96113300323486</v>
+        <v>4.96113252639771</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>5.57513809204102</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.94332695007324</v>
+        <v>4.9433274269104</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>4.36100006103516</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>9785475</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>4.36299991607666</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>4.31099987030029</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>4.34800004959106</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>4.34899997711182</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>4.34899997711182</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>22.8775520324707</v>
       </c>
       <c r="G2" t="n">
-        <v>20.2849197387695</v>
+        <v>20.2849216461182</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>21.9295864105225</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4443836212158</v>
+        <v>19.4443855285645</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540729522705</v>
+        <v>18.9540710449219</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.8786602020264</v>
+        <v>19.878662109375</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>20.9184246063232</v>
       </c>
       <c r="G11" t="n">
-        <v>18.547815322876</v>
+        <v>18.5478134155273</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552736282349</v>
+        <v>13.9552726745605</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087121963501</v>
+        <v>12.6087112426758</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.358302116394</v>
       </c>
       <c r="G22" t="n">
-        <v>12.7311277389526</v>
+        <v>12.7311267852783</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.8813648223877</v>
       </c>
       <c r="G23" t="n">
-        <v>12.30823802948</v>
+        <v>12.3082389831543</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.75209808349609</v>
       </c>
       <c r="G27" t="n">
-        <v>8.64692783355713</v>
+        <v>8.64692687988281</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G29" t="n">
-        <v>8.05711078643799</v>
+        <v>8.0571117401123</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G31" t="n">
-        <v>6.70832395553589</v>
+        <v>6.70832443237305</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393510818481</v>
+        <v>6.74393558502197</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.87747859954834</v>
+        <v>6.8774790763855</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51181030273438</v>
+        <v>7.51180934906006</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243886947632</v>
+        <v>7.91243982315063</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.67679214477539</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58015632629395</v>
+        <v>8.58015537261963</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683204650879</v>
+        <v>8.58683300018311</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.26261138916016</v>
       </c>
       <c r="G54" t="n">
-        <v>8.21291255950928</v>
+        <v>8.21291351318359</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.31752109527588</v>
+        <v>8.3175220489502</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870714187622</v>
+        <v>7.65870809555054</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973592758179</v>
+        <v>6.89973640441895</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.61341381072998</v>
       </c>
       <c r="G68" t="n">
-        <v>6.75061225891113</v>
+        <v>6.75061273574829</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365779876709</v>
+        <v>7.27365732192993</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.55128288269043</v>
       </c>
       <c r="G81" t="n">
-        <v>8.46887016296387</v>
+        <v>8.46886920928955</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G83" t="n">
-        <v>9.68188858032227</v>
+        <v>9.68188762664795</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.36803913116455</v>
       </c>
       <c r="G90" t="n">
-        <v>8.30639266967773</v>
+        <v>8.30639171600342</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.26855373382568</v>
+        <v>8.2685546875</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G96" t="n">
-        <v>8.31974697113037</v>
+        <v>8.31974601745605</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588752746582</v>
+        <v>7.98588848114014</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.92875480651855</v>
       </c>
       <c r="G100" t="n">
-        <v>7.91689109802246</v>
+        <v>7.91689014434814</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.14212131500244</v>
       </c>
       <c r="G101" t="n">
-        <v>8.10607719421387</v>
+        <v>8.10607814788818</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.04924392700195</v>
       </c>
       <c r="G108" t="n">
-        <v>8.02372550964355</v>
+        <v>8.02372455596924</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.5261812210083</v>
       </c>
       <c r="G111" t="n">
-        <v>8.44661235809326</v>
+        <v>8.44661331176758</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837078094482</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G113" t="n">
-        <v>8.67363548278809</v>
+        <v>8.6736364364624</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808242797852</v>
+        <v>7.96808338165283</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.80230236053467</v>
       </c>
       <c r="G120" t="n">
-        <v>8.69144153594971</v>
+        <v>8.69144248962402</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76488971710205</v>
+        <v>8.76489067077637</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G123" t="n">
-        <v>9.00749397277832</v>
+        <v>9.007493019104</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933666229248</v>
+        <v>8.05933570861816</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G132" t="n">
-        <v>7.82341051101685</v>
+        <v>7.82341146469116</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420257568359</v>
+        <v>9.03420352935791</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G138" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G141" t="n">
-        <v>9.55947303771973</v>
+        <v>9.55947208404541</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>10.8590927124023</v>
       </c>
       <c r="G143" t="n">
-        <v>9.6284704208374</v>
+        <v>9.62846946716309</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427219390869</v>
+        <v>9.78427124023438</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G148" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228736877441</v>
+        <v>8.5222864151001</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122665405273</v>
+        <v>9.26122570037842</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G166" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>10.442400932312</v>
       </c>
       <c r="G168" t="n">
-        <v>9.25899982452393</v>
+        <v>9.25900077819824</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G169" t="n">
-        <v>9.0809440612793</v>
+        <v>9.08094310760498</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548873901367</v>
+        <v>9.14548778533936</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G176" t="n">
-        <v>9.20780944824219</v>
+        <v>9.2078104019165</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G179" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.28771305084229</v>
       </c>
       <c r="G188" t="n">
-        <v>8.23516941070557</v>
+        <v>8.23516845703125</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G196" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G197" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G209" t="n">
-        <v>9.68188858032227</v>
+        <v>9.68188762664795</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G212" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.2240142822266</v>
       </c>
       <c r="G225" t="n">
-        <v>9.06536388397217</v>
+        <v>9.06536293029785</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072246551514</v>
+        <v>8.94072341918945</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G228" t="n">
-        <v>8.67363548278809</v>
+        <v>8.6736364364624</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G230" t="n">
-        <v>8.9451732635498</v>
+        <v>8.94517421722412</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.2215042114258</v>
       </c>
       <c r="G231" t="n">
-        <v>9.06313705444336</v>
+        <v>9.06313800811768</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G233" t="n">
-        <v>8.92514228820801</v>
+        <v>8.92514324188232</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>12.2748422622681</v>
       </c>
       <c r="G248" t="n">
-        <v>10.8837776184082</v>
+        <v>10.8837785720825</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12.8019819259644</v>
       </c>
       <c r="G250" t="n">
-        <v>11.3511781692505</v>
+        <v>11.3511791229248</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G252" t="n">
-        <v>11.2844085693359</v>
+        <v>11.2844076156616</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076108932495</v>
+        <v>11.9076099395752</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>13.9817733764648</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3972682952881</v>
+        <v>12.3972692489624</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195261001587</v>
+        <v>12.4195251464844</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858243942261</v>
+        <v>12.1858253479004</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>13.1032047271729</v>
       </c>
       <c r="G265" t="n">
-        <v>11.6182651519775</v>
+        <v>11.6182661056519</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.2999439239502</v>
       </c>
       <c r="G268" t="n">
-        <v>10.9060354232788</v>
+        <v>10.9060344696045</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.5635137557983</v>
       </c>
       <c r="G269" t="n">
-        <v>11.1397352218628</v>
+        <v>11.1397342681885</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G270" t="n">
-        <v>11.2844085693359</v>
+        <v>11.2844076156616</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619939804077</v>
+        <v>11.1619930267334</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>12.6011667251587</v>
       </c>
       <c r="G272" t="n">
-        <v>11.1731214523315</v>
+        <v>11.1731204986572</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.5007591247559</v>
       </c>
       <c r="G274" t="n">
-        <v>11.0840930938721</v>
+        <v>11.0840921401978</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>13.1283073425293</v>
       </c>
       <c r="G276" t="n">
-        <v>11.6405229568481</v>
+        <v>11.6405220031738</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.251672744751</v>
+        <v>10.2516717910767</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.707537651062</v>
       </c>
       <c r="G287" t="n">
-        <v>10.3807649612427</v>
+        <v>10.3807640075684</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651838302612</v>
+        <v>10.3651847839355</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>11.3310089111328</v>
       </c>
       <c r="G296" t="n">
-        <v>10.0469055175781</v>
+        <v>10.0469064712524</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486450195312</v>
+        <v>9.45486354827881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10.6984405517578</v>
       </c>
       <c r="G302" t="n">
-        <v>9.48602485656738</v>
+        <v>9.48602390289307</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G306" t="n">
-        <v>9.00749397277832</v>
+        <v>9.007493019104</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10.1386680603027</v>
       </c>
       <c r="G307" t="n">
-        <v>8.9896879196167</v>
+        <v>8.98968887329102</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.3244218826294</v>
       </c>
       <c r="G311" t="n">
-        <v>9.15439128875732</v>
+        <v>9.15439224243164</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G313" t="n">
-        <v>9.01639652252197</v>
+        <v>9.01639747619629</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539390563965</v>
+        <v>9.08539485931396</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.1336479187012</v>
       </c>
       <c r="G315" t="n">
-        <v>8.98523807525635</v>
+        <v>8.98523712158203</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10.1562385559082</v>
       </c>
       <c r="G317" t="n">
-        <v>9.00526714324951</v>
+        <v>9.00526809692383</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G320" t="n">
-        <v>9.46154117584229</v>
+        <v>9.4615421295166</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10.6808700561523</v>
       </c>
       <c r="G322" t="n">
-        <v>9.47044563293457</v>
+        <v>9.47044467926025</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981853485107</v>
+        <v>9.77981948852539</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G325" t="n">
-        <v>9.51050758361816</v>
+        <v>9.51050853729248</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>10.5227270126343</v>
       </c>
       <c r="G328" t="n">
-        <v>9.33022308349609</v>
+        <v>9.33022403717041</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G330" t="n">
-        <v>9.12990951538086</v>
+        <v>9.12990856170654</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>10.2691984176636</v>
       </c>
       <c r="G331" t="n">
-        <v>9.10542583465576</v>
+        <v>9.10542678833008</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.20335865020752</v>
+        <v>9.2033576965332</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837078094482</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G344" t="n">
-        <v>8.87840270996094</v>
+        <v>8.87840175628662</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G347" t="n">
-        <v>8.87840270996094</v>
+        <v>8.87840175628662</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G355" t="n">
-        <v>8.86282348632812</v>
+        <v>8.86282253265381</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.36301803588867</v>
       </c>
       <c r="G359" t="n">
-        <v>8.30193996429443</v>
+        <v>8.30194091796875</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033975601196</v>
+        <v>7.99033880233765</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215579986572</v>
+        <v>7.73215675354004</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209337234497</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G370" t="n">
-        <v>8.05711078643799</v>
+        <v>8.0571117401123</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>8.27861499786377</v>
       </c>
       <c r="G375" t="n">
-        <v>7.34042882919312</v>
+        <v>7.34042930603027</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G376" t="n">
-        <v>7.1979832649231</v>
+        <v>7.19798278808594</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817245483398</v>
+        <v>7.31817197799683</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G384" t="n">
-        <v>7.1979832649231</v>
+        <v>7.19798278808594</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.6965446472168</v>
+        <v>7.69654560089111</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390846252441</v>
+        <v>7.43390941619873</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.85679721832275</v>
+        <v>7.85679626464844</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>8.52461433410645</v>
       </c>
       <c r="G397" t="n">
-        <v>7.55854988098145</v>
+        <v>7.55854940414429</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842311859131</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196756362915</v>
+        <v>7.61196660995483</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G405" t="n">
-        <v>7.70099496841431</v>
+        <v>7.70099592208862</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209337234497</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757966995239</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428636550903</v>
+        <v>7.67428731918335</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G413" t="n">
-        <v>7.50513172149658</v>
+        <v>7.5051326751709</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249792098999</v>
+        <v>7.24249744415283</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701210021973</v>
+        <v>7.28701162338257</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.15812587738037</v>
       </c>
       <c r="G417" t="n">
-        <v>7.23359441757202</v>
+        <v>7.23359394073486</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G418" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.08281993865967</v>
       </c>
       <c r="G419" t="n">
-        <v>7.16682195663452</v>
+        <v>7.16682243347168</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7.84184217453003</v>
       </c>
       <c r="G421" t="n">
-        <v>6.95315361022949</v>
+        <v>6.95315408706665</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>7.70127105712891</v>
       </c>
       <c r="G423" t="n">
-        <v>6.82851362228394</v>
+        <v>6.82851314544678</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.68621015548706</v>
       </c>
       <c r="G424" t="n">
-        <v>6.8151593208313</v>
+        <v>6.81515884399414</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.9397988319397</v>
+        <v>6.93979930877686</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G431" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.96233081817627</v>
       </c>
       <c r="G433" t="n">
-        <v>7.05998849868774</v>
+        <v>7.05998802185059</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591417312622</v>
+        <v>7.29591464996338</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.4739727973938</v>
+        <v>7.47397184371948</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538381576538</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G442" t="n">
-        <v>7.70099496841431</v>
+        <v>7.70099592208862</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491779327393</v>
+        <v>8.07491683959961</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692350387573</v>
+        <v>7.93692255020142</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504360198975</v>
+        <v>8.15504264831543</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.42945718765259</v>
+        <v>7.4294581413269</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538381576538</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G468" t="n">
-        <v>7.64312648773193</v>
+        <v>7.64312744140625</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>9.53371143341064</v>
       </c>
       <c r="G471" t="n">
-        <v>8.45328998565674</v>
+        <v>8.45328903198242</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757966995239</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209337234497</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344244003296</v>
+        <v>7.84344148635864</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G492" t="n">
-        <v>7.50513172149658</v>
+        <v>7.5051326751709</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G493" t="n">
-        <v>7.64312648773193</v>
+        <v>7.64312744140625</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.6342248916626</v>
+        <v>7.63422393798828</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.50225639343262</v>
+        <v>8.5022554397583</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>10.1763210296631</v>
       </c>
       <c r="G520" t="n">
-        <v>9.02307510375977</v>
+        <v>9.02307415008545</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G522" t="n">
-        <v>9.12990951538086</v>
+        <v>9.12990856170654</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G528" t="n">
-        <v>9.16552066802979</v>
+        <v>9.16551971435547</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833885192871</v>
+        <v>8.83833980560303</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.41990375518799</v>
+        <v>8.4199047088623</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G537" t="n">
-        <v>7.82341051101685</v>
+        <v>7.82341146469116</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196756362915</v>
+        <v>7.61196660995483</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49623012542725</v>
+        <v>7.49622917175293</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.83587837219238</v>
       </c>
       <c r="G550" t="n">
-        <v>7.83453893661499</v>
+        <v>7.83453989028931</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368829727173</v>
+        <v>7.29368877410889</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G556" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663948059082</v>
+        <v>7.7566385269165</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>8.32379913330078</v>
       </c>
       <c r="G563" t="n">
-        <v>7.38049268722534</v>
+        <v>7.38049221038818</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613481521606</v>
+        <v>7.43613386154175</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585174560547</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.1079216003418</v>
       </c>
       <c r="G584" t="n">
-        <v>7.18907928466797</v>
+        <v>7.18907976150513</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842311859131</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610431671143</v>
+        <v>7.41610336303711</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766731262207</v>
+        <v>6.99766778945923</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443929672241</v>
+        <v>7.06443977355957</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>7.92969799041748</v>
       </c>
       <c r="G596" t="n">
-        <v>7.03105354309082</v>
+        <v>7.03105306625366</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G608" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37538909912109</v>
+        <v>8.37539005279541</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>9.42326259613037</v>
       </c>
       <c r="G619" t="n">
-        <v>8.35535717010498</v>
+        <v>8.3553581237793</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.31783485412598</v>
       </c>
       <c r="G620" t="n">
-        <v>8.26187801361084</v>
+        <v>8.26187705993652</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>9.72448635101318</v>
       </c>
       <c r="G622" t="n">
-        <v>8.62244415283203</v>
+        <v>8.62244510650635</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902599334717</v>
+        <v>8.56902694702148</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>9.47848701477051</v>
       </c>
       <c r="G625" t="n">
-        <v>8.40432357788086</v>
+        <v>8.40432453155518</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.86254692077637</v>
       </c>
       <c r="G639" t="n">
-        <v>8.74485874176025</v>
+        <v>8.74485969543457</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009727478027</v>
+        <v>9.25009822845459</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>10.0181789398193</v>
       </c>
       <c r="G648" t="n">
-        <v>8.88285350799561</v>
+        <v>8.88285446166992</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>10.0608520507812</v>
       </c>
       <c r="G649" t="n">
-        <v>8.92069149017334</v>
+        <v>8.92069053649902</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G650" t="n">
-        <v>9.01639652252197</v>
+        <v>9.01639747619629</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100505828857</v>
+        <v>9.12100601196289</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G660" t="n">
-        <v>9.84659194946289</v>
+        <v>9.84659099578857</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G661" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>11.2331123352051</v>
       </c>
       <c r="G666" t="n">
-        <v>9.96010303497314</v>
+        <v>9.96010398864746</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G667" t="n">
-        <v>9.87107372283936</v>
+        <v>9.87107467651367</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>11.200478553772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.93116760253906</v>
+        <v>9.93116855621338</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139925003052</v>
+        <v>10.3139934539795</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>11.4414577484131</v>
       </c>
       <c r="G670" t="n">
-        <v>10.1448383331299</v>
+        <v>10.1448373794556</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>11.700008392334</v>
       </c>
       <c r="G683" t="n">
-        <v>10.3740882873535</v>
+        <v>10.3740873336792</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>11.9259252548218</v>
       </c>
       <c r="G689" t="n">
-        <v>10.5744018554688</v>
+        <v>10.5744028091431</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.7569122314453</v>
+        <v>10.756911277771</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.1232872009277</v>
       </c>
       <c r="G698" t="n">
-        <v>11.6360721588135</v>
+        <v>11.6360712051392</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>13.2086343765259</v>
       </c>
       <c r="G699" t="n">
-        <v>11.7117471694946</v>
+        <v>11.7117462158203</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395784378052</v>
+        <v>11.0395774841309</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364070892334</v>
+        <v>10.4364080429077</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006391525269</v>
+        <v>10.3006381988525</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>11.1377248764038</v>
       </c>
       <c r="G732" t="n">
-        <v>9.87552642822266</v>
+        <v>9.87552547454834</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>10.6607875823975</v>
       </c>
       <c r="G734" t="n">
-        <v>9.45263767242432</v>
+        <v>9.45263862609863</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580421447754</v>
+        <v>9.34580516815186</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081249237061</v>
+        <v>8.29081153869629</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219158172607</v>
+        <v>8.46219253540039</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>9.69938373565674</v>
       </c>
       <c r="G746" t="n">
-        <v>8.60018634796143</v>
+        <v>8.60018730163574</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>9.75209808349609</v>
       </c>
       <c r="G751" t="n">
-        <v>8.64692783355713</v>
+        <v>8.64692687988281</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>9.33540630340576</v>
       </c>
       <c r="G753" t="n">
-        <v>8.27745819091797</v>
+        <v>8.27745723724365</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466617584229</v>
+        <v>7.91466522216797</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G757" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.25602340698242</v>
       </c>
       <c r="G758" t="n">
-        <v>7.32039785385132</v>
+        <v>7.32039737701416</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873331069946</v>
+        <v>6.96873378753662</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>8.19577884674072</v>
       </c>
       <c r="G763" t="n">
-        <v>7.26698017120361</v>
+        <v>7.26698064804077</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G764" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096832275391</v>
+        <v>8.39096927642822</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G781" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G782" t="n">
-        <v>8.86282348632812</v>
+        <v>8.86282253265381</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G783" t="n">
-        <v>8.9451732635498</v>
+        <v>8.94517421722412</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>10.1763210296631</v>
       </c>
       <c r="G784" t="n">
-        <v>9.02307510375977</v>
+        <v>9.02307415008545</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G792" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G795" t="n">
-        <v>9.0809440612793</v>
+        <v>9.08094310760498</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232986450195</v>
+        <v>9.96232891082764</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496036529541</v>
+        <v>10.3496046066284</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371948242188</v>
+        <v>10.9371957778931</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>11.8355579376221</v>
       </c>
       <c r="G826" t="n">
-        <v>10.4942760467529</v>
+        <v>10.4942770004272</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>12.1116790771484</v>
       </c>
       <c r="G827" t="n">
-        <v>10.7391052246094</v>
+        <v>10.7391061782837</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>12.4856977462769</v>
       </c>
       <c r="G831" t="n">
-        <v>11.0707378387451</v>
+        <v>11.0707368850708</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295726776123</v>
+        <v>10.3295736312866</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271890640259</v>
+        <v>10.2271900177002</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>11.7150688171387</v>
       </c>
       <c r="G840" t="n">
-        <v>10.3874416351318</v>
+        <v>10.3874425888062</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.0564546585083</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6901388168335</v>
+        <v>10.6901397705078</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>10.836501121521</v>
       </c>
       <c r="G849" t="n">
-        <v>9.60843944549561</v>
+        <v>9.60843849182129</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G851" t="n">
-        <v>9.33912754058838</v>
+        <v>9.33912658691406</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>10.203932762146</v>
       </c>
       <c r="G854" t="n">
-        <v>9.04755687713623</v>
+        <v>9.04755783081055</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G855" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>10.4072589874268</v>
       </c>
       <c r="G856" t="n">
-        <v>9.22784042358398</v>
+        <v>9.2278413772583</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>10.5101757049561</v>
       </c>
       <c r="G860" t="n">
-        <v>9.31909465789795</v>
+        <v>9.31909561157227</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G861" t="n">
-        <v>9.25232410430908</v>
+        <v>9.25232315063477</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G864" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G869" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G871" t="n">
-        <v>9.07204151153564</v>
+        <v>9.07204055786133</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>10.582971572876</v>
       </c>
       <c r="G873" t="n">
-        <v>9.38364124298096</v>
+        <v>9.38364028930664</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>10.768726348877</v>
       </c>
       <c r="G874" t="n">
-        <v>9.54834461212158</v>
+        <v>9.5483455657959</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395576477051</v>
+        <v>9.58395671844482</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G877" t="n">
-        <v>9.33912754058838</v>
+        <v>9.33912658691406</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G879" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G880" t="n">
-        <v>9.55947303771973</v>
+        <v>9.55947208404541</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G881" t="n">
-        <v>9.60621356964111</v>
+        <v>9.60621452331543</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079113006592</v>
+        <v>9.69079208374023</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.2431526184082</v>
       </c>
       <c r="G889" t="n">
-        <v>9.96900653839111</v>
+        <v>9.9690055847168</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>11.2130298614502</v>
       </c>
       <c r="G894" t="n">
-        <v>9.94229698181152</v>
+        <v>9.94229793548584</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>11.2381324768066</v>
       </c>
       <c r="G899" t="n">
-        <v>9.96455478668213</v>
+        <v>9.96455383300781</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.4715795516968</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1715469360352</v>
+        <v>10.1715459823608</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>11.4941720962524</v>
       </c>
       <c r="G907" t="n">
-        <v>10.191577911377</v>
+        <v>10.1915788650513</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>11.5845394134521</v>
       </c>
       <c r="G908" t="n">
-        <v>10.2717037200928</v>
+        <v>10.2717046737671</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794101715088</v>
+        <v>9.99794006347656</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.1829080581665</v>
       </c>
       <c r="G912" t="n">
-        <v>9.91558837890625</v>
+        <v>9.91558933258057</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G914" t="n">
-        <v>9.20780944824219</v>
+        <v>9.2078104019165</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>10.4248304367065</v>
       </c>
       <c r="G915" t="n">
-        <v>9.24342060089111</v>
+        <v>9.24342155456543</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G916" t="n">
-        <v>8.92514228820801</v>
+        <v>8.92514324188232</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G918" t="n">
-        <v>9.12545871734619</v>
+        <v>9.12545776367188</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.9067869186401</v>
       </c>
       <c r="G933" t="n">
-        <v>9.6707592010498</v>
+        <v>9.67076015472412</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.1047735214233</v>
+        <v>10.1047744750977</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136779785156</v>
+        <v>10.1136770248413</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230527877808</v>
+        <v>10.4230537414551</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>11.1854181289673</v>
       </c>
       <c r="G945" t="n">
-        <v>9.91781520843506</v>
+        <v>9.91781425476074</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G946" t="n">
-        <v>9.87107372283936</v>
+        <v>9.87107467651367</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G947" t="n">
-        <v>9.84659194946289</v>
+        <v>9.84659099578857</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>10.4524421691895</v>
       </c>
       <c r="G951" t="n">
-        <v>9.26790428161621</v>
+        <v>9.26790332794189</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>10.4499320983887</v>
       </c>
       <c r="G952" t="n">
-        <v>9.26567840576172</v>
+        <v>9.26567935943604</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G958" t="n">
-        <v>9.16552066802979</v>
+        <v>9.16551971435547</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65963077545166</v>
+        <v>9.65963172912598</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G974" t="n">
-        <v>9.51050758361816</v>
+        <v>9.51050853729248</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G978" t="n">
-        <v>9.60621356964111</v>
+        <v>9.60621452331543</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>11.2306022644043</v>
       </c>
       <c r="G981" t="n">
-        <v>9.95787811279297</v>
+        <v>9.95787906646729</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>11.0573978424072</v>
       </c>
       <c r="G983" t="n">
-        <v>9.80430221557617</v>
+        <v>9.80430126190186</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>10.7536649703979</v>
       </c>
       <c r="G988" t="n">
-        <v>9.53499031066895</v>
+        <v>9.53498935699463</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812397003174</v>
+        <v>9.40812492370605</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>10.7536649703979</v>
       </c>
       <c r="G992" t="n">
-        <v>9.53499031066895</v>
+        <v>9.53498935699463</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>10.7135019302368</v>
       </c>
       <c r="G996" t="n">
-        <v>9.49937915802002</v>
+        <v>9.4993782043457</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G998" t="n">
-        <v>9.07204151153564</v>
+        <v>9.07204055786133</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.25232410430908</v>
+        <v>9.25232315063477</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>10.582971572876</v>
       </c>
       <c r="G1006" t="n">
-        <v>9.38364124298096</v>
+        <v>9.38364028930664</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>11.0925407409668</v>
       </c>
       <c r="G1017" t="n">
-        <v>9.83546257019043</v>
+        <v>9.83546352386475</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>11.120153427124</v>
       </c>
       <c r="G1023" t="n">
-        <v>9.85994625091553</v>
+        <v>9.85994529724121</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G1030" t="n">
-        <v>9.46154117584229</v>
+        <v>9.4615421295166</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G1032" t="n">
-        <v>9.12545871734619</v>
+        <v>9.12545776367188</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.31974697113037</v>
+        <v>8.31974601745605</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>9.51613998413086</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.43770980834961</v>
+        <v>8.43770885467529</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>9.41573238372803</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.34868144989014</v>
+        <v>8.34868049621582</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657609939575</v>
+        <v>7.71657657623291</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754726409912</v>
+        <v>7.62754821777344</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>8.3037166595459</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.36268615722656</v>
+        <v>7.36268663406372</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585174560547</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.70832395553589</v>
+        <v>6.70832443237305</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.89613008499146</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.34126901626587</v>
+        <v>4.34126853942871</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>5.16848611831665</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.58275985717773</v>
+        <v>4.58275938034058</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342178344727</v>
+        <v>5.00342130661011</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.88990926742554</v>
+        <v>4.8899097442627</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>5.89393186569214</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.22599315643311</v>
+        <v>5.22599363327026</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386211395264</v>
+        <v>5.28386259078979</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.29276514053345</v>
+        <v>5.29276561737061</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>5.47473001480103</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.85429859161377</v>
+        <v>4.85429811477661</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445489883423</v>
+        <v>4.95445537567139</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>5.55505609512329</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.92552089691162</v>
+        <v>4.92552137374878</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041345596313</v>
+        <v>5.21041393280029</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470746994019</v>
+        <v>5.11470794677734</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.92329597473145</v>
+        <v>4.92329549789429</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>4.35400009155273</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>9729209</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>4.37099981307983</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>4.31400012969971</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>4.32600021362305</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>4.35400009155273</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>4.35400009155273</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>4.32200002670288</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>4.45499992370605</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>18773408</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>4.46799993515015</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>4.2810001373291</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>4.44999980926514</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>4.44999980926514</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>4.37599992752075</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>13242016</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>4.44299983978271</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>4.35699987411499</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>4.36999988555908</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>4.36999988555908</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>4.38100004196167</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>12756118</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>4.46600008010864</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>4.34600019454956</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>4.38000011444092</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>4.4060001373291</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>19600135</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>4.57000017166138</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>4.40799999237061</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>21300928</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>4.66300010681152</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>4.56899976730347</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>4.64699983596802</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>23.2093391418457</v>
       </c>
       <c r="G3" t="n">
-        <v>20.5791053771973</v>
+        <v>20.5791072845459</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540729522705</v>
+        <v>18.9540748596191</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.8786602020264</v>
+        <v>19.878662109375</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>22.1665782928467</v>
       </c>
       <c r="G9" t="n">
-        <v>19.6545181274414</v>
+        <v>19.65452003479</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811958312988</v>
+        <v>17.5811977386475</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460289001465</v>
+        <v>15.7460269927979</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.8214406967163</v>
+        <v>14.821439743042</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552736282349</v>
+        <v>13.9552726745605</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.806058883667</v>
       </c>
       <c r="G19" t="n">
-        <v>12.2414674758911</v>
+        <v>12.2414665222168</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087121963501</v>
+        <v>12.6087112426758</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G21" t="n">
-        <v>12.6977405548096</v>
+        <v>12.6977415084839</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.358302116394</v>
       </c>
       <c r="G22" t="n">
-        <v>12.7311267852783</v>
+        <v>12.7311277389526</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.8813648223877</v>
       </c>
       <c r="G23" t="n">
-        <v>12.3082389831543</v>
+        <v>12.30823802948</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>13.5048360824585</v>
       </c>
       <c r="G24" t="n">
-        <v>11.9743804931641</v>
+        <v>11.9743814468384</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G29" t="n">
-        <v>8.0571117401123</v>
+        <v>8.05711078643799</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393510818481</v>
+        <v>6.74393558502197</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.8774790763855</v>
+        <v>6.87747859954834</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51180982589722</v>
+        <v>7.51181030273438</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36045980453491</v>
+        <v>7.36046028137207</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.67679214477539</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58015537261963</v>
+        <v>8.58015632629395</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.96546459197998</v>
       </c>
       <c r="G46" t="n">
-        <v>8.83611392974854</v>
+        <v>8.83611297607422</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.07714366912842</v>
+        <v>8.0771427154541</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811340332031</v>
+        <v>7.98811292648315</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683395385742</v>
+        <v>8.58683300018311</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G53" t="n">
-        <v>8.29526329040527</v>
+        <v>8.29526424407959</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.3175220489502</v>
+        <v>8.31752109527588</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G57" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218772888184</v>
+        <v>7.75218820571899</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.34488010406494</v>
+        <v>7.34487962722778</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.93628597259521</v>
       </c>
       <c r="G62" t="n">
-        <v>7.92356824874878</v>
+        <v>7.92356872558594</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870809555054</v>
+        <v>7.65870761871338</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973592758179</v>
+        <v>6.89973640441895</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.93220806121826</v>
       </c>
       <c r="G67" t="n">
-        <v>7.03327941894531</v>
+        <v>7.03327894210815</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365732192993</v>
+        <v>7.27365779876709</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.86347389221191</v>
+        <v>7.86347341537476</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09939956665039</v>
+        <v>8.09940052032471</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86570024490356</v>
+        <v>7.86569976806641</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G75" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.55128288269043</v>
       </c>
       <c r="G81" t="n">
-        <v>8.46886920928955</v>
+        <v>8.46887016296387</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912178039551</v>
+        <v>8.62912082672119</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G83" t="n">
-        <v>9.68188762664795</v>
+        <v>9.68188858032227</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G86" t="n">
-        <v>8.54009342193604</v>
+        <v>8.54009246826172</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.20487594604492</v>
       </c>
       <c r="G91" t="n">
-        <v>8.16172027587891</v>
+        <v>8.16171932220459</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.2685546875</v>
+        <v>8.26855373382568</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542007446289</v>
+        <v>8.39542102813721</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G96" t="n">
-        <v>8.31974601745605</v>
+        <v>8.31974697113037</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588800430298</v>
+        <v>7.98588752746582</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701738357544</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.14212131500244</v>
       </c>
       <c r="G101" t="n">
-        <v>8.10607814788818</v>
+        <v>8.10607719421387</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.3303861618042</v>
       </c>
       <c r="G105" t="n">
-        <v>8.27300643920898</v>
+        <v>8.27300548553467</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G106" t="n">
-        <v>8.18842887878418</v>
+        <v>8.1884298324585</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889633178711</v>
+        <v>7.77889537811279</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701738357544</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.5261812210083</v>
       </c>
       <c r="G111" t="n">
-        <v>8.44661331176758</v>
+        <v>8.44661235809326</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837268829346</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.28018188476562</v>
       </c>
       <c r="G114" t="n">
-        <v>8.22849178314209</v>
+        <v>8.22849273681641</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325325012207</v>
+        <v>7.72325372695923</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660659790039</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808242797852</v>
+        <v>7.96808195114136</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G118" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76489067077637</v>
+        <v>8.76488971710205</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G123" t="n">
-        <v>9.00749492645264</v>
+        <v>9.00749397277832</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.5919361114502</v>
+        <v>7.59193563461304</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G131" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.44083404541016</v>
       </c>
       <c r="G134" t="n">
-        <v>8.37093734741211</v>
+        <v>8.37093830108643</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.7114725112915</v>
+        <v>8.71147346496582</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420352935791</v>
+        <v>9.03420257568359</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G137" t="n">
-        <v>9.25454998016357</v>
+        <v>9.25454902648926</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G138" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856620788574</v>
+        <v>9.68856430053711</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>10.6934204101562</v>
       </c>
       <c r="G146" t="n">
-        <v>9.4815731048584</v>
+        <v>9.48157215118408</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427219390869</v>
+        <v>9.78427124023438</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G151" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.3881196975708</v>
       </c>
       <c r="G152" t="n">
-        <v>8.32419681549072</v>
+        <v>8.32419776916504</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228832244873</v>
+        <v>8.52228736877441</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.0056276321411</v>
       </c>
       <c r="G156" t="n">
-        <v>8.87172508239746</v>
+        <v>8.87172603607178</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G157" t="n">
-        <v>8.7760181427002</v>
+        <v>8.77601909637451</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>10.3269319534302</v>
       </c>
       <c r="G159" t="n">
-        <v>9.15661716461182</v>
+        <v>9.15661811828613</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.98303604125977</v>
       </c>
       <c r="G164" t="n">
-        <v>8.85169315338135</v>
+        <v>8.85169410705566</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122570037842</v>
+        <v>9.26122665405273</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G169" t="n">
-        <v>9.08094310760498</v>
+        <v>9.0809440612793</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548778533936</v>
+        <v>9.14548873901367</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G176" t="n">
-        <v>9.2078104019165</v>
+        <v>9.20780944824219</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G179" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359874725342</v>
+        <v>7.94359827041626</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.07936668395996</v>
       </c>
       <c r="G184" t="n">
-        <v>8.05043315887451</v>
+        <v>8.05043411254883</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.7922511100769</v>
+        <v>7.79224967956543</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798711776733</v>
+        <v>7.90798759460449</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.73883295059204</v>
+        <v>7.7388334274292</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G192" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G197" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473293304443</v>
+        <v>8.66473388671875</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G199" t="n">
-        <v>8.94294929504395</v>
+        <v>8.94294834136963</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.063362121582</v>
       </c>
       <c r="G200" t="n">
-        <v>8.92291736602783</v>
+        <v>8.92291641235352</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.1662797927856</v>
       </c>
       <c r="G202" t="n">
-        <v>9.0141716003418</v>
+        <v>9.01417064666748</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.8139095306396</v>
       </c>
       <c r="G206" t="n">
-        <v>9.58840847015381</v>
+        <v>9.58840751647949</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856620788574</v>
+        <v>9.68856430053711</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.9519701004028</v>
       </c>
       <c r="G208" t="n">
-        <v>9.71082210540771</v>
+        <v>9.71082305908203</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G209" t="n">
-        <v>9.68188762664795</v>
+        <v>9.68188858032227</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G212" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.34645557403564</v>
+        <v>8.34645462036133</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.22244834899902</v>
       </c>
       <c r="G216" t="n">
-        <v>8.17730140686035</v>
+        <v>8.17730045318604</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G220" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G221" t="n">
-        <v>8.73373126983643</v>
+        <v>8.73373031616211</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.2240142822266</v>
       </c>
       <c r="G225" t="n">
-        <v>9.06536293029785</v>
+        <v>9.06536388397217</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072246551514</v>
+        <v>8.94072341918945</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.1185855865479</v>
       </c>
       <c r="G229" t="n">
-        <v>8.97188091278076</v>
+        <v>8.97188186645508</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.2215042114258</v>
       </c>
       <c r="G231" t="n">
-        <v>9.06313800811768</v>
+        <v>9.06313705444336</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.6457271575928</v>
       </c>
       <c r="G236" t="n">
-        <v>9.439284324646</v>
+        <v>9.43928527832031</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640228271484</v>
+        <v>9.72640323638916</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.6507472991943</v>
       </c>
       <c r="G238" t="n">
-        <v>9.4437370300293</v>
+        <v>9.44373607635498</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.182674407959</v>
+        <v>10.1826753616333</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.6347427368164</v>
       </c>
       <c r="G241" t="n">
-        <v>10.316219329834</v>
+        <v>10.3162183761597</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.4088249206543</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1159029006958</v>
+        <v>10.1159038543701</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G246" t="n">
-        <v>10.5721759796143</v>
+        <v>10.5721769332886</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788536071777</v>
+        <v>10.5788545608521</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12.8019819259644</v>
       </c>
       <c r="G250" t="n">
-        <v>11.3511791229248</v>
+        <v>11.3511781692505</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.0906553268433</v>
       </c>
       <c r="G254" t="n">
-        <v>11.6071376800537</v>
+        <v>11.607138633728</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295513153076</v>
+        <v>11.7295522689819</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076099395752</v>
+        <v>11.9076108932495</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.0319766998291</v>
       </c>
       <c r="G258" t="n">
-        <v>12.4417819976807</v>
+        <v>12.441782951355</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G259" t="n">
-        <v>12.6977405548096</v>
+        <v>12.6977415084839</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195261001587</v>
+        <v>12.4195251464844</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858243942261</v>
+        <v>12.1858253479004</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.3165721893311</v>
       </c>
       <c r="G263" t="n">
-        <v>11.8074531555176</v>
+        <v>11.8074522018433</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>12.7517786026001</v>
       </c>
       <c r="G264" t="n">
-        <v>11.3066654205322</v>
+        <v>11.3066644668579</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>12.7392282485962</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2955360412598</v>
+        <v>11.2955369949341</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351257324219</v>
+        <v>11.0351266860962</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.5007591247559</v>
       </c>
       <c r="G274" t="n">
-        <v>11.0840921401978</v>
+        <v>11.0840930938721</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963228225708</v>
+        <v>11.7963237762451</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960083007812</v>
+        <v>11.5960092544556</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.1995363235474</v>
       </c>
       <c r="G278" t="n">
-        <v>10.8170070648193</v>
+        <v>10.817006111145</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G280" t="n">
-        <v>10.5276622772217</v>
+        <v>10.5276613235474</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141492843628</v>
+        <v>10.4141502380371</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.251672744751</v>
+        <v>10.2516717910767</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.3711729049683</v>
       </c>
       <c r="G285" t="n">
-        <v>10.0825176239014</v>
+        <v>10.0825185775757</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.39857006073</v>
+        <v>10.3985710144043</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651857376099</v>
+        <v>10.3651847839355</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>11.3787031173706</v>
       </c>
       <c r="G290" t="n">
-        <v>10.0891962051392</v>
+        <v>10.0891952514648</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939605712891</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.6874570846558</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3629579544067</v>
+        <v>10.3629589080811</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G297" t="n">
-        <v>9.36361026763916</v>
+        <v>9.36360931396484</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486354827881</v>
+        <v>9.45486450195312</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5428085327148</v>
       </c>
       <c r="G303" t="n">
-        <v>9.34803009033203</v>
+        <v>9.34802913665771</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G305" t="n">
-        <v>9.25454998016357</v>
+        <v>9.25454902648926</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G306" t="n">
-        <v>9.00749492645264</v>
+        <v>9.00749397277832</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.2491159439087</v>
       </c>
       <c r="G308" t="n">
-        <v>9.08762073516846</v>
+        <v>9.08761978149414</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520614624023</v>
+        <v>8.96520709991455</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.3244218826294</v>
       </c>
       <c r="G311" t="n">
-        <v>9.15439224243164</v>
+        <v>9.15439128875732</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539390563965</v>
+        <v>9.08539485931396</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10.6808700561523</v>
       </c>
       <c r="G322" t="n">
-        <v>9.47044467926025</v>
+        <v>9.47044563293457</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981948852539</v>
+        <v>9.77981853485107</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>10.2691984176636</v>
       </c>
       <c r="G331" t="n">
-        <v>9.10542678833008</v>
+        <v>9.10542583465576</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>10.0106477737427</v>
       </c>
       <c r="G332" t="n">
-        <v>8.87617588043213</v>
+        <v>8.87617683410645</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10.0784225463867</v>
       </c>
       <c r="G333" t="n">
-        <v>8.93626976013184</v>
+        <v>8.93627071380615</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.7671594619751</v>
       </c>
       <c r="G335" t="n">
-        <v>8.66028118133545</v>
+        <v>8.66028213500977</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.20335865020752</v>
+        <v>9.2033576965332</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G339" t="n">
-        <v>8.94294929504395</v>
+        <v>8.94294834136963</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837268829346</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G346" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10.003116607666</v>
       </c>
       <c r="G349" t="n">
-        <v>8.86949920654297</v>
+        <v>8.86949825286865</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.80481243133545</v>
       </c>
       <c r="G354" t="n">
-        <v>8.6936674118042</v>
+        <v>8.69366836547852</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.36301803588867</v>
       </c>
       <c r="G359" t="n">
-        <v>8.30194091796875</v>
+        <v>8.30193996429443</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G362" t="n">
-        <v>8.03485298156738</v>
+        <v>8.03485488891602</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033975601196</v>
+        <v>7.9903392791748</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>8.97142791748047</v>
       </c>
       <c r="G364" t="n">
-        <v>7.95472812652588</v>
+        <v>7.95472764968872</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G365" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G366" t="n">
-        <v>7.66093301773071</v>
+        <v>7.66093397140503</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G370" t="n">
-        <v>8.0571117401123</v>
+        <v>8.05711078643799</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133756637573</v>
+        <v>7.21133661270142</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G378" t="n">
-        <v>7.18017721176147</v>
+        <v>7.18017673492432</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.07779979705811</v>
       </c>
       <c r="G380" t="n">
-        <v>7.16237163543701</v>
+        <v>7.16237115859985</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914218902588</v>
+        <v>7.22914266586304</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817197799683</v>
+        <v>7.31817245483398</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390893936157</v>
+        <v>7.43390846252441</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842359542847</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757871627808</v>
+        <v>7.64757919311523</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G408" t="n">
-        <v>7.58525800704956</v>
+        <v>7.5852575302124</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428731918335</v>
+        <v>7.67428636550903</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.5748176574707</v>
       </c>
       <c r="G411" t="n">
-        <v>7.60306358337402</v>
+        <v>7.60306453704834</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>8.53967475891113</v>
       </c>
       <c r="G412" t="n">
-        <v>7.57190370559692</v>
+        <v>7.57190418243408</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701162338257</v>
+        <v>7.28701210021973</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G416" t="n">
-        <v>7.26475429534912</v>
+        <v>7.26475477218628</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.15812587738037</v>
       </c>
       <c r="G417" t="n">
-        <v>7.23359489440918</v>
+        <v>7.23359441757202</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7.93220806121826</v>
       </c>
       <c r="G420" t="n">
-        <v>7.03327941894531</v>
+        <v>7.03327894210815</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.61592388153076</v>
       </c>
       <c r="G422" t="n">
-        <v>6.75283813476562</v>
+        <v>6.75283861160278</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.40004777908325</v>
       </c>
       <c r="G426" t="n">
-        <v>6.56142616271973</v>
+        <v>6.56142663955688</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.93979835510254</v>
+        <v>6.9397988319397</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.76151514053345</v>
       </c>
       <c r="G429" t="n">
-        <v>6.88192987442017</v>
+        <v>6.88193035125732</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.00751399993896</v>
       </c>
       <c r="G430" t="n">
-        <v>7.10005044937134</v>
+        <v>7.1000509262085</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591417312622</v>
+        <v>7.29591369628906</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409908294678</v>
+        <v>7.55409860610962</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G439" t="n">
-        <v>7.58525800704956</v>
+        <v>7.5852575302124</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.66538429260254</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491779327393</v>
+        <v>8.07491683959961</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.10195827484131</v>
       </c>
       <c r="G445" t="n">
-        <v>8.07046604156494</v>
+        <v>8.07046508789062</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G449" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692350387573</v>
+        <v>7.93692302703857</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504264831543</v>
+        <v>8.15504360198975</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.15216159820557</v>
       </c>
       <c r="G455" t="n">
-        <v>8.1149787902832</v>
+        <v>8.11497974395752</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.82081699371338</v>
       </c>
       <c r="G456" t="n">
-        <v>7.82118463516235</v>
+        <v>7.82118511199951</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G457" t="n">
-        <v>7.77221775054932</v>
+        <v>7.77221822738647</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.85093879699707</v>
       </c>
       <c r="G458" t="n">
-        <v>7.84789371490479</v>
+        <v>7.84789323806763</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.92122364044189</v>
       </c>
       <c r="G459" t="n">
-        <v>7.91021251678467</v>
+        <v>7.91021299362183</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G460" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939523696899</v>
+        <v>7.38939476013184</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.04673385620117</v>
       </c>
       <c r="G465" t="n">
-        <v>8.02150058746338</v>
+        <v>8.02149963378906</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.66538429260254</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479150772095</v>
+        <v>7.99479103088379</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G470" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.54677104949951</v>
+        <v>8.5467700958252</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.49354839324951</v>
       </c>
       <c r="G478" t="n">
-        <v>8.41767883300781</v>
+        <v>8.4176778793335</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757871627808</v>
+        <v>7.64757919311523</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576314926147</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344148635864</v>
+        <v>7.84344244003296</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>8.60494041442871</v>
       </c>
       <c r="G488" t="n">
-        <v>7.62977313995361</v>
+        <v>7.62977266311646</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>8.44930839538574</v>
       </c>
       <c r="G497" t="n">
-        <v>7.49177837371826</v>
+        <v>7.4917778968811</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G500" t="n">
-        <v>7.77221775054932</v>
+        <v>7.77221822738647</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996185302734</v>
+        <v>7.74996280670166</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G505" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.11199855804443</v>
       </c>
       <c r="G506" t="n">
-        <v>8.07936763763428</v>
+        <v>8.07936859130859</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.34795665740967</v>
       </c>
       <c r="G508" t="n">
-        <v>8.2885856628418</v>
+        <v>8.28858661651611</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.61403846740723</v>
       </c>
       <c r="G510" t="n">
-        <v>8.52451419830322</v>
+        <v>8.52451324462891</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109508514404</v>
+        <v>8.47109603881836</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.5067081451416</v>
+        <v>8.50670719146729</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.5022554397583</v>
+        <v>8.50225639343262</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G514" t="n">
-        <v>8.73373126983643</v>
+        <v>8.73373031616211</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.1813411712646</v>
       </c>
       <c r="G524" t="n">
-        <v>9.02752685546875</v>
+        <v>9.02752590179443</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G529" t="n">
-        <v>9.04087924957275</v>
+        <v>9.04088020324707</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G530" t="n">
-        <v>9.04087924957275</v>
+        <v>9.04088020324707</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833980560303</v>
+        <v>8.83833885192871</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.60399723052979</v>
       </c>
       <c r="G532" t="n">
-        <v>8.51560974121094</v>
+        <v>8.51561069488525</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.24852466583252</v>
+        <v>8.2485237121582</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G538" t="n">
-        <v>8.03485298156738</v>
+        <v>8.03485488891602</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660659790039</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G545" t="n">
-        <v>7.66093301773071</v>
+        <v>7.66093397140503</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083818435669</v>
+        <v>7.60083913803101</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.76331663131714</v>
+        <v>7.76331615447998</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368877410889</v>
+        <v>7.29368829727173</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.56979656219482</v>
       </c>
       <c r="G558" t="n">
-        <v>7.5986123085022</v>
+        <v>7.59861183166504</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.7566385269165</v>
+        <v>7.75663900375366</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218772888184</v>
+        <v>7.75218820571899</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936330795288</v>
+        <v>7.36936378479004</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585079193115</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>8.43173694610596</v>
       </c>
       <c r="G568" t="n">
-        <v>7.47619867324829</v>
+        <v>7.47619771957397</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>8.16063594818115</v>
       </c>
       <c r="G569" t="n">
-        <v>7.23582029342651</v>
+        <v>7.23581981658936</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.17820739746094</v>
       </c>
       <c r="G570" t="n">
-        <v>7.25140047073364</v>
+        <v>7.25139999389648</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.03512573242188</v>
       </c>
       <c r="G571" t="n">
-        <v>7.12453317642212</v>
+        <v>7.12453365325928</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G578" t="n">
-        <v>6.98876523971558</v>
+        <v>6.98876571655273</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G585" t="n">
-        <v>7.18017721176147</v>
+        <v>7.18017673492432</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842359542847</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610431671143</v>
+        <v>7.41610383987427</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G590" t="n">
-        <v>7.26475429534912</v>
+        <v>7.26475477218628</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G591" t="n">
-        <v>6.98876523971558</v>
+        <v>6.98876571655273</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766778945923</v>
+        <v>6.99766731262207</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443929672241</v>
+        <v>7.06443881988525</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.06022834777832</v>
       </c>
       <c r="G599" t="n">
-        <v>7.14679145812988</v>
+        <v>7.14679098129272</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939523696899</v>
+        <v>7.38939476013184</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.55222606658936</v>
       </c>
       <c r="G603" t="n">
-        <v>7.58303260803223</v>
+        <v>7.58303213119507</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.83242416381836</v>
       </c>
       <c r="G605" t="n">
-        <v>8.7181510925293</v>
+        <v>8.71815013885498</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G607" t="n">
-        <v>8.54009342193604</v>
+        <v>8.54009246826172</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37538909912109</v>
+        <v>8.37539005279541</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065380096436</v>
+        <v>8.19065475463867</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.85250568389893</v>
       </c>
       <c r="G623" t="n">
-        <v>8.7359561920166</v>
+        <v>8.73595523834229</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902599334717</v>
+        <v>8.56902694702148</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G627" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G629" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>9.36552906036377</v>
       </c>
       <c r="G630" t="n">
-        <v>8.30416679382324</v>
+        <v>8.30416774749756</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G636" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.7114725112915</v>
+        <v>8.71147346496582</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>10.0608520507812</v>
       </c>
       <c r="G649" t="n">
-        <v>8.92069053649902</v>
+        <v>8.92069149017334</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G651" t="n">
-        <v>9.0564603805542</v>
+        <v>9.05646133422852</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100601196289</v>
+        <v>9.12100505828857</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>11.401294708252</v>
       </c>
       <c r="G658" t="n">
-        <v>10.109227180481</v>
+        <v>10.1092262268066</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G661" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>11.2331123352051</v>
       </c>
       <c r="G666" t="n">
-        <v>9.96010398864746</v>
+        <v>9.96010303497314</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>11.200478553772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.93116855621338</v>
+        <v>9.93116760253906</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139925003052</v>
+        <v>10.3139934539795</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G671" t="n">
-        <v>9.80652809143066</v>
+        <v>9.80652904510498</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.6648645401001</v>
       </c>
       <c r="G674" t="n">
-        <v>10.3429260253906</v>
+        <v>10.3429269790649</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939605712891</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>11.3711729049683</v>
       </c>
       <c r="G679" t="n">
-        <v>10.0825176239014</v>
+        <v>10.0825185775757</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>11.700008392334</v>
       </c>
       <c r="G683" t="n">
-        <v>10.3740873336792</v>
+        <v>10.3740882873535</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G684" t="n">
-        <v>10.3340244293213</v>
+        <v>10.334023475647</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99348926544189</v>
+        <v>9.99349021911621</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694797515869</v>
+        <v>10.2694787979126</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>11.5017032623291</v>
       </c>
       <c r="G688" t="n">
-        <v>10.1982555389404</v>
+        <v>10.1982564926147</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>11.9259252548218</v>
       </c>
       <c r="G689" t="n">
-        <v>10.5744028091431</v>
+        <v>10.5744018554688</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>11.328498840332</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0446805953979</v>
+        <v>10.0446796417236</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>12.0489253997803</v>
       </c>
       <c r="G692" t="n">
-        <v>10.6834630966187</v>
+        <v>10.683464050293</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G693" t="n">
-        <v>10.8259086608887</v>
+        <v>10.8259077072144</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.756911277771</v>
+        <v>10.7569122314453</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>12.0238227844238</v>
       </c>
       <c r="G696" t="n">
-        <v>10.6612062454224</v>
+        <v>10.661205291748</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>12.4580860137939</v>
       </c>
       <c r="G697" t="n">
-        <v>11.0462560653687</v>
+        <v>11.0462551116943</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.1232872009277</v>
       </c>
       <c r="G698" t="n">
-        <v>11.6360712051392</v>
+        <v>11.6360721588135</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>13.233736038208</v>
       </c>
       <c r="G700" t="n">
-        <v>11.7340030670166</v>
+        <v>11.7340040206909</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>13.7558555603027</v>
       </c>
       <c r="G704" t="n">
-        <v>12.1969528198242</v>
+        <v>12.1969537734985</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856676101685</v>
+        <v>12.0856685638428</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.032919883728</v>
       </c>
       <c r="G706" t="n">
-        <v>11.555944442749</v>
+        <v>11.5559453964233</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>12.7618188858032</v>
       </c>
       <c r="G709" t="n">
-        <v>11.3155660629272</v>
+        <v>11.3155679702759</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395765304565</v>
+        <v>11.0395784378052</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>12.7065954208374</v>
       </c>
       <c r="G712" t="n">
-        <v>11.2666015625</v>
+        <v>11.2666025161743</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349679946899</v>
+        <v>10.9349699020386</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>11.8004150390625</v>
       </c>
       <c r="G715" t="n">
-        <v>10.4631156921387</v>
+        <v>10.463116645813</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364080429077</v>
+        <v>10.4364070892334</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G719" t="n">
-        <v>10.549919128418</v>
+        <v>10.5499200820923</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G720" t="n">
-        <v>10.5721759796143</v>
+        <v>10.5721769332886</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G722" t="n">
-        <v>10.5721759796143</v>
+        <v>10.5721769332886</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>11.7025184631348</v>
       </c>
       <c r="G727" t="n">
-        <v>10.3763132095337</v>
+        <v>10.376314163208</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006391525269</v>
+        <v>10.3006381988525</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>11.1251735687256</v>
       </c>
       <c r="G731" t="n">
-        <v>9.86439800262451</v>
+        <v>9.8643970489502</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>11.1377248764038</v>
       </c>
       <c r="G732" t="n">
-        <v>9.87552547454834</v>
+        <v>9.87552642822266</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580421447754</v>
+        <v>9.34580516815186</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G737" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G738" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081058502197</v>
+        <v>8.29081249237061</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889633178711</v>
+        <v>7.77889537811279</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>9.65169143676758</v>
       </c>
       <c r="G742" t="n">
-        <v>8.55790042877197</v>
+        <v>8.55789947509766</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219253540039</v>
+        <v>8.46219158172607</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.65922069549561</v>
       </c>
       <c r="G745" t="n">
-        <v>8.5645751953125</v>
+        <v>8.56457614898682</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>10.0307302474976</v>
       </c>
       <c r="G748" t="n">
-        <v>8.89398384094238</v>
+        <v>8.89398288726807</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G750" t="n">
-        <v>8.18842887878418</v>
+        <v>8.1884298324585</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G754" t="n">
-        <v>8.29526329040527</v>
+        <v>8.29526424407959</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.8122820854187</v>
+        <v>7.81228256225586</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.25602340698242</v>
       </c>
       <c r="G758" t="n">
-        <v>7.32039737701416</v>
+        <v>7.32039785385132</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>8.17318725585938</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24694871902466</v>
+        <v>7.24694919586182</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>8.12800407409668</v>
       </c>
       <c r="G761" t="n">
-        <v>7.20688629150391</v>
+        <v>7.20688581466675</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873378753662</v>
+        <v>6.96873331069946</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>8.19577884674072</v>
       </c>
       <c r="G763" t="n">
-        <v>7.26698064804077</v>
+        <v>7.26698017120361</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.37400245666504</v>
       </c>
       <c r="G765" t="n">
-        <v>7.42500638961792</v>
+        <v>7.42500686645508</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576314926147</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9.12957000732422</v>
       </c>
       <c r="G767" t="n">
-        <v>8.09494781494141</v>
+        <v>8.09494876861572</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096832275391</v>
+        <v>8.39096927642822</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G778" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G779" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>10.3445043563843</v>
       </c>
       <c r="G787" t="n">
-        <v>9.17219829559326</v>
+        <v>9.17219924926758</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G788" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>10.4298496246338</v>
       </c>
       <c r="G789" t="n">
-        <v>9.24787139892578</v>
+        <v>9.2478723526001</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G795" t="n">
-        <v>9.08094310760498</v>
+        <v>9.0809440612793</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G796" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>10.7963380813599</v>
       </c>
       <c r="G797" t="n">
-        <v>9.57282733917236</v>
+        <v>9.57282638549805</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>10.6557683944702</v>
       </c>
       <c r="G800" t="n">
-        <v>9.44818878173828</v>
+        <v>9.44818782806396</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>10.6833801269531</v>
       </c>
       <c r="G801" t="n">
-        <v>9.47266960144043</v>
+        <v>9.47267055511475</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>10.8440322875977</v>
       </c>
       <c r="G803" t="n">
-        <v>9.61511611938477</v>
+        <v>9.61511707305908</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746685028076</v>
+        <v>9.69746875762939</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232891082764</v>
+        <v>9.96232986450195</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496055603027</v>
+        <v>10.3496036529541</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>11.8882722854614</v>
       </c>
       <c r="G809" t="n">
-        <v>10.5410165786743</v>
+        <v>10.541015625</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G812" t="n">
-        <v>10.5276622772217</v>
+        <v>10.5276613235474</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.2572708129883</v>
       </c>
       <c r="G814" t="n">
-        <v>10.8681983947754</v>
+        <v>10.8681974411011</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.3150053024292</v>
       </c>
       <c r="G815" t="n">
-        <v>10.9193887710571</v>
+        <v>10.9193897247314</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371948242188</v>
+        <v>10.9371957778931</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G820" t="n">
-        <v>10.8259086608887</v>
+        <v>10.8259077072144</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>11.5368452072144</v>
       </c>
       <c r="G822" t="n">
-        <v>10.2294158935547</v>
+        <v>10.2294149398804</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G825" t="n">
-        <v>10.3340244293213</v>
+        <v>10.334023475647</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147792816162</v>
+        <v>10.8147811889648</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295736312866</v>
+        <v>10.3295726776123</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.0564546585083</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6901397705078</v>
+        <v>10.6901388168335</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G842" t="n">
-        <v>10.549919128418</v>
+        <v>10.5499200820923</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>11.8154773712158</v>
       </c>
       <c r="G843" t="n">
-        <v>10.4764709472656</v>
+        <v>10.4764719009399</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>11.3912544250488</v>
       </c>
       <c r="G844" t="n">
-        <v>10.100323677063</v>
+        <v>10.1003246307373</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>11.3385400772095</v>
       </c>
       <c r="G846" t="n">
-        <v>10.0535831451416</v>
+        <v>10.0535840988159</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>10.203932762146</v>
       </c>
       <c r="G854" t="n">
-        <v>9.04755783081055</v>
+        <v>9.04755687713623</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G855" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G858" t="n">
-        <v>9.2701301574707</v>
+        <v>9.27012920379639</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G863" t="n">
-        <v>8.7760181427002</v>
+        <v>8.77601909637451</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>9.62156772613525</v>
       </c>
       <c r="G868" t="n">
-        <v>8.53118896484375</v>
+        <v>8.53118991851807</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>10.768726348877</v>
       </c>
       <c r="G874" t="n">
-        <v>9.5483455657959</v>
+        <v>9.54834461212158</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395671844482</v>
+        <v>9.58395576477051</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G878" t="n">
-        <v>9.2701301574707</v>
+        <v>9.27012920379639</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079208374023</v>
+        <v>9.69079113006592</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0498676300049</v>
       </c>
       <c r="G887" t="n">
-        <v>9.7976245880127</v>
+        <v>9.79762649536133</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.2431526184082</v>
       </c>
       <c r="G889" t="n">
-        <v>9.96900653839111</v>
+        <v>9.9690055847168</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746685028076</v>
+        <v>9.69746875762939</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>11.2130298614502</v>
       </c>
       <c r="G894" t="n">
-        <v>9.94229602813721</v>
+        <v>9.94229698181152</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070013046265</v>
+        <v>10.1070003509521</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>11.2381324768066</v>
       </c>
       <c r="G899" t="n">
-        <v>9.96455574035645</v>
+        <v>9.96455478668213</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>11.1603164672852</v>
       </c>
       <c r="G901" t="n">
-        <v>9.89555835723877</v>
+        <v>9.89555740356445</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304798126221</v>
+        <v>9.71304893493652</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>11.0423374176025</v>
       </c>
       <c r="G905" t="n">
-        <v>9.79094886779785</v>
+        <v>9.79094791412354</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G910" t="n">
-        <v>9.75088596343994</v>
+        <v>9.75088500976562</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794006347656</v>
+        <v>9.99794101715088</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.1829080581665</v>
       </c>
       <c r="G912" t="n">
-        <v>9.91558933258057</v>
+        <v>9.91558837890625</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G914" t="n">
-        <v>9.2078104019165</v>
+        <v>9.20780944824219</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>10.3721160888672</v>
       </c>
       <c r="G917" t="n">
-        <v>9.19668006896973</v>
+        <v>9.19668102264404</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G919" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>9.84497547149658</v>
       </c>
       <c r="G921" t="n">
-        <v>8.72927856445312</v>
+        <v>8.72927951812744</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.95185089111328</v>
+        <v>8.9518518447876</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.4474220275879</v>
       </c>
       <c r="G925" t="n">
-        <v>9.26345252990723</v>
+        <v>9.26345348358154</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>10.7586851119995</v>
       </c>
       <c r="G930" t="n">
-        <v>9.53944206237793</v>
+        <v>9.53944110870361</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.9067869186401</v>
       </c>
       <c r="G933" t="n">
-        <v>9.67076015472412</v>
+        <v>9.6707592010498</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G934" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G937" t="n">
-        <v>9.80652809143066</v>
+        <v>9.80652904510498</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.104775428772</v>
+        <v>10.1047744750977</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136770248413</v>
+        <v>10.1136779785156</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403875350952</v>
+        <v>10.1403865814209</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>11.2155408859253</v>
       </c>
       <c r="G944" t="n">
-        <v>9.94452381134033</v>
+        <v>9.94452285766602</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>11.1854181289673</v>
       </c>
       <c r="G945" t="n">
-        <v>9.91781425476074</v>
+        <v>9.91781520843506</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.881685256958</v>
       </c>
       <c r="G948" t="n">
-        <v>9.64850234985352</v>
+        <v>9.64850330352783</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G950" t="n">
-        <v>9.36361026763916</v>
+        <v>9.36360931396484</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.92736911773682</v>
+        <v>8.92736721038818</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00972080230713</v>
+        <v>9.00971984863281</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G962" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G964" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>10.6557683944702</v>
       </c>
       <c r="G971" t="n">
-        <v>9.44818878173828</v>
+        <v>9.44818782806396</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65963077545166</v>
+        <v>9.65962982177734</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>11.1904392242432</v>
       </c>
       <c r="G979" t="n">
-        <v>9.92226600646973</v>
+        <v>9.92226696014404</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812492370605</v>
+        <v>9.40812397003174</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G999" t="n">
-        <v>9.0564603805542</v>
+        <v>9.05646133422852</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>10.427339553833</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.24564552307129</v>
+        <v>9.24564647674561</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G1004" t="n">
-        <v>9.36361026763916</v>
+        <v>9.36360931396484</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467578887939</v>
+        <v>9.33467674255371</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.5616979598999</v>
+        <v>9.56169891357422</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G1014" t="n">
-        <v>9.75088596343994</v>
+        <v>9.75088500976562</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G1016" t="n">
-        <v>9.75088596343994</v>
+        <v>9.75088500976562</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>11.1728668212891</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.90668487548828</v>
+        <v>9.9066858291626</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>11.1678466796875</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.90223407745361</v>
+        <v>9.90223503112793</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>11.1251735687256</v>
       </c>
       <c r="G1028" t="n">
-        <v>9.86439800262451</v>
+        <v>9.8643970489502</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G1031" t="n">
-        <v>9.25454998016357</v>
+        <v>9.25454902648926</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.31974601745605</v>
+        <v>8.31974697113037</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>9.75962924957275</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.65360546112061</v>
+        <v>8.65360450744629</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.34645557403564</v>
+        <v>8.34645462036133</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>9.63411903381348</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.54231929779053</v>
+        <v>8.54231834411621</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657609939575</v>
+        <v>7.71657657623291</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083818435669</v>
+        <v>7.60083913803101</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>8.3037166595459</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.36268615722656</v>
+        <v>7.36268663406372</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585079193115</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.89613008499146</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.34126949310303</v>
+        <v>4.34126901626587</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.16346597671509</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.57830858230591</v>
+        <v>4.57830905914307</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.18605804443359</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.59834003448486</v>
+        <v>4.59834051132202</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342130661011</v>
+        <v>5.00342178344727</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.8899097442627</v>
+        <v>4.88990926742554</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>5.8261570930481</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.16589975357056</v>
+        <v>5.1658992767334</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.06713485717773</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.37956762313843</v>
+        <v>5.37956809997559</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386211395264</v>
+        <v>5.28386259078979</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445489883423</v>
+        <v>4.95445537567139</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>5.67303514480591</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.03013038635254</v>
+        <v>5.03012990951538</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928503036499</v>
+        <v>5.19928550720215</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041393280029</v>
+        <v>5.21041345596313</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470746994019</v>
+        <v>5.11470699310303</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>5.80858516693115</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15031909942627</v>
+        <v>5.15031862258911</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248207092285</v>
+        <v>5.11248159408569</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>5.59521913528442</v>
       </c>
       <c r="G1108" t="n">
-        <v>4.96113252639771</v>
+        <v>4.96113300323486</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>5.57513809204102</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.9433274269104</v>
+        <v>4.94332695007324</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>4.62599992752075</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>24485261</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>4.38100004196167</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>4.40899991989136</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>4.40899991989136</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -71672,7 +71672,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B2743" t="n">
-        <v>24485261</v>
+        <v>24538066</v>
       </c>
       <c r="C2743" t="n">
         <v>4.57999992370605</v>
@@ -71690,6 +71690,32 @@
         <v>4.40899991989136</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>18269574</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>4.59100008010864</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>4.42500019073486</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>4.42799997329712</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>4.59100008010864</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>4.59100008010864</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -485,7 +485,7 @@
         <v>22.3245735168457</v>
       </c>
       <c r="G4" t="n">
-        <v>19.7946071624756</v>
+        <v>19.7946090698242</v>
       </c>
       <c r="H4" t="n">
         <v>808293</v>
@@ -601,7 +601,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.878662109375</v>
+        <v>19.8786602020264</v>
       </c>
       <c r="H8" t="n">
         <v>1620392</v>
@@ -630,7 +630,7 @@
         <v>22.1665782928467</v>
       </c>
       <c r="G9" t="n">
-        <v>19.6545181274414</v>
+        <v>19.65452003479</v>
       </c>
       <c r="H9" t="n">
         <v>916025</v>
@@ -659,7 +659,7 @@
         <v>22.1823787689209</v>
       </c>
       <c r="G10" t="n">
-        <v>19.668529510498</v>
+        <v>19.6685276031494</v>
       </c>
       <c r="H10" t="n">
         <v>887518</v>
@@ -688,7 +688,7 @@
         <v>20.9184246063232</v>
       </c>
       <c r="G11" t="n">
-        <v>18.5478134155273</v>
+        <v>18.547815322876</v>
       </c>
       <c r="H11" t="n">
         <v>1339292</v>
@@ -717,7 +717,7 @@
         <v>19.8440647125244</v>
       </c>
       <c r="G12" t="n">
-        <v>17.5952091217041</v>
+        <v>17.5952072143555</v>
       </c>
       <c r="H12" t="n">
         <v>1467001</v>
@@ -746,7 +746,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811958312988</v>
+        <v>17.5811977386475</v>
       </c>
       <c r="H13" t="n">
         <v>989105</v>
@@ -775,7 +775,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460289001465</v>
+        <v>15.7460279464722</v>
       </c>
       <c r="H14" t="n">
         <v>2077512</v>
@@ -804,7 +804,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.821439743042</v>
+        <v>14.8214406967163</v>
       </c>
       <c r="H15" t="n">
         <v>2435960</v>
@@ -862,7 +862,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552726745605</v>
+        <v>13.9552736282349</v>
       </c>
       <c r="H17" t="n">
         <v>354113</v>
@@ -949,7 +949,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087112426758</v>
+        <v>12.6087121963501</v>
       </c>
       <c r="H20" t="n">
         <v>1225889</v>
@@ -1123,7 +1123,7 @@
         <v>13.0530023574829</v>
       </c>
       <c r="G26" t="n">
-        <v>11.573751449585</v>
+        <v>11.5737524032593</v>
       </c>
       <c r="H26" t="n">
         <v>1877083</v>
@@ -1181,7 +1181,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H28" t="n">
         <v>1981662</v>
@@ -1239,7 +1239,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G30" t="n">
-        <v>7.08892202377319</v>
+        <v>7.08892250061035</v>
       </c>
       <c r="H30" t="n">
         <v>5755429</v>
@@ -1268,7 +1268,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G31" t="n">
-        <v>6.70832347869873</v>
+        <v>6.70832395553589</v>
       </c>
       <c r="H31" t="n">
         <v>7709298</v>
@@ -1297,7 +1297,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393558502197</v>
+        <v>6.74393510818481</v>
       </c>
       <c r="H32" t="n">
         <v>7100655</v>
@@ -1326,7 +1326,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.8774790763855</v>
+        <v>6.87747859954834</v>
       </c>
       <c r="H33" t="n">
         <v>7581026</v>
@@ -1355,7 +1355,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51180982589722</v>
+        <v>7.51181030273438</v>
       </c>
       <c r="H34" t="n">
         <v>6329665</v>
@@ -1413,7 +1413,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36046028137207</v>
+        <v>7.36045980453491</v>
       </c>
       <c r="H36" t="n">
         <v>4978216</v>
@@ -1471,7 +1471,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243934631348</v>
+        <v>7.91243886947632</v>
       </c>
       <c r="H38" t="n">
         <v>4762357</v>
@@ -1529,7 +1529,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H40" t="n">
         <v>5230684</v>
@@ -1587,7 +1587,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H42" t="n">
         <v>8046415</v>
@@ -1616,7 +1616,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H43" t="n">
         <v>5632607</v>
@@ -1732,7 +1732,7 @@
         <v>10.6884002685547</v>
       </c>
       <c r="G47" t="n">
-        <v>9.47712135314941</v>
+        <v>9.47712230682373</v>
       </c>
       <c r="H47" t="n">
         <v>6263628</v>
@@ -1761,7 +1761,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.07714366912842</v>
+        <v>8.0771427154541</v>
       </c>
       <c r="H48" t="n">
         <v>18012438</v>
@@ -1819,7 +1819,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811388015747</v>
+        <v>7.98811340332031</v>
       </c>
       <c r="H50" t="n">
         <v>5464353</v>
@@ -1877,7 +1877,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683300018311</v>
+        <v>8.58683204650879</v>
       </c>
       <c r="H52" t="n">
         <v>4362352</v>
@@ -1935,7 +1935,7 @@
         <v>9.26261138916016</v>
       </c>
       <c r="G54" t="n">
-        <v>8.21291351318359</v>
+        <v>8.21291255950928</v>
       </c>
       <c r="H54" t="n">
         <v>3721362</v>
@@ -1964,7 +1964,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.3175220489502</v>
+        <v>8.31752109527588</v>
       </c>
       <c r="H55" t="n">
         <v>4485559</v>
@@ -2080,7 +2080,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G59" t="n">
-        <v>8.20623397827148</v>
+        <v>8.2062349319458</v>
       </c>
       <c r="H59" t="n">
         <v>2418203</v>
@@ -2109,7 +2109,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218725204468</v>
+        <v>7.75218820571899</v>
       </c>
       <c r="H60" t="n">
         <v>3776976</v>
@@ -2138,7 +2138,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.3448805809021</v>
+        <v>7.34488010406494</v>
       </c>
       <c r="H61" t="n">
         <v>3010233</v>
@@ -2225,7 +2225,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870809555054</v>
+        <v>7.65870714187622</v>
       </c>
       <c r="H64" t="n">
         <v>2688899</v>
@@ -2283,7 +2283,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973640441895</v>
+        <v>6.89973592758179</v>
       </c>
       <c r="H66" t="n">
         <v>4271134</v>
@@ -2341,7 +2341,7 @@
         <v>7.61341381072998</v>
       </c>
       <c r="G68" t="n">
-        <v>6.75061273574829</v>
+        <v>6.75061225891113</v>
       </c>
       <c r="H68" t="n">
         <v>2618453</v>
@@ -2370,7 +2370,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365732192993</v>
+        <v>7.27365779876709</v>
       </c>
       <c r="H69" t="n">
         <v>3294930</v>
@@ -2399,7 +2399,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H70" t="n">
         <v>3239759</v>
@@ -2428,7 +2428,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G71" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H71" t="n">
         <v>3489116</v>
@@ -2457,7 +2457,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.86347436904907</v>
+        <v>7.8634729385376</v>
       </c>
       <c r="H72" t="n">
         <v>3751875</v>
@@ -2486,7 +2486,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09939956665039</v>
+        <v>8.09940052032471</v>
       </c>
       <c r="H73" t="n">
         <v>4017372</v>
@@ -2515,7 +2515,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86570072174072</v>
+        <v>7.86569976806641</v>
       </c>
       <c r="H74" t="n">
         <v>2931733</v>
@@ -2573,7 +2573,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H76" t="n">
         <v>3700496</v>
@@ -2689,7 +2689,7 @@
         <v>9.39816093444824</v>
       </c>
       <c r="G80" t="n">
-        <v>8.33310127258301</v>
+        <v>8.33310031890869</v>
       </c>
       <c r="H80" t="n">
         <v>1866023</v>
@@ -2747,7 +2747,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912178039551</v>
+        <v>8.62912082672119</v>
       </c>
       <c r="H82" t="n">
         <v>3841073</v>
@@ -2805,7 +2805,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H84" t="n">
         <v>6156371</v>
@@ -2834,7 +2834,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H85" t="n">
         <v>3915352</v>
@@ -2863,7 +2863,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G86" t="n">
-        <v>8.54009342193604</v>
+        <v>8.54009246826172</v>
       </c>
       <c r="H86" t="n">
         <v>4877613</v>
@@ -2892,7 +2892,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H87" t="n">
         <v>3783755</v>
@@ -2921,7 +2921,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G88" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H88" t="n">
         <v>2952497</v>
@@ -2950,7 +2950,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G89" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H89" t="n">
         <v>2726335</v>
@@ -2979,7 +2979,7 @@
         <v>9.36803913116455</v>
       </c>
       <c r="G90" t="n">
-        <v>8.30639171600342</v>
+        <v>8.30639266967773</v>
       </c>
       <c r="H90" t="n">
         <v>2595903</v>
@@ -3066,7 +3066,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H93" t="n">
         <v>3351378</v>
@@ -3095,7 +3095,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.2685546875</v>
+        <v>8.26855373382568</v>
       </c>
       <c r="H94" t="n">
         <v>2791506</v>
@@ -3124,7 +3124,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542007446289</v>
+        <v>8.39542102813721</v>
       </c>
       <c r="H95" t="n">
         <v>1782012</v>
@@ -3182,7 +3182,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G97" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H97" t="n">
         <v>1772130</v>
@@ -3211,7 +3211,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588848114014</v>
+        <v>7.98588752746582</v>
       </c>
       <c r="H98" t="n">
         <v>4712589</v>
@@ -3240,7 +3240,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701642990112</v>
+        <v>7.99701690673828</v>
       </c>
       <c r="H99" t="n">
         <v>2418605</v>
@@ -3327,7 +3327,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H102" t="n">
         <v>3679752</v>
@@ -3356,7 +3356,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G103" t="n">
-        <v>8.39764595031738</v>
+        <v>8.3976469039917</v>
       </c>
       <c r="H103" t="n">
         <v>2642334</v>
@@ -3530,7 +3530,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889633178711</v>
+        <v>7.77889585494995</v>
       </c>
       <c r="H109" t="n">
         <v>2101522</v>
@@ -3559,7 +3559,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701642990112</v>
+        <v>7.99701690673828</v>
       </c>
       <c r="H110" t="n">
         <v>2370853</v>
@@ -3646,7 +3646,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G113" t="n">
-        <v>8.6736364364624</v>
+        <v>8.67363548278809</v>
       </c>
       <c r="H113" t="n">
         <v>2693817</v>
@@ -3704,7 +3704,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325372695923</v>
+        <v>7.72325325012207</v>
       </c>
       <c r="H115" t="n">
         <v>4121823</v>
@@ -3733,7 +3733,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660612106323</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H116" t="n">
         <v>3931446</v>
@@ -3762,7 +3762,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808290481567</v>
+        <v>7.96808242797852</v>
       </c>
       <c r="H117" t="n">
         <v>3606977</v>
@@ -3820,7 +3820,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G119" t="n">
-        <v>8.20623397827148</v>
+        <v>8.2062349319458</v>
       </c>
       <c r="H119" t="n">
         <v>6157104</v>
@@ -3907,7 +3907,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76489067077637</v>
+        <v>8.76488971710205</v>
       </c>
       <c r="H122" t="n">
         <v>3417145</v>
@@ -3965,7 +3965,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.0593376159668</v>
+        <v>8.05933666229248</v>
       </c>
       <c r="H124" t="n">
         <v>4551998</v>
@@ -3994,7 +3994,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.59193563461304</v>
+        <v>7.5919361114502</v>
       </c>
       <c r="H125" t="n">
         <v>3711164</v>
@@ -4023,7 +4023,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78557348251343</v>
+        <v>7.78557395935059</v>
       </c>
       <c r="H126" t="n">
         <v>3269289</v>
@@ -4052,7 +4052,7 @@
         <v>8.86349010467529</v>
       </c>
       <c r="G127" t="n">
-        <v>7.85902214050293</v>
+        <v>7.85902261734009</v>
       </c>
       <c r="H127" t="n">
         <v>3013097</v>
@@ -4139,7 +4139,7 @@
         <v>9.60650730133057</v>
       </c>
       <c r="G130" t="n">
-        <v>8.51783561706543</v>
+        <v>8.51783657073975</v>
       </c>
       <c r="H130" t="n">
         <v>3045817</v>
@@ -4284,7 +4284,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.7114725112915</v>
+        <v>8.71147441864014</v>
       </c>
       <c r="H135" t="n">
         <v>4380711</v>
@@ -4313,7 +4313,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420352935791</v>
+        <v>9.03420257568359</v>
       </c>
       <c r="H136" t="n">
         <v>5039193</v>
@@ -4400,7 +4400,7 @@
         <v>10.3771362304688</v>
       </c>
       <c r="G139" t="n">
-        <v>9.20113277435303</v>
+        <v>9.20113182067871</v>
       </c>
       <c r="H139" t="n">
         <v>1660292</v>
@@ -4429,7 +4429,7 @@
         <v>10.5679111480713</v>
       </c>
       <c r="G140" t="n">
-        <v>9.37028694152832</v>
+        <v>9.37028789520264</v>
       </c>
       <c r="H140" t="n">
         <v>1710004</v>
@@ -4458,7 +4458,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G141" t="n">
-        <v>9.55947208404541</v>
+        <v>9.55947303771973</v>
       </c>
       <c r="H141" t="n">
         <v>3718667</v>
@@ -4603,7 +4603,7 @@
         <v>10.6934204101562</v>
       </c>
       <c r="G146" t="n">
-        <v>9.4815731048584</v>
+        <v>9.48157215118408</v>
       </c>
       <c r="H146" t="n">
         <v>2462145</v>
@@ -4632,7 +4632,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427124023438</v>
+        <v>9.78427219390869</v>
       </c>
       <c r="H147" t="n">
         <v>3288854</v>
@@ -4661,7 +4661,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G148" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H148" t="n">
         <v>11514563</v>
@@ -4690,7 +4690,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G149" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H149" t="n">
         <v>5327998</v>
@@ -4806,7 +4806,7 @@
         <v>9.37807941436768</v>
       </c>
       <c r="G153" t="n">
-        <v>8.31529521942139</v>
+        <v>8.31529426574707</v>
       </c>
       <c r="H153" t="n">
         <v>2495200</v>
@@ -4835,7 +4835,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228832244873</v>
+        <v>8.52228736877441</v>
       </c>
       <c r="H154" t="n">
         <v>2111524</v>
@@ -5009,7 +5009,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H160" t="n">
         <v>2723125</v>
@@ -5096,7 +5096,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H163" t="n">
         <v>1929655</v>
@@ -5125,7 +5125,7 @@
         <v>9.98303604125977</v>
       </c>
       <c r="G164" t="n">
-        <v>8.85169315338135</v>
+        <v>8.85169410705566</v>
       </c>
       <c r="H164" t="n">
         <v>1474788</v>
@@ -5154,7 +5154,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122570037842</v>
+        <v>9.26122665405273</v>
       </c>
       <c r="H165" t="n">
         <v>1784826</v>
@@ -5183,7 +5183,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G166" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H166" t="n">
         <v>2357597</v>
@@ -5241,7 +5241,7 @@
         <v>10.442400932312</v>
       </c>
       <c r="G168" t="n">
-        <v>9.25900077819824</v>
+        <v>9.25899982452393</v>
       </c>
       <c r="H168" t="n">
         <v>1567170</v>
@@ -5328,7 +5328,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548778533936</v>
+        <v>9.14548873901367</v>
       </c>
       <c r="H171" t="n">
         <v>1904678</v>
@@ -5386,7 +5386,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H173" t="n">
         <v>2380805</v>
@@ -5415,7 +5415,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.2723560333252</v>
+        <v>9.27235507965088</v>
       </c>
       <c r="H174" t="n">
         <v>1895264</v>
@@ -5502,7 +5502,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G177" t="n">
-        <v>9.23451900482178</v>
+        <v>9.23451805114746</v>
       </c>
       <c r="H177" t="n">
         <v>2950107</v>
@@ -5531,7 +5531,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G178" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H178" t="n">
         <v>1678053</v>
@@ -5647,7 +5647,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G182" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H182" t="n">
         <v>2932072</v>
@@ -5676,7 +5676,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359827041626</v>
+        <v>7.94359874725342</v>
       </c>
       <c r="H183" t="n">
         <v>4194583</v>
@@ -5763,7 +5763,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463329315186</v>
+        <v>7.89463376998901</v>
       </c>
       <c r="H186" t="n">
         <v>1967156</v>
@@ -5850,7 +5850,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798664093018</v>
+        <v>7.90798759460449</v>
       </c>
       <c r="H189" t="n">
         <v>3574353</v>
@@ -5908,7 +5908,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.73883247375488</v>
+        <v>7.7388334274292</v>
       </c>
       <c r="H191" t="n">
         <v>2882632</v>
@@ -5966,7 +5966,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G193" t="n">
-        <v>8.38429260253906</v>
+        <v>8.38429164886475</v>
       </c>
       <c r="H193" t="n">
         <v>3268951</v>
@@ -6024,7 +6024,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H195" t="n">
         <v>3058208</v>
@@ -6053,7 +6053,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G196" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H196" t="n">
         <v>2921152</v>
@@ -6111,7 +6111,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473388671875</v>
+        <v>8.66473293304443</v>
       </c>
       <c r="H198" t="n">
         <v>3635783</v>
@@ -6256,7 +6256,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H203" t="n">
         <v>2739605</v>
@@ -6285,7 +6285,7 @@
         <v>10.3696060180664</v>
       </c>
       <c r="G204" t="n">
-        <v>9.19445514678955</v>
+        <v>9.19445610046387</v>
       </c>
       <c r="H204" t="n">
         <v>2291727</v>
@@ -6314,7 +6314,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H205" t="n">
         <v>2047802</v>
@@ -6459,7 +6459,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G210" t="n">
-        <v>9.31464385986328</v>
+        <v>9.31464290618896</v>
       </c>
       <c r="H210" t="n">
         <v>2902413</v>
@@ -6488,7 +6488,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H211" t="n">
         <v>10102433</v>
@@ -6546,7 +6546,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H213" t="n">
         <v>3655602</v>
@@ -6720,7 +6720,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G219" t="n">
-        <v>8.38429260253906</v>
+        <v>8.38429164886475</v>
       </c>
       <c r="H219" t="n">
         <v>2139887</v>
@@ -6749,7 +6749,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G220" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H220" t="n">
         <v>2461590</v>
@@ -6778,7 +6778,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G221" t="n">
-        <v>8.73373126983643</v>
+        <v>8.73373031616211</v>
       </c>
       <c r="H221" t="n">
         <v>7014824</v>
@@ -6865,7 +6865,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H224" t="n">
         <v>2930403</v>
@@ -6923,7 +6923,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072341918945</v>
+        <v>8.94072246551514</v>
       </c>
       <c r="H226" t="n">
         <v>2515113</v>
@@ -6981,7 +6981,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G228" t="n">
-        <v>8.6736364364624</v>
+        <v>8.67363548278809</v>
       </c>
       <c r="H228" t="n">
         <v>3095637</v>
@@ -7039,7 +7039,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G230" t="n">
-        <v>8.94517421722412</v>
+        <v>8.9451732635498</v>
       </c>
       <c r="H230" t="n">
         <v>2705648</v>
@@ -7097,7 +7097,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G232" t="n">
-        <v>9.16329383850098</v>
+        <v>9.16329479217529</v>
       </c>
       <c r="H232" t="n">
         <v>2155204</v>
@@ -7126,7 +7126,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G233" t="n">
-        <v>8.92514324188232</v>
+        <v>8.92514228820801</v>
       </c>
       <c r="H233" t="n">
         <v>1340077</v>
@@ -7155,7 +7155,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G234" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H234" t="n">
         <v>2193109</v>
@@ -7242,7 +7242,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640323638916</v>
+        <v>9.72640228271484</v>
       </c>
       <c r="H237" t="n">
         <v>6656648</v>
@@ -7329,7 +7329,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1826753616333</v>
+        <v>10.182674407959</v>
       </c>
       <c r="H240" t="n">
         <v>4126096</v>
@@ -7387,7 +7387,7 @@
         <v>11.4088249206543</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1159029006958</v>
+        <v>10.1159038543701</v>
       </c>
       <c r="H242" t="n">
         <v>4919856</v>
@@ -7474,7 +7474,7 @@
         <v>11.8230066299438</v>
       </c>
       <c r="G245" t="n">
-        <v>10.4831466674805</v>
+        <v>10.4831476211548</v>
       </c>
       <c r="H245" t="n">
         <v>7748349</v>
@@ -7532,7 +7532,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788545608521</v>
+        <v>10.5788536071777</v>
       </c>
       <c r="H247" t="n">
         <v>3112020</v>
@@ -7648,7 +7648,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G251" t="n">
-        <v>10.9883861541748</v>
+        <v>10.9883871078491</v>
       </c>
       <c r="H251" t="n">
         <v>3493539</v>
@@ -7677,7 +7677,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G252" t="n">
-        <v>11.2844076156616</v>
+        <v>11.2844085693359</v>
       </c>
       <c r="H252" t="n">
         <v>3211844</v>
@@ -7706,7 +7706,7 @@
         <v>12.8772878646851</v>
       </c>
       <c r="G253" t="n">
-        <v>11.4179496765137</v>
+        <v>11.417950630188</v>
       </c>
       <c r="H253" t="n">
         <v>1908982</v>
@@ -7764,7 +7764,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295522689819</v>
+        <v>11.7295513153076</v>
       </c>
       <c r="H255" t="n">
         <v>2571001</v>
@@ -7822,7 +7822,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076099395752</v>
+        <v>11.9076108932495</v>
       </c>
       <c r="H257" t="n">
         <v>1775884</v>
@@ -7909,7 +7909,7 @@
         <v>13.9817733764648</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3972692489624</v>
+        <v>12.3972682952881</v>
       </c>
       <c r="H260" t="n">
         <v>3761116</v>
@@ -7938,7 +7938,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195251464844</v>
+        <v>12.4195261001587</v>
       </c>
       <c r="H261" t="n">
         <v>2771934</v>
@@ -7967,7 +7967,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858253479004</v>
+        <v>12.1858243942261</v>
       </c>
       <c r="H262" t="n">
         <v>2214682</v>
@@ -8112,7 +8112,7 @@
         <v>12.8647365570068</v>
       </c>
       <c r="G267" t="n">
-        <v>11.4068222045898</v>
+        <v>11.4068212509155</v>
       </c>
       <c r="H267" t="n">
         <v>2415292</v>
@@ -8199,7 +8199,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G270" t="n">
-        <v>11.2844076156616</v>
+        <v>11.2844085693359</v>
       </c>
       <c r="H270" t="n">
         <v>3414444</v>
@@ -8228,7 +8228,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619920730591</v>
+        <v>11.1619939804077</v>
       </c>
       <c r="H271" t="n">
         <v>2083536</v>
@@ -8286,7 +8286,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351266860962</v>
+        <v>11.0351257324219</v>
       </c>
       <c r="H273" t="n">
         <v>2426178</v>
@@ -8344,7 +8344,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963237762451</v>
+        <v>11.7963228225708</v>
       </c>
       <c r="H275" t="n">
         <v>5968291</v>
@@ -8402,7 +8402,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960083007812</v>
+        <v>11.5960092544556</v>
       </c>
       <c r="H277" t="n">
         <v>1743449</v>
@@ -8518,7 +8518,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G281" t="n">
-        <v>10.2383184432983</v>
+        <v>10.2383193969727</v>
       </c>
       <c r="H281" t="n">
         <v>3878344</v>
@@ -8547,7 +8547,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141492843628</v>
+        <v>10.4141502380371</v>
       </c>
       <c r="H282" t="n">
         <v>2834757</v>
@@ -8576,7 +8576,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.2516717910767</v>
+        <v>10.251672744751</v>
       </c>
       <c r="H283" t="n">
         <v>3104757</v>
@@ -8663,7 +8663,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.39857006073</v>
+        <v>10.3985710144043</v>
       </c>
       <c r="H286" t="n">
         <v>2660739</v>
@@ -8750,7 +8750,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651847839355</v>
+        <v>10.3651838302612</v>
       </c>
       <c r="H289" t="n">
         <v>3308303</v>
@@ -8837,7 +8837,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H292" t="n">
         <v>2600664</v>
@@ -8895,7 +8895,7 @@
         <v>11.6874570846558</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3629579544067</v>
+        <v>10.3629589080811</v>
       </c>
       <c r="H294" t="n">
         <v>2084853</v>
@@ -9011,7 +9011,7 @@
         <v>10.5754413604736</v>
       </c>
       <c r="G298" t="n">
-        <v>9.3769645690918</v>
+        <v>9.37696361541748</v>
       </c>
       <c r="H298" t="n">
         <v>3692492</v>
@@ -9098,7 +9098,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486354827881</v>
+        <v>9.45486450195312</v>
       </c>
       <c r="H301" t="n">
         <v>3459059</v>
@@ -9127,7 +9127,7 @@
         <v>10.6984405517578</v>
       </c>
       <c r="G302" t="n">
-        <v>9.48602390289307</v>
+        <v>9.48602485656738</v>
       </c>
       <c r="H302" t="n">
         <v>2707699</v>
@@ -9185,7 +9185,7 @@
         <v>10.4675025939941</v>
       </c>
       <c r="G304" t="n">
-        <v>9.28125762939453</v>
+        <v>9.28125858306885</v>
       </c>
       <c r="H304" t="n">
         <v>3507793</v>
@@ -9330,7 +9330,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520709991455</v>
+        <v>8.96520614624023</v>
       </c>
       <c r="H309" t="n">
         <v>3858069</v>
@@ -9359,7 +9359,7 @@
         <v>10.218994140625</v>
       </c>
       <c r="G310" t="n">
-        <v>9.06091213226318</v>
+        <v>9.06091117858887</v>
       </c>
       <c r="H310" t="n">
         <v>3308377</v>
@@ -9446,7 +9446,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G313" t="n">
-        <v>9.01639747619629</v>
+        <v>9.01639652252197</v>
       </c>
       <c r="H313" t="n">
         <v>2624769</v>
@@ -9475,7 +9475,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539485931396</v>
+        <v>9.08539390563965</v>
       </c>
       <c r="H314" t="n">
         <v>3039918</v>
@@ -9504,7 +9504,7 @@
         <v>10.1336479187012</v>
       </c>
       <c r="G315" t="n">
-        <v>8.98523712158203</v>
+        <v>8.98523807525635</v>
       </c>
       <c r="H315" t="n">
         <v>3230495</v>
@@ -9591,7 +9591,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H318" t="n">
         <v>3081207</v>
@@ -9620,7 +9620,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G319" t="n">
-        <v>9.39254474639893</v>
+        <v>9.39254379272461</v>
       </c>
       <c r="H319" t="n">
         <v>5837585</v>
@@ -9649,7 +9649,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G320" t="n">
-        <v>9.4615421295166</v>
+        <v>9.46154117584229</v>
       </c>
       <c r="H320" t="n">
         <v>4855845</v>
@@ -9736,7 +9736,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981948852539</v>
+        <v>9.77981853485107</v>
       </c>
       <c r="H323" t="n">
         <v>5715259</v>
@@ -9765,7 +9765,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G324" t="n">
-        <v>9.49047565460205</v>
+        <v>9.49047470092773</v>
       </c>
       <c r="H324" t="n">
         <v>4124738</v>
@@ -9794,7 +9794,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G325" t="n">
-        <v>9.51050662994385</v>
+        <v>9.51050758361816</v>
       </c>
       <c r="H325" t="n">
         <v>3181766</v>
@@ -9823,7 +9823,7 @@
         <v>10.7310733795166</v>
       </c>
       <c r="G326" t="n">
-        <v>9.51495838165283</v>
+        <v>9.51495933532715</v>
       </c>
       <c r="H326" t="n">
         <v>2539231</v>
@@ -9881,7 +9881,7 @@
         <v>10.5227270126343</v>
       </c>
       <c r="G328" t="n">
-        <v>9.33022403717041</v>
+        <v>9.33022308349609</v>
       </c>
       <c r="H328" t="n">
         <v>2488647</v>
@@ -9910,7 +9910,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H329" t="n">
         <v>3030394</v>
@@ -9939,7 +9939,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G330" t="n">
-        <v>9.12990856170654</v>
+        <v>9.12990951538086</v>
       </c>
       <c r="H330" t="n">
         <v>3092166</v>
@@ -10084,7 +10084,7 @@
         <v>9.7671594619751</v>
       </c>
       <c r="G335" t="n">
-        <v>8.66028118133545</v>
+        <v>8.66028213500977</v>
       </c>
       <c r="H335" t="n">
         <v>6899556</v>
@@ -10171,7 +10171,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.2033576965332</v>
+        <v>9.20335865020752</v>
       </c>
       <c r="H338" t="n">
         <v>3676909</v>
@@ -10316,7 +10316,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H343" t="n">
         <v>4027196</v>
@@ -10606,7 +10606,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G353" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H353" t="n">
         <v>3851850</v>
@@ -10635,7 +10635,7 @@
         <v>9.80481243133545</v>
       </c>
       <c r="G354" t="n">
-        <v>8.6936674118042</v>
+        <v>8.69366836547852</v>
       </c>
       <c r="H354" t="n">
         <v>2634747</v>
@@ -10693,7 +10693,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H356" t="n">
         <v>1939986</v>
@@ -10722,7 +10722,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G357" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H357" t="n">
         <v>2035124</v>
@@ -10809,7 +10809,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H360" t="n">
         <v>1852849</v>
@@ -10896,7 +10896,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.9903392791748</v>
+        <v>7.99033975601196</v>
       </c>
       <c r="H363" t="n">
         <v>4201110</v>
@@ -11012,7 +11012,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215627670288</v>
+        <v>7.73215579986572</v>
       </c>
       <c r="H367" t="n">
         <v>4573774</v>
@@ -11041,7 +11041,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H368" t="n">
         <v>4145288</v>
@@ -11157,7 +11157,7 @@
         <v>8.88106060028076</v>
       </c>
       <c r="G372" t="n">
-        <v>7.87460136413574</v>
+        <v>7.8746018409729</v>
       </c>
       <c r="H372" t="n">
         <v>3226298</v>
@@ -11186,7 +11186,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H373" t="n">
         <v>5046714</v>
@@ -11331,7 +11331,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G378" t="n">
-        <v>7.18017721176147</v>
+        <v>7.18017673492432</v>
       </c>
       <c r="H378" t="n">
         <v>2433304</v>
@@ -11360,7 +11360,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H379" t="n">
         <v>2182310</v>
@@ -11389,7 +11389,7 @@
         <v>8.07779979705811</v>
       </c>
       <c r="G380" t="n">
-        <v>7.16237163543701</v>
+        <v>7.16237115859985</v>
       </c>
       <c r="H380" t="n">
         <v>2966514</v>
@@ -11418,7 +11418,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914218902588</v>
+        <v>7.22914266586304</v>
       </c>
       <c r="H381" t="n">
         <v>2924827</v>
@@ -11447,7 +11447,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817150115967</v>
+        <v>7.31817245483398</v>
       </c>
       <c r="H382" t="n">
         <v>2594435</v>
@@ -11476,7 +11476,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804521560669</v>
+        <v>7.23804569244385</v>
       </c>
       <c r="H383" t="n">
         <v>2583014</v>
@@ -11534,7 +11534,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055559158325</v>
+        <v>7.42055463790894</v>
       </c>
       <c r="H385" t="n">
         <v>3239198</v>
@@ -11563,7 +11563,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.69654512405396</v>
+        <v>7.6965446472168</v>
       </c>
       <c r="H386" t="n">
         <v>4250748</v>
@@ -11592,7 +11592,7 @@
         <v>8.44428825378418</v>
       </c>
       <c r="G387" t="n">
-        <v>7.48732709884644</v>
+        <v>7.48732662200928</v>
       </c>
       <c r="H387" t="n">
         <v>4117666</v>
@@ -11708,7 +11708,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390893936157</v>
+        <v>7.43390846252441</v>
       </c>
       <c r="H391" t="n">
         <v>1190917</v>
@@ -11737,7 +11737,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H392" t="n">
         <v>4462543</v>
@@ -11766,7 +11766,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G393" t="n">
-        <v>7.74551010131836</v>
+        <v>7.7455096244812</v>
       </c>
       <c r="H393" t="n">
         <v>2051870</v>
@@ -11824,7 +11824,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.85679578781128</v>
+        <v>7.85679721832275</v>
       </c>
       <c r="H395" t="n">
         <v>2325966</v>
@@ -11853,7 +11853,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H396" t="n">
         <v>3714587</v>
@@ -11911,7 +11911,7 @@
         <v>8.514573097229</v>
       </c>
       <c r="G398" t="n">
-        <v>7.54964685440063</v>
+        <v>7.54964637756348</v>
       </c>
       <c r="H398" t="n">
         <v>1501586</v>
@@ -11940,7 +11940,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842311859131</v>
       </c>
       <c r="H399" t="n">
         <v>1479093</v>
@@ -11969,7 +11969,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196708679199</v>
+        <v>7.61196756362915</v>
       </c>
       <c r="H400" t="n">
         <v>2662388</v>
@@ -12056,7 +12056,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H403" t="n">
         <v>2870111</v>
@@ -12085,7 +12085,7 @@
         <v>8.6953067779541</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70989894866943</v>
+        <v>7.70989847183228</v>
       </c>
       <c r="H404" t="n">
         <v>2592503</v>
@@ -12143,7 +12143,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H406" t="n">
         <v>2779239</v>
@@ -12172,7 +12172,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757871627808</v>
+        <v>7.64757966995239</v>
       </c>
       <c r="H407" t="n">
         <v>1870136</v>
@@ -12259,7 +12259,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428731918335</v>
+        <v>7.67428636550903</v>
       </c>
       <c r="H410" t="n">
         <v>1678906</v>
@@ -12375,7 +12375,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249744415283</v>
+        <v>7.24249792098999</v>
       </c>
       <c r="H414" t="n">
         <v>3391728</v>
@@ -12404,7 +12404,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701162338257</v>
+        <v>7.28701210021973</v>
       </c>
       <c r="H415" t="n">
         <v>1909890</v>
@@ -12433,7 +12433,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G416" t="n">
-        <v>7.26475429534912</v>
+        <v>7.26475477218628</v>
       </c>
       <c r="H416" t="n">
         <v>2058975</v>
@@ -12520,7 +12520,7 @@
         <v>8.08281993865967</v>
       </c>
       <c r="G419" t="n">
-        <v>7.16682243347168</v>
+        <v>7.16682195663452</v>
       </c>
       <c r="H419" t="n">
         <v>1874275</v>
@@ -12578,7 +12578,7 @@
         <v>7.84184217453003</v>
       </c>
       <c r="G421" t="n">
-        <v>6.95315408706665</v>
+        <v>6.95315361022949</v>
       </c>
       <c r="H421" t="n">
         <v>2449535</v>
@@ -12607,7 +12607,7 @@
         <v>7.61592388153076</v>
       </c>
       <c r="G422" t="n">
-        <v>6.75283813476562</v>
+        <v>6.75283861160278</v>
       </c>
       <c r="H422" t="n">
         <v>5344638</v>
@@ -12636,7 +12636,7 @@
         <v>7.70127105712891</v>
       </c>
       <c r="G423" t="n">
-        <v>6.82851314544678</v>
+        <v>6.82851362228394</v>
       </c>
       <c r="H423" t="n">
         <v>3972357</v>
@@ -12665,7 +12665,7 @@
         <v>7.68621015548706</v>
       </c>
       <c r="G424" t="n">
-        <v>6.81515884399414</v>
+        <v>6.8151593208313</v>
       </c>
       <c r="H424" t="n">
         <v>2199628</v>
@@ -12723,7 +12723,7 @@
         <v>7.40004777908325</v>
       </c>
       <c r="G426" t="n">
-        <v>6.56142616271973</v>
+        <v>6.56142663955688</v>
       </c>
       <c r="H426" t="n">
         <v>1915267</v>
@@ -12752,7 +12752,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.93979835510254</v>
+        <v>6.9397988319397</v>
       </c>
       <c r="H427" t="n">
         <v>6403078</v>
@@ -12781,7 +12781,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857604980469</v>
+        <v>6.86857557296753</v>
       </c>
       <c r="H428" t="n">
         <v>3961179</v>
@@ -12897,7 +12897,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H432" t="n">
         <v>2571750</v>
@@ -12926,7 +12926,7 @@
         <v>7.96233081817627</v>
       </c>
       <c r="G433" t="n">
-        <v>7.05998802185059</v>
+        <v>7.05998849868774</v>
       </c>
       <c r="H433" t="n">
         <v>2066064</v>
@@ -13042,7 +13042,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409908294678</v>
+        <v>7.55409860610962</v>
       </c>
       <c r="H437" t="n">
         <v>2971867</v>
@@ -13071,7 +13071,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.47397232055664</v>
+        <v>7.4739727973938</v>
       </c>
       <c r="H438" t="n">
         <v>2774137</v>
@@ -13129,7 +13129,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H440" t="n">
         <v>3440039</v>
@@ -13158,7 +13158,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.66538429260254</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H441" t="n">
         <v>3163095</v>
@@ -13216,7 +13216,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H443" t="n">
         <v>2311936</v>
@@ -13448,7 +13448,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692302703857</v>
+        <v>7.93692350387573</v>
       </c>
       <c r="H451" t="n">
         <v>4589432</v>
@@ -13477,7 +13477,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504264831543</v>
+        <v>8.15504360198975</v>
       </c>
       <c r="H452" t="n">
         <v>4598808</v>
@@ -13767,7 +13767,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939523696899</v>
+        <v>7.38939476013184</v>
       </c>
       <c r="H462" t="n">
         <v>5765617</v>
@@ -13796,7 +13796,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.42945766448975</v>
+        <v>7.42945718765259</v>
       </c>
       <c r="H463" t="n">
         <v>3847044</v>
@@ -13825,7 +13825,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804521560669</v>
+        <v>7.23804569244385</v>
       </c>
       <c r="H464" t="n">
         <v>4793014</v>
@@ -13883,7 +13883,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H466" t="n">
         <v>9145143</v>
@@ -13912,7 +13912,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.66538429260254</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H467" t="n">
         <v>3470929</v>
@@ -13970,7 +13970,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479103088379</v>
+        <v>7.99479198455811</v>
       </c>
       <c r="H469" t="n">
         <v>8252776</v>
@@ -14057,7 +14057,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.5467700958252</v>
+        <v>8.54677104949951</v>
       </c>
       <c r="H472" t="n">
         <v>5904097</v>
@@ -14115,7 +14115,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H474" t="n">
         <v>5603952</v>
@@ -14144,7 +14144,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H475" t="n">
         <v>5013333</v>
@@ -14173,7 +14173,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H476" t="n">
         <v>3307360</v>
@@ -14231,7 +14231,7 @@
         <v>9.49354839324951</v>
       </c>
       <c r="G478" t="n">
-        <v>8.41767883300781</v>
+        <v>8.4176778793335</v>
       </c>
       <c r="H478" t="n">
         <v>4520776</v>
@@ -14289,7 +14289,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G480" t="n">
-        <v>7.78557348251343</v>
+        <v>7.78557395935059</v>
       </c>
       <c r="H480" t="n">
         <v>11572956</v>
@@ -14318,7 +14318,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757871627808</v>
+        <v>7.64757966995239</v>
       </c>
       <c r="H481" t="n">
         <v>6391732</v>
@@ -14347,7 +14347,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G482" t="n">
-        <v>7.62532186508179</v>
+        <v>7.62532234191895</v>
       </c>
       <c r="H482" t="n">
         <v>3509049</v>
@@ -14376,7 +14376,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G483" t="n">
-        <v>7.62532186508179</v>
+        <v>7.62532234191895</v>
       </c>
       <c r="H483" t="n">
         <v>4716149</v>
@@ -14405,7 +14405,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H484" t="n">
         <v>3256857</v>
@@ -14463,7 +14463,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576219558716</v>
+        <v>7.90576267242432</v>
       </c>
       <c r="H486" t="n">
         <v>2564414</v>
@@ -14492,7 +14492,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344148635864</v>
+        <v>7.84344244003296</v>
       </c>
       <c r="H487" t="n">
         <v>2436747</v>
@@ -14521,7 +14521,7 @@
         <v>8.60494041442871</v>
       </c>
       <c r="G488" t="n">
-        <v>7.62977313995361</v>
+        <v>7.62977266311646</v>
       </c>
       <c r="H488" t="n">
         <v>3215714</v>
@@ -14579,7 +14579,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H490" t="n">
         <v>2757855</v>
@@ -14608,7 +14608,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G491" t="n">
-        <v>7.74551010131836</v>
+        <v>7.7455096244812</v>
       </c>
       <c r="H491" t="n">
         <v>3546514</v>
@@ -14695,7 +14695,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H494" t="n">
         <v>4714362</v>
@@ -14724,7 +14724,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H495" t="n">
         <v>2456311</v>
@@ -14840,7 +14840,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63422441482544</v>
+        <v>7.6342248916626</v>
       </c>
       <c r="H499" t="n">
         <v>4090789</v>
@@ -14898,7 +14898,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H501" t="n">
         <v>2766406</v>
@@ -14985,7 +14985,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996185302734</v>
+        <v>7.74996280670166</v>
       </c>
       <c r="H504" t="n">
         <v>4120969</v>
@@ -15072,7 +15072,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G507" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H507" t="n">
         <v>4480449</v>
@@ -15130,7 +15130,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H509" t="n">
         <v>5719334</v>
@@ -15159,7 +15159,7 @@
         <v>9.61403846740723</v>
       </c>
       <c r="G510" t="n">
-        <v>8.52451419830322</v>
+        <v>8.52451324462891</v>
       </c>
       <c r="H510" t="n">
         <v>2445873</v>
@@ -15188,7 +15188,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109603881836</v>
+        <v>8.47109508514404</v>
       </c>
       <c r="H511" t="n">
         <v>3770392</v>
@@ -15217,7 +15217,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670719146729</v>
+        <v>8.50670623779297</v>
       </c>
       <c r="H512" t="n">
         <v>2875008</v>
@@ -15246,7 +15246,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.5022554397583</v>
+        <v>8.50225639343262</v>
       </c>
       <c r="H513" t="n">
         <v>2779890</v>
@@ -15275,7 +15275,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G514" t="n">
-        <v>8.73373126983643</v>
+        <v>8.73373031616211</v>
       </c>
       <c r="H514" t="n">
         <v>6368024</v>
@@ -15304,7 +15304,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H515" t="n">
         <v>3023534</v>
@@ -15391,7 +15391,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805530548096</v>
+        <v>8.65805625915527</v>
       </c>
       <c r="H518" t="n">
         <v>3468959</v>
@@ -15420,7 +15420,7 @@
         <v>10.1210966110229</v>
       </c>
       <c r="G519" t="n">
-        <v>8.9741096496582</v>
+        <v>8.97410869598389</v>
       </c>
       <c r="H519" t="n">
         <v>7443734</v>
@@ -15507,7 +15507,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G522" t="n">
-        <v>9.12990856170654</v>
+        <v>9.12990951538086</v>
       </c>
       <c r="H522" t="n">
         <v>5817803</v>
@@ -15536,7 +15536,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H523" t="n">
         <v>4786463</v>
@@ -15565,7 +15565,7 @@
         <v>10.1813411712646</v>
       </c>
       <c r="G524" t="n">
-        <v>9.02752685546875</v>
+        <v>9.02752590179443</v>
       </c>
       <c r="H524" t="n">
         <v>2378154</v>
@@ -15652,7 +15652,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G527" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H527" t="n">
         <v>5274403</v>
@@ -15681,7 +15681,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G528" t="n">
-        <v>9.1655216217041</v>
+        <v>9.16552066802979</v>
       </c>
       <c r="H528" t="n">
         <v>3314321</v>
@@ -15768,7 +15768,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833980560303</v>
+        <v>8.83833885192871</v>
       </c>
       <c r="H531" t="n">
         <v>2823997</v>
@@ -15826,7 +15826,7 @@
         <v>9.46593570709229</v>
       </c>
       <c r="G533" t="n">
-        <v>8.3931941986084</v>
+        <v>8.39319515228271</v>
       </c>
       <c r="H533" t="n">
         <v>3664518</v>
@@ -15855,7 +15855,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.41990566253662</v>
+        <v>8.41990375518799</v>
       </c>
       <c r="H534" t="n">
         <v>2981971</v>
@@ -15884,7 +15884,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.2485237121582</v>
+        <v>8.24852466583252</v>
       </c>
       <c r="H535" t="n">
         <v>4093310</v>
@@ -15913,7 +15913,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H536" t="n">
         <v>4347986</v>
@@ -16000,7 +16000,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660612106323</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H539" t="n">
         <v>5267752</v>
@@ -16029,7 +16029,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196708679199</v>
+        <v>7.61196756362915</v>
       </c>
       <c r="H540" t="n">
         <v>7866114</v>
@@ -16058,7 +16058,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519605636597</v>
+        <v>7.54519510269165</v>
       </c>
       <c r="H541" t="n">
         <v>2933056</v>
@@ -16116,7 +16116,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49622964859009</v>
+        <v>7.49623012542725</v>
       </c>
       <c r="H543" t="n">
         <v>5612249</v>
@@ -16232,7 +16232,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H547" t="n">
         <v>2390591</v>
@@ -16319,7 +16319,7 @@
         <v>8.83587837219238</v>
       </c>
       <c r="G550" t="n">
-        <v>7.83453989028931</v>
+        <v>7.83453893661499</v>
       </c>
       <c r="H550" t="n">
         <v>5628339</v>
@@ -16348,7 +16348,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.7633171081543</v>
+        <v>7.76331663131714</v>
       </c>
       <c r="H551" t="n">
         <v>3521552</v>
@@ -16377,7 +16377,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H552" t="n">
         <v>3398436</v>
@@ -16406,7 +16406,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G553" t="n">
-        <v>7.50068092346191</v>
+        <v>7.50068044662476</v>
       </c>
       <c r="H553" t="n">
         <v>4181215</v>
@@ -16435,7 +16435,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.52293872833252</v>
+        <v>7.5229377746582</v>
       </c>
       <c r="H554" t="n">
         <v>2585190</v>
@@ -16464,7 +16464,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368877410889</v>
+        <v>7.29368829727173</v>
       </c>
       <c r="H555" t="n">
         <v>4043829</v>
@@ -16522,7 +16522,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G557" t="n">
-        <v>7.50068092346191</v>
+        <v>7.50068044662476</v>
       </c>
       <c r="H557" t="n">
         <v>7379464</v>
@@ -16551,7 +16551,7 @@
         <v>8.56979656219482</v>
       </c>
       <c r="G558" t="n">
-        <v>7.5986123085022</v>
+        <v>7.59861183166504</v>
       </c>
       <c r="H558" t="n">
         <v>4269884</v>
@@ -16580,7 +16580,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663805007935</v>
+        <v>7.75663948059082</v>
       </c>
       <c r="H559" t="n">
         <v>3729295</v>
@@ -16609,7 +16609,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218725204468</v>
+        <v>7.75218820571899</v>
       </c>
       <c r="H560" t="n">
         <v>2796916</v>
@@ -16725,7 +16725,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936378479004</v>
+        <v>7.36936330795288</v>
       </c>
       <c r="H564" t="n">
         <v>2801339</v>
@@ -16754,7 +16754,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613433837891</v>
+        <v>7.43613481521606</v>
       </c>
       <c r="H565" t="n">
         <v>3258776</v>
@@ -16812,7 +16812,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826585769653</v>
+        <v>7.37826633453369</v>
       </c>
       <c r="H567" t="n">
         <v>3350760</v>
@@ -16899,7 +16899,7 @@
         <v>8.17820739746094</v>
       </c>
       <c r="G570" t="n">
-        <v>7.25140047073364</v>
+        <v>7.25139999389648</v>
       </c>
       <c r="H570" t="n">
         <v>3395514</v>
@@ -16986,7 +16986,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H573" t="n">
         <v>3487395</v>
@@ -17015,7 +17015,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H574" t="n">
         <v>1774619</v>
@@ -17131,7 +17131,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G578" t="n">
-        <v>6.98876523971558</v>
+        <v>6.98876571655273</v>
       </c>
       <c r="H578" t="n">
         <v>2910934</v>
@@ -17160,7 +17160,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744667053223</v>
+        <v>6.85744762420654</v>
       </c>
       <c r="H579" t="n">
         <v>4059831</v>
@@ -17218,7 +17218,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G581" t="n">
-        <v>7.08892202377319</v>
+        <v>7.08892250061035</v>
       </c>
       <c r="H581" t="n">
         <v>8326804</v>
@@ -17276,7 +17276,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H583" t="n">
         <v>5007935</v>
@@ -17305,7 +17305,7 @@
         <v>8.1079216003418</v>
       </c>
       <c r="G584" t="n">
-        <v>7.18907976150513</v>
+        <v>7.18907928466797</v>
       </c>
       <c r="H584" t="n">
         <v>3472564</v>
@@ -17334,7 +17334,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G585" t="n">
-        <v>7.18017721176147</v>
+        <v>7.18017673492432</v>
       </c>
       <c r="H585" t="n">
         <v>3344302</v>
@@ -17392,7 +17392,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842311859131</v>
       </c>
       <c r="H587" t="n">
         <v>5249327</v>
@@ -17421,7 +17421,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610383987427</v>
+        <v>7.41610431671143</v>
       </c>
       <c r="H588" t="n">
         <v>4009682</v>
@@ -17479,7 +17479,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G590" t="n">
-        <v>7.26475429534912</v>
+        <v>7.26475477218628</v>
       </c>
       <c r="H590" t="n">
         <v>7182347</v>
@@ -17508,7 +17508,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G591" t="n">
-        <v>6.98876523971558</v>
+        <v>6.98876571655273</v>
       </c>
       <c r="H591" t="n">
         <v>9716283</v>
@@ -17537,7 +17537,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766778945923</v>
+        <v>6.99766731262207</v>
       </c>
       <c r="H592" t="n">
         <v>4887233</v>
@@ -17595,7 +17595,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443881988525</v>
+        <v>7.06443929672241</v>
       </c>
       <c r="H594" t="n">
         <v>3740621</v>
@@ -17653,7 +17653,7 @@
         <v>7.92969799041748</v>
       </c>
       <c r="G596" t="n">
-        <v>7.03105306625366</v>
+        <v>7.03105354309082</v>
       </c>
       <c r="H596" t="n">
         <v>3230176</v>
@@ -17769,7 +17769,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G600" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H600" t="n">
         <v>11169423</v>
@@ -17798,7 +17798,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939523696899</v>
+        <v>7.38939476013184</v>
       </c>
       <c r="H601" t="n">
         <v>4478703</v>
@@ -17827,7 +17827,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G602" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H602" t="n">
         <v>3638485</v>
@@ -17914,7 +17914,7 @@
         <v>9.83242416381836</v>
       </c>
       <c r="G605" t="n">
-        <v>8.7181510925293</v>
+        <v>8.71815013885498</v>
       </c>
       <c r="H605" t="n">
         <v>23153988</v>
@@ -17943,7 +17943,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H606" t="n">
         <v>9737590</v>
@@ -17972,7 +17972,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G607" t="n">
-        <v>8.54009342193604</v>
+        <v>8.54009246826172</v>
       </c>
       <c r="H607" t="n">
         <v>5543597</v>
@@ -18001,7 +18001,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G608" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H608" t="n">
         <v>4747845</v>
@@ -18030,7 +18030,7 @@
         <v>10.0909738540649</v>
       </c>
       <c r="G609" t="n">
-        <v>8.9473991394043</v>
+        <v>8.94740009307861</v>
       </c>
       <c r="H609" t="n">
         <v>8237079</v>
@@ -18088,7 +18088,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37539005279541</v>
+        <v>8.37538909912109</v>
       </c>
       <c r="H611" t="n">
         <v>5678009</v>
@@ -18117,7 +18117,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065380096436</v>
+        <v>8.19065475463867</v>
       </c>
       <c r="H612" t="n">
         <v>4712315</v>
@@ -18146,7 +18146,7 @@
         <v>8.79822540283203</v>
       </c>
       <c r="G613" t="n">
-        <v>7.80115365982056</v>
+        <v>7.80115413665771</v>
       </c>
       <c r="H613" t="n">
         <v>4731371</v>
@@ -18262,7 +18262,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H617" t="n">
         <v>5676159</v>
@@ -18349,7 +18349,7 @@
         <v>9.31783485412598</v>
       </c>
       <c r="G620" t="n">
-        <v>8.26187896728516</v>
+        <v>8.26187801361084</v>
       </c>
       <c r="H620" t="n">
         <v>3046319</v>
@@ -18378,7 +18378,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H621" t="n">
         <v>4359962</v>
@@ -18407,7 +18407,7 @@
         <v>9.72448635101318</v>
       </c>
       <c r="G622" t="n">
-        <v>8.62244510650635</v>
+        <v>8.62244415283203</v>
       </c>
       <c r="H622" t="n">
         <v>5253374</v>
@@ -18436,7 +18436,7 @@
         <v>9.85250568389893</v>
       </c>
       <c r="G623" t="n">
-        <v>8.7359561920166</v>
+        <v>8.73595523834229</v>
       </c>
       <c r="H623" t="n">
         <v>3059274</v>
@@ -18465,7 +18465,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902694702148</v>
+        <v>8.56902599334717</v>
       </c>
       <c r="H624" t="n">
         <v>3124054</v>
@@ -18610,7 +18610,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G629" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H629" t="n">
         <v>1664123</v>
@@ -18813,7 +18813,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G636" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H636" t="n">
         <v>6312564</v>
@@ -18871,7 +18871,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H638" t="n">
         <v>2970699</v>
@@ -18929,7 +18929,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G640" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H640" t="n">
         <v>1067132</v>
@@ -18958,7 +18958,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.7114725112915</v>
+        <v>8.71147441864014</v>
       </c>
       <c r="H641" t="n">
         <v>2154097</v>
@@ -19045,7 +19045,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G644" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H644" t="n">
         <v>5210482</v>
@@ -19074,7 +19074,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009632110596</v>
+        <v>9.25009727478027</v>
       </c>
       <c r="H645" t="n">
         <v>6365259</v>
@@ -19103,7 +19103,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G646" t="n">
-        <v>9.39254474639893</v>
+        <v>9.39254379272461</v>
       </c>
       <c r="H646" t="n">
         <v>3391737</v>
@@ -19161,7 +19161,7 @@
         <v>10.0181789398193</v>
       </c>
       <c r="G648" t="n">
-        <v>8.88285446166992</v>
+        <v>8.88285350799561</v>
       </c>
       <c r="H648" t="n">
         <v>3244003</v>
@@ -19219,7 +19219,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G650" t="n">
-        <v>9.01639747619629</v>
+        <v>9.01639652252197</v>
       </c>
       <c r="H650" t="n">
         <v>2301830</v>
@@ -19277,7 +19277,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100601196289</v>
+        <v>9.12100505828857</v>
       </c>
       <c r="H652" t="n">
         <v>2816086</v>
@@ -19335,7 +19335,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G654" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H654" t="n">
         <v>2782854</v>
@@ -19422,7 +19422,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H657" t="n">
         <v>3819447</v>
@@ -19567,7 +19567,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686973571777</v>
+        <v>9.31686878204346</v>
       </c>
       <c r="H662" t="n">
         <v>5059956</v>
@@ -19625,7 +19625,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317378997803</v>
+        <v>9.79317283630371</v>
       </c>
       <c r="H664" t="n">
         <v>4580403</v>
@@ -19741,7 +19741,7 @@
         <v>11.200478553772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.93116855621338</v>
+        <v>9.93116760253906</v>
       </c>
       <c r="H668" t="n">
         <v>2563518</v>
@@ -19770,7 +19770,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139934539795</v>
+        <v>10.3139925003052</v>
       </c>
       <c r="H669" t="n">
         <v>8750009</v>
@@ -19973,7 +19973,7 @@
         <v>11.6046199798584</v>
       </c>
       <c r="G676" t="n">
-        <v>10.2895097732544</v>
+        <v>10.2895088195801</v>
       </c>
       <c r="H676" t="n">
         <v>1818429</v>
@@ -20002,7 +20002,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H677" t="n">
         <v>2314476</v>
@@ -20031,7 +20031,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G678" t="n">
-        <v>10.0157451629639</v>
+        <v>10.0157461166382</v>
       </c>
       <c r="H678" t="n">
         <v>2115163</v>
@@ -20118,7 +20118,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H681" t="n">
         <v>2245212</v>
@@ -20234,7 +20234,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99348926544189</v>
+        <v>9.99349021911621</v>
       </c>
       <c r="H685" t="n">
         <v>2940239</v>
@@ -20292,7 +20292,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694797515869</v>
+        <v>10.2694787979126</v>
       </c>
       <c r="H687" t="n">
         <v>2357662</v>
@@ -20321,7 +20321,7 @@
         <v>11.5017032623291</v>
       </c>
       <c r="G688" t="n">
-        <v>10.1982564926147</v>
+        <v>10.1982555389404</v>
       </c>
       <c r="H688" t="n">
         <v>1979022</v>
@@ -20350,7 +20350,7 @@
         <v>11.9259252548218</v>
       </c>
       <c r="G689" t="n">
-        <v>10.5744028091431</v>
+        <v>10.5744018554688</v>
       </c>
       <c r="H689" t="n">
         <v>2992968</v>
@@ -20379,7 +20379,7 @@
         <v>11.328498840332</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0446796417236</v>
+        <v>10.0446805953979</v>
       </c>
       <c r="H690" t="n">
         <v>5499203</v>
@@ -20408,7 +20408,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.3941192626953</v>
+        <v>10.394118309021</v>
       </c>
       <c r="H691" t="n">
         <v>4155413</v>
@@ -20437,7 +20437,7 @@
         <v>12.0489253997803</v>
       </c>
       <c r="G692" t="n">
-        <v>10.683464050293</v>
+        <v>10.6834630966187</v>
       </c>
       <c r="H692" t="n">
         <v>2537540</v>
@@ -20524,7 +20524,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.756911277771</v>
+        <v>10.7569122314453</v>
       </c>
       <c r="H695" t="n">
         <v>4827551</v>
@@ -20582,7 +20582,7 @@
         <v>12.4580860137939</v>
       </c>
       <c r="G697" t="n">
-        <v>11.0462551116943</v>
+        <v>11.0462560653687</v>
       </c>
       <c r="H697" t="n">
         <v>11143856</v>
@@ -20640,7 +20640,7 @@
         <v>13.2086343765259</v>
       </c>
       <c r="G699" t="n">
-        <v>11.7117462158203</v>
+        <v>11.7117471694946</v>
       </c>
       <c r="H699" t="n">
         <v>7959306</v>
@@ -20727,7 +20727,7 @@
         <v>13.5500202178955</v>
       </c>
       <c r="G702" t="n">
-        <v>12.014443397522</v>
+        <v>12.0144443511963</v>
       </c>
       <c r="H702" t="n">
         <v>7155972</v>
@@ -20814,7 +20814,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856685638428</v>
+        <v>12.0856676101685</v>
       </c>
       <c r="H705" t="n">
         <v>4491851</v>
@@ -20988,7 +20988,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395774841309</v>
+        <v>11.0395784378052</v>
       </c>
       <c r="H711" t="n">
         <v>3266745</v>
@@ -21017,7 +21017,7 @@
         <v>12.7065954208374</v>
       </c>
       <c r="G712" t="n">
-        <v>11.2666015625</v>
+        <v>11.2666025161743</v>
       </c>
       <c r="H712" t="n">
         <v>5559737</v>
@@ -21046,7 +21046,7 @@
         <v>12.7015752792358</v>
       </c>
       <c r="G713" t="n">
-        <v>11.2621507644653</v>
+        <v>11.262149810791</v>
       </c>
       <c r="H713" t="n">
         <v>2952425</v>
@@ -21162,7 +21162,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364080429077</v>
+        <v>10.4364070892334</v>
       </c>
       <c r="H717" t="n">
         <v>3926528</v>
@@ -21278,7 +21278,7 @@
         <v>11.7979049682617</v>
       </c>
       <c r="G721" t="n">
-        <v>10.4608898162842</v>
+        <v>10.4608907699585</v>
       </c>
       <c r="H721" t="n">
         <v>10788083</v>
@@ -21336,7 +21336,7 @@
         <v>11.8857622146606</v>
       </c>
       <c r="G723" t="n">
-        <v>10.5387916564941</v>
+        <v>10.5387907028198</v>
       </c>
       <c r="H723" t="n">
         <v>2694375</v>
@@ -21394,7 +21394,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.3941192626953</v>
+        <v>10.394118309021</v>
       </c>
       <c r="H725" t="n">
         <v>5437862</v>
@@ -21423,7 +21423,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H726" t="n">
         <v>2638902</v>
@@ -21452,7 +21452,7 @@
         <v>11.7025184631348</v>
       </c>
       <c r="G727" t="n">
-        <v>10.376314163208</v>
+        <v>10.3763132095337</v>
       </c>
       <c r="H727" t="n">
         <v>2777725</v>
@@ -21481,7 +21481,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H728" t="n">
         <v>6325209</v>
@@ -21510,7 +21510,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006381988525</v>
+        <v>10.3006391525269</v>
       </c>
       <c r="H729" t="n">
         <v>3047850</v>
@@ -21539,7 +21539,7 @@
         <v>11.7251100540161</v>
       </c>
       <c r="G730" t="n">
-        <v>10.3963441848755</v>
+        <v>10.3963451385498</v>
       </c>
       <c r="H730" t="n">
         <v>2649841</v>
@@ -21684,7 +21684,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580516815186</v>
+        <v>9.34580421447754</v>
       </c>
       <c r="H735" t="n">
         <v>2646670</v>
@@ -21713,7 +21713,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G736" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H736" t="n">
         <v>2599002</v>
@@ -21771,7 +21771,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G738" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H738" t="n">
         <v>10323921</v>
@@ -21800,7 +21800,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081153869629</v>
+        <v>8.29081249237061</v>
       </c>
       <c r="H739" t="n">
         <v>8509660</v>
@@ -21858,7 +21858,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889633178711</v>
+        <v>7.77889585494995</v>
       </c>
       <c r="H741" t="n">
         <v>8894223</v>
@@ -21916,7 +21916,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219253540039</v>
+        <v>8.46219158172607</v>
       </c>
       <c r="H743" t="n">
         <v>3711740</v>
@@ -21945,7 +21945,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H744" t="n">
         <v>2830649</v>
@@ -21974,7 +21974,7 @@
         <v>9.65922069549561</v>
       </c>
       <c r="G745" t="n">
-        <v>8.56457614898682</v>
+        <v>8.5645751953125</v>
       </c>
       <c r="H745" t="n">
         <v>3590690</v>
@@ -22090,7 +22090,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G749" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H749" t="n">
         <v>3226454</v>
@@ -22177,7 +22177,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G752" t="n">
-        <v>8.25519943237305</v>
+        <v>8.25520038604736</v>
       </c>
       <c r="H752" t="n">
         <v>4141957</v>
@@ -22206,7 +22206,7 @@
         <v>9.33540630340576</v>
       </c>
       <c r="G753" t="n">
-        <v>8.27745723724365</v>
+        <v>8.27745819091797</v>
       </c>
       <c r="H753" t="n">
         <v>2716829</v>
@@ -22264,7 +22264,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466569900513</v>
+        <v>7.91466617584229</v>
       </c>
       <c r="H755" t="n">
         <v>4636928</v>
@@ -22293,7 +22293,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.81228256225586</v>
+        <v>7.81228160858154</v>
       </c>
       <c r="H756" t="n">
         <v>3199541</v>
@@ -22380,7 +22380,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H759" t="n">
         <v>5059632</v>
@@ -22409,7 +22409,7 @@
         <v>8.17318725585938</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24694919586182</v>
+        <v>7.24694871902466</v>
       </c>
       <c r="H760" t="n">
         <v>5578537</v>
@@ -22438,7 +22438,7 @@
         <v>8.12800407409668</v>
       </c>
       <c r="G761" t="n">
-        <v>7.20688629150391</v>
+        <v>7.20688581466675</v>
       </c>
       <c r="H761" t="n">
         <v>4333423</v>
@@ -22467,7 +22467,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873378753662</v>
+        <v>6.96873331069946</v>
       </c>
       <c r="H762" t="n">
         <v>4541420</v>
@@ -22583,7 +22583,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576219558716</v>
+        <v>7.90576267242432</v>
       </c>
       <c r="H766" t="n">
         <v>6705143</v>
@@ -22728,7 +22728,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G771" t="n">
-        <v>8.39764595031738</v>
+        <v>8.3976469039917</v>
       </c>
       <c r="H771" t="n">
         <v>5244277</v>
@@ -22757,7 +22757,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G772" t="n">
-        <v>8.25519943237305</v>
+        <v>8.25520038604736</v>
       </c>
       <c r="H772" t="n">
         <v>3230113</v>
@@ -22786,7 +22786,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096927642822</v>
+        <v>8.39096832275391</v>
       </c>
       <c r="H773" t="n">
         <v>2691134</v>
@@ -22815,7 +22815,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H774" t="n">
         <v>4518486</v>
@@ -22931,7 +22931,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G778" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H778" t="n">
         <v>3928570</v>
@@ -22960,7 +22960,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G779" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H779" t="n">
         <v>5108708</v>
@@ -23018,7 +23018,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G781" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H781" t="n">
         <v>3452225</v>
@@ -23076,7 +23076,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G783" t="n">
-        <v>8.94517421722412</v>
+        <v>8.9451732635498</v>
       </c>
       <c r="H783" t="n">
         <v>2493851</v>
@@ -23192,7 +23192,7 @@
         <v>10.3445043563843</v>
       </c>
       <c r="G787" t="n">
-        <v>9.17219924926758</v>
+        <v>9.17219829559326</v>
       </c>
       <c r="H787" t="n">
         <v>3191829</v>
@@ -23221,7 +23221,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G788" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H788" t="n">
         <v>2462687</v>
@@ -23250,7 +23250,7 @@
         <v>10.4298496246338</v>
       </c>
       <c r="G789" t="n">
-        <v>9.24787139892578</v>
+        <v>9.2478723526001</v>
       </c>
       <c r="H789" t="n">
         <v>2010428</v>
@@ -23337,7 +23337,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G792" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H792" t="n">
         <v>1988992</v>
@@ -23453,7 +23453,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G796" t="n">
-        <v>9.43705940246582</v>
+        <v>9.4370584487915</v>
       </c>
       <c r="H796" t="n">
         <v>5910919</v>
@@ -23540,7 +23540,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H799" t="n">
         <v>2749374</v>
@@ -23656,7 +23656,7 @@
         <v>10.8440322875977</v>
       </c>
       <c r="G803" t="n">
-        <v>9.61511611938477</v>
+        <v>9.61511707305908</v>
       </c>
       <c r="H803" t="n">
         <v>5049854</v>
@@ -23714,7 +23714,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H805" t="n">
         <v>7839193</v>
@@ -23743,7 +23743,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232891082764</v>
+        <v>9.96232986450195</v>
       </c>
       <c r="H806" t="n">
         <v>5597634</v>
@@ -23801,7 +23801,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496046066284</v>
+        <v>10.3496036529541</v>
       </c>
       <c r="H808" t="n">
         <v>2858722</v>
@@ -24004,7 +24004,7 @@
         <v>12.3150053024292</v>
       </c>
       <c r="G815" t="n">
-        <v>10.9193887710571</v>
+        <v>10.9193897247314</v>
       </c>
       <c r="H815" t="n">
         <v>3038261</v>
@@ -24033,7 +24033,7 @@
         <v>12.1091690063477</v>
       </c>
       <c r="G816" t="n">
-        <v>10.7368803024292</v>
+        <v>10.7368793487549</v>
       </c>
       <c r="H816" t="n">
         <v>3221057</v>
@@ -24062,7 +24062,7 @@
         <v>12.2145967483521</v>
       </c>
       <c r="G817" t="n">
-        <v>10.8303594589233</v>
+        <v>10.8303604125977</v>
       </c>
       <c r="H817" t="n">
         <v>2672807</v>
@@ -24120,7 +24120,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G819" t="n">
-        <v>10.9883861541748</v>
+        <v>10.9883871078491</v>
       </c>
       <c r="H819" t="n">
         <v>2021022</v>
@@ -24381,7 +24381,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147802352905</v>
+        <v>10.8147811889648</v>
       </c>
       <c r="H828" t="n">
         <v>2456179</v>
@@ -24410,7 +24410,7 @@
         <v>12.2522497177124</v>
       </c>
       <c r="G829" t="n">
-        <v>10.8637447357178</v>
+        <v>10.8637456893921</v>
       </c>
       <c r="H829" t="n">
         <v>3054118</v>
@@ -24468,7 +24468,7 @@
         <v>12.4856977462769</v>
       </c>
       <c r="G831" t="n">
-        <v>11.0707368850708</v>
+        <v>11.0707378387451</v>
       </c>
       <c r="H831" t="n">
         <v>5821659</v>
@@ -24497,7 +24497,7 @@
         <v>12.6312885284424</v>
       </c>
       <c r="G832" t="n">
-        <v>11.1998300552368</v>
+        <v>11.1998291015625</v>
       </c>
       <c r="H832" t="n">
         <v>2539989</v>
@@ -24555,7 +24555,7 @@
         <v>12.0991277694702</v>
       </c>
       <c r="G834" t="n">
-        <v>10.7279777526855</v>
+        <v>10.7279767990112</v>
       </c>
       <c r="H834" t="n">
         <v>3226626</v>
@@ -24584,7 +24584,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G835" t="n">
-        <v>10.4386339187622</v>
+        <v>10.4386329650879</v>
       </c>
       <c r="H835" t="n">
         <v>4190619</v>
@@ -24642,7 +24642,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295736312866</v>
+        <v>10.3295726776123</v>
       </c>
       <c r="H837" t="n">
         <v>2609971</v>
@@ -24671,7 +24671,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271909713745</v>
+        <v>10.2271890640259</v>
       </c>
       <c r="H838" t="n">
         <v>2776794</v>
@@ -24700,7 +24700,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G839" t="n">
-        <v>10.4386339187622</v>
+        <v>10.4386329650879</v>
       </c>
       <c r="H839" t="n">
         <v>3240942</v>
@@ -24845,7 +24845,7 @@
         <v>11.3912544250488</v>
       </c>
       <c r="G844" t="n">
-        <v>10.100323677063</v>
+        <v>10.1003246307373</v>
       </c>
       <c r="H844" t="n">
         <v>5169154</v>
@@ -24874,7 +24874,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G845" t="n">
-        <v>10.2383184432983</v>
+        <v>10.2383193969727</v>
       </c>
       <c r="H845" t="n">
         <v>2752665</v>
@@ -24990,7 +24990,7 @@
         <v>10.836501121521</v>
       </c>
       <c r="G849" t="n">
-        <v>9.60843849182129</v>
+        <v>9.60843944549561</v>
       </c>
       <c r="H849" t="n">
         <v>2642683</v>
@@ -25019,7 +25019,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H850" t="n">
         <v>3580640</v>
@@ -25193,7 +25193,7 @@
         <v>10.4072589874268</v>
       </c>
       <c r="G856" t="n">
-        <v>9.2278413772583</v>
+        <v>9.22784042358398</v>
       </c>
       <c r="H856" t="n">
         <v>2374666</v>
@@ -25251,7 +25251,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G858" t="n">
-        <v>9.2701301574707</v>
+        <v>9.27012920379639</v>
       </c>
       <c r="H858" t="n">
         <v>2728302</v>
@@ -25280,7 +25280,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G859" t="n">
-        <v>9.16329383850098</v>
+        <v>9.16329479217529</v>
       </c>
       <c r="H859" t="n">
         <v>1906242</v>
@@ -25425,7 +25425,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G864" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H864" t="n">
         <v>1703266</v>
@@ -25570,7 +25570,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G869" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H869" t="n">
         <v>2768616</v>
@@ -25628,7 +25628,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G871" t="n">
-        <v>9.07204055786133</v>
+        <v>9.07204151153564</v>
       </c>
       <c r="H871" t="n">
         <v>6949172</v>
@@ -25744,7 +25744,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395671844482</v>
+        <v>9.58395576477051</v>
       </c>
       <c r="H875" t="n">
         <v>2681902</v>
@@ -25773,7 +25773,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G876" t="n">
-        <v>9.23451900482178</v>
+        <v>9.23451805114746</v>
       </c>
       <c r="H876" t="n">
         <v>3483538</v>
@@ -25831,7 +25831,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G878" t="n">
-        <v>9.2701301574707</v>
+        <v>9.27012920379639</v>
       </c>
       <c r="H878" t="n">
         <v>1207602</v>
@@ -25860,7 +25860,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G879" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H879" t="n">
         <v>2123211</v>
@@ -25889,7 +25889,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G880" t="n">
-        <v>9.55947208404541</v>
+        <v>9.55947303771973</v>
       </c>
       <c r="H880" t="n">
         <v>2840452</v>
@@ -25918,7 +25918,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G881" t="n">
-        <v>9.6062126159668</v>
+        <v>9.60621356964111</v>
       </c>
       <c r="H881" t="n">
         <v>3879724</v>
@@ -26005,7 +26005,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079208374023</v>
+        <v>9.69079113006592</v>
       </c>
       <c r="H884" t="n">
         <v>1520396</v>
@@ -26034,7 +26034,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G885" t="n">
-        <v>9.49047565460205</v>
+        <v>9.49047470092773</v>
       </c>
       <c r="H885" t="n">
         <v>1721405</v>
@@ -26121,7 +26121,7 @@
         <v>10.9820928573608</v>
       </c>
       <c r="G888" t="n">
-        <v>9.73753070831299</v>
+        <v>9.7375316619873</v>
       </c>
       <c r="H888" t="n">
         <v>1257161</v>
@@ -26266,7 +26266,7 @@
         <v>11.0272760391235</v>
       </c>
       <c r="G893" t="n">
-        <v>9.77759456634521</v>
+        <v>9.7775936126709</v>
       </c>
       <c r="H893" t="n">
         <v>2592934</v>
@@ -26353,7 +26353,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H896" t="n">
         <v>5491999</v>
@@ -26411,7 +26411,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070003509521</v>
+        <v>10.1070013046265</v>
       </c>
       <c r="H898" t="n">
         <v>2738861</v>
@@ -26527,7 +26527,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304798126221</v>
+        <v>9.71304893493652</v>
       </c>
       <c r="H902" t="n">
         <v>2481185</v>
@@ -26556,7 +26556,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H903" t="n">
         <v>2794057</v>
@@ -26643,7 +26643,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G906" t="n">
-        <v>10.0157451629639</v>
+        <v>10.0157461166382</v>
       </c>
       <c r="H906" t="n">
         <v>2792394</v>
@@ -26672,7 +26672,7 @@
         <v>11.4941720962524</v>
       </c>
       <c r="G907" t="n">
-        <v>10.1915788650513</v>
+        <v>10.191577911377</v>
       </c>
       <c r="H907" t="n">
         <v>5764525</v>
@@ -26701,7 +26701,7 @@
         <v>11.5845394134521</v>
       </c>
       <c r="G908" t="n">
-        <v>10.2717046737671</v>
+        <v>10.2717037200928</v>
       </c>
       <c r="H908" t="n">
         <v>2267960</v>
@@ -26788,7 +26788,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794006347656</v>
+        <v>9.99794101715088</v>
       </c>
       <c r="H911" t="n">
         <v>3280881</v>
@@ -26846,7 +26846,7 @@
         <v>10.7411136627197</v>
       </c>
       <c r="G913" t="n">
-        <v>9.5238618850708</v>
+        <v>9.52386093139648</v>
       </c>
       <c r="H913" t="n">
         <v>4157164</v>
@@ -26904,7 +26904,7 @@
         <v>10.4248304367065</v>
       </c>
       <c r="G915" t="n">
-        <v>9.24342155456543</v>
+        <v>9.24342060089111</v>
       </c>
       <c r="H915" t="n">
         <v>2417247</v>
@@ -26933,7 +26933,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G916" t="n">
-        <v>8.92514324188232</v>
+        <v>8.92514228820801</v>
       </c>
       <c r="H916" t="n">
         <v>4019358</v>
@@ -26991,7 +26991,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G918" t="n">
-        <v>9.12545776367188</v>
+        <v>9.12545871734619</v>
       </c>
       <c r="H918" t="n">
         <v>3054696</v>
@@ -27049,7 +27049,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G920" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H920" t="n">
         <v>3210453</v>
@@ -27107,7 +27107,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.95185089111328</v>
+        <v>8.9518518447876</v>
       </c>
       <c r="H922" t="n">
         <v>2394616</v>
@@ -27223,7 +27223,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G926" t="n">
-        <v>9.31464385986328</v>
+        <v>9.31464290618896</v>
       </c>
       <c r="H926" t="n">
         <v>1774533</v>
@@ -27252,7 +27252,7 @@
         <v>10.2842588424683</v>
       </c>
       <c r="G927" t="n">
-        <v>9.11878108978271</v>
+        <v>9.1187801361084</v>
       </c>
       <c r="H927" t="n">
         <v>2220798</v>
@@ -27281,7 +27281,7 @@
         <v>10.3545436859131</v>
       </c>
       <c r="G928" t="n">
-        <v>9.18110084533691</v>
+        <v>9.1810998916626</v>
       </c>
       <c r="H928" t="n">
         <v>1304029</v>
@@ -27310,7 +27310,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H929" t="n">
         <v>2564513</v>
@@ -27368,7 +27368,7 @@
         <v>10.9092969894409</v>
       </c>
       <c r="G931" t="n">
-        <v>9.67298603057861</v>
+        <v>9.6729850769043</v>
       </c>
       <c r="H931" t="n">
         <v>2301134</v>
@@ -27426,7 +27426,7 @@
         <v>10.9067869186401</v>
       </c>
       <c r="G933" t="n">
-        <v>9.67076015472412</v>
+        <v>9.6707592010498</v>
       </c>
       <c r="H933" t="n">
         <v>1044571</v>
@@ -27455,7 +27455,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G934" t="n">
-        <v>9.43705940246582</v>
+        <v>9.4370584487915</v>
       </c>
       <c r="H934" t="n">
         <v>1857397</v>
@@ -27629,7 +27629,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.1047744750977</v>
+        <v>10.1047735214233</v>
       </c>
       <c r="H940" t="n">
         <v>3374955</v>
@@ -27658,7 +27658,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136770248413</v>
+        <v>10.1136779785156</v>
       </c>
       <c r="H941" t="n">
         <v>3120641</v>
@@ -27687,7 +27687,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403875350952</v>
+        <v>10.1403856277466</v>
       </c>
       <c r="H942" t="n">
         <v>2004685</v>
@@ -27716,7 +27716,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230537414551</v>
+        <v>10.4230527877808</v>
       </c>
       <c r="H943" t="n">
         <v>5842648</v>
@@ -27890,7 +27890,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392383575439</v>
+        <v>9.56392574310303</v>
       </c>
       <c r="H949" t="n">
         <v>2157126</v>
@@ -28035,7 +28035,7 @@
         <v>10.2164840698242</v>
       </c>
       <c r="G954" t="n">
-        <v>9.05868530273438</v>
+        <v>9.05868625640869</v>
       </c>
       <c r="H954" t="n">
         <v>3488046</v>
@@ -28151,7 +28151,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G958" t="n">
-        <v>9.1655216217041</v>
+        <v>9.16552066802979</v>
       </c>
       <c r="H958" t="n">
         <v>3044501</v>
@@ -28209,7 +28209,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00971984863281</v>
+        <v>9.00972080230713</v>
       </c>
       <c r="H960" t="n">
         <v>3059945</v>
@@ -28267,7 +28267,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G962" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H962" t="n">
         <v>3934669</v>
@@ -28325,7 +28325,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G964" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H964" t="n">
         <v>4071910</v>
@@ -28354,7 +28354,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686973571777</v>
+        <v>9.31686878204346</v>
       </c>
       <c r="H965" t="n">
         <v>2851396</v>
@@ -28441,7 +28441,7 @@
         <v>10.3294429779053</v>
       </c>
       <c r="G968" t="n">
-        <v>9.15884304046631</v>
+        <v>9.15884399414062</v>
       </c>
       <c r="H968" t="n">
         <v>2590661</v>
@@ -28470,7 +28470,7 @@
         <v>10.2792387008667</v>
       </c>
       <c r="G969" t="n">
-        <v>9.11433029174805</v>
+        <v>9.11432933807373</v>
       </c>
       <c r="H969" t="n">
         <v>2928089</v>
@@ -28586,7 +28586,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65962982177734</v>
+        <v>9.65963077545166</v>
       </c>
       <c r="H973" t="n">
         <v>3880597</v>
@@ -28615,7 +28615,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G974" t="n">
-        <v>9.51050662994385</v>
+        <v>9.51050758361816</v>
       </c>
       <c r="H974" t="n">
         <v>4349124</v>
@@ -28673,7 +28673,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H976" t="n">
         <v>4961745</v>
@@ -28731,7 +28731,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G978" t="n">
-        <v>9.6062126159668</v>
+        <v>9.60621356964111</v>
       </c>
       <c r="H978" t="n">
         <v>5460186</v>
@@ -28789,7 +28789,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H980" t="n">
         <v>4874447</v>
@@ -28818,7 +28818,7 @@
         <v>11.2306022644043</v>
       </c>
       <c r="G981" t="n">
-        <v>9.95787715911865</v>
+        <v>9.95787811279297</v>
       </c>
       <c r="H981" t="n">
         <v>2713471</v>
@@ -28847,7 +28847,7 @@
         <v>11.1402349472046</v>
       </c>
       <c r="G982" t="n">
-        <v>9.87775230407715</v>
+        <v>9.87775135040283</v>
       </c>
       <c r="H982" t="n">
         <v>2778291</v>
@@ -28876,7 +28876,7 @@
         <v>11.0573978424072</v>
       </c>
       <c r="G983" t="n">
-        <v>9.80430126190186</v>
+        <v>9.80430221557617</v>
       </c>
       <c r="H983" t="n">
         <v>2502883</v>
@@ -28992,7 +28992,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H987" t="n">
         <v>8182251</v>
@@ -29050,7 +29050,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812492370605</v>
+        <v>9.40812397003174</v>
       </c>
       <c r="H989" t="n">
         <v>2714951</v>
@@ -29195,7 +29195,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G994" t="n">
-        <v>9.45931529998779</v>
+        <v>9.45931625366211</v>
       </c>
       <c r="H994" t="n">
         <v>2914765</v>
@@ -29282,7 +29282,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G997" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H997" t="n">
         <v>4136816</v>
@@ -29311,7 +29311,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G998" t="n">
-        <v>9.07204055786133</v>
+        <v>9.07204151153564</v>
       </c>
       <c r="H998" t="n">
         <v>3580666</v>
@@ -29398,7 +29398,7 @@
         <v>10.427339553833</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.24564552307129</v>
+        <v>9.24564647674561</v>
       </c>
       <c r="H1001" t="n">
         <v>2310864</v>
@@ -29427,7 +29427,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.39254474639893</v>
+        <v>9.39254379272461</v>
       </c>
       <c r="H1002" t="n">
         <v>2942968</v>
@@ -29514,7 +29514,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H1005" t="n">
         <v>2212645</v>
@@ -29572,7 +29572,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467578887939</v>
+        <v>9.33467674255371</v>
       </c>
       <c r="H1007" t="n">
         <v>3861795</v>
@@ -29601,7 +29601,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.45931529998779</v>
+        <v>9.45931625366211</v>
       </c>
       <c r="H1008" t="n">
         <v>2116813</v>
@@ -29630,7 +29630,7 @@
         <v>10.7938280105591</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.57060241699219</v>
+        <v>9.57060146331787</v>
       </c>
       <c r="H1009" t="n">
         <v>3043149</v>
@@ -29717,7 +29717,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H1012" t="n">
         <v>3418112</v>
@@ -29746,7 +29746,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.5616979598999</v>
+        <v>9.56169891357422</v>
       </c>
       <c r="H1013" t="n">
         <v>1635593</v>
@@ -29804,7 +29804,7 @@
         <v>10.934398651123</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.69524192810059</v>
+        <v>9.6952428817749</v>
       </c>
       <c r="H1015" t="n">
         <v>2311969</v>
@@ -29891,7 +29891,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H1018" t="n">
         <v>2839366</v>
@@ -29920,7 +29920,7 @@
         <v>11.1728668212891</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.90668487548828</v>
+        <v>9.9066858291626</v>
       </c>
       <c r="H1019" t="n">
         <v>3341541</v>
@@ -30065,7 +30065,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317378997803</v>
+        <v>9.79317283630371</v>
       </c>
       <c r="H1024" t="n">
         <v>1781897</v>
@@ -30152,7 +30152,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H1027" t="n">
         <v>2223593</v>
@@ -30210,7 +30210,7 @@
         <v>11.1126232147217</v>
       </c>
       <c r="G1029" t="n">
-        <v>9.85326862335205</v>
+        <v>9.85326957702637</v>
       </c>
       <c r="H1029" t="n">
         <v>1959789</v>
@@ -30239,7 +30239,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G1030" t="n">
-        <v>9.4615421295166</v>
+        <v>9.46154117584229</v>
       </c>
       <c r="H1030" t="n">
         <v>7606013</v>
@@ -30297,7 +30297,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G1032" t="n">
-        <v>9.12545776367188</v>
+        <v>9.12545871734619</v>
       </c>
       <c r="H1032" t="n">
         <v>2852190</v>
@@ -30471,7 +30471,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.20623397827148</v>
+        <v>8.2062349319458</v>
       </c>
       <c r="H1038" t="n">
         <v>4452658</v>
@@ -30529,7 +30529,7 @@
         <v>9.75962924957275</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.65360450744629</v>
+        <v>8.65360546112061</v>
       </c>
       <c r="H1040" t="n">
         <v>7621307</v>
@@ -30558,7 +30558,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H1041" t="n">
         <v>4707102</v>
@@ -30674,7 +30674,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H1045" t="n">
         <v>5766485</v>
@@ -30761,7 +30761,7 @@
         <v>9.55630302429199</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.47332191467285</v>
+        <v>8.47332096099854</v>
       </c>
       <c r="H1048" t="n">
         <v>2650515</v>
@@ -30819,7 +30819,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.43548488616943</v>
+        <v>8.43548393249512</v>
       </c>
       <c r="H1050" t="n">
         <v>4171244</v>
@@ -30906,7 +30906,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657657623291</v>
+        <v>7.71657609939575</v>
       </c>
       <c r="H1053" t="n">
         <v>7295256</v>
@@ -30935,7 +30935,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754774093628</v>
+        <v>7.62754726409912</v>
       </c>
       <c r="H1054" t="n">
         <v>5328087</v>
@@ -31109,7 +31109,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H1060" t="n">
         <v>4984381</v>
@@ -31138,7 +31138,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.70832347869873</v>
+        <v>6.70832395553589</v>
       </c>
       <c r="H1061" t="n">
         <v>5838598</v>
@@ -31196,7 +31196,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.95000410079956</v>
+        <v>4.9500036239624</v>
       </c>
       <c r="H1063" t="n">
         <v>15725169</v>
@@ -31225,7 +31225,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.95000410079956</v>
+        <v>4.9500036239624</v>
       </c>
       <c r="H1064" t="n">
         <v>14702152</v>
@@ -31312,7 +31312,7 @@
         <v>5.16848611831665</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.58276033401489</v>
+        <v>4.58275985717773</v>
       </c>
       <c r="H1067" t="n">
         <v>9831037</v>
@@ -31457,7 +31457,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342130661011</v>
+        <v>5.00342178344727</v>
       </c>
       <c r="H1072" t="n">
         <v>6911923</v>
@@ -31486,7 +31486,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.8899097442627</v>
+        <v>4.88990926742554</v>
       </c>
       <c r="H1073" t="n">
         <v>3925543</v>
@@ -31515,7 +31515,7 @@
         <v>5.85627889633179</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.19260787963867</v>
+        <v>5.19260740280151</v>
       </c>
       <c r="H1074" t="n">
         <v>6147761</v>
@@ -31544,7 +31544,7 @@
         <v>5.8261570930481</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.16589975357056</v>
+        <v>5.1658992767334</v>
       </c>
       <c r="H1075" t="n">
         <v>7136455</v>
@@ -31573,7 +31573,7 @@
         <v>5.89393186569214</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.22599363327026</v>
+        <v>5.22599315643311</v>
       </c>
       <c r="H1076" t="n">
         <v>4232448</v>
@@ -31631,7 +31631,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.98561573028564</v>
+        <v>4.98561525344849</v>
       </c>
       <c r="H1078" t="n">
         <v>2485771</v>
@@ -31660,7 +31660,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1079" t="n">
-        <v>4.98561573028564</v>
+        <v>4.98561525344849</v>
       </c>
       <c r="H1079" t="n">
         <v>4812027</v>
@@ -31718,7 +31718,7 @@
         <v>6.06713485717773</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.37956762313843</v>
+        <v>5.37956809997559</v>
       </c>
       <c r="H1081" t="n">
         <v>8617110</v>
@@ -31776,7 +31776,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950614929199</v>
+        <v>5.33950567245483</v>
       </c>
       <c r="H1083" t="n">
         <v>4088673</v>
@@ -31863,7 +31863,7 @@
         <v>6.04956388473511</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.36398887634277</v>
+        <v>5.36398839950562</v>
       </c>
       <c r="H1086" t="n">
         <v>5596784</v>
@@ -31921,7 +31921,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1088" t="n">
         <v>5337056</v>
@@ -31950,7 +31950,7 @@
         <v>5.47473001480103</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.85429811477661</v>
+        <v>4.85429859161377</v>
       </c>
       <c r="H1089" t="n">
         <v>3542169</v>
@@ -32037,7 +32037,7 @@
         <v>5.28395509719849</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.685142993927</v>
+        <v>4.68514347076416</v>
       </c>
       <c r="H1092" t="n">
         <v>4658214</v>
@@ -32124,7 +32124,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1095" t="n">
         <v>3476797</v>
@@ -32182,7 +32182,7 @@
         <v>5.55505609512329</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.92552137374878</v>
+        <v>4.92552089691162</v>
       </c>
       <c r="H1097" t="n">
         <v>3776492</v>
@@ -32211,7 +32211,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928503036499</v>
+        <v>5.19928550720215</v>
       </c>
       <c r="H1098" t="n">
         <v>4783125</v>
@@ -32240,7 +32240,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041393280029</v>
+        <v>5.21041345596313</v>
       </c>
       <c r="H1099" t="n">
         <v>4870688</v>
@@ -32298,7 +32298,7 @@
         <v>5.79101419448853</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.1347393989563</v>
+        <v>5.13473892211914</v>
       </c>
       <c r="H1101" t="n">
         <v>3599923</v>
@@ -32385,7 +32385,7 @@
         <v>5.80858516693115</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15031862258911</v>
+        <v>5.15031909942627</v>
       </c>
       <c r="H1104" t="n">
         <v>2378841</v>
@@ -32414,7 +32414,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248207092285</v>
+        <v>5.11248159408569</v>
       </c>
       <c r="H1105" t="n">
         <v>2051727</v>
@@ -32646,7 +32646,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.79800033569336</v>
+        <v>4.79800081253052</v>
       </c>
       <c r="H1113" t="n">
         <v>3350805</v>
@@ -32733,7 +32733,7 @@
         <v>5.46217918395996</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.86507511138916</v>
+        <v>4.865074634552</v>
       </c>
       <c r="H1116" t="n">
         <v>3829378</v>
@@ -32762,7 +32762,7 @@
         <v>5.30905723571777</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.72869157791138</v>
+        <v>4.72869110107422</v>
       </c>
       <c r="H1117" t="n">
         <v>7700374</v>
@@ -32907,7 +32907,7 @@
         <v>5.79854488372803</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.16467046737671</v>
+        <v>5.16466999053955</v>
       </c>
       <c r="H1122" t="n">
         <v>12491580</v>
@@ -32965,7 +32965,7 @@
         <v>6.46876621246338</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.76162528991699</v>
+        <v>5.76162576675415</v>
       </c>
       <c r="H1124" t="n">
         <v>11268120</v>
@@ -32994,7 +32994,7 @@
         <v>6.59176588058472</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.87117958068848</v>
+        <v>5.87117910385132</v>
       </c>
       <c r="H1125" t="n">
         <v>10577677</v>
@@ -33023,7 +33023,7 @@
         <v>6.41354179382324</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.71243810653687</v>
+        <v>5.71243762969971</v>
       </c>
       <c r="H1126" t="n">
         <v>6490655</v>
@@ -33139,7 +33139,7 @@
         <v>5.99182987213135</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33682632446289</v>
+        <v>5.33682584762573</v>
       </c>
       <c r="H1130" t="n">
         <v>5065402</v>
@@ -33197,7 +33197,7 @@
         <v>5.98680877685547</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.33235359191895</v>
+        <v>5.3323540687561</v>
       </c>
       <c r="H1132" t="n">
         <v>5119610</v>
@@ -33342,7 +33342,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.08418226242065</v>
+        <v>5.0841817855835</v>
       </c>
       <c r="H1137" t="n">
         <v>3931365</v>
@@ -33429,7 +33429,7 @@
         <v>5.61530113220215</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.00145769119263</v>
+        <v>5.00145816802979</v>
       </c>
       <c r="H1140" t="n">
         <v>4272132</v>
@@ -33487,7 +33487,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.97686290740967</v>
+        <v>4.97686338424683</v>
       </c>
       <c r="H1142" t="n">
         <v>3387639</v>
@@ -33574,7 +33574,7 @@
         <v>5.68558597564697</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.06405925750732</v>
+        <v>5.06405973434448</v>
       </c>
       <c r="H1145" t="n">
         <v>3689754</v>
@@ -33661,7 +33661,7 @@
         <v>5.27642488479614</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.69962644577026</v>
+        <v>4.69962596893311</v>
       </c>
       <c r="H1148" t="n">
         <v>5584746</v>
@@ -33748,7 +33748,7 @@
         <v>5.28897619247437</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.71080589294434</v>
+        <v>4.71080541610718</v>
       </c>
       <c r="H1151" t="n">
         <v>6369097</v>
@@ -33777,7 +33777,7 @@
         <v>5.36679220199585</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.78011512756348</v>
+        <v>4.78011465072632</v>
       </c>
       <c r="H1152" t="n">
         <v>6019418</v>
@@ -33806,7 +33806,7 @@
         <v>5.47724008560181</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.87848901748657</v>
+        <v>4.87848949432373</v>
       </c>
       <c r="H1153" t="n">
         <v>3853871</v>
@@ -34067,7 +34067,7 @@
         <v>4.92123222351074</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.38326168060303</v>
+        <v>4.38326215744019</v>
       </c>
       <c r="H1162" t="n">
         <v>24661467</v>
@@ -34154,7 +34154,7 @@
         <v>4.57357120513916</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.07360601425171</v>
+        <v>4.07360553741455</v>
       </c>
       <c r="H1165" t="n">
         <v>7438646</v>
@@ -34299,7 +34299,7 @@
         <v>4.96892595291138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.42574167251587</v>
+        <v>4.42574214935303</v>
       </c>
       <c r="H1170" t="n">
         <v>3451603</v>
@@ -34415,7 +34415,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1174" t="n">
-        <v>4.34190034866333</v>
+        <v>4.34189987182617</v>
       </c>
       <c r="H1174" t="n">
         <v>4695442</v>
@@ -34589,7 +34589,7 @@
         <v>4.66895818710327</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.15856599807739</v>
+        <v>4.15856552124023</v>
       </c>
       <c r="H1180" t="n">
         <v>6557504</v>
@@ -34734,7 +34734,7 @@
         <v>4.50579500198364</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.01323890686035</v>
+        <v>4.01323843002319</v>
       </c>
       <c r="H1185" t="n">
         <v>4155094</v>
@@ -34821,7 +34821,7 @@
         <v>4.39032697677612</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.91039323806763</v>
+        <v>3.91039347648621</v>
       </c>
       <c r="H1188" t="n">
         <v>4258438</v>
@@ -34850,7 +34850,7 @@
         <v>4.29242897033691</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.82319688796997</v>
+        <v>3.82319736480713</v>
       </c>
       <c r="H1189" t="n">
         <v>7837081</v>
@@ -34937,7 +34937,7 @@
         <v>4.19327592849731</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.73488306999207</v>
+        <v>3.73488283157349</v>
       </c>
       <c r="H1192" t="n">
         <v>4846298</v>
@@ -34995,7 +34995,7 @@
         <v>4.07906293869019</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.63315558433533</v>
+        <v>3.63315534591675</v>
       </c>
       <c r="H1194" t="n">
         <v>8280016</v>
@@ -35111,7 +35111,7 @@
         <v>4.22465419769287</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.76283121109009</v>
+        <v>3.76283097267151</v>
       </c>
       <c r="H1198" t="n">
         <v>5589044</v>
@@ -35401,7 +35401,7 @@
         <v>3.56321811676025</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.17370057106018</v>
+        <v>3.17370080947876</v>
       </c>
       <c r="H1208" t="n">
         <v>6464136</v>
@@ -35459,7 +35459,7 @@
         <v>3.86444091796875</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.44199514389038</v>
+        <v>3.4419949054718</v>
       </c>
       <c r="H1210" t="n">
         <v>7063864</v>
@@ -35604,7 +35604,7 @@
         <v>3.79415607452393</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.37939357757568</v>
+        <v>3.3793933391571</v>
       </c>
       <c r="H1215" t="n">
         <v>3909509</v>
@@ -35633,7 +35633,7 @@
         <v>3.65609502792358</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.25642490386963</v>
+        <v>3.25642466545105</v>
       </c>
       <c r="H1216" t="n">
         <v>4082735</v>
@@ -35807,7 +35807,7 @@
         <v>3.59585094451904</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.20276618003845</v>
+        <v>3.20276641845703</v>
       </c>
       <c r="H1222" t="n">
         <v>5346240</v>
@@ -35836,7 +35836,7 @@
         <v>3.62597298622131</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.22959542274475</v>
+        <v>3.22959566116333</v>
       </c>
       <c r="H1223" t="n">
         <v>3204692</v>
@@ -35865,7 +35865,7 @@
         <v>3.68496203422546</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.28213596343994</v>
+        <v>3.28213620185852</v>
       </c>
       <c r="H1224" t="n">
         <v>4139377</v>
@@ -36010,7 +36010,7 @@
         <v>3.78411507606506</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.370450258255</v>
+        <v>3.37045001983643</v>
       </c>
       <c r="H1229" t="n">
         <v>8618018</v>
@@ -36184,7 +36184,7 @@
         <v>4.6940598487854</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.1809229850769</v>
+        <v>4.18092346191406</v>
       </c>
       <c r="H1235" t="n">
         <v>15804964</v>
@@ -36387,7 +36387,7 @@
         <v>4.89487504959106</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.35978603363037</v>
+        <v>4.35978651046753</v>
       </c>
       <c r="H1242" t="n">
         <v>6079967</v>
@@ -36445,7 +36445,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.2770619392395</v>
+        <v>4.27706241607666</v>
       </c>
       <c r="H1244" t="n">
         <v>4685519</v>
@@ -36474,7 +36474,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.47157526016235</v>
+        <v>4.47157573699951</v>
       </c>
       <c r="H1245" t="n">
         <v>7739906</v>
@@ -36532,7 +36532,7 @@
         <v>5.42201614379883</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.82930183410645</v>
+        <v>4.8293023109436</v>
       </c>
       <c r="H1247" t="n">
         <v>8336834</v>
@@ -36561,7 +36561,7 @@
         <v>5.30654716491699</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.72645616531372</v>
+        <v>4.72645568847656</v>
       </c>
       <c r="H1248" t="n">
         <v>6460441</v>
@@ -36619,7 +36619,7 @@
         <v>5.1333441734314</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.57218647003174</v>
+        <v>4.5721869468689</v>
       </c>
       <c r="H1250" t="n">
         <v>5110006</v>
@@ -36706,7 +36706,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.62584447860718</v>
+        <v>4.62584495544434</v>
       </c>
       <c r="H1253" t="n">
         <v>2827257</v>
@@ -36735,7 +36735,7 @@
         <v>5.35675096511841</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.77117156982422</v>
+        <v>4.77117109298706</v>
       </c>
       <c r="H1254" t="n">
         <v>5955094</v>
@@ -36793,7 +36793,7 @@
         <v>5.37683200836182</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.78905725479126</v>
+        <v>4.78905773162842</v>
       </c>
       <c r="H1256" t="n">
         <v>1840506</v>
@@ -36880,7 +36880,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1259" t="n">
         <v>4061775</v>
@@ -36938,7 +36938,7 @@
         <v>5.46719884872437</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.86954545974731</v>
+        <v>4.86954593658447</v>
       </c>
       <c r="H1261" t="n">
         <v>2064399</v>
@@ -36967,7 +36967,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1262" t="n">
         <v>5407097</v>
@@ -36996,7 +36996,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.86060237884521</v>
+        <v>4.86060285568237</v>
       </c>
       <c r="H1263" t="n">
         <v>3511782</v>
@@ -37112,7 +37112,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1267" t="n">
         <v>3396789</v>
@@ -37257,7 +37257,7 @@
         <v>5.82364702224731</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.18702793121338</v>
+        <v>5.18702840805054</v>
       </c>
       <c r="H1272" t="n">
         <v>7105248</v>
@@ -37315,7 +37315,7 @@
         <v>6.17256307601929</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.49780225753784</v>
+        <v>5.49780178070068</v>
       </c>
       <c r="H1274" t="n">
         <v>7287173</v>
@@ -37344,7 +37344,7 @@
         <v>6.10729789733887</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.4396710395813</v>
+        <v>5.43967151641846</v>
       </c>
       <c r="H1275" t="n">
         <v>6169237</v>
@@ -37431,7 +37431,7 @@
         <v>6.08721685409546</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.42178535461426</v>
+        <v>5.42178583145142</v>
       </c>
       <c r="H1278" t="n">
         <v>4068724</v>
@@ -37460,7 +37460,7 @@
         <v>6.00689077377319</v>
       </c>
       <c r="G1279" t="n">
-        <v>5.3502402305603</v>
+        <v>5.35024070739746</v>
       </c>
       <c r="H1279" t="n">
         <v>3024433</v>
@@ -37547,7 +37547,7 @@
         <v>5.85878896713257</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.21832847595215</v>
+        <v>5.21832895278931</v>
       </c>
       <c r="H1282" t="n">
         <v>3059439</v>
@@ -37692,7 +37692,7 @@
         <v>5.34169006347656</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.75775671005249</v>
+        <v>4.75775718688965</v>
       </c>
       <c r="H1287" t="n">
         <v>4046294</v>
@@ -37721,7 +37721,7 @@
         <v>5.59019899368286</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.97910022735596</v>
+        <v>4.9790997505188</v>
       </c>
       <c r="H1288" t="n">
         <v>7589590</v>
@@ -37924,7 +37924,7 @@
         <v>5.98178911209106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.32788324356079</v>
+        <v>5.32788276672363</v>
       </c>
       <c r="H1295" t="n">
         <v>5483636</v>
@@ -38098,7 +38098,7 @@
         <v>6.55160188674927</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.8354058265686</v>
+        <v>5.83540630340576</v>
       </c>
       <c r="H1301" t="n">
         <v>9385518</v>
@@ -38156,7 +38156,7 @@
         <v>6.3457670211792</v>
       </c>
       <c r="G1303" t="n">
-        <v>5.65207242965698</v>
+        <v>5.65207195281982</v>
       </c>
       <c r="H1303" t="n">
         <v>6157528</v>
@@ -38185,7 +38185,7 @@
         <v>6.35078716278076</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.65654325485229</v>
+        <v>5.65654373168945</v>
       </c>
       <c r="H1304" t="n">
         <v>5745479</v>
@@ -38214,7 +38214,7 @@
         <v>6.40852212905884</v>
       </c>
       <c r="G1305" t="n">
-        <v>5.70796680450439</v>
+        <v>5.70796728134155</v>
       </c>
       <c r="H1305" t="n">
         <v>3560044</v>
@@ -38243,7 +38243,7 @@
         <v>6.63192892074585</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.90695190429688</v>
+        <v>5.90695142745972</v>
       </c>
       <c r="H1306" t="n">
         <v>7874391</v>
@@ -38330,7 +38330,7 @@
         <v>6.00940084457397</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.35247611999512</v>
+        <v>5.35247659683228</v>
       </c>
       <c r="H1309" t="n">
         <v>24228663</v>
@@ -38388,7 +38388,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.08418226242065</v>
+        <v>5.0841817855835</v>
       </c>
       <c r="H1311" t="n">
         <v>8961866</v>
@@ -38417,7 +38417,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1312" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1312" t="n">
         <v>9655227</v>
@@ -38504,7 +38504,7 @@
         <v>5.91652393341064</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.26975202560425</v>
+        <v>5.26975250244141</v>
       </c>
       <c r="H1315" t="n">
         <v>12797834</v>
@@ -38533,7 +38533,7 @@
         <v>6.07215595245361</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.40837144851685</v>
+        <v>5.40837097167969</v>
       </c>
       <c r="H1316" t="n">
         <v>9400118</v>
@@ -38591,7 +38591,7 @@
         <v>6.07717609405518</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.41284227371216</v>
+        <v>5.41284275054932</v>
       </c>
       <c r="H1318" t="n">
         <v>4627496</v>
@@ -38649,7 +38649,7 @@
         <v>6.12486982345581</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.455322265625</v>
+        <v>5.45532274246216</v>
       </c>
       <c r="H1320" t="n">
         <v>2675208</v>
@@ -38707,7 +38707,7 @@
         <v>5.97174787521362</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.31893968582153</v>
+        <v>5.31893920898438</v>
       </c>
       <c r="H1322" t="n">
         <v>5171781</v>
@@ -38765,7 +38765,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.31670331954956</v>
+        <v>5.31670379638672</v>
       </c>
       <c r="H1324" t="n">
         <v>4027905</v>
@@ -38852,7 +38852,7 @@
         <v>5.69060611724854</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.06853103637695</v>
+        <v>5.06853055953979</v>
       </c>
       <c r="H1327" t="n">
         <v>7314312</v>
@@ -39055,7 +39055,7 @@
         <v>5.87887096405029</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.23621511459351</v>
+        <v>5.23621559143066</v>
       </c>
       <c r="H1334" t="n">
         <v>3164034</v>
@@ -39287,7 +39287,7 @@
         <v>5.83870792388916</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.20044279098511</v>
+        <v>5.20044231414795</v>
       </c>
       <c r="H1342" t="n">
         <v>4486409</v>
@@ -39374,7 +39374,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.97686290740967</v>
+        <v>4.97686338424683</v>
       </c>
       <c r="H1345" t="n">
         <v>5024234</v>
@@ -39490,7 +39490,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.94556331634521</v>
+        <v>4.94556283950806</v>
       </c>
       <c r="H1349" t="n">
         <v>4621291</v>
@@ -39577,7 +39577,7 @@
         <v>4.87855911254883</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.34525394439697</v>
+        <v>4.34525346755981</v>
       </c>
       <c r="H1352" t="n">
         <v>14868855</v>
@@ -39606,7 +39606,7 @@
         <v>4.82333517074585</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.29606628417969</v>
+        <v>4.29606676101685</v>
       </c>
       <c r="H1353" t="n">
         <v>10990037</v>
@@ -39751,7 +39751,7 @@
         <v>5.06054782867432</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.50734853744507</v>
+        <v>4.50734806060791</v>
       </c>
       <c r="H1358" t="n">
         <v>3316325</v>
@@ -39954,7 +39954,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.69068336486816</v>
+        <v>4.69068288803101</v>
       </c>
       <c r="H1365" t="n">
         <v>9046399</v>
@@ -40012,7 +40012,7 @@
         <v>5.1383638381958</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.57665777206421</v>
+        <v>4.57665729522705</v>
       </c>
       <c r="H1367" t="n">
         <v>2528599</v>
@@ -40070,7 +40070,7 @@
         <v>5.12832307815552</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.56771469116211</v>
+        <v>4.56771421432495</v>
       </c>
       <c r="H1369" t="n">
         <v>2605182</v>
@@ -40186,7 +40186,7 @@
         <v>5.11828184127808</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.55877113342285</v>
+        <v>4.55877065658569</v>
       </c>
       <c r="H1373" t="n">
         <v>4133342</v>
@@ -40244,7 +40244,7 @@
         <v>5.3793420791626</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.79129314422607</v>
+        <v>4.79129266738892</v>
       </c>
       <c r="H1375" t="n">
         <v>10178926</v>
@@ -40273,7 +40273,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1376" t="n">
         <v>5287449</v>
@@ -40389,7 +40389,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1380" t="n">
         <v>6843942</v>
@@ -40476,7 +40476,7 @@
         <v>5.56760692596436</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.95897722244263</v>
+        <v>4.95897769927979</v>
       </c>
       <c r="H1383" t="n">
         <v>4282870</v>
@@ -40679,7 +40679,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.72421979904175</v>
+        <v>4.72422027587891</v>
       </c>
       <c r="H1390" t="n">
         <v>3701384</v>
@@ -40737,7 +40737,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.72421979904175</v>
+        <v>4.72422027587891</v>
       </c>
       <c r="H1392" t="n">
         <v>2649454</v>
@@ -40766,7 +40766,7 @@
         <v>5.29901599884033</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.71974802017212</v>
+        <v>4.71974754333496</v>
       </c>
       <c r="H1393" t="n">
         <v>2108129</v>
@@ -40853,7 +40853,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1396" t="n">
-        <v>4.56324291229248</v>
+        <v>4.56324338912964</v>
       </c>
       <c r="H1396" t="n">
         <v>3303148</v>
@@ -40882,7 +40882,7 @@
         <v>5.22873115539551</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.65714645385742</v>
+        <v>4.65714597702026</v>
       </c>
       <c r="H1397" t="n">
         <v>3565887</v>
@@ -40911,7 +40911,7 @@
         <v>5.21868991851807</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.64820289611816</v>
+        <v>4.64820241928101</v>
       </c>
       <c r="H1398" t="n">
         <v>2418474</v>
@@ -41027,7 +41027,7 @@
         <v>4.90617084503174</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.36984729766846</v>
+        <v>4.3698468208313</v>
       </c>
       <c r="H1402" t="n">
         <v>5231002</v>
@@ -41056,7 +41056,7 @@
         <v>4.97143602371216</v>
       </c>
       <c r="G1403" t="n">
-        <v>4.42797803878784</v>
+        <v>4.42797756195068</v>
       </c>
       <c r="H1403" t="n">
         <v>3203342</v>
@@ -41114,7 +41114,7 @@
         <v>4.88483476638794</v>
       </c>
       <c r="G1405" t="n">
-        <v>4.35084342956543</v>
+        <v>4.35084295272827</v>
       </c>
       <c r="H1405" t="n">
         <v>3408367</v>
@@ -41172,7 +41172,7 @@
         <v>4.90240621566772</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.36649370193481</v>
+        <v>4.36649417877197</v>
       </c>
       <c r="H1407" t="n">
         <v>3512290</v>
@@ -41288,7 +41288,7 @@
         <v>4.75681495666504</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.23681831359863</v>
+        <v>4.23681783676147</v>
       </c>
       <c r="H1411" t="n">
         <v>4771701</v>
@@ -41462,7 +41462,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1417" t="n">
-        <v>4.52970600128174</v>
+        <v>4.5297064781189</v>
       </c>
       <c r="H1417" t="n">
         <v>3747890</v>
@@ -41549,7 +41549,7 @@
         <v>4.91119194030762</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.37431907653809</v>
+        <v>4.37431955337524</v>
       </c>
       <c r="H1420" t="n">
         <v>4386657</v>
@@ -41636,7 +41636,7 @@
         <v>4.92499780654907</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.38661623001099</v>
+        <v>4.38661575317383</v>
       </c>
       <c r="H1423" t="n">
         <v>3890806</v>
@@ -41694,7 +41694,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.56324291229248</v>
+        <v>4.56324338912964</v>
       </c>
       <c r="H1425" t="n">
         <v>5305491</v>
@@ -41723,7 +41723,7 @@
         <v>5.16597604751587</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.60125112533569</v>
+        <v>4.60125160217285</v>
       </c>
       <c r="H1426" t="n">
         <v>3581797</v>
@@ -41868,7 +41868,7 @@
         <v>4.98147678375244</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.43692111968994</v>
+        <v>4.43692064285278</v>
       </c>
       <c r="H1431" t="n">
         <v>1848823</v>
@@ -41926,7 +41926,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.2770619392395</v>
+        <v>4.27706241607666</v>
       </c>
       <c r="H1433" t="n">
         <v>3356625</v>
@@ -42013,7 +42013,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.47157526016235</v>
+        <v>4.47157573699951</v>
       </c>
       <c r="H1436" t="n">
         <v>3876966</v>
@@ -42216,7 +42216,7 @@
         <v>4.96139478683472</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41903448104858</v>
+        <v>4.41903400421143</v>
       </c>
       <c r="H1443" t="n">
         <v>3045903</v>
@@ -42332,7 +42332,7 @@
         <v>5.01662015914917</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.46822261810303</v>
+        <v>4.46822214126587</v>
       </c>
       <c r="H1447" t="n">
         <v>5734258</v>
@@ -42390,7 +42390,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.62584447860718</v>
+        <v>4.62584495544434</v>
       </c>
       <c r="H1449" t="n">
         <v>7048976</v>
@@ -42419,7 +42419,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.52970600128174</v>
+        <v>4.5297064781189</v>
       </c>
       <c r="H1450" t="n">
         <v>6506615</v>
@@ -42506,7 +42506,7 @@
         <v>4.99151802062988</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.44586420059204</v>
+        <v>4.4458646774292</v>
       </c>
       <c r="H1453" t="n">
         <v>2739262</v>
@@ -42535,7 +42535,7 @@
         <v>4.91244697570801</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.37543678283691</v>
+        <v>4.37543725967407</v>
       </c>
       <c r="H1454" t="n">
         <v>3529674</v>
@@ -42564,7 +42564,7 @@
         <v>5.07058906555176</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.51629209518433</v>
+        <v>4.51629161834717</v>
       </c>
       <c r="H1455" t="n">
         <v>5222595</v>
@@ -42825,7 +42825,7 @@
         <v>5.55003595352173</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.94332695007324</v>
+        <v>4.9433274269104</v>
       </c>
       <c r="H1464" t="n">
         <v>6413047</v>
@@ -42883,7 +42883,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.69068336486816</v>
+        <v>4.69068288803101</v>
       </c>
       <c r="H1466" t="n">
         <v>7328705</v>
@@ -42941,7 +42941,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.79800033569336</v>
+        <v>4.79800081253052</v>
       </c>
       <c r="H1468" t="n">
         <v>8090619</v>
@@ -42999,7 +42999,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1470" t="n">
         <v>6942701</v>
@@ -43144,7 +43144,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.91202592849731</v>
+        <v>4.91202640533447</v>
       </c>
       <c r="H1475" t="n">
         <v>2995584</v>
@@ -43202,7 +43202,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1477" t="n">
         <v>4075860</v>
@@ -43289,7 +43289,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.94556331634521</v>
+        <v>4.94556283950806</v>
       </c>
       <c r="H1480" t="n">
         <v>5065969</v>
@@ -43347,7 +43347,7 @@
         <v>4.87353897094727</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.34078216552734</v>
+        <v>4.3407826423645</v>
       </c>
       <c r="H1482" t="n">
         <v>28990116</v>
@@ -43492,7 +43492,7 @@
         <v>4.81203889846802</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.2860050201416</v>
+        <v>4.28600549697876</v>
       </c>
       <c r="H1487" t="n">
         <v>5381782</v>
@@ -43521,7 +43521,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.34190034866333</v>
+        <v>4.34189987182617</v>
       </c>
       <c r="H1488" t="n">
         <v>5511409</v>
@@ -43666,7 +43666,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.39220476150513</v>
+        <v>4.39220523834229</v>
       </c>
       <c r="H1493" t="n">
         <v>2167743</v>
@@ -43956,7 +43956,7 @@
         <v>4.46563196182251</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.97746634483337</v>
+        <v>3.97746610641479</v>
       </c>
       <c r="H1503" t="n">
         <v>7272410</v>
@@ -43985,7 +43985,7 @@
         <v>4.50328493118286</v>
       </c>
       <c r="G1504" t="n">
-        <v>4.01100301742554</v>
+        <v>4.0110034942627</v>
       </c>
       <c r="H1504" t="n">
         <v>4367193</v>
@@ -44014,7 +44014,7 @@
         <v>4.42170381546021</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.93833994865417</v>
+        <v>3.93834018707275</v>
       </c>
       <c r="H1505" t="n">
         <v>3362331</v>
@@ -44130,7 +44130,7 @@
         <v>4.59365177154541</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.09149122238159</v>
+        <v>4.09149169921875</v>
       </c>
       <c r="H1509" t="n">
         <v>4350486</v>
@@ -44188,7 +44188,7 @@
         <v>4.56729507446289</v>
       </c>
       <c r="G1511" t="n">
-        <v>4.06801557540894</v>
+        <v>4.06801605224609</v>
       </c>
       <c r="H1511" t="n">
         <v>4359136</v>
@@ -44275,7 +44275,7 @@
         <v>4.41040802001953</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.92827892303467</v>
+        <v>3.92827916145325</v>
       </c>
       <c r="H1514" t="n">
         <v>3179388</v>
@@ -44304,7 +44304,7 @@
         <v>4.4455509185791</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.95958042144775</v>
+        <v>3.95958018302917</v>
       </c>
       <c r="H1515" t="n">
         <v>2325197</v>
@@ -44333,7 +44333,7 @@
         <v>4.37275505065918</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.89474201202393</v>
+        <v>3.89474248886108</v>
       </c>
       <c r="H1516" t="n">
         <v>3004717</v>
@@ -44507,7 +44507,7 @@
         <v>4.55097913742065</v>
       </c>
       <c r="G1522" t="n">
-        <v>4.0534839630127</v>
+        <v>4.05348348617554</v>
       </c>
       <c r="H1522" t="n">
         <v>1502529</v>
@@ -44652,7 +44652,7 @@
         <v>4.78317213058472</v>
       </c>
       <c r="G1527" t="n">
-        <v>4.26029396057129</v>
+        <v>4.26029443740845</v>
       </c>
       <c r="H1527" t="n">
         <v>2970018</v>
@@ -44768,7 +44768,7 @@
         <v>4.91495704650879</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.37767314910889</v>
+        <v>4.37767267227173</v>
       </c>
       <c r="H1531" t="n">
         <v>2759069</v>
@@ -44913,7 +44913,7 @@
         <v>5.03042602539062</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.48051881790161</v>
+        <v>4.48051929473877</v>
       </c>
       <c r="H1536" t="n">
         <v>2349535</v>
@@ -44971,7 +44971,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.39220476150513</v>
+        <v>4.39220523834229</v>
       </c>
       <c r="H1538" t="n">
         <v>3995107</v>
@@ -45058,7 +45058,7 @@
         <v>5.01410913467407</v>
       </c>
       <c r="G1541" t="n">
-        <v>4.4659857749939</v>
+        <v>4.46598625183105</v>
       </c>
       <c r="H1541" t="n">
         <v>2334898</v>
@@ -45348,7 +45348,7 @@
         <v>2.99591493606567</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.66841316223145</v>
+        <v>2.66841292381287</v>
       </c>
       <c r="H1551" t="n">
         <v>17072505</v>
@@ -45377,7 +45377,7 @@
         <v>3.02854704856873</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.6974778175354</v>
+        <v>2.69747805595398</v>
       </c>
       <c r="H1552" t="n">
         <v>16828629</v>
@@ -45522,7 +45522,7 @@
         <v>2.8616189956665</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.54879760742188</v>
+        <v>2.54879784584045</v>
       </c>
       <c r="H1557" t="n">
         <v>12600027</v>
@@ -45551,7 +45551,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.5622124671936</v>
+        <v>2.56221222877502</v>
       </c>
       <c r="H1558" t="n">
         <v>9318354</v>
@@ -45725,7 +45725,7 @@
         <v>2.51521301269531</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.24025940895081</v>
+        <v>2.24025964736938</v>
       </c>
       <c r="H1564" t="n">
         <v>6732142</v>
@@ -45754,7 +45754,7 @@
         <v>2.56165099143982</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.28162097930908</v>
+        <v>2.28162121772766</v>
       </c>
       <c r="H1565" t="n">
         <v>16777908</v>
@@ -45899,7 +45899,7 @@
         <v>2.56792688369751</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.2872109413147</v>
+        <v>2.28721117973328</v>
       </c>
       <c r="H1570" t="n">
         <v>5399583</v>
@@ -45928,7 +45928,7 @@
         <v>2.37715196609497</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.11729073524475</v>
+        <v>2.11729097366333</v>
       </c>
       <c r="H1571" t="n">
         <v>6070659</v>
@@ -46015,7 +46015,7 @@
         <v>2.58047795295715</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.29839015007019</v>
+        <v>2.29838991165161</v>
       </c>
       <c r="H1574" t="n">
         <v>9240163</v>
@@ -46131,7 +46131,7 @@
         <v>2.46450710296631</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.19509649276733</v>
+        <v>2.19509673118591</v>
       </c>
       <c r="H1578" t="n">
         <v>4819541</v>
@@ -46247,7 +46247,7 @@
         <v>2.67335510253906</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.38111424446106</v>
+        <v>2.38111400604248</v>
       </c>
       <c r="H1582" t="n">
         <v>3911764</v>
@@ -46392,7 +46392,7 @@
         <v>2.86287403106689</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.54991579055786</v>
+        <v>2.54991555213928</v>
       </c>
       <c r="H1587" t="n">
         <v>13747439</v>
@@ -46479,7 +46479,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.5622124671936</v>
+        <v>2.56221222877502</v>
       </c>
       <c r="H1590" t="n">
         <v>10760896</v>
@@ -46508,7 +46508,7 @@
         <v>2.93943500518799</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.61810708045959</v>
+        <v>2.61810731887817</v>
       </c>
       <c r="H1591" t="n">
         <v>7063060</v>
@@ -46537,7 +46537,7 @@
         <v>2.87919092178345</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.56444883346558</v>
+        <v>2.564448595047</v>
       </c>
       <c r="H1592" t="n">
         <v>10358249</v>
@@ -46566,7 +46566,7 @@
         <v>2.84404802322388</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.53314757347107</v>
+        <v>2.53314781188965</v>
       </c>
       <c r="H1593" t="n">
         <v>5883247</v>
@@ -46595,7 +46595,7 @@
         <v>2.77878308296204</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.47501707077026</v>
+        <v>2.47501730918884</v>
       </c>
       <c r="H1594" t="n">
         <v>7471517</v>
@@ -46653,7 +46653,7 @@
         <v>2.80262994766235</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.49625706672668</v>
+        <v>2.49625730514526</v>
       </c>
       <c r="H1596" t="n">
         <v>3079893</v>
@@ -46711,7 +46711,7 @@
         <v>2.79384398460388</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.48843145370483</v>
+        <v>2.48843169212341</v>
       </c>
       <c r="H1598" t="n">
         <v>2912676</v>
@@ -46740,7 +46740,7 @@
         <v>2.75744605064392</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.4560124874115</v>
+        <v>2.45601272583008</v>
       </c>
       <c r="H1599" t="n">
         <v>3637078</v>
@@ -46769,7 +46769,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.43700909614563</v>
+        <v>2.43700885772705</v>
       </c>
       <c r="H1600" t="n">
         <v>2248107</v>
@@ -46798,7 +46798,7 @@
         <v>2.84028291702271</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.52979421615601</v>
+        <v>2.52979397773743</v>
       </c>
       <c r="H1601" t="n">
         <v>4359715</v>
@@ -46885,7 +46885,7 @@
         <v>2.92437410354614</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.60469269752502</v>
+        <v>2.6046929359436</v>
       </c>
       <c r="H1604" t="n">
         <v>10127429</v>
@@ -46914,7 +46914,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.43700909614563</v>
+        <v>2.43700885772705</v>
       </c>
       <c r="H1605" t="n">
         <v>8650581</v>
@@ -47233,7 +47233,7 @@
         <v>2.48509001731873</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.21342968940735</v>
+        <v>2.21342945098877</v>
       </c>
       <c r="H1616" t="n">
         <v>11509858</v>
@@ -47262,7 +47262,7 @@
         <v>2.53780388832092</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.26038074493408</v>
+        <v>2.26038098335266</v>
       </c>
       <c r="H1617" t="n">
         <v>13634558</v>
@@ -47320,7 +47320,7 @@
         <v>2.68841600418091</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.39452862739563</v>
+        <v>2.39452886581421</v>
       </c>
       <c r="H1619" t="n">
         <v>6670481</v>
@@ -47349,7 +47349,7 @@
         <v>2.90680289268494</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.58904218673706</v>
+        <v>2.58904242515564</v>
       </c>
       <c r="H1620" t="n">
         <v>11371682</v>
@@ -47581,7 +47581,7 @@
         <v>2.97517991065979</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.64994478225708</v>
+        <v>2.6499445438385</v>
       </c>
       <c r="H1628" t="n">
         <v>9786163</v>
@@ -47755,7 +47755,7 @@
         <v>2.72426104545593</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.4264554977417</v>
+        <v>2.42645525932312</v>
       </c>
       <c r="H1634" t="n">
         <v>3222869</v>
@@ -47900,7 +47900,7 @@
         <v>2.37423992156982</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.11469697952271</v>
+        <v>2.11469721794128</v>
       </c>
       <c r="H1639" t="n">
         <v>5658326</v>
@@ -47987,7 +47987,7 @@
         <v>1.96649694442749</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.75152695178986</v>
+        <v>1.75152707099915</v>
       </c>
       <c r="H1642" t="n">
         <v>12639154</v>
@@ -48016,7 +48016,7 @@
         <v>2.01657509803772</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.79613089561462</v>
+        <v>1.79613077640533</v>
       </c>
       <c r="H1643" t="n">
         <v>25382152</v>
@@ -48103,7 +48103,7 @@
         <v>2.21557092666626</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.97337317466736</v>
+        <v>1.97337329387665</v>
       </c>
       <c r="H1646" t="n">
         <v>8434013</v>
@@ -48132,7 +48132,7 @@
         <v>1.73798203468323</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.54799258708954</v>
+        <v>1.54799246788025</v>
       </c>
       <c r="H1647" t="n">
         <v>26496542</v>
@@ -48161,7 +48161,7 @@
         <v>1.59776198863983</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.42310082912445</v>
+        <v>1.42310070991516</v>
       </c>
       <c r="H1648" t="n">
         <v>48720201</v>
@@ -48190,7 +48190,7 @@
         <v>1.24932205677032</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.11275088787079</v>
+        <v>1.11275100708008</v>
       </c>
       <c r="H1649" t="n">
         <v>56877192</v>
@@ -48451,7 +48451,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98913502693176</v>
+        <v>2.98913478851318</v>
       </c>
       <c r="H1658" t="n">
         <v>6899464</v>
@@ -48538,7 +48538,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.73594272136688</v>
+        <v>1.73594284057617</v>
       </c>
       <c r="H1661" t="n">
         <v>7745580</v>
@@ -48567,7 +48567,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.98598700761795</v>
+        <v>0.985986948013306</v>
       </c>
       <c r="H1662" t="n">
         <v>25986719</v>
@@ -48596,7 +48596,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.04210007190704</v>
+        <v>1.04209995269775</v>
       </c>
       <c r="H1663" t="n">
         <v>15517197</v>
@@ -48625,7 +48625,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.730360746383667</v>
+        <v>0.730360686779022</v>
       </c>
       <c r="H1664" t="n">
         <v>50412931</v>
@@ -48770,7 +48770,7 @@
         <v>0.71340000629425</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.635413885116577</v>
+        <v>0.635413825511932</v>
       </c>
       <c r="H1669" t="n">
         <v>28781555</v>
@@ -48828,7 +48828,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.659106016159058</v>
+        <v>0.659106075763702</v>
       </c>
       <c r="H1671" t="n">
         <v>27445946</v>
@@ -48857,7 +48857,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.692061305046082</v>
+        <v>0.692061364650726</v>
       </c>
       <c r="H1672" t="n">
         <v>35674340</v>
@@ -48944,7 +48944,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.751737117767334</v>
+        <v>0.751737177371979</v>
       </c>
       <c r="H1675" t="n">
         <v>37326895</v>
@@ -49002,7 +49002,7 @@
         <v>0.833599984645844</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.742474019527435</v>
+        <v>0.74247407913208</v>
       </c>
       <c r="H1677" t="n">
         <v>19689110</v>
@@ -49205,7 +49205,7 @@
         <v>0.821799993515015</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.731963932514191</v>
+        <v>0.731963992118835</v>
       </c>
       <c r="H1684" t="n">
         <v>16957436</v>
@@ -49292,7 +49292,7 @@
         <v>0.762199997901917</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.678879201412201</v>
+        <v>0.678879261016846</v>
       </c>
       <c r="H1687" t="n">
         <v>13487789</v>
@@ -49524,7 +49524,7 @@
         <v>0.716400027275085</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.638085961341858</v>
+        <v>0.638085901737213</v>
       </c>
       <c r="H1695" t="n">
         <v>20717644</v>
@@ -49756,7 +49756,7 @@
         <v>0.674600005149841</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.600855350494385</v>
+        <v>0.60085529088974</v>
       </c>
       <c r="H1703" t="n">
         <v>12648147</v>
@@ -49785,7 +49785,7 @@
         <v>0.697399973869324</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.621162831783295</v>
+        <v>0.621162891387939</v>
       </c>
       <c r="H1704" t="n">
         <v>26443104</v>
@@ -49843,7 +49843,7 @@
         <v>0.683200001716614</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.60851514339447</v>
+        <v>0.608515202999115</v>
       </c>
       <c r="H1706" t="n">
         <v>9988795</v>
@@ -49872,7 +49872,7 @@
         <v>0.662199974060059</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589810788631439</v>
+        <v>0.589810848236084</v>
       </c>
       <c r="H1707" t="n">
         <v>13712596</v>
@@ -49901,7 +49901,7 @@
         <v>0.64300000667572</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.572709679603577</v>
+        <v>0.572709739208221</v>
       </c>
       <c r="H1708" t="n">
         <v>58766149</v>
@@ -49930,7 +49930,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.540645122528076</v>
+        <v>0.540645062923431</v>
       </c>
       <c r="H1709" t="n">
         <v>28764901</v>
@@ -49959,7 +49959,7 @@
         <v>0.584800004959106</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.520871877670288</v>
+        <v>0.520871937274933</v>
       </c>
       <c r="H1710" t="n">
         <v>20980769</v>
@@ -49988,7 +49988,7 @@
         <v>0.59280002117157</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.527997434139252</v>
+        <v>0.527997374534607</v>
       </c>
       <c r="H1711" t="n">
         <v>21540866</v>
@@ -50075,7 +50075,7 @@
         <v>0.597199976444244</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.531916379928589</v>
+        <v>0.531916320323944</v>
       </c>
       <c r="H1714" t="n">
         <v>19250857</v>
@@ -50191,7 +50191,7 @@
         <v>0.637600004673004</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.567900061607361</v>
+        <v>0.567900002002716</v>
       </c>
       <c r="H1718" t="n">
         <v>20242520</v>
@@ -50336,7 +50336,7 @@
         <v>0.72759997844696</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.648061573505402</v>
+        <v>0.648061513900757</v>
       </c>
       <c r="H1723" t="n">
         <v>11884557</v>
@@ -50365,7 +50365,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.620806634426117</v>
+        <v>0.620806694030762</v>
       </c>
       <c r="H1724" t="n">
         <v>15320781</v>
@@ -50626,7 +50626,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.658215403556824</v>
+        <v>0.658215343952179</v>
       </c>
       <c r="H1733" t="n">
         <v>21488740</v>
@@ -50655,7 +50655,7 @@
         <v>0.758199989795685</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.675316512584686</v>
+        <v>0.675316452980042</v>
       </c>
       <c r="H1734" t="n">
         <v>33917790</v>
@@ -50713,7 +50713,7 @@
         <v>0.828599989414215</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.738020658493042</v>
+        <v>0.738020598888397</v>
       </c>
       <c r="H1736" t="n">
         <v>35628898</v>
@@ -50742,7 +50742,7 @@
         <v>0.958599984645844</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.853809475898743</v>
+        <v>0.853809535503387</v>
       </c>
       <c r="H1737" t="n">
         <v>99646498</v>
@@ -50800,7 +50800,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.876432955265045</v>
+        <v>0.8764328956604</v>
       </c>
       <c r="H1739" t="n">
         <v>39414006</v>
@@ -50829,7 +50829,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.873760879039764</v>
+        <v>0.87376081943512</v>
       </c>
       <c r="H1740" t="n">
         <v>36774205</v>
@@ -51003,7 +51003,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.882667720317841</v>
+        <v>0.882667660713196</v>
       </c>
       <c r="H1746" t="n">
         <v>44222060</v>
@@ -51061,7 +51061,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.919185638427734</v>
+        <v>0.919185698032379</v>
       </c>
       <c r="H1748" t="n">
         <v>60743048</v>
@@ -51090,7 +51090,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.957485139369965</v>
+        <v>0.957485198974609</v>
       </c>
       <c r="H1749" t="n">
         <v>38369686</v>
@@ -51148,7 +51148,7 @@
         <v>1.09650003910065</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.976634919643402</v>
+        <v>0.976634860038757</v>
       </c>
       <c r="H1751" t="n">
         <v>33789817</v>
@@ -51177,7 +51177,7 @@
         <v>1.03250002861023</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.919631123542786</v>
+        <v>0.919631063938141</v>
       </c>
       <c r="H1752" t="n">
         <v>95803812</v>
@@ -51206,7 +51206,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.92185777425766</v>
+        <v>0.921857714653015</v>
       </c>
       <c r="H1753" t="n">
         <v>44395351</v>
@@ -51322,7 +51322,7 @@
         <v>1.04649996757507</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.932100594043732</v>
+        <v>0.932100653648376</v>
       </c>
       <c r="H1757" t="n">
         <v>32064633</v>
@@ -51351,7 +51351,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.926311194896698</v>
+        <v>0.926311135292053</v>
       </c>
       <c r="H1758" t="n">
         <v>21110965</v>
@@ -51409,7 +51409,7 @@
         <v>1.04750001430511</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.932991325855255</v>
+        <v>0.93299126625061</v>
       </c>
       <c r="H1760" t="n">
         <v>40631058</v>
@@ -51438,7 +51438,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.912950932979584</v>
+        <v>0.912950873374939</v>
       </c>
       <c r="H1761" t="n">
         <v>26582079</v>
@@ -51467,7 +51467,7 @@
         <v>1.01950001716614</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.908052206039429</v>
+        <v>0.908052146434784</v>
       </c>
       <c r="H1762" t="n">
         <v>27481158</v>
@@ -51525,7 +51525,7 @@
         <v>1.04449999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.930319249629974</v>
+        <v>0.93031919002533</v>
       </c>
       <c r="H1764" t="n">
         <v>52512389</v>
@@ -51786,7 +51786,7 @@
         <v>1.00650000572205</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.896473288536072</v>
+        <v>0.896473228931427</v>
       </c>
       <c r="H1773" t="n">
         <v>22532469</v>
@@ -51844,7 +51844,7 @@
         <v>1.04949998855591</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.934772670269012</v>
+        <v>0.934772729873657</v>
       </c>
       <c r="H1775" t="n">
         <v>27222601</v>
@@ -51931,7 +51931,7 @@
         <v>1.10950005054474</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.988213717937469</v>
+        <v>0.988213777542114</v>
       </c>
       <c r="H1778" t="n">
         <v>33156068</v>
@@ -51989,7 +51989,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.977970898151398</v>
+        <v>0.977970957756042</v>
       </c>
       <c r="H1780" t="n">
         <v>82522322</v>
@@ -52047,7 +52047,7 @@
         <v>1.12750005722046</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.00424611568451</v>
+        <v>1.00424599647522</v>
       </c>
       <c r="H1782" t="n">
         <v>38953976</v>
@@ -52076,7 +52076,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.05456972122192</v>
+        <v>1.05456960201263</v>
       </c>
       <c r="H1783" t="n">
         <v>44539150</v>
@@ -52424,7 +52424,7 @@
         <v>1.31149995326996</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.16813170909882</v>
+        <v>1.16813182830811</v>
       </c>
       <c r="H1795" t="n">
         <v>88039189</v>
@@ -52685,7 +52685,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.25141084194183</v>
+        <v>1.25141072273254</v>
       </c>
       <c r="H1804" t="n">
         <v>50505371</v>
@@ -52772,7 +52772,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.23092496395111</v>
+        <v>1.2309250831604</v>
       </c>
       <c r="H1807" t="n">
         <v>27498297</v>
@@ -52801,7 +52801,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.21845543384552</v>
+        <v>1.21845555305481</v>
       </c>
       <c r="H1808" t="n">
         <v>27228579</v>
@@ -52946,7 +52946,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H1813" t="n">
         <v>201277103</v>
@@ -53062,7 +53062,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.25586426258087</v>
+        <v>1.25586414337158</v>
       </c>
       <c r="H1817" t="n">
         <v>26785082</v>
@@ -53149,7 +53149,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.24962937831879</v>
+        <v>1.24962949752808</v>
       </c>
       <c r="H1820" t="n">
         <v>28478257</v>
@@ -53236,7 +53236,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.31464922428131</v>
+        <v>1.3146493434906</v>
       </c>
       <c r="H1823" t="n">
         <v>73649010</v>
@@ -53265,7 +53265,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.35116732120514</v>
+        <v>1.35116744041443</v>
       </c>
       <c r="H1824" t="n">
         <v>173226691</v>
@@ -53294,7 +53294,7 @@
         <v>1.53450000286102</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.36675441265106</v>
+        <v>1.36675429344177</v>
       </c>
       <c r="H1825" t="n">
         <v>147696002</v>
@@ -53381,7 +53381,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.31643080711365</v>
+        <v>1.31643068790436</v>
       </c>
       <c r="H1828" t="n">
         <v>36445476</v>
@@ -53497,7 +53497,7 @@
         <v>1.35749995708466</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.20910322666168</v>
+        <v>1.20910334587097</v>
       </c>
       <c r="H1832" t="n">
         <v>30266079</v>
@@ -53555,7 +53555,7 @@
         <v>1.26549994945526</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.12716042995453</v>
+        <v>1.12716031074524</v>
       </c>
       <c r="H1834" t="n">
         <v>56083977</v>
@@ -53584,7 +53584,7 @@
         <v>1.14049994945526</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.01582479476929</v>
+        <v>1.01582491397858</v>
       </c>
       <c r="H1835" t="n">
         <v>70991471</v>
@@ -53671,7 +53671,7 @@
         <v>1.23450005054474</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.09954917430878</v>
+        <v>1.09954929351807</v>
       </c>
       <c r="H1838" t="n">
         <v>44048652</v>
@@ -53729,7 +53729,7 @@
         <v>1.32550001144409</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.1806013584137</v>
+        <v>1.18060147762299</v>
       </c>
       <c r="H1840" t="n">
         <v>26361553</v>
@@ -53758,7 +53758,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.14007520675659</v>
+        <v>1.14007532596588</v>
       </c>
       <c r="H1841" t="n">
         <v>30477091</v>
@@ -53932,7 +53932,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23181569576263</v>
+        <v>1.23181581497192</v>
       </c>
       <c r="H1847" t="n">
         <v>23160786</v>
@@ -53990,7 +53990,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1849" t="n">
         <v>61303523</v>
@@ -54512,7 +54512,7 @@
         <v>1.25049996376038</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.11380016803741</v>
+        <v>1.11380004882812</v>
       </c>
       <c r="H1867" t="n">
         <v>30080800</v>
@@ -54628,7 +54628,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.150763630867</v>
+        <v>1.15076351165771</v>
       </c>
       <c r="H1871" t="n">
         <v>24313190</v>
@@ -54715,7 +54715,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.13473117351532</v>
+        <v>1.13473129272461</v>
       </c>
       <c r="H1874" t="n">
         <v>17632468</v>
@@ -54802,7 +54802,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.12048029899597</v>
+        <v>1.12048017978668</v>
       </c>
       <c r="H1877" t="n">
         <v>12144067</v>
@@ -54831,7 +54831,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.15788888931274</v>
+        <v>1.15788900852203</v>
       </c>
       <c r="H1878" t="n">
         <v>28606803</v>
@@ -54976,7 +54976,7 @@
         <v>1.25750005245209</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.12003493309021</v>
+        <v>1.1200350522995</v>
       </c>
       <c r="H1883" t="n">
         <v>22657079</v>
@@ -55005,7 +55005,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.12226152420044</v>
+        <v>1.12226164340973</v>
       </c>
       <c r="H1884" t="n">
         <v>17046265</v>
@@ -55121,7 +55121,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.07416462898254</v>
+        <v>1.07416474819183</v>
       </c>
       <c r="H1888" t="n">
         <v>25051867</v>
@@ -55150,7 +55150,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.13473117351532</v>
+        <v>1.13473129272461</v>
       </c>
       <c r="H1889" t="n">
         <v>28793517</v>
@@ -55440,7 +55440,7 @@
         <v>1.25450003147125</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.11736285686493</v>
+        <v>1.11736297607422</v>
       </c>
       <c r="H1899" t="n">
         <v>19379185</v>
@@ -55498,7 +55498,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.08663439750671</v>
+        <v>1.08663427829742</v>
       </c>
       <c r="H1901" t="n">
         <v>20926564</v>
@@ -55585,7 +55585,7 @@
         <v>1.16250002384186</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.03542006015778</v>
+        <v>1.03541994094849</v>
       </c>
       <c r="H1904" t="n">
         <v>44264066</v>
@@ -55643,7 +55643,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.04833483695984</v>
+        <v>1.04833495616913</v>
       </c>
       <c r="H1906" t="n">
         <v>29040859</v>
@@ -55672,7 +55672,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.07772755622864</v>
+        <v>1.07772743701935</v>
       </c>
       <c r="H1907" t="n">
         <v>35754602</v>
@@ -55875,7 +55875,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.30039834976196</v>
+        <v>1.30039846897125</v>
       </c>
       <c r="H1914" t="n">
         <v>60137225</v>
@@ -55904,7 +55904,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.31108665466309</v>
+        <v>1.3110865354538</v>
       </c>
       <c r="H1915" t="n">
         <v>40402535</v>
@@ -55933,7 +55933,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.32266545295715</v>
+        <v>1.32266557216644</v>
       </c>
       <c r="H1916" t="n">
         <v>40030022</v>
@@ -56020,7 +56020,7 @@
         <v>1.43949997425079</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.28213930130005</v>
+        <v>1.28213942050934</v>
       </c>
       <c r="H1919" t="n">
         <v>27592628</v>
@@ -56049,7 +56049,7 @@
         <v>1.43250000476837</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.27590465545654</v>
+        <v>1.27590453624725</v>
       </c>
       <c r="H1920" t="n">
         <v>21395530</v>
@@ -56078,7 +56078,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.30039834976196</v>
+        <v>1.30039846897125</v>
       </c>
       <c r="H1921" t="n">
         <v>18806426</v>
@@ -56194,7 +56194,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.32800960540771</v>
+        <v>1.328009724617</v>
       </c>
       <c r="H1925" t="n">
         <v>26562115</v>
@@ -56281,7 +56281,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1928" t="n">
         <v>65561642</v>
@@ -56310,7 +56310,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1929" t="n">
         <v>29757990</v>
@@ -56339,7 +56339,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1930" t="n">
-        <v>1.29683554172516</v>
+        <v>1.29683566093445</v>
       </c>
       <c r="H1930" t="n">
         <v>46308940</v>
@@ -56368,7 +56368,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.29327297210693</v>
+        <v>1.29327285289764</v>
       </c>
       <c r="H1931" t="n">
         <v>26931723</v>
@@ -56426,7 +56426,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.25586426258087</v>
+        <v>1.25586414337158</v>
       </c>
       <c r="H1933" t="n">
         <v>26197753</v>
@@ -56484,7 +56484,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.24339473247528</v>
+        <v>1.24339461326599</v>
       </c>
       <c r="H1935" t="n">
         <v>23656707</v>
@@ -56658,7 +56658,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.304851770401</v>
+        <v>1.30485188961029</v>
       </c>
       <c r="H1941" t="n">
         <v>36097664</v>
@@ -56687,7 +56687,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H1942" t="n">
         <v>21886700</v>
@@ -56774,7 +56774,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.33869791030884</v>
+        <v>1.33869779109955</v>
       </c>
       <c r="H1945" t="n">
         <v>21109505</v>
@@ -56861,7 +56861,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.32266545295715</v>
+        <v>1.32266557216644</v>
       </c>
       <c r="H1948" t="n">
         <v>24397332</v>
@@ -56948,7 +56948,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1951" t="n">
-        <v>1.40193629264832</v>
+        <v>1.4019364118576</v>
       </c>
       <c r="H1951" t="n">
         <v>45002851</v>
@@ -56977,7 +56977,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.32800960540771</v>
+        <v>1.328009724617</v>
       </c>
       <c r="H1952" t="n">
         <v>124985920</v>
@@ -57093,7 +57093,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H1956" t="n">
         <v>39334965</v>
@@ -57151,7 +57151,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.37566125392914</v>
+        <v>1.37566113471985</v>
       </c>
       <c r="H1958" t="n">
         <v>66425360</v>
@@ -57238,7 +57238,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.41974997520447</v>
+        <v>1.41975009441376</v>
       </c>
       <c r="H1961" t="n">
         <v>31281838</v>
@@ -57325,7 +57325,7 @@
         <v>1.60950005054474</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.43355560302734</v>
+        <v>1.43355572223663</v>
       </c>
       <c r="H1964" t="n">
         <v>26138694</v>
@@ -57383,7 +57383,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.40104556083679</v>
+        <v>1.40104568004608</v>
       </c>
       <c r="H1966" t="n">
         <v>153129411</v>
@@ -57470,7 +57470,7 @@
         <v>1.46249997615814</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.30262506008148</v>
+        <v>1.30262517929077</v>
       </c>
       <c r="H1969" t="n">
         <v>26919423</v>
@@ -57499,7 +57499,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.27679526805878</v>
+        <v>1.27679538726807</v>
       </c>
       <c r="H1970" t="n">
         <v>26802260</v>
@@ -57528,7 +57528,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.29683554172516</v>
+        <v>1.29683566093445</v>
       </c>
       <c r="H1971" t="n">
         <v>25191162</v>
@@ -57731,7 +57731,7 @@
         <v>1.41849994659424</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.26343488693237</v>
+        <v>1.26343500614166</v>
       </c>
       <c r="H1978" t="n">
         <v>88712511</v>
@@ -57934,7 +57934,7 @@
         <v>1.5275000333786</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.36051952838898</v>
+        <v>1.36051964759827</v>
       </c>
       <c r="H1985" t="n">
         <v>16749025</v>
@@ -57992,7 +57992,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.37566125392914</v>
+        <v>1.37566113471985</v>
       </c>
       <c r="H1987" t="n">
         <v>51105926</v>
@@ -58021,7 +58021,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.29015552997589</v>
+        <v>1.29015564918518</v>
       </c>
       <c r="H1988" t="n">
         <v>67066172</v>
@@ -58079,7 +58079,7 @@
         <v>1.41449999809265</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.25987219810486</v>
+        <v>1.25987231731415</v>
       </c>
       <c r="H1990" t="n">
         <v>29949971</v>
@@ -58166,7 +58166,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.23626911640167</v>
+        <v>1.23626923561096</v>
       </c>
       <c r="H1993" t="n">
         <v>49894794</v>
@@ -58427,7 +58427,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H2002" t="n">
         <v>21379601</v>
@@ -58456,7 +58456,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.23805058002472</v>
+        <v>1.23805046081543</v>
       </c>
       <c r="H2003" t="n">
         <v>18744870</v>
@@ -58572,7 +58572,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H2007" t="n">
         <v>40689470</v>
@@ -58717,7 +58717,7 @@
         <v>1.44749999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>1.28926491737366</v>
+        <v>1.28926479816437</v>
       </c>
       <c r="H2012" t="n">
         <v>13752928</v>
@@ -58862,7 +58862,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H2017" t="n">
         <v>79262449</v>
@@ -58978,7 +58978,7 @@
         <v>1.46150004863739</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.30173456668854</v>
+        <v>1.30173444747925</v>
       </c>
       <c r="H2021" t="n">
         <v>32246011</v>
@@ -59007,7 +59007,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.24784815311432</v>
+        <v>1.24784803390503</v>
       </c>
       <c r="H2022" t="n">
         <v>61474648</v>
@@ -59036,7 +59036,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.24784815311432</v>
+        <v>1.24784803390503</v>
       </c>
       <c r="H2023" t="n">
         <v>34906238</v>
@@ -59123,7 +59123,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.22647154331207</v>
+        <v>1.22647166252136</v>
       </c>
       <c r="H2026" t="n">
         <v>31335128</v>
@@ -59210,7 +59210,7 @@
         <v>1.42050004005432</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.26521646976471</v>
+        <v>1.26521635055542</v>
       </c>
       <c r="H2029" t="n">
         <v>35969343</v>
@@ -59268,7 +59268,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.29015552997589</v>
+        <v>1.29015564918518</v>
       </c>
       <c r="H2031" t="n">
         <v>21961584</v>
@@ -59326,7 +59326,7 @@
         <v>1.44649994373322</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.28837418556213</v>
+        <v>1.28837406635284</v>
       </c>
       <c r="H2033" t="n">
         <v>15340362</v>
@@ -59384,7 +59384,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.32088422775269</v>
+        <v>1.3208841085434</v>
       </c>
       <c r="H2035" t="n">
         <v>16248522</v>
@@ -59413,7 +59413,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.30930519104004</v>
+        <v>1.30930531024933</v>
       </c>
       <c r="H2036" t="n">
         <v>16596498</v>
@@ -59471,7 +59471,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.32622826099396</v>
+        <v>1.32622814178467</v>
       </c>
       <c r="H2038" t="n">
         <v>31598891</v>
@@ -59558,7 +59558,7 @@
         <v>1.50650000572205</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.3418151140213</v>
+        <v>1.34181523323059</v>
       </c>
       <c r="H2041" t="n">
         <v>49175369</v>
@@ -59790,7 +59790,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.27679526805878</v>
+        <v>1.27679538726807</v>
       </c>
       <c r="H2049" t="n">
         <v>35782956</v>
@@ -59877,7 +59877,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31643080711365</v>
+        <v>1.31643068790436</v>
       </c>
       <c r="H2052" t="n">
         <v>70363678</v>
@@ -59964,7 +59964,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.34315133094788</v>
+        <v>1.34315121173859</v>
       </c>
       <c r="H2055" t="n">
         <v>21291896</v>
@@ -60399,7 +60399,7 @@
         <v>1.375</v>
       </c>
       <c r="G2070" t="n">
-        <v>1.2246903181076</v>
+        <v>1.22469019889832</v>
       </c>
       <c r="H2070" t="n">
         <v>37201230</v>
@@ -60486,7 +60486,7 @@
         <v>1.38100004196167</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.23003447055817</v>
+        <v>1.23003435134888</v>
       </c>
       <c r="H2073" t="n">
         <v>23884244</v>
@@ -60602,7 +60602,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.32979106903076</v>
+        <v>1.32979094982147</v>
       </c>
       <c r="H2077" t="n">
         <v>97981694</v>
@@ -60689,7 +60689,7 @@
         <v>1.82149994373322</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.62238049507141</v>
+        <v>1.6223806142807</v>
       </c>
       <c r="H2080" t="n">
         <v>170004032</v>
@@ -60776,7 +60776,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.723473072052</v>
+        <v>1.72347319126129</v>
       </c>
       <c r="H2083" t="n">
         <v>102058873</v>
@@ -60863,7 +60863,7 @@
         <v>1.97650003433228</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.76043653488159</v>
+        <v>1.76043665409088</v>
       </c>
       <c r="H2086" t="n">
         <v>36852781</v>
@@ -60979,7 +60979,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.87488949298859</v>
+        <v>1.87488961219788</v>
       </c>
       <c r="H2090" t="n">
         <v>47381130</v>
@@ -61008,7 +61008,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.88112425804138</v>
+        <v>1.88112413883209</v>
       </c>
       <c r="H2091" t="n">
         <v>28755854</v>
@@ -61037,7 +61037,7 @@
         <v>2.08699989318848</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.8588570356369</v>
+        <v>1.85885715484619</v>
       </c>
       <c r="H2092" t="n">
         <v>29642492</v>
@@ -61153,7 +61153,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.91318893432617</v>
+        <v>1.91318881511688</v>
       </c>
       <c r="H2096" t="n">
         <v>51280827</v>
@@ -61356,7 +61356,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.98889708518982</v>
+        <v>1.98889696598053</v>
       </c>
       <c r="H2103" t="n">
         <v>20444616</v>
@@ -61385,7 +61385,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2104" t="n">
-        <v>2.0076014995575</v>
+        <v>2.00760126113892</v>
       </c>
       <c r="H2104" t="n">
         <v>25187040</v>
@@ -61414,7 +61414,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G2105" t="n">
-        <v>2.00849223136902</v>
+        <v>2.00849199295044</v>
       </c>
       <c r="H2105" t="n">
         <v>29639951</v>
@@ -61472,7 +61472,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.06994891166687</v>
+        <v>2.06994915008545</v>
       </c>
       <c r="H2107" t="n">
         <v>41532484</v>
@@ -61530,7 +61530,7 @@
         <v>2.3970000743866</v>
       </c>
       <c r="G2109" t="n">
-        <v>2.13496899604797</v>
+        <v>2.13496923446655</v>
       </c>
       <c r="H2109" t="n">
         <v>81592175</v>
@@ -61559,7 +61559,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2110" t="n">
-        <v>2.08420014381409</v>
+        <v>2.08419990539551</v>
       </c>
       <c r="H2110" t="n">
         <v>42505018</v>
@@ -61646,7 +61646,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.99513173103333</v>
+        <v>1.99513185024261</v>
       </c>
       <c r="H2113" t="n">
         <v>34419597</v>
@@ -61675,7 +61675,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2114" t="n">
         <v>27318033</v>
@@ -61733,7 +61733,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.94258153438568</v>
+        <v>1.94258141517639</v>
       </c>
       <c r="H2116" t="n">
         <v>46811721</v>
@@ -61820,7 +61820,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.9719740152359</v>
+        <v>1.97197389602661</v>
       </c>
       <c r="H2119" t="n">
         <v>18487545</v>
@@ -61878,7 +61878,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.95237898826599</v>
+        <v>1.9523788690567</v>
       </c>
       <c r="H2121" t="n">
         <v>27702781</v>
@@ -61936,7 +61936,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.94079983234406</v>
+        <v>1.94080007076263</v>
       </c>
       <c r="H2123" t="n">
         <v>20243345</v>
@@ -62023,7 +62023,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2126" t="n">
-        <v>1.91318893432617</v>
+        <v>1.91318881511688</v>
       </c>
       <c r="H2126" t="n">
         <v>16042180</v>
@@ -62081,7 +62081,7 @@
         <v>2.13100004196167</v>
       </c>
       <c r="G2128" t="n">
-        <v>1.89804720878601</v>
+        <v>1.8980473279953</v>
       </c>
       <c r="H2128" t="n">
         <v>22011055</v>
@@ -62110,7 +62110,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2129" t="n">
         <v>19775385</v>
@@ -62168,7 +62168,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G2131" t="n">
-        <v>1.97019267082214</v>
+        <v>1.97019255161285</v>
       </c>
       <c r="H2131" t="n">
         <v>19971385</v>
@@ -62197,7 +62197,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2132" t="n">
-        <v>2.02541518211365</v>
+        <v>2.02541494369507</v>
       </c>
       <c r="H2132" t="n">
         <v>39975168</v>
@@ -62255,7 +62255,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2134" t="n">
-        <v>2.11359262466431</v>
+        <v>2.11359286308289</v>
       </c>
       <c r="H2134" t="n">
         <v>44554345</v>
@@ -62371,7 +62371,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2138" t="n">
-        <v>2.12160873413086</v>
+        <v>2.12160897254944</v>
       </c>
       <c r="H2138" t="n">
         <v>27147448</v>
@@ -62400,7 +62400,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2139" t="n">
-        <v>2.11359262466431</v>
+        <v>2.11359286308289</v>
       </c>
       <c r="H2139" t="n">
         <v>18307723</v>
@@ -62458,7 +62458,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2141" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2141" t="n">
         <v>13550932</v>
@@ -62516,7 +62516,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2143" t="n">
-        <v>1.98889708518982</v>
+        <v>1.98889696598053</v>
       </c>
       <c r="H2143" t="n">
         <v>26661132</v>
@@ -62574,7 +62574,7 @@
         <v>2.15300011634827</v>
       </c>
       <c r="G2145" t="n">
-        <v>1.9176424741745</v>
+        <v>1.91764235496521</v>
       </c>
       <c r="H2145" t="n">
         <v>22296682</v>
@@ -62603,7 +62603,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.92031419277191</v>
+        <v>1.9203143119812</v>
       </c>
       <c r="H2146" t="n">
         <v>35218310</v>
@@ -62632,7 +62632,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.9336746931076</v>
+        <v>1.93367457389832</v>
       </c>
       <c r="H2147" t="n">
         <v>17467441</v>
@@ -62661,7 +62661,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2148" t="n">
         <v>28506448</v>
@@ -62690,7 +62690,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.83926224708557</v>
+        <v>1.83926212787628</v>
       </c>
       <c r="H2149" t="n">
         <v>27905894</v>
@@ -62748,7 +62748,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2151" t="n">
         <v>33021803</v>
@@ -62835,7 +62835,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.86152923107147</v>
+        <v>1.86152911186218</v>
       </c>
       <c r="H2154" t="n">
         <v>35977989</v>
@@ -62864,7 +62864,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.86152923107147</v>
+        <v>1.86152911186218</v>
       </c>
       <c r="H2155" t="n">
         <v>22290014</v>
@@ -62893,7 +62893,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2156" t="n">
-        <v>1.89626586437225</v>
+        <v>1.89626574516296</v>
       </c>
       <c r="H2156" t="n">
         <v>21085975</v>
@@ -62922,7 +62922,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2157" t="n">
         <v>35756797</v>
@@ -62951,7 +62951,7 @@
         <v>2.15899991989136</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.92298638820648</v>
+        <v>1.92298626899719</v>
       </c>
       <c r="H2158" t="n">
         <v>16359113</v>
@@ -62980,7 +62980,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.99245977401733</v>
+        <v>1.99245965480804</v>
       </c>
       <c r="H2159" t="n">
         <v>39248301</v>
@@ -63096,7 +63096,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.13585996627808</v>
+        <v>2.1358597278595</v>
       </c>
       <c r="H2163" t="n">
         <v>33746318</v>
@@ -63212,7 +63212,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2167" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2167" t="n">
         <v>25601227</v>
@@ -63299,7 +63299,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G2170" t="n">
-        <v>2.07351207733154</v>
+        <v>2.07351183891296</v>
       </c>
       <c r="H2170" t="n">
         <v>26440425</v>
@@ -63328,7 +63328,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.06371450424194</v>
+        <v>2.06371426582336</v>
       </c>
       <c r="H2171" t="n">
         <v>26757191</v>
@@ -63357,7 +63357,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G2172" t="n">
-        <v>2.09666967391968</v>
+        <v>2.09666991233826</v>
       </c>
       <c r="H2172" t="n">
         <v>24912702</v>
@@ -63415,7 +63415,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2174" t="n">
-        <v>2.10913944244385</v>
+        <v>2.10913920402527</v>
       </c>
       <c r="H2174" t="n">
         <v>19724218</v>
@@ -63444,7 +63444,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.12339019775391</v>
+        <v>2.12339043617249</v>
       </c>
       <c r="H2175" t="n">
         <v>29130431</v>
@@ -63473,7 +63473,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.14476680755615</v>
+        <v>2.14476656913757</v>
       </c>
       <c r="H2176" t="n">
         <v>16678363</v>
@@ -63560,7 +63560,7 @@
         <v>2.41899991035461</v>
       </c>
       <c r="G2179" t="n">
-        <v>2.15456414222717</v>
+        <v>2.15456390380859</v>
       </c>
       <c r="H2179" t="n">
         <v>23246952</v>
@@ -63618,7 +63618,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2181" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2181" t="n">
         <v>45523587</v>
@@ -63647,7 +63647,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G2182" t="n">
-        <v>1.9844434261322</v>
+        <v>1.98444354534149</v>
       </c>
       <c r="H2182" t="n">
         <v>44868347</v>
@@ -63705,7 +63705,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.94614410400391</v>
+        <v>1.9461442232132</v>
       </c>
       <c r="H2184" t="n">
         <v>18067908</v>
@@ -63734,7 +63734,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2185" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2185" t="n">
         <v>20351307</v>
@@ -63763,7 +63763,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.94079983234406</v>
+        <v>1.94080007076263</v>
       </c>
       <c r="H2186" t="n">
         <v>18512647</v>
@@ -63879,7 +63879,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G2190" t="n">
-        <v>1.79294657707214</v>
+        <v>1.79294645786285</v>
       </c>
       <c r="H2190" t="n">
         <v>24047004</v>
@@ -63995,7 +63995,7 @@
         <v>1.98450005054474</v>
       </c>
       <c r="G2194" t="n">
-        <v>1.7675621509552</v>
+        <v>1.76756203174591</v>
       </c>
       <c r="H2194" t="n">
         <v>23362020</v>
@@ -64140,7 +64140,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G2199" t="n">
-        <v>1.8428248167038</v>
+        <v>1.84282493591309</v>
       </c>
       <c r="H2199" t="n">
         <v>32985049</v>
@@ -64227,7 +64227,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.84549689292908</v>
+        <v>1.84549701213837</v>
       </c>
       <c r="H2202" t="n">
         <v>16439030</v>
@@ -64256,7 +64256,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.81521368026733</v>
+        <v>1.81521379947662</v>
       </c>
       <c r="H2203" t="n">
         <v>23581831</v>
@@ -64343,7 +64343,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2206" t="n">
         <v>19255054</v>
@@ -64372,7 +64372,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2207" t="n">
-        <v>1.80185329914093</v>
+        <v>1.80185341835022</v>
       </c>
       <c r="H2207" t="n">
         <v>12789945</v>
@@ -64401,7 +64401,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.67448568344116</v>
+        <v>1.67448556423187</v>
       </c>
       <c r="H2208" t="n">
         <v>53900944</v>
@@ -64430,7 +64430,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.71189439296722</v>
+        <v>1.71189427375793</v>
       </c>
       <c r="H2209" t="n">
         <v>35189302</v>
@@ -64546,7 +64546,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G2213" t="n">
-        <v>1.60055899620056</v>
+        <v>1.60055887699127</v>
       </c>
       <c r="H2213" t="n">
         <v>37765591</v>
@@ -64575,7 +64575,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.62727928161621</v>
+        <v>1.6272794008255</v>
       </c>
       <c r="H2214" t="n">
         <v>22594695</v>
@@ -64865,7 +64865,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.81343233585358</v>
+        <v>1.81343221664429</v>
       </c>
       <c r="H2224" t="n">
         <v>24725349</v>
@@ -65097,7 +65097,7 @@
         <v>2.05699992179871</v>
       </c>
       <c r="G2232" t="n">
-        <v>1.83213651180267</v>
+        <v>1.83213663101196</v>
       </c>
       <c r="H2232" t="n">
         <v>29472348</v>
@@ -65155,7 +65155,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2234" t="n">
-        <v>1.79027450084686</v>
+        <v>1.79027438163757</v>
       </c>
       <c r="H2234" t="n">
         <v>16876658</v>
@@ -65184,7 +65184,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.80185329914093</v>
+        <v>1.80185341835022</v>
       </c>
       <c r="H2235" t="n">
         <v>20529123</v>
@@ -65358,7 +65358,7 @@
         <v>1.99150002002716</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.77379679679871</v>
+        <v>1.773796916008</v>
       </c>
       <c r="H2241" t="n">
         <v>46698722</v>
@@ -65416,7 +65416,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2243" t="n">
-        <v>1.83926224708557</v>
+        <v>1.83926212787628</v>
       </c>
       <c r="H2243" t="n">
         <v>48994310</v>
@@ -65445,7 +65445,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G2244" t="n">
-        <v>1.80630683898926</v>
+        <v>1.80630695819855</v>
       </c>
       <c r="H2244" t="n">
         <v>29352657</v>
@@ -65474,7 +65474,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G2245" t="n">
-        <v>1.89003109931946</v>
+        <v>1.89003121852875</v>
       </c>
       <c r="H2245" t="n">
         <v>81646961</v>
@@ -65503,7 +65503,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.94970667362213</v>
+        <v>1.94970679283142</v>
       </c>
       <c r="H2246" t="n">
         <v>74141845</v>
@@ -65561,7 +65561,7 @@
         <v>2.16300010681152</v>
       </c>
       <c r="G2248" t="n">
-        <v>1.92654931545258</v>
+        <v>1.92654919624329</v>
       </c>
       <c r="H2248" t="n">
         <v>30842480</v>
@@ -65590,7 +65590,7 @@
         <v>2.16700005531311</v>
       </c>
       <c r="G2249" t="n">
-        <v>1.9301118850708</v>
+        <v>1.93011200428009</v>
       </c>
       <c r="H2249" t="n">
         <v>30050128</v>
@@ -65619,7 +65619,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2250" t="n">
-        <v>1.94525349140167</v>
+        <v>1.94525361061096</v>
       </c>
       <c r="H2250" t="n">
         <v>26979522</v>
@@ -65648,7 +65648,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2251" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2251" t="n">
         <v>53288446</v>
@@ -65677,7 +65677,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2252" t="n">
         <v>41701778</v>
@@ -65735,7 +65735,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2254" t="n">
-        <v>2.00314807891846</v>
+        <v>2.00314784049988</v>
       </c>
       <c r="H2254" t="n">
         <v>44091922</v>
@@ -65793,7 +65793,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2256" t="n">
-        <v>2.06994891166687</v>
+        <v>2.06994915008545</v>
       </c>
       <c r="H2256" t="n">
         <v>54666411</v>
@@ -65880,7 +65880,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2259" t="n">
-        <v>2.0530264377594</v>
+        <v>2.05302619934082</v>
       </c>
       <c r="H2259" t="n">
         <v>24934085</v>
@@ -65909,7 +65909,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2260" t="n">
-        <v>2.06371450424194</v>
+        <v>2.06371426582336</v>
       </c>
       <c r="H2260" t="n">
         <v>40038315</v>
@@ -65938,7 +65938,7 @@
         <v>2.33299994468689</v>
       </c>
       <c r="G2261" t="n">
-        <v>2.077965259552</v>
+        <v>2.07796549797058</v>
       </c>
       <c r="H2261" t="n">
         <v>34552742</v>
@@ -65967,7 +65967,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2262" t="n">
-        <v>2.10913944244385</v>
+        <v>2.10913920402527</v>
       </c>
       <c r="H2262" t="n">
         <v>21092827</v>
@@ -66170,7 +66170,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G2269" t="n">
-        <v>2.1652524471283</v>
+        <v>2.16525220870972</v>
       </c>
       <c r="H2269" t="n">
         <v>38389055</v>
@@ -66315,7 +66315,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G2274" t="n">
-        <v>2.26768112182617</v>
+        <v>2.26768088340759</v>
       </c>
       <c r="H2274" t="n">
         <v>31890329</v>
@@ -66431,7 +66431,7 @@
         <v>2.48699998855591</v>
       </c>
       <c r="G2278" t="n">
-        <v>2.21513056755066</v>
+        <v>2.21513080596924</v>
       </c>
       <c r="H2278" t="n">
         <v>18431422</v>
@@ -66518,7 +66518,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2281" t="n">
-        <v>2.29262018203735</v>
+        <v>2.29261994361877</v>
       </c>
       <c r="H2281" t="n">
         <v>22696347</v>
@@ -66547,7 +66547,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2282" t="n">
-        <v>2.31577777862549</v>
+        <v>2.31577801704407</v>
       </c>
       <c r="H2282" t="n">
         <v>26132220</v>
@@ -66634,7 +66634,7 @@
         <v>2.64299988746643</v>
       </c>
       <c r="G2285" t="n">
-        <v>2.35407710075378</v>
+        <v>2.35407733917236</v>
       </c>
       <c r="H2285" t="n">
         <v>60652789</v>
@@ -66721,7 +66721,7 @@
         <v>2.51099991798401</v>
       </c>
       <c r="G2288" t="n">
-        <v>2.23650717735291</v>
+        <v>2.23650693893433</v>
       </c>
       <c r="H2288" t="n">
         <v>15785363</v>
@@ -66750,7 +66750,7 @@
         <v>2.5090000629425</v>
       </c>
       <c r="G2289" t="n">
-        <v>2.23472571372986</v>
+        <v>2.23472595214844</v>
       </c>
       <c r="H2289" t="n">
         <v>11480911</v>
@@ -66924,7 +66924,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G2295" t="n">
-        <v>2.45294308662415</v>
+        <v>2.45294332504272</v>
       </c>
       <c r="H2295" t="n">
         <v>20214762</v>
@@ -67040,7 +67040,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G2299" t="n">
-        <v>2.31221532821655</v>
+        <v>2.31221508979797</v>
       </c>
       <c r="H2299" t="n">
         <v>74870654</v>
@@ -67098,7 +67098,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G2301" t="n">
-        <v>2.27658796310425</v>
+        <v>2.27658772468567</v>
       </c>
       <c r="H2301" t="n">
         <v>30195449</v>
@@ -67127,7 +67127,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G2302" t="n">
-        <v>2.25164890289307</v>
+        <v>2.25164866447449</v>
       </c>
       <c r="H2302" t="n">
         <v>24626119</v>
@@ -67156,7 +67156,7 @@
         <v>2.51300001144409</v>
       </c>
       <c r="G2303" t="n">
-        <v>2.23828864097595</v>
+        <v>2.23828840255737</v>
       </c>
       <c r="H2303" t="n">
         <v>20104873</v>
@@ -67214,7 +67214,7 @@
         <v>2.48300004005432</v>
       </c>
       <c r="G2305" t="n">
-        <v>2.21156811714172</v>
+        <v>2.21156787872314</v>
       </c>
       <c r="H2305" t="n">
         <v>27751479</v>
@@ -67243,7 +67243,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G2306" t="n">
-        <v>2.14832925796509</v>
+        <v>2.14832949638367</v>
       </c>
       <c r="H2306" t="n">
         <v>43140551</v>
@@ -67272,7 +67272,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2307" t="n">
-        <v>2.12160873413086</v>
+        <v>2.12160897254944</v>
       </c>
       <c r="H2307" t="n">
         <v>24111895</v>
@@ -67504,7 +67504,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2315" t="n">
-        <v>2.04411959648132</v>
+        <v>2.04411935806274</v>
       </c>
       <c r="H2315" t="n">
         <v>24791375</v>
@@ -67562,7 +67562,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G2317" t="n">
-        <v>2.04768204689026</v>
+        <v>2.04768228530884</v>
       </c>
       <c r="H2317" t="n">
         <v>21357944</v>
@@ -67707,7 +67707,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G2322" t="n">
-        <v>2.05658888816833</v>
+        <v>2.05658912658691</v>
       </c>
       <c r="H2322" t="n">
         <v>15248097</v>
@@ -67794,7 +67794,7 @@
         <v>2.28099989891052</v>
       </c>
       <c r="G2325" t="n">
-        <v>2.03164958953857</v>
+        <v>2.03164982795715</v>
       </c>
       <c r="H2325" t="n">
         <v>20004250</v>
@@ -67823,7 +67823,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G2326" t="n">
-        <v>2.06816792488098</v>
+        <v>2.0681676864624</v>
       </c>
       <c r="H2326" t="n">
         <v>27029721</v>
@@ -67910,7 +67910,7 @@
         <v>2.20300006866455</v>
       </c>
       <c r="G2329" t="n">
-        <v>1.96217656135559</v>
+        <v>1.9621764421463</v>
       </c>
       <c r="H2329" t="n">
         <v>165427959</v>
@@ -67939,7 +67939,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2330" t="n">
-        <v>2.00314807891846</v>
+        <v>2.00314784049988</v>
       </c>
       <c r="H2330" t="n">
         <v>90357314</v>
@@ -67997,7 +67997,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2332" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2332" t="n">
         <v>49106059</v>
@@ -68055,7 +68055,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2334" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2334" t="n">
         <v>47390121</v>
@@ -68200,7 +68200,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G2339" t="n">
-        <v>1.85440373420715</v>
+        <v>1.85440385341644</v>
       </c>
       <c r="H2339" t="n">
         <v>52881442</v>
@@ -68287,7 +68287,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2342" t="n">
-        <v>1.89626586437225</v>
+        <v>1.89626574516296</v>
       </c>
       <c r="H2342" t="n">
         <v>54335801</v>
@@ -68316,7 +68316,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.93278384208679</v>
+        <v>1.93278396129608</v>
       </c>
       <c r="H2343" t="n">
         <v>54028041</v>
@@ -68345,7 +68345,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2344" t="n">
         <v>32171346</v>
@@ -68432,7 +68432,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2347" t="n">
-        <v>1.9684112071991</v>
+        <v>1.96841132640839</v>
       </c>
       <c r="H2347" t="n">
         <v>31365241</v>
@@ -68461,7 +68461,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2348" t="n">
-        <v>1.94525349140167</v>
+        <v>1.94525361061096</v>
       </c>
       <c r="H2348" t="n">
         <v>43704455</v>
@@ -68519,7 +68519,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G2350" t="n">
-        <v>1.95861351490021</v>
+        <v>1.9586136341095</v>
       </c>
       <c r="H2350" t="n">
         <v>35346168</v>
@@ -68548,7 +68548,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2351" t="n">
-        <v>1.9336746931076</v>
+        <v>1.93367457389832</v>
       </c>
       <c r="H2351" t="n">
         <v>29069827</v>
@@ -68635,7 +68635,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2354" t="n">
-        <v>1.89537525177002</v>
+        <v>1.89537537097931</v>
       </c>
       <c r="H2354" t="n">
         <v>33627039</v>
@@ -68664,7 +68664,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.72436392307281</v>
+        <v>1.72436380386353</v>
       </c>
       <c r="H2355" t="n">
         <v>85443225</v>
@@ -68838,7 +68838,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G2361" t="n">
-        <v>1.52128791809082</v>
+        <v>1.52128803730011</v>
       </c>
       <c r="H2361" t="n">
         <v>38867170</v>
@@ -68867,7 +68867,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G2362" t="n">
-        <v>1.56493151187897</v>
+        <v>1.56493139266968</v>
       </c>
       <c r="H2362" t="n">
         <v>50829326</v>
@@ -69041,7 +69041,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G2368" t="n">
-        <v>1.749302983284</v>
+        <v>1.74930310249329</v>
       </c>
       <c r="H2368" t="n">
         <v>65053471</v>
@@ -69128,7 +69128,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.82590186595917</v>
+        <v>1.82590174674988</v>
       </c>
       <c r="H2371" t="n">
         <v>29975796</v>
@@ -69186,7 +69186,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2373" t="n">
-        <v>1.8526223897934</v>
+        <v>1.85262227058411</v>
       </c>
       <c r="H2373" t="n">
         <v>37413416</v>
@@ -69215,7 +69215,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G2374" t="n">
-        <v>1.83302736282349</v>
+        <v>1.83302748203278</v>
       </c>
       <c r="H2374" t="n">
         <v>32042896</v>
@@ -69244,7 +69244,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G2375" t="n">
-        <v>1.82768321037292</v>
+        <v>1.82768332958221</v>
       </c>
       <c r="H2375" t="n">
         <v>38839501</v>
@@ -69273,7 +69273,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G2376" t="n">
-        <v>1.83837127685547</v>
+        <v>1.83837139606476</v>
       </c>
       <c r="H2376" t="n">
         <v>30420999</v>
@@ -69331,7 +69331,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G2378" t="n">
-        <v>1.93990933895111</v>
+        <v>1.9399094581604</v>
       </c>
       <c r="H2378" t="n">
         <v>64329397</v>
@@ -79951,6 +79951,64 @@
         <v>18269574</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>4.61899995803833</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>4.63000011444092</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>4.55200004577637</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>4.60099983215332</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>4.60099983215332</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>11220388</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>4.59000015258789</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>4.40399980545044</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>4.40399980545044</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>4.40399980545044</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>13759907</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -543,7 +543,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540729522705</v>
+        <v>18.9540748596191</v>
       </c>
       <c r="H6" t="n">
         <v>681723</v>
@@ -601,7 +601,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.8786602020264</v>
+        <v>19.878662109375</v>
       </c>
       <c r="H8" t="n">
         <v>1620392</v>
@@ -659,7 +659,7 @@
         <v>22.1823787689209</v>
       </c>
       <c r="G10" t="n">
-        <v>19.6685276031494</v>
+        <v>19.668529510498</v>
       </c>
       <c r="H10" t="n">
         <v>887518</v>
@@ -688,7 +688,7 @@
         <v>20.9184246063232</v>
       </c>
       <c r="G11" t="n">
-        <v>18.547815322876</v>
+        <v>18.5478134155273</v>
       </c>
       <c r="H11" t="n">
         <v>1339292</v>
@@ -775,7 +775,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460279464722</v>
+        <v>15.7460269927979</v>
       </c>
       <c r="H14" t="n">
         <v>2077512</v>
@@ -804,7 +804,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.8214406967163</v>
+        <v>14.821439743042</v>
       </c>
       <c r="H15" t="n">
         <v>2435960</v>
@@ -862,7 +862,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552736282349</v>
+        <v>13.9552726745605</v>
       </c>
       <c r="H17" t="n">
         <v>354113</v>
@@ -920,7 +920,7 @@
         <v>13.806058883667</v>
       </c>
       <c r="G19" t="n">
-        <v>12.2414674758911</v>
+        <v>12.2414665222168</v>
       </c>
       <c r="H19" t="n">
         <v>1211251</v>
@@ -949,7 +949,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087121963501</v>
+        <v>12.6087112426758</v>
       </c>
       <c r="H20" t="n">
         <v>1225889</v>
@@ -1065,7 +1065,7 @@
         <v>13.5048360824585</v>
       </c>
       <c r="G24" t="n">
-        <v>11.9743804931641</v>
+        <v>11.9743814468384</v>
       </c>
       <c r="H24" t="n">
         <v>1141642</v>
@@ -1123,7 +1123,7 @@
         <v>13.0530023574829</v>
       </c>
       <c r="G26" t="n">
-        <v>11.5737524032593</v>
+        <v>11.573751449585</v>
       </c>
       <c r="H26" t="n">
         <v>1877083</v>
@@ -1297,7 +1297,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393510818481</v>
+        <v>6.74393558502197</v>
       </c>
       <c r="H32" t="n">
         <v>7100655</v>
@@ -1413,7 +1413,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36045980453491</v>
+        <v>7.36046028137207</v>
       </c>
       <c r="H36" t="n">
         <v>4978216</v>
@@ -1471,7 +1471,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243886947632</v>
+        <v>7.91243934631348</v>
       </c>
       <c r="H38" t="n">
         <v>4762357</v>
@@ -1529,7 +1529,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H40" t="n">
         <v>5230684</v>
@@ -1587,7 +1587,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H42" t="n">
         <v>8046415</v>
@@ -1616,7 +1616,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H43" t="n">
         <v>5632607</v>
@@ -1703,7 +1703,7 @@
         <v>9.96546459197998</v>
       </c>
       <c r="G46" t="n">
-        <v>8.83611392974854</v>
+        <v>8.83611297607422</v>
       </c>
       <c r="H46" t="n">
         <v>3768604</v>
@@ -1732,7 +1732,7 @@
         <v>10.6884002685547</v>
       </c>
       <c r="G47" t="n">
-        <v>9.47712230682373</v>
+        <v>9.47712135314941</v>
       </c>
       <c r="H47" t="n">
         <v>6263628</v>
@@ -1819,7 +1819,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811340332031</v>
+        <v>7.98811292648315</v>
       </c>
       <c r="H50" t="n">
         <v>5464353</v>
@@ -1877,7 +1877,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683204650879</v>
+        <v>8.58683300018311</v>
       </c>
       <c r="H52" t="n">
         <v>4362352</v>
@@ -1906,7 +1906,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G53" t="n">
-        <v>8.29526329040527</v>
+        <v>8.29526424407959</v>
       </c>
       <c r="H53" t="n">
         <v>3258288</v>
@@ -2138,7 +2138,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.34488010406494</v>
+        <v>7.34487962722778</v>
       </c>
       <c r="H61" t="n">
         <v>3010233</v>
@@ -2225,7 +2225,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870714187622</v>
+        <v>7.65870761871338</v>
       </c>
       <c r="H64" t="n">
         <v>2688899</v>
@@ -2283,7 +2283,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973592758179</v>
+        <v>6.89973640441895</v>
       </c>
       <c r="H66" t="n">
         <v>4271134</v>
@@ -2341,7 +2341,7 @@
         <v>7.61341381072998</v>
       </c>
       <c r="G68" t="n">
-        <v>6.75061225891113</v>
+        <v>6.75061273574829</v>
       </c>
       <c r="H68" t="n">
         <v>2618453</v>
@@ -2399,7 +2399,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H70" t="n">
         <v>3239759</v>
@@ -2428,7 +2428,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G71" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H71" t="n">
         <v>3489116</v>
@@ -2457,7 +2457,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.8634729385376</v>
+        <v>7.86347341537476</v>
       </c>
       <c r="H72" t="n">
         <v>3751875</v>
@@ -2660,7 +2660,7 @@
         <v>9.25006008148193</v>
       </c>
       <c r="G79" t="n">
-        <v>8.20178318023682</v>
+        <v>8.20178413391113</v>
       </c>
       <c r="H79" t="n">
         <v>2478794</v>
@@ -2689,7 +2689,7 @@
         <v>9.39816093444824</v>
       </c>
       <c r="G80" t="n">
-        <v>8.33310031890869</v>
+        <v>8.33310127258301</v>
       </c>
       <c r="H80" t="n">
         <v>1866023</v>
@@ -2805,7 +2805,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H84" t="n">
         <v>6156371</v>
@@ -2892,7 +2892,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H87" t="n">
         <v>3783755</v>
@@ -2921,7 +2921,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G88" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H88" t="n">
         <v>2952497</v>
@@ -2950,7 +2950,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G89" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H89" t="n">
         <v>2726335</v>
@@ -3008,7 +3008,7 @@
         <v>9.20487594604492</v>
       </c>
       <c r="G91" t="n">
-        <v>8.16172027587891</v>
+        <v>8.16171932220459</v>
       </c>
       <c r="H91" t="n">
         <v>2650097</v>
@@ -3066,7 +3066,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H93" t="n">
         <v>3351378</v>
@@ -3182,7 +3182,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G97" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H97" t="n">
         <v>1772130</v>
@@ -3240,7 +3240,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701738357544</v>
       </c>
       <c r="H99" t="n">
         <v>2418605</v>
@@ -3327,7 +3327,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H102" t="n">
         <v>3679752</v>
@@ -3414,7 +3414,7 @@
         <v>9.3303861618042</v>
       </c>
       <c r="G105" t="n">
-        <v>8.27300643920898</v>
+        <v>8.27300548553467</v>
       </c>
       <c r="H105" t="n">
         <v>1253897</v>
@@ -3443,7 +3443,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G106" t="n">
-        <v>8.18842887878418</v>
+        <v>8.1884298324585</v>
       </c>
       <c r="H106" t="n">
         <v>2368543</v>
@@ -3530,7 +3530,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889585494995</v>
+        <v>7.77889537811279</v>
       </c>
       <c r="H109" t="n">
         <v>2101522</v>
@@ -3559,7 +3559,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701738357544</v>
       </c>
       <c r="H110" t="n">
         <v>2370853</v>
@@ -3617,7 +3617,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837268829346</v>
       </c>
       <c r="H112" t="n">
         <v>4508416</v>
@@ -3646,7 +3646,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G113" t="n">
-        <v>8.67363548278809</v>
+        <v>8.6736364364624</v>
       </c>
       <c r="H113" t="n">
         <v>2693817</v>
@@ -3704,7 +3704,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325325012207</v>
+        <v>7.72325372695923</v>
       </c>
       <c r="H115" t="n">
         <v>4121823</v>
@@ -3762,7 +3762,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808242797852</v>
+        <v>7.96808195114136</v>
       </c>
       <c r="H117" t="n">
         <v>3606977</v>
@@ -3994,7 +3994,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.5919361114502</v>
+        <v>7.59193563461304</v>
       </c>
       <c r="H125" t="n">
         <v>3711164</v>
@@ -4023,7 +4023,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78557395935059</v>
+        <v>7.78557348251343</v>
       </c>
       <c r="H126" t="n">
         <v>3269289</v>
@@ -4052,7 +4052,7 @@
         <v>8.86349010467529</v>
       </c>
       <c r="G127" t="n">
-        <v>7.85902261734009</v>
+        <v>7.85902214050293</v>
       </c>
       <c r="H127" t="n">
         <v>3013097</v>
@@ -4139,7 +4139,7 @@
         <v>9.60650730133057</v>
       </c>
       <c r="G130" t="n">
-        <v>8.51783657073975</v>
+        <v>8.51783561706543</v>
       </c>
       <c r="H130" t="n">
         <v>3045817</v>
@@ -4284,7 +4284,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.71147441864014</v>
+        <v>8.71147346496582</v>
       </c>
       <c r="H135" t="n">
         <v>4380711</v>
@@ -4400,7 +4400,7 @@
         <v>10.3771362304688</v>
       </c>
       <c r="G139" t="n">
-        <v>9.20113182067871</v>
+        <v>9.20113277435303</v>
       </c>
       <c r="H139" t="n">
         <v>1660292</v>
@@ -4429,7 +4429,7 @@
         <v>10.5679111480713</v>
       </c>
       <c r="G140" t="n">
-        <v>9.37028789520264</v>
+        <v>9.37028694152832</v>
       </c>
       <c r="H140" t="n">
         <v>1710004</v>
@@ -4545,7 +4545,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856525421143</v>
+        <v>9.68856430053711</v>
       </c>
       <c r="H144" t="n">
         <v>1705188</v>
@@ -4632,7 +4632,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427219390869</v>
+        <v>9.78427124023438</v>
       </c>
       <c r="H147" t="n">
         <v>3288854</v>
@@ -4661,7 +4661,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G148" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H148" t="n">
         <v>11514563</v>
@@ -4690,7 +4690,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G149" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H149" t="n">
         <v>5327998</v>
@@ -4806,7 +4806,7 @@
         <v>9.37807941436768</v>
       </c>
       <c r="G153" t="n">
-        <v>8.31529426574707</v>
+        <v>8.31529521942139</v>
       </c>
       <c r="H153" t="n">
         <v>2495200</v>
@@ -4980,7 +4980,7 @@
         <v>10.3269319534302</v>
       </c>
       <c r="G159" t="n">
-        <v>9.15661716461182</v>
+        <v>9.15661811828613</v>
       </c>
       <c r="H159" t="n">
         <v>2500199</v>
@@ -5009,7 +5009,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H160" t="n">
         <v>2723125</v>
@@ -5096,7 +5096,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H163" t="n">
         <v>1929655</v>
@@ -5183,7 +5183,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G166" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H166" t="n">
         <v>2357597</v>
@@ -5241,7 +5241,7 @@
         <v>10.442400932312</v>
       </c>
       <c r="G168" t="n">
-        <v>9.25899982452393</v>
+        <v>9.25900077819824</v>
       </c>
       <c r="H168" t="n">
         <v>1567170</v>
@@ -5386,7 +5386,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H173" t="n">
         <v>2380805</v>
@@ -5502,7 +5502,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G177" t="n">
-        <v>9.23451805114746</v>
+        <v>9.23451900482178</v>
       </c>
       <c r="H177" t="n">
         <v>2950107</v>
@@ -5531,7 +5531,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G178" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H178" t="n">
         <v>1678053</v>
@@ -5647,7 +5647,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G182" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H182" t="n">
         <v>2932072</v>
@@ -5676,7 +5676,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359874725342</v>
+        <v>7.94359827041626</v>
       </c>
       <c r="H183" t="n">
         <v>4194583</v>
@@ -5734,7 +5734,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.79225063323975</v>
+        <v>7.79224967956543</v>
       </c>
       <c r="H185" t="n">
         <v>2776938</v>
@@ -5763,7 +5763,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463376998901</v>
+        <v>7.89463329315186</v>
       </c>
       <c r="H186" t="n">
         <v>1967156</v>
@@ -5966,7 +5966,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G193" t="n">
-        <v>8.38429164886475</v>
+        <v>8.38429260253906</v>
       </c>
       <c r="H193" t="n">
         <v>3268951</v>
@@ -6053,7 +6053,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G196" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H196" t="n">
         <v>2921152</v>
@@ -6111,7 +6111,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473293304443</v>
+        <v>8.66473388671875</v>
       </c>
       <c r="H198" t="n">
         <v>3635783</v>
@@ -6169,7 +6169,7 @@
         <v>10.063362121582</v>
       </c>
       <c r="G200" t="n">
-        <v>8.92291736602783</v>
+        <v>8.92291641235352</v>
       </c>
       <c r="H200" t="n">
         <v>3921088</v>
@@ -6227,7 +6227,7 @@
         <v>10.1662797927856</v>
       </c>
       <c r="G202" t="n">
-        <v>9.0141716003418</v>
+        <v>9.01417064666748</v>
       </c>
       <c r="H202" t="n">
         <v>2012851</v>
@@ -6256,7 +6256,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H203" t="n">
         <v>2739605</v>
@@ -6285,7 +6285,7 @@
         <v>10.3696060180664</v>
       </c>
       <c r="G204" t="n">
-        <v>9.19445610046387</v>
+        <v>9.19445514678955</v>
       </c>
       <c r="H204" t="n">
         <v>2291727</v>
@@ -6372,7 +6372,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856525421143</v>
+        <v>9.68856430053711</v>
       </c>
       <c r="H207" t="n">
         <v>3565425</v>
@@ -6401,7 +6401,7 @@
         <v>10.9519701004028</v>
       </c>
       <c r="G208" t="n">
-        <v>9.71082210540771</v>
+        <v>9.71082305908203</v>
       </c>
       <c r="H208" t="n">
         <v>3749471</v>
@@ -6459,7 +6459,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G210" t="n">
-        <v>9.31464290618896</v>
+        <v>9.31464385986328</v>
       </c>
       <c r="H210" t="n">
         <v>2902413</v>
@@ -6488,7 +6488,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H211" t="n">
         <v>10102433</v>
@@ -6633,7 +6633,7 @@
         <v>9.22244834899902</v>
       </c>
       <c r="G216" t="n">
-        <v>8.17730140686035</v>
+        <v>8.17730045318604</v>
       </c>
       <c r="H216" t="n">
         <v>3009845</v>
@@ -6720,7 +6720,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G219" t="n">
-        <v>8.38429164886475</v>
+        <v>8.38429260253906</v>
       </c>
       <c r="H219" t="n">
         <v>2139887</v>
@@ -6865,7 +6865,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H224" t="n">
         <v>2930403</v>
@@ -6923,7 +6923,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072246551514</v>
+        <v>8.94072341918945</v>
       </c>
       <c r="H226" t="n">
         <v>2515113</v>
@@ -6981,7 +6981,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G228" t="n">
-        <v>8.67363548278809</v>
+        <v>8.6736364364624</v>
       </c>
       <c r="H228" t="n">
         <v>3095637</v>
@@ -7039,7 +7039,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G230" t="n">
-        <v>8.9451732635498</v>
+        <v>8.94517421722412</v>
       </c>
       <c r="H230" t="n">
         <v>2705648</v>
@@ -7155,7 +7155,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G234" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H234" t="n">
         <v>2193109</v>
@@ -7213,7 +7213,7 @@
         <v>10.6457271575928</v>
       </c>
       <c r="G236" t="n">
-        <v>9.439284324646</v>
+        <v>9.43928527832031</v>
       </c>
       <c r="H236" t="n">
         <v>6766822</v>
@@ -7242,7 +7242,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640228271484</v>
+        <v>9.72640323638916</v>
       </c>
       <c r="H237" t="n">
         <v>6656648</v>
@@ -7329,7 +7329,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.182674407959</v>
+        <v>10.1826753616333</v>
       </c>
       <c r="H240" t="n">
         <v>4126096</v>
@@ -7474,7 +7474,7 @@
         <v>11.8230066299438</v>
       </c>
       <c r="G245" t="n">
-        <v>10.4831476211548</v>
+        <v>10.4831466674805</v>
       </c>
       <c r="H245" t="n">
         <v>7748349</v>
@@ -7532,7 +7532,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788536071777</v>
+        <v>10.5788545608521</v>
       </c>
       <c r="H247" t="n">
         <v>3112020</v>
@@ -7648,7 +7648,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G251" t="n">
-        <v>10.9883871078491</v>
+        <v>10.9883861541748</v>
       </c>
       <c r="H251" t="n">
         <v>3493539</v>
@@ -7677,7 +7677,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G252" t="n">
-        <v>11.2844085693359</v>
+        <v>11.2844076156616</v>
       </c>
       <c r="H252" t="n">
         <v>3211844</v>
@@ -7735,7 +7735,7 @@
         <v>13.0906553268433</v>
       </c>
       <c r="G254" t="n">
-        <v>11.6071376800537</v>
+        <v>11.607138633728</v>
       </c>
       <c r="H254" t="n">
         <v>1718855</v>
@@ -7764,7 +7764,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295513153076</v>
+        <v>11.7295522689819</v>
       </c>
       <c r="H255" t="n">
         <v>2571001</v>
@@ -7938,7 +7938,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195261001587</v>
+        <v>12.4195251464844</v>
       </c>
       <c r="H261" t="n">
         <v>2771934</v>
@@ -7967,7 +7967,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858243942261</v>
+        <v>12.1858253479004</v>
       </c>
       <c r="H262" t="n">
         <v>2214682</v>
@@ -8112,7 +8112,7 @@
         <v>12.8647365570068</v>
       </c>
       <c r="G267" t="n">
-        <v>11.4068212509155</v>
+        <v>11.4068222045898</v>
       </c>
       <c r="H267" t="n">
         <v>2415292</v>
@@ -8199,7 +8199,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G270" t="n">
-        <v>11.2844085693359</v>
+        <v>11.2844076156616</v>
       </c>
       <c r="H270" t="n">
         <v>3414444</v>
@@ -8228,7 +8228,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619939804077</v>
+        <v>11.1619930267334</v>
       </c>
       <c r="H271" t="n">
         <v>2083536</v>
@@ -8286,7 +8286,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351257324219</v>
+        <v>11.0351266860962</v>
       </c>
       <c r="H273" t="n">
         <v>2426178</v>
@@ -8344,7 +8344,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963228225708</v>
+        <v>11.7963237762451</v>
       </c>
       <c r="H275" t="n">
         <v>5968291</v>
@@ -8489,7 +8489,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G280" t="n">
-        <v>10.5276622772217</v>
+        <v>10.5276613235474</v>
       </c>
       <c r="H280" t="n">
         <v>3406649</v>
@@ -8518,7 +8518,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G281" t="n">
-        <v>10.2383193969727</v>
+        <v>10.2383184432983</v>
       </c>
       <c r="H281" t="n">
         <v>3878344</v>
@@ -8576,7 +8576,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.251672744751</v>
+        <v>10.2516717910767</v>
       </c>
       <c r="H283" t="n">
         <v>3104757</v>
@@ -8750,7 +8750,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651838302612</v>
+        <v>10.3651847839355</v>
       </c>
       <c r="H289" t="n">
         <v>3308303</v>
@@ -9127,7 +9127,7 @@
         <v>10.6984405517578</v>
       </c>
       <c r="G302" t="n">
-        <v>9.48602485656738</v>
+        <v>9.48602390289307</v>
       </c>
       <c r="H302" t="n">
         <v>2707699</v>
@@ -9185,7 +9185,7 @@
         <v>10.4675025939941</v>
       </c>
       <c r="G304" t="n">
-        <v>9.28125858306885</v>
+        <v>9.28125762939453</v>
       </c>
       <c r="H304" t="n">
         <v>3507793</v>
@@ -9330,7 +9330,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520614624023</v>
+        <v>8.96520709991455</v>
       </c>
       <c r="H309" t="n">
         <v>3858069</v>
@@ -9359,7 +9359,7 @@
         <v>10.218994140625</v>
       </c>
       <c r="G310" t="n">
-        <v>9.06091117858887</v>
+        <v>9.06091213226318</v>
       </c>
       <c r="H310" t="n">
         <v>3308377</v>
@@ -9475,7 +9475,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539390563965</v>
+        <v>9.08539485931396</v>
       </c>
       <c r="H314" t="n">
         <v>3039918</v>
@@ -9504,7 +9504,7 @@
         <v>10.1336479187012</v>
       </c>
       <c r="G315" t="n">
-        <v>8.98523807525635</v>
+        <v>8.98523712158203</v>
       </c>
       <c r="H315" t="n">
         <v>3230495</v>
@@ -9649,7 +9649,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G320" t="n">
-        <v>9.46154117584229</v>
+        <v>9.4615421295166</v>
       </c>
       <c r="H320" t="n">
         <v>4855845</v>
@@ -9765,7 +9765,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G324" t="n">
-        <v>9.49047470092773</v>
+        <v>9.49047565460205</v>
       </c>
       <c r="H324" t="n">
         <v>4124738</v>
@@ -9881,7 +9881,7 @@
         <v>10.5227270126343</v>
       </c>
       <c r="G328" t="n">
-        <v>9.33022308349609</v>
+        <v>9.33022403717041</v>
       </c>
       <c r="H328" t="n">
         <v>2488647</v>
@@ -9939,7 +9939,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G330" t="n">
-        <v>9.12990951538086</v>
+        <v>9.12990856170654</v>
       </c>
       <c r="H330" t="n">
         <v>3092166</v>
@@ -10171,7 +10171,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.20335865020752</v>
+        <v>9.2033576965332</v>
       </c>
       <c r="H338" t="n">
         <v>3676909</v>
@@ -10287,7 +10287,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837268829346</v>
       </c>
       <c r="H342" t="n">
         <v>3153124</v>
@@ -10316,7 +10316,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H343" t="n">
         <v>4027196</v>
@@ -10403,7 +10403,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G346" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H346" t="n">
         <v>3221801</v>
@@ -10490,7 +10490,7 @@
         <v>10.003116607666</v>
       </c>
       <c r="G349" t="n">
-        <v>8.86949920654297</v>
+        <v>8.86949825286865</v>
       </c>
       <c r="H349" t="n">
         <v>2547965</v>
@@ -10606,7 +10606,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G353" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H353" t="n">
         <v>3851850</v>
@@ -10722,7 +10722,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G357" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H357" t="n">
         <v>2035124</v>
@@ -10867,7 +10867,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G362" t="n">
-        <v>8.0348539352417</v>
+        <v>8.03485488891602</v>
       </c>
       <c r="H362" t="n">
         <v>6065761</v>
@@ -10896,7 +10896,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033975601196</v>
+        <v>7.9903392791748</v>
       </c>
       <c r="H363" t="n">
         <v>4201110</v>
@@ -10983,7 +10983,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G366" t="n">
-        <v>7.66093349456787</v>
+        <v>7.66093397140503</v>
       </c>
       <c r="H366" t="n">
         <v>3865901</v>
@@ -11012,7 +11012,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215579986572</v>
+        <v>7.73215627670288</v>
       </c>
       <c r="H367" t="n">
         <v>4573774</v>
@@ -11041,7 +11041,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H368" t="n">
         <v>4145288</v>
@@ -11157,7 +11157,7 @@
         <v>8.88106060028076</v>
       </c>
       <c r="G372" t="n">
-        <v>7.8746018409729</v>
+        <v>7.87460136413574</v>
       </c>
       <c r="H372" t="n">
         <v>3226298</v>
@@ -11186,7 +11186,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H373" t="n">
         <v>5046714</v>
@@ -11302,7 +11302,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133708953857</v>
+        <v>7.21133661270142</v>
       </c>
       <c r="H377" t="n">
         <v>3761237</v>
@@ -11476,7 +11476,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H383" t="n">
         <v>2583014</v>
@@ -11534,7 +11534,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055463790894</v>
+        <v>7.42055511474609</v>
       </c>
       <c r="H385" t="n">
         <v>3239198</v>
@@ -11563,7 +11563,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.6965446472168</v>
+        <v>7.69654512405396</v>
       </c>
       <c r="H386" t="n">
         <v>4250748</v>
@@ -11592,7 +11592,7 @@
         <v>8.44428825378418</v>
       </c>
       <c r="G387" t="n">
-        <v>7.48732662200928</v>
+        <v>7.48732709884644</v>
       </c>
       <c r="H387" t="n">
         <v>4117666</v>
@@ -11737,7 +11737,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H392" t="n">
         <v>4462543</v>
@@ -11766,7 +11766,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G393" t="n">
-        <v>7.7455096244812</v>
+        <v>7.74551010131836</v>
       </c>
       <c r="H393" t="n">
         <v>2051870</v>
@@ -11824,7 +11824,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.85679721832275</v>
+        <v>7.8567967414856</v>
       </c>
       <c r="H395" t="n">
         <v>2325966</v>
@@ -11853,7 +11853,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H396" t="n">
         <v>3714587</v>
@@ -11882,7 +11882,7 @@
         <v>8.52461433410645</v>
       </c>
       <c r="G397" t="n">
-        <v>7.55854988098145</v>
+        <v>7.5585503578186</v>
       </c>
       <c r="H397" t="n">
         <v>2332643</v>
@@ -11911,7 +11911,7 @@
         <v>8.514573097229</v>
       </c>
       <c r="G398" t="n">
-        <v>7.54964637756348</v>
+        <v>7.54964685440063</v>
       </c>
       <c r="H398" t="n">
         <v>1501586</v>
@@ -11940,7 +11940,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842311859131</v>
+        <v>7.47842359542847</v>
       </c>
       <c r="H399" t="n">
         <v>1479093</v>
@@ -11969,7 +11969,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196756362915</v>
+        <v>7.61196708679199</v>
       </c>
       <c r="H400" t="n">
         <v>2662388</v>
@@ -12085,7 +12085,7 @@
         <v>8.6953067779541</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70989847183228</v>
+        <v>7.70989894866943</v>
       </c>
       <c r="H404" t="n">
         <v>2592503</v>
@@ -12143,7 +12143,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H406" t="n">
         <v>2779239</v>
@@ -12172,7 +12172,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757966995239</v>
+        <v>7.64757919311523</v>
       </c>
       <c r="H407" t="n">
         <v>1870136</v>
@@ -12201,7 +12201,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G408" t="n">
-        <v>7.58525800704956</v>
+        <v>7.5852575302124</v>
       </c>
       <c r="H408" t="n">
         <v>2173007</v>
@@ -12288,7 +12288,7 @@
         <v>8.5748176574707</v>
       </c>
       <c r="G411" t="n">
-        <v>7.60306406021118</v>
+        <v>7.60306453704834</v>
       </c>
       <c r="H411" t="n">
         <v>1663436</v>
@@ -12520,7 +12520,7 @@
         <v>8.08281993865967</v>
       </c>
       <c r="G419" t="n">
-        <v>7.16682195663452</v>
+        <v>7.16682243347168</v>
       </c>
       <c r="H419" t="n">
         <v>1874275</v>
@@ -12578,7 +12578,7 @@
         <v>7.84184217453003</v>
       </c>
       <c r="G421" t="n">
-        <v>6.95315361022949</v>
+        <v>6.95315408706665</v>
       </c>
       <c r="H421" t="n">
         <v>2449535</v>
@@ -12636,7 +12636,7 @@
         <v>7.70127105712891</v>
       </c>
       <c r="G423" t="n">
-        <v>6.82851362228394</v>
+        <v>6.82851314544678</v>
       </c>
       <c r="H423" t="n">
         <v>3972357</v>
@@ -12810,7 +12810,7 @@
         <v>7.76151514053345</v>
       </c>
       <c r="G429" t="n">
-        <v>6.88192987442017</v>
+        <v>6.88193035125732</v>
       </c>
       <c r="H429" t="n">
         <v>1920708</v>
@@ -12926,7 +12926,7 @@
         <v>7.96233081817627</v>
       </c>
       <c r="G433" t="n">
-        <v>7.05998849868774</v>
+        <v>7.05998802185059</v>
       </c>
       <c r="H433" t="n">
         <v>2066064</v>
@@ -12955,7 +12955,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591417312622</v>
+        <v>7.29591369628906</v>
       </c>
       <c r="H434" t="n">
         <v>3040311</v>
@@ -13071,7 +13071,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.4739727973938</v>
+        <v>7.47397232055664</v>
       </c>
       <c r="H438" t="n">
         <v>2774137</v>
@@ -13100,7 +13100,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G439" t="n">
-        <v>7.58525800704956</v>
+        <v>7.5852575302124</v>
       </c>
       <c r="H439" t="n">
         <v>2999352</v>
@@ -13129,7 +13129,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H440" t="n">
         <v>3440039</v>
@@ -13216,7 +13216,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H443" t="n">
         <v>2311936</v>
@@ -13245,7 +13245,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491779327393</v>
+        <v>8.07491683959961</v>
       </c>
       <c r="H444" t="n">
         <v>9651321</v>
@@ -13274,7 +13274,7 @@
         <v>9.10195827484131</v>
       </c>
       <c r="G445" t="n">
-        <v>8.07046604156494</v>
+        <v>8.07046508789062</v>
       </c>
       <c r="H445" t="n">
         <v>8925850</v>
@@ -13448,7 +13448,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692350387573</v>
+        <v>7.93692302703857</v>
       </c>
       <c r="H451" t="n">
         <v>4589432</v>
@@ -13796,7 +13796,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.42945718765259</v>
+        <v>7.42945766448975</v>
       </c>
       <c r="H463" t="n">
         <v>3847044</v>
@@ -13825,7 +13825,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H464" t="n">
         <v>4793014</v>
@@ -13883,7 +13883,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H466" t="n">
         <v>9145143</v>
@@ -13970,7 +13970,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479198455811</v>
+        <v>7.99479103088379</v>
       </c>
       <c r="H469" t="n">
         <v>8252776</v>
@@ -14057,7 +14057,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.54677104949951</v>
+        <v>8.5467700958252</v>
       </c>
       <c r="H472" t="n">
         <v>5904097</v>
@@ -14115,7 +14115,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H474" t="n">
         <v>5603952</v>
@@ -14144,7 +14144,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H475" t="n">
         <v>5013333</v>
@@ -14173,7 +14173,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H476" t="n">
         <v>3307360</v>
@@ -14289,7 +14289,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G480" t="n">
-        <v>7.78557395935059</v>
+        <v>7.78557348251343</v>
       </c>
       <c r="H480" t="n">
         <v>11572956</v>
@@ -14318,7 +14318,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757966995239</v>
+        <v>7.64757919311523</v>
       </c>
       <c r="H481" t="n">
         <v>6391732</v>
@@ -14347,7 +14347,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G482" t="n">
-        <v>7.62532234191895</v>
+        <v>7.62532186508179</v>
       </c>
       <c r="H482" t="n">
         <v>3509049</v>
@@ -14376,7 +14376,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G483" t="n">
-        <v>7.62532234191895</v>
+        <v>7.62532186508179</v>
       </c>
       <c r="H483" t="n">
         <v>4716149</v>
@@ -14405,7 +14405,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H484" t="n">
         <v>3256857</v>
@@ -14463,7 +14463,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576314926147</v>
       </c>
       <c r="H486" t="n">
         <v>2564414</v>
@@ -14579,7 +14579,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H490" t="n">
         <v>2757855</v>
@@ -14608,7 +14608,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G491" t="n">
-        <v>7.7455096244812</v>
+        <v>7.74551010131836</v>
       </c>
       <c r="H491" t="n">
         <v>3546514</v>
@@ -14695,7 +14695,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H494" t="n">
         <v>4714362</v>
@@ -14724,7 +14724,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H495" t="n">
         <v>2456311</v>
@@ -14840,7 +14840,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.6342248916626</v>
+        <v>7.63422441482544</v>
       </c>
       <c r="H499" t="n">
         <v>4090789</v>
@@ -14898,7 +14898,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H501" t="n">
         <v>2766406</v>
@@ -15072,7 +15072,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G507" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H507" t="n">
         <v>4480449</v>
@@ -15101,7 +15101,7 @@
         <v>9.34795665740967</v>
       </c>
       <c r="G508" t="n">
-        <v>8.2885856628418</v>
+        <v>8.28858661651611</v>
       </c>
       <c r="H508" t="n">
         <v>3999486</v>
@@ -15188,7 +15188,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109508514404</v>
+        <v>8.47109603881836</v>
       </c>
       <c r="H511" t="n">
         <v>3770392</v>
@@ -15217,7 +15217,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670623779297</v>
+        <v>8.50670719146729</v>
       </c>
       <c r="H512" t="n">
         <v>2875008</v>
@@ -15304,7 +15304,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H515" t="n">
         <v>3023534</v>
@@ -15362,7 +15362,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H517" t="n">
         <v>4311139</v>
@@ -15507,7 +15507,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G522" t="n">
-        <v>9.12990951538086</v>
+        <v>9.12990856170654</v>
       </c>
       <c r="H522" t="n">
         <v>5817803</v>
@@ -15536,7 +15536,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H523" t="n">
         <v>4786463</v>
@@ -15652,7 +15652,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G527" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H527" t="n">
         <v>5274403</v>
@@ -15710,7 +15710,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G529" t="n">
-        <v>9.04087924957275</v>
+        <v>9.04088020324707</v>
       </c>
       <c r="H529" t="n">
         <v>2663725</v>
@@ -15739,7 +15739,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G530" t="n">
-        <v>9.04087924957275</v>
+        <v>9.04088020324707</v>
       </c>
       <c r="H530" t="n">
         <v>2198884</v>
@@ -15855,7 +15855,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.41990375518799</v>
+        <v>8.4199047088623</v>
       </c>
       <c r="H534" t="n">
         <v>2981971</v>
@@ -15884,7 +15884,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.24852466583252</v>
+        <v>8.2485237121582</v>
       </c>
       <c r="H535" t="n">
         <v>4093310</v>
@@ -15971,7 +15971,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G538" t="n">
-        <v>8.0348539352417</v>
+        <v>8.03485488891602</v>
       </c>
       <c r="H538" t="n">
         <v>4649230</v>
@@ -16029,7 +16029,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196756362915</v>
+        <v>7.61196708679199</v>
       </c>
       <c r="H540" t="n">
         <v>7866114</v>
@@ -16058,7 +16058,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519510269165</v>
+        <v>7.54519557952881</v>
       </c>
       <c r="H541" t="n">
         <v>2933056</v>
@@ -16116,7 +16116,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49623012542725</v>
+        <v>7.49622964859009</v>
       </c>
       <c r="H543" t="n">
         <v>5612249</v>
@@ -16174,7 +16174,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G545" t="n">
-        <v>7.66093349456787</v>
+        <v>7.66093397140503</v>
       </c>
       <c r="H545" t="n">
         <v>2737321</v>
@@ -16232,7 +16232,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H547" t="n">
         <v>2390591</v>
@@ -16261,7 +16261,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083866119385</v>
+        <v>7.60083913803101</v>
       </c>
       <c r="H548" t="n">
         <v>2684043</v>
@@ -16319,7 +16319,7 @@
         <v>8.83587837219238</v>
       </c>
       <c r="G550" t="n">
-        <v>7.83453893661499</v>
+        <v>7.83453989028931</v>
       </c>
       <c r="H550" t="n">
         <v>5628339</v>
@@ -16348,7 +16348,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.76331663131714</v>
+        <v>7.76331615447998</v>
       </c>
       <c r="H551" t="n">
         <v>3521552</v>
@@ -16377,7 +16377,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H552" t="n">
         <v>3398436</v>
@@ -16406,7 +16406,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G553" t="n">
-        <v>7.50068044662476</v>
+        <v>7.50068092346191</v>
       </c>
       <c r="H553" t="n">
         <v>4181215</v>
@@ -16435,7 +16435,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.5229377746582</v>
+        <v>7.52293825149536</v>
       </c>
       <c r="H554" t="n">
         <v>2585190</v>
@@ -16522,7 +16522,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G557" t="n">
-        <v>7.50068044662476</v>
+        <v>7.50068092346191</v>
       </c>
       <c r="H557" t="n">
         <v>7379464</v>
@@ -16580,7 +16580,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663948059082</v>
+        <v>7.75663900375366</v>
       </c>
       <c r="H559" t="n">
         <v>3729295</v>
@@ -16725,7 +16725,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936330795288</v>
+        <v>7.36936378479004</v>
       </c>
       <c r="H564" t="n">
         <v>2801339</v>
@@ -16783,7 +16783,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585079193115</v>
       </c>
       <c r="H566" t="n">
         <v>4081106</v>
@@ -16841,7 +16841,7 @@
         <v>8.43173694610596</v>
       </c>
       <c r="G568" t="n">
-        <v>7.47619819641113</v>
+        <v>7.47619771957397</v>
       </c>
       <c r="H568" t="n">
         <v>3125867</v>
@@ -17160,7 +17160,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744762420654</v>
+        <v>6.85744714736938</v>
       </c>
       <c r="H579" t="n">
         <v>4059831</v>
@@ -17305,7 +17305,7 @@
         <v>8.1079216003418</v>
       </c>
       <c r="G584" t="n">
-        <v>7.18907928466797</v>
+        <v>7.18907976150513</v>
       </c>
       <c r="H584" t="n">
         <v>3472564</v>
@@ -17363,7 +17363,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G586" t="n">
-        <v>7.48064947128296</v>
+        <v>7.4806489944458</v>
       </c>
       <c r="H586" t="n">
         <v>7983682</v>
@@ -17392,7 +17392,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842311859131</v>
+        <v>7.47842359542847</v>
       </c>
       <c r="H587" t="n">
         <v>5249327</v>
@@ -17421,7 +17421,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610431671143</v>
+        <v>7.41610383987427</v>
       </c>
       <c r="H588" t="n">
         <v>4009682</v>
@@ -17450,7 +17450,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G589" t="n">
-        <v>7.48064947128296</v>
+        <v>7.4806489944458</v>
       </c>
       <c r="H589" t="n">
         <v>4006210</v>
@@ -17595,7 +17595,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443929672241</v>
+        <v>7.06443881988525</v>
       </c>
       <c r="H594" t="n">
         <v>3740621</v>
@@ -17740,7 +17740,7 @@
         <v>8.06022834777832</v>
       </c>
       <c r="G599" t="n">
-        <v>7.14679145812988</v>
+        <v>7.14679098129272</v>
       </c>
       <c r="H599" t="n">
         <v>10681822</v>
@@ -17769,7 +17769,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H600" t="n">
         <v>11169423</v>
@@ -17827,7 +17827,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G602" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H602" t="n">
         <v>3638485</v>
@@ -17856,7 +17856,7 @@
         <v>8.55222606658936</v>
       </c>
       <c r="G603" t="n">
-        <v>7.58303260803223</v>
+        <v>7.58303213119507</v>
       </c>
       <c r="H603" t="n">
         <v>3271522</v>
@@ -18001,7 +18001,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G608" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H608" t="n">
         <v>4747845</v>
@@ -18088,7 +18088,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37538909912109</v>
+        <v>8.37539005279541</v>
       </c>
       <c r="H611" t="n">
         <v>5678009</v>
@@ -18146,7 +18146,7 @@
         <v>8.79822540283203</v>
       </c>
       <c r="G613" t="n">
-        <v>7.80115413665771</v>
+        <v>7.80115365982056</v>
       </c>
       <c r="H613" t="n">
         <v>4731371</v>
@@ -18262,7 +18262,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H617" t="n">
         <v>5676159</v>
@@ -18378,7 +18378,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H621" t="n">
         <v>4359962</v>
@@ -18407,7 +18407,7 @@
         <v>9.72448635101318</v>
       </c>
       <c r="G622" t="n">
-        <v>8.62244415283203</v>
+        <v>8.62244510650635</v>
       </c>
       <c r="H622" t="n">
         <v>5253374</v>
@@ -18465,7 +18465,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902599334717</v>
+        <v>8.56902694702148</v>
       </c>
       <c r="H624" t="n">
         <v>3124054</v>
@@ -18639,7 +18639,7 @@
         <v>9.36552906036377</v>
       </c>
       <c r="G630" t="n">
-        <v>8.30416679382324</v>
+        <v>8.30416774749756</v>
       </c>
       <c r="H630" t="n">
         <v>2245651</v>
@@ -18813,7 +18813,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G636" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H636" t="n">
         <v>6312564</v>
@@ -18871,7 +18871,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H638" t="n">
         <v>2970699</v>
@@ -18929,7 +18929,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G640" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H640" t="n">
         <v>1067132</v>
@@ -18958,7 +18958,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.71147441864014</v>
+        <v>8.71147346496582</v>
       </c>
       <c r="H641" t="n">
         <v>2154097</v>
@@ -19045,7 +19045,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G644" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H644" t="n">
         <v>5210482</v>
@@ -19161,7 +19161,7 @@
         <v>10.0181789398193</v>
       </c>
       <c r="G648" t="n">
-        <v>8.88285350799561</v>
+        <v>8.88285446166992</v>
       </c>
       <c r="H648" t="n">
         <v>3244003</v>
@@ -19248,7 +19248,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G651" t="n">
-        <v>9.0564603805542</v>
+        <v>9.05646133422852</v>
       </c>
       <c r="H651" t="n">
         <v>1641266</v>
@@ -19335,7 +19335,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G654" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H654" t="n">
         <v>2782854</v>
@@ -19422,7 +19422,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H657" t="n">
         <v>3819447</v>
@@ -19567,7 +19567,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H662" t="n">
         <v>5059956</v>
@@ -19625,7 +19625,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H664" t="n">
         <v>4580403</v>
@@ -19770,7 +19770,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139925003052</v>
+        <v>10.3139934539795</v>
       </c>
       <c r="H669" t="n">
         <v>8750009</v>
@@ -19828,7 +19828,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G671" t="n">
-        <v>9.80652809143066</v>
+        <v>9.80652904510498</v>
       </c>
       <c r="H671" t="n">
         <v>2692978</v>
@@ -19973,7 +19973,7 @@
         <v>11.6046199798584</v>
       </c>
       <c r="G676" t="n">
-        <v>10.2895088195801</v>
+        <v>10.2895097732544</v>
       </c>
       <c r="H676" t="n">
         <v>1818429</v>
@@ -20205,7 +20205,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G684" t="n">
-        <v>10.3340244293213</v>
+        <v>10.334023475647</v>
       </c>
       <c r="H684" t="n">
         <v>4874391</v>
@@ -20321,7 +20321,7 @@
         <v>11.5017032623291</v>
       </c>
       <c r="G688" t="n">
-        <v>10.1982555389404</v>
+        <v>10.1982564926147</v>
       </c>
       <c r="H688" t="n">
         <v>1979022</v>
@@ -20379,7 +20379,7 @@
         <v>11.328498840332</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0446805953979</v>
+        <v>10.0446796417236</v>
       </c>
       <c r="H690" t="n">
         <v>5499203</v>
@@ -20408,7 +20408,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H691" t="n">
         <v>4155413</v>
@@ -20437,7 +20437,7 @@
         <v>12.0489253997803</v>
       </c>
       <c r="G692" t="n">
-        <v>10.6834630966187</v>
+        <v>10.683464050293</v>
       </c>
       <c r="H692" t="n">
         <v>2537540</v>
@@ -20466,7 +20466,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G693" t="n">
-        <v>10.8259086608887</v>
+        <v>10.8259077072144</v>
       </c>
       <c r="H693" t="n">
         <v>4672055</v>
@@ -20582,7 +20582,7 @@
         <v>12.4580860137939</v>
       </c>
       <c r="G697" t="n">
-        <v>11.0462560653687</v>
+        <v>11.0462551116943</v>
       </c>
       <c r="H697" t="n">
         <v>11143856</v>
@@ -20814,7 +20814,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856676101685</v>
+        <v>12.0856685638428</v>
       </c>
       <c r="H705" t="n">
         <v>4491851</v>
@@ -20930,7 +20930,7 @@
         <v>12.7618188858032</v>
       </c>
       <c r="G709" t="n">
-        <v>11.3155670166016</v>
+        <v>11.3155679702759</v>
       </c>
       <c r="H709" t="n">
         <v>4616138</v>
@@ -21046,7 +21046,7 @@
         <v>12.7015752792358</v>
       </c>
       <c r="G713" t="n">
-        <v>11.262149810791</v>
+        <v>11.2621507644653</v>
       </c>
       <c r="H713" t="n">
         <v>2952425</v>
@@ -21075,7 +21075,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349689483643</v>
+        <v>10.9349699020386</v>
       </c>
       <c r="H714" t="n">
         <v>2894320</v>
@@ -21104,7 +21104,7 @@
         <v>11.8004150390625</v>
       </c>
       <c r="G715" t="n">
-        <v>10.4631156921387</v>
+        <v>10.463116645813</v>
       </c>
       <c r="H715" t="n">
         <v>3263911</v>
@@ -21220,7 +21220,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G719" t="n">
-        <v>10.549919128418</v>
+        <v>10.5499200820923</v>
       </c>
       <c r="H719" t="n">
         <v>9162422</v>
@@ -21365,7 +21365,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H724" t="n">
         <v>4731058</v>
@@ -21394,7 +21394,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H725" t="n">
         <v>5437862</v>
@@ -21452,7 +21452,7 @@
         <v>11.7025184631348</v>
       </c>
       <c r="G727" t="n">
-        <v>10.3763132095337</v>
+        <v>10.376314163208</v>
       </c>
       <c r="H727" t="n">
         <v>2777725</v>
@@ -21481,7 +21481,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H728" t="n">
         <v>6325209</v>
@@ -21510,7 +21510,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006391525269</v>
+        <v>10.3006381988525</v>
       </c>
       <c r="H729" t="n">
         <v>3047850</v>
@@ -21684,7 +21684,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580421447754</v>
+        <v>9.34580516815186</v>
       </c>
       <c r="H735" t="n">
         <v>2646670</v>
@@ -21713,7 +21713,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G736" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H736" t="n">
         <v>2599002</v>
@@ -21742,7 +21742,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G737" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H737" t="n">
         <v>3254391</v>
@@ -21858,7 +21858,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889585494995</v>
+        <v>7.77889537811279</v>
       </c>
       <c r="H741" t="n">
         <v>8894223</v>
@@ -21945,7 +21945,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H744" t="n">
         <v>2830649</v>
@@ -21974,7 +21974,7 @@
         <v>9.65922069549561</v>
       </c>
       <c r="G745" t="n">
-        <v>8.5645751953125</v>
+        <v>8.56457614898682</v>
       </c>
       <c r="H745" t="n">
         <v>3590690</v>
@@ -22090,7 +22090,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G749" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H749" t="n">
         <v>3226454</v>
@@ -22119,7 +22119,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G750" t="n">
-        <v>8.18842887878418</v>
+        <v>8.1884298324585</v>
       </c>
       <c r="H750" t="n">
         <v>5632615</v>
@@ -22177,7 +22177,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G752" t="n">
-        <v>8.25520038604736</v>
+        <v>8.25519943237305</v>
       </c>
       <c r="H752" t="n">
         <v>4141957</v>
@@ -22206,7 +22206,7 @@
         <v>9.33540630340576</v>
       </c>
       <c r="G753" t="n">
-        <v>8.27745819091797</v>
+        <v>8.27745723724365</v>
       </c>
       <c r="H753" t="n">
         <v>2716829</v>
@@ -22235,7 +22235,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G754" t="n">
-        <v>8.29526329040527</v>
+        <v>8.29526424407959</v>
       </c>
       <c r="H754" t="n">
         <v>2607977</v>
@@ -22264,7 +22264,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466617584229</v>
+        <v>7.91466569900513</v>
       </c>
       <c r="H755" t="n">
         <v>4636928</v>
@@ -22293,7 +22293,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.81228160858154</v>
+        <v>7.81228256225586</v>
       </c>
       <c r="H756" t="n">
         <v>3199541</v>
@@ -22409,7 +22409,7 @@
         <v>8.17318725585938</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24694871902466</v>
+        <v>7.24694919586182</v>
       </c>
       <c r="H760" t="n">
         <v>5578537</v>
@@ -22583,7 +22583,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576314926147</v>
       </c>
       <c r="H766" t="n">
         <v>6705143</v>
@@ -22612,7 +22612,7 @@
         <v>9.12957000732422</v>
       </c>
       <c r="G767" t="n">
-        <v>8.09494781494141</v>
+        <v>8.09494876861572</v>
       </c>
       <c r="H767" t="n">
         <v>5185119</v>
@@ -22757,7 +22757,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G772" t="n">
-        <v>8.25520038604736</v>
+        <v>8.25519943237305</v>
       </c>
       <c r="H772" t="n">
         <v>3230113</v>
@@ -22786,7 +22786,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096832275391</v>
+        <v>8.39096927642822</v>
       </c>
       <c r="H773" t="n">
         <v>2691134</v>
@@ -22931,7 +22931,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G778" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H778" t="n">
         <v>3928570</v>
@@ -22960,7 +22960,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G779" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H779" t="n">
         <v>5108708</v>
@@ -23018,7 +23018,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G781" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H781" t="n">
         <v>3452225</v>
@@ -23076,7 +23076,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G783" t="n">
-        <v>8.9451732635498</v>
+        <v>8.94517421722412</v>
       </c>
       <c r="H783" t="n">
         <v>2493851</v>
@@ -23163,7 +23163,7 @@
         <v>10.2817487716675</v>
       </c>
       <c r="G786" t="n">
-        <v>9.11655521392822</v>
+        <v>9.11655426025391</v>
       </c>
       <c r="H786" t="n">
         <v>3216304</v>
@@ -23192,7 +23192,7 @@
         <v>10.3445043563843</v>
       </c>
       <c r="G787" t="n">
-        <v>9.17219829559326</v>
+        <v>9.17219924926758</v>
       </c>
       <c r="H787" t="n">
         <v>3191829</v>
@@ -23221,7 +23221,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G788" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H788" t="n">
         <v>2462687</v>
@@ -23337,7 +23337,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G792" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H792" t="n">
         <v>1988992</v>
@@ -23453,7 +23453,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G796" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H796" t="n">
         <v>5910919</v>
@@ -23482,7 +23482,7 @@
         <v>10.7963380813599</v>
       </c>
       <c r="G797" t="n">
-        <v>9.57282733917236</v>
+        <v>9.57282638549805</v>
       </c>
       <c r="H797" t="n">
         <v>2938128</v>
@@ -23540,7 +23540,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H799" t="n">
         <v>2749374</v>
@@ -23685,7 +23685,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746780395508</v>
+        <v>9.69746875762939</v>
       </c>
       <c r="H804" t="n">
         <v>2499039</v>
@@ -23714,7 +23714,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H805" t="n">
         <v>7839193</v>
@@ -23830,7 +23830,7 @@
         <v>11.8882722854614</v>
       </c>
       <c r="G809" t="n">
-        <v>10.5410165786743</v>
+        <v>10.541015625</v>
       </c>
       <c r="H809" t="n">
         <v>4281611</v>
@@ -23917,7 +23917,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G812" t="n">
-        <v>10.5276622772217</v>
+        <v>10.5276613235474</v>
       </c>
       <c r="H812" t="n">
         <v>2784960</v>
@@ -24033,7 +24033,7 @@
         <v>12.1091690063477</v>
       </c>
       <c r="G816" t="n">
-        <v>10.7368793487549</v>
+        <v>10.7368803024292</v>
       </c>
       <c r="H816" t="n">
         <v>3221057</v>
@@ -24062,7 +24062,7 @@
         <v>12.2145967483521</v>
       </c>
       <c r="G817" t="n">
-        <v>10.8303604125977</v>
+        <v>10.8303594589233</v>
       </c>
       <c r="H817" t="n">
         <v>2672807</v>
@@ -24091,7 +24091,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371948242188</v>
+        <v>10.9371957778931</v>
       </c>
       <c r="H818" t="n">
         <v>2377360</v>
@@ -24120,7 +24120,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G819" t="n">
-        <v>10.9883871078491</v>
+        <v>10.9883861541748</v>
       </c>
       <c r="H819" t="n">
         <v>2021022</v>
@@ -24149,7 +24149,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G820" t="n">
-        <v>10.8259086608887</v>
+        <v>10.8259077072144</v>
       </c>
       <c r="H820" t="n">
         <v>2828403</v>
@@ -24207,7 +24207,7 @@
         <v>11.5368452072144</v>
       </c>
       <c r="G822" t="n">
-        <v>10.2294158935547</v>
+        <v>10.2294149398804</v>
       </c>
       <c r="H822" t="n">
         <v>4110160</v>
@@ -24294,7 +24294,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G825" t="n">
-        <v>10.3340244293213</v>
+        <v>10.334023475647</v>
       </c>
       <c r="H825" t="n">
         <v>1775286</v>
@@ -24439,7 +24439,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H830" t="n">
         <v>3008620</v>
@@ -24671,7 +24671,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271890640259</v>
+        <v>10.2271900177002</v>
       </c>
       <c r="H838" t="n">
         <v>2776794</v>
@@ -24787,7 +24787,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G842" t="n">
-        <v>10.549919128418</v>
+        <v>10.5499200820923</v>
       </c>
       <c r="H842" t="n">
         <v>2618477</v>
@@ -24874,7 +24874,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G845" t="n">
-        <v>10.2383193969727</v>
+        <v>10.2383184432983</v>
       </c>
       <c r="H845" t="n">
         <v>2752665</v>
@@ -25193,7 +25193,7 @@
         <v>10.4072589874268</v>
       </c>
       <c r="G856" t="n">
-        <v>9.22784042358398</v>
+        <v>9.2278413772583</v>
       </c>
       <c r="H856" t="n">
         <v>2374666</v>
@@ -25425,7 +25425,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G864" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H864" t="n">
         <v>1703266</v>
@@ -25512,7 +25512,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H867" t="n">
         <v>1477729</v>
@@ -25570,7 +25570,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G869" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H869" t="n">
         <v>2768616</v>
@@ -25628,7 +25628,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G871" t="n">
-        <v>9.07204151153564</v>
+        <v>9.07204055786133</v>
       </c>
       <c r="H871" t="n">
         <v>6949172</v>
@@ -25773,7 +25773,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G876" t="n">
-        <v>9.23451805114746</v>
+        <v>9.23451900482178</v>
       </c>
       <c r="H876" t="n">
         <v>3483538</v>
@@ -25860,7 +25860,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G879" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H879" t="n">
         <v>2123211</v>
@@ -25976,7 +25976,7 @@
         <v>11.0699491500854</v>
       </c>
       <c r="G883" t="n">
-        <v>9.81543064117432</v>
+        <v>9.81543159484863</v>
       </c>
       <c r="H883" t="n">
         <v>2715923</v>
@@ -26034,7 +26034,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G885" t="n">
-        <v>9.49047470092773</v>
+        <v>9.49047565460205</v>
       </c>
       <c r="H885" t="n">
         <v>1721405</v>
@@ -26092,7 +26092,7 @@
         <v>11.0498676300049</v>
       </c>
       <c r="G887" t="n">
-        <v>9.79762554168701</v>
+        <v>9.79762649536133</v>
       </c>
       <c r="H887" t="n">
         <v>1557244</v>
@@ -26121,7 +26121,7 @@
         <v>10.9820928573608</v>
       </c>
       <c r="G888" t="n">
-        <v>9.7375316619873</v>
+        <v>9.73753070831299</v>
       </c>
       <c r="H888" t="n">
         <v>1257161</v>
@@ -26150,7 +26150,7 @@
         <v>11.2431526184082</v>
       </c>
       <c r="G889" t="n">
-        <v>9.96900653839111</v>
+        <v>9.9690055847168</v>
       </c>
       <c r="H889" t="n">
         <v>2480426</v>
@@ -26179,7 +26179,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746780395508</v>
+        <v>9.69746875762939</v>
       </c>
       <c r="H890" t="n">
         <v>1851009</v>
@@ -26353,7 +26353,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H896" t="n">
         <v>5491999</v>
@@ -26411,7 +26411,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070013046265</v>
+        <v>10.1070003509521</v>
       </c>
       <c r="H898" t="n">
         <v>2738861</v>
@@ -26614,7 +26614,7 @@
         <v>11.0423374176025</v>
       </c>
       <c r="G905" t="n">
-        <v>9.79094886779785</v>
+        <v>9.79094791412354</v>
       </c>
       <c r="H905" t="n">
         <v>2518956</v>
@@ -26672,7 +26672,7 @@
         <v>11.4941720962524</v>
       </c>
       <c r="G907" t="n">
-        <v>10.191577911377</v>
+        <v>10.1915788650513</v>
       </c>
       <c r="H907" t="n">
         <v>5764525</v>
@@ -26701,7 +26701,7 @@
         <v>11.5845394134521</v>
       </c>
       <c r="G908" t="n">
-        <v>10.2717037200928</v>
+        <v>10.2717046737671</v>
       </c>
       <c r="H908" t="n">
         <v>2267960</v>
@@ -26846,7 +26846,7 @@
         <v>10.7411136627197</v>
       </c>
       <c r="G913" t="n">
-        <v>9.52386093139648</v>
+        <v>9.5238618850708</v>
       </c>
       <c r="H913" t="n">
         <v>4157164</v>
@@ -26904,7 +26904,7 @@
         <v>10.4248304367065</v>
       </c>
       <c r="G915" t="n">
-        <v>9.24342060089111</v>
+        <v>9.24342155456543</v>
       </c>
       <c r="H915" t="n">
         <v>2417247</v>
@@ -26991,7 +26991,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G918" t="n">
-        <v>9.12545871734619</v>
+        <v>9.12545776367188</v>
       </c>
       <c r="H918" t="n">
         <v>3054696</v>
@@ -27020,7 +27020,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G919" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H919" t="n">
         <v>1782514</v>
@@ -27049,7 +27049,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G920" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H920" t="n">
         <v>3210453</v>
@@ -27194,7 +27194,7 @@
         <v>10.4474220275879</v>
       </c>
       <c r="G925" t="n">
-        <v>9.26345252990723</v>
+        <v>9.26345348358154</v>
       </c>
       <c r="H925" t="n">
         <v>2715195</v>
@@ -27223,7 +27223,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G926" t="n">
-        <v>9.31464290618896</v>
+        <v>9.31464385986328</v>
       </c>
       <c r="H926" t="n">
         <v>1774533</v>
@@ -27310,7 +27310,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H929" t="n">
         <v>2564513</v>
@@ -27455,7 +27455,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G934" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H934" t="n">
         <v>1857397</v>
@@ -27542,7 +27542,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G937" t="n">
-        <v>9.80652809143066</v>
+        <v>9.80652904510498</v>
       </c>
       <c r="H937" t="n">
         <v>2548178</v>
@@ -27629,7 +27629,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.1047735214233</v>
+        <v>10.1047744750977</v>
       </c>
       <c r="H940" t="n">
         <v>3374955</v>
@@ -27687,7 +27687,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403856277466</v>
+        <v>10.1403865814209</v>
       </c>
       <c r="H942" t="n">
         <v>2004685</v>
@@ -27861,7 +27861,7 @@
         <v>10.881685256958</v>
       </c>
       <c r="G948" t="n">
-        <v>9.64850234985352</v>
+        <v>9.64850330352783</v>
       </c>
       <c r="H948" t="n">
         <v>3341804</v>
@@ -27890,7 +27890,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392574310303</v>
+        <v>9.56392478942871</v>
       </c>
       <c r="H949" t="n">
         <v>2157126</v>
@@ -28064,7 +28064,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.9273681640625</v>
+        <v>8.92736721038818</v>
       </c>
       <c r="H955" t="n">
         <v>5044840</v>
@@ -28209,7 +28209,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00972080230713</v>
+        <v>9.00971984863281</v>
       </c>
       <c r="H960" t="n">
         <v>3059945</v>
@@ -28267,7 +28267,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G962" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H962" t="n">
         <v>3934669</v>
@@ -28325,7 +28325,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G964" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H964" t="n">
         <v>4071910</v>
@@ -28354,7 +28354,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H965" t="n">
         <v>2851396</v>
@@ -28586,7 +28586,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65963077545166</v>
+        <v>9.65962982177734</v>
       </c>
       <c r="H973" t="n">
         <v>3880597</v>
@@ -28673,7 +28673,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H976" t="n">
         <v>4961745</v>
@@ -28818,7 +28818,7 @@
         <v>11.2306022644043</v>
       </c>
       <c r="G981" t="n">
-        <v>9.95787811279297</v>
+        <v>9.95787715911865</v>
       </c>
       <c r="H981" t="n">
         <v>2713471</v>
@@ -29282,7 +29282,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G997" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H997" t="n">
         <v>4136816</v>
@@ -29311,7 +29311,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G998" t="n">
-        <v>9.07204151153564</v>
+        <v>9.07204055786133</v>
       </c>
       <c r="H998" t="n">
         <v>3580666</v>
@@ -29340,7 +29340,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G999" t="n">
-        <v>9.0564603805542</v>
+        <v>9.05646133422852</v>
       </c>
       <c r="H999" t="n">
         <v>3079093</v>
@@ -29514,7 +29514,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H1005" t="n">
         <v>2212645</v>
@@ -29804,7 +29804,7 @@
         <v>10.934398651123</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.6952428817749</v>
+        <v>9.69524192810059</v>
       </c>
       <c r="H1015" t="n">
         <v>2311969</v>
@@ -30007,7 +30007,7 @@
         <v>11.1678466796875</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.90223407745361</v>
+        <v>9.90223503112793</v>
       </c>
       <c r="H1022" t="n">
         <v>2894790</v>
@@ -30065,7 +30065,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H1024" t="n">
         <v>1781897</v>
@@ -30210,7 +30210,7 @@
         <v>11.1126232147217</v>
       </c>
       <c r="G1029" t="n">
-        <v>9.85326957702637</v>
+        <v>9.85326862335205</v>
       </c>
       <c r="H1029" t="n">
         <v>1959789</v>
@@ -30239,7 +30239,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G1030" t="n">
-        <v>9.46154117584229</v>
+        <v>9.4615421295166</v>
       </c>
       <c r="H1030" t="n">
         <v>7606013</v>
@@ -30297,7 +30297,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G1032" t="n">
-        <v>9.12545871734619</v>
+        <v>9.12545776367188</v>
       </c>
       <c r="H1032" t="n">
         <v>2852190</v>
@@ -30355,7 +30355,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H1034" t="n">
         <v>4214085</v>
@@ -30529,7 +30529,7 @@
         <v>9.75962924957275</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.65360546112061</v>
+        <v>8.65360450744629</v>
       </c>
       <c r="H1040" t="n">
         <v>7621307</v>
@@ -30558,7 +30558,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H1041" t="n">
         <v>4707102</v>
@@ -30674,7 +30674,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H1045" t="n">
         <v>5766485</v>
@@ -30761,7 +30761,7 @@
         <v>9.55630302429199</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.47332096099854</v>
+        <v>8.47332191467285</v>
       </c>
       <c r="H1048" t="n">
         <v>2650515</v>
@@ -30906,7 +30906,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657609939575</v>
+        <v>7.71657657623291</v>
       </c>
       <c r="H1053" t="n">
         <v>7295256</v>
@@ -31022,7 +31022,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083866119385</v>
+        <v>7.60083913803101</v>
       </c>
       <c r="H1057" t="n">
         <v>6276118</v>
@@ -31051,7 +31051,7 @@
         <v>8.3037166595459</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.36268615722656</v>
+        <v>7.36268663406372</v>
       </c>
       <c r="H1058" t="n">
         <v>5909074</v>
@@ -31080,7 +31080,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585079193115</v>
       </c>
       <c r="H1059" t="n">
         <v>5991896</v>
@@ -31196,7 +31196,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.9500036239624</v>
+        <v>4.95000410079956</v>
       </c>
       <c r="H1063" t="n">
         <v>15725169</v>
@@ -31225,7 +31225,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.9500036239624</v>
+        <v>4.95000410079956</v>
       </c>
       <c r="H1064" t="n">
         <v>14702152</v>
@@ -31370,7 +31370,7 @@
         <v>5.16346597671509</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.57830858230591</v>
+        <v>4.57830905914307</v>
       </c>
       <c r="H1069" t="n">
         <v>8246612</v>
@@ -31515,7 +31515,7 @@
         <v>5.85627889633179</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.19260740280151</v>
+        <v>5.19260787963867</v>
       </c>
       <c r="H1074" t="n">
         <v>6147761</v>
@@ -31573,7 +31573,7 @@
         <v>5.89393186569214</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.22599315643311</v>
+        <v>5.22599363327026</v>
       </c>
       <c r="H1076" t="n">
         <v>4232448</v>
@@ -31747,7 +31747,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386211395264</v>
+        <v>5.28386259078979</v>
       </c>
       <c r="H1082" t="n">
         <v>6987858</v>
@@ -31834,7 +31834,7 @@
         <v>5.9014630317688</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.23267078399658</v>
+        <v>5.23267126083374</v>
       </c>
       <c r="H1085" t="n">
         <v>3564831</v>
@@ -32037,7 +32037,7 @@
         <v>5.28395509719849</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.68514347076416</v>
+        <v>4.685142993927</v>
       </c>
       <c r="H1092" t="n">
         <v>4658214</v>
@@ -32066,7 +32066,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445489883423</v>
+        <v>4.95445537567139</v>
       </c>
       <c r="H1093" t="n">
         <v>3686235</v>
@@ -32182,7 +32182,7 @@
         <v>5.55505609512329</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.92552089691162</v>
+        <v>4.92552137374878</v>
       </c>
       <c r="H1097" t="n">
         <v>3776492</v>
@@ -32298,7 +32298,7 @@
         <v>5.79101419448853</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.13473892211914</v>
+        <v>5.1347393989563</v>
       </c>
       <c r="H1101" t="n">
         <v>3599923</v>
@@ -32356,7 +32356,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470746994019</v>
+        <v>5.11470699310303</v>
       </c>
       <c r="H1103" t="n">
         <v>2616491</v>
@@ -32385,7 +32385,7 @@
         <v>5.80858516693115</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15031909942627</v>
+        <v>5.15031862258911</v>
       </c>
       <c r="H1104" t="n">
         <v>2378841</v>
@@ -32530,7 +32530,7 @@
         <v>5.57513809204102</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.9433274269104</v>
+        <v>4.94332695007324</v>
       </c>
       <c r="H1109" t="n">
         <v>2046001</v>
@@ -32646,7 +32646,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.79800081253052</v>
+        <v>4.79800033569336</v>
       </c>
       <c r="H1113" t="n">
         <v>3350805</v>
@@ -32733,7 +32733,7 @@
         <v>5.46217918395996</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.865074634552</v>
+        <v>4.86507511138916</v>
       </c>
       <c r="H1116" t="n">
         <v>3829378</v>
@@ -32762,7 +32762,7 @@
         <v>5.30905723571777</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.72869110107422</v>
+        <v>4.72869157791138</v>
       </c>
       <c r="H1117" t="n">
         <v>7700374</v>
@@ -32907,7 +32907,7 @@
         <v>5.79854488372803</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.16466999053955</v>
+        <v>5.16467046737671</v>
       </c>
       <c r="H1122" t="n">
         <v>12491580</v>
@@ -32965,7 +32965,7 @@
         <v>6.46876621246338</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.76162576675415</v>
+        <v>5.76162528991699</v>
       </c>
       <c r="H1124" t="n">
         <v>11268120</v>
@@ -32994,7 +32994,7 @@
         <v>6.59176588058472</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.87117910385132</v>
+        <v>5.87117958068848</v>
       </c>
       <c r="H1125" t="n">
         <v>10577677</v>
@@ -33023,7 +33023,7 @@
         <v>6.41354179382324</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.71243762969971</v>
+        <v>5.71243810653687</v>
       </c>
       <c r="H1126" t="n">
         <v>6490655</v>
@@ -33139,7 +33139,7 @@
         <v>5.99182987213135</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33682584762573</v>
+        <v>5.33682632446289</v>
       </c>
       <c r="H1130" t="n">
         <v>5065402</v>
@@ -33197,7 +33197,7 @@
         <v>5.98680877685547</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.3323540687561</v>
+        <v>5.33235359191895</v>
       </c>
       <c r="H1132" t="n">
         <v>5119610</v>
@@ -33342,7 +33342,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.0841817855835</v>
+        <v>5.08418226242065</v>
       </c>
       <c r="H1137" t="n">
         <v>3931365</v>
@@ -33429,7 +33429,7 @@
         <v>5.61530113220215</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.00145816802979</v>
+        <v>5.00145769119263</v>
       </c>
       <c r="H1140" t="n">
         <v>4272132</v>
@@ -33487,7 +33487,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.97686338424683</v>
+        <v>4.97686290740967</v>
       </c>
       <c r="H1142" t="n">
         <v>3387639</v>
@@ -33574,7 +33574,7 @@
         <v>5.68558597564697</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.06405973434448</v>
+        <v>5.06405925750732</v>
       </c>
       <c r="H1145" t="n">
         <v>3689754</v>
@@ -33661,7 +33661,7 @@
         <v>5.27642488479614</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.69962596893311</v>
+        <v>4.69962644577026</v>
       </c>
       <c r="H1148" t="n">
         <v>5584746</v>
@@ -33748,7 +33748,7 @@
         <v>5.28897619247437</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.71080541610718</v>
+        <v>4.71080589294434</v>
       </c>
       <c r="H1151" t="n">
         <v>6369097</v>
@@ -33777,7 +33777,7 @@
         <v>5.36679220199585</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.78011465072632</v>
+        <v>4.78011512756348</v>
       </c>
       <c r="H1152" t="n">
         <v>6019418</v>
@@ -33806,7 +33806,7 @@
         <v>5.47724008560181</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.87848949432373</v>
+        <v>4.87848901748657</v>
       </c>
       <c r="H1153" t="n">
         <v>3853871</v>
@@ -34067,7 +34067,7 @@
         <v>4.92123222351074</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.38326215744019</v>
+        <v>4.38326168060303</v>
       </c>
       <c r="H1162" t="n">
         <v>24661467</v>
@@ -34154,7 +34154,7 @@
         <v>4.57357120513916</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.07360553741455</v>
+        <v>4.07360601425171</v>
       </c>
       <c r="H1165" t="n">
         <v>7438646</v>
@@ -34299,7 +34299,7 @@
         <v>4.96892595291138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.42574214935303</v>
+        <v>4.42574167251587</v>
       </c>
       <c r="H1170" t="n">
         <v>3451603</v>
@@ -34415,7 +34415,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1174" t="n">
-        <v>4.34189987182617</v>
+        <v>4.34190034866333</v>
       </c>
       <c r="H1174" t="n">
         <v>4695442</v>
@@ -34589,7 +34589,7 @@
         <v>4.66895818710327</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.15856552124023</v>
+        <v>4.15856599807739</v>
       </c>
       <c r="H1180" t="n">
         <v>6557504</v>
@@ -34734,7 +34734,7 @@
         <v>4.50579500198364</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.01323843002319</v>
+        <v>4.01323890686035</v>
       </c>
       <c r="H1185" t="n">
         <v>4155094</v>
@@ -34821,7 +34821,7 @@
         <v>4.39032697677612</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.91039347648621</v>
+        <v>3.91039323806763</v>
       </c>
       <c r="H1188" t="n">
         <v>4258438</v>
@@ -34850,7 +34850,7 @@
         <v>4.29242897033691</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.82319736480713</v>
+        <v>3.82319688796997</v>
       </c>
       <c r="H1189" t="n">
         <v>7837081</v>
@@ -34937,7 +34937,7 @@
         <v>4.19327592849731</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.73488283157349</v>
+        <v>3.73488306999207</v>
       </c>
       <c r="H1192" t="n">
         <v>4846298</v>
@@ -34995,7 +34995,7 @@
         <v>4.07906293869019</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.63315534591675</v>
+        <v>3.63315558433533</v>
       </c>
       <c r="H1194" t="n">
         <v>8280016</v>
@@ -35111,7 +35111,7 @@
         <v>4.22465419769287</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.76283097267151</v>
+        <v>3.76283121109009</v>
       </c>
       <c r="H1198" t="n">
         <v>5589044</v>
@@ -35401,7 +35401,7 @@
         <v>3.56321811676025</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.17370080947876</v>
+        <v>3.17370057106018</v>
       </c>
       <c r="H1208" t="n">
         <v>6464136</v>
@@ -35459,7 +35459,7 @@
         <v>3.86444091796875</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.4419949054718</v>
+        <v>3.44199514389038</v>
       </c>
       <c r="H1210" t="n">
         <v>7063864</v>
@@ -35604,7 +35604,7 @@
         <v>3.79415607452393</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.3793933391571</v>
+        <v>3.37939357757568</v>
       </c>
       <c r="H1215" t="n">
         <v>3909509</v>
@@ -35633,7 +35633,7 @@
         <v>3.65609502792358</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.25642466545105</v>
+        <v>3.25642490386963</v>
       </c>
       <c r="H1216" t="n">
         <v>4082735</v>
@@ -35807,7 +35807,7 @@
         <v>3.59585094451904</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.20276641845703</v>
+        <v>3.20276618003845</v>
       </c>
       <c r="H1222" t="n">
         <v>5346240</v>
@@ -35836,7 +35836,7 @@
         <v>3.62597298622131</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.22959566116333</v>
+        <v>3.22959542274475</v>
       </c>
       <c r="H1223" t="n">
         <v>3204692</v>
@@ -35865,7 +35865,7 @@
         <v>3.68496203422546</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.28213620185852</v>
+        <v>3.28213596343994</v>
       </c>
       <c r="H1224" t="n">
         <v>4139377</v>
@@ -36010,7 +36010,7 @@
         <v>3.78411507606506</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.37045001983643</v>
+        <v>3.370450258255</v>
       </c>
       <c r="H1229" t="n">
         <v>8618018</v>
@@ -36184,7 +36184,7 @@
         <v>4.6940598487854</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.18092346191406</v>
+        <v>4.1809229850769</v>
       </c>
       <c r="H1235" t="n">
         <v>15804964</v>
@@ -36387,7 +36387,7 @@
         <v>4.89487504959106</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.35978651046753</v>
+        <v>4.35978603363037</v>
       </c>
       <c r="H1242" t="n">
         <v>6079967</v>
@@ -36445,7 +36445,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.27706241607666</v>
+        <v>4.2770619392395</v>
       </c>
       <c r="H1244" t="n">
         <v>4685519</v>
@@ -36474,7 +36474,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.47157573699951</v>
+        <v>4.47157526016235</v>
       </c>
       <c r="H1245" t="n">
         <v>7739906</v>
@@ -36532,7 +36532,7 @@
         <v>5.42201614379883</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.8293023109436</v>
+        <v>4.82930183410645</v>
       </c>
       <c r="H1247" t="n">
         <v>8336834</v>
@@ -36561,7 +36561,7 @@
         <v>5.30654716491699</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.72645568847656</v>
+        <v>4.72645616531372</v>
       </c>
       <c r="H1248" t="n">
         <v>6460441</v>
@@ -36619,7 +36619,7 @@
         <v>5.1333441734314</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.5721869468689</v>
+        <v>4.57218647003174</v>
       </c>
       <c r="H1250" t="n">
         <v>5110006</v>
@@ -36706,7 +36706,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.62584495544434</v>
+        <v>4.62584447860718</v>
       </c>
       <c r="H1253" t="n">
         <v>2827257</v>
@@ -36735,7 +36735,7 @@
         <v>5.35675096511841</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.77117109298706</v>
+        <v>4.77117156982422</v>
       </c>
       <c r="H1254" t="n">
         <v>5955094</v>
@@ -36793,7 +36793,7 @@
         <v>5.37683200836182</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.78905773162842</v>
+        <v>4.78905725479126</v>
       </c>
       <c r="H1256" t="n">
         <v>1840506</v>
@@ -36880,7 +36880,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1259" t="n">
         <v>4061775</v>
@@ -36938,7 +36938,7 @@
         <v>5.46719884872437</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.86954593658447</v>
+        <v>4.86954545974731</v>
       </c>
       <c r="H1261" t="n">
         <v>2064399</v>
@@ -36967,7 +36967,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1262" t="n">
         <v>5407097</v>
@@ -36996,7 +36996,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.86060285568237</v>
+        <v>4.86060237884521</v>
       </c>
       <c r="H1263" t="n">
         <v>3511782</v>
@@ -37112,7 +37112,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1267" t="n">
         <v>3396789</v>
@@ -37257,7 +37257,7 @@
         <v>5.82364702224731</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.18702840805054</v>
+        <v>5.18702793121338</v>
       </c>
       <c r="H1272" t="n">
         <v>7105248</v>
@@ -37315,7 +37315,7 @@
         <v>6.17256307601929</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.49780178070068</v>
+        <v>5.49780225753784</v>
       </c>
       <c r="H1274" t="n">
         <v>7287173</v>
@@ -37344,7 +37344,7 @@
         <v>6.10729789733887</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.43967151641846</v>
+        <v>5.4396710395813</v>
       </c>
       <c r="H1275" t="n">
         <v>6169237</v>
@@ -37431,7 +37431,7 @@
         <v>6.08721685409546</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.42178583145142</v>
+        <v>5.42178535461426</v>
       </c>
       <c r="H1278" t="n">
         <v>4068724</v>
@@ -37460,7 +37460,7 @@
         <v>6.00689077377319</v>
       </c>
       <c r="G1279" t="n">
-        <v>5.35024070739746</v>
+        <v>5.3502402305603</v>
       </c>
       <c r="H1279" t="n">
         <v>3024433</v>
@@ -37547,7 +37547,7 @@
         <v>5.85878896713257</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.21832895278931</v>
+        <v>5.21832847595215</v>
       </c>
       <c r="H1282" t="n">
         <v>3059439</v>
@@ -37692,7 +37692,7 @@
         <v>5.34169006347656</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.75775718688965</v>
+        <v>4.75775671005249</v>
       </c>
       <c r="H1287" t="n">
         <v>4046294</v>
@@ -37721,7 +37721,7 @@
         <v>5.59019899368286</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.9790997505188</v>
+        <v>4.97910022735596</v>
       </c>
       <c r="H1288" t="n">
         <v>7589590</v>
@@ -37924,7 +37924,7 @@
         <v>5.98178911209106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.32788276672363</v>
+        <v>5.32788324356079</v>
       </c>
       <c r="H1295" t="n">
         <v>5483636</v>
@@ -38098,7 +38098,7 @@
         <v>6.55160188674927</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.83540630340576</v>
+        <v>5.8354058265686</v>
       </c>
       <c r="H1301" t="n">
         <v>9385518</v>
@@ -38156,7 +38156,7 @@
         <v>6.3457670211792</v>
       </c>
       <c r="G1303" t="n">
-        <v>5.65207195281982</v>
+        <v>5.65207242965698</v>
       </c>
       <c r="H1303" t="n">
         <v>6157528</v>
@@ -38185,7 +38185,7 @@
         <v>6.35078716278076</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.65654373168945</v>
+        <v>5.65654325485229</v>
       </c>
       <c r="H1304" t="n">
         <v>5745479</v>
@@ -38214,7 +38214,7 @@
         <v>6.40852212905884</v>
       </c>
       <c r="G1305" t="n">
-        <v>5.70796728134155</v>
+        <v>5.70796680450439</v>
       </c>
       <c r="H1305" t="n">
         <v>3560044</v>
@@ -38243,7 +38243,7 @@
         <v>6.63192892074585</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.90695142745972</v>
+        <v>5.90695190429688</v>
       </c>
       <c r="H1306" t="n">
         <v>7874391</v>
@@ -38330,7 +38330,7 @@
         <v>6.00940084457397</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.35247659683228</v>
+        <v>5.35247611999512</v>
       </c>
       <c r="H1309" t="n">
         <v>24228663</v>
@@ -38388,7 +38388,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.0841817855835</v>
+        <v>5.08418226242065</v>
       </c>
       <c r="H1311" t="n">
         <v>8961866</v>
@@ -38417,7 +38417,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1312" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1312" t="n">
         <v>9655227</v>
@@ -38504,7 +38504,7 @@
         <v>5.91652393341064</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.26975250244141</v>
+        <v>5.26975202560425</v>
       </c>
       <c r="H1315" t="n">
         <v>12797834</v>
@@ -38533,7 +38533,7 @@
         <v>6.07215595245361</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.40837097167969</v>
+        <v>5.40837144851685</v>
       </c>
       <c r="H1316" t="n">
         <v>9400118</v>
@@ -38591,7 +38591,7 @@
         <v>6.07717609405518</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.41284275054932</v>
+        <v>5.41284227371216</v>
       </c>
       <c r="H1318" t="n">
         <v>4627496</v>
@@ -38649,7 +38649,7 @@
         <v>6.12486982345581</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.45532274246216</v>
+        <v>5.455322265625</v>
       </c>
       <c r="H1320" t="n">
         <v>2675208</v>
@@ -38707,7 +38707,7 @@
         <v>5.97174787521362</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.31893920898438</v>
+        <v>5.31893968582153</v>
       </c>
       <c r="H1322" t="n">
         <v>5171781</v>
@@ -38765,7 +38765,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.31670379638672</v>
+        <v>5.31670331954956</v>
       </c>
       <c r="H1324" t="n">
         <v>4027905</v>
@@ -38852,7 +38852,7 @@
         <v>5.69060611724854</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.06853055953979</v>
+        <v>5.06853103637695</v>
       </c>
       <c r="H1327" t="n">
         <v>7314312</v>
@@ -39055,7 +39055,7 @@
         <v>5.87887096405029</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.23621559143066</v>
+        <v>5.23621511459351</v>
       </c>
       <c r="H1334" t="n">
         <v>3164034</v>
@@ -39287,7 +39287,7 @@
         <v>5.83870792388916</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.20044231414795</v>
+        <v>5.20044279098511</v>
       </c>
       <c r="H1342" t="n">
         <v>4486409</v>
@@ -39374,7 +39374,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.97686338424683</v>
+        <v>4.97686290740967</v>
       </c>
       <c r="H1345" t="n">
         <v>5024234</v>
@@ -39490,7 +39490,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.94556283950806</v>
+        <v>4.94556331634521</v>
       </c>
       <c r="H1349" t="n">
         <v>4621291</v>
@@ -39577,7 +39577,7 @@
         <v>4.87855911254883</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.34525346755981</v>
+        <v>4.34525394439697</v>
       </c>
       <c r="H1352" t="n">
         <v>14868855</v>
@@ -39606,7 +39606,7 @@
         <v>4.82333517074585</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.29606676101685</v>
+        <v>4.29606628417969</v>
       </c>
       <c r="H1353" t="n">
         <v>10990037</v>
@@ -39751,7 +39751,7 @@
         <v>5.06054782867432</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.50734806060791</v>
+        <v>4.50734853744507</v>
       </c>
       <c r="H1358" t="n">
         <v>3316325</v>
@@ -39954,7 +39954,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.69068288803101</v>
+        <v>4.69068336486816</v>
       </c>
       <c r="H1365" t="n">
         <v>9046399</v>
@@ -40012,7 +40012,7 @@
         <v>5.1383638381958</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.57665729522705</v>
+        <v>4.57665777206421</v>
       </c>
       <c r="H1367" t="n">
         <v>2528599</v>
@@ -40070,7 +40070,7 @@
         <v>5.12832307815552</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.56771421432495</v>
+        <v>4.56771469116211</v>
       </c>
       <c r="H1369" t="n">
         <v>2605182</v>
@@ -40186,7 +40186,7 @@
         <v>5.11828184127808</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.55877065658569</v>
+        <v>4.55877113342285</v>
       </c>
       <c r="H1373" t="n">
         <v>4133342</v>
@@ -40244,7 +40244,7 @@
         <v>5.3793420791626</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.79129266738892</v>
+        <v>4.79129314422607</v>
       </c>
       <c r="H1375" t="n">
         <v>10178926</v>
@@ -40273,7 +40273,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1376" t="n">
         <v>5287449</v>
@@ -40389,7 +40389,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1380" t="n">
         <v>6843942</v>
@@ -40476,7 +40476,7 @@
         <v>5.56760692596436</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.95897769927979</v>
+        <v>4.95897722244263</v>
       </c>
       <c r="H1383" t="n">
         <v>4282870</v>
@@ -40679,7 +40679,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.72422027587891</v>
+        <v>4.72421979904175</v>
       </c>
       <c r="H1390" t="n">
         <v>3701384</v>
@@ -40737,7 +40737,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.72422027587891</v>
+        <v>4.72421979904175</v>
       </c>
       <c r="H1392" t="n">
         <v>2649454</v>
@@ -40766,7 +40766,7 @@
         <v>5.29901599884033</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.71974754333496</v>
+        <v>4.71974802017212</v>
       </c>
       <c r="H1393" t="n">
         <v>2108129</v>
@@ -40853,7 +40853,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1396" t="n">
-        <v>4.56324338912964</v>
+        <v>4.56324291229248</v>
       </c>
       <c r="H1396" t="n">
         <v>3303148</v>
@@ -40882,7 +40882,7 @@
         <v>5.22873115539551</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.65714597702026</v>
+        <v>4.65714645385742</v>
       </c>
       <c r="H1397" t="n">
         <v>3565887</v>
@@ -40911,7 +40911,7 @@
         <v>5.21868991851807</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.64820241928101</v>
+        <v>4.64820289611816</v>
       </c>
       <c r="H1398" t="n">
         <v>2418474</v>
@@ -41027,7 +41027,7 @@
         <v>4.90617084503174</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.3698468208313</v>
+        <v>4.36984729766846</v>
       </c>
       <c r="H1402" t="n">
         <v>5231002</v>
@@ -41056,7 +41056,7 @@
         <v>4.97143602371216</v>
       </c>
       <c r="G1403" t="n">
-        <v>4.42797756195068</v>
+        <v>4.42797803878784</v>
       </c>
       <c r="H1403" t="n">
         <v>3203342</v>
@@ -41114,7 +41114,7 @@
         <v>4.88483476638794</v>
       </c>
       <c r="G1405" t="n">
-        <v>4.35084295272827</v>
+        <v>4.35084342956543</v>
       </c>
       <c r="H1405" t="n">
         <v>3408367</v>
@@ -41172,7 +41172,7 @@
         <v>4.90240621566772</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.36649417877197</v>
+        <v>4.36649370193481</v>
       </c>
       <c r="H1407" t="n">
         <v>3512290</v>
@@ -41288,7 +41288,7 @@
         <v>4.75681495666504</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.23681783676147</v>
+        <v>4.23681831359863</v>
       </c>
       <c r="H1411" t="n">
         <v>4771701</v>
@@ -41462,7 +41462,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1417" t="n">
-        <v>4.5297064781189</v>
+        <v>4.52970600128174</v>
       </c>
       <c r="H1417" t="n">
         <v>3747890</v>
@@ -41549,7 +41549,7 @@
         <v>4.91119194030762</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.37431955337524</v>
+        <v>4.37431907653809</v>
       </c>
       <c r="H1420" t="n">
         <v>4386657</v>
@@ -41636,7 +41636,7 @@
         <v>4.92499780654907</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.38661575317383</v>
+        <v>4.38661623001099</v>
       </c>
       <c r="H1423" t="n">
         <v>3890806</v>
@@ -41694,7 +41694,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.56324338912964</v>
+        <v>4.56324291229248</v>
       </c>
       <c r="H1425" t="n">
         <v>5305491</v>
@@ -41723,7 +41723,7 @@
         <v>5.16597604751587</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.60125160217285</v>
+        <v>4.60125112533569</v>
       </c>
       <c r="H1426" t="n">
         <v>3581797</v>
@@ -41868,7 +41868,7 @@
         <v>4.98147678375244</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.43692064285278</v>
+        <v>4.43692111968994</v>
       </c>
       <c r="H1431" t="n">
         <v>1848823</v>
@@ -41926,7 +41926,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.27706241607666</v>
+        <v>4.2770619392395</v>
       </c>
       <c r="H1433" t="n">
         <v>3356625</v>
@@ -42013,7 +42013,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.47157573699951</v>
+        <v>4.47157526016235</v>
       </c>
       <c r="H1436" t="n">
         <v>3876966</v>
@@ -42216,7 +42216,7 @@
         <v>4.96139478683472</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41903400421143</v>
+        <v>4.41903448104858</v>
       </c>
       <c r="H1443" t="n">
         <v>3045903</v>
@@ -42332,7 +42332,7 @@
         <v>5.01662015914917</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.46822214126587</v>
+        <v>4.46822261810303</v>
       </c>
       <c r="H1447" t="n">
         <v>5734258</v>
@@ -42390,7 +42390,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.62584495544434</v>
+        <v>4.62584447860718</v>
       </c>
       <c r="H1449" t="n">
         <v>7048976</v>
@@ -42419,7 +42419,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.5297064781189</v>
+        <v>4.52970600128174</v>
       </c>
       <c r="H1450" t="n">
         <v>6506615</v>
@@ -42506,7 +42506,7 @@
         <v>4.99151802062988</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.4458646774292</v>
+        <v>4.44586420059204</v>
       </c>
       <c r="H1453" t="n">
         <v>2739262</v>
@@ -42535,7 +42535,7 @@
         <v>4.91244697570801</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.37543725967407</v>
+        <v>4.37543678283691</v>
       </c>
       <c r="H1454" t="n">
         <v>3529674</v>
@@ -42564,7 +42564,7 @@
         <v>5.07058906555176</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.51629161834717</v>
+        <v>4.51629209518433</v>
       </c>
       <c r="H1455" t="n">
         <v>5222595</v>
@@ -42825,7 +42825,7 @@
         <v>5.55003595352173</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.9433274269104</v>
+        <v>4.94332695007324</v>
       </c>
       <c r="H1464" t="n">
         <v>6413047</v>
@@ -42883,7 +42883,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.69068288803101</v>
+        <v>4.69068336486816</v>
       </c>
       <c r="H1466" t="n">
         <v>7328705</v>
@@ -42941,7 +42941,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.79800081253052</v>
+        <v>4.79800033569336</v>
       </c>
       <c r="H1468" t="n">
         <v>8090619</v>
@@ -42999,7 +42999,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1470" t="n">
         <v>6942701</v>
@@ -43144,7 +43144,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.91202640533447</v>
+        <v>4.91202592849731</v>
       </c>
       <c r="H1475" t="n">
         <v>2995584</v>
@@ -43202,7 +43202,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1477" t="n">
         <v>4075860</v>
@@ -43289,7 +43289,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.94556283950806</v>
+        <v>4.94556331634521</v>
       </c>
       <c r="H1480" t="n">
         <v>5065969</v>
@@ -43347,7 +43347,7 @@
         <v>4.87353897094727</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.3407826423645</v>
+        <v>4.34078216552734</v>
       </c>
       <c r="H1482" t="n">
         <v>28990116</v>
@@ -43492,7 +43492,7 @@
         <v>4.81203889846802</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.28600549697876</v>
+        <v>4.2860050201416</v>
       </c>
       <c r="H1487" t="n">
         <v>5381782</v>
@@ -43521,7 +43521,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.34189987182617</v>
+        <v>4.34190034866333</v>
       </c>
       <c r="H1488" t="n">
         <v>5511409</v>
@@ -43666,7 +43666,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.39220523834229</v>
+        <v>4.39220476150513</v>
       </c>
       <c r="H1493" t="n">
         <v>2167743</v>
@@ -43956,7 +43956,7 @@
         <v>4.46563196182251</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.97746610641479</v>
+        <v>3.97746634483337</v>
       </c>
       <c r="H1503" t="n">
         <v>7272410</v>
@@ -43985,7 +43985,7 @@
         <v>4.50328493118286</v>
       </c>
       <c r="G1504" t="n">
-        <v>4.0110034942627</v>
+        <v>4.01100301742554</v>
       </c>
       <c r="H1504" t="n">
         <v>4367193</v>
@@ -44014,7 +44014,7 @@
         <v>4.42170381546021</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.93834018707275</v>
+        <v>3.93833994865417</v>
       </c>
       <c r="H1505" t="n">
         <v>3362331</v>
@@ -44130,7 +44130,7 @@
         <v>4.59365177154541</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.09149169921875</v>
+        <v>4.09149122238159</v>
       </c>
       <c r="H1509" t="n">
         <v>4350486</v>
@@ -44188,7 +44188,7 @@
         <v>4.56729507446289</v>
       </c>
       <c r="G1511" t="n">
-        <v>4.06801605224609</v>
+        <v>4.06801557540894</v>
       </c>
       <c r="H1511" t="n">
         <v>4359136</v>
@@ -44275,7 +44275,7 @@
         <v>4.41040802001953</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.92827916145325</v>
+        <v>3.92827892303467</v>
       </c>
       <c r="H1514" t="n">
         <v>3179388</v>
@@ -44304,7 +44304,7 @@
         <v>4.4455509185791</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.95958018302917</v>
+        <v>3.95958042144775</v>
       </c>
       <c r="H1515" t="n">
         <v>2325197</v>
@@ -44333,7 +44333,7 @@
         <v>4.37275505065918</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.89474248886108</v>
+        <v>3.89474201202393</v>
       </c>
       <c r="H1516" t="n">
         <v>3004717</v>
@@ -44507,7 +44507,7 @@
         <v>4.55097913742065</v>
       </c>
       <c r="G1522" t="n">
-        <v>4.05348348617554</v>
+        <v>4.0534839630127</v>
       </c>
       <c r="H1522" t="n">
         <v>1502529</v>
@@ -44652,7 +44652,7 @@
         <v>4.78317213058472</v>
       </c>
       <c r="G1527" t="n">
-        <v>4.26029443740845</v>
+        <v>4.26029396057129</v>
       </c>
       <c r="H1527" t="n">
         <v>2970018</v>
@@ -44768,7 +44768,7 @@
         <v>4.91495704650879</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.37767267227173</v>
+        <v>4.37767314910889</v>
       </c>
       <c r="H1531" t="n">
         <v>2759069</v>
@@ -44913,7 +44913,7 @@
         <v>5.03042602539062</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.48051929473877</v>
+        <v>4.48051881790161</v>
       </c>
       <c r="H1536" t="n">
         <v>2349535</v>
@@ -44971,7 +44971,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.39220523834229</v>
+        <v>4.39220476150513</v>
       </c>
       <c r="H1538" t="n">
         <v>3995107</v>
@@ -45058,7 +45058,7 @@
         <v>5.01410913467407</v>
       </c>
       <c r="G1541" t="n">
-        <v>4.46598625183105</v>
+        <v>4.4659857749939</v>
       </c>
       <c r="H1541" t="n">
         <v>2334898</v>
@@ -45348,7 +45348,7 @@
         <v>2.99591493606567</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.66841292381287</v>
+        <v>2.66841316223145</v>
       </c>
       <c r="H1551" t="n">
         <v>17072505</v>
@@ -45377,7 +45377,7 @@
         <v>3.02854704856873</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.69747805595398</v>
+        <v>2.6974778175354</v>
       </c>
       <c r="H1552" t="n">
         <v>16828629</v>
@@ -45522,7 +45522,7 @@
         <v>2.8616189956665</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.54879784584045</v>
+        <v>2.54879760742188</v>
       </c>
       <c r="H1557" t="n">
         <v>12600027</v>
@@ -45551,7 +45551,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.56221222877502</v>
+        <v>2.5622124671936</v>
       </c>
       <c r="H1558" t="n">
         <v>9318354</v>
@@ -45725,7 +45725,7 @@
         <v>2.51521301269531</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.24025964736938</v>
+        <v>2.24025940895081</v>
       </c>
       <c r="H1564" t="n">
         <v>6732142</v>
@@ -45754,7 +45754,7 @@
         <v>2.56165099143982</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.28162121772766</v>
+        <v>2.28162097930908</v>
       </c>
       <c r="H1565" t="n">
         <v>16777908</v>
@@ -45899,7 +45899,7 @@
         <v>2.56792688369751</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.28721117973328</v>
+        <v>2.2872109413147</v>
       </c>
       <c r="H1570" t="n">
         <v>5399583</v>
@@ -45928,7 +45928,7 @@
         <v>2.37715196609497</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.11729097366333</v>
+        <v>2.11729073524475</v>
       </c>
       <c r="H1571" t="n">
         <v>6070659</v>
@@ -46015,7 +46015,7 @@
         <v>2.58047795295715</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.29838991165161</v>
+        <v>2.29839015007019</v>
       </c>
       <c r="H1574" t="n">
         <v>9240163</v>
@@ -46131,7 +46131,7 @@
         <v>2.46450710296631</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.19509673118591</v>
+        <v>2.19509649276733</v>
       </c>
       <c r="H1578" t="n">
         <v>4819541</v>
@@ -46247,7 +46247,7 @@
         <v>2.67335510253906</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.38111400604248</v>
+        <v>2.38111424446106</v>
       </c>
       <c r="H1582" t="n">
         <v>3911764</v>
@@ -46392,7 +46392,7 @@
         <v>2.86287403106689</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.54991555213928</v>
+        <v>2.54991579055786</v>
       </c>
       <c r="H1587" t="n">
         <v>13747439</v>
@@ -46479,7 +46479,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.56221222877502</v>
+        <v>2.5622124671936</v>
       </c>
       <c r="H1590" t="n">
         <v>10760896</v>
@@ -46508,7 +46508,7 @@
         <v>2.93943500518799</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.61810731887817</v>
+        <v>2.61810708045959</v>
       </c>
       <c r="H1591" t="n">
         <v>7063060</v>
@@ -46537,7 +46537,7 @@
         <v>2.87919092178345</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.564448595047</v>
+        <v>2.56444883346558</v>
       </c>
       <c r="H1592" t="n">
         <v>10358249</v>
@@ -46566,7 +46566,7 @@
         <v>2.84404802322388</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.53314781188965</v>
+        <v>2.53314757347107</v>
       </c>
       <c r="H1593" t="n">
         <v>5883247</v>
@@ -46595,7 +46595,7 @@
         <v>2.77878308296204</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.47501730918884</v>
+        <v>2.47501707077026</v>
       </c>
       <c r="H1594" t="n">
         <v>7471517</v>
@@ -46653,7 +46653,7 @@
         <v>2.80262994766235</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.49625730514526</v>
+        <v>2.49625706672668</v>
       </c>
       <c r="H1596" t="n">
         <v>3079893</v>
@@ -46711,7 +46711,7 @@
         <v>2.79384398460388</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.48843169212341</v>
+        <v>2.48843145370483</v>
       </c>
       <c r="H1598" t="n">
         <v>2912676</v>
@@ -46740,7 +46740,7 @@
         <v>2.75744605064392</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.45601272583008</v>
+        <v>2.4560124874115</v>
       </c>
       <c r="H1599" t="n">
         <v>3637078</v>
@@ -46769,7 +46769,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.43700885772705</v>
+        <v>2.43700909614563</v>
       </c>
       <c r="H1600" t="n">
         <v>2248107</v>
@@ -46798,7 +46798,7 @@
         <v>2.84028291702271</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.52979397773743</v>
+        <v>2.52979421615601</v>
       </c>
       <c r="H1601" t="n">
         <v>4359715</v>
@@ -46885,7 +46885,7 @@
         <v>2.92437410354614</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.6046929359436</v>
+        <v>2.60469269752502</v>
       </c>
       <c r="H1604" t="n">
         <v>10127429</v>
@@ -46914,7 +46914,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.43700885772705</v>
+        <v>2.43700909614563</v>
       </c>
       <c r="H1605" t="n">
         <v>8650581</v>
@@ -47233,7 +47233,7 @@
         <v>2.48509001731873</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.21342945098877</v>
+        <v>2.21342968940735</v>
       </c>
       <c r="H1616" t="n">
         <v>11509858</v>
@@ -47262,7 +47262,7 @@
         <v>2.53780388832092</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.26038098335266</v>
+        <v>2.26038074493408</v>
       </c>
       <c r="H1617" t="n">
         <v>13634558</v>
@@ -47320,7 +47320,7 @@
         <v>2.68841600418091</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.39452886581421</v>
+        <v>2.39452862739563</v>
       </c>
       <c r="H1619" t="n">
         <v>6670481</v>
@@ -47349,7 +47349,7 @@
         <v>2.90680289268494</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.58904242515564</v>
+        <v>2.58904218673706</v>
       </c>
       <c r="H1620" t="n">
         <v>11371682</v>
@@ -47581,7 +47581,7 @@
         <v>2.97517991065979</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.6499445438385</v>
+        <v>2.64994478225708</v>
       </c>
       <c r="H1628" t="n">
         <v>9786163</v>
@@ -47755,7 +47755,7 @@
         <v>2.72426104545593</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.42645525932312</v>
+        <v>2.4264554977417</v>
       </c>
       <c r="H1634" t="n">
         <v>3222869</v>
@@ -47900,7 +47900,7 @@
         <v>2.37423992156982</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.11469721794128</v>
+        <v>2.11469697952271</v>
       </c>
       <c r="H1639" t="n">
         <v>5658326</v>
@@ -47987,7 +47987,7 @@
         <v>1.96649694442749</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.75152707099915</v>
+        <v>1.75152695178986</v>
       </c>
       <c r="H1642" t="n">
         <v>12639154</v>
@@ -48016,7 +48016,7 @@
         <v>2.01657509803772</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.79613077640533</v>
+        <v>1.79613089561462</v>
       </c>
       <c r="H1643" t="n">
         <v>25382152</v>
@@ -48103,7 +48103,7 @@
         <v>2.21557092666626</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.97337329387665</v>
+        <v>1.97337317466736</v>
       </c>
       <c r="H1646" t="n">
         <v>8434013</v>
@@ -48132,7 +48132,7 @@
         <v>1.73798203468323</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.54799246788025</v>
+        <v>1.54799258708954</v>
       </c>
       <c r="H1647" t="n">
         <v>26496542</v>
@@ -48161,7 +48161,7 @@
         <v>1.59776198863983</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.42310070991516</v>
+        <v>1.42310082912445</v>
       </c>
       <c r="H1648" t="n">
         <v>48720201</v>
@@ -48190,7 +48190,7 @@
         <v>1.24932205677032</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.11275100708008</v>
+        <v>1.11275088787079</v>
       </c>
       <c r="H1649" t="n">
         <v>56877192</v>
@@ -48451,7 +48451,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98913478851318</v>
+        <v>2.98913502693176</v>
       </c>
       <c r="H1658" t="n">
         <v>6899464</v>
@@ -48538,7 +48538,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.73594284057617</v>
+        <v>1.73594272136688</v>
       </c>
       <c r="H1661" t="n">
         <v>7745580</v>
@@ -48567,7 +48567,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.985986948013306</v>
+        <v>0.98598700761795</v>
       </c>
       <c r="H1662" t="n">
         <v>25986719</v>
@@ -48596,7 +48596,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.04209995269775</v>
+        <v>1.04210007190704</v>
       </c>
       <c r="H1663" t="n">
         <v>15517197</v>
@@ -48625,7 +48625,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.730360686779022</v>
+        <v>0.730360746383667</v>
       </c>
       <c r="H1664" t="n">
         <v>50412931</v>
@@ -48770,7 +48770,7 @@
         <v>0.71340000629425</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.635413825511932</v>
+        <v>0.635413885116577</v>
       </c>
       <c r="H1669" t="n">
         <v>28781555</v>
@@ -48828,7 +48828,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.659106075763702</v>
+        <v>0.659106016159058</v>
       </c>
       <c r="H1671" t="n">
         <v>27445946</v>
@@ -48857,7 +48857,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.692061364650726</v>
+        <v>0.692061305046082</v>
       </c>
       <c r="H1672" t="n">
         <v>35674340</v>
@@ -48944,7 +48944,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.751737177371979</v>
+        <v>0.751737117767334</v>
       </c>
       <c r="H1675" t="n">
         <v>37326895</v>
@@ -49002,7 +49002,7 @@
         <v>0.833599984645844</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.74247407913208</v>
+        <v>0.742474019527435</v>
       </c>
       <c r="H1677" t="n">
         <v>19689110</v>
@@ -49205,7 +49205,7 @@
         <v>0.821799993515015</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.731963992118835</v>
+        <v>0.731963932514191</v>
       </c>
       <c r="H1684" t="n">
         <v>16957436</v>
@@ -49292,7 +49292,7 @@
         <v>0.762199997901917</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.678879261016846</v>
+        <v>0.678879201412201</v>
       </c>
       <c r="H1687" t="n">
         <v>13487789</v>
@@ -49524,7 +49524,7 @@
         <v>0.716400027275085</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.638085901737213</v>
+        <v>0.638085961341858</v>
       </c>
       <c r="H1695" t="n">
         <v>20717644</v>
@@ -49756,7 +49756,7 @@
         <v>0.674600005149841</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.60085529088974</v>
+        <v>0.600855350494385</v>
       </c>
       <c r="H1703" t="n">
         <v>12648147</v>
@@ -49785,7 +49785,7 @@
         <v>0.697399973869324</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.621162891387939</v>
+        <v>0.621162831783295</v>
       </c>
       <c r="H1704" t="n">
         <v>26443104</v>
@@ -49843,7 +49843,7 @@
         <v>0.683200001716614</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.608515202999115</v>
+        <v>0.60851514339447</v>
       </c>
       <c r="H1706" t="n">
         <v>9988795</v>
@@ -49872,7 +49872,7 @@
         <v>0.662199974060059</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589810848236084</v>
+        <v>0.589810788631439</v>
       </c>
       <c r="H1707" t="n">
         <v>13712596</v>
@@ -49901,7 +49901,7 @@
         <v>0.64300000667572</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.572709739208221</v>
+        <v>0.572709679603577</v>
       </c>
       <c r="H1708" t="n">
         <v>58766149</v>
@@ -49930,7 +49930,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.540645062923431</v>
+        <v>0.540645122528076</v>
       </c>
       <c r="H1709" t="n">
         <v>28764901</v>
@@ -49959,7 +49959,7 @@
         <v>0.584800004959106</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.520871937274933</v>
+        <v>0.520871877670288</v>
       </c>
       <c r="H1710" t="n">
         <v>20980769</v>
@@ -49988,7 +49988,7 @@
         <v>0.59280002117157</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.527997374534607</v>
+        <v>0.527997434139252</v>
       </c>
       <c r="H1711" t="n">
         <v>21540866</v>
@@ -50075,7 +50075,7 @@
         <v>0.597199976444244</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.531916320323944</v>
+        <v>0.531916379928589</v>
       </c>
       <c r="H1714" t="n">
         <v>19250857</v>
@@ -50191,7 +50191,7 @@
         <v>0.637600004673004</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.567900002002716</v>
+        <v>0.567900061607361</v>
       </c>
       <c r="H1718" t="n">
         <v>20242520</v>
@@ -50336,7 +50336,7 @@
         <v>0.72759997844696</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.648061513900757</v>
+        <v>0.648061573505402</v>
       </c>
       <c r="H1723" t="n">
         <v>11884557</v>
@@ -50365,7 +50365,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.620806694030762</v>
+        <v>0.620806634426117</v>
       </c>
       <c r="H1724" t="n">
         <v>15320781</v>
@@ -50626,7 +50626,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.658215343952179</v>
+        <v>0.658215403556824</v>
       </c>
       <c r="H1733" t="n">
         <v>21488740</v>
@@ -50655,7 +50655,7 @@
         <v>0.758199989795685</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.675316452980042</v>
+        <v>0.675316512584686</v>
       </c>
       <c r="H1734" t="n">
         <v>33917790</v>
@@ -50713,7 +50713,7 @@
         <v>0.828599989414215</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.738020598888397</v>
+        <v>0.738020658493042</v>
       </c>
       <c r="H1736" t="n">
         <v>35628898</v>
@@ -50742,7 +50742,7 @@
         <v>0.958599984645844</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.853809535503387</v>
+        <v>0.853809475898743</v>
       </c>
       <c r="H1737" t="n">
         <v>99646498</v>
@@ -50800,7 +50800,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.8764328956604</v>
+        <v>0.876432955265045</v>
       </c>
       <c r="H1739" t="n">
         <v>39414006</v>
@@ -50829,7 +50829,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.87376081943512</v>
+        <v>0.873760879039764</v>
       </c>
       <c r="H1740" t="n">
         <v>36774205</v>
@@ -51003,7 +51003,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.882667660713196</v>
+        <v>0.882667720317841</v>
       </c>
       <c r="H1746" t="n">
         <v>44222060</v>
@@ -51061,7 +51061,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.919185698032379</v>
+        <v>0.919185638427734</v>
       </c>
       <c r="H1748" t="n">
         <v>60743048</v>
@@ -51090,7 +51090,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.957485198974609</v>
+        <v>0.957485139369965</v>
       </c>
       <c r="H1749" t="n">
         <v>38369686</v>
@@ -51148,7 +51148,7 @@
         <v>1.09650003910065</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.976634860038757</v>
+        <v>0.976634919643402</v>
       </c>
       <c r="H1751" t="n">
         <v>33789817</v>
@@ -51177,7 +51177,7 @@
         <v>1.03250002861023</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.919631063938141</v>
+        <v>0.919631123542786</v>
       </c>
       <c r="H1752" t="n">
         <v>95803812</v>
@@ -51206,7 +51206,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.921857714653015</v>
+        <v>0.92185777425766</v>
       </c>
       <c r="H1753" t="n">
         <v>44395351</v>
@@ -51322,7 +51322,7 @@
         <v>1.04649996757507</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.932100653648376</v>
+        <v>0.932100594043732</v>
       </c>
       <c r="H1757" t="n">
         <v>32064633</v>
@@ -51351,7 +51351,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.926311135292053</v>
+        <v>0.926311194896698</v>
       </c>
       <c r="H1758" t="n">
         <v>21110965</v>
@@ -51409,7 +51409,7 @@
         <v>1.04750001430511</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.93299126625061</v>
+        <v>0.932991325855255</v>
       </c>
       <c r="H1760" t="n">
         <v>40631058</v>
@@ -51438,7 +51438,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.912950873374939</v>
+        <v>0.912950932979584</v>
       </c>
       <c r="H1761" t="n">
         <v>26582079</v>
@@ -51467,7 +51467,7 @@
         <v>1.01950001716614</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.908052146434784</v>
+        <v>0.908052206039429</v>
       </c>
       <c r="H1762" t="n">
         <v>27481158</v>
@@ -51525,7 +51525,7 @@
         <v>1.04449999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.93031919002533</v>
+        <v>0.930319249629974</v>
       </c>
       <c r="H1764" t="n">
         <v>52512389</v>
@@ -51786,7 +51786,7 @@
         <v>1.00650000572205</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.896473228931427</v>
+        <v>0.896473288536072</v>
       </c>
       <c r="H1773" t="n">
         <v>22532469</v>
@@ -51844,7 +51844,7 @@
         <v>1.04949998855591</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.934772729873657</v>
+        <v>0.934772670269012</v>
       </c>
       <c r="H1775" t="n">
         <v>27222601</v>
@@ -51931,7 +51931,7 @@
         <v>1.10950005054474</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.988213777542114</v>
+        <v>0.988213717937469</v>
       </c>
       <c r="H1778" t="n">
         <v>33156068</v>
@@ -51989,7 +51989,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.977970957756042</v>
+        <v>0.977970898151398</v>
       </c>
       <c r="H1780" t="n">
         <v>82522322</v>
@@ -52047,7 +52047,7 @@
         <v>1.12750005722046</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.00424599647522</v>
+        <v>1.00424611568451</v>
       </c>
       <c r="H1782" t="n">
         <v>38953976</v>
@@ -52076,7 +52076,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.05456960201263</v>
+        <v>1.05456972122192</v>
       </c>
       <c r="H1783" t="n">
         <v>44539150</v>
@@ -52424,7 +52424,7 @@
         <v>1.31149995326996</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.16813182830811</v>
+        <v>1.16813170909882</v>
       </c>
       <c r="H1795" t="n">
         <v>88039189</v>
@@ -52685,7 +52685,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.25141072273254</v>
+        <v>1.25141084194183</v>
       </c>
       <c r="H1804" t="n">
         <v>50505371</v>
@@ -52772,7 +52772,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.2309250831604</v>
+        <v>1.23092496395111</v>
       </c>
       <c r="H1807" t="n">
         <v>27498297</v>
@@ -52801,7 +52801,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.21845555305481</v>
+        <v>1.21845543384552</v>
       </c>
       <c r="H1808" t="n">
         <v>27228579</v>
@@ -52946,7 +52946,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H1813" t="n">
         <v>201277103</v>
@@ -53062,7 +53062,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.25586414337158</v>
+        <v>1.25586426258087</v>
       </c>
       <c r="H1817" t="n">
         <v>26785082</v>
@@ -53149,7 +53149,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.24962949752808</v>
+        <v>1.24962937831879</v>
       </c>
       <c r="H1820" t="n">
         <v>28478257</v>
@@ -53236,7 +53236,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.3146493434906</v>
+        <v>1.31464922428131</v>
       </c>
       <c r="H1823" t="n">
         <v>73649010</v>
@@ -53265,7 +53265,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.35116744041443</v>
+        <v>1.35116732120514</v>
       </c>
       <c r="H1824" t="n">
         <v>173226691</v>
@@ -53294,7 +53294,7 @@
         <v>1.53450000286102</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.36675429344177</v>
+        <v>1.36675441265106</v>
       </c>
       <c r="H1825" t="n">
         <v>147696002</v>
@@ -53381,7 +53381,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.31643068790436</v>
+        <v>1.31643080711365</v>
       </c>
       <c r="H1828" t="n">
         <v>36445476</v>
@@ -53497,7 +53497,7 @@
         <v>1.35749995708466</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.20910334587097</v>
+        <v>1.20910322666168</v>
       </c>
       <c r="H1832" t="n">
         <v>30266079</v>
@@ -53555,7 +53555,7 @@
         <v>1.26549994945526</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.12716031074524</v>
+        <v>1.12716042995453</v>
       </c>
       <c r="H1834" t="n">
         <v>56083977</v>
@@ -53584,7 +53584,7 @@
         <v>1.14049994945526</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.01582491397858</v>
+        <v>1.01582479476929</v>
       </c>
       <c r="H1835" t="n">
         <v>70991471</v>
@@ -53671,7 +53671,7 @@
         <v>1.23450005054474</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.09954929351807</v>
+        <v>1.09954917430878</v>
       </c>
       <c r="H1838" t="n">
         <v>44048652</v>
@@ -53729,7 +53729,7 @@
         <v>1.32550001144409</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.18060147762299</v>
+        <v>1.1806013584137</v>
       </c>
       <c r="H1840" t="n">
         <v>26361553</v>
@@ -53758,7 +53758,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.14007532596588</v>
+        <v>1.14007520675659</v>
       </c>
       <c r="H1841" t="n">
         <v>30477091</v>
@@ -53932,7 +53932,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23181581497192</v>
+        <v>1.23181569576263</v>
       </c>
       <c r="H1847" t="n">
         <v>23160786</v>
@@ -53990,7 +53990,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1849" t="n">
         <v>61303523</v>
@@ -54512,7 +54512,7 @@
         <v>1.25049996376038</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.11380004882812</v>
+        <v>1.11380016803741</v>
       </c>
       <c r="H1867" t="n">
         <v>30080800</v>
@@ -54628,7 +54628,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.15076351165771</v>
+        <v>1.150763630867</v>
       </c>
       <c r="H1871" t="n">
         <v>24313190</v>
@@ -54715,7 +54715,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.13473129272461</v>
+        <v>1.13473117351532</v>
       </c>
       <c r="H1874" t="n">
         <v>17632468</v>
@@ -54802,7 +54802,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.12048017978668</v>
+        <v>1.12048029899597</v>
       </c>
       <c r="H1877" t="n">
         <v>12144067</v>
@@ -54831,7 +54831,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.15788900852203</v>
+        <v>1.15788888931274</v>
       </c>
       <c r="H1878" t="n">
         <v>28606803</v>
@@ -54976,7 +54976,7 @@
         <v>1.25750005245209</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.1200350522995</v>
+        <v>1.12003493309021</v>
       </c>
       <c r="H1883" t="n">
         <v>22657079</v>
@@ -55005,7 +55005,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.12226164340973</v>
+        <v>1.12226152420044</v>
       </c>
       <c r="H1884" t="n">
         <v>17046265</v>
@@ -55121,7 +55121,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.07416474819183</v>
+        <v>1.07416462898254</v>
       </c>
       <c r="H1888" t="n">
         <v>25051867</v>
@@ -55150,7 +55150,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.13473129272461</v>
+        <v>1.13473117351532</v>
       </c>
       <c r="H1889" t="n">
         <v>28793517</v>
@@ -55440,7 +55440,7 @@
         <v>1.25450003147125</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.11736297607422</v>
+        <v>1.11736285686493</v>
       </c>
       <c r="H1899" t="n">
         <v>19379185</v>
@@ -55498,7 +55498,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.08663427829742</v>
+        <v>1.08663439750671</v>
       </c>
       <c r="H1901" t="n">
         <v>20926564</v>
@@ -55585,7 +55585,7 @@
         <v>1.16250002384186</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.03541994094849</v>
+        <v>1.03542006015778</v>
       </c>
       <c r="H1904" t="n">
         <v>44264066</v>
@@ -55643,7 +55643,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.04833495616913</v>
+        <v>1.04833483695984</v>
       </c>
       <c r="H1906" t="n">
         <v>29040859</v>
@@ -55672,7 +55672,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.07772743701935</v>
+        <v>1.07772755622864</v>
       </c>
       <c r="H1907" t="n">
         <v>35754602</v>
@@ -55875,7 +55875,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.30039846897125</v>
+        <v>1.30039834976196</v>
       </c>
       <c r="H1914" t="n">
         <v>60137225</v>
@@ -55904,7 +55904,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.3110865354538</v>
+        <v>1.31108665466309</v>
       </c>
       <c r="H1915" t="n">
         <v>40402535</v>
@@ -55933,7 +55933,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.32266557216644</v>
+        <v>1.32266545295715</v>
       </c>
       <c r="H1916" t="n">
         <v>40030022</v>
@@ -56020,7 +56020,7 @@
         <v>1.43949997425079</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.28213942050934</v>
+        <v>1.28213930130005</v>
       </c>
       <c r="H1919" t="n">
         <v>27592628</v>
@@ -56049,7 +56049,7 @@
         <v>1.43250000476837</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.27590453624725</v>
+        <v>1.27590465545654</v>
       </c>
       <c r="H1920" t="n">
         <v>21395530</v>
@@ -56078,7 +56078,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.30039846897125</v>
+        <v>1.30039834976196</v>
       </c>
       <c r="H1921" t="n">
         <v>18806426</v>
@@ -56194,7 +56194,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.328009724617</v>
+        <v>1.32800960540771</v>
       </c>
       <c r="H1925" t="n">
         <v>26562115</v>
@@ -56281,7 +56281,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1928" t="n">
         <v>65561642</v>
@@ -56310,7 +56310,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1929" t="n">
         <v>29757990</v>
@@ -56339,7 +56339,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1930" t="n">
-        <v>1.29683566093445</v>
+        <v>1.29683554172516</v>
       </c>
       <c r="H1930" t="n">
         <v>46308940</v>
@@ -56368,7 +56368,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.29327285289764</v>
+        <v>1.29327297210693</v>
       </c>
       <c r="H1931" t="n">
         <v>26931723</v>
@@ -56426,7 +56426,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.25586414337158</v>
+        <v>1.25586426258087</v>
       </c>
       <c r="H1933" t="n">
         <v>26197753</v>
@@ -56484,7 +56484,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.24339461326599</v>
+        <v>1.24339473247528</v>
       </c>
       <c r="H1935" t="n">
         <v>23656707</v>
@@ -56658,7 +56658,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.30485188961029</v>
+        <v>1.304851770401</v>
       </c>
       <c r="H1941" t="n">
         <v>36097664</v>
@@ -56687,7 +56687,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H1942" t="n">
         <v>21886700</v>
@@ -56774,7 +56774,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.33869779109955</v>
+        <v>1.33869791030884</v>
       </c>
       <c r="H1945" t="n">
         <v>21109505</v>
@@ -56861,7 +56861,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.32266557216644</v>
+        <v>1.32266545295715</v>
       </c>
       <c r="H1948" t="n">
         <v>24397332</v>
@@ -56948,7 +56948,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1951" t="n">
-        <v>1.4019364118576</v>
+        <v>1.40193629264832</v>
       </c>
       <c r="H1951" t="n">
         <v>45002851</v>
@@ -56977,7 +56977,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.328009724617</v>
+        <v>1.32800960540771</v>
       </c>
       <c r="H1952" t="n">
         <v>124985920</v>
@@ -57093,7 +57093,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H1956" t="n">
         <v>39334965</v>
@@ -57151,7 +57151,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.37566113471985</v>
+        <v>1.37566125392914</v>
       </c>
       <c r="H1958" t="n">
         <v>66425360</v>
@@ -57238,7 +57238,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.41975009441376</v>
+        <v>1.41974997520447</v>
       </c>
       <c r="H1961" t="n">
         <v>31281838</v>
@@ -57325,7 +57325,7 @@
         <v>1.60950005054474</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.43355572223663</v>
+        <v>1.43355560302734</v>
       </c>
       <c r="H1964" t="n">
         <v>26138694</v>
@@ -57383,7 +57383,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.40104568004608</v>
+        <v>1.40104556083679</v>
       </c>
       <c r="H1966" t="n">
         <v>153129411</v>
@@ -57470,7 +57470,7 @@
         <v>1.46249997615814</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.30262517929077</v>
+        <v>1.30262506008148</v>
       </c>
       <c r="H1969" t="n">
         <v>26919423</v>
@@ -57499,7 +57499,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.27679538726807</v>
+        <v>1.27679526805878</v>
       </c>
       <c r="H1970" t="n">
         <v>26802260</v>
@@ -57528,7 +57528,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.29683566093445</v>
+        <v>1.29683554172516</v>
       </c>
       <c r="H1971" t="n">
         <v>25191162</v>
@@ -57731,7 +57731,7 @@
         <v>1.41849994659424</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.26343500614166</v>
+        <v>1.26343488693237</v>
       </c>
       <c r="H1978" t="n">
         <v>88712511</v>
@@ -57934,7 +57934,7 @@
         <v>1.5275000333786</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.36051964759827</v>
+        <v>1.36051952838898</v>
       </c>
       <c r="H1985" t="n">
         <v>16749025</v>
@@ -57992,7 +57992,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.37566113471985</v>
+        <v>1.37566125392914</v>
       </c>
       <c r="H1987" t="n">
         <v>51105926</v>
@@ -58021,7 +58021,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.29015564918518</v>
+        <v>1.29015552997589</v>
       </c>
       <c r="H1988" t="n">
         <v>67066172</v>
@@ -58079,7 +58079,7 @@
         <v>1.41449999809265</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.25987231731415</v>
+        <v>1.25987219810486</v>
       </c>
       <c r="H1990" t="n">
         <v>29949971</v>
@@ -58166,7 +58166,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.23626923561096</v>
+        <v>1.23626911640167</v>
       </c>
       <c r="H1993" t="n">
         <v>49894794</v>
@@ -58427,7 +58427,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H2002" t="n">
         <v>21379601</v>
@@ -58456,7 +58456,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.23805046081543</v>
+        <v>1.23805058002472</v>
       </c>
       <c r="H2003" t="n">
         <v>18744870</v>
@@ -58572,7 +58572,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H2007" t="n">
         <v>40689470</v>
@@ -58717,7 +58717,7 @@
         <v>1.44749999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>1.28926479816437</v>
+        <v>1.28926491737366</v>
       </c>
       <c r="H2012" t="n">
         <v>13752928</v>
@@ -58862,7 +58862,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H2017" t="n">
         <v>79262449</v>
@@ -58978,7 +58978,7 @@
         <v>1.46150004863739</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.30173444747925</v>
+        <v>1.30173456668854</v>
       </c>
       <c r="H2021" t="n">
         <v>32246011</v>
@@ -59007,7 +59007,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.24784803390503</v>
+        <v>1.24784815311432</v>
       </c>
       <c r="H2022" t="n">
         <v>61474648</v>
@@ -59036,7 +59036,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.24784803390503</v>
+        <v>1.24784815311432</v>
       </c>
       <c r="H2023" t="n">
         <v>34906238</v>
@@ -59123,7 +59123,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.22647166252136</v>
+        <v>1.22647154331207</v>
       </c>
       <c r="H2026" t="n">
         <v>31335128</v>
@@ -59210,7 +59210,7 @@
         <v>1.42050004005432</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.26521635055542</v>
+        <v>1.26521646976471</v>
       </c>
       <c r="H2029" t="n">
         <v>35969343</v>
@@ -59268,7 +59268,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.29015564918518</v>
+        <v>1.29015552997589</v>
       </c>
       <c r="H2031" t="n">
         <v>21961584</v>
@@ -59326,7 +59326,7 @@
         <v>1.44649994373322</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.28837406635284</v>
+        <v>1.28837418556213</v>
       </c>
       <c r="H2033" t="n">
         <v>15340362</v>
@@ -59384,7 +59384,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.3208841085434</v>
+        <v>1.32088422775269</v>
       </c>
       <c r="H2035" t="n">
         <v>16248522</v>
@@ -59413,7 +59413,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.30930531024933</v>
+        <v>1.30930519104004</v>
       </c>
       <c r="H2036" t="n">
         <v>16596498</v>
@@ -59471,7 +59471,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.32622814178467</v>
+        <v>1.32622826099396</v>
       </c>
       <c r="H2038" t="n">
         <v>31598891</v>
@@ -59558,7 +59558,7 @@
         <v>1.50650000572205</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.34181523323059</v>
+        <v>1.3418151140213</v>
       </c>
       <c r="H2041" t="n">
         <v>49175369</v>
@@ -59790,7 +59790,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.27679538726807</v>
+        <v>1.27679526805878</v>
       </c>
       <c r="H2049" t="n">
         <v>35782956</v>
@@ -59877,7 +59877,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31643068790436</v>
+        <v>1.31643080711365</v>
       </c>
       <c r="H2052" t="n">
         <v>70363678</v>
@@ -59964,7 +59964,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.34315121173859</v>
+        <v>1.34315133094788</v>
       </c>
       <c r="H2055" t="n">
         <v>21291896</v>
@@ -60399,7 +60399,7 @@
         <v>1.375</v>
       </c>
       <c r="G2070" t="n">
-        <v>1.22469019889832</v>
+        <v>1.2246903181076</v>
       </c>
       <c r="H2070" t="n">
         <v>37201230</v>
@@ -60486,7 +60486,7 @@
         <v>1.38100004196167</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.23003435134888</v>
+        <v>1.23003447055817</v>
       </c>
       <c r="H2073" t="n">
         <v>23884244</v>
@@ -60602,7 +60602,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.32979094982147</v>
+        <v>1.32979106903076</v>
       </c>
       <c r="H2077" t="n">
         <v>97981694</v>
@@ -60689,7 +60689,7 @@
         <v>1.82149994373322</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.6223806142807</v>
+        <v>1.62238049507141</v>
       </c>
       <c r="H2080" t="n">
         <v>170004032</v>
@@ -60776,7 +60776,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.72347319126129</v>
+        <v>1.723473072052</v>
       </c>
       <c r="H2083" t="n">
         <v>102058873</v>
@@ -60863,7 +60863,7 @@
         <v>1.97650003433228</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.76043665409088</v>
+        <v>1.76043653488159</v>
       </c>
       <c r="H2086" t="n">
         <v>36852781</v>
@@ -60979,7 +60979,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.87488961219788</v>
+        <v>1.87488949298859</v>
       </c>
       <c r="H2090" t="n">
         <v>47381130</v>
@@ -61008,7 +61008,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.88112413883209</v>
+        <v>1.88112425804138</v>
       </c>
       <c r="H2091" t="n">
         <v>28755854</v>
@@ -61037,7 +61037,7 @@
         <v>2.08699989318848</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.85885715484619</v>
+        <v>1.8588570356369</v>
       </c>
       <c r="H2092" t="n">
         <v>29642492</v>
@@ -61153,7 +61153,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.91318881511688</v>
+        <v>1.91318893432617</v>
       </c>
       <c r="H2096" t="n">
         <v>51280827</v>
@@ -61356,7 +61356,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.98889696598053</v>
+        <v>1.98889708518982</v>
       </c>
       <c r="H2103" t="n">
         <v>20444616</v>
@@ -61385,7 +61385,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2104" t="n">
-        <v>2.00760126113892</v>
+        <v>2.0076014995575</v>
       </c>
       <c r="H2104" t="n">
         <v>25187040</v>
@@ -61414,7 +61414,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G2105" t="n">
-        <v>2.00849199295044</v>
+        <v>2.00849223136902</v>
       </c>
       <c r="H2105" t="n">
         <v>29639951</v>
@@ -61472,7 +61472,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.06994915008545</v>
+        <v>2.06994891166687</v>
       </c>
       <c r="H2107" t="n">
         <v>41532484</v>
@@ -61530,7 +61530,7 @@
         <v>2.3970000743866</v>
       </c>
       <c r="G2109" t="n">
-        <v>2.13496923446655</v>
+        <v>2.13496899604797</v>
       </c>
       <c r="H2109" t="n">
         <v>81592175</v>
@@ -61559,7 +61559,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2110" t="n">
-        <v>2.08419990539551</v>
+        <v>2.08420014381409</v>
       </c>
       <c r="H2110" t="n">
         <v>42505018</v>
@@ -61646,7 +61646,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.99513185024261</v>
+        <v>1.99513173103333</v>
       </c>
       <c r="H2113" t="n">
         <v>34419597</v>
@@ -61675,7 +61675,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2114" t="n">
         <v>27318033</v>
@@ -61733,7 +61733,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.94258141517639</v>
+        <v>1.94258153438568</v>
       </c>
       <c r="H2116" t="n">
         <v>46811721</v>
@@ -61820,7 +61820,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.97197389602661</v>
+        <v>1.9719740152359</v>
       </c>
       <c r="H2119" t="n">
         <v>18487545</v>
@@ -61878,7 +61878,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.9523788690567</v>
+        <v>1.95237898826599</v>
       </c>
       <c r="H2121" t="n">
         <v>27702781</v>
@@ -61936,7 +61936,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.94080007076263</v>
+        <v>1.94079983234406</v>
       </c>
       <c r="H2123" t="n">
         <v>20243345</v>
@@ -62023,7 +62023,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2126" t="n">
-        <v>1.91318881511688</v>
+        <v>1.91318893432617</v>
       </c>
       <c r="H2126" t="n">
         <v>16042180</v>
@@ -62081,7 +62081,7 @@
         <v>2.13100004196167</v>
       </c>
       <c r="G2128" t="n">
-        <v>1.8980473279953</v>
+        <v>1.89804720878601</v>
       </c>
       <c r="H2128" t="n">
         <v>22011055</v>
@@ -62110,7 +62110,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2129" t="n">
         <v>19775385</v>
@@ -62168,7 +62168,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G2131" t="n">
-        <v>1.97019255161285</v>
+        <v>1.97019267082214</v>
       </c>
       <c r="H2131" t="n">
         <v>19971385</v>
@@ -62197,7 +62197,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2132" t="n">
-        <v>2.02541494369507</v>
+        <v>2.02541518211365</v>
       </c>
       <c r="H2132" t="n">
         <v>39975168</v>
@@ -62255,7 +62255,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2134" t="n">
-        <v>2.11359286308289</v>
+        <v>2.11359262466431</v>
       </c>
       <c r="H2134" t="n">
         <v>44554345</v>
@@ -62371,7 +62371,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2138" t="n">
-        <v>2.12160897254944</v>
+        <v>2.12160873413086</v>
       </c>
       <c r="H2138" t="n">
         <v>27147448</v>
@@ -62400,7 +62400,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2139" t="n">
-        <v>2.11359286308289</v>
+        <v>2.11359262466431</v>
       </c>
       <c r="H2139" t="n">
         <v>18307723</v>
@@ -62458,7 +62458,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2141" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2141" t="n">
         <v>13550932</v>
@@ -62516,7 +62516,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2143" t="n">
-        <v>1.98889696598053</v>
+        <v>1.98889708518982</v>
       </c>
       <c r="H2143" t="n">
         <v>26661132</v>
@@ -62574,7 +62574,7 @@
         <v>2.15300011634827</v>
       </c>
       <c r="G2145" t="n">
-        <v>1.91764235496521</v>
+        <v>1.9176424741745</v>
       </c>
       <c r="H2145" t="n">
         <v>22296682</v>
@@ -62603,7 +62603,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.9203143119812</v>
+        <v>1.92031419277191</v>
       </c>
       <c r="H2146" t="n">
         <v>35218310</v>
@@ -62632,7 +62632,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.93367457389832</v>
+        <v>1.9336746931076</v>
       </c>
       <c r="H2147" t="n">
         <v>17467441</v>
@@ -62661,7 +62661,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2148" t="n">
         <v>28506448</v>
@@ -62690,7 +62690,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.83926212787628</v>
+        <v>1.83926224708557</v>
       </c>
       <c r="H2149" t="n">
         <v>27905894</v>
@@ -62748,7 +62748,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2151" t="n">
         <v>33021803</v>
@@ -62835,7 +62835,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.86152911186218</v>
+        <v>1.86152923107147</v>
       </c>
       <c r="H2154" t="n">
         <v>35977989</v>
@@ -62864,7 +62864,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.86152911186218</v>
+        <v>1.86152923107147</v>
       </c>
       <c r="H2155" t="n">
         <v>22290014</v>
@@ -62893,7 +62893,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2156" t="n">
-        <v>1.89626574516296</v>
+        <v>1.89626586437225</v>
       </c>
       <c r="H2156" t="n">
         <v>21085975</v>
@@ -62922,7 +62922,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2157" t="n">
         <v>35756797</v>
@@ -62951,7 +62951,7 @@
         <v>2.15899991989136</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.92298626899719</v>
+        <v>1.92298638820648</v>
       </c>
       <c r="H2158" t="n">
         <v>16359113</v>
@@ -62980,7 +62980,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.99245965480804</v>
+        <v>1.99245977401733</v>
       </c>
       <c r="H2159" t="n">
         <v>39248301</v>
@@ -63096,7 +63096,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.1358597278595</v>
+        <v>2.13585996627808</v>
       </c>
       <c r="H2163" t="n">
         <v>33746318</v>
@@ -63212,7 +63212,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2167" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2167" t="n">
         <v>25601227</v>
@@ -63299,7 +63299,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G2170" t="n">
-        <v>2.07351183891296</v>
+        <v>2.07351207733154</v>
       </c>
       <c r="H2170" t="n">
         <v>26440425</v>
@@ -63328,7 +63328,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.06371426582336</v>
+        <v>2.06371450424194</v>
       </c>
       <c r="H2171" t="n">
         <v>26757191</v>
@@ -63357,7 +63357,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G2172" t="n">
-        <v>2.09666991233826</v>
+        <v>2.09666967391968</v>
       </c>
       <c r="H2172" t="n">
         <v>24912702</v>
@@ -63415,7 +63415,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2174" t="n">
-        <v>2.10913920402527</v>
+        <v>2.10913944244385</v>
       </c>
       <c r="H2174" t="n">
         <v>19724218</v>
@@ -63444,7 +63444,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.12339043617249</v>
+        <v>2.12339019775391</v>
       </c>
       <c r="H2175" t="n">
         <v>29130431</v>
@@ -63473,7 +63473,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.14476656913757</v>
+        <v>2.14476680755615</v>
       </c>
       <c r="H2176" t="n">
         <v>16678363</v>
@@ -63560,7 +63560,7 @@
         <v>2.41899991035461</v>
       </c>
       <c r="G2179" t="n">
-        <v>2.15456390380859</v>
+        <v>2.15456414222717</v>
       </c>
       <c r="H2179" t="n">
         <v>23246952</v>
@@ -63618,7 +63618,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2181" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2181" t="n">
         <v>45523587</v>
@@ -63647,7 +63647,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G2182" t="n">
-        <v>1.98444354534149</v>
+        <v>1.9844434261322</v>
       </c>
       <c r="H2182" t="n">
         <v>44868347</v>
@@ -63705,7 +63705,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.9461442232132</v>
+        <v>1.94614410400391</v>
       </c>
       <c r="H2184" t="n">
         <v>18067908</v>
@@ -63734,7 +63734,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2185" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2185" t="n">
         <v>20351307</v>
@@ -63763,7 +63763,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.94080007076263</v>
+        <v>1.94079983234406</v>
       </c>
       <c r="H2186" t="n">
         <v>18512647</v>
@@ -63879,7 +63879,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G2190" t="n">
-        <v>1.79294645786285</v>
+        <v>1.79294657707214</v>
       </c>
       <c r="H2190" t="n">
         <v>24047004</v>
@@ -63995,7 +63995,7 @@
         <v>1.98450005054474</v>
       </c>
       <c r="G2194" t="n">
-        <v>1.76756203174591</v>
+        <v>1.7675621509552</v>
       </c>
       <c r="H2194" t="n">
         <v>23362020</v>
@@ -64140,7 +64140,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G2199" t="n">
-        <v>1.84282493591309</v>
+        <v>1.8428248167038</v>
       </c>
       <c r="H2199" t="n">
         <v>32985049</v>
@@ -64227,7 +64227,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.84549701213837</v>
+        <v>1.84549689292908</v>
       </c>
       <c r="H2202" t="n">
         <v>16439030</v>
@@ -64256,7 +64256,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.81521379947662</v>
+        <v>1.81521368026733</v>
       </c>
       <c r="H2203" t="n">
         <v>23581831</v>
@@ -64343,7 +64343,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2206" t="n">
         <v>19255054</v>
@@ -64372,7 +64372,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2207" t="n">
-        <v>1.80185341835022</v>
+        <v>1.80185329914093</v>
       </c>
       <c r="H2207" t="n">
         <v>12789945</v>
@@ -64401,7 +64401,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.67448556423187</v>
+        <v>1.67448568344116</v>
       </c>
       <c r="H2208" t="n">
         <v>53900944</v>
@@ -64430,7 +64430,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.71189427375793</v>
+        <v>1.71189439296722</v>
       </c>
       <c r="H2209" t="n">
         <v>35189302</v>
@@ -64546,7 +64546,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G2213" t="n">
-        <v>1.60055887699127</v>
+        <v>1.60055899620056</v>
       </c>
       <c r="H2213" t="n">
         <v>37765591</v>
@@ -64575,7 +64575,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.6272794008255</v>
+        <v>1.62727928161621</v>
       </c>
       <c r="H2214" t="n">
         <v>22594695</v>
@@ -64865,7 +64865,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.81343221664429</v>
+        <v>1.81343233585358</v>
       </c>
       <c r="H2224" t="n">
         <v>24725349</v>
@@ -65097,7 +65097,7 @@
         <v>2.05699992179871</v>
       </c>
       <c r="G2232" t="n">
-        <v>1.83213663101196</v>
+        <v>1.83213651180267</v>
       </c>
       <c r="H2232" t="n">
         <v>29472348</v>
@@ -65155,7 +65155,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2234" t="n">
-        <v>1.79027438163757</v>
+        <v>1.79027450084686</v>
       </c>
       <c r="H2234" t="n">
         <v>16876658</v>
@@ -65184,7 +65184,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.80185341835022</v>
+        <v>1.80185329914093</v>
       </c>
       <c r="H2235" t="n">
         <v>20529123</v>
@@ -65358,7 +65358,7 @@
         <v>1.99150002002716</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.773796916008</v>
+        <v>1.77379679679871</v>
       </c>
       <c r="H2241" t="n">
         <v>46698722</v>
@@ -65416,7 +65416,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2243" t="n">
-        <v>1.83926212787628</v>
+        <v>1.83926224708557</v>
       </c>
       <c r="H2243" t="n">
         <v>48994310</v>
@@ -65445,7 +65445,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G2244" t="n">
-        <v>1.80630695819855</v>
+        <v>1.80630683898926</v>
       </c>
       <c r="H2244" t="n">
         <v>29352657</v>
@@ -65474,7 +65474,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G2245" t="n">
-        <v>1.89003121852875</v>
+        <v>1.89003109931946</v>
       </c>
       <c r="H2245" t="n">
         <v>81646961</v>
@@ -65503,7 +65503,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.94970679283142</v>
+        <v>1.94970667362213</v>
       </c>
       <c r="H2246" t="n">
         <v>74141845</v>
@@ -65561,7 +65561,7 @@
         <v>2.16300010681152</v>
       </c>
       <c r="G2248" t="n">
-        <v>1.92654919624329</v>
+        <v>1.92654931545258</v>
       </c>
       <c r="H2248" t="n">
         <v>30842480</v>
@@ -65590,7 +65590,7 @@
         <v>2.16700005531311</v>
       </c>
       <c r="G2249" t="n">
-        <v>1.93011200428009</v>
+        <v>1.9301118850708</v>
       </c>
       <c r="H2249" t="n">
         <v>30050128</v>
@@ -65619,7 +65619,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2250" t="n">
-        <v>1.94525361061096</v>
+        <v>1.94525349140167</v>
       </c>
       <c r="H2250" t="n">
         <v>26979522</v>
@@ -65648,7 +65648,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2251" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2251" t="n">
         <v>53288446</v>
@@ -65677,7 +65677,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2252" t="n">
         <v>41701778</v>
@@ -65735,7 +65735,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2254" t="n">
-        <v>2.00314784049988</v>
+        <v>2.00314807891846</v>
       </c>
       <c r="H2254" t="n">
         <v>44091922</v>
@@ -65793,7 +65793,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2256" t="n">
-        <v>2.06994915008545</v>
+        <v>2.06994891166687</v>
       </c>
       <c r="H2256" t="n">
         <v>54666411</v>
@@ -65880,7 +65880,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2259" t="n">
-        <v>2.05302619934082</v>
+        <v>2.0530264377594</v>
       </c>
       <c r="H2259" t="n">
         <v>24934085</v>
@@ -65909,7 +65909,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2260" t="n">
-        <v>2.06371426582336</v>
+        <v>2.06371450424194</v>
       </c>
       <c r="H2260" t="n">
         <v>40038315</v>
@@ -65938,7 +65938,7 @@
         <v>2.33299994468689</v>
       </c>
       <c r="G2261" t="n">
-        <v>2.07796549797058</v>
+        <v>2.077965259552</v>
       </c>
       <c r="H2261" t="n">
         <v>34552742</v>
@@ -65967,7 +65967,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2262" t="n">
-        <v>2.10913920402527</v>
+        <v>2.10913944244385</v>
       </c>
       <c r="H2262" t="n">
         <v>21092827</v>
@@ -66170,7 +66170,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G2269" t="n">
-        <v>2.16525220870972</v>
+        <v>2.1652524471283</v>
       </c>
       <c r="H2269" t="n">
         <v>38389055</v>
@@ -66315,7 +66315,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G2274" t="n">
-        <v>2.26768088340759</v>
+        <v>2.26768112182617</v>
       </c>
       <c r="H2274" t="n">
         <v>31890329</v>
@@ -66431,7 +66431,7 @@
         <v>2.48699998855591</v>
       </c>
       <c r="G2278" t="n">
-        <v>2.21513080596924</v>
+        <v>2.21513056755066</v>
       </c>
       <c r="H2278" t="n">
         <v>18431422</v>
@@ -66518,7 +66518,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2281" t="n">
-        <v>2.29261994361877</v>
+        <v>2.29262018203735</v>
       </c>
       <c r="H2281" t="n">
         <v>22696347</v>
@@ -66547,7 +66547,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2282" t="n">
-        <v>2.31577801704407</v>
+        <v>2.31577777862549</v>
       </c>
       <c r="H2282" t="n">
         <v>26132220</v>
@@ -66634,7 +66634,7 @@
         <v>2.64299988746643</v>
       </c>
       <c r="G2285" t="n">
-        <v>2.35407733917236</v>
+        <v>2.35407710075378</v>
       </c>
       <c r="H2285" t="n">
         <v>60652789</v>
@@ -66721,7 +66721,7 @@
         <v>2.51099991798401</v>
       </c>
       <c r="G2288" t="n">
-        <v>2.23650693893433</v>
+        <v>2.23650717735291</v>
       </c>
       <c r="H2288" t="n">
         <v>15785363</v>
@@ -66750,7 +66750,7 @@
         <v>2.5090000629425</v>
       </c>
       <c r="G2289" t="n">
-        <v>2.23472595214844</v>
+        <v>2.23472571372986</v>
       </c>
       <c r="H2289" t="n">
         <v>11480911</v>
@@ -66924,7 +66924,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G2295" t="n">
-        <v>2.45294332504272</v>
+        <v>2.45294308662415</v>
       </c>
       <c r="H2295" t="n">
         <v>20214762</v>
@@ -67040,7 +67040,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G2299" t="n">
-        <v>2.31221508979797</v>
+        <v>2.31221532821655</v>
       </c>
       <c r="H2299" t="n">
         <v>74870654</v>
@@ -67098,7 +67098,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G2301" t="n">
-        <v>2.27658772468567</v>
+        <v>2.27658796310425</v>
       </c>
       <c r="H2301" t="n">
         <v>30195449</v>
@@ -67127,7 +67127,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G2302" t="n">
-        <v>2.25164866447449</v>
+        <v>2.25164890289307</v>
       </c>
       <c r="H2302" t="n">
         <v>24626119</v>
@@ -67156,7 +67156,7 @@
         <v>2.51300001144409</v>
       </c>
       <c r="G2303" t="n">
-        <v>2.23828840255737</v>
+        <v>2.23828864097595</v>
       </c>
       <c r="H2303" t="n">
         <v>20104873</v>
@@ -67214,7 +67214,7 @@
         <v>2.48300004005432</v>
       </c>
       <c r="G2305" t="n">
-        <v>2.21156787872314</v>
+        <v>2.21156811714172</v>
       </c>
       <c r="H2305" t="n">
         <v>27751479</v>
@@ -67243,7 +67243,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G2306" t="n">
-        <v>2.14832949638367</v>
+        <v>2.14832925796509</v>
       </c>
       <c r="H2306" t="n">
         <v>43140551</v>
@@ -67272,7 +67272,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2307" t="n">
-        <v>2.12160897254944</v>
+        <v>2.12160873413086</v>
       </c>
       <c r="H2307" t="n">
         <v>24111895</v>
@@ -67504,7 +67504,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2315" t="n">
-        <v>2.04411935806274</v>
+        <v>2.04411959648132</v>
       </c>
       <c r="H2315" t="n">
         <v>24791375</v>
@@ -67562,7 +67562,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G2317" t="n">
-        <v>2.04768228530884</v>
+        <v>2.04768204689026</v>
       </c>
       <c r="H2317" t="n">
         <v>21357944</v>
@@ -67707,7 +67707,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G2322" t="n">
-        <v>2.05658912658691</v>
+        <v>2.05658888816833</v>
       </c>
       <c r="H2322" t="n">
         <v>15248097</v>
@@ -67794,7 +67794,7 @@
         <v>2.28099989891052</v>
       </c>
       <c r="G2325" t="n">
-        <v>2.03164982795715</v>
+        <v>2.03164958953857</v>
       </c>
       <c r="H2325" t="n">
         <v>20004250</v>
@@ -67823,7 +67823,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G2326" t="n">
-        <v>2.0681676864624</v>
+        <v>2.06816792488098</v>
       </c>
       <c r="H2326" t="n">
         <v>27029721</v>
@@ -67910,7 +67910,7 @@
         <v>2.20300006866455</v>
       </c>
       <c r="G2329" t="n">
-        <v>1.9621764421463</v>
+        <v>1.96217656135559</v>
       </c>
       <c r="H2329" t="n">
         <v>165427959</v>
@@ -67939,7 +67939,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2330" t="n">
-        <v>2.00314784049988</v>
+        <v>2.00314807891846</v>
       </c>
       <c r="H2330" t="n">
         <v>90357314</v>
@@ -67997,7 +67997,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2332" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2332" t="n">
         <v>49106059</v>
@@ -68055,7 +68055,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2334" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2334" t="n">
         <v>47390121</v>
@@ -68200,7 +68200,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G2339" t="n">
-        <v>1.85440385341644</v>
+        <v>1.85440373420715</v>
       </c>
       <c r="H2339" t="n">
         <v>52881442</v>
@@ -68287,7 +68287,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2342" t="n">
-        <v>1.89626574516296</v>
+        <v>1.89626586437225</v>
       </c>
       <c r="H2342" t="n">
         <v>54335801</v>
@@ -68316,7 +68316,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.93278396129608</v>
+        <v>1.93278384208679</v>
       </c>
       <c r="H2343" t="n">
         <v>54028041</v>
@@ -68345,7 +68345,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2344" t="n">
         <v>32171346</v>
@@ -68432,7 +68432,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2347" t="n">
-        <v>1.96841132640839</v>
+        <v>1.9684112071991</v>
       </c>
       <c r="H2347" t="n">
         <v>31365241</v>
@@ -68461,7 +68461,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2348" t="n">
-        <v>1.94525361061096</v>
+        <v>1.94525349140167</v>
       </c>
       <c r="H2348" t="n">
         <v>43704455</v>
@@ -68519,7 +68519,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G2350" t="n">
-        <v>1.9586136341095</v>
+        <v>1.95861351490021</v>
       </c>
       <c r="H2350" t="n">
         <v>35346168</v>
@@ -68548,7 +68548,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2351" t="n">
-        <v>1.93367457389832</v>
+        <v>1.9336746931076</v>
       </c>
       <c r="H2351" t="n">
         <v>29069827</v>
@@ -68635,7 +68635,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2354" t="n">
-        <v>1.89537537097931</v>
+        <v>1.89537525177002</v>
       </c>
       <c r="H2354" t="n">
         <v>33627039</v>
@@ -68664,7 +68664,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.72436380386353</v>
+        <v>1.72436392307281</v>
       </c>
       <c r="H2355" t="n">
         <v>85443225</v>
@@ -68838,7 +68838,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G2361" t="n">
-        <v>1.52128803730011</v>
+        <v>1.52128791809082</v>
       </c>
       <c r="H2361" t="n">
         <v>38867170</v>
@@ -68867,7 +68867,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G2362" t="n">
-        <v>1.56493139266968</v>
+        <v>1.56493151187897</v>
       </c>
       <c r="H2362" t="n">
         <v>50829326</v>
@@ -69041,7 +69041,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G2368" t="n">
-        <v>1.74930310249329</v>
+        <v>1.749302983284</v>
       </c>
       <c r="H2368" t="n">
         <v>65053471</v>
@@ -69128,7 +69128,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.82590174674988</v>
+        <v>1.82590186595917</v>
       </c>
       <c r="H2371" t="n">
         <v>29975796</v>
@@ -69186,7 +69186,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2373" t="n">
-        <v>1.85262227058411</v>
+        <v>1.8526223897934</v>
       </c>
       <c r="H2373" t="n">
         <v>37413416</v>
@@ -69215,7 +69215,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G2374" t="n">
-        <v>1.83302748203278</v>
+        <v>1.83302736282349</v>
       </c>
       <c r="H2374" t="n">
         <v>32042896</v>
@@ -69244,7 +69244,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G2375" t="n">
-        <v>1.82768332958221</v>
+        <v>1.82768321037292</v>
       </c>
       <c r="H2375" t="n">
         <v>38839501</v>
@@ -69273,7 +69273,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G2376" t="n">
-        <v>1.83837139606476</v>
+        <v>1.83837127685547</v>
       </c>
       <c r="H2376" t="n">
         <v>30420999</v>
@@ -69331,7 +69331,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G2378" t="n">
-        <v>1.9399094581604</v>
+        <v>1.93990933895111</v>
       </c>
       <c r="H2378" t="n">
         <v>64329397</v>
@@ -80009,6 +80009,35 @@
         <v>13759907</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>4.44999980926514</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>4.48899984359741</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>4.39799976348877</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>4.4850001335144</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>4.4850001335144</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>9721756</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -543,7 +543,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540748596191</v>
+        <v>18.9540729522705</v>
       </c>
       <c r="H6" t="n">
         <v>681723</v>
@@ -601,7 +601,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.878662109375</v>
+        <v>19.8786602020264</v>
       </c>
       <c r="H8" t="n">
         <v>1620392</v>
@@ -659,7 +659,7 @@
         <v>22.1823787689209</v>
       </c>
       <c r="G10" t="n">
-        <v>19.668529510498</v>
+        <v>19.6685276031494</v>
       </c>
       <c r="H10" t="n">
         <v>887518</v>
@@ -688,7 +688,7 @@
         <v>20.9184246063232</v>
       </c>
       <c r="G11" t="n">
-        <v>18.5478134155273</v>
+        <v>18.547815322876</v>
       </c>
       <c r="H11" t="n">
         <v>1339292</v>
@@ -775,7 +775,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460269927979</v>
+        <v>15.7460279464722</v>
       </c>
       <c r="H14" t="n">
         <v>2077512</v>
@@ -804,7 +804,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.821439743042</v>
+        <v>14.8214406967163</v>
       </c>
       <c r="H15" t="n">
         <v>2435960</v>
@@ -862,7 +862,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552726745605</v>
+        <v>13.9552736282349</v>
       </c>
       <c r="H17" t="n">
         <v>354113</v>
@@ -920,7 +920,7 @@
         <v>13.806058883667</v>
       </c>
       <c r="G19" t="n">
-        <v>12.2414665222168</v>
+        <v>12.2414674758911</v>
       </c>
       <c r="H19" t="n">
         <v>1211251</v>
@@ -949,7 +949,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087112426758</v>
+        <v>12.6087121963501</v>
       </c>
       <c r="H20" t="n">
         <v>1225889</v>
@@ -1065,7 +1065,7 @@
         <v>13.5048360824585</v>
       </c>
       <c r="G24" t="n">
-        <v>11.9743814468384</v>
+        <v>11.9743804931641</v>
       </c>
       <c r="H24" t="n">
         <v>1141642</v>
@@ -1123,7 +1123,7 @@
         <v>13.0530023574829</v>
       </c>
       <c r="G26" t="n">
-        <v>11.573751449585</v>
+        <v>11.5737524032593</v>
       </c>
       <c r="H26" t="n">
         <v>1877083</v>
@@ -1297,7 +1297,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393558502197</v>
+        <v>6.74393510818481</v>
       </c>
       <c r="H32" t="n">
         <v>7100655</v>
@@ -1413,7 +1413,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36046028137207</v>
+        <v>7.36045980453491</v>
       </c>
       <c r="H36" t="n">
         <v>4978216</v>
@@ -1471,7 +1471,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243934631348</v>
+        <v>7.91243886947632</v>
       </c>
       <c r="H38" t="n">
         <v>4762357</v>
@@ -1529,7 +1529,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H40" t="n">
         <v>5230684</v>
@@ -1587,7 +1587,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H42" t="n">
         <v>8046415</v>
@@ -1616,7 +1616,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H43" t="n">
         <v>5632607</v>
@@ -1703,7 +1703,7 @@
         <v>9.96546459197998</v>
       </c>
       <c r="G46" t="n">
-        <v>8.83611297607422</v>
+        <v>8.83611392974854</v>
       </c>
       <c r="H46" t="n">
         <v>3768604</v>
@@ -1732,7 +1732,7 @@
         <v>10.6884002685547</v>
       </c>
       <c r="G47" t="n">
-        <v>9.47712135314941</v>
+        <v>9.47712230682373</v>
       </c>
       <c r="H47" t="n">
         <v>6263628</v>
@@ -1819,7 +1819,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811292648315</v>
+        <v>7.98811340332031</v>
       </c>
       <c r="H50" t="n">
         <v>5464353</v>
@@ -1877,7 +1877,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683300018311</v>
+        <v>8.58683204650879</v>
       </c>
       <c r="H52" t="n">
         <v>4362352</v>
@@ -1906,7 +1906,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G53" t="n">
-        <v>8.29526424407959</v>
+        <v>8.29526329040527</v>
       </c>
       <c r="H53" t="n">
         <v>3258288</v>
@@ -2138,7 +2138,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.34487962722778</v>
+        <v>7.34488010406494</v>
       </c>
       <c r="H61" t="n">
         <v>3010233</v>
@@ -2225,7 +2225,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870761871338</v>
+        <v>7.65870714187622</v>
       </c>
       <c r="H64" t="n">
         <v>2688899</v>
@@ -2283,7 +2283,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973640441895</v>
+        <v>6.89973592758179</v>
       </c>
       <c r="H66" t="n">
         <v>4271134</v>
@@ -2341,7 +2341,7 @@
         <v>7.61341381072998</v>
       </c>
       <c r="G68" t="n">
-        <v>6.75061273574829</v>
+        <v>6.75061225891113</v>
       </c>
       <c r="H68" t="n">
         <v>2618453</v>
@@ -2399,7 +2399,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H70" t="n">
         <v>3239759</v>
@@ -2428,7 +2428,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G71" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H71" t="n">
         <v>3489116</v>
@@ -2457,7 +2457,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.86347341537476</v>
+        <v>7.8634729385376</v>
       </c>
       <c r="H72" t="n">
         <v>3751875</v>
@@ -2660,7 +2660,7 @@
         <v>9.25006008148193</v>
       </c>
       <c r="G79" t="n">
-        <v>8.20178413391113</v>
+        <v>8.20178318023682</v>
       </c>
       <c r="H79" t="n">
         <v>2478794</v>
@@ -2689,7 +2689,7 @@
         <v>9.39816093444824</v>
       </c>
       <c r="G80" t="n">
-        <v>8.33310127258301</v>
+        <v>8.33310031890869</v>
       </c>
       <c r="H80" t="n">
         <v>1866023</v>
@@ -2805,7 +2805,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H84" t="n">
         <v>6156371</v>
@@ -2892,7 +2892,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H87" t="n">
         <v>3783755</v>
@@ -2921,7 +2921,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G88" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H88" t="n">
         <v>2952497</v>
@@ -2950,7 +2950,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G89" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H89" t="n">
         <v>2726335</v>
@@ -3008,7 +3008,7 @@
         <v>9.20487594604492</v>
       </c>
       <c r="G91" t="n">
-        <v>8.16171932220459</v>
+        <v>8.16172027587891</v>
       </c>
       <c r="H91" t="n">
         <v>2650097</v>
@@ -3066,7 +3066,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H93" t="n">
         <v>3351378</v>
@@ -3182,7 +3182,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G97" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H97" t="n">
         <v>1772130</v>
@@ -3240,7 +3240,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701738357544</v>
+        <v>7.99701690673828</v>
       </c>
       <c r="H99" t="n">
         <v>2418605</v>
@@ -3327,7 +3327,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H102" t="n">
         <v>3679752</v>
@@ -3414,7 +3414,7 @@
         <v>9.3303861618042</v>
       </c>
       <c r="G105" t="n">
-        <v>8.27300548553467</v>
+        <v>8.27300643920898</v>
       </c>
       <c r="H105" t="n">
         <v>1253897</v>
@@ -3443,7 +3443,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G106" t="n">
-        <v>8.1884298324585</v>
+        <v>8.18842887878418</v>
       </c>
       <c r="H106" t="n">
         <v>2368543</v>
@@ -3530,7 +3530,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889537811279</v>
+        <v>7.77889585494995</v>
       </c>
       <c r="H109" t="n">
         <v>2101522</v>
@@ -3559,7 +3559,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701738357544</v>
+        <v>7.99701690673828</v>
       </c>
       <c r="H110" t="n">
         <v>2370853</v>
@@ -3617,7 +3617,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837268829346</v>
+        <v>8.85837173461914</v>
       </c>
       <c r="H112" t="n">
         <v>4508416</v>
@@ -3646,7 +3646,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G113" t="n">
-        <v>8.6736364364624</v>
+        <v>8.67363548278809</v>
       </c>
       <c r="H113" t="n">
         <v>2693817</v>
@@ -3704,7 +3704,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325372695923</v>
+        <v>7.72325325012207</v>
       </c>
       <c r="H115" t="n">
         <v>4121823</v>
@@ -3762,7 +3762,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808195114136</v>
+        <v>7.96808242797852</v>
       </c>
       <c r="H117" t="n">
         <v>3606977</v>
@@ -3994,7 +3994,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.59193563461304</v>
+        <v>7.5919361114502</v>
       </c>
       <c r="H125" t="n">
         <v>3711164</v>
@@ -4023,7 +4023,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78557348251343</v>
+        <v>7.78557395935059</v>
       </c>
       <c r="H126" t="n">
         <v>3269289</v>
@@ -4052,7 +4052,7 @@
         <v>8.86349010467529</v>
       </c>
       <c r="G127" t="n">
-        <v>7.85902214050293</v>
+        <v>7.85902261734009</v>
       </c>
       <c r="H127" t="n">
         <v>3013097</v>
@@ -4139,7 +4139,7 @@
         <v>9.60650730133057</v>
       </c>
       <c r="G130" t="n">
-        <v>8.51783561706543</v>
+        <v>8.51783657073975</v>
       </c>
       <c r="H130" t="n">
         <v>3045817</v>
@@ -4284,7 +4284,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.71147346496582</v>
+        <v>8.71147441864014</v>
       </c>
       <c r="H135" t="n">
         <v>4380711</v>
@@ -4400,7 +4400,7 @@
         <v>10.3771362304688</v>
       </c>
       <c r="G139" t="n">
-        <v>9.20113277435303</v>
+        <v>9.20113182067871</v>
       </c>
       <c r="H139" t="n">
         <v>1660292</v>
@@ -4429,7 +4429,7 @@
         <v>10.5679111480713</v>
       </c>
       <c r="G140" t="n">
-        <v>9.37028694152832</v>
+        <v>9.37028789520264</v>
       </c>
       <c r="H140" t="n">
         <v>1710004</v>
@@ -4545,7 +4545,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856430053711</v>
+        <v>9.68856525421143</v>
       </c>
       <c r="H144" t="n">
         <v>1705188</v>
@@ -4632,7 +4632,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427124023438</v>
+        <v>9.78427219390869</v>
       </c>
       <c r="H147" t="n">
         <v>3288854</v>
@@ -4661,7 +4661,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G148" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H148" t="n">
         <v>11514563</v>
@@ -4690,7 +4690,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G149" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H149" t="n">
         <v>5327998</v>
@@ -4806,7 +4806,7 @@
         <v>9.37807941436768</v>
       </c>
       <c r="G153" t="n">
-        <v>8.31529521942139</v>
+        <v>8.31529426574707</v>
       </c>
       <c r="H153" t="n">
         <v>2495200</v>
@@ -4980,7 +4980,7 @@
         <v>10.3269319534302</v>
       </c>
       <c r="G159" t="n">
-        <v>9.15661811828613</v>
+        <v>9.15661716461182</v>
       </c>
       <c r="H159" t="n">
         <v>2500199</v>
@@ -5009,7 +5009,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H160" t="n">
         <v>2723125</v>
@@ -5096,7 +5096,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H163" t="n">
         <v>1929655</v>
@@ -5183,7 +5183,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G166" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H166" t="n">
         <v>2357597</v>
@@ -5241,7 +5241,7 @@
         <v>10.442400932312</v>
       </c>
       <c r="G168" t="n">
-        <v>9.25900077819824</v>
+        <v>9.25899982452393</v>
       </c>
       <c r="H168" t="n">
         <v>1567170</v>
@@ -5386,7 +5386,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H173" t="n">
         <v>2380805</v>
@@ -5502,7 +5502,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G177" t="n">
-        <v>9.23451900482178</v>
+        <v>9.23451805114746</v>
       </c>
       <c r="H177" t="n">
         <v>2950107</v>
@@ -5531,7 +5531,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G178" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H178" t="n">
         <v>1678053</v>
@@ -5647,7 +5647,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G182" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H182" t="n">
         <v>2932072</v>
@@ -5676,7 +5676,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359827041626</v>
+        <v>7.94359874725342</v>
       </c>
       <c r="H183" t="n">
         <v>4194583</v>
@@ -5734,7 +5734,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.79224967956543</v>
+        <v>7.79225063323975</v>
       </c>
       <c r="H185" t="n">
         <v>2776938</v>
@@ -5763,7 +5763,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463329315186</v>
+        <v>7.89463376998901</v>
       </c>
       <c r="H186" t="n">
         <v>1967156</v>
@@ -5966,7 +5966,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G193" t="n">
-        <v>8.38429260253906</v>
+        <v>8.38429164886475</v>
       </c>
       <c r="H193" t="n">
         <v>3268951</v>
@@ -6053,7 +6053,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G196" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H196" t="n">
         <v>2921152</v>
@@ -6111,7 +6111,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473388671875</v>
+        <v>8.66473293304443</v>
       </c>
       <c r="H198" t="n">
         <v>3635783</v>
@@ -6169,7 +6169,7 @@
         <v>10.063362121582</v>
       </c>
       <c r="G200" t="n">
-        <v>8.92291641235352</v>
+        <v>8.92291736602783</v>
       </c>
       <c r="H200" t="n">
         <v>3921088</v>
@@ -6227,7 +6227,7 @@
         <v>10.1662797927856</v>
       </c>
       <c r="G202" t="n">
-        <v>9.01417064666748</v>
+        <v>9.0141716003418</v>
       </c>
       <c r="H202" t="n">
         <v>2012851</v>
@@ -6256,7 +6256,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H203" t="n">
         <v>2739605</v>
@@ -6285,7 +6285,7 @@
         <v>10.3696060180664</v>
       </c>
       <c r="G204" t="n">
-        <v>9.19445514678955</v>
+        <v>9.19445610046387</v>
       </c>
       <c r="H204" t="n">
         <v>2291727</v>
@@ -6372,7 +6372,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856430053711</v>
+        <v>9.68856525421143</v>
       </c>
       <c r="H207" t="n">
         <v>3565425</v>
@@ -6401,7 +6401,7 @@
         <v>10.9519701004028</v>
       </c>
       <c r="G208" t="n">
-        <v>9.71082305908203</v>
+        <v>9.71082210540771</v>
       </c>
       <c r="H208" t="n">
         <v>3749471</v>
@@ -6459,7 +6459,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G210" t="n">
-        <v>9.31464385986328</v>
+        <v>9.31464290618896</v>
       </c>
       <c r="H210" t="n">
         <v>2902413</v>
@@ -6488,7 +6488,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H211" t="n">
         <v>10102433</v>
@@ -6633,7 +6633,7 @@
         <v>9.22244834899902</v>
       </c>
       <c r="G216" t="n">
-        <v>8.17730045318604</v>
+        <v>8.17730140686035</v>
       </c>
       <c r="H216" t="n">
         <v>3009845</v>
@@ -6720,7 +6720,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G219" t="n">
-        <v>8.38429260253906</v>
+        <v>8.38429164886475</v>
       </c>
       <c r="H219" t="n">
         <v>2139887</v>
@@ -6865,7 +6865,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H224" t="n">
         <v>2930403</v>
@@ -6923,7 +6923,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072341918945</v>
+        <v>8.94072246551514</v>
       </c>
       <c r="H226" t="n">
         <v>2515113</v>
@@ -6981,7 +6981,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G228" t="n">
-        <v>8.6736364364624</v>
+        <v>8.67363548278809</v>
       </c>
       <c r="H228" t="n">
         <v>3095637</v>
@@ -7039,7 +7039,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G230" t="n">
-        <v>8.94517421722412</v>
+        <v>8.9451732635498</v>
       </c>
       <c r="H230" t="n">
         <v>2705648</v>
@@ -7155,7 +7155,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G234" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H234" t="n">
         <v>2193109</v>
@@ -7213,7 +7213,7 @@
         <v>10.6457271575928</v>
       </c>
       <c r="G236" t="n">
-        <v>9.43928527832031</v>
+        <v>9.439284324646</v>
       </c>
       <c r="H236" t="n">
         <v>6766822</v>
@@ -7242,7 +7242,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640323638916</v>
+        <v>9.72640228271484</v>
       </c>
       <c r="H237" t="n">
         <v>6656648</v>
@@ -7329,7 +7329,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1826753616333</v>
+        <v>10.182674407959</v>
       </c>
       <c r="H240" t="n">
         <v>4126096</v>
@@ -7474,7 +7474,7 @@
         <v>11.8230066299438</v>
       </c>
       <c r="G245" t="n">
-        <v>10.4831466674805</v>
+        <v>10.4831476211548</v>
       </c>
       <c r="H245" t="n">
         <v>7748349</v>
@@ -7532,7 +7532,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788545608521</v>
+        <v>10.5788536071777</v>
       </c>
       <c r="H247" t="n">
         <v>3112020</v>
@@ -7648,7 +7648,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G251" t="n">
-        <v>10.9883861541748</v>
+        <v>10.9883871078491</v>
       </c>
       <c r="H251" t="n">
         <v>3493539</v>
@@ -7677,7 +7677,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G252" t="n">
-        <v>11.2844076156616</v>
+        <v>11.2844085693359</v>
       </c>
       <c r="H252" t="n">
         <v>3211844</v>
@@ -7735,7 +7735,7 @@
         <v>13.0906553268433</v>
       </c>
       <c r="G254" t="n">
-        <v>11.607138633728</v>
+        <v>11.6071376800537</v>
       </c>
       <c r="H254" t="n">
         <v>1718855</v>
@@ -7764,7 +7764,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295522689819</v>
+        <v>11.7295513153076</v>
       </c>
       <c r="H255" t="n">
         <v>2571001</v>
@@ -7938,7 +7938,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195251464844</v>
+        <v>12.4195261001587</v>
       </c>
       <c r="H261" t="n">
         <v>2771934</v>
@@ -7967,7 +7967,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858253479004</v>
+        <v>12.1858243942261</v>
       </c>
       <c r="H262" t="n">
         <v>2214682</v>
@@ -8112,7 +8112,7 @@
         <v>12.8647365570068</v>
       </c>
       <c r="G267" t="n">
-        <v>11.4068222045898</v>
+        <v>11.4068212509155</v>
       </c>
       <c r="H267" t="n">
         <v>2415292</v>
@@ -8199,7 +8199,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G270" t="n">
-        <v>11.2844076156616</v>
+        <v>11.2844085693359</v>
       </c>
       <c r="H270" t="n">
         <v>3414444</v>
@@ -8228,7 +8228,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619930267334</v>
+        <v>11.1619939804077</v>
       </c>
       <c r="H271" t="n">
         <v>2083536</v>
@@ -8286,7 +8286,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351266860962</v>
+        <v>11.0351257324219</v>
       </c>
       <c r="H273" t="n">
         <v>2426178</v>
@@ -8344,7 +8344,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963237762451</v>
+        <v>11.7963228225708</v>
       </c>
       <c r="H275" t="n">
         <v>5968291</v>
@@ -8489,7 +8489,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G280" t="n">
-        <v>10.5276613235474</v>
+        <v>10.5276622772217</v>
       </c>
       <c r="H280" t="n">
         <v>3406649</v>
@@ -8518,7 +8518,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G281" t="n">
-        <v>10.2383184432983</v>
+        <v>10.2383193969727</v>
       </c>
       <c r="H281" t="n">
         <v>3878344</v>
@@ -8576,7 +8576,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.2516717910767</v>
+        <v>10.251672744751</v>
       </c>
       <c r="H283" t="n">
         <v>3104757</v>
@@ -8750,7 +8750,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651847839355</v>
+        <v>10.3651838302612</v>
       </c>
       <c r="H289" t="n">
         <v>3308303</v>
@@ -9127,7 +9127,7 @@
         <v>10.6984405517578</v>
       </c>
       <c r="G302" t="n">
-        <v>9.48602390289307</v>
+        <v>9.48602485656738</v>
       </c>
       <c r="H302" t="n">
         <v>2707699</v>
@@ -9185,7 +9185,7 @@
         <v>10.4675025939941</v>
       </c>
       <c r="G304" t="n">
-        <v>9.28125762939453</v>
+        <v>9.28125858306885</v>
       </c>
       <c r="H304" t="n">
         <v>3507793</v>
@@ -9330,7 +9330,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520709991455</v>
+        <v>8.96520614624023</v>
       </c>
       <c r="H309" t="n">
         <v>3858069</v>
@@ -9359,7 +9359,7 @@
         <v>10.218994140625</v>
       </c>
       <c r="G310" t="n">
-        <v>9.06091213226318</v>
+        <v>9.06091117858887</v>
       </c>
       <c r="H310" t="n">
         <v>3308377</v>
@@ -9475,7 +9475,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539485931396</v>
+        <v>9.08539390563965</v>
       </c>
       <c r="H314" t="n">
         <v>3039918</v>
@@ -9504,7 +9504,7 @@
         <v>10.1336479187012</v>
       </c>
       <c r="G315" t="n">
-        <v>8.98523712158203</v>
+        <v>8.98523807525635</v>
       </c>
       <c r="H315" t="n">
         <v>3230495</v>
@@ -9649,7 +9649,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G320" t="n">
-        <v>9.4615421295166</v>
+        <v>9.46154117584229</v>
       </c>
       <c r="H320" t="n">
         <v>4855845</v>
@@ -9765,7 +9765,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G324" t="n">
-        <v>9.49047565460205</v>
+        <v>9.49047470092773</v>
       </c>
       <c r="H324" t="n">
         <v>4124738</v>
@@ -9881,7 +9881,7 @@
         <v>10.5227270126343</v>
       </c>
       <c r="G328" t="n">
-        <v>9.33022403717041</v>
+        <v>9.33022308349609</v>
       </c>
       <c r="H328" t="n">
         <v>2488647</v>
@@ -9939,7 +9939,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G330" t="n">
-        <v>9.12990856170654</v>
+        <v>9.12990951538086</v>
       </c>
       <c r="H330" t="n">
         <v>3092166</v>
@@ -10171,7 +10171,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.2033576965332</v>
+        <v>9.20335865020752</v>
       </c>
       <c r="H338" t="n">
         <v>3676909</v>
@@ -10287,7 +10287,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837268829346</v>
+        <v>8.85837173461914</v>
       </c>
       <c r="H342" t="n">
         <v>3153124</v>
@@ -10316,7 +10316,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H343" t="n">
         <v>4027196</v>
@@ -10403,7 +10403,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G346" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H346" t="n">
         <v>3221801</v>
@@ -10490,7 +10490,7 @@
         <v>10.003116607666</v>
       </c>
       <c r="G349" t="n">
-        <v>8.86949825286865</v>
+        <v>8.86949920654297</v>
       </c>
       <c r="H349" t="n">
         <v>2547965</v>
@@ -10606,7 +10606,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G353" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H353" t="n">
         <v>3851850</v>
@@ -10722,7 +10722,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G357" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H357" t="n">
         <v>2035124</v>
@@ -10867,7 +10867,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G362" t="n">
-        <v>8.03485488891602</v>
+        <v>8.0348539352417</v>
       </c>
       <c r="H362" t="n">
         <v>6065761</v>
@@ -10896,7 +10896,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.9903392791748</v>
+        <v>7.99033975601196</v>
       </c>
       <c r="H363" t="n">
         <v>4201110</v>
@@ -10983,7 +10983,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G366" t="n">
-        <v>7.66093397140503</v>
+        <v>7.66093349456787</v>
       </c>
       <c r="H366" t="n">
         <v>3865901</v>
@@ -11012,7 +11012,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215627670288</v>
+        <v>7.73215579986572</v>
       </c>
       <c r="H367" t="n">
         <v>4573774</v>
@@ -11041,7 +11041,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H368" t="n">
         <v>4145288</v>
@@ -11157,7 +11157,7 @@
         <v>8.88106060028076</v>
       </c>
       <c r="G372" t="n">
-        <v>7.87460136413574</v>
+        <v>7.8746018409729</v>
       </c>
       <c r="H372" t="n">
         <v>3226298</v>
@@ -11186,7 +11186,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H373" t="n">
         <v>5046714</v>
@@ -11302,7 +11302,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133661270142</v>
+        <v>7.21133708953857</v>
       </c>
       <c r="H377" t="n">
         <v>3761237</v>
@@ -11476,7 +11476,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804521560669</v>
+        <v>7.23804569244385</v>
       </c>
       <c r="H383" t="n">
         <v>2583014</v>
@@ -11534,7 +11534,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055511474609</v>
+        <v>7.42055463790894</v>
       </c>
       <c r="H385" t="n">
         <v>3239198</v>
@@ -11563,7 +11563,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.69654512405396</v>
+        <v>7.6965446472168</v>
       </c>
       <c r="H386" t="n">
         <v>4250748</v>
@@ -11592,7 +11592,7 @@
         <v>8.44428825378418</v>
       </c>
       <c r="G387" t="n">
-        <v>7.48732709884644</v>
+        <v>7.48732662200928</v>
       </c>
       <c r="H387" t="n">
         <v>4117666</v>
@@ -11737,7 +11737,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H392" t="n">
         <v>4462543</v>
@@ -11766,7 +11766,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G393" t="n">
-        <v>7.74551010131836</v>
+        <v>7.7455096244812</v>
       </c>
       <c r="H393" t="n">
         <v>2051870</v>
@@ -11824,7 +11824,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.8567967414856</v>
+        <v>7.85679721832275</v>
       </c>
       <c r="H395" t="n">
         <v>2325966</v>
@@ -11853,7 +11853,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H396" t="n">
         <v>3714587</v>
@@ -11882,7 +11882,7 @@
         <v>8.52461433410645</v>
       </c>
       <c r="G397" t="n">
-        <v>7.5585503578186</v>
+        <v>7.55854988098145</v>
       </c>
       <c r="H397" t="n">
         <v>2332643</v>
@@ -11911,7 +11911,7 @@
         <v>8.514573097229</v>
       </c>
       <c r="G398" t="n">
-        <v>7.54964685440063</v>
+        <v>7.54964637756348</v>
       </c>
       <c r="H398" t="n">
         <v>1501586</v>
@@ -11940,7 +11940,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842359542847</v>
+        <v>7.47842311859131</v>
       </c>
       <c r="H399" t="n">
         <v>1479093</v>
@@ -11969,7 +11969,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196708679199</v>
+        <v>7.61196756362915</v>
       </c>
       <c r="H400" t="n">
         <v>2662388</v>
@@ -12085,7 +12085,7 @@
         <v>8.6953067779541</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70989894866943</v>
+        <v>7.70989847183228</v>
       </c>
       <c r="H404" t="n">
         <v>2592503</v>
@@ -12143,7 +12143,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H406" t="n">
         <v>2779239</v>
@@ -12172,7 +12172,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757919311523</v>
+        <v>7.64757966995239</v>
       </c>
       <c r="H407" t="n">
         <v>1870136</v>
@@ -12201,7 +12201,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G408" t="n">
-        <v>7.5852575302124</v>
+        <v>7.58525800704956</v>
       </c>
       <c r="H408" t="n">
         <v>2173007</v>
@@ -12288,7 +12288,7 @@
         <v>8.5748176574707</v>
       </c>
       <c r="G411" t="n">
-        <v>7.60306453704834</v>
+        <v>7.60306406021118</v>
       </c>
       <c r="H411" t="n">
         <v>1663436</v>
@@ -12520,7 +12520,7 @@
         <v>8.08281993865967</v>
       </c>
       <c r="G419" t="n">
-        <v>7.16682243347168</v>
+        <v>7.16682195663452</v>
       </c>
       <c r="H419" t="n">
         <v>1874275</v>
@@ -12578,7 +12578,7 @@
         <v>7.84184217453003</v>
       </c>
       <c r="G421" t="n">
-        <v>6.95315408706665</v>
+        <v>6.95315361022949</v>
       </c>
       <c r="H421" t="n">
         <v>2449535</v>
@@ -12636,7 +12636,7 @@
         <v>7.70127105712891</v>
       </c>
       <c r="G423" t="n">
-        <v>6.82851314544678</v>
+        <v>6.82851362228394</v>
       </c>
       <c r="H423" t="n">
         <v>3972357</v>
@@ -12810,7 +12810,7 @@
         <v>7.76151514053345</v>
       </c>
       <c r="G429" t="n">
-        <v>6.88193035125732</v>
+        <v>6.88192987442017</v>
       </c>
       <c r="H429" t="n">
         <v>1920708</v>
@@ -12926,7 +12926,7 @@
         <v>7.96233081817627</v>
       </c>
       <c r="G433" t="n">
-        <v>7.05998802185059</v>
+        <v>7.05998849868774</v>
       </c>
       <c r="H433" t="n">
         <v>2066064</v>
@@ -12955,7 +12955,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591369628906</v>
+        <v>7.29591417312622</v>
       </c>
       <c r="H434" t="n">
         <v>3040311</v>
@@ -13071,7 +13071,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.47397232055664</v>
+        <v>7.4739727973938</v>
       </c>
       <c r="H438" t="n">
         <v>2774137</v>
@@ -13100,7 +13100,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G439" t="n">
-        <v>7.5852575302124</v>
+        <v>7.58525800704956</v>
       </c>
       <c r="H439" t="n">
         <v>2999352</v>
@@ -13129,7 +13129,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H440" t="n">
         <v>3440039</v>
@@ -13216,7 +13216,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H443" t="n">
         <v>2311936</v>
@@ -13245,7 +13245,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491683959961</v>
+        <v>8.07491779327393</v>
       </c>
       <c r="H444" t="n">
         <v>9651321</v>
@@ -13274,7 +13274,7 @@
         <v>9.10195827484131</v>
       </c>
       <c r="G445" t="n">
-        <v>8.07046508789062</v>
+        <v>8.07046604156494</v>
       </c>
       <c r="H445" t="n">
         <v>8925850</v>
@@ -13448,7 +13448,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692302703857</v>
+        <v>7.93692350387573</v>
       </c>
       <c r="H451" t="n">
         <v>4589432</v>
@@ -13796,7 +13796,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.42945766448975</v>
+        <v>7.42945718765259</v>
       </c>
       <c r="H463" t="n">
         <v>3847044</v>
@@ -13825,7 +13825,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804521560669</v>
+        <v>7.23804569244385</v>
       </c>
       <c r="H464" t="n">
         <v>4793014</v>
@@ -13883,7 +13883,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H466" t="n">
         <v>9145143</v>
@@ -13970,7 +13970,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479103088379</v>
+        <v>7.99479198455811</v>
       </c>
       <c r="H469" t="n">
         <v>8252776</v>
@@ -14057,7 +14057,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.5467700958252</v>
+        <v>8.54677104949951</v>
       </c>
       <c r="H472" t="n">
         <v>5904097</v>
@@ -14115,7 +14115,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H474" t="n">
         <v>5603952</v>
@@ -14144,7 +14144,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H475" t="n">
         <v>5013333</v>
@@ -14173,7 +14173,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H476" t="n">
         <v>3307360</v>
@@ -14289,7 +14289,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G480" t="n">
-        <v>7.78557348251343</v>
+        <v>7.78557395935059</v>
       </c>
       <c r="H480" t="n">
         <v>11572956</v>
@@ -14318,7 +14318,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757919311523</v>
+        <v>7.64757966995239</v>
       </c>
       <c r="H481" t="n">
         <v>6391732</v>
@@ -14347,7 +14347,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G482" t="n">
-        <v>7.62532186508179</v>
+        <v>7.62532234191895</v>
       </c>
       <c r="H482" t="n">
         <v>3509049</v>
@@ -14376,7 +14376,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G483" t="n">
-        <v>7.62532186508179</v>
+        <v>7.62532234191895</v>
       </c>
       <c r="H483" t="n">
         <v>4716149</v>
@@ -14405,7 +14405,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H484" t="n">
         <v>3256857</v>
@@ -14463,7 +14463,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576314926147</v>
+        <v>7.90576267242432</v>
       </c>
       <c r="H486" t="n">
         <v>2564414</v>
@@ -14579,7 +14579,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H490" t="n">
         <v>2757855</v>
@@ -14608,7 +14608,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G491" t="n">
-        <v>7.74551010131836</v>
+        <v>7.7455096244812</v>
       </c>
       <c r="H491" t="n">
         <v>3546514</v>
@@ -14695,7 +14695,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H494" t="n">
         <v>4714362</v>
@@ -14724,7 +14724,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H495" t="n">
         <v>2456311</v>
@@ -14840,7 +14840,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63422441482544</v>
+        <v>7.6342248916626</v>
       </c>
       <c r="H499" t="n">
         <v>4090789</v>
@@ -14898,7 +14898,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H501" t="n">
         <v>2766406</v>
@@ -15072,7 +15072,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G507" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H507" t="n">
         <v>4480449</v>
@@ -15101,7 +15101,7 @@
         <v>9.34795665740967</v>
       </c>
       <c r="G508" t="n">
-        <v>8.28858661651611</v>
+        <v>8.2885856628418</v>
       </c>
       <c r="H508" t="n">
         <v>3999486</v>
@@ -15188,7 +15188,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109603881836</v>
+        <v>8.47109508514404</v>
       </c>
       <c r="H511" t="n">
         <v>3770392</v>
@@ -15217,7 +15217,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670719146729</v>
+        <v>8.50670623779297</v>
       </c>
       <c r="H512" t="n">
         <v>2875008</v>
@@ -15304,7 +15304,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H515" t="n">
         <v>3023534</v>
@@ -15362,7 +15362,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H517" t="n">
         <v>4311139</v>
@@ -15507,7 +15507,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G522" t="n">
-        <v>9.12990856170654</v>
+        <v>9.12990951538086</v>
       </c>
       <c r="H522" t="n">
         <v>5817803</v>
@@ -15536,7 +15536,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H523" t="n">
         <v>4786463</v>
@@ -15652,7 +15652,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G527" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H527" t="n">
         <v>5274403</v>
@@ -15710,7 +15710,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G529" t="n">
-        <v>9.04088020324707</v>
+        <v>9.04087924957275</v>
       </c>
       <c r="H529" t="n">
         <v>2663725</v>
@@ -15739,7 +15739,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G530" t="n">
-        <v>9.04088020324707</v>
+        <v>9.04087924957275</v>
       </c>
       <c r="H530" t="n">
         <v>2198884</v>
@@ -15855,7 +15855,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.4199047088623</v>
+        <v>8.41990375518799</v>
       </c>
       <c r="H534" t="n">
         <v>2981971</v>
@@ -15884,7 +15884,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.2485237121582</v>
+        <v>8.24852466583252</v>
       </c>
       <c r="H535" t="n">
         <v>4093310</v>
@@ -15971,7 +15971,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G538" t="n">
-        <v>8.03485488891602</v>
+        <v>8.0348539352417</v>
       </c>
       <c r="H538" t="n">
         <v>4649230</v>
@@ -16029,7 +16029,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196708679199</v>
+        <v>7.61196756362915</v>
       </c>
       <c r="H540" t="n">
         <v>7866114</v>
@@ -16058,7 +16058,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519557952881</v>
+        <v>7.54519510269165</v>
       </c>
       <c r="H541" t="n">
         <v>2933056</v>
@@ -16116,7 +16116,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49622964859009</v>
+        <v>7.49623012542725</v>
       </c>
       <c r="H543" t="n">
         <v>5612249</v>
@@ -16174,7 +16174,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G545" t="n">
-        <v>7.66093397140503</v>
+        <v>7.66093349456787</v>
       </c>
       <c r="H545" t="n">
         <v>2737321</v>
@@ -16232,7 +16232,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H547" t="n">
         <v>2390591</v>
@@ -16261,7 +16261,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083913803101</v>
+        <v>7.60083866119385</v>
       </c>
       <c r="H548" t="n">
         <v>2684043</v>
@@ -16319,7 +16319,7 @@
         <v>8.83587837219238</v>
       </c>
       <c r="G550" t="n">
-        <v>7.83453989028931</v>
+        <v>7.83453893661499</v>
       </c>
       <c r="H550" t="n">
         <v>5628339</v>
@@ -16348,7 +16348,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.76331615447998</v>
+        <v>7.76331663131714</v>
       </c>
       <c r="H551" t="n">
         <v>3521552</v>
@@ -16377,7 +16377,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H552" t="n">
         <v>3398436</v>
@@ -16406,7 +16406,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G553" t="n">
-        <v>7.50068092346191</v>
+        <v>7.50068044662476</v>
       </c>
       <c r="H553" t="n">
         <v>4181215</v>
@@ -16435,7 +16435,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.52293825149536</v>
+        <v>7.5229377746582</v>
       </c>
       <c r="H554" t="n">
         <v>2585190</v>
@@ -16522,7 +16522,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G557" t="n">
-        <v>7.50068092346191</v>
+        <v>7.50068044662476</v>
       </c>
       <c r="H557" t="n">
         <v>7379464</v>
@@ -16580,7 +16580,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663900375366</v>
+        <v>7.75663948059082</v>
       </c>
       <c r="H559" t="n">
         <v>3729295</v>
@@ -16725,7 +16725,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936378479004</v>
+        <v>7.36936330795288</v>
       </c>
       <c r="H564" t="n">
         <v>2801339</v>
@@ -16783,7 +16783,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585079193115</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H566" t="n">
         <v>4081106</v>
@@ -16841,7 +16841,7 @@
         <v>8.43173694610596</v>
       </c>
       <c r="G568" t="n">
-        <v>7.47619771957397</v>
+        <v>7.47619819641113</v>
       </c>
       <c r="H568" t="n">
         <v>3125867</v>
@@ -17160,7 +17160,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744714736938</v>
+        <v>6.85744762420654</v>
       </c>
       <c r="H579" t="n">
         <v>4059831</v>
@@ -17305,7 +17305,7 @@
         <v>8.1079216003418</v>
       </c>
       <c r="G584" t="n">
-        <v>7.18907976150513</v>
+        <v>7.18907928466797</v>
       </c>
       <c r="H584" t="n">
         <v>3472564</v>
@@ -17363,7 +17363,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G586" t="n">
-        <v>7.4806489944458</v>
+        <v>7.48064947128296</v>
       </c>
       <c r="H586" t="n">
         <v>7983682</v>
@@ -17392,7 +17392,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842359542847</v>
+        <v>7.47842311859131</v>
       </c>
       <c r="H587" t="n">
         <v>5249327</v>
@@ -17421,7 +17421,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610383987427</v>
+        <v>7.41610431671143</v>
       </c>
       <c r="H588" t="n">
         <v>4009682</v>
@@ -17450,7 +17450,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G589" t="n">
-        <v>7.4806489944458</v>
+        <v>7.48064947128296</v>
       </c>
       <c r="H589" t="n">
         <v>4006210</v>
@@ -17595,7 +17595,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443881988525</v>
+        <v>7.06443929672241</v>
       </c>
       <c r="H594" t="n">
         <v>3740621</v>
@@ -17740,7 +17740,7 @@
         <v>8.06022834777832</v>
       </c>
       <c r="G599" t="n">
-        <v>7.14679098129272</v>
+        <v>7.14679145812988</v>
       </c>
       <c r="H599" t="n">
         <v>10681822</v>
@@ -17769,7 +17769,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G600" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H600" t="n">
         <v>11169423</v>
@@ -17827,7 +17827,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G602" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H602" t="n">
         <v>3638485</v>
@@ -17856,7 +17856,7 @@
         <v>8.55222606658936</v>
       </c>
       <c r="G603" t="n">
-        <v>7.58303213119507</v>
+        <v>7.58303260803223</v>
       </c>
       <c r="H603" t="n">
         <v>3271522</v>
@@ -18001,7 +18001,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G608" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H608" t="n">
         <v>4747845</v>
@@ -18088,7 +18088,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37539005279541</v>
+        <v>8.37538909912109</v>
       </c>
       <c r="H611" t="n">
         <v>5678009</v>
@@ -18146,7 +18146,7 @@
         <v>8.79822540283203</v>
       </c>
       <c r="G613" t="n">
-        <v>7.80115365982056</v>
+        <v>7.80115413665771</v>
       </c>
       <c r="H613" t="n">
         <v>4731371</v>
@@ -18262,7 +18262,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H617" t="n">
         <v>5676159</v>
@@ -18378,7 +18378,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H621" t="n">
         <v>4359962</v>
@@ -18407,7 +18407,7 @@
         <v>9.72448635101318</v>
       </c>
       <c r="G622" t="n">
-        <v>8.62244510650635</v>
+        <v>8.62244415283203</v>
       </c>
       <c r="H622" t="n">
         <v>5253374</v>
@@ -18465,7 +18465,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902694702148</v>
+        <v>8.56902599334717</v>
       </c>
       <c r="H624" t="n">
         <v>3124054</v>
@@ -18639,7 +18639,7 @@
         <v>9.36552906036377</v>
       </c>
       <c r="G630" t="n">
-        <v>8.30416774749756</v>
+        <v>8.30416679382324</v>
       </c>
       <c r="H630" t="n">
         <v>2245651</v>
@@ -18813,7 +18813,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G636" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H636" t="n">
         <v>6312564</v>
@@ -18871,7 +18871,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H638" t="n">
         <v>2970699</v>
@@ -18929,7 +18929,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G640" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H640" t="n">
         <v>1067132</v>
@@ -18958,7 +18958,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.71147346496582</v>
+        <v>8.71147441864014</v>
       </c>
       <c r="H641" t="n">
         <v>2154097</v>
@@ -19045,7 +19045,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G644" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H644" t="n">
         <v>5210482</v>
@@ -19161,7 +19161,7 @@
         <v>10.0181789398193</v>
       </c>
       <c r="G648" t="n">
-        <v>8.88285446166992</v>
+        <v>8.88285350799561</v>
       </c>
       <c r="H648" t="n">
         <v>3244003</v>
@@ -19248,7 +19248,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G651" t="n">
-        <v>9.05646133422852</v>
+        <v>9.0564603805542</v>
       </c>
       <c r="H651" t="n">
         <v>1641266</v>
@@ -19335,7 +19335,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G654" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H654" t="n">
         <v>2782854</v>
@@ -19422,7 +19422,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H657" t="n">
         <v>3819447</v>
@@ -19567,7 +19567,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686973571777</v>
+        <v>9.31686878204346</v>
       </c>
       <c r="H662" t="n">
         <v>5059956</v>
@@ -19625,7 +19625,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317378997803</v>
+        <v>9.79317283630371</v>
       </c>
       <c r="H664" t="n">
         <v>4580403</v>
@@ -19770,7 +19770,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139934539795</v>
+        <v>10.3139925003052</v>
       </c>
       <c r="H669" t="n">
         <v>8750009</v>
@@ -19828,7 +19828,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G671" t="n">
-        <v>9.80652904510498</v>
+        <v>9.80652809143066</v>
       </c>
       <c r="H671" t="n">
         <v>2692978</v>
@@ -19973,7 +19973,7 @@
         <v>11.6046199798584</v>
       </c>
       <c r="G676" t="n">
-        <v>10.2895097732544</v>
+        <v>10.2895088195801</v>
       </c>
       <c r="H676" t="n">
         <v>1818429</v>
@@ -20205,7 +20205,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G684" t="n">
-        <v>10.334023475647</v>
+        <v>10.3340244293213</v>
       </c>
       <c r="H684" t="n">
         <v>4874391</v>
@@ -20321,7 +20321,7 @@
         <v>11.5017032623291</v>
       </c>
       <c r="G688" t="n">
-        <v>10.1982564926147</v>
+        <v>10.1982555389404</v>
       </c>
       <c r="H688" t="n">
         <v>1979022</v>
@@ -20379,7 +20379,7 @@
         <v>11.328498840332</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0446796417236</v>
+        <v>10.0446805953979</v>
       </c>
       <c r="H690" t="n">
         <v>5499203</v>
@@ -20408,7 +20408,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.3941192626953</v>
+        <v>10.394118309021</v>
       </c>
       <c r="H691" t="n">
         <v>4155413</v>
@@ -20437,7 +20437,7 @@
         <v>12.0489253997803</v>
       </c>
       <c r="G692" t="n">
-        <v>10.683464050293</v>
+        <v>10.6834630966187</v>
       </c>
       <c r="H692" t="n">
         <v>2537540</v>
@@ -20466,7 +20466,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G693" t="n">
-        <v>10.8259077072144</v>
+        <v>10.8259086608887</v>
       </c>
       <c r="H693" t="n">
         <v>4672055</v>
@@ -20582,7 +20582,7 @@
         <v>12.4580860137939</v>
       </c>
       <c r="G697" t="n">
-        <v>11.0462551116943</v>
+        <v>11.0462560653687</v>
       </c>
       <c r="H697" t="n">
         <v>11143856</v>
@@ -20814,7 +20814,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856685638428</v>
+        <v>12.0856676101685</v>
       </c>
       <c r="H705" t="n">
         <v>4491851</v>
@@ -20930,7 +20930,7 @@
         <v>12.7618188858032</v>
       </c>
       <c r="G709" t="n">
-        <v>11.3155679702759</v>
+        <v>11.3155670166016</v>
       </c>
       <c r="H709" t="n">
         <v>4616138</v>
@@ -21046,7 +21046,7 @@
         <v>12.7015752792358</v>
       </c>
       <c r="G713" t="n">
-        <v>11.2621507644653</v>
+        <v>11.262149810791</v>
       </c>
       <c r="H713" t="n">
         <v>2952425</v>
@@ -21075,7 +21075,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349699020386</v>
+        <v>10.9349689483643</v>
       </c>
       <c r="H714" t="n">
         <v>2894320</v>
@@ -21104,7 +21104,7 @@
         <v>11.8004150390625</v>
       </c>
       <c r="G715" t="n">
-        <v>10.463116645813</v>
+        <v>10.4631156921387</v>
       </c>
       <c r="H715" t="n">
         <v>3263911</v>
@@ -21220,7 +21220,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G719" t="n">
-        <v>10.5499200820923</v>
+        <v>10.549919128418</v>
       </c>
       <c r="H719" t="n">
         <v>9162422</v>
@@ -21365,7 +21365,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H724" t="n">
         <v>4731058</v>
@@ -21394,7 +21394,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.3941192626953</v>
+        <v>10.394118309021</v>
       </c>
       <c r="H725" t="n">
         <v>5437862</v>
@@ -21452,7 +21452,7 @@
         <v>11.7025184631348</v>
       </c>
       <c r="G727" t="n">
-        <v>10.376314163208</v>
+        <v>10.3763132095337</v>
       </c>
       <c r="H727" t="n">
         <v>2777725</v>
@@ -21481,7 +21481,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H728" t="n">
         <v>6325209</v>
@@ -21510,7 +21510,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006381988525</v>
+        <v>10.3006391525269</v>
       </c>
       <c r="H729" t="n">
         <v>3047850</v>
@@ -21684,7 +21684,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580516815186</v>
+        <v>9.34580421447754</v>
       </c>
       <c r="H735" t="n">
         <v>2646670</v>
@@ -21713,7 +21713,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G736" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H736" t="n">
         <v>2599002</v>
@@ -21742,7 +21742,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G737" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H737" t="n">
         <v>3254391</v>
@@ -21858,7 +21858,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889537811279</v>
+        <v>7.77889585494995</v>
       </c>
       <c r="H741" t="n">
         <v>8894223</v>
@@ -21945,7 +21945,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H744" t="n">
         <v>2830649</v>
@@ -21974,7 +21974,7 @@
         <v>9.65922069549561</v>
       </c>
       <c r="G745" t="n">
-        <v>8.56457614898682</v>
+        <v>8.5645751953125</v>
       </c>
       <c r="H745" t="n">
         <v>3590690</v>
@@ -22090,7 +22090,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G749" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H749" t="n">
         <v>3226454</v>
@@ -22119,7 +22119,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G750" t="n">
-        <v>8.1884298324585</v>
+        <v>8.18842887878418</v>
       </c>
       <c r="H750" t="n">
         <v>5632615</v>
@@ -22177,7 +22177,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G752" t="n">
-        <v>8.25519943237305</v>
+        <v>8.25520038604736</v>
       </c>
       <c r="H752" t="n">
         <v>4141957</v>
@@ -22206,7 +22206,7 @@
         <v>9.33540630340576</v>
       </c>
       <c r="G753" t="n">
-        <v>8.27745723724365</v>
+        <v>8.27745819091797</v>
       </c>
       <c r="H753" t="n">
         <v>2716829</v>
@@ -22235,7 +22235,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G754" t="n">
-        <v>8.29526424407959</v>
+        <v>8.29526329040527</v>
       </c>
       <c r="H754" t="n">
         <v>2607977</v>
@@ -22264,7 +22264,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466569900513</v>
+        <v>7.91466617584229</v>
       </c>
       <c r="H755" t="n">
         <v>4636928</v>
@@ -22293,7 +22293,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.81228256225586</v>
+        <v>7.81228160858154</v>
       </c>
       <c r="H756" t="n">
         <v>3199541</v>
@@ -22409,7 +22409,7 @@
         <v>8.17318725585938</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24694919586182</v>
+        <v>7.24694871902466</v>
       </c>
       <c r="H760" t="n">
         <v>5578537</v>
@@ -22583,7 +22583,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576314926147</v>
+        <v>7.90576267242432</v>
       </c>
       <c r="H766" t="n">
         <v>6705143</v>
@@ -22612,7 +22612,7 @@
         <v>9.12957000732422</v>
       </c>
       <c r="G767" t="n">
-        <v>8.09494876861572</v>
+        <v>8.09494781494141</v>
       </c>
       <c r="H767" t="n">
         <v>5185119</v>
@@ -22757,7 +22757,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G772" t="n">
-        <v>8.25519943237305</v>
+        <v>8.25520038604736</v>
       </c>
       <c r="H772" t="n">
         <v>3230113</v>
@@ -22786,7 +22786,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096927642822</v>
+        <v>8.39096832275391</v>
       </c>
       <c r="H773" t="n">
         <v>2691134</v>
@@ -22931,7 +22931,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G778" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H778" t="n">
         <v>3928570</v>
@@ -22960,7 +22960,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G779" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H779" t="n">
         <v>5108708</v>
@@ -23018,7 +23018,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G781" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H781" t="n">
         <v>3452225</v>
@@ -23076,7 +23076,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G783" t="n">
-        <v>8.94517421722412</v>
+        <v>8.9451732635498</v>
       </c>
       <c r="H783" t="n">
         <v>2493851</v>
@@ -23163,7 +23163,7 @@
         <v>10.2817487716675</v>
       </c>
       <c r="G786" t="n">
-        <v>9.11655426025391</v>
+        <v>9.11655521392822</v>
       </c>
       <c r="H786" t="n">
         <v>3216304</v>
@@ -23192,7 +23192,7 @@
         <v>10.3445043563843</v>
       </c>
       <c r="G787" t="n">
-        <v>9.17219924926758</v>
+        <v>9.17219829559326</v>
       </c>
       <c r="H787" t="n">
         <v>3191829</v>
@@ -23221,7 +23221,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G788" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H788" t="n">
         <v>2462687</v>
@@ -23337,7 +23337,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G792" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H792" t="n">
         <v>1988992</v>
@@ -23453,7 +23453,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G796" t="n">
-        <v>9.43705940246582</v>
+        <v>9.4370584487915</v>
       </c>
       <c r="H796" t="n">
         <v>5910919</v>
@@ -23482,7 +23482,7 @@
         <v>10.7963380813599</v>
       </c>
       <c r="G797" t="n">
-        <v>9.57282638549805</v>
+        <v>9.57282733917236</v>
       </c>
       <c r="H797" t="n">
         <v>2938128</v>
@@ -23540,7 +23540,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H799" t="n">
         <v>2749374</v>
@@ -23685,7 +23685,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746875762939</v>
+        <v>9.69746780395508</v>
       </c>
       <c r="H804" t="n">
         <v>2499039</v>
@@ -23714,7 +23714,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H805" t="n">
         <v>7839193</v>
@@ -23830,7 +23830,7 @@
         <v>11.8882722854614</v>
       </c>
       <c r="G809" t="n">
-        <v>10.541015625</v>
+        <v>10.5410165786743</v>
       </c>
       <c r="H809" t="n">
         <v>4281611</v>
@@ -23917,7 +23917,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G812" t="n">
-        <v>10.5276613235474</v>
+        <v>10.5276622772217</v>
       </c>
       <c r="H812" t="n">
         <v>2784960</v>
@@ -24033,7 +24033,7 @@
         <v>12.1091690063477</v>
       </c>
       <c r="G816" t="n">
-        <v>10.7368803024292</v>
+        <v>10.7368793487549</v>
       </c>
       <c r="H816" t="n">
         <v>3221057</v>
@@ -24062,7 +24062,7 @@
         <v>12.2145967483521</v>
       </c>
       <c r="G817" t="n">
-        <v>10.8303594589233</v>
+        <v>10.8303604125977</v>
       </c>
       <c r="H817" t="n">
         <v>2672807</v>
@@ -24091,7 +24091,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371957778931</v>
+        <v>10.9371948242188</v>
       </c>
       <c r="H818" t="n">
         <v>2377360</v>
@@ -24120,7 +24120,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G819" t="n">
-        <v>10.9883861541748</v>
+        <v>10.9883871078491</v>
       </c>
       <c r="H819" t="n">
         <v>2021022</v>
@@ -24149,7 +24149,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G820" t="n">
-        <v>10.8259077072144</v>
+        <v>10.8259086608887</v>
       </c>
       <c r="H820" t="n">
         <v>2828403</v>
@@ -24207,7 +24207,7 @@
         <v>11.5368452072144</v>
       </c>
       <c r="G822" t="n">
-        <v>10.2294149398804</v>
+        <v>10.2294158935547</v>
       </c>
       <c r="H822" t="n">
         <v>4110160</v>
@@ -24294,7 +24294,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G825" t="n">
-        <v>10.334023475647</v>
+        <v>10.3340244293213</v>
       </c>
       <c r="H825" t="n">
         <v>1775286</v>
@@ -24439,7 +24439,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H830" t="n">
         <v>3008620</v>
@@ -24671,7 +24671,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271900177002</v>
+        <v>10.2271890640259</v>
       </c>
       <c r="H838" t="n">
         <v>2776794</v>
@@ -24787,7 +24787,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G842" t="n">
-        <v>10.5499200820923</v>
+        <v>10.549919128418</v>
       </c>
       <c r="H842" t="n">
         <v>2618477</v>
@@ -24874,7 +24874,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G845" t="n">
-        <v>10.2383184432983</v>
+        <v>10.2383193969727</v>
       </c>
       <c r="H845" t="n">
         <v>2752665</v>
@@ -25193,7 +25193,7 @@
         <v>10.4072589874268</v>
       </c>
       <c r="G856" t="n">
-        <v>9.2278413772583</v>
+        <v>9.22784042358398</v>
       </c>
       <c r="H856" t="n">
         <v>2374666</v>
@@ -25425,7 +25425,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G864" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H864" t="n">
         <v>1703266</v>
@@ -25512,7 +25512,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H867" t="n">
         <v>1477729</v>
@@ -25570,7 +25570,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G869" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H869" t="n">
         <v>2768616</v>
@@ -25628,7 +25628,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G871" t="n">
-        <v>9.07204055786133</v>
+        <v>9.07204151153564</v>
       </c>
       <c r="H871" t="n">
         <v>6949172</v>
@@ -25773,7 +25773,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G876" t="n">
-        <v>9.23451900482178</v>
+        <v>9.23451805114746</v>
       </c>
       <c r="H876" t="n">
         <v>3483538</v>
@@ -25860,7 +25860,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G879" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H879" t="n">
         <v>2123211</v>
@@ -25976,7 +25976,7 @@
         <v>11.0699491500854</v>
       </c>
       <c r="G883" t="n">
-        <v>9.81543159484863</v>
+        <v>9.81543064117432</v>
       </c>
       <c r="H883" t="n">
         <v>2715923</v>
@@ -26034,7 +26034,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G885" t="n">
-        <v>9.49047565460205</v>
+        <v>9.49047470092773</v>
       </c>
       <c r="H885" t="n">
         <v>1721405</v>
@@ -26092,7 +26092,7 @@
         <v>11.0498676300049</v>
       </c>
       <c r="G887" t="n">
-        <v>9.79762649536133</v>
+        <v>9.79762554168701</v>
       </c>
       <c r="H887" t="n">
         <v>1557244</v>
@@ -26121,7 +26121,7 @@
         <v>10.9820928573608</v>
       </c>
       <c r="G888" t="n">
-        <v>9.73753070831299</v>
+        <v>9.7375316619873</v>
       </c>
       <c r="H888" t="n">
         <v>1257161</v>
@@ -26150,7 +26150,7 @@
         <v>11.2431526184082</v>
       </c>
       <c r="G889" t="n">
-        <v>9.9690055847168</v>
+        <v>9.96900653839111</v>
       </c>
       <c r="H889" t="n">
         <v>2480426</v>
@@ -26179,7 +26179,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746875762939</v>
+        <v>9.69746780395508</v>
       </c>
       <c r="H890" t="n">
         <v>1851009</v>
@@ -26353,7 +26353,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H896" t="n">
         <v>5491999</v>
@@ -26411,7 +26411,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070003509521</v>
+        <v>10.1070013046265</v>
       </c>
       <c r="H898" t="n">
         <v>2738861</v>
@@ -26614,7 +26614,7 @@
         <v>11.0423374176025</v>
       </c>
       <c r="G905" t="n">
-        <v>9.79094791412354</v>
+        <v>9.79094886779785</v>
       </c>
       <c r="H905" t="n">
         <v>2518956</v>
@@ -26672,7 +26672,7 @@
         <v>11.4941720962524</v>
       </c>
       <c r="G907" t="n">
-        <v>10.1915788650513</v>
+        <v>10.191577911377</v>
       </c>
       <c r="H907" t="n">
         <v>5764525</v>
@@ -26701,7 +26701,7 @@
         <v>11.5845394134521</v>
       </c>
       <c r="G908" t="n">
-        <v>10.2717046737671</v>
+        <v>10.2717037200928</v>
       </c>
       <c r="H908" t="n">
         <v>2267960</v>
@@ -26846,7 +26846,7 @@
         <v>10.7411136627197</v>
       </c>
       <c r="G913" t="n">
-        <v>9.5238618850708</v>
+        <v>9.52386093139648</v>
       </c>
       <c r="H913" t="n">
         <v>4157164</v>
@@ -26904,7 +26904,7 @@
         <v>10.4248304367065</v>
       </c>
       <c r="G915" t="n">
-        <v>9.24342155456543</v>
+        <v>9.24342060089111</v>
       </c>
       <c r="H915" t="n">
         <v>2417247</v>
@@ -26991,7 +26991,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G918" t="n">
-        <v>9.12545776367188</v>
+        <v>9.12545871734619</v>
       </c>
       <c r="H918" t="n">
         <v>3054696</v>
@@ -27020,7 +27020,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G919" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H919" t="n">
         <v>1782514</v>
@@ -27049,7 +27049,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G920" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H920" t="n">
         <v>3210453</v>
@@ -27194,7 +27194,7 @@
         <v>10.4474220275879</v>
       </c>
       <c r="G925" t="n">
-        <v>9.26345348358154</v>
+        <v>9.26345252990723</v>
       </c>
       <c r="H925" t="n">
         <v>2715195</v>
@@ -27223,7 +27223,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G926" t="n">
-        <v>9.31464385986328</v>
+        <v>9.31464290618896</v>
       </c>
       <c r="H926" t="n">
         <v>1774533</v>
@@ -27310,7 +27310,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H929" t="n">
         <v>2564513</v>
@@ -27455,7 +27455,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G934" t="n">
-        <v>9.43705940246582</v>
+        <v>9.4370584487915</v>
       </c>
       <c r="H934" t="n">
         <v>1857397</v>
@@ -27542,7 +27542,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G937" t="n">
-        <v>9.80652904510498</v>
+        <v>9.80652809143066</v>
       </c>
       <c r="H937" t="n">
         <v>2548178</v>
@@ -27629,7 +27629,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.1047744750977</v>
+        <v>10.1047735214233</v>
       </c>
       <c r="H940" t="n">
         <v>3374955</v>
@@ -27687,7 +27687,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403865814209</v>
+        <v>10.1403856277466</v>
       </c>
       <c r="H942" t="n">
         <v>2004685</v>
@@ -27861,7 +27861,7 @@
         <v>10.881685256958</v>
       </c>
       <c r="G948" t="n">
-        <v>9.64850330352783</v>
+        <v>9.64850234985352</v>
       </c>
       <c r="H948" t="n">
         <v>3341804</v>
@@ -27890,7 +27890,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392478942871</v>
+        <v>9.56392574310303</v>
       </c>
       <c r="H949" t="n">
         <v>2157126</v>
@@ -28064,7 +28064,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.92736721038818</v>
+        <v>8.9273681640625</v>
       </c>
       <c r="H955" t="n">
         <v>5044840</v>
@@ -28209,7 +28209,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00971984863281</v>
+        <v>9.00972080230713</v>
       </c>
       <c r="H960" t="n">
         <v>3059945</v>
@@ -28267,7 +28267,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G962" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H962" t="n">
         <v>3934669</v>
@@ -28325,7 +28325,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G964" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H964" t="n">
         <v>4071910</v>
@@ -28354,7 +28354,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686973571777</v>
+        <v>9.31686878204346</v>
       </c>
       <c r="H965" t="n">
         <v>2851396</v>
@@ -28586,7 +28586,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65962982177734</v>
+        <v>9.65963077545166</v>
       </c>
       <c r="H973" t="n">
         <v>3880597</v>
@@ -28673,7 +28673,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H976" t="n">
         <v>4961745</v>
@@ -28818,7 +28818,7 @@
         <v>11.2306022644043</v>
       </c>
       <c r="G981" t="n">
-        <v>9.95787715911865</v>
+        <v>9.95787811279297</v>
       </c>
       <c r="H981" t="n">
         <v>2713471</v>
@@ -29282,7 +29282,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G997" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H997" t="n">
         <v>4136816</v>
@@ -29311,7 +29311,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G998" t="n">
-        <v>9.07204055786133</v>
+        <v>9.07204151153564</v>
       </c>
       <c r="H998" t="n">
         <v>3580666</v>
@@ -29340,7 +29340,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G999" t="n">
-        <v>9.05646133422852</v>
+        <v>9.0564603805542</v>
       </c>
       <c r="H999" t="n">
         <v>3079093</v>
@@ -29514,7 +29514,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H1005" t="n">
         <v>2212645</v>
@@ -29804,7 +29804,7 @@
         <v>10.934398651123</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.69524192810059</v>
+        <v>9.6952428817749</v>
       </c>
       <c r="H1015" t="n">
         <v>2311969</v>
@@ -30007,7 +30007,7 @@
         <v>11.1678466796875</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.90223503112793</v>
+        <v>9.90223407745361</v>
       </c>
       <c r="H1022" t="n">
         <v>2894790</v>
@@ -30065,7 +30065,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317378997803</v>
+        <v>9.79317283630371</v>
       </c>
       <c r="H1024" t="n">
         <v>1781897</v>
@@ -30210,7 +30210,7 @@
         <v>11.1126232147217</v>
       </c>
       <c r="G1029" t="n">
-        <v>9.85326862335205</v>
+        <v>9.85326957702637</v>
       </c>
       <c r="H1029" t="n">
         <v>1959789</v>
@@ -30239,7 +30239,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G1030" t="n">
-        <v>9.4615421295166</v>
+        <v>9.46154117584229</v>
       </c>
       <c r="H1030" t="n">
         <v>7606013</v>
@@ -30297,7 +30297,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G1032" t="n">
-        <v>9.12545776367188</v>
+        <v>9.12545871734619</v>
       </c>
       <c r="H1032" t="n">
         <v>2852190</v>
@@ -30355,7 +30355,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H1034" t="n">
         <v>4214085</v>
@@ -30529,7 +30529,7 @@
         <v>9.75962924957275</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.65360450744629</v>
+        <v>8.65360546112061</v>
       </c>
       <c r="H1040" t="n">
         <v>7621307</v>
@@ -30558,7 +30558,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H1041" t="n">
         <v>4707102</v>
@@ -30674,7 +30674,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H1045" t="n">
         <v>5766485</v>
@@ -30761,7 +30761,7 @@
         <v>9.55630302429199</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.47332191467285</v>
+        <v>8.47332096099854</v>
       </c>
       <c r="H1048" t="n">
         <v>2650515</v>
@@ -30906,7 +30906,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657657623291</v>
+        <v>7.71657609939575</v>
       </c>
       <c r="H1053" t="n">
         <v>7295256</v>
@@ -31022,7 +31022,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083913803101</v>
+        <v>7.60083866119385</v>
       </c>
       <c r="H1057" t="n">
         <v>6276118</v>
@@ -31051,7 +31051,7 @@
         <v>8.3037166595459</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.36268663406372</v>
+        <v>7.36268615722656</v>
       </c>
       <c r="H1058" t="n">
         <v>5909074</v>
@@ -31080,7 +31080,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585079193115</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H1059" t="n">
         <v>5991896</v>
@@ -31196,7 +31196,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.95000410079956</v>
+        <v>4.9500036239624</v>
       </c>
       <c r="H1063" t="n">
         <v>15725169</v>
@@ -31225,7 +31225,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.95000410079956</v>
+        <v>4.9500036239624</v>
       </c>
       <c r="H1064" t="n">
         <v>14702152</v>
@@ -31370,7 +31370,7 @@
         <v>5.16346597671509</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.57830905914307</v>
+        <v>4.57830858230591</v>
       </c>
       <c r="H1069" t="n">
         <v>8246612</v>
@@ -31515,7 +31515,7 @@
         <v>5.85627889633179</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.19260787963867</v>
+        <v>5.19260740280151</v>
       </c>
       <c r="H1074" t="n">
         <v>6147761</v>
@@ -31573,7 +31573,7 @@
         <v>5.89393186569214</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.22599363327026</v>
+        <v>5.22599315643311</v>
       </c>
       <c r="H1076" t="n">
         <v>4232448</v>
@@ -31747,7 +31747,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386259078979</v>
+        <v>5.28386211395264</v>
       </c>
       <c r="H1082" t="n">
         <v>6987858</v>
@@ -31834,7 +31834,7 @@
         <v>5.9014630317688</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.23267126083374</v>
+        <v>5.23267078399658</v>
       </c>
       <c r="H1085" t="n">
         <v>3564831</v>
@@ -32037,7 +32037,7 @@
         <v>5.28395509719849</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.685142993927</v>
+        <v>4.68514347076416</v>
       </c>
       <c r="H1092" t="n">
         <v>4658214</v>
@@ -32066,7 +32066,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445537567139</v>
+        <v>4.95445489883423</v>
       </c>
       <c r="H1093" t="n">
         <v>3686235</v>
@@ -32182,7 +32182,7 @@
         <v>5.55505609512329</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.92552137374878</v>
+        <v>4.92552089691162</v>
       </c>
       <c r="H1097" t="n">
         <v>3776492</v>
@@ -32298,7 +32298,7 @@
         <v>5.79101419448853</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.1347393989563</v>
+        <v>5.13473892211914</v>
       </c>
       <c r="H1101" t="n">
         <v>3599923</v>
@@ -32356,7 +32356,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470699310303</v>
+        <v>5.11470746994019</v>
       </c>
       <c r="H1103" t="n">
         <v>2616491</v>
@@ -32385,7 +32385,7 @@
         <v>5.80858516693115</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15031862258911</v>
+        <v>5.15031909942627</v>
       </c>
       <c r="H1104" t="n">
         <v>2378841</v>
@@ -32530,7 +32530,7 @@
         <v>5.57513809204102</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.94332695007324</v>
+        <v>4.9433274269104</v>
       </c>
       <c r="H1109" t="n">
         <v>2046001</v>
@@ -32646,7 +32646,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.79800033569336</v>
+        <v>4.79800081253052</v>
       </c>
       <c r="H1113" t="n">
         <v>3350805</v>
@@ -32733,7 +32733,7 @@
         <v>5.46217918395996</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.86507511138916</v>
+        <v>4.865074634552</v>
       </c>
       <c r="H1116" t="n">
         <v>3829378</v>
@@ -32762,7 +32762,7 @@
         <v>5.30905723571777</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.72869157791138</v>
+        <v>4.72869110107422</v>
       </c>
       <c r="H1117" t="n">
         <v>7700374</v>
@@ -32907,7 +32907,7 @@
         <v>5.79854488372803</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.16467046737671</v>
+        <v>5.16466999053955</v>
       </c>
       <c r="H1122" t="n">
         <v>12491580</v>
@@ -32965,7 +32965,7 @@
         <v>6.46876621246338</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.76162528991699</v>
+        <v>5.76162576675415</v>
       </c>
       <c r="H1124" t="n">
         <v>11268120</v>
@@ -32994,7 +32994,7 @@
         <v>6.59176588058472</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.87117958068848</v>
+        <v>5.87117910385132</v>
       </c>
       <c r="H1125" t="n">
         <v>10577677</v>
@@ -33023,7 +33023,7 @@
         <v>6.41354179382324</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.71243810653687</v>
+        <v>5.71243762969971</v>
       </c>
       <c r="H1126" t="n">
         <v>6490655</v>
@@ -33139,7 +33139,7 @@
         <v>5.99182987213135</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33682632446289</v>
+        <v>5.33682584762573</v>
       </c>
       <c r="H1130" t="n">
         <v>5065402</v>
@@ -33197,7 +33197,7 @@
         <v>5.98680877685547</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.33235359191895</v>
+        <v>5.3323540687561</v>
       </c>
       <c r="H1132" t="n">
         <v>5119610</v>
@@ -33342,7 +33342,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.08418226242065</v>
+        <v>5.0841817855835</v>
       </c>
       <c r="H1137" t="n">
         <v>3931365</v>
@@ -33429,7 +33429,7 @@
         <v>5.61530113220215</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.00145769119263</v>
+        <v>5.00145816802979</v>
       </c>
       <c r="H1140" t="n">
         <v>4272132</v>
@@ -33487,7 +33487,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.97686290740967</v>
+        <v>4.97686338424683</v>
       </c>
       <c r="H1142" t="n">
         <v>3387639</v>
@@ -33574,7 +33574,7 @@
         <v>5.68558597564697</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.06405925750732</v>
+        <v>5.06405973434448</v>
       </c>
       <c r="H1145" t="n">
         <v>3689754</v>
@@ -33661,7 +33661,7 @@
         <v>5.27642488479614</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.69962644577026</v>
+        <v>4.69962596893311</v>
       </c>
       <c r="H1148" t="n">
         <v>5584746</v>
@@ -33748,7 +33748,7 @@
         <v>5.28897619247437</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.71080589294434</v>
+        <v>4.71080541610718</v>
       </c>
       <c r="H1151" t="n">
         <v>6369097</v>
@@ -33777,7 +33777,7 @@
         <v>5.36679220199585</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.78011512756348</v>
+        <v>4.78011465072632</v>
       </c>
       <c r="H1152" t="n">
         <v>6019418</v>
@@ -33806,7 +33806,7 @@
         <v>5.47724008560181</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.87848901748657</v>
+        <v>4.87848949432373</v>
       </c>
       <c r="H1153" t="n">
         <v>3853871</v>
@@ -34067,7 +34067,7 @@
         <v>4.92123222351074</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.38326168060303</v>
+        <v>4.38326215744019</v>
       </c>
       <c r="H1162" t="n">
         <v>24661467</v>
@@ -34154,7 +34154,7 @@
         <v>4.57357120513916</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.07360601425171</v>
+        <v>4.07360553741455</v>
       </c>
       <c r="H1165" t="n">
         <v>7438646</v>
@@ -34299,7 +34299,7 @@
         <v>4.96892595291138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.42574167251587</v>
+        <v>4.42574214935303</v>
       </c>
       <c r="H1170" t="n">
         <v>3451603</v>
@@ -34415,7 +34415,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1174" t="n">
-        <v>4.34190034866333</v>
+        <v>4.34189987182617</v>
       </c>
       <c r="H1174" t="n">
         <v>4695442</v>
@@ -34589,7 +34589,7 @@
         <v>4.66895818710327</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.15856599807739</v>
+        <v>4.15856552124023</v>
       </c>
       <c r="H1180" t="n">
         <v>6557504</v>
@@ -34734,7 +34734,7 @@
         <v>4.50579500198364</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.01323890686035</v>
+        <v>4.01323843002319</v>
       </c>
       <c r="H1185" t="n">
         <v>4155094</v>
@@ -34821,7 +34821,7 @@
         <v>4.39032697677612</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.91039323806763</v>
+        <v>3.91039347648621</v>
       </c>
       <c r="H1188" t="n">
         <v>4258438</v>
@@ -34850,7 +34850,7 @@
         <v>4.29242897033691</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.82319688796997</v>
+        <v>3.82319736480713</v>
       </c>
       <c r="H1189" t="n">
         <v>7837081</v>
@@ -34937,7 +34937,7 @@
         <v>4.19327592849731</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.73488306999207</v>
+        <v>3.73488283157349</v>
       </c>
       <c r="H1192" t="n">
         <v>4846298</v>
@@ -34995,7 +34995,7 @@
         <v>4.07906293869019</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.63315558433533</v>
+        <v>3.63315534591675</v>
       </c>
       <c r="H1194" t="n">
         <v>8280016</v>
@@ -35111,7 +35111,7 @@
         <v>4.22465419769287</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.76283121109009</v>
+        <v>3.76283097267151</v>
       </c>
       <c r="H1198" t="n">
         <v>5589044</v>
@@ -35401,7 +35401,7 @@
         <v>3.56321811676025</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.17370057106018</v>
+        <v>3.17370080947876</v>
       </c>
       <c r="H1208" t="n">
         <v>6464136</v>
@@ -35459,7 +35459,7 @@
         <v>3.86444091796875</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.44199514389038</v>
+        <v>3.4419949054718</v>
       </c>
       <c r="H1210" t="n">
         <v>7063864</v>
@@ -35604,7 +35604,7 @@
         <v>3.79415607452393</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.37939357757568</v>
+        <v>3.3793933391571</v>
       </c>
       <c r="H1215" t="n">
         <v>3909509</v>
@@ -35633,7 +35633,7 @@
         <v>3.65609502792358</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.25642490386963</v>
+        <v>3.25642466545105</v>
       </c>
       <c r="H1216" t="n">
         <v>4082735</v>
@@ -35807,7 +35807,7 @@
         <v>3.59585094451904</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.20276618003845</v>
+        <v>3.20276641845703</v>
       </c>
       <c r="H1222" t="n">
         <v>5346240</v>
@@ -35836,7 +35836,7 @@
         <v>3.62597298622131</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.22959542274475</v>
+        <v>3.22959566116333</v>
       </c>
       <c r="H1223" t="n">
         <v>3204692</v>
@@ -35865,7 +35865,7 @@
         <v>3.68496203422546</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.28213596343994</v>
+        <v>3.28213620185852</v>
       </c>
       <c r="H1224" t="n">
         <v>4139377</v>
@@ -36010,7 +36010,7 @@
         <v>3.78411507606506</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.370450258255</v>
+        <v>3.37045001983643</v>
       </c>
       <c r="H1229" t="n">
         <v>8618018</v>
@@ -36184,7 +36184,7 @@
         <v>4.6940598487854</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.1809229850769</v>
+        <v>4.18092346191406</v>
       </c>
       <c r="H1235" t="n">
         <v>15804964</v>
@@ -36387,7 +36387,7 @@
         <v>4.89487504959106</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.35978603363037</v>
+        <v>4.35978651046753</v>
       </c>
       <c r="H1242" t="n">
         <v>6079967</v>
@@ -36445,7 +36445,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.2770619392395</v>
+        <v>4.27706241607666</v>
       </c>
       <c r="H1244" t="n">
         <v>4685519</v>
@@ -36474,7 +36474,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.47157526016235</v>
+        <v>4.47157573699951</v>
       </c>
       <c r="H1245" t="n">
         <v>7739906</v>
@@ -36532,7 +36532,7 @@
         <v>5.42201614379883</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.82930183410645</v>
+        <v>4.8293023109436</v>
       </c>
       <c r="H1247" t="n">
         <v>8336834</v>
@@ -36561,7 +36561,7 @@
         <v>5.30654716491699</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.72645616531372</v>
+        <v>4.72645568847656</v>
       </c>
       <c r="H1248" t="n">
         <v>6460441</v>
@@ -36619,7 +36619,7 @@
         <v>5.1333441734314</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.57218647003174</v>
+        <v>4.5721869468689</v>
       </c>
       <c r="H1250" t="n">
         <v>5110006</v>
@@ -36706,7 +36706,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.62584447860718</v>
+        <v>4.62584495544434</v>
       </c>
       <c r="H1253" t="n">
         <v>2827257</v>
@@ -36735,7 +36735,7 @@
         <v>5.35675096511841</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.77117156982422</v>
+        <v>4.77117109298706</v>
       </c>
       <c r="H1254" t="n">
         <v>5955094</v>
@@ -36793,7 +36793,7 @@
         <v>5.37683200836182</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.78905725479126</v>
+        <v>4.78905773162842</v>
       </c>
       <c r="H1256" t="n">
         <v>1840506</v>
@@ -36880,7 +36880,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1259" t="n">
         <v>4061775</v>
@@ -36938,7 +36938,7 @@
         <v>5.46719884872437</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.86954545974731</v>
+        <v>4.86954593658447</v>
       </c>
       <c r="H1261" t="n">
         <v>2064399</v>
@@ -36967,7 +36967,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1262" t="n">
         <v>5407097</v>
@@ -36996,7 +36996,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.86060237884521</v>
+        <v>4.86060285568237</v>
       </c>
       <c r="H1263" t="n">
         <v>3511782</v>
@@ -37112,7 +37112,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1267" t="n">
         <v>3396789</v>
@@ -37257,7 +37257,7 @@
         <v>5.82364702224731</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.18702793121338</v>
+        <v>5.18702840805054</v>
       </c>
       <c r="H1272" t="n">
         <v>7105248</v>
@@ -37315,7 +37315,7 @@
         <v>6.17256307601929</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.49780225753784</v>
+        <v>5.49780178070068</v>
       </c>
       <c r="H1274" t="n">
         <v>7287173</v>
@@ -37344,7 +37344,7 @@
         <v>6.10729789733887</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.4396710395813</v>
+        <v>5.43967151641846</v>
       </c>
       <c r="H1275" t="n">
         <v>6169237</v>
@@ -37431,7 +37431,7 @@
         <v>6.08721685409546</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.42178535461426</v>
+        <v>5.42178583145142</v>
       </c>
       <c r="H1278" t="n">
         <v>4068724</v>
@@ -37460,7 +37460,7 @@
         <v>6.00689077377319</v>
       </c>
       <c r="G1279" t="n">
-        <v>5.3502402305603</v>
+        <v>5.35024070739746</v>
       </c>
       <c r="H1279" t="n">
         <v>3024433</v>
@@ -37547,7 +37547,7 @@
         <v>5.85878896713257</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.21832847595215</v>
+        <v>5.21832895278931</v>
       </c>
       <c r="H1282" t="n">
         <v>3059439</v>
@@ -37692,7 +37692,7 @@
         <v>5.34169006347656</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.75775671005249</v>
+        <v>4.75775718688965</v>
       </c>
       <c r="H1287" t="n">
         <v>4046294</v>
@@ -37721,7 +37721,7 @@
         <v>5.59019899368286</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.97910022735596</v>
+        <v>4.9790997505188</v>
       </c>
       <c r="H1288" t="n">
         <v>7589590</v>
@@ -37924,7 +37924,7 @@
         <v>5.98178911209106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.32788324356079</v>
+        <v>5.32788276672363</v>
       </c>
       <c r="H1295" t="n">
         <v>5483636</v>
@@ -38098,7 +38098,7 @@
         <v>6.55160188674927</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.8354058265686</v>
+        <v>5.83540630340576</v>
       </c>
       <c r="H1301" t="n">
         <v>9385518</v>
@@ -38156,7 +38156,7 @@
         <v>6.3457670211792</v>
       </c>
       <c r="G1303" t="n">
-        <v>5.65207242965698</v>
+        <v>5.65207195281982</v>
       </c>
       <c r="H1303" t="n">
         <v>6157528</v>
@@ -38185,7 +38185,7 @@
         <v>6.35078716278076</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.65654325485229</v>
+        <v>5.65654373168945</v>
       </c>
       <c r="H1304" t="n">
         <v>5745479</v>
@@ -38214,7 +38214,7 @@
         <v>6.40852212905884</v>
       </c>
       <c r="G1305" t="n">
-        <v>5.70796680450439</v>
+        <v>5.70796728134155</v>
       </c>
       <c r="H1305" t="n">
         <v>3560044</v>
@@ -38243,7 +38243,7 @@
         <v>6.63192892074585</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.90695190429688</v>
+        <v>5.90695142745972</v>
       </c>
       <c r="H1306" t="n">
         <v>7874391</v>
@@ -38330,7 +38330,7 @@
         <v>6.00940084457397</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.35247611999512</v>
+        <v>5.35247659683228</v>
       </c>
       <c r="H1309" t="n">
         <v>24228663</v>
@@ -38388,7 +38388,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.08418226242065</v>
+        <v>5.0841817855835</v>
       </c>
       <c r="H1311" t="n">
         <v>8961866</v>
@@ -38417,7 +38417,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1312" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1312" t="n">
         <v>9655227</v>
@@ -38504,7 +38504,7 @@
         <v>5.91652393341064</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.26975202560425</v>
+        <v>5.26975250244141</v>
       </c>
       <c r="H1315" t="n">
         <v>12797834</v>
@@ -38533,7 +38533,7 @@
         <v>6.07215595245361</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.40837144851685</v>
+        <v>5.40837097167969</v>
       </c>
       <c r="H1316" t="n">
         <v>9400118</v>
@@ -38591,7 +38591,7 @@
         <v>6.07717609405518</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.41284227371216</v>
+        <v>5.41284275054932</v>
       </c>
       <c r="H1318" t="n">
         <v>4627496</v>
@@ -38649,7 +38649,7 @@
         <v>6.12486982345581</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.455322265625</v>
+        <v>5.45532274246216</v>
       </c>
       <c r="H1320" t="n">
         <v>2675208</v>
@@ -38707,7 +38707,7 @@
         <v>5.97174787521362</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.31893968582153</v>
+        <v>5.31893920898438</v>
       </c>
       <c r="H1322" t="n">
         <v>5171781</v>
@@ -38765,7 +38765,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.31670331954956</v>
+        <v>5.31670379638672</v>
       </c>
       <c r="H1324" t="n">
         <v>4027905</v>
@@ -38852,7 +38852,7 @@
         <v>5.69060611724854</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.06853103637695</v>
+        <v>5.06853055953979</v>
       </c>
       <c r="H1327" t="n">
         <v>7314312</v>
@@ -39055,7 +39055,7 @@
         <v>5.87887096405029</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.23621511459351</v>
+        <v>5.23621559143066</v>
       </c>
       <c r="H1334" t="n">
         <v>3164034</v>
@@ -39287,7 +39287,7 @@
         <v>5.83870792388916</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.20044279098511</v>
+        <v>5.20044231414795</v>
       </c>
       <c r="H1342" t="n">
         <v>4486409</v>
@@ -39374,7 +39374,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.97686290740967</v>
+        <v>4.97686338424683</v>
       </c>
       <c r="H1345" t="n">
         <v>5024234</v>
@@ -39490,7 +39490,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.94556331634521</v>
+        <v>4.94556283950806</v>
       </c>
       <c r="H1349" t="n">
         <v>4621291</v>
@@ -39577,7 +39577,7 @@
         <v>4.87855911254883</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.34525394439697</v>
+        <v>4.34525346755981</v>
       </c>
       <c r="H1352" t="n">
         <v>14868855</v>
@@ -39606,7 +39606,7 @@
         <v>4.82333517074585</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.29606628417969</v>
+        <v>4.29606676101685</v>
       </c>
       <c r="H1353" t="n">
         <v>10990037</v>
@@ -39751,7 +39751,7 @@
         <v>5.06054782867432</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.50734853744507</v>
+        <v>4.50734806060791</v>
       </c>
       <c r="H1358" t="n">
         <v>3316325</v>
@@ -39954,7 +39954,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.69068336486816</v>
+        <v>4.69068288803101</v>
       </c>
       <c r="H1365" t="n">
         <v>9046399</v>
@@ -40012,7 +40012,7 @@
         <v>5.1383638381958</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.57665777206421</v>
+        <v>4.57665729522705</v>
       </c>
       <c r="H1367" t="n">
         <v>2528599</v>
@@ -40070,7 +40070,7 @@
         <v>5.12832307815552</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.56771469116211</v>
+        <v>4.56771421432495</v>
       </c>
       <c r="H1369" t="n">
         <v>2605182</v>
@@ -40186,7 +40186,7 @@
         <v>5.11828184127808</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.55877113342285</v>
+        <v>4.55877065658569</v>
       </c>
       <c r="H1373" t="n">
         <v>4133342</v>
@@ -40244,7 +40244,7 @@
         <v>5.3793420791626</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.79129314422607</v>
+        <v>4.79129266738892</v>
       </c>
       <c r="H1375" t="n">
         <v>10178926</v>
@@ -40273,7 +40273,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1376" t="n">
         <v>5287449</v>
@@ -40389,7 +40389,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1380" t="n">
         <v>6843942</v>
@@ -40476,7 +40476,7 @@
         <v>5.56760692596436</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.95897722244263</v>
+        <v>4.95897769927979</v>
       </c>
       <c r="H1383" t="n">
         <v>4282870</v>
@@ -40679,7 +40679,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.72421979904175</v>
+        <v>4.72422027587891</v>
       </c>
       <c r="H1390" t="n">
         <v>3701384</v>
@@ -40737,7 +40737,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.72421979904175</v>
+        <v>4.72422027587891</v>
       </c>
       <c r="H1392" t="n">
         <v>2649454</v>
@@ -40766,7 +40766,7 @@
         <v>5.29901599884033</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.71974802017212</v>
+        <v>4.71974754333496</v>
       </c>
       <c r="H1393" t="n">
         <v>2108129</v>
@@ -40853,7 +40853,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1396" t="n">
-        <v>4.56324291229248</v>
+        <v>4.56324338912964</v>
       </c>
       <c r="H1396" t="n">
         <v>3303148</v>
@@ -40882,7 +40882,7 @@
         <v>5.22873115539551</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.65714645385742</v>
+        <v>4.65714597702026</v>
       </c>
       <c r="H1397" t="n">
         <v>3565887</v>
@@ -40911,7 +40911,7 @@
         <v>5.21868991851807</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.64820289611816</v>
+        <v>4.64820241928101</v>
       </c>
       <c r="H1398" t="n">
         <v>2418474</v>
@@ -41027,7 +41027,7 @@
         <v>4.90617084503174</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.36984729766846</v>
+        <v>4.3698468208313</v>
       </c>
       <c r="H1402" t="n">
         <v>5231002</v>
@@ -41056,7 +41056,7 @@
         <v>4.97143602371216</v>
       </c>
       <c r="G1403" t="n">
-        <v>4.42797803878784</v>
+        <v>4.42797756195068</v>
       </c>
       <c r="H1403" t="n">
         <v>3203342</v>
@@ -41114,7 +41114,7 @@
         <v>4.88483476638794</v>
       </c>
       <c r="G1405" t="n">
-        <v>4.35084342956543</v>
+        <v>4.35084295272827</v>
       </c>
       <c r="H1405" t="n">
         <v>3408367</v>
@@ -41172,7 +41172,7 @@
         <v>4.90240621566772</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.36649370193481</v>
+        <v>4.36649417877197</v>
       </c>
       <c r="H1407" t="n">
         <v>3512290</v>
@@ -41288,7 +41288,7 @@
         <v>4.75681495666504</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.23681831359863</v>
+        <v>4.23681783676147</v>
       </c>
       <c r="H1411" t="n">
         <v>4771701</v>
@@ -41462,7 +41462,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1417" t="n">
-        <v>4.52970600128174</v>
+        <v>4.5297064781189</v>
       </c>
       <c r="H1417" t="n">
         <v>3747890</v>
@@ -41549,7 +41549,7 @@
         <v>4.91119194030762</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.37431907653809</v>
+        <v>4.37431955337524</v>
       </c>
       <c r="H1420" t="n">
         <v>4386657</v>
@@ -41636,7 +41636,7 @@
         <v>4.92499780654907</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.38661623001099</v>
+        <v>4.38661575317383</v>
       </c>
       <c r="H1423" t="n">
         <v>3890806</v>
@@ -41694,7 +41694,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.56324291229248</v>
+        <v>4.56324338912964</v>
       </c>
       <c r="H1425" t="n">
         <v>5305491</v>
@@ -41723,7 +41723,7 @@
         <v>5.16597604751587</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.60125112533569</v>
+        <v>4.60125160217285</v>
       </c>
       <c r="H1426" t="n">
         <v>3581797</v>
@@ -41868,7 +41868,7 @@
         <v>4.98147678375244</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.43692111968994</v>
+        <v>4.43692064285278</v>
       </c>
       <c r="H1431" t="n">
         <v>1848823</v>
@@ -41926,7 +41926,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.2770619392395</v>
+        <v>4.27706241607666</v>
       </c>
       <c r="H1433" t="n">
         <v>3356625</v>
@@ -42013,7 +42013,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.47157526016235</v>
+        <v>4.47157573699951</v>
       </c>
       <c r="H1436" t="n">
         <v>3876966</v>
@@ -42216,7 +42216,7 @@
         <v>4.96139478683472</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41903448104858</v>
+        <v>4.41903400421143</v>
       </c>
       <c r="H1443" t="n">
         <v>3045903</v>
@@ -42332,7 +42332,7 @@
         <v>5.01662015914917</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.46822261810303</v>
+        <v>4.46822214126587</v>
       </c>
       <c r="H1447" t="n">
         <v>5734258</v>
@@ -42390,7 +42390,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.62584447860718</v>
+        <v>4.62584495544434</v>
       </c>
       <c r="H1449" t="n">
         <v>7048976</v>
@@ -42419,7 +42419,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.52970600128174</v>
+        <v>4.5297064781189</v>
       </c>
       <c r="H1450" t="n">
         <v>6506615</v>
@@ -42506,7 +42506,7 @@
         <v>4.99151802062988</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.44586420059204</v>
+        <v>4.4458646774292</v>
       </c>
       <c r="H1453" t="n">
         <v>2739262</v>
@@ -42535,7 +42535,7 @@
         <v>4.91244697570801</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.37543678283691</v>
+        <v>4.37543725967407</v>
       </c>
       <c r="H1454" t="n">
         <v>3529674</v>
@@ -42564,7 +42564,7 @@
         <v>5.07058906555176</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.51629209518433</v>
+        <v>4.51629161834717</v>
       </c>
       <c r="H1455" t="n">
         <v>5222595</v>
@@ -42825,7 +42825,7 @@
         <v>5.55003595352173</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.94332695007324</v>
+        <v>4.9433274269104</v>
       </c>
       <c r="H1464" t="n">
         <v>6413047</v>
@@ -42883,7 +42883,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.69068336486816</v>
+        <v>4.69068288803101</v>
       </c>
       <c r="H1466" t="n">
         <v>7328705</v>
@@ -42941,7 +42941,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.79800033569336</v>
+        <v>4.79800081253052</v>
       </c>
       <c r="H1468" t="n">
         <v>8090619</v>
@@ -42999,7 +42999,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1470" t="n">
         <v>6942701</v>
@@ -43144,7 +43144,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.91202592849731</v>
+        <v>4.91202640533447</v>
       </c>
       <c r="H1475" t="n">
         <v>2995584</v>
@@ -43202,7 +43202,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1477" t="n">
         <v>4075860</v>
@@ -43289,7 +43289,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.94556331634521</v>
+        <v>4.94556283950806</v>
       </c>
       <c r="H1480" t="n">
         <v>5065969</v>
@@ -43347,7 +43347,7 @@
         <v>4.87353897094727</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.34078216552734</v>
+        <v>4.3407826423645</v>
       </c>
       <c r="H1482" t="n">
         <v>28990116</v>
@@ -43492,7 +43492,7 @@
         <v>4.81203889846802</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.2860050201416</v>
+        <v>4.28600549697876</v>
       </c>
       <c r="H1487" t="n">
         <v>5381782</v>
@@ -43521,7 +43521,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.34190034866333</v>
+        <v>4.34189987182617</v>
       </c>
       <c r="H1488" t="n">
         <v>5511409</v>
@@ -43666,7 +43666,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.39220476150513</v>
+        <v>4.39220523834229</v>
       </c>
       <c r="H1493" t="n">
         <v>2167743</v>
@@ -43956,7 +43956,7 @@
         <v>4.46563196182251</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.97746634483337</v>
+        <v>3.97746610641479</v>
       </c>
       <c r="H1503" t="n">
         <v>7272410</v>
@@ -43985,7 +43985,7 @@
         <v>4.50328493118286</v>
       </c>
       <c r="G1504" t="n">
-        <v>4.01100301742554</v>
+        <v>4.0110034942627</v>
       </c>
       <c r="H1504" t="n">
         <v>4367193</v>
@@ -44014,7 +44014,7 @@
         <v>4.42170381546021</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.93833994865417</v>
+        <v>3.93834018707275</v>
       </c>
       <c r="H1505" t="n">
         <v>3362331</v>
@@ -44130,7 +44130,7 @@
         <v>4.59365177154541</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.09149122238159</v>
+        <v>4.09149169921875</v>
       </c>
       <c r="H1509" t="n">
         <v>4350486</v>
@@ -44188,7 +44188,7 @@
         <v>4.56729507446289</v>
       </c>
       <c r="G1511" t="n">
-        <v>4.06801557540894</v>
+        <v>4.06801605224609</v>
       </c>
       <c r="H1511" t="n">
         <v>4359136</v>
@@ -44275,7 +44275,7 @@
         <v>4.41040802001953</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.92827892303467</v>
+        <v>3.92827916145325</v>
       </c>
       <c r="H1514" t="n">
         <v>3179388</v>
@@ -44304,7 +44304,7 @@
         <v>4.4455509185791</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.95958042144775</v>
+        <v>3.95958018302917</v>
       </c>
       <c r="H1515" t="n">
         <v>2325197</v>
@@ -44333,7 +44333,7 @@
         <v>4.37275505065918</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.89474201202393</v>
+        <v>3.89474248886108</v>
       </c>
       <c r="H1516" t="n">
         <v>3004717</v>
@@ -44507,7 +44507,7 @@
         <v>4.55097913742065</v>
       </c>
       <c r="G1522" t="n">
-        <v>4.0534839630127</v>
+        <v>4.05348348617554</v>
       </c>
       <c r="H1522" t="n">
         <v>1502529</v>
@@ -44652,7 +44652,7 @@
         <v>4.78317213058472</v>
       </c>
       <c r="G1527" t="n">
-        <v>4.26029396057129</v>
+        <v>4.26029443740845</v>
       </c>
       <c r="H1527" t="n">
         <v>2970018</v>
@@ -44768,7 +44768,7 @@
         <v>4.91495704650879</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.37767314910889</v>
+        <v>4.37767267227173</v>
       </c>
       <c r="H1531" t="n">
         <v>2759069</v>
@@ -44913,7 +44913,7 @@
         <v>5.03042602539062</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.48051881790161</v>
+        <v>4.48051929473877</v>
       </c>
       <c r="H1536" t="n">
         <v>2349535</v>
@@ -44971,7 +44971,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.39220476150513</v>
+        <v>4.39220523834229</v>
       </c>
       <c r="H1538" t="n">
         <v>3995107</v>
@@ -45058,7 +45058,7 @@
         <v>5.01410913467407</v>
       </c>
       <c r="G1541" t="n">
-        <v>4.4659857749939</v>
+        <v>4.46598625183105</v>
       </c>
       <c r="H1541" t="n">
         <v>2334898</v>
@@ -45348,7 +45348,7 @@
         <v>2.99591493606567</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.66841316223145</v>
+        <v>2.66841292381287</v>
       </c>
       <c r="H1551" t="n">
         <v>17072505</v>
@@ -45377,7 +45377,7 @@
         <v>3.02854704856873</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.6974778175354</v>
+        <v>2.69747805595398</v>
       </c>
       <c r="H1552" t="n">
         <v>16828629</v>
@@ -45522,7 +45522,7 @@
         <v>2.8616189956665</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.54879760742188</v>
+        <v>2.54879784584045</v>
       </c>
       <c r="H1557" t="n">
         <v>12600027</v>
@@ -45551,7 +45551,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.5622124671936</v>
+        <v>2.56221222877502</v>
       </c>
       <c r="H1558" t="n">
         <v>9318354</v>
@@ -45725,7 +45725,7 @@
         <v>2.51521301269531</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.24025940895081</v>
+        <v>2.24025964736938</v>
       </c>
       <c r="H1564" t="n">
         <v>6732142</v>
@@ -45754,7 +45754,7 @@
         <v>2.56165099143982</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.28162097930908</v>
+        <v>2.28162121772766</v>
       </c>
       <c r="H1565" t="n">
         <v>16777908</v>
@@ -45899,7 +45899,7 @@
         <v>2.56792688369751</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.2872109413147</v>
+        <v>2.28721117973328</v>
       </c>
       <c r="H1570" t="n">
         <v>5399583</v>
@@ -45928,7 +45928,7 @@
         <v>2.37715196609497</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.11729073524475</v>
+        <v>2.11729097366333</v>
       </c>
       <c r="H1571" t="n">
         <v>6070659</v>
@@ -46015,7 +46015,7 @@
         <v>2.58047795295715</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.29839015007019</v>
+        <v>2.29838991165161</v>
       </c>
       <c r="H1574" t="n">
         <v>9240163</v>
@@ -46131,7 +46131,7 @@
         <v>2.46450710296631</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.19509649276733</v>
+        <v>2.19509673118591</v>
       </c>
       <c r="H1578" t="n">
         <v>4819541</v>
@@ -46247,7 +46247,7 @@
         <v>2.67335510253906</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.38111424446106</v>
+        <v>2.38111400604248</v>
       </c>
       <c r="H1582" t="n">
         <v>3911764</v>
@@ -46392,7 +46392,7 @@
         <v>2.86287403106689</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.54991579055786</v>
+        <v>2.54991555213928</v>
       </c>
       <c r="H1587" t="n">
         <v>13747439</v>
@@ -46479,7 +46479,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.5622124671936</v>
+        <v>2.56221222877502</v>
       </c>
       <c r="H1590" t="n">
         <v>10760896</v>
@@ -46508,7 +46508,7 @@
         <v>2.93943500518799</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.61810708045959</v>
+        <v>2.61810731887817</v>
       </c>
       <c r="H1591" t="n">
         <v>7063060</v>
@@ -46537,7 +46537,7 @@
         <v>2.87919092178345</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.56444883346558</v>
+        <v>2.564448595047</v>
       </c>
       <c r="H1592" t="n">
         <v>10358249</v>
@@ -46566,7 +46566,7 @@
         <v>2.84404802322388</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.53314757347107</v>
+        <v>2.53314781188965</v>
       </c>
       <c r="H1593" t="n">
         <v>5883247</v>
@@ -46595,7 +46595,7 @@
         <v>2.77878308296204</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.47501707077026</v>
+        <v>2.47501730918884</v>
       </c>
       <c r="H1594" t="n">
         <v>7471517</v>
@@ -46653,7 +46653,7 @@
         <v>2.80262994766235</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.49625706672668</v>
+        <v>2.49625730514526</v>
       </c>
       <c r="H1596" t="n">
         <v>3079893</v>
@@ -46711,7 +46711,7 @@
         <v>2.79384398460388</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.48843145370483</v>
+        <v>2.48843169212341</v>
       </c>
       <c r="H1598" t="n">
         <v>2912676</v>
@@ -46740,7 +46740,7 @@
         <v>2.75744605064392</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.4560124874115</v>
+        <v>2.45601272583008</v>
       </c>
       <c r="H1599" t="n">
         <v>3637078</v>
@@ -46769,7 +46769,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.43700909614563</v>
+        <v>2.43700885772705</v>
       </c>
       <c r="H1600" t="n">
         <v>2248107</v>
@@ -46798,7 +46798,7 @@
         <v>2.84028291702271</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.52979421615601</v>
+        <v>2.52979397773743</v>
       </c>
       <c r="H1601" t="n">
         <v>4359715</v>
@@ -46885,7 +46885,7 @@
         <v>2.92437410354614</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.60469269752502</v>
+        <v>2.6046929359436</v>
       </c>
       <c r="H1604" t="n">
         <v>10127429</v>
@@ -46914,7 +46914,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.43700909614563</v>
+        <v>2.43700885772705</v>
       </c>
       <c r="H1605" t="n">
         <v>8650581</v>
@@ -47233,7 +47233,7 @@
         <v>2.48509001731873</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.21342968940735</v>
+        <v>2.21342945098877</v>
       </c>
       <c r="H1616" t="n">
         <v>11509858</v>
@@ -47262,7 +47262,7 @@
         <v>2.53780388832092</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.26038074493408</v>
+        <v>2.26038098335266</v>
       </c>
       <c r="H1617" t="n">
         <v>13634558</v>
@@ -47320,7 +47320,7 @@
         <v>2.68841600418091</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.39452862739563</v>
+        <v>2.39452886581421</v>
       </c>
       <c r="H1619" t="n">
         <v>6670481</v>
@@ -47349,7 +47349,7 @@
         <v>2.90680289268494</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.58904218673706</v>
+        <v>2.58904242515564</v>
       </c>
       <c r="H1620" t="n">
         <v>11371682</v>
@@ -47581,7 +47581,7 @@
         <v>2.97517991065979</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.64994478225708</v>
+        <v>2.6499445438385</v>
       </c>
       <c r="H1628" t="n">
         <v>9786163</v>
@@ -47755,7 +47755,7 @@
         <v>2.72426104545593</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.4264554977417</v>
+        <v>2.42645525932312</v>
       </c>
       <c r="H1634" t="n">
         <v>3222869</v>
@@ -47900,7 +47900,7 @@
         <v>2.37423992156982</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.11469697952271</v>
+        <v>2.11469721794128</v>
       </c>
       <c r="H1639" t="n">
         <v>5658326</v>
@@ -47987,7 +47987,7 @@
         <v>1.96649694442749</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.75152695178986</v>
+        <v>1.75152707099915</v>
       </c>
       <c r="H1642" t="n">
         <v>12639154</v>
@@ -48016,7 +48016,7 @@
         <v>2.01657509803772</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.79613089561462</v>
+        <v>1.79613077640533</v>
       </c>
       <c r="H1643" t="n">
         <v>25382152</v>
@@ -48103,7 +48103,7 @@
         <v>2.21557092666626</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.97337317466736</v>
+        <v>1.97337329387665</v>
       </c>
       <c r="H1646" t="n">
         <v>8434013</v>
@@ -48132,7 +48132,7 @@
         <v>1.73798203468323</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.54799258708954</v>
+        <v>1.54799246788025</v>
       </c>
       <c r="H1647" t="n">
         <v>26496542</v>
@@ -48161,7 +48161,7 @@
         <v>1.59776198863983</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.42310082912445</v>
+        <v>1.42310070991516</v>
       </c>
       <c r="H1648" t="n">
         <v>48720201</v>
@@ -48190,7 +48190,7 @@
         <v>1.24932205677032</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.11275088787079</v>
+        <v>1.11275100708008</v>
       </c>
       <c r="H1649" t="n">
         <v>56877192</v>
@@ -48451,7 +48451,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98913502693176</v>
+        <v>2.98913478851318</v>
       </c>
       <c r="H1658" t="n">
         <v>6899464</v>
@@ -48538,7 +48538,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.73594272136688</v>
+        <v>1.73594284057617</v>
       </c>
       <c r="H1661" t="n">
         <v>7745580</v>
@@ -48567,7 +48567,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.98598700761795</v>
+        <v>0.985986948013306</v>
       </c>
       <c r="H1662" t="n">
         <v>25986719</v>
@@ -48596,7 +48596,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.04210007190704</v>
+        <v>1.04209995269775</v>
       </c>
       <c r="H1663" t="n">
         <v>15517197</v>
@@ -48625,7 +48625,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.730360746383667</v>
+        <v>0.730360686779022</v>
       </c>
       <c r="H1664" t="n">
         <v>50412931</v>
@@ -48770,7 +48770,7 @@
         <v>0.71340000629425</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.635413885116577</v>
+        <v>0.635413825511932</v>
       </c>
       <c r="H1669" t="n">
         <v>28781555</v>
@@ -48828,7 +48828,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.659106016159058</v>
+        <v>0.659106075763702</v>
       </c>
       <c r="H1671" t="n">
         <v>27445946</v>
@@ -48857,7 +48857,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.692061305046082</v>
+        <v>0.692061364650726</v>
       </c>
       <c r="H1672" t="n">
         <v>35674340</v>
@@ -48944,7 +48944,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.751737117767334</v>
+        <v>0.751737177371979</v>
       </c>
       <c r="H1675" t="n">
         <v>37326895</v>
@@ -49002,7 +49002,7 @@
         <v>0.833599984645844</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.742474019527435</v>
+        <v>0.74247407913208</v>
       </c>
       <c r="H1677" t="n">
         <v>19689110</v>
@@ -49205,7 +49205,7 @@
         <v>0.821799993515015</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.731963932514191</v>
+        <v>0.731963992118835</v>
       </c>
       <c r="H1684" t="n">
         <v>16957436</v>
@@ -49292,7 +49292,7 @@
         <v>0.762199997901917</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.678879201412201</v>
+        <v>0.678879261016846</v>
       </c>
       <c r="H1687" t="n">
         <v>13487789</v>
@@ -49524,7 +49524,7 @@
         <v>0.716400027275085</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.638085961341858</v>
+        <v>0.638085901737213</v>
       </c>
       <c r="H1695" t="n">
         <v>20717644</v>
@@ -49756,7 +49756,7 @@
         <v>0.674600005149841</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.600855350494385</v>
+        <v>0.60085529088974</v>
       </c>
       <c r="H1703" t="n">
         <v>12648147</v>
@@ -49785,7 +49785,7 @@
         <v>0.697399973869324</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.621162831783295</v>
+        <v>0.621162891387939</v>
       </c>
       <c r="H1704" t="n">
         <v>26443104</v>
@@ -49843,7 +49843,7 @@
         <v>0.683200001716614</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.60851514339447</v>
+        <v>0.608515202999115</v>
       </c>
       <c r="H1706" t="n">
         <v>9988795</v>
@@ -49872,7 +49872,7 @@
         <v>0.662199974060059</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589810788631439</v>
+        <v>0.589810848236084</v>
       </c>
       <c r="H1707" t="n">
         <v>13712596</v>
@@ -49901,7 +49901,7 @@
         <v>0.64300000667572</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.572709679603577</v>
+        <v>0.572709739208221</v>
       </c>
       <c r="H1708" t="n">
         <v>58766149</v>
@@ -49930,7 +49930,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.540645122528076</v>
+        <v>0.540645062923431</v>
       </c>
       <c r="H1709" t="n">
         <v>28764901</v>
@@ -49959,7 +49959,7 @@
         <v>0.584800004959106</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.520871877670288</v>
+        <v>0.520871937274933</v>
       </c>
       <c r="H1710" t="n">
         <v>20980769</v>
@@ -49988,7 +49988,7 @@
         <v>0.59280002117157</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.527997434139252</v>
+        <v>0.527997374534607</v>
       </c>
       <c r="H1711" t="n">
         <v>21540866</v>
@@ -50075,7 +50075,7 @@
         <v>0.597199976444244</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.531916379928589</v>
+        <v>0.531916320323944</v>
       </c>
       <c r="H1714" t="n">
         <v>19250857</v>
@@ -50191,7 +50191,7 @@
         <v>0.637600004673004</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.567900061607361</v>
+        <v>0.567900002002716</v>
       </c>
       <c r="H1718" t="n">
         <v>20242520</v>
@@ -50336,7 +50336,7 @@
         <v>0.72759997844696</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.648061573505402</v>
+        <v>0.648061513900757</v>
       </c>
       <c r="H1723" t="n">
         <v>11884557</v>
@@ -50365,7 +50365,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.620806634426117</v>
+        <v>0.620806694030762</v>
       </c>
       <c r="H1724" t="n">
         <v>15320781</v>
@@ -50626,7 +50626,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.658215403556824</v>
+        <v>0.658215343952179</v>
       </c>
       <c r="H1733" t="n">
         <v>21488740</v>
@@ -50655,7 +50655,7 @@
         <v>0.758199989795685</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.675316512584686</v>
+        <v>0.675316452980042</v>
       </c>
       <c r="H1734" t="n">
         <v>33917790</v>
@@ -50713,7 +50713,7 @@
         <v>0.828599989414215</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.738020658493042</v>
+        <v>0.738020598888397</v>
       </c>
       <c r="H1736" t="n">
         <v>35628898</v>
@@ -50742,7 +50742,7 @@
         <v>0.958599984645844</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.853809475898743</v>
+        <v>0.853809535503387</v>
       </c>
       <c r="H1737" t="n">
         <v>99646498</v>
@@ -50800,7 +50800,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.876432955265045</v>
+        <v>0.8764328956604</v>
       </c>
       <c r="H1739" t="n">
         <v>39414006</v>
@@ -50829,7 +50829,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.873760879039764</v>
+        <v>0.87376081943512</v>
       </c>
       <c r="H1740" t="n">
         <v>36774205</v>
@@ -51003,7 +51003,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.882667720317841</v>
+        <v>0.882667660713196</v>
       </c>
       <c r="H1746" t="n">
         <v>44222060</v>
@@ -51061,7 +51061,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.919185638427734</v>
+        <v>0.919185698032379</v>
       </c>
       <c r="H1748" t="n">
         <v>60743048</v>
@@ -51090,7 +51090,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.957485139369965</v>
+        <v>0.957485198974609</v>
       </c>
       <c r="H1749" t="n">
         <v>38369686</v>
@@ -51148,7 +51148,7 @@
         <v>1.09650003910065</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.976634919643402</v>
+        <v>0.976634860038757</v>
       </c>
       <c r="H1751" t="n">
         <v>33789817</v>
@@ -51177,7 +51177,7 @@
         <v>1.03250002861023</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.919631123542786</v>
+        <v>0.919631063938141</v>
       </c>
       <c r="H1752" t="n">
         <v>95803812</v>
@@ -51206,7 +51206,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.92185777425766</v>
+        <v>0.921857714653015</v>
       </c>
       <c r="H1753" t="n">
         <v>44395351</v>
@@ -51322,7 +51322,7 @@
         <v>1.04649996757507</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.932100594043732</v>
+        <v>0.932100653648376</v>
       </c>
       <c r="H1757" t="n">
         <v>32064633</v>
@@ -51351,7 +51351,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.926311194896698</v>
+        <v>0.926311135292053</v>
       </c>
       <c r="H1758" t="n">
         <v>21110965</v>
@@ -51409,7 +51409,7 @@
         <v>1.04750001430511</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.932991325855255</v>
+        <v>0.93299126625061</v>
       </c>
       <c r="H1760" t="n">
         <v>40631058</v>
@@ -51438,7 +51438,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.912950932979584</v>
+        <v>0.912950873374939</v>
       </c>
       <c r="H1761" t="n">
         <v>26582079</v>
@@ -51467,7 +51467,7 @@
         <v>1.01950001716614</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.908052206039429</v>
+        <v>0.908052146434784</v>
       </c>
       <c r="H1762" t="n">
         <v>27481158</v>
@@ -51525,7 +51525,7 @@
         <v>1.04449999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.930319249629974</v>
+        <v>0.93031919002533</v>
       </c>
       <c r="H1764" t="n">
         <v>52512389</v>
@@ -51786,7 +51786,7 @@
         <v>1.00650000572205</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.896473288536072</v>
+        <v>0.896473228931427</v>
       </c>
       <c r="H1773" t="n">
         <v>22532469</v>
@@ -51844,7 +51844,7 @@
         <v>1.04949998855591</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.934772670269012</v>
+        <v>0.934772729873657</v>
       </c>
       <c r="H1775" t="n">
         <v>27222601</v>
@@ -51931,7 +51931,7 @@
         <v>1.10950005054474</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.988213717937469</v>
+        <v>0.988213777542114</v>
       </c>
       <c r="H1778" t="n">
         <v>33156068</v>
@@ -51989,7 +51989,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.977970898151398</v>
+        <v>0.977970957756042</v>
       </c>
       <c r="H1780" t="n">
         <v>82522322</v>
@@ -52047,7 +52047,7 @@
         <v>1.12750005722046</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.00424611568451</v>
+        <v>1.00424599647522</v>
       </c>
       <c r="H1782" t="n">
         <v>38953976</v>
@@ -52076,7 +52076,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.05456972122192</v>
+        <v>1.05456960201263</v>
       </c>
       <c r="H1783" t="n">
         <v>44539150</v>
@@ -52424,7 +52424,7 @@
         <v>1.31149995326996</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.16813170909882</v>
+        <v>1.16813182830811</v>
       </c>
       <c r="H1795" t="n">
         <v>88039189</v>
@@ -52685,7 +52685,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.25141084194183</v>
+        <v>1.25141072273254</v>
       </c>
       <c r="H1804" t="n">
         <v>50505371</v>
@@ -52772,7 +52772,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.23092496395111</v>
+        <v>1.2309250831604</v>
       </c>
       <c r="H1807" t="n">
         <v>27498297</v>
@@ -52801,7 +52801,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.21845543384552</v>
+        <v>1.21845555305481</v>
       </c>
       <c r="H1808" t="n">
         <v>27228579</v>
@@ -52946,7 +52946,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H1813" t="n">
         <v>201277103</v>
@@ -53062,7 +53062,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.25586426258087</v>
+        <v>1.25586414337158</v>
       </c>
       <c r="H1817" t="n">
         <v>26785082</v>
@@ -53149,7 +53149,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.24962937831879</v>
+        <v>1.24962949752808</v>
       </c>
       <c r="H1820" t="n">
         <v>28478257</v>
@@ -53236,7 +53236,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.31464922428131</v>
+        <v>1.3146493434906</v>
       </c>
       <c r="H1823" t="n">
         <v>73649010</v>
@@ -53265,7 +53265,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.35116732120514</v>
+        <v>1.35116744041443</v>
       </c>
       <c r="H1824" t="n">
         <v>173226691</v>
@@ -53294,7 +53294,7 @@
         <v>1.53450000286102</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.36675441265106</v>
+        <v>1.36675429344177</v>
       </c>
       <c r="H1825" t="n">
         <v>147696002</v>
@@ -53381,7 +53381,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.31643080711365</v>
+        <v>1.31643068790436</v>
       </c>
       <c r="H1828" t="n">
         <v>36445476</v>
@@ -53497,7 +53497,7 @@
         <v>1.35749995708466</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.20910322666168</v>
+        <v>1.20910334587097</v>
       </c>
       <c r="H1832" t="n">
         <v>30266079</v>
@@ -53555,7 +53555,7 @@
         <v>1.26549994945526</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.12716042995453</v>
+        <v>1.12716031074524</v>
       </c>
       <c r="H1834" t="n">
         <v>56083977</v>
@@ -53584,7 +53584,7 @@
         <v>1.14049994945526</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.01582479476929</v>
+        <v>1.01582491397858</v>
       </c>
       <c r="H1835" t="n">
         <v>70991471</v>
@@ -53671,7 +53671,7 @@
         <v>1.23450005054474</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.09954917430878</v>
+        <v>1.09954929351807</v>
       </c>
       <c r="H1838" t="n">
         <v>44048652</v>
@@ -53729,7 +53729,7 @@
         <v>1.32550001144409</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.1806013584137</v>
+        <v>1.18060147762299</v>
       </c>
       <c r="H1840" t="n">
         <v>26361553</v>
@@ -53758,7 +53758,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.14007520675659</v>
+        <v>1.14007532596588</v>
       </c>
       <c r="H1841" t="n">
         <v>30477091</v>
@@ -53932,7 +53932,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23181569576263</v>
+        <v>1.23181581497192</v>
       </c>
       <c r="H1847" t="n">
         <v>23160786</v>
@@ -53990,7 +53990,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1849" t="n">
         <v>61303523</v>
@@ -54512,7 +54512,7 @@
         <v>1.25049996376038</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.11380016803741</v>
+        <v>1.11380004882812</v>
       </c>
       <c r="H1867" t="n">
         <v>30080800</v>
@@ -54628,7 +54628,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.150763630867</v>
+        <v>1.15076351165771</v>
       </c>
       <c r="H1871" t="n">
         <v>24313190</v>
@@ -54715,7 +54715,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.13473117351532</v>
+        <v>1.13473129272461</v>
       </c>
       <c r="H1874" t="n">
         <v>17632468</v>
@@ -54802,7 +54802,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.12048029899597</v>
+        <v>1.12048017978668</v>
       </c>
       <c r="H1877" t="n">
         <v>12144067</v>
@@ -54831,7 +54831,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.15788888931274</v>
+        <v>1.15788900852203</v>
       </c>
       <c r="H1878" t="n">
         <v>28606803</v>
@@ -54976,7 +54976,7 @@
         <v>1.25750005245209</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.12003493309021</v>
+        <v>1.1200350522995</v>
       </c>
       <c r="H1883" t="n">
         <v>22657079</v>
@@ -55005,7 +55005,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.12226152420044</v>
+        <v>1.12226164340973</v>
       </c>
       <c r="H1884" t="n">
         <v>17046265</v>
@@ -55121,7 +55121,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.07416462898254</v>
+        <v>1.07416474819183</v>
       </c>
       <c r="H1888" t="n">
         <v>25051867</v>
@@ -55150,7 +55150,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.13473117351532</v>
+        <v>1.13473129272461</v>
       </c>
       <c r="H1889" t="n">
         <v>28793517</v>
@@ -55440,7 +55440,7 @@
         <v>1.25450003147125</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.11736285686493</v>
+        <v>1.11736297607422</v>
       </c>
       <c r="H1899" t="n">
         <v>19379185</v>
@@ -55498,7 +55498,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.08663439750671</v>
+        <v>1.08663427829742</v>
       </c>
       <c r="H1901" t="n">
         <v>20926564</v>
@@ -55585,7 +55585,7 @@
         <v>1.16250002384186</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.03542006015778</v>
+        <v>1.03541994094849</v>
       </c>
       <c r="H1904" t="n">
         <v>44264066</v>
@@ -55643,7 +55643,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.04833483695984</v>
+        <v>1.04833495616913</v>
       </c>
       <c r="H1906" t="n">
         <v>29040859</v>
@@ -55672,7 +55672,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.07772755622864</v>
+        <v>1.07772743701935</v>
       </c>
       <c r="H1907" t="n">
         <v>35754602</v>
@@ -55875,7 +55875,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.30039834976196</v>
+        <v>1.30039846897125</v>
       </c>
       <c r="H1914" t="n">
         <v>60137225</v>
@@ -55904,7 +55904,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.31108665466309</v>
+        <v>1.3110865354538</v>
       </c>
       <c r="H1915" t="n">
         <v>40402535</v>
@@ -55933,7 +55933,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.32266545295715</v>
+        <v>1.32266557216644</v>
       </c>
       <c r="H1916" t="n">
         <v>40030022</v>
@@ -56020,7 +56020,7 @@
         <v>1.43949997425079</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.28213930130005</v>
+        <v>1.28213942050934</v>
       </c>
       <c r="H1919" t="n">
         <v>27592628</v>
@@ -56049,7 +56049,7 @@
         <v>1.43250000476837</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.27590465545654</v>
+        <v>1.27590453624725</v>
       </c>
       <c r="H1920" t="n">
         <v>21395530</v>
@@ -56078,7 +56078,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.30039834976196</v>
+        <v>1.30039846897125</v>
       </c>
       <c r="H1921" t="n">
         <v>18806426</v>
@@ -56194,7 +56194,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.32800960540771</v>
+        <v>1.328009724617</v>
       </c>
       <c r="H1925" t="n">
         <v>26562115</v>
@@ -56281,7 +56281,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1928" t="n">
         <v>65561642</v>
@@ -56310,7 +56310,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1929" t="n">
         <v>29757990</v>
@@ -56339,7 +56339,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1930" t="n">
-        <v>1.29683554172516</v>
+        <v>1.29683566093445</v>
       </c>
       <c r="H1930" t="n">
         <v>46308940</v>
@@ -56368,7 +56368,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.29327297210693</v>
+        <v>1.29327285289764</v>
       </c>
       <c r="H1931" t="n">
         <v>26931723</v>
@@ -56426,7 +56426,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.25586426258087</v>
+        <v>1.25586414337158</v>
       </c>
       <c r="H1933" t="n">
         <v>26197753</v>
@@ -56484,7 +56484,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.24339473247528</v>
+        <v>1.24339461326599</v>
       </c>
       <c r="H1935" t="n">
         <v>23656707</v>
@@ -56658,7 +56658,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.304851770401</v>
+        <v>1.30485188961029</v>
       </c>
       <c r="H1941" t="n">
         <v>36097664</v>
@@ -56687,7 +56687,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H1942" t="n">
         <v>21886700</v>
@@ -56774,7 +56774,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.33869791030884</v>
+        <v>1.33869779109955</v>
       </c>
       <c r="H1945" t="n">
         <v>21109505</v>
@@ -56861,7 +56861,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.32266545295715</v>
+        <v>1.32266557216644</v>
       </c>
       <c r="H1948" t="n">
         <v>24397332</v>
@@ -56948,7 +56948,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1951" t="n">
-        <v>1.40193629264832</v>
+        <v>1.4019364118576</v>
       </c>
       <c r="H1951" t="n">
         <v>45002851</v>
@@ -56977,7 +56977,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.32800960540771</v>
+        <v>1.328009724617</v>
       </c>
       <c r="H1952" t="n">
         <v>124985920</v>
@@ -57093,7 +57093,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H1956" t="n">
         <v>39334965</v>
@@ -57151,7 +57151,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.37566125392914</v>
+        <v>1.37566113471985</v>
       </c>
       <c r="H1958" t="n">
         <v>66425360</v>
@@ -57238,7 +57238,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.41974997520447</v>
+        <v>1.41975009441376</v>
       </c>
       <c r="H1961" t="n">
         <v>31281838</v>
@@ -57325,7 +57325,7 @@
         <v>1.60950005054474</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.43355560302734</v>
+        <v>1.43355572223663</v>
       </c>
       <c r="H1964" t="n">
         <v>26138694</v>
@@ -57383,7 +57383,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.40104556083679</v>
+        <v>1.40104568004608</v>
       </c>
       <c r="H1966" t="n">
         <v>153129411</v>
@@ -57470,7 +57470,7 @@
         <v>1.46249997615814</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.30262506008148</v>
+        <v>1.30262517929077</v>
       </c>
       <c r="H1969" t="n">
         <v>26919423</v>
@@ -57499,7 +57499,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.27679526805878</v>
+        <v>1.27679538726807</v>
       </c>
       <c r="H1970" t="n">
         <v>26802260</v>
@@ -57528,7 +57528,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.29683554172516</v>
+        <v>1.29683566093445</v>
       </c>
       <c r="H1971" t="n">
         <v>25191162</v>
@@ -57731,7 +57731,7 @@
         <v>1.41849994659424</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.26343488693237</v>
+        <v>1.26343500614166</v>
       </c>
       <c r="H1978" t="n">
         <v>88712511</v>
@@ -57934,7 +57934,7 @@
         <v>1.5275000333786</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.36051952838898</v>
+        <v>1.36051964759827</v>
       </c>
       <c r="H1985" t="n">
         <v>16749025</v>
@@ -57992,7 +57992,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.37566125392914</v>
+        <v>1.37566113471985</v>
       </c>
       <c r="H1987" t="n">
         <v>51105926</v>
@@ -58021,7 +58021,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.29015552997589</v>
+        <v>1.29015564918518</v>
       </c>
       <c r="H1988" t="n">
         <v>67066172</v>
@@ -58079,7 +58079,7 @@
         <v>1.41449999809265</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.25987219810486</v>
+        <v>1.25987231731415</v>
       </c>
       <c r="H1990" t="n">
         <v>29949971</v>
@@ -58166,7 +58166,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.23626911640167</v>
+        <v>1.23626923561096</v>
       </c>
       <c r="H1993" t="n">
         <v>49894794</v>
@@ -58427,7 +58427,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H2002" t="n">
         <v>21379601</v>
@@ -58456,7 +58456,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.23805058002472</v>
+        <v>1.23805046081543</v>
       </c>
       <c r="H2003" t="n">
         <v>18744870</v>
@@ -58572,7 +58572,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H2007" t="n">
         <v>40689470</v>
@@ -58717,7 +58717,7 @@
         <v>1.44749999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>1.28926491737366</v>
+        <v>1.28926479816437</v>
       </c>
       <c r="H2012" t="n">
         <v>13752928</v>
@@ -58862,7 +58862,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H2017" t="n">
         <v>79262449</v>
@@ -58978,7 +58978,7 @@
         <v>1.46150004863739</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.30173456668854</v>
+        <v>1.30173444747925</v>
       </c>
       <c r="H2021" t="n">
         <v>32246011</v>
@@ -59007,7 +59007,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.24784815311432</v>
+        <v>1.24784803390503</v>
       </c>
       <c r="H2022" t="n">
         <v>61474648</v>
@@ -59036,7 +59036,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.24784815311432</v>
+        <v>1.24784803390503</v>
       </c>
       <c r="H2023" t="n">
         <v>34906238</v>
@@ -59123,7 +59123,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.22647154331207</v>
+        <v>1.22647166252136</v>
       </c>
       <c r="H2026" t="n">
         <v>31335128</v>
@@ -59210,7 +59210,7 @@
         <v>1.42050004005432</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.26521646976471</v>
+        <v>1.26521635055542</v>
       </c>
       <c r="H2029" t="n">
         <v>35969343</v>
@@ -59268,7 +59268,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.29015552997589</v>
+        <v>1.29015564918518</v>
       </c>
       <c r="H2031" t="n">
         <v>21961584</v>
@@ -59326,7 +59326,7 @@
         <v>1.44649994373322</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.28837418556213</v>
+        <v>1.28837406635284</v>
       </c>
       <c r="H2033" t="n">
         <v>15340362</v>
@@ -59384,7 +59384,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.32088422775269</v>
+        <v>1.3208841085434</v>
       </c>
       <c r="H2035" t="n">
         <v>16248522</v>
@@ -59413,7 +59413,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.30930519104004</v>
+        <v>1.30930531024933</v>
       </c>
       <c r="H2036" t="n">
         <v>16596498</v>
@@ -59471,7 +59471,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.32622826099396</v>
+        <v>1.32622814178467</v>
       </c>
       <c r="H2038" t="n">
         <v>31598891</v>
@@ -59558,7 +59558,7 @@
         <v>1.50650000572205</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.3418151140213</v>
+        <v>1.34181523323059</v>
       </c>
       <c r="H2041" t="n">
         <v>49175369</v>
@@ -59790,7 +59790,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.27679526805878</v>
+        <v>1.27679538726807</v>
       </c>
       <c r="H2049" t="n">
         <v>35782956</v>
@@ -59877,7 +59877,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31643080711365</v>
+        <v>1.31643068790436</v>
       </c>
       <c r="H2052" t="n">
         <v>70363678</v>
@@ -59964,7 +59964,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.34315133094788</v>
+        <v>1.34315121173859</v>
       </c>
       <c r="H2055" t="n">
         <v>21291896</v>
@@ -60399,7 +60399,7 @@
         <v>1.375</v>
       </c>
       <c r="G2070" t="n">
-        <v>1.2246903181076</v>
+        <v>1.22469019889832</v>
       </c>
       <c r="H2070" t="n">
         <v>37201230</v>
@@ -60486,7 +60486,7 @@
         <v>1.38100004196167</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.23003447055817</v>
+        <v>1.23003435134888</v>
       </c>
       <c r="H2073" t="n">
         <v>23884244</v>
@@ -60602,7 +60602,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.32979106903076</v>
+        <v>1.32979094982147</v>
       </c>
       <c r="H2077" t="n">
         <v>97981694</v>
@@ -60689,7 +60689,7 @@
         <v>1.82149994373322</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.62238049507141</v>
+        <v>1.6223806142807</v>
       </c>
       <c r="H2080" t="n">
         <v>170004032</v>
@@ -60776,7 +60776,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.723473072052</v>
+        <v>1.72347319126129</v>
       </c>
       <c r="H2083" t="n">
         <v>102058873</v>
@@ -60863,7 +60863,7 @@
         <v>1.97650003433228</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.76043653488159</v>
+        <v>1.76043665409088</v>
       </c>
       <c r="H2086" t="n">
         <v>36852781</v>
@@ -60979,7 +60979,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.87488949298859</v>
+        <v>1.87488961219788</v>
       </c>
       <c r="H2090" t="n">
         <v>47381130</v>
@@ -61008,7 +61008,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.88112425804138</v>
+        <v>1.88112413883209</v>
       </c>
       <c r="H2091" t="n">
         <v>28755854</v>
@@ -61037,7 +61037,7 @@
         <v>2.08699989318848</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.8588570356369</v>
+        <v>1.85885715484619</v>
       </c>
       <c r="H2092" t="n">
         <v>29642492</v>
@@ -61153,7 +61153,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.91318893432617</v>
+        <v>1.91318881511688</v>
       </c>
       <c r="H2096" t="n">
         <v>51280827</v>
@@ -61356,7 +61356,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.98889708518982</v>
+        <v>1.98889696598053</v>
       </c>
       <c r="H2103" t="n">
         <v>20444616</v>
@@ -61385,7 +61385,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2104" t="n">
-        <v>2.0076014995575</v>
+        <v>2.00760126113892</v>
       </c>
       <c r="H2104" t="n">
         <v>25187040</v>
@@ -61414,7 +61414,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G2105" t="n">
-        <v>2.00849223136902</v>
+        <v>2.00849199295044</v>
       </c>
       <c r="H2105" t="n">
         <v>29639951</v>
@@ -61472,7 +61472,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.06994891166687</v>
+        <v>2.06994915008545</v>
       </c>
       <c r="H2107" t="n">
         <v>41532484</v>
@@ -61530,7 +61530,7 @@
         <v>2.3970000743866</v>
       </c>
       <c r="G2109" t="n">
-        <v>2.13496899604797</v>
+        <v>2.13496923446655</v>
       </c>
       <c r="H2109" t="n">
         <v>81592175</v>
@@ -61559,7 +61559,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2110" t="n">
-        <v>2.08420014381409</v>
+        <v>2.08419990539551</v>
       </c>
       <c r="H2110" t="n">
         <v>42505018</v>
@@ -61646,7 +61646,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.99513173103333</v>
+        <v>1.99513185024261</v>
       </c>
       <c r="H2113" t="n">
         <v>34419597</v>
@@ -61675,7 +61675,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2114" t="n">
         <v>27318033</v>
@@ -61733,7 +61733,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.94258153438568</v>
+        <v>1.94258141517639</v>
       </c>
       <c r="H2116" t="n">
         <v>46811721</v>
@@ -61820,7 +61820,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.9719740152359</v>
+        <v>1.97197389602661</v>
       </c>
       <c r="H2119" t="n">
         <v>18487545</v>
@@ -61878,7 +61878,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.95237898826599</v>
+        <v>1.9523788690567</v>
       </c>
       <c r="H2121" t="n">
         <v>27702781</v>
@@ -61936,7 +61936,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.94079983234406</v>
+        <v>1.94080007076263</v>
       </c>
       <c r="H2123" t="n">
         <v>20243345</v>
@@ -62023,7 +62023,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2126" t="n">
-        <v>1.91318893432617</v>
+        <v>1.91318881511688</v>
       </c>
       <c r="H2126" t="n">
         <v>16042180</v>
@@ -62081,7 +62081,7 @@
         <v>2.13100004196167</v>
       </c>
       <c r="G2128" t="n">
-        <v>1.89804720878601</v>
+        <v>1.8980473279953</v>
       </c>
       <c r="H2128" t="n">
         <v>22011055</v>
@@ -62110,7 +62110,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2129" t="n">
         <v>19775385</v>
@@ -62168,7 +62168,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G2131" t="n">
-        <v>1.97019267082214</v>
+        <v>1.97019255161285</v>
       </c>
       <c r="H2131" t="n">
         <v>19971385</v>
@@ -62197,7 +62197,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2132" t="n">
-        <v>2.02541518211365</v>
+        <v>2.02541494369507</v>
       </c>
       <c r="H2132" t="n">
         <v>39975168</v>
@@ -62255,7 +62255,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2134" t="n">
-        <v>2.11359262466431</v>
+        <v>2.11359286308289</v>
       </c>
       <c r="H2134" t="n">
         <v>44554345</v>
@@ -62371,7 +62371,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2138" t="n">
-        <v>2.12160873413086</v>
+        <v>2.12160897254944</v>
       </c>
       <c r="H2138" t="n">
         <v>27147448</v>
@@ -62400,7 +62400,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2139" t="n">
-        <v>2.11359262466431</v>
+        <v>2.11359286308289</v>
       </c>
       <c r="H2139" t="n">
         <v>18307723</v>
@@ -62458,7 +62458,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2141" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2141" t="n">
         <v>13550932</v>
@@ -62516,7 +62516,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2143" t="n">
-        <v>1.98889708518982</v>
+        <v>1.98889696598053</v>
       </c>
       <c r="H2143" t="n">
         <v>26661132</v>
@@ -62574,7 +62574,7 @@
         <v>2.15300011634827</v>
       </c>
       <c r="G2145" t="n">
-        <v>1.9176424741745</v>
+        <v>1.91764235496521</v>
       </c>
       <c r="H2145" t="n">
         <v>22296682</v>
@@ -62603,7 +62603,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.92031419277191</v>
+        <v>1.9203143119812</v>
       </c>
       <c r="H2146" t="n">
         <v>35218310</v>
@@ -62632,7 +62632,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.9336746931076</v>
+        <v>1.93367457389832</v>
       </c>
       <c r="H2147" t="n">
         <v>17467441</v>
@@ -62661,7 +62661,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2148" t="n">
         <v>28506448</v>
@@ -62690,7 +62690,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.83926224708557</v>
+        <v>1.83926212787628</v>
       </c>
       <c r="H2149" t="n">
         <v>27905894</v>
@@ -62748,7 +62748,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2151" t="n">
         <v>33021803</v>
@@ -62835,7 +62835,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.86152923107147</v>
+        <v>1.86152911186218</v>
       </c>
       <c r="H2154" t="n">
         <v>35977989</v>
@@ -62864,7 +62864,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.86152923107147</v>
+        <v>1.86152911186218</v>
       </c>
       <c r="H2155" t="n">
         <v>22290014</v>
@@ -62893,7 +62893,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2156" t="n">
-        <v>1.89626586437225</v>
+        <v>1.89626574516296</v>
       </c>
       <c r="H2156" t="n">
         <v>21085975</v>
@@ -62922,7 +62922,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2157" t="n">
         <v>35756797</v>
@@ -62951,7 +62951,7 @@
         <v>2.15899991989136</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.92298638820648</v>
+        <v>1.92298626899719</v>
       </c>
       <c r="H2158" t="n">
         <v>16359113</v>
@@ -62980,7 +62980,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.99245977401733</v>
+        <v>1.99245965480804</v>
       </c>
       <c r="H2159" t="n">
         <v>39248301</v>
@@ -63096,7 +63096,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.13585996627808</v>
+        <v>2.1358597278595</v>
       </c>
       <c r="H2163" t="n">
         <v>33746318</v>
@@ -63212,7 +63212,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2167" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2167" t="n">
         <v>25601227</v>
@@ -63299,7 +63299,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G2170" t="n">
-        <v>2.07351207733154</v>
+        <v>2.07351183891296</v>
       </c>
       <c r="H2170" t="n">
         <v>26440425</v>
@@ -63328,7 +63328,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.06371450424194</v>
+        <v>2.06371426582336</v>
       </c>
       <c r="H2171" t="n">
         <v>26757191</v>
@@ -63357,7 +63357,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G2172" t="n">
-        <v>2.09666967391968</v>
+        <v>2.09666991233826</v>
       </c>
       <c r="H2172" t="n">
         <v>24912702</v>
@@ -63415,7 +63415,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2174" t="n">
-        <v>2.10913944244385</v>
+        <v>2.10913920402527</v>
       </c>
       <c r="H2174" t="n">
         <v>19724218</v>
@@ -63444,7 +63444,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.12339019775391</v>
+        <v>2.12339043617249</v>
       </c>
       <c r="H2175" t="n">
         <v>29130431</v>
@@ -63473,7 +63473,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.14476680755615</v>
+        <v>2.14476656913757</v>
       </c>
       <c r="H2176" t="n">
         <v>16678363</v>
@@ -63560,7 +63560,7 @@
         <v>2.41899991035461</v>
       </c>
       <c r="G2179" t="n">
-        <v>2.15456414222717</v>
+        <v>2.15456390380859</v>
       </c>
       <c r="H2179" t="n">
         <v>23246952</v>
@@ -63618,7 +63618,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2181" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2181" t="n">
         <v>45523587</v>
@@ -63647,7 +63647,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G2182" t="n">
-        <v>1.9844434261322</v>
+        <v>1.98444354534149</v>
       </c>
       <c r="H2182" t="n">
         <v>44868347</v>
@@ -63705,7 +63705,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.94614410400391</v>
+        <v>1.9461442232132</v>
       </c>
       <c r="H2184" t="n">
         <v>18067908</v>
@@ -63734,7 +63734,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2185" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2185" t="n">
         <v>20351307</v>
@@ -63763,7 +63763,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.94079983234406</v>
+        <v>1.94080007076263</v>
       </c>
       <c r="H2186" t="n">
         <v>18512647</v>
@@ -63879,7 +63879,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G2190" t="n">
-        <v>1.79294657707214</v>
+        <v>1.79294645786285</v>
       </c>
       <c r="H2190" t="n">
         <v>24047004</v>
@@ -63995,7 +63995,7 @@
         <v>1.98450005054474</v>
       </c>
       <c r="G2194" t="n">
-        <v>1.7675621509552</v>
+        <v>1.76756203174591</v>
       </c>
       <c r="H2194" t="n">
         <v>23362020</v>
@@ -64140,7 +64140,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G2199" t="n">
-        <v>1.8428248167038</v>
+        <v>1.84282493591309</v>
       </c>
       <c r="H2199" t="n">
         <v>32985049</v>
@@ -64227,7 +64227,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.84549689292908</v>
+        <v>1.84549701213837</v>
       </c>
       <c r="H2202" t="n">
         <v>16439030</v>
@@ -64256,7 +64256,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.81521368026733</v>
+        <v>1.81521379947662</v>
       </c>
       <c r="H2203" t="n">
         <v>23581831</v>
@@ -64343,7 +64343,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2206" t="n">
         <v>19255054</v>
@@ -64372,7 +64372,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2207" t="n">
-        <v>1.80185329914093</v>
+        <v>1.80185341835022</v>
       </c>
       <c r="H2207" t="n">
         <v>12789945</v>
@@ -64401,7 +64401,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.67448568344116</v>
+        <v>1.67448556423187</v>
       </c>
       <c r="H2208" t="n">
         <v>53900944</v>
@@ -64430,7 +64430,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.71189439296722</v>
+        <v>1.71189427375793</v>
       </c>
       <c r="H2209" t="n">
         <v>35189302</v>
@@ -64546,7 +64546,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G2213" t="n">
-        <v>1.60055899620056</v>
+        <v>1.60055887699127</v>
       </c>
       <c r="H2213" t="n">
         <v>37765591</v>
@@ -64575,7 +64575,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.62727928161621</v>
+        <v>1.6272794008255</v>
       </c>
       <c r="H2214" t="n">
         <v>22594695</v>
@@ -64865,7 +64865,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.81343233585358</v>
+        <v>1.81343221664429</v>
       </c>
       <c r="H2224" t="n">
         <v>24725349</v>
@@ -65097,7 +65097,7 @@
         <v>2.05699992179871</v>
       </c>
       <c r="G2232" t="n">
-        <v>1.83213651180267</v>
+        <v>1.83213663101196</v>
       </c>
       <c r="H2232" t="n">
         <v>29472348</v>
@@ -65155,7 +65155,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2234" t="n">
-        <v>1.79027450084686</v>
+        <v>1.79027438163757</v>
       </c>
       <c r="H2234" t="n">
         <v>16876658</v>
@@ -65184,7 +65184,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.80185329914093</v>
+        <v>1.80185341835022</v>
       </c>
       <c r="H2235" t="n">
         <v>20529123</v>
@@ -65358,7 +65358,7 @@
         <v>1.99150002002716</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.77379679679871</v>
+        <v>1.773796916008</v>
       </c>
       <c r="H2241" t="n">
         <v>46698722</v>
@@ -65416,7 +65416,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2243" t="n">
-        <v>1.83926224708557</v>
+        <v>1.83926212787628</v>
       </c>
       <c r="H2243" t="n">
         <v>48994310</v>
@@ -65445,7 +65445,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G2244" t="n">
-        <v>1.80630683898926</v>
+        <v>1.80630695819855</v>
       </c>
       <c r="H2244" t="n">
         <v>29352657</v>
@@ -65474,7 +65474,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G2245" t="n">
-        <v>1.89003109931946</v>
+        <v>1.89003121852875</v>
       </c>
       <c r="H2245" t="n">
         <v>81646961</v>
@@ -65503,7 +65503,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.94970667362213</v>
+        <v>1.94970679283142</v>
       </c>
       <c r="H2246" t="n">
         <v>74141845</v>
@@ -65561,7 +65561,7 @@
         <v>2.16300010681152</v>
       </c>
       <c r="G2248" t="n">
-        <v>1.92654931545258</v>
+        <v>1.92654919624329</v>
       </c>
       <c r="H2248" t="n">
         <v>30842480</v>
@@ -65590,7 +65590,7 @@
         <v>2.16700005531311</v>
       </c>
       <c r="G2249" t="n">
-        <v>1.9301118850708</v>
+        <v>1.93011200428009</v>
       </c>
       <c r="H2249" t="n">
         <v>30050128</v>
@@ -65619,7 +65619,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2250" t="n">
-        <v>1.94525349140167</v>
+        <v>1.94525361061096</v>
       </c>
       <c r="H2250" t="n">
         <v>26979522</v>
@@ -65648,7 +65648,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2251" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2251" t="n">
         <v>53288446</v>
@@ -65677,7 +65677,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2252" t="n">
         <v>41701778</v>
@@ -65735,7 +65735,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2254" t="n">
-        <v>2.00314807891846</v>
+        <v>2.00314784049988</v>
       </c>
       <c r="H2254" t="n">
         <v>44091922</v>
@@ -65793,7 +65793,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2256" t="n">
-        <v>2.06994891166687</v>
+        <v>2.06994915008545</v>
       </c>
       <c r="H2256" t="n">
         <v>54666411</v>
@@ -65880,7 +65880,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2259" t="n">
-        <v>2.0530264377594</v>
+        <v>2.05302619934082</v>
       </c>
       <c r="H2259" t="n">
         <v>24934085</v>
@@ -65909,7 +65909,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2260" t="n">
-        <v>2.06371450424194</v>
+        <v>2.06371426582336</v>
       </c>
       <c r="H2260" t="n">
         <v>40038315</v>
@@ -65938,7 +65938,7 @@
         <v>2.33299994468689</v>
       </c>
       <c r="G2261" t="n">
-        <v>2.077965259552</v>
+        <v>2.07796549797058</v>
       </c>
       <c r="H2261" t="n">
         <v>34552742</v>
@@ -65967,7 +65967,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2262" t="n">
-        <v>2.10913944244385</v>
+        <v>2.10913920402527</v>
       </c>
       <c r="H2262" t="n">
         <v>21092827</v>
@@ -66170,7 +66170,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G2269" t="n">
-        <v>2.1652524471283</v>
+        <v>2.16525220870972</v>
       </c>
       <c r="H2269" t="n">
         <v>38389055</v>
@@ -66315,7 +66315,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G2274" t="n">
-        <v>2.26768112182617</v>
+        <v>2.26768088340759</v>
       </c>
       <c r="H2274" t="n">
         <v>31890329</v>
@@ -66431,7 +66431,7 @@
         <v>2.48699998855591</v>
       </c>
       <c r="G2278" t="n">
-        <v>2.21513056755066</v>
+        <v>2.21513080596924</v>
       </c>
       <c r="H2278" t="n">
         <v>18431422</v>
@@ -66518,7 +66518,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2281" t="n">
-        <v>2.29262018203735</v>
+        <v>2.29261994361877</v>
       </c>
       <c r="H2281" t="n">
         <v>22696347</v>
@@ -66547,7 +66547,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2282" t="n">
-        <v>2.31577777862549</v>
+        <v>2.31577801704407</v>
       </c>
       <c r="H2282" t="n">
         <v>26132220</v>
@@ -66634,7 +66634,7 @@
         <v>2.64299988746643</v>
       </c>
       <c r="G2285" t="n">
-        <v>2.35407710075378</v>
+        <v>2.35407733917236</v>
       </c>
       <c r="H2285" t="n">
         <v>60652789</v>
@@ -66721,7 +66721,7 @@
         <v>2.51099991798401</v>
       </c>
       <c r="G2288" t="n">
-        <v>2.23650717735291</v>
+        <v>2.23650693893433</v>
       </c>
       <c r="H2288" t="n">
         <v>15785363</v>
@@ -66750,7 +66750,7 @@
         <v>2.5090000629425</v>
       </c>
       <c r="G2289" t="n">
-        <v>2.23472571372986</v>
+        <v>2.23472595214844</v>
       </c>
       <c r="H2289" t="n">
         <v>11480911</v>
@@ -66924,7 +66924,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G2295" t="n">
-        <v>2.45294308662415</v>
+        <v>2.45294332504272</v>
       </c>
       <c r="H2295" t="n">
         <v>20214762</v>
@@ -67040,7 +67040,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G2299" t="n">
-        <v>2.31221532821655</v>
+        <v>2.31221508979797</v>
       </c>
       <c r="H2299" t="n">
         <v>74870654</v>
@@ -67098,7 +67098,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G2301" t="n">
-        <v>2.27658796310425</v>
+        <v>2.27658772468567</v>
       </c>
       <c r="H2301" t="n">
         <v>30195449</v>
@@ -67127,7 +67127,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G2302" t="n">
-        <v>2.25164890289307</v>
+        <v>2.25164866447449</v>
       </c>
       <c r="H2302" t="n">
         <v>24626119</v>
@@ -67156,7 +67156,7 @@
         <v>2.51300001144409</v>
       </c>
       <c r="G2303" t="n">
-        <v>2.23828864097595</v>
+        <v>2.23828840255737</v>
       </c>
       <c r="H2303" t="n">
         <v>20104873</v>
@@ -67214,7 +67214,7 @@
         <v>2.48300004005432</v>
       </c>
       <c r="G2305" t="n">
-        <v>2.21156811714172</v>
+        <v>2.21156787872314</v>
       </c>
       <c r="H2305" t="n">
         <v>27751479</v>
@@ -67243,7 +67243,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G2306" t="n">
-        <v>2.14832925796509</v>
+        <v>2.14832949638367</v>
       </c>
       <c r="H2306" t="n">
         <v>43140551</v>
@@ -67272,7 +67272,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2307" t="n">
-        <v>2.12160873413086</v>
+        <v>2.12160897254944</v>
       </c>
       <c r="H2307" t="n">
         <v>24111895</v>
@@ -67504,7 +67504,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2315" t="n">
-        <v>2.04411959648132</v>
+        <v>2.04411935806274</v>
       </c>
       <c r="H2315" t="n">
         <v>24791375</v>
@@ -67562,7 +67562,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G2317" t="n">
-        <v>2.04768204689026</v>
+        <v>2.04768228530884</v>
       </c>
       <c r="H2317" t="n">
         <v>21357944</v>
@@ -67707,7 +67707,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G2322" t="n">
-        <v>2.05658888816833</v>
+        <v>2.05658912658691</v>
       </c>
       <c r="H2322" t="n">
         <v>15248097</v>
@@ -67794,7 +67794,7 @@
         <v>2.28099989891052</v>
       </c>
       <c r="G2325" t="n">
-        <v>2.03164958953857</v>
+        <v>2.03164982795715</v>
       </c>
       <c r="H2325" t="n">
         <v>20004250</v>
@@ -67823,7 +67823,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G2326" t="n">
-        <v>2.06816792488098</v>
+        <v>2.0681676864624</v>
       </c>
       <c r="H2326" t="n">
         <v>27029721</v>
@@ -67910,7 +67910,7 @@
         <v>2.20300006866455</v>
       </c>
       <c r="G2329" t="n">
-        <v>1.96217656135559</v>
+        <v>1.9621764421463</v>
       </c>
       <c r="H2329" t="n">
         <v>165427959</v>
@@ -67939,7 +67939,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2330" t="n">
-        <v>2.00314807891846</v>
+        <v>2.00314784049988</v>
       </c>
       <c r="H2330" t="n">
         <v>90357314</v>
@@ -67997,7 +67997,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2332" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2332" t="n">
         <v>49106059</v>
@@ -68055,7 +68055,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2334" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2334" t="n">
         <v>47390121</v>
@@ -68200,7 +68200,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G2339" t="n">
-        <v>1.85440373420715</v>
+        <v>1.85440385341644</v>
       </c>
       <c r="H2339" t="n">
         <v>52881442</v>
@@ -68287,7 +68287,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2342" t="n">
-        <v>1.89626586437225</v>
+        <v>1.89626574516296</v>
       </c>
       <c r="H2342" t="n">
         <v>54335801</v>
@@ -68316,7 +68316,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.93278384208679</v>
+        <v>1.93278396129608</v>
       </c>
       <c r="H2343" t="n">
         <v>54028041</v>
@@ -68345,7 +68345,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2344" t="n">
         <v>32171346</v>
@@ -68432,7 +68432,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2347" t="n">
-        <v>1.9684112071991</v>
+        <v>1.96841132640839</v>
       </c>
       <c r="H2347" t="n">
         <v>31365241</v>
@@ -68461,7 +68461,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2348" t="n">
-        <v>1.94525349140167</v>
+        <v>1.94525361061096</v>
       </c>
       <c r="H2348" t="n">
         <v>43704455</v>
@@ -68519,7 +68519,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G2350" t="n">
-        <v>1.95861351490021</v>
+        <v>1.9586136341095</v>
       </c>
       <c r="H2350" t="n">
         <v>35346168</v>
@@ -68548,7 +68548,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2351" t="n">
-        <v>1.9336746931076</v>
+        <v>1.93367457389832</v>
       </c>
       <c r="H2351" t="n">
         <v>29069827</v>
@@ -68635,7 +68635,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2354" t="n">
-        <v>1.89537525177002</v>
+        <v>1.89537537097931</v>
       </c>
       <c r="H2354" t="n">
         <v>33627039</v>
@@ -68664,7 +68664,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.72436392307281</v>
+        <v>1.72436380386353</v>
       </c>
       <c r="H2355" t="n">
         <v>85443225</v>
@@ -68838,7 +68838,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G2361" t="n">
-        <v>1.52128791809082</v>
+        <v>1.52128803730011</v>
       </c>
       <c r="H2361" t="n">
         <v>38867170</v>
@@ -68867,7 +68867,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G2362" t="n">
-        <v>1.56493151187897</v>
+        <v>1.56493139266968</v>
       </c>
       <c r="H2362" t="n">
         <v>50829326</v>
@@ -69041,7 +69041,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G2368" t="n">
-        <v>1.749302983284</v>
+        <v>1.74930310249329</v>
       </c>
       <c r="H2368" t="n">
         <v>65053471</v>
@@ -69128,7 +69128,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.82590186595917</v>
+        <v>1.82590174674988</v>
       </c>
       <c r="H2371" t="n">
         <v>29975796</v>
@@ -69186,7 +69186,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2373" t="n">
-        <v>1.8526223897934</v>
+        <v>1.85262227058411</v>
       </c>
       <c r="H2373" t="n">
         <v>37413416</v>
@@ -69215,7 +69215,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G2374" t="n">
-        <v>1.83302736282349</v>
+        <v>1.83302748203278</v>
       </c>
       <c r="H2374" t="n">
         <v>32042896</v>
@@ -69244,7 +69244,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G2375" t="n">
-        <v>1.82768321037292</v>
+        <v>1.82768332958221</v>
       </c>
       <c r="H2375" t="n">
         <v>38839501</v>
@@ -69273,7 +69273,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G2376" t="n">
-        <v>1.83837127685547</v>
+        <v>1.83837139606476</v>
       </c>
       <c r="H2376" t="n">
         <v>30420999</v>
@@ -69331,7 +69331,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G2378" t="n">
-        <v>1.93990933895111</v>
+        <v>1.9399094581604</v>
       </c>
       <c r="H2378" t="n">
         <v>64329397</v>
@@ -80038,6 +80038,35 @@
         <v>9721756</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>4.47499990463257</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>4.48299980163574</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>4.21600008010864</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>4.21600008010864</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>4.21600008010864</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>20543618</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -80070,6 +80070,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>4.2649998664856</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>4.39200019836426</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>4.24399995803833</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>4.39200019836426</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>4.39200019836426</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>17690897</v>
+      </c>
+      <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>22.8775520324707</v>
       </c>
       <c r="G2" t="n">
-        <v>20.2849197387695</v>
+        <v>20.2849216461182</v>
       </c>
       <c r="H2" t="n">
         <v>974058</v>
@@ -514,7 +514,7 @@
         <v>21.9295864105225</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4443836212158</v>
+        <v>19.4443855285645</v>
       </c>
       <c r="H5" t="n">
         <v>1112292</v>
@@ -543,7 +543,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540729522705</v>
+        <v>18.9540710449219</v>
       </c>
       <c r="H6" t="n">
         <v>681723</v>
@@ -601,7 +601,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.8786602020264</v>
+        <v>19.878662109375</v>
       </c>
       <c r="H8" t="n">
         <v>1620392</v>
@@ -688,7 +688,7 @@
         <v>20.9184246063232</v>
       </c>
       <c r="G11" t="n">
-        <v>18.547815322876</v>
+        <v>18.5478134155273</v>
       </c>
       <c r="H11" t="n">
         <v>1339292</v>
@@ -862,7 +862,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552736282349</v>
+        <v>13.9552726745605</v>
       </c>
       <c r="H17" t="n">
         <v>354113</v>
@@ -949,7 +949,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087121963501</v>
+        <v>12.6087112426758</v>
       </c>
       <c r="H20" t="n">
         <v>1225889</v>
@@ -1007,7 +1007,7 @@
         <v>14.358302116394</v>
       </c>
       <c r="G22" t="n">
-        <v>12.7311277389526</v>
+        <v>12.7311267852783</v>
       </c>
       <c r="H22" t="n">
         <v>659234</v>
@@ -1036,7 +1036,7 @@
         <v>13.8813648223877</v>
       </c>
       <c r="G23" t="n">
-        <v>12.30823802948</v>
+        <v>12.3082389831543</v>
       </c>
       <c r="H23" t="n">
         <v>760726</v>
@@ -1152,7 +1152,7 @@
         <v>9.75209808349609</v>
       </c>
       <c r="G27" t="n">
-        <v>8.64692783355713</v>
+        <v>8.64692687988281</v>
       </c>
       <c r="H27" t="n">
         <v>1596070</v>
@@ -1210,7 +1210,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G29" t="n">
-        <v>8.05711078643799</v>
+        <v>8.0571117401123</v>
       </c>
       <c r="H29" t="n">
         <v>5695730</v>
@@ -1268,7 +1268,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G31" t="n">
-        <v>6.70832395553589</v>
+        <v>6.70832443237305</v>
       </c>
       <c r="H31" t="n">
         <v>7709298</v>
@@ -1297,7 +1297,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393510818481</v>
+        <v>6.74393558502197</v>
       </c>
       <c r="H32" t="n">
         <v>7100655</v>
@@ -1326,7 +1326,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.87747859954834</v>
+        <v>6.8774790763855</v>
       </c>
       <c r="H33" t="n">
         <v>7581026</v>
@@ -1355,7 +1355,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51181030273438</v>
+        <v>7.51180934906006</v>
       </c>
       <c r="H34" t="n">
         <v>6329665</v>
@@ -1471,7 +1471,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243886947632</v>
+        <v>7.91243982315063</v>
       </c>
       <c r="H38" t="n">
         <v>4762357</v>
@@ -1674,7 +1674,7 @@
         <v>9.67679214477539</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58015632629395</v>
+        <v>8.58015537261963</v>
       </c>
       <c r="H45" t="n">
         <v>3665603</v>
@@ -1877,7 +1877,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683204650879</v>
+        <v>8.58683300018311</v>
       </c>
       <c r="H52" t="n">
         <v>4362352</v>
@@ -1935,7 +1935,7 @@
         <v>9.26261138916016</v>
       </c>
       <c r="G54" t="n">
-        <v>8.21291255950928</v>
+        <v>8.21291351318359</v>
       </c>
       <c r="H54" t="n">
         <v>3721362</v>
@@ -1964,7 +1964,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.31752109527588</v>
+        <v>8.3175220489502</v>
       </c>
       <c r="H55" t="n">
         <v>4485559</v>
@@ -2225,7 +2225,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870714187622</v>
+        <v>7.65870809555054</v>
       </c>
       <c r="H64" t="n">
         <v>2688899</v>
@@ -2283,7 +2283,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973592758179</v>
+        <v>6.89973640441895</v>
       </c>
       <c r="H66" t="n">
         <v>4271134</v>
@@ -2341,7 +2341,7 @@
         <v>7.61341381072998</v>
       </c>
       <c r="G68" t="n">
-        <v>6.75061225891113</v>
+        <v>6.75061273574829</v>
       </c>
       <c r="H68" t="n">
         <v>2618453</v>
@@ -2370,7 +2370,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365779876709</v>
+        <v>7.27365732192993</v>
       </c>
       <c r="H69" t="n">
         <v>3294930</v>
@@ -2573,7 +2573,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H76" t="n">
         <v>3700496</v>
@@ -2718,7 +2718,7 @@
         <v>9.55128288269043</v>
       </c>
       <c r="G81" t="n">
-        <v>8.46887016296387</v>
+        <v>8.46886920928955</v>
       </c>
       <c r="H81" t="n">
         <v>3453580</v>
@@ -2776,7 +2776,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G83" t="n">
-        <v>9.68188858032227</v>
+        <v>9.68188762664795</v>
       </c>
       <c r="H83" t="n">
         <v>13679976</v>
@@ -2834,7 +2834,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H85" t="n">
         <v>3915352</v>
@@ -2979,7 +2979,7 @@
         <v>9.36803913116455</v>
       </c>
       <c r="G90" t="n">
-        <v>8.30639266967773</v>
+        <v>8.30639171600342</v>
       </c>
       <c r="H90" t="n">
         <v>2595903</v>
@@ -3095,7 +3095,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.26855373382568</v>
+        <v>8.2685546875</v>
       </c>
       <c r="H94" t="n">
         <v>2791506</v>
@@ -3153,7 +3153,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G96" t="n">
-        <v>8.31974697113037</v>
+        <v>8.31974601745605</v>
       </c>
       <c r="H96" t="n">
         <v>2286483</v>
@@ -3211,7 +3211,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588752746582</v>
+        <v>7.98588848114014</v>
       </c>
       <c r="H98" t="n">
         <v>4712589</v>
@@ -3269,7 +3269,7 @@
         <v>8.92875480651855</v>
       </c>
       <c r="G100" t="n">
-        <v>7.91689109802246</v>
+        <v>7.91689014434814</v>
       </c>
       <c r="H100" t="n">
         <v>1802404</v>
@@ -3298,7 +3298,7 @@
         <v>9.14212131500244</v>
       </c>
       <c r="G101" t="n">
-        <v>8.10607719421387</v>
+        <v>8.10607814788818</v>
       </c>
       <c r="H101" t="n">
         <v>2228168</v>
@@ -3501,7 +3501,7 @@
         <v>9.04924392700195</v>
       </c>
       <c r="G108" t="n">
-        <v>8.02372550964355</v>
+        <v>8.02372455596924</v>
       </c>
       <c r="H108" t="n">
         <v>2261709</v>
@@ -3588,7 +3588,7 @@
         <v>9.5261812210083</v>
       </c>
       <c r="G111" t="n">
-        <v>8.44661235809326</v>
+        <v>8.44661331176758</v>
       </c>
       <c r="H111" t="n">
         <v>3958468</v>
@@ -3617,7 +3617,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837078094482</v>
       </c>
       <c r="H112" t="n">
         <v>4508416</v>
@@ -3646,7 +3646,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G113" t="n">
-        <v>8.67363548278809</v>
+        <v>8.6736364364624</v>
       </c>
       <c r="H113" t="n">
         <v>2693817</v>
@@ -3762,7 +3762,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808242797852</v>
+        <v>7.96808338165283</v>
       </c>
       <c r="H117" t="n">
         <v>3606977</v>
@@ -3849,7 +3849,7 @@
         <v>9.80230236053467</v>
       </c>
       <c r="G120" t="n">
-        <v>8.69144153594971</v>
+        <v>8.69144248962402</v>
       </c>
       <c r="H120" t="n">
         <v>4234729</v>
@@ -3907,7 +3907,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76488971710205</v>
+        <v>8.76489067077637</v>
       </c>
       <c r="H122" t="n">
         <v>3417145</v>
@@ -3936,7 +3936,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G123" t="n">
-        <v>9.00749397277832</v>
+        <v>9.007493019104</v>
       </c>
       <c r="H123" t="n">
         <v>3474390</v>
@@ -3965,7 +3965,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933666229248</v>
+        <v>8.05933570861816</v>
       </c>
       <c r="H124" t="n">
         <v>4551998</v>
@@ -4197,7 +4197,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G132" t="n">
-        <v>7.82341051101685</v>
+        <v>7.82341146469116</v>
       </c>
       <c r="H132" t="n">
         <v>3383064</v>
@@ -4313,7 +4313,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420257568359</v>
+        <v>9.03420352935791</v>
       </c>
       <c r="H136" t="n">
         <v>5039193</v>
@@ -4371,7 +4371,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G138" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H138" t="n">
         <v>2932449</v>
@@ -4458,7 +4458,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G141" t="n">
-        <v>9.55947303771973</v>
+        <v>9.55947208404541</v>
       </c>
       <c r="H141" t="n">
         <v>3718667</v>
@@ -4516,7 +4516,7 @@
         <v>10.8590927124023</v>
       </c>
       <c r="G143" t="n">
-        <v>9.6284704208374</v>
+        <v>9.62846946716309</v>
       </c>
       <c r="H143" t="n">
         <v>2762374</v>
@@ -4632,7 +4632,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427219390869</v>
+        <v>9.78427124023438</v>
       </c>
       <c r="H147" t="n">
         <v>3288854</v>
@@ -4661,7 +4661,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G148" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H148" t="n">
         <v>11514563</v>
@@ -4835,7 +4835,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228736877441</v>
+        <v>8.5222864151001</v>
       </c>
       <c r="H154" t="n">
         <v>2111524</v>
@@ -5096,7 +5096,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H163" t="n">
         <v>1929655</v>
@@ -5154,7 +5154,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122665405273</v>
+        <v>9.26122570037842</v>
       </c>
       <c r="H165" t="n">
         <v>1784826</v>
@@ -5183,7 +5183,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G166" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H166" t="n">
         <v>2357597</v>
@@ -5241,7 +5241,7 @@
         <v>10.442400932312</v>
       </c>
       <c r="G168" t="n">
-        <v>9.25899982452393</v>
+        <v>9.25900077819824</v>
       </c>
       <c r="H168" t="n">
         <v>1567170</v>
@@ -5270,7 +5270,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G169" t="n">
-        <v>9.0809440612793</v>
+        <v>9.08094310760498</v>
       </c>
       <c r="H169" t="n">
         <v>1117249</v>
@@ -5328,7 +5328,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548873901367</v>
+        <v>9.14548778533936</v>
       </c>
       <c r="H171" t="n">
         <v>1904678</v>
@@ -5473,7 +5473,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G176" t="n">
-        <v>9.20780944824219</v>
+        <v>9.2078104019165</v>
       </c>
       <c r="H176" t="n">
         <v>1550105</v>
@@ -5560,7 +5560,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G179" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H179" t="n">
         <v>3246340</v>
@@ -5821,7 +5821,7 @@
         <v>9.28771305084229</v>
       </c>
       <c r="G188" t="n">
-        <v>8.23516941070557</v>
+        <v>8.23516845703125</v>
       </c>
       <c r="H188" t="n">
         <v>1917572</v>
@@ -6024,7 +6024,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H195" t="n">
         <v>3058208</v>
@@ -6053,7 +6053,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G196" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H196" t="n">
         <v>2921152</v>
@@ -6082,7 +6082,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G197" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H197" t="n">
         <v>2803083</v>
@@ -6314,7 +6314,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H205" t="n">
         <v>2047802</v>
@@ -6430,7 +6430,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G209" t="n">
-        <v>9.68188858032227</v>
+        <v>9.68188762664795</v>
       </c>
       <c r="H209" t="n">
         <v>3157831</v>
@@ -6488,7 +6488,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H211" t="n">
         <v>10102433</v>
@@ -6517,7 +6517,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G212" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H212" t="n">
         <v>3931503</v>
@@ -6546,7 +6546,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H213" t="n">
         <v>3655602</v>
@@ -6894,7 +6894,7 @@
         <v>10.2240142822266</v>
       </c>
       <c r="G225" t="n">
-        <v>9.06536388397217</v>
+        <v>9.06536293029785</v>
       </c>
       <c r="H225" t="n">
         <v>2711291</v>
@@ -6923,7 +6923,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072246551514</v>
+        <v>8.94072341918945</v>
       </c>
       <c r="H226" t="n">
         <v>2515113</v>
@@ -6981,7 +6981,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G228" t="n">
-        <v>8.67363548278809</v>
+        <v>8.6736364364624</v>
       </c>
       <c r="H228" t="n">
         <v>3095637</v>
@@ -7039,7 +7039,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G230" t="n">
-        <v>8.9451732635498</v>
+        <v>8.94517421722412</v>
       </c>
       <c r="H230" t="n">
         <v>2705648</v>
@@ -7068,7 +7068,7 @@
         <v>10.2215042114258</v>
       </c>
       <c r="G231" t="n">
-        <v>9.06313705444336</v>
+        <v>9.06313800811768</v>
       </c>
       <c r="H231" t="n">
         <v>2430715</v>
@@ -7126,7 +7126,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G233" t="n">
-        <v>8.92514228820801</v>
+        <v>8.92514324188232</v>
       </c>
       <c r="H233" t="n">
         <v>1340077</v>
@@ -7561,7 +7561,7 @@
         <v>12.2748422622681</v>
       </c>
       <c r="G248" t="n">
-        <v>10.8837776184082</v>
+        <v>10.8837785720825</v>
       </c>
       <c r="H248" t="n">
         <v>3278242</v>
@@ -7619,7 +7619,7 @@
         <v>12.8019819259644</v>
       </c>
       <c r="G250" t="n">
-        <v>11.3511781692505</v>
+        <v>11.3511791229248</v>
       </c>
       <c r="H250" t="n">
         <v>3391155</v>
@@ -7677,7 +7677,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G252" t="n">
-        <v>11.2844085693359</v>
+        <v>11.2844076156616</v>
       </c>
       <c r="H252" t="n">
         <v>3211844</v>
@@ -7822,7 +7822,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076108932495</v>
+        <v>11.9076099395752</v>
       </c>
       <c r="H257" t="n">
         <v>1775884</v>
@@ -7909,7 +7909,7 @@
         <v>13.9817733764648</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3972682952881</v>
+        <v>12.3972692489624</v>
       </c>
       <c r="H260" t="n">
         <v>3761116</v>
@@ -7938,7 +7938,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195261001587</v>
+        <v>12.4195251464844</v>
       </c>
       <c r="H261" t="n">
         <v>2771934</v>
@@ -7967,7 +7967,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858243942261</v>
+        <v>12.1858253479004</v>
       </c>
       <c r="H262" t="n">
         <v>2214682</v>
@@ -8054,7 +8054,7 @@
         <v>13.1032047271729</v>
       </c>
       <c r="G265" t="n">
-        <v>11.6182651519775</v>
+        <v>11.6182661056519</v>
       </c>
       <c r="H265" t="n">
         <v>3089766</v>
@@ -8141,7 +8141,7 @@
         <v>12.2999439239502</v>
       </c>
       <c r="G268" t="n">
-        <v>10.9060354232788</v>
+        <v>10.9060344696045</v>
       </c>
       <c r="H268" t="n">
         <v>3796302</v>
@@ -8170,7 +8170,7 @@
         <v>12.5635137557983</v>
       </c>
       <c r="G269" t="n">
-        <v>11.1397352218628</v>
+        <v>11.1397342681885</v>
       </c>
       <c r="H269" t="n">
         <v>3707353</v>
@@ -8199,7 +8199,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G270" t="n">
-        <v>11.2844085693359</v>
+        <v>11.2844076156616</v>
       </c>
       <c r="H270" t="n">
         <v>3414444</v>
@@ -8228,7 +8228,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619939804077</v>
+        <v>11.1619930267334</v>
       </c>
       <c r="H271" t="n">
         <v>2083536</v>
@@ -8257,7 +8257,7 @@
         <v>12.6011667251587</v>
       </c>
       <c r="G272" t="n">
-        <v>11.1731214523315</v>
+        <v>11.1731204986572</v>
       </c>
       <c r="H272" t="n">
         <v>2804708</v>
@@ -8315,7 +8315,7 @@
         <v>12.5007591247559</v>
       </c>
       <c r="G274" t="n">
-        <v>11.0840930938721</v>
+        <v>11.0840921401978</v>
       </c>
       <c r="H274" t="n">
         <v>2614176</v>
@@ -8373,7 +8373,7 @@
         <v>13.1283073425293</v>
       </c>
       <c r="G276" t="n">
-        <v>11.6405229568481</v>
+        <v>11.6405220031738</v>
       </c>
       <c r="H276" t="n">
         <v>2868878</v>
@@ -8576,7 +8576,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.251672744751</v>
+        <v>10.2516717910767</v>
       </c>
       <c r="H283" t="n">
         <v>3104757</v>
@@ -8692,7 +8692,7 @@
         <v>11.707537651062</v>
       </c>
       <c r="G287" t="n">
-        <v>10.3807649612427</v>
+        <v>10.3807640075684</v>
       </c>
       <c r="H287" t="n">
         <v>2250311</v>
@@ -8750,7 +8750,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651838302612</v>
+        <v>10.3651847839355</v>
       </c>
       <c r="H289" t="n">
         <v>3308303</v>
@@ -8837,7 +8837,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H292" t="n">
         <v>2600664</v>
@@ -8953,7 +8953,7 @@
         <v>11.3310089111328</v>
       </c>
       <c r="G296" t="n">
-        <v>10.0469055175781</v>
+        <v>10.0469064712524</v>
       </c>
       <c r="H296" t="n">
         <v>2645855</v>
@@ -9098,7 +9098,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486450195312</v>
+        <v>9.45486354827881</v>
       </c>
       <c r="H301" t="n">
         <v>3459059</v>
@@ -9127,7 +9127,7 @@
         <v>10.6984405517578</v>
       </c>
       <c r="G302" t="n">
-        <v>9.48602485656738</v>
+        <v>9.48602390289307</v>
       </c>
       <c r="H302" t="n">
         <v>2707699</v>
@@ -9243,7 +9243,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G306" t="n">
-        <v>9.00749397277832</v>
+        <v>9.007493019104</v>
       </c>
       <c r="H306" t="n">
         <v>4803773</v>
@@ -9272,7 +9272,7 @@
         <v>10.1386680603027</v>
       </c>
       <c r="G307" t="n">
-        <v>8.9896879196167</v>
+        <v>8.98968887329102</v>
       </c>
       <c r="H307" t="n">
         <v>3615164</v>
@@ -9388,7 +9388,7 @@
         <v>10.3244218826294</v>
       </c>
       <c r="G311" t="n">
-        <v>9.15439128875732</v>
+        <v>9.15439224243164</v>
       </c>
       <c r="H311" t="n">
         <v>3767044</v>
@@ -9446,7 +9446,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G313" t="n">
-        <v>9.01639652252197</v>
+        <v>9.01639747619629</v>
       </c>
       <c r="H313" t="n">
         <v>2624769</v>
@@ -9475,7 +9475,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539390563965</v>
+        <v>9.08539485931396</v>
       </c>
       <c r="H314" t="n">
         <v>3039918</v>
@@ -9504,7 +9504,7 @@
         <v>10.1336479187012</v>
       </c>
       <c r="G315" t="n">
-        <v>8.98523807525635</v>
+        <v>8.98523712158203</v>
       </c>
       <c r="H315" t="n">
         <v>3230495</v>
@@ -9562,7 +9562,7 @@
         <v>10.1562385559082</v>
       </c>
       <c r="G317" t="n">
-        <v>9.00526714324951</v>
+        <v>9.00526809692383</v>
       </c>
       <c r="H317" t="n">
         <v>2490908</v>
@@ -9591,7 +9591,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H318" t="n">
         <v>3081207</v>
@@ -9649,7 +9649,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G320" t="n">
-        <v>9.46154117584229</v>
+        <v>9.4615421295166</v>
       </c>
       <c r="H320" t="n">
         <v>4855845</v>
@@ -9707,7 +9707,7 @@
         <v>10.6808700561523</v>
       </c>
       <c r="G322" t="n">
-        <v>9.47044563293457</v>
+        <v>9.47044467926025</v>
       </c>
       <c r="H322" t="n">
         <v>3003542</v>
@@ -9736,7 +9736,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981853485107</v>
+        <v>9.77981948852539</v>
       </c>
       <c r="H323" t="n">
         <v>5715259</v>
@@ -9794,7 +9794,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G325" t="n">
-        <v>9.51050758361816</v>
+        <v>9.51050853729248</v>
       </c>
       <c r="H325" t="n">
         <v>3181766</v>
@@ -9881,7 +9881,7 @@
         <v>10.5227270126343</v>
       </c>
       <c r="G328" t="n">
-        <v>9.33022308349609</v>
+        <v>9.33022403717041</v>
       </c>
       <c r="H328" t="n">
         <v>2488647</v>
@@ -9910,7 +9910,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H329" t="n">
         <v>3030394</v>
@@ -9939,7 +9939,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G330" t="n">
-        <v>9.12990951538086</v>
+        <v>9.12990856170654</v>
       </c>
       <c r="H330" t="n">
         <v>3092166</v>
@@ -9968,7 +9968,7 @@
         <v>10.2691984176636</v>
       </c>
       <c r="G331" t="n">
-        <v>9.10542583465576</v>
+        <v>9.10542678833008</v>
       </c>
       <c r="H331" t="n">
         <v>2262671</v>
@@ -10171,7 +10171,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.20335865020752</v>
+        <v>9.2033576965332</v>
       </c>
       <c r="H338" t="n">
         <v>3676909</v>
@@ -10287,7 +10287,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837078094482</v>
       </c>
       <c r="H342" t="n">
         <v>3153124</v>
@@ -10345,7 +10345,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G344" t="n">
-        <v>8.87840270996094</v>
+        <v>8.87840175628662</v>
       </c>
       <c r="H344" t="n">
         <v>4939603</v>
@@ -10432,7 +10432,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G347" t="n">
-        <v>8.87840270996094</v>
+        <v>8.87840175628662</v>
       </c>
       <c r="H347" t="n">
         <v>4232992</v>
@@ -10664,7 +10664,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G355" t="n">
-        <v>8.86282348632812</v>
+        <v>8.86282253265381</v>
       </c>
       <c r="H355" t="n">
         <v>4334969</v>
@@ -10693,7 +10693,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H356" t="n">
         <v>1939986</v>
@@ -10780,7 +10780,7 @@
         <v>9.36301803588867</v>
       </c>
       <c r="G359" t="n">
-        <v>8.30193996429443</v>
+        <v>8.30194091796875</v>
       </c>
       <c r="H359" t="n">
         <v>3581572</v>
@@ -10809,7 +10809,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H360" t="n">
         <v>1852849</v>
@@ -10896,7 +10896,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033975601196</v>
+        <v>7.99033880233765</v>
       </c>
       <c r="H363" t="n">
         <v>4201110</v>
@@ -11012,7 +11012,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215579986572</v>
+        <v>7.73215675354004</v>
       </c>
       <c r="H367" t="n">
         <v>4573774</v>
@@ -11041,7 +11041,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209337234497</v>
       </c>
       <c r="H368" t="n">
         <v>4145288</v>
@@ -11099,7 +11099,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G370" t="n">
-        <v>8.05711078643799</v>
+        <v>8.0571117401123</v>
       </c>
       <c r="H370" t="n">
         <v>5171240</v>
@@ -11244,7 +11244,7 @@
         <v>8.27861499786377</v>
       </c>
       <c r="G375" t="n">
-        <v>7.34042882919312</v>
+        <v>7.34042930603027</v>
       </c>
       <c r="H375" t="n">
         <v>3956309</v>
@@ -11273,7 +11273,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G376" t="n">
-        <v>7.1979832649231</v>
+        <v>7.19798278808594</v>
       </c>
       <c r="H376" t="n">
         <v>3156325</v>
@@ -11360,7 +11360,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H379" t="n">
         <v>2182310</v>
@@ -11447,7 +11447,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817245483398</v>
+        <v>7.31817197799683</v>
       </c>
       <c r="H382" t="n">
         <v>2594435</v>
@@ -11505,7 +11505,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G384" t="n">
-        <v>7.1979832649231</v>
+        <v>7.19798278808594</v>
       </c>
       <c r="H384" t="n">
         <v>2069812</v>
@@ -11563,7 +11563,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.6965446472168</v>
+        <v>7.69654560089111</v>
       </c>
       <c r="H386" t="n">
         <v>4250748</v>
@@ -11708,7 +11708,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390846252441</v>
+        <v>7.43390941619873</v>
       </c>
       <c r="H391" t="n">
         <v>1190917</v>
@@ -11824,7 +11824,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.85679721832275</v>
+        <v>7.85679626464844</v>
       </c>
       <c r="H395" t="n">
         <v>2325966</v>
@@ -11882,7 +11882,7 @@
         <v>8.52461433410645</v>
       </c>
       <c r="G397" t="n">
-        <v>7.55854988098145</v>
+        <v>7.55854940414429</v>
       </c>
       <c r="H397" t="n">
         <v>2332643</v>
@@ -11940,7 +11940,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842311859131</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H399" t="n">
         <v>1479093</v>
@@ -11969,7 +11969,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196756362915</v>
+        <v>7.61196660995483</v>
       </c>
       <c r="H400" t="n">
         <v>2662388</v>
@@ -12114,7 +12114,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G405" t="n">
-        <v>7.70099496841431</v>
+        <v>7.70099592208862</v>
       </c>
       <c r="H405" t="n">
         <v>3030024</v>
@@ -12143,7 +12143,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209337234497</v>
       </c>
       <c r="H406" t="n">
         <v>2779239</v>
@@ -12172,7 +12172,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757966995239</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H407" t="n">
         <v>1870136</v>
@@ -12259,7 +12259,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428636550903</v>
+        <v>7.67428731918335</v>
       </c>
       <c r="H410" t="n">
         <v>1678906</v>
@@ -12346,7 +12346,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G413" t="n">
-        <v>7.50513172149658</v>
+        <v>7.5051326751709</v>
       </c>
       <c r="H413" t="n">
         <v>2055106</v>
@@ -12375,7 +12375,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249792098999</v>
+        <v>7.24249744415283</v>
       </c>
       <c r="H414" t="n">
         <v>3391728</v>
@@ -12404,7 +12404,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701210021973</v>
+        <v>7.28701162338257</v>
       </c>
       <c r="H415" t="n">
         <v>1909890</v>
@@ -12462,7 +12462,7 @@
         <v>8.15812587738037</v>
       </c>
       <c r="G417" t="n">
-        <v>7.23359441757202</v>
+        <v>7.23359394073486</v>
       </c>
       <c r="H417" t="n">
         <v>3351310</v>
@@ -12491,7 +12491,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G418" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H418" t="n">
         <v>1896151</v>
@@ -12520,7 +12520,7 @@
         <v>8.08281993865967</v>
       </c>
       <c r="G419" t="n">
-        <v>7.16682195663452</v>
+        <v>7.16682243347168</v>
       </c>
       <c r="H419" t="n">
         <v>1874275</v>
@@ -12578,7 +12578,7 @@
         <v>7.84184217453003</v>
       </c>
       <c r="G421" t="n">
-        <v>6.95315361022949</v>
+        <v>6.95315408706665</v>
       </c>
       <c r="H421" t="n">
         <v>2449535</v>
@@ -12636,7 +12636,7 @@
         <v>7.70127105712891</v>
       </c>
       <c r="G423" t="n">
-        <v>6.82851362228394</v>
+        <v>6.82851314544678</v>
       </c>
       <c r="H423" t="n">
         <v>3972357</v>
@@ -12665,7 +12665,7 @@
         <v>7.68621015548706</v>
       </c>
       <c r="G424" t="n">
-        <v>6.8151593208313</v>
+        <v>6.81515884399414</v>
       </c>
       <c r="H424" t="n">
         <v>2199628</v>
@@ -12752,7 +12752,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.9397988319397</v>
+        <v>6.93979930877686</v>
       </c>
       <c r="H427" t="n">
         <v>6403078</v>
@@ -12868,7 +12868,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G431" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H431" t="n">
         <v>5992264</v>
@@ -12926,7 +12926,7 @@
         <v>7.96233081817627</v>
       </c>
       <c r="G433" t="n">
-        <v>7.05998849868774</v>
+        <v>7.05998802185059</v>
       </c>
       <c r="H433" t="n">
         <v>2066064</v>
@@ -12955,7 +12955,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591417312622</v>
+        <v>7.29591464996338</v>
       </c>
       <c r="H434" t="n">
         <v>3040311</v>
@@ -13071,7 +13071,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.4739727973938</v>
+        <v>7.47397184371948</v>
       </c>
       <c r="H438" t="n">
         <v>2774137</v>
@@ -13158,7 +13158,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538381576538</v>
       </c>
       <c r="H441" t="n">
         <v>3163095</v>
@@ -13187,7 +13187,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G442" t="n">
-        <v>7.70099496841431</v>
+        <v>7.70099592208862</v>
       </c>
       <c r="H442" t="n">
         <v>2989271</v>
@@ -13245,7 +13245,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491779327393</v>
+        <v>8.07491683959961</v>
       </c>
       <c r="H444" t="n">
         <v>9651321</v>
@@ -13448,7 +13448,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692350387573</v>
+        <v>7.93692255020142</v>
       </c>
       <c r="H451" t="n">
         <v>4589432</v>
@@ -13477,7 +13477,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504360198975</v>
+        <v>8.15504264831543</v>
       </c>
       <c r="H452" t="n">
         <v>4598808</v>
@@ -13767,7 +13767,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H462" t="n">
         <v>5765617</v>
@@ -13796,7 +13796,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.42945718765259</v>
+        <v>7.4294581413269</v>
       </c>
       <c r="H463" t="n">
         <v>3847044</v>
@@ -13912,7 +13912,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538381576538</v>
       </c>
       <c r="H467" t="n">
         <v>3470929</v>
@@ -13941,7 +13941,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G468" t="n">
-        <v>7.64312648773193</v>
+        <v>7.64312744140625</v>
       </c>
       <c r="H468" t="n">
         <v>2766448</v>
@@ -14028,7 +14028,7 @@
         <v>9.53371143341064</v>
       </c>
       <c r="G471" t="n">
-        <v>8.45328998565674</v>
+        <v>8.45328903198242</v>
       </c>
       <c r="H471" t="n">
         <v>8570157</v>
@@ -14115,7 +14115,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H474" t="n">
         <v>5603952</v>
@@ -14144,7 +14144,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H475" t="n">
         <v>5013333</v>
@@ -14318,7 +14318,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757966995239</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H481" t="n">
         <v>6391732</v>
@@ -14405,7 +14405,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209337234497</v>
       </c>
       <c r="H484" t="n">
         <v>3256857</v>
@@ -14492,7 +14492,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344244003296</v>
+        <v>7.84344148635864</v>
       </c>
       <c r="H487" t="n">
         <v>2436747</v>
@@ -14637,7 +14637,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G492" t="n">
-        <v>7.50513172149658</v>
+        <v>7.5051326751709</v>
       </c>
       <c r="H492" t="n">
         <v>28943183</v>
@@ -14666,7 +14666,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G493" t="n">
-        <v>7.64312648773193</v>
+        <v>7.64312744140625</v>
       </c>
       <c r="H493" t="n">
         <v>7994237</v>
@@ -14840,7 +14840,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.6342248916626</v>
+        <v>7.63422393798828</v>
       </c>
       <c r="H499" t="n">
         <v>4090789</v>
@@ -15130,7 +15130,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H509" t="n">
         <v>5719334</v>
@@ -15246,7 +15246,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.50225639343262</v>
+        <v>8.5022554397583</v>
       </c>
       <c r="H513" t="n">
         <v>2779890</v>
@@ -15304,7 +15304,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H515" t="n">
         <v>3023534</v>
@@ -15362,7 +15362,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H517" t="n">
         <v>4311139</v>
@@ -15449,7 +15449,7 @@
         <v>10.1763210296631</v>
       </c>
       <c r="G520" t="n">
-        <v>9.02307510375977</v>
+        <v>9.02307415008545</v>
       </c>
       <c r="H520" t="n">
         <v>5305812</v>
@@ -15507,7 +15507,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G522" t="n">
-        <v>9.12990951538086</v>
+        <v>9.12990856170654</v>
       </c>
       <c r="H522" t="n">
         <v>5817803</v>
@@ -15536,7 +15536,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H523" t="n">
         <v>4786463</v>
@@ -15681,7 +15681,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G528" t="n">
-        <v>9.16552066802979</v>
+        <v>9.16551971435547</v>
       </c>
       <c r="H528" t="n">
         <v>3314321</v>
@@ -15768,7 +15768,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833885192871</v>
+        <v>8.83833980560303</v>
       </c>
       <c r="H531" t="n">
         <v>2823997</v>
@@ -15855,7 +15855,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.41990375518799</v>
+        <v>8.4199047088623</v>
       </c>
       <c r="H534" t="n">
         <v>2981971</v>
@@ -15942,7 +15942,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G537" t="n">
-        <v>7.82341051101685</v>
+        <v>7.82341146469116</v>
       </c>
       <c r="H537" t="n">
         <v>8270004</v>
@@ -16029,7 +16029,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196756362915</v>
+        <v>7.61196660995483</v>
       </c>
       <c r="H540" t="n">
         <v>7866114</v>
@@ -16116,7 +16116,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49623012542725</v>
+        <v>7.49622917175293</v>
       </c>
       <c r="H543" t="n">
         <v>5612249</v>
@@ -16319,7 +16319,7 @@
         <v>8.83587837219238</v>
       </c>
       <c r="G550" t="n">
-        <v>7.83453893661499</v>
+        <v>7.83453989028931</v>
       </c>
       <c r="H550" t="n">
         <v>5628339</v>
@@ -16464,7 +16464,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368829727173</v>
+        <v>7.29368877410889</v>
       </c>
       <c r="H555" t="n">
         <v>4043829</v>
@@ -16493,7 +16493,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G556" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H556" t="n">
         <v>4331827</v>
@@ -16580,7 +16580,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663948059082</v>
+        <v>7.7566385269165</v>
       </c>
       <c r="H559" t="n">
         <v>3729295</v>
@@ -16696,7 +16696,7 @@
         <v>8.32379913330078</v>
       </c>
       <c r="G563" t="n">
-        <v>7.38049268722534</v>
+        <v>7.38049221038818</v>
       </c>
       <c r="H563" t="n">
         <v>3760036</v>
@@ -16754,7 +16754,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613481521606</v>
+        <v>7.43613386154175</v>
       </c>
       <c r="H565" t="n">
         <v>3258776</v>
@@ -16783,7 +16783,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585174560547</v>
       </c>
       <c r="H566" t="n">
         <v>4081106</v>
@@ -17015,7 +17015,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H574" t="n">
         <v>1774619</v>
@@ -17305,7 +17305,7 @@
         <v>8.1079216003418</v>
       </c>
       <c r="G584" t="n">
-        <v>7.18907928466797</v>
+        <v>7.18907976150513</v>
       </c>
       <c r="H584" t="n">
         <v>3472564</v>
@@ -17392,7 +17392,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842311859131</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H587" t="n">
         <v>5249327</v>
@@ -17421,7 +17421,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610431671143</v>
+        <v>7.41610336303711</v>
       </c>
       <c r="H588" t="n">
         <v>4009682</v>
@@ -17537,7 +17537,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766731262207</v>
+        <v>6.99766778945923</v>
       </c>
       <c r="H592" t="n">
         <v>4887233</v>
@@ -17595,7 +17595,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443929672241</v>
+        <v>7.06443977355957</v>
       </c>
       <c r="H594" t="n">
         <v>3740621</v>
@@ -17653,7 +17653,7 @@
         <v>7.92969799041748</v>
       </c>
       <c r="G596" t="n">
-        <v>7.03105354309082</v>
+        <v>7.03105306625366</v>
       </c>
       <c r="H596" t="n">
         <v>3230176</v>
@@ -17798,7 +17798,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H601" t="n">
         <v>4478703</v>
@@ -17943,7 +17943,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H606" t="n">
         <v>9737590</v>
@@ -18001,7 +18001,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G608" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H608" t="n">
         <v>4747845</v>
@@ -18088,7 +18088,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37538909912109</v>
+        <v>8.37539005279541</v>
       </c>
       <c r="H611" t="n">
         <v>5678009</v>
@@ -18262,7 +18262,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H617" t="n">
         <v>5676159</v>
@@ -18320,7 +18320,7 @@
         <v>9.42326259613037</v>
       </c>
       <c r="G619" t="n">
-        <v>8.35535717010498</v>
+        <v>8.3553581237793</v>
       </c>
       <c r="H619" t="n">
         <v>6500575</v>
@@ -18349,7 +18349,7 @@
         <v>9.31783485412598</v>
       </c>
       <c r="G620" t="n">
-        <v>8.26187801361084</v>
+        <v>8.26187705993652</v>
       </c>
       <c r="H620" t="n">
         <v>3046319</v>
@@ -18407,7 +18407,7 @@
         <v>9.72448635101318</v>
       </c>
       <c r="G622" t="n">
-        <v>8.62244415283203</v>
+        <v>8.62244510650635</v>
       </c>
       <c r="H622" t="n">
         <v>5253374</v>
@@ -18465,7 +18465,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902599334717</v>
+        <v>8.56902694702148</v>
       </c>
       <c r="H624" t="n">
         <v>3124054</v>
@@ -18494,7 +18494,7 @@
         <v>9.47848701477051</v>
       </c>
       <c r="G625" t="n">
-        <v>8.40432357788086</v>
+        <v>8.40432453155518</v>
       </c>
       <c r="H625" t="n">
         <v>3369292</v>
@@ -18871,7 +18871,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H638" t="n">
         <v>2970699</v>
@@ -18900,7 +18900,7 @@
         <v>9.86254692077637</v>
       </c>
       <c r="G639" t="n">
-        <v>8.74485874176025</v>
+        <v>8.74485969543457</v>
       </c>
       <c r="H639" t="n">
         <v>2222101</v>
@@ -19074,7 +19074,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009727478027</v>
+        <v>9.25009822845459</v>
       </c>
       <c r="H645" t="n">
         <v>6365259</v>
@@ -19161,7 +19161,7 @@
         <v>10.0181789398193</v>
       </c>
       <c r="G648" t="n">
-        <v>8.88285350799561</v>
+        <v>8.88285446166992</v>
       </c>
       <c r="H648" t="n">
         <v>3244003</v>
@@ -19190,7 +19190,7 @@
         <v>10.0608520507812</v>
       </c>
       <c r="G649" t="n">
-        <v>8.92069149017334</v>
+        <v>8.92069053649902</v>
       </c>
       <c r="H649" t="n">
         <v>3535639</v>
@@ -19219,7 +19219,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G650" t="n">
-        <v>9.01639652252197</v>
+        <v>9.01639747619629</v>
       </c>
       <c r="H650" t="n">
         <v>2301830</v>
@@ -19277,7 +19277,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100505828857</v>
+        <v>9.12100601196289</v>
       </c>
       <c r="H652" t="n">
         <v>2816086</v>
@@ -19422,7 +19422,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H657" t="n">
         <v>3819447</v>
@@ -19509,7 +19509,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G660" t="n">
-        <v>9.84659194946289</v>
+        <v>9.84659099578857</v>
       </c>
       <c r="H660" t="n">
         <v>3631961</v>
@@ -19538,7 +19538,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G661" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H661" t="n">
         <v>5649923</v>
@@ -19567,7 +19567,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H662" t="n">
         <v>5059956</v>
@@ -19625,7 +19625,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H664" t="n">
         <v>4580403</v>
@@ -19683,7 +19683,7 @@
         <v>11.2331123352051</v>
       </c>
       <c r="G666" t="n">
-        <v>9.96010303497314</v>
+        <v>9.96010398864746</v>
       </c>
       <c r="H666" t="n">
         <v>2694360</v>
@@ -19712,7 +19712,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G667" t="n">
-        <v>9.87107372283936</v>
+        <v>9.87107467651367</v>
       </c>
       <c r="H667" t="n">
         <v>3825674</v>
@@ -19741,7 +19741,7 @@
         <v>11.200478553772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.93116760253906</v>
+        <v>9.93116855621338</v>
       </c>
       <c r="H668" t="n">
         <v>2563518</v>
@@ -19770,7 +19770,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139925003052</v>
+        <v>10.3139934539795</v>
       </c>
       <c r="H669" t="n">
         <v>8750009</v>
@@ -19799,7 +19799,7 @@
         <v>11.4414577484131</v>
       </c>
       <c r="G670" t="n">
-        <v>10.1448383331299</v>
+        <v>10.1448373794556</v>
       </c>
       <c r="H670" t="n">
         <v>4154794</v>
@@ -20002,7 +20002,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H677" t="n">
         <v>2314476</v>
@@ -20118,7 +20118,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H681" t="n">
         <v>2245212</v>
@@ -20176,7 +20176,7 @@
         <v>11.700008392334</v>
       </c>
       <c r="G683" t="n">
-        <v>10.3740882873535</v>
+        <v>10.3740873336792</v>
       </c>
       <c r="H683" t="n">
         <v>3804319</v>
@@ -20350,7 +20350,7 @@
         <v>11.9259252548218</v>
       </c>
       <c r="G689" t="n">
-        <v>10.5744018554688</v>
+        <v>10.5744028091431</v>
       </c>
       <c r="H689" t="n">
         <v>2992968</v>
@@ -20408,7 +20408,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H691" t="n">
         <v>4155413</v>
@@ -20524,7 +20524,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.7569122314453</v>
+        <v>10.756911277771</v>
       </c>
       <c r="H695" t="n">
         <v>4827551</v>
@@ -20611,7 +20611,7 @@
         <v>13.1232872009277</v>
       </c>
       <c r="G698" t="n">
-        <v>11.6360721588135</v>
+        <v>11.6360712051392</v>
       </c>
       <c r="H698" t="n">
         <v>8601699</v>
@@ -20640,7 +20640,7 @@
         <v>13.2086343765259</v>
       </c>
       <c r="G699" t="n">
-        <v>11.7117471694946</v>
+        <v>11.7117462158203</v>
       </c>
       <c r="H699" t="n">
         <v>7959306</v>
@@ -20988,7 +20988,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395784378052</v>
+        <v>11.0395774841309</v>
       </c>
       <c r="H711" t="n">
         <v>3266745</v>
@@ -21162,7 +21162,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364070892334</v>
+        <v>10.4364080429077</v>
       </c>
       <c r="H717" t="n">
         <v>3926528</v>
@@ -21365,7 +21365,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H724" t="n">
         <v>4731058</v>
@@ -21394,7 +21394,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H725" t="n">
         <v>5437862</v>
@@ -21423,7 +21423,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H726" t="n">
         <v>2638902</v>
@@ -21510,7 +21510,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006391525269</v>
+        <v>10.3006381988525</v>
       </c>
       <c r="H729" t="n">
         <v>3047850</v>
@@ -21597,7 +21597,7 @@
         <v>11.1377248764038</v>
       </c>
       <c r="G732" t="n">
-        <v>9.87552642822266</v>
+        <v>9.87552547454834</v>
       </c>
       <c r="H732" t="n">
         <v>3029135</v>
@@ -21655,7 +21655,7 @@
         <v>10.6607875823975</v>
       </c>
       <c r="G734" t="n">
-        <v>9.45263767242432</v>
+        <v>9.45263862609863</v>
       </c>
       <c r="H734" t="n">
         <v>4394592</v>
@@ -21684,7 +21684,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580421447754</v>
+        <v>9.34580516815186</v>
       </c>
       <c r="H735" t="n">
         <v>2646670</v>
@@ -21800,7 +21800,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081249237061</v>
+        <v>8.29081153869629</v>
       </c>
       <c r="H739" t="n">
         <v>8509660</v>
@@ -21916,7 +21916,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219158172607</v>
+        <v>8.46219253540039</v>
       </c>
       <c r="H743" t="n">
         <v>3711740</v>
@@ -22003,7 +22003,7 @@
         <v>9.69938373565674</v>
       </c>
       <c r="G746" t="n">
-        <v>8.60018634796143</v>
+        <v>8.60018730163574</v>
       </c>
       <c r="H746" t="n">
         <v>4899103</v>
@@ -22148,7 +22148,7 @@
         <v>9.75209808349609</v>
       </c>
       <c r="G751" t="n">
-        <v>8.64692783355713</v>
+        <v>8.64692687988281</v>
       </c>
       <c r="H751" t="n">
         <v>7331392</v>
@@ -22206,7 +22206,7 @@
         <v>9.33540630340576</v>
       </c>
       <c r="G753" t="n">
-        <v>8.27745819091797</v>
+        <v>8.27745723724365</v>
       </c>
       <c r="H753" t="n">
         <v>2716829</v>
@@ -22264,7 +22264,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466617584229</v>
+        <v>7.91466522216797</v>
       </c>
       <c r="H755" t="n">
         <v>4636928</v>
@@ -22322,7 +22322,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G757" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H757" t="n">
         <v>6552833</v>
@@ -22351,7 +22351,7 @@
         <v>8.25602340698242</v>
       </c>
       <c r="G758" t="n">
-        <v>7.32039785385132</v>
+        <v>7.32039737701416</v>
       </c>
       <c r="H758" t="n">
         <v>7880235</v>
@@ -22467,7 +22467,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873331069946</v>
+        <v>6.96873378753662</v>
       </c>
       <c r="H762" t="n">
         <v>4541420</v>
@@ -22496,7 +22496,7 @@
         <v>8.19577884674072</v>
       </c>
       <c r="G763" t="n">
-        <v>7.26698017120361</v>
+        <v>7.26698064804077</v>
       </c>
       <c r="H763" t="n">
         <v>4297434</v>
@@ -22525,7 +22525,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G764" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H764" t="n">
         <v>3809859</v>
@@ -22786,7 +22786,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096832275391</v>
+        <v>8.39096927642822</v>
       </c>
       <c r="H773" t="n">
         <v>2691134</v>
@@ -22815,7 +22815,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H774" t="n">
         <v>4518486</v>
@@ -23018,7 +23018,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G781" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H781" t="n">
         <v>3452225</v>
@@ -23047,7 +23047,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G782" t="n">
-        <v>8.86282348632812</v>
+        <v>8.86282253265381</v>
       </c>
       <c r="H782" t="n">
         <v>3274045</v>
@@ -23076,7 +23076,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G783" t="n">
-        <v>8.9451732635498</v>
+        <v>8.94517421722412</v>
       </c>
       <c r="H783" t="n">
         <v>2493851</v>
@@ -23105,7 +23105,7 @@
         <v>10.1763210296631</v>
       </c>
       <c r="G784" t="n">
-        <v>9.02307510375977</v>
+        <v>9.02307415008545</v>
       </c>
       <c r="H784" t="n">
         <v>2474098</v>
@@ -23337,7 +23337,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G792" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H792" t="n">
         <v>1988992</v>
@@ -23424,7 +23424,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G795" t="n">
-        <v>9.0809440612793</v>
+        <v>9.08094310760498</v>
       </c>
       <c r="H795" t="n">
         <v>2539926</v>
@@ -23743,7 +23743,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232986450195</v>
+        <v>9.96232891082764</v>
       </c>
       <c r="H806" t="n">
         <v>5597634</v>
@@ -23801,7 +23801,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496036529541</v>
+        <v>10.3496046066284</v>
       </c>
       <c r="H808" t="n">
         <v>2858722</v>
@@ -24091,7 +24091,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371948242188</v>
+        <v>10.9371957778931</v>
       </c>
       <c r="H818" t="n">
         <v>2377360</v>
@@ -24323,7 +24323,7 @@
         <v>11.8355579376221</v>
       </c>
       <c r="G826" t="n">
-        <v>10.4942760467529</v>
+        <v>10.4942770004272</v>
       </c>
       <c r="H826" t="n">
         <v>1876163</v>
@@ -24352,7 +24352,7 @@
         <v>12.1116790771484</v>
       </c>
       <c r="G827" t="n">
-        <v>10.7391052246094</v>
+        <v>10.7391061782837</v>
       </c>
       <c r="H827" t="n">
         <v>3457397</v>
@@ -24439,7 +24439,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H830" t="n">
         <v>3008620</v>
@@ -24468,7 +24468,7 @@
         <v>12.4856977462769</v>
       </c>
       <c r="G831" t="n">
-        <v>11.0707378387451</v>
+        <v>11.0707368850708</v>
       </c>
       <c r="H831" t="n">
         <v>5821659</v>
@@ -24642,7 +24642,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295726776123</v>
+        <v>10.3295736312866</v>
       </c>
       <c r="H837" t="n">
         <v>2609971</v>
@@ -24671,7 +24671,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271890640259</v>
+        <v>10.2271900177002</v>
       </c>
       <c r="H838" t="n">
         <v>2776794</v>
@@ -24729,7 +24729,7 @@
         <v>11.7150688171387</v>
       </c>
       <c r="G840" t="n">
-        <v>10.3874416351318</v>
+        <v>10.3874425888062</v>
       </c>
       <c r="H840" t="n">
         <v>7174346</v>
@@ -24758,7 +24758,7 @@
         <v>12.0564546585083</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6901388168335</v>
+        <v>10.6901397705078</v>
       </c>
       <c r="H841" t="n">
         <v>5047664</v>
@@ -24990,7 +24990,7 @@
         <v>10.836501121521</v>
       </c>
       <c r="G849" t="n">
-        <v>9.60843944549561</v>
+        <v>9.60843849182129</v>
       </c>
       <c r="H849" t="n">
         <v>2642683</v>
@@ -25019,7 +25019,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H850" t="n">
         <v>3580640</v>
@@ -25048,7 +25048,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G851" t="n">
-        <v>9.33912754058838</v>
+        <v>9.33912658691406</v>
       </c>
       <c r="H851" t="n">
         <v>2781028</v>
@@ -25135,7 +25135,7 @@
         <v>10.203932762146</v>
       </c>
       <c r="G854" t="n">
-        <v>9.04755687713623</v>
+        <v>9.04755783081055</v>
       </c>
       <c r="H854" t="n">
         <v>3132004</v>
@@ -25164,7 +25164,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G855" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H855" t="n">
         <v>2818749</v>
@@ -25193,7 +25193,7 @@
         <v>10.4072589874268</v>
       </c>
       <c r="G856" t="n">
-        <v>9.22784042358398</v>
+        <v>9.2278413772583</v>
       </c>
       <c r="H856" t="n">
         <v>2374666</v>
@@ -25309,7 +25309,7 @@
         <v>10.5101757049561</v>
       </c>
       <c r="G860" t="n">
-        <v>9.31909465789795</v>
+        <v>9.31909561157227</v>
       </c>
       <c r="H860" t="n">
         <v>1842259</v>
@@ -25338,7 +25338,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G861" t="n">
-        <v>9.25232410430908</v>
+        <v>9.25232315063477</v>
       </c>
       <c r="H861" t="n">
         <v>2313809</v>
@@ -25425,7 +25425,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G864" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H864" t="n">
         <v>1703266</v>
@@ -25512,7 +25512,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H867" t="n">
         <v>1477729</v>
@@ -25570,7 +25570,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G869" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H869" t="n">
         <v>2768616</v>
@@ -25628,7 +25628,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G871" t="n">
-        <v>9.07204151153564</v>
+        <v>9.07204055786133</v>
       </c>
       <c r="H871" t="n">
         <v>6949172</v>
@@ -25686,7 +25686,7 @@
         <v>10.582971572876</v>
       </c>
       <c r="G873" t="n">
-        <v>9.38364124298096</v>
+        <v>9.38364028930664</v>
       </c>
       <c r="H873" t="n">
         <v>4424197</v>
@@ -25715,7 +25715,7 @@
         <v>10.768726348877</v>
       </c>
       <c r="G874" t="n">
-        <v>9.54834461212158</v>
+        <v>9.5483455657959</v>
       </c>
       <c r="H874" t="n">
         <v>1898679</v>
@@ -25744,7 +25744,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395576477051</v>
+        <v>9.58395671844482</v>
       </c>
       <c r="H875" t="n">
         <v>2681902</v>
@@ -25802,7 +25802,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G877" t="n">
-        <v>9.33912754058838</v>
+        <v>9.33912658691406</v>
       </c>
       <c r="H877" t="n">
         <v>2554085</v>
@@ -25860,7 +25860,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G879" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H879" t="n">
         <v>2123211</v>
@@ -25889,7 +25889,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G880" t="n">
-        <v>9.55947303771973</v>
+        <v>9.55947208404541</v>
       </c>
       <c r="H880" t="n">
         <v>2840452</v>
@@ -25918,7 +25918,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G881" t="n">
-        <v>9.60621356964111</v>
+        <v>9.60621452331543</v>
       </c>
       <c r="H881" t="n">
         <v>3879724</v>
@@ -26005,7 +26005,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079113006592</v>
+        <v>9.69079208374023</v>
       </c>
       <c r="H884" t="n">
         <v>1520396</v>
@@ -26150,7 +26150,7 @@
         <v>11.2431526184082</v>
       </c>
       <c r="G889" t="n">
-        <v>9.96900653839111</v>
+        <v>9.9690055847168</v>
       </c>
       <c r="H889" t="n">
         <v>2480426</v>
@@ -26295,7 +26295,7 @@
         <v>11.2130298614502</v>
       </c>
       <c r="G894" t="n">
-        <v>9.94229698181152</v>
+        <v>9.94229793548584</v>
       </c>
       <c r="H894" t="n">
         <v>2717697</v>
@@ -26353,7 +26353,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H896" t="n">
         <v>5491999</v>
@@ -26440,7 +26440,7 @@
         <v>11.2381324768066</v>
       </c>
       <c r="G899" t="n">
-        <v>9.96455478668213</v>
+        <v>9.96455383300781</v>
       </c>
       <c r="H899" t="n">
         <v>2760288</v>
@@ -26469,7 +26469,7 @@
         <v>11.4715795516968</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1715469360352</v>
+        <v>10.1715459823608</v>
       </c>
       <c r="H900" t="n">
         <v>3265887</v>
@@ -26556,7 +26556,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H903" t="n">
         <v>2794057</v>
@@ -26672,7 +26672,7 @@
         <v>11.4941720962524</v>
       </c>
       <c r="G907" t="n">
-        <v>10.191577911377</v>
+        <v>10.1915788650513</v>
       </c>
       <c r="H907" t="n">
         <v>5764525</v>
@@ -26701,7 +26701,7 @@
         <v>11.5845394134521</v>
       </c>
       <c r="G908" t="n">
-        <v>10.2717037200928</v>
+        <v>10.2717046737671</v>
       </c>
       <c r="H908" t="n">
         <v>2267960</v>
@@ -26788,7 +26788,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794101715088</v>
+        <v>9.99794006347656</v>
       </c>
       <c r="H911" t="n">
         <v>3280881</v>
@@ -26817,7 +26817,7 @@
         <v>11.1829080581665</v>
       </c>
       <c r="G912" t="n">
-        <v>9.91558837890625</v>
+        <v>9.91558933258057</v>
       </c>
       <c r="H912" t="n">
         <v>2387048</v>
@@ -26875,7 +26875,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G914" t="n">
-        <v>9.20780944824219</v>
+        <v>9.2078104019165</v>
       </c>
       <c r="H914" t="n">
         <v>3497415</v>
@@ -26904,7 +26904,7 @@
         <v>10.4248304367065</v>
       </c>
       <c r="G915" t="n">
-        <v>9.24342060089111</v>
+        <v>9.24342155456543</v>
       </c>
       <c r="H915" t="n">
         <v>2417247</v>
@@ -26933,7 +26933,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G916" t="n">
-        <v>8.92514228820801</v>
+        <v>8.92514324188232</v>
       </c>
       <c r="H916" t="n">
         <v>4019358</v>
@@ -26991,7 +26991,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G918" t="n">
-        <v>9.12545871734619</v>
+        <v>9.12545776367188</v>
       </c>
       <c r="H918" t="n">
         <v>3054696</v>
@@ -27426,7 +27426,7 @@
         <v>10.9067869186401</v>
       </c>
       <c r="G933" t="n">
-        <v>9.6707592010498</v>
+        <v>9.67076015472412</v>
       </c>
       <c r="H933" t="n">
         <v>1044571</v>
@@ -27629,7 +27629,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.1047735214233</v>
+        <v>10.1047744750977</v>
       </c>
       <c r="H940" t="n">
         <v>3374955</v>
@@ -27658,7 +27658,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136779785156</v>
+        <v>10.1136770248413</v>
       </c>
       <c r="H941" t="n">
         <v>3120641</v>
@@ -27716,7 +27716,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230527877808</v>
+        <v>10.4230537414551</v>
       </c>
       <c r="H943" t="n">
         <v>5842648</v>
@@ -27774,7 +27774,7 @@
         <v>11.1854181289673</v>
       </c>
       <c r="G945" t="n">
-        <v>9.91781520843506</v>
+        <v>9.91781425476074</v>
       </c>
       <c r="H945" t="n">
         <v>2493319</v>
@@ -27803,7 +27803,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G946" t="n">
-        <v>9.87107372283936</v>
+        <v>9.87107467651367</v>
       </c>
       <c r="H946" t="n">
         <v>2839086</v>
@@ -27832,7 +27832,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G947" t="n">
-        <v>9.84659194946289</v>
+        <v>9.84659099578857</v>
       </c>
       <c r="H947" t="n">
         <v>2212266</v>
@@ -27948,7 +27948,7 @@
         <v>10.4524421691895</v>
       </c>
       <c r="G951" t="n">
-        <v>9.26790428161621</v>
+        <v>9.26790332794189</v>
       </c>
       <c r="H951" t="n">
         <v>2009025</v>
@@ -27977,7 +27977,7 @@
         <v>10.4499320983887</v>
       </c>
       <c r="G952" t="n">
-        <v>9.26567840576172</v>
+        <v>9.26567935943604</v>
       </c>
       <c r="H952" t="n">
         <v>2896071</v>
@@ -28151,7 +28151,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G958" t="n">
-        <v>9.16552066802979</v>
+        <v>9.16551971435547</v>
       </c>
       <c r="H958" t="n">
         <v>3044501</v>
@@ -28354,7 +28354,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H965" t="n">
         <v>2851396</v>
@@ -28586,7 +28586,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65963077545166</v>
+        <v>9.65963172912598</v>
       </c>
       <c r="H973" t="n">
         <v>3880597</v>
@@ -28615,7 +28615,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G974" t="n">
-        <v>9.51050758361816</v>
+        <v>9.51050853729248</v>
       </c>
       <c r="H974" t="n">
         <v>4349124</v>
@@ -28673,7 +28673,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H976" t="n">
         <v>4961745</v>
@@ -28731,7 +28731,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G978" t="n">
-        <v>9.60621356964111</v>
+        <v>9.60621452331543</v>
       </c>
       <c r="H978" t="n">
         <v>5460186</v>
@@ -28789,7 +28789,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H980" t="n">
         <v>4874447</v>
@@ -28818,7 +28818,7 @@
         <v>11.2306022644043</v>
       </c>
       <c r="G981" t="n">
-        <v>9.95787811279297</v>
+        <v>9.95787906646729</v>
       </c>
       <c r="H981" t="n">
         <v>2713471</v>
@@ -28876,7 +28876,7 @@
         <v>11.0573978424072</v>
       </c>
       <c r="G983" t="n">
-        <v>9.80430221557617</v>
+        <v>9.80430126190186</v>
       </c>
       <c r="H983" t="n">
         <v>2502883</v>
@@ -29021,7 +29021,7 @@
         <v>10.7536649703979</v>
       </c>
       <c r="G988" t="n">
-        <v>9.53499031066895</v>
+        <v>9.53498935699463</v>
       </c>
       <c r="H988" t="n">
         <v>3248486</v>
@@ -29050,7 +29050,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812397003174</v>
+        <v>9.40812492370605</v>
       </c>
       <c r="H989" t="n">
         <v>2714951</v>
@@ -29137,7 +29137,7 @@
         <v>10.7536649703979</v>
       </c>
       <c r="G992" t="n">
-        <v>9.53499031066895</v>
+        <v>9.53498935699463</v>
       </c>
       <c r="H992" t="n">
         <v>3374594</v>
@@ -29253,7 +29253,7 @@
         <v>10.7135019302368</v>
       </c>
       <c r="G996" t="n">
-        <v>9.49937915802002</v>
+        <v>9.4993782043457</v>
       </c>
       <c r="H996" t="n">
         <v>2076226</v>
@@ -29311,7 +29311,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G998" t="n">
-        <v>9.07204151153564</v>
+        <v>9.07204055786133</v>
       </c>
       <c r="H998" t="n">
         <v>3580666</v>
@@ -29369,7 +29369,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.25232410430908</v>
+        <v>9.25232315063477</v>
       </c>
       <c r="H1000" t="n">
         <v>2435099</v>
@@ -29514,7 +29514,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H1005" t="n">
         <v>2212645</v>
@@ -29543,7 +29543,7 @@
         <v>10.582971572876</v>
       </c>
       <c r="G1006" t="n">
-        <v>9.38364124298096</v>
+        <v>9.38364028930664</v>
       </c>
       <c r="H1006" t="n">
         <v>2721399</v>
@@ -29717,7 +29717,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H1012" t="n">
         <v>3418112</v>
@@ -29862,7 +29862,7 @@
         <v>11.0925407409668</v>
       </c>
       <c r="G1017" t="n">
-        <v>9.83546257019043</v>
+        <v>9.83546352386475</v>
       </c>
       <c r="H1017" t="n">
         <v>3772987</v>
@@ -29891,7 +29891,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H1018" t="n">
         <v>2839366</v>
@@ -30036,7 +30036,7 @@
         <v>11.120153427124</v>
       </c>
       <c r="G1023" t="n">
-        <v>9.85994625091553</v>
+        <v>9.85994529724121</v>
       </c>
       <c r="H1023" t="n">
         <v>2013478</v>
@@ -30065,7 +30065,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H1024" t="n">
         <v>1781897</v>
@@ -30239,7 +30239,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G1030" t="n">
-        <v>9.46154117584229</v>
+        <v>9.4615421295166</v>
       </c>
       <c r="H1030" t="n">
         <v>7606013</v>
@@ -30297,7 +30297,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G1032" t="n">
-        <v>9.12545871734619</v>
+        <v>9.12545776367188</v>
       </c>
       <c r="H1032" t="n">
         <v>2852190</v>
@@ -30500,7 +30500,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.31974697113037</v>
+        <v>8.31974601745605</v>
       </c>
       <c r="H1039" t="n">
         <v>4814559</v>
@@ -30558,7 +30558,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H1041" t="n">
         <v>4707102</v>
@@ -30732,7 +30732,7 @@
         <v>9.51613998413086</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.43770980834961</v>
+        <v>8.43770885467529</v>
       </c>
       <c r="H1047" t="n">
         <v>3892374</v>
@@ -30790,7 +30790,7 @@
         <v>9.41573238372803</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.34868144989014</v>
+        <v>8.34868049621582</v>
       </c>
       <c r="H1049" t="n">
         <v>4412760</v>
@@ -30906,7 +30906,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657609939575</v>
+        <v>7.71657657623291</v>
       </c>
       <c r="H1053" t="n">
         <v>7295256</v>
@@ -30935,7 +30935,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754726409912</v>
+        <v>7.62754821777344</v>
       </c>
       <c r="H1054" t="n">
         <v>5328087</v>
@@ -31051,7 +31051,7 @@
         <v>8.3037166595459</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.36268615722656</v>
+        <v>7.36268663406372</v>
       </c>
       <c r="H1058" t="n">
         <v>5909074</v>
@@ -31080,7 +31080,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585174560547</v>
       </c>
       <c r="H1059" t="n">
         <v>5991896</v>
@@ -31138,7 +31138,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.70832395553589</v>
+        <v>6.70832443237305</v>
       </c>
       <c r="H1061" t="n">
         <v>5838598</v>
@@ -31283,7 +31283,7 @@
         <v>4.89613008499146</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.34126901626587</v>
+        <v>4.34126853942871</v>
       </c>
       <c r="H1066" t="n">
         <v>10214235</v>
@@ -31312,7 +31312,7 @@
         <v>5.16848611831665</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.58275985717773</v>
+        <v>4.58275938034058</v>
       </c>
       <c r="H1067" t="n">
         <v>9831037</v>
@@ -31457,7 +31457,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342178344727</v>
+        <v>5.00342130661011</v>
       </c>
       <c r="H1072" t="n">
         <v>6911923</v>
@@ -31486,7 +31486,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.88990926742554</v>
+        <v>4.8899097442627</v>
       </c>
       <c r="H1073" t="n">
         <v>3925543</v>
@@ -31573,7 +31573,7 @@
         <v>5.89393186569214</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.22599315643311</v>
+        <v>5.22599363327026</v>
       </c>
       <c r="H1076" t="n">
         <v>4232448</v>
@@ -31747,7 +31747,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386211395264</v>
+        <v>5.28386259078979</v>
       </c>
       <c r="H1082" t="n">
         <v>6987858</v>
@@ -31892,7 +31892,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.29276514053345</v>
+        <v>5.29276561737061</v>
       </c>
       <c r="H1087" t="n">
         <v>3514754</v>
@@ -31921,7 +31921,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1088" t="n">
         <v>5337056</v>
@@ -31950,7 +31950,7 @@
         <v>5.47473001480103</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.85429859161377</v>
+        <v>4.85429811477661</v>
       </c>
       <c r="H1089" t="n">
         <v>3542169</v>
@@ -32066,7 +32066,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445489883423</v>
+        <v>4.95445537567139</v>
       </c>
       <c r="H1093" t="n">
         <v>3686235</v>
@@ -32124,7 +32124,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1095" t="n">
         <v>3476797</v>
@@ -32182,7 +32182,7 @@
         <v>5.55505609512329</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.92552089691162</v>
+        <v>4.92552137374878</v>
       </c>
       <c r="H1097" t="n">
         <v>3776492</v>
@@ -32240,7 +32240,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041345596313</v>
+        <v>5.21041393280029</v>
       </c>
       <c r="H1099" t="n">
         <v>4870688</v>
@@ -32356,7 +32356,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470746994019</v>
+        <v>5.11470794677734</v>
       </c>
       <c r="H1103" t="n">
         <v>2616491</v>
@@ -32472,7 +32472,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.92329597473145</v>
+        <v>4.92329549789429</v>
       </c>
       <c r="H1107" t="n">
         <v>1872366</v>
@@ -80096,6 +80096,35 @@
         <v>17690897</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>4.36199998855591</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>4.4539999961853</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>4.31199979782104</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>4.44700002670288</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>4.44700002670288</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>12177376</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -80122,9 +80122,38 @@
         <v>4.44700002670288</v>
       </c>
       <c r="H2750" t="n">
-        <v>12177376</v>
+        <v>12218982</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>4.43499994277954</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>4.55000019073486</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>4.42899990081787</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>4.53299999237061</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>4.53299999237061</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>10959746</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>22.8775520324707</v>
       </c>
       <c r="G2" t="n">
-        <v>20.2849216461182</v>
+        <v>20.2849197387695</v>
       </c>
       <c r="H2" t="n">
         <v>974058</v>
@@ -485,7 +485,7 @@
         <v>22.3245735168457</v>
       </c>
       <c r="G4" t="n">
-        <v>19.7946090698242</v>
+        <v>19.7946071624756</v>
       </c>
       <c r="H4" t="n">
         <v>808293</v>
@@ -514,7 +514,7 @@
         <v>21.9295864105225</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4443855285645</v>
+        <v>19.4443836212158</v>
       </c>
       <c r="H5" t="n">
         <v>1112292</v>
@@ -543,7 +543,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540710449219</v>
+        <v>18.9540729522705</v>
       </c>
       <c r="H6" t="n">
         <v>681723</v>
@@ -630,7 +630,7 @@
         <v>22.1665782928467</v>
       </c>
       <c r="G9" t="n">
-        <v>19.65452003479</v>
+        <v>19.6545181274414</v>
       </c>
       <c r="H9" t="n">
         <v>916025</v>
@@ -659,7 +659,7 @@
         <v>22.1823787689209</v>
       </c>
       <c r="G10" t="n">
-        <v>19.6685276031494</v>
+        <v>19.668529510498</v>
       </c>
       <c r="H10" t="n">
         <v>887518</v>
@@ -717,7 +717,7 @@
         <v>19.8440647125244</v>
       </c>
       <c r="G12" t="n">
-        <v>17.5952072143555</v>
+        <v>17.5952091217041</v>
       </c>
       <c r="H12" t="n">
         <v>1467001</v>
@@ -746,7 +746,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811977386475</v>
+        <v>17.5811958312988</v>
       </c>
       <c r="H13" t="n">
         <v>989105</v>
@@ -775,7 +775,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460279464722</v>
+        <v>15.7460289001465</v>
       </c>
       <c r="H14" t="n">
         <v>2077512</v>
@@ -804,7 +804,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.8214406967163</v>
+        <v>14.821439743042</v>
       </c>
       <c r="H15" t="n">
         <v>2435960</v>
@@ -1007,7 +1007,7 @@
         <v>14.358302116394</v>
       </c>
       <c r="G22" t="n">
-        <v>12.7311267852783</v>
+        <v>12.7311277389526</v>
       </c>
       <c r="H22" t="n">
         <v>659234</v>
@@ -1036,7 +1036,7 @@
         <v>13.8813648223877</v>
       </c>
       <c r="G23" t="n">
-        <v>12.3082389831543</v>
+        <v>12.30823802948</v>
       </c>
       <c r="H23" t="n">
         <v>760726</v>
@@ -1123,7 +1123,7 @@
         <v>13.0530023574829</v>
       </c>
       <c r="G26" t="n">
-        <v>11.5737524032593</v>
+        <v>11.573751449585</v>
       </c>
       <c r="H26" t="n">
         <v>1877083</v>
@@ -1152,7 +1152,7 @@
         <v>9.75209808349609</v>
       </c>
       <c r="G27" t="n">
-        <v>8.64692687988281</v>
+        <v>8.64692783355713</v>
       </c>
       <c r="H27" t="n">
         <v>1596070</v>
@@ -1181,7 +1181,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H28" t="n">
         <v>1981662</v>
@@ -1210,7 +1210,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G29" t="n">
-        <v>8.0571117401123</v>
+        <v>8.05711078643799</v>
       </c>
       <c r="H29" t="n">
         <v>5695730</v>
@@ -1239,7 +1239,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G30" t="n">
-        <v>7.08892250061035</v>
+        <v>7.08892202377319</v>
       </c>
       <c r="H30" t="n">
         <v>5755429</v>
@@ -1268,7 +1268,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G31" t="n">
-        <v>6.70832443237305</v>
+        <v>6.70832347869873</v>
       </c>
       <c r="H31" t="n">
         <v>7709298</v>
@@ -1355,7 +1355,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51180934906006</v>
+        <v>7.51180982589722</v>
       </c>
       <c r="H34" t="n">
         <v>6329665</v>
@@ -1413,7 +1413,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36045980453491</v>
+        <v>7.36046028137207</v>
       </c>
       <c r="H36" t="n">
         <v>4978216</v>
@@ -1471,7 +1471,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243982315063</v>
+        <v>7.91243934631348</v>
       </c>
       <c r="H38" t="n">
         <v>4762357</v>
@@ -1529,7 +1529,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H40" t="n">
         <v>5230684</v>
@@ -1587,7 +1587,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H42" t="n">
         <v>8046415</v>
@@ -1616,7 +1616,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H43" t="n">
         <v>5632607</v>
@@ -1674,7 +1674,7 @@
         <v>9.67679214477539</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58015537261963</v>
+        <v>8.58015632629395</v>
       </c>
       <c r="H45" t="n">
         <v>3665603</v>
@@ -1732,7 +1732,7 @@
         <v>10.6884002685547</v>
       </c>
       <c r="G47" t="n">
-        <v>9.47712230682373</v>
+        <v>9.47712135314941</v>
       </c>
       <c r="H47" t="n">
         <v>6263628</v>
@@ -1761,7 +1761,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.0771427154541</v>
+        <v>8.07714366912842</v>
       </c>
       <c r="H48" t="n">
         <v>18012438</v>
@@ -1819,7 +1819,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811340332031</v>
+        <v>7.98811388015747</v>
       </c>
       <c r="H50" t="n">
         <v>5464353</v>
@@ -2080,7 +2080,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G59" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H59" t="n">
         <v>2418203</v>
@@ -2109,7 +2109,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218820571899</v>
+        <v>7.75218725204468</v>
       </c>
       <c r="H60" t="n">
         <v>3776976</v>
@@ -2138,7 +2138,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.34488010406494</v>
+        <v>7.3448805809021</v>
       </c>
       <c r="H61" t="n">
         <v>3010233</v>
@@ -2399,7 +2399,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H70" t="n">
         <v>3239759</v>
@@ -2428,7 +2428,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G71" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H71" t="n">
         <v>3489116</v>
@@ -2457,7 +2457,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.8634729385376</v>
+        <v>7.86347436904907</v>
       </c>
       <c r="H72" t="n">
         <v>3751875</v>
@@ -2486,7 +2486,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09940052032471</v>
+        <v>8.09939956665039</v>
       </c>
       <c r="H73" t="n">
         <v>4017372</v>
@@ -2515,7 +2515,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86569976806641</v>
+        <v>7.86570072174072</v>
       </c>
       <c r="H74" t="n">
         <v>2931733</v>
@@ -2689,7 +2689,7 @@
         <v>9.39816093444824</v>
       </c>
       <c r="G80" t="n">
-        <v>8.33310031890869</v>
+        <v>8.33310127258301</v>
       </c>
       <c r="H80" t="n">
         <v>1866023</v>
@@ -2718,7 +2718,7 @@
         <v>9.55128288269043</v>
       </c>
       <c r="G81" t="n">
-        <v>8.46886920928955</v>
+        <v>8.46887016296387</v>
       </c>
       <c r="H81" t="n">
         <v>3453580</v>
@@ -2747,7 +2747,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912082672119</v>
+        <v>8.62912178039551</v>
       </c>
       <c r="H82" t="n">
         <v>3841073</v>
@@ -2776,7 +2776,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G83" t="n">
-        <v>9.68188762664795</v>
+        <v>9.68188858032227</v>
       </c>
       <c r="H83" t="n">
         <v>13679976</v>
@@ -2805,7 +2805,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H84" t="n">
         <v>6156371</v>
@@ -2863,7 +2863,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G86" t="n">
-        <v>8.54009246826172</v>
+        <v>8.54009342193604</v>
       </c>
       <c r="H86" t="n">
         <v>4877613</v>
@@ -2892,7 +2892,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H87" t="n">
         <v>3783755</v>
@@ -2921,7 +2921,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G88" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H88" t="n">
         <v>2952497</v>
@@ -2950,7 +2950,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G89" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H89" t="n">
         <v>2726335</v>
@@ -3066,7 +3066,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H93" t="n">
         <v>3351378</v>
@@ -3124,7 +3124,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542102813721</v>
+        <v>8.39542007446289</v>
       </c>
       <c r="H95" t="n">
         <v>1782012</v>
@@ -3153,7 +3153,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G96" t="n">
-        <v>8.31974601745605</v>
+        <v>8.31974697113037</v>
       </c>
       <c r="H96" t="n">
         <v>2286483</v>
@@ -3182,7 +3182,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G97" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H97" t="n">
         <v>1772130</v>
@@ -3240,7 +3240,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701642990112</v>
       </c>
       <c r="H99" t="n">
         <v>2418605</v>
@@ -3269,7 +3269,7 @@
         <v>8.92875480651855</v>
       </c>
       <c r="G100" t="n">
-        <v>7.91689014434814</v>
+        <v>7.91689109802246</v>
       </c>
       <c r="H100" t="n">
         <v>1802404</v>
@@ -3298,7 +3298,7 @@
         <v>9.14212131500244</v>
       </c>
       <c r="G101" t="n">
-        <v>8.10607814788818</v>
+        <v>8.10607719421387</v>
       </c>
       <c r="H101" t="n">
         <v>2228168</v>
@@ -3327,7 +3327,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H102" t="n">
         <v>3679752</v>
@@ -3356,7 +3356,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G103" t="n">
-        <v>8.3976469039917</v>
+        <v>8.39764595031738</v>
       </c>
       <c r="H103" t="n">
         <v>2642334</v>
@@ -3501,7 +3501,7 @@
         <v>9.04924392700195</v>
       </c>
       <c r="G108" t="n">
-        <v>8.02372455596924</v>
+        <v>8.02372550964355</v>
       </c>
       <c r="H108" t="n">
         <v>2261709</v>
@@ -3530,7 +3530,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889585494995</v>
+        <v>7.77889633178711</v>
       </c>
       <c r="H109" t="n">
         <v>2101522</v>
@@ -3559,7 +3559,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701642990112</v>
       </c>
       <c r="H110" t="n">
         <v>2370853</v>
@@ -3588,7 +3588,7 @@
         <v>9.5261812210083</v>
       </c>
       <c r="G111" t="n">
-        <v>8.44661331176758</v>
+        <v>8.44661235809326</v>
       </c>
       <c r="H111" t="n">
         <v>3958468</v>
@@ -3617,7 +3617,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837078094482</v>
+        <v>8.85837173461914</v>
       </c>
       <c r="H112" t="n">
         <v>4508416</v>
@@ -3704,7 +3704,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325325012207</v>
+        <v>7.72325372695923</v>
       </c>
       <c r="H115" t="n">
         <v>4121823</v>
@@ -3733,7 +3733,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660612106323</v>
       </c>
       <c r="H116" t="n">
         <v>3931446</v>
@@ -3762,7 +3762,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808338165283</v>
+        <v>7.96808290481567</v>
       </c>
       <c r="H117" t="n">
         <v>3606977</v>
@@ -3820,7 +3820,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G119" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H119" t="n">
         <v>6157104</v>
@@ -3849,7 +3849,7 @@
         <v>9.80230236053467</v>
       </c>
       <c r="G120" t="n">
-        <v>8.69144248962402</v>
+        <v>8.69144153594971</v>
       </c>
       <c r="H120" t="n">
         <v>4234729</v>
@@ -3936,7 +3936,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G123" t="n">
-        <v>9.007493019104</v>
+        <v>9.00749397277832</v>
       </c>
       <c r="H123" t="n">
         <v>3474390</v>
@@ -3965,7 +3965,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933570861816</v>
+        <v>8.0593376159668</v>
       </c>
       <c r="H124" t="n">
         <v>4551998</v>
@@ -3994,7 +3994,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.5919361114502</v>
+        <v>7.59193563461304</v>
       </c>
       <c r="H125" t="n">
         <v>3711164</v>
@@ -4023,7 +4023,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78557395935059</v>
+        <v>7.78557348251343</v>
       </c>
       <c r="H126" t="n">
         <v>3269289</v>
@@ -4052,7 +4052,7 @@
         <v>8.86349010467529</v>
       </c>
       <c r="G127" t="n">
-        <v>7.85902261734009</v>
+        <v>7.85902214050293</v>
       </c>
       <c r="H127" t="n">
         <v>3013097</v>
@@ -4139,7 +4139,7 @@
         <v>9.60650730133057</v>
       </c>
       <c r="G130" t="n">
-        <v>8.51783657073975</v>
+        <v>8.51783561706543</v>
       </c>
       <c r="H130" t="n">
         <v>3045817</v>
@@ -4197,7 +4197,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G132" t="n">
-        <v>7.82341146469116</v>
+        <v>7.82341051101685</v>
       </c>
       <c r="H132" t="n">
         <v>3383064</v>
@@ -4284,7 +4284,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.71147441864014</v>
+        <v>8.7114725112915</v>
       </c>
       <c r="H135" t="n">
         <v>4380711</v>
@@ -4371,7 +4371,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G138" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H138" t="n">
         <v>2932449</v>
@@ -4400,7 +4400,7 @@
         <v>10.3771362304688</v>
       </c>
       <c r="G139" t="n">
-        <v>9.20113182067871</v>
+        <v>9.20113277435303</v>
       </c>
       <c r="H139" t="n">
         <v>1660292</v>
@@ -4429,7 +4429,7 @@
         <v>10.5679111480713</v>
       </c>
       <c r="G140" t="n">
-        <v>9.37028789520264</v>
+        <v>9.37028694152832</v>
       </c>
       <c r="H140" t="n">
         <v>1710004</v>
@@ -4516,7 +4516,7 @@
         <v>10.8590927124023</v>
       </c>
       <c r="G143" t="n">
-        <v>9.62846946716309</v>
+        <v>9.6284704208374</v>
       </c>
       <c r="H143" t="n">
         <v>2762374</v>
@@ -4603,7 +4603,7 @@
         <v>10.6934204101562</v>
       </c>
       <c r="G146" t="n">
-        <v>9.48157215118408</v>
+        <v>9.4815731048584</v>
       </c>
       <c r="H146" t="n">
         <v>2462145</v>
@@ -4690,7 +4690,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G149" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H149" t="n">
         <v>5327998</v>
@@ -4806,7 +4806,7 @@
         <v>9.37807941436768</v>
       </c>
       <c r="G153" t="n">
-        <v>8.31529426574707</v>
+        <v>8.31529521942139</v>
       </c>
       <c r="H153" t="n">
         <v>2495200</v>
@@ -4835,7 +4835,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.5222864151001</v>
+        <v>8.52228832244873</v>
       </c>
       <c r="H154" t="n">
         <v>2111524</v>
@@ -5009,7 +5009,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H160" t="n">
         <v>2723125</v>
@@ -5125,7 +5125,7 @@
         <v>9.98303604125977</v>
       </c>
       <c r="G164" t="n">
-        <v>8.85169410705566</v>
+        <v>8.85169315338135</v>
       </c>
       <c r="H164" t="n">
         <v>1474788</v>
@@ -5270,7 +5270,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G169" t="n">
-        <v>9.08094310760498</v>
+        <v>9.0809440612793</v>
       </c>
       <c r="H169" t="n">
         <v>1117249</v>
@@ -5386,7 +5386,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H173" t="n">
         <v>2380805</v>
@@ -5415,7 +5415,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.27235507965088</v>
+        <v>9.2723560333252</v>
       </c>
       <c r="H174" t="n">
         <v>1895264</v>
@@ -5473,7 +5473,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G176" t="n">
-        <v>9.2078104019165</v>
+        <v>9.20780944824219</v>
       </c>
       <c r="H176" t="n">
         <v>1550105</v>
@@ -5502,7 +5502,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G177" t="n">
-        <v>9.23451805114746</v>
+        <v>9.23451900482178</v>
       </c>
       <c r="H177" t="n">
         <v>2950107</v>
@@ -5531,7 +5531,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G178" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H178" t="n">
         <v>1678053</v>
@@ -5560,7 +5560,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G179" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H179" t="n">
         <v>3246340</v>
@@ -5647,7 +5647,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G182" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H182" t="n">
         <v>2932072</v>
@@ -5676,7 +5676,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359874725342</v>
+        <v>7.94359827041626</v>
       </c>
       <c r="H183" t="n">
         <v>4194583</v>
@@ -5763,7 +5763,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463376998901</v>
+        <v>7.89463329315186</v>
       </c>
       <c r="H186" t="n">
         <v>1967156</v>
@@ -5821,7 +5821,7 @@
         <v>9.28771305084229</v>
       </c>
       <c r="G188" t="n">
-        <v>8.23516845703125</v>
+        <v>8.23516941070557</v>
       </c>
       <c r="H188" t="n">
         <v>1917572</v>
@@ -5850,7 +5850,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798759460449</v>
+        <v>7.90798664093018</v>
       </c>
       <c r="H189" t="n">
         <v>3574353</v>
@@ -5908,7 +5908,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.7388334274292</v>
+        <v>7.73883247375488</v>
       </c>
       <c r="H191" t="n">
         <v>2882632</v>
@@ -5966,7 +5966,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G193" t="n">
-        <v>8.38429164886475</v>
+        <v>8.38429260253906</v>
       </c>
       <c r="H193" t="n">
         <v>3268951</v>
@@ -6082,7 +6082,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G197" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H197" t="n">
         <v>2803083</v>
@@ -6111,7 +6111,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473293304443</v>
+        <v>8.66473388671875</v>
       </c>
       <c r="H198" t="n">
         <v>3635783</v>
@@ -6256,7 +6256,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H203" t="n">
         <v>2739605</v>
@@ -6285,7 +6285,7 @@
         <v>10.3696060180664</v>
       </c>
       <c r="G204" t="n">
-        <v>9.19445610046387</v>
+        <v>9.19445514678955</v>
       </c>
       <c r="H204" t="n">
         <v>2291727</v>
@@ -6430,7 +6430,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G209" t="n">
-        <v>9.68188762664795</v>
+        <v>9.68188858032227</v>
       </c>
       <c r="H209" t="n">
         <v>3157831</v>
@@ -6459,7 +6459,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G210" t="n">
-        <v>9.31464290618896</v>
+        <v>9.31464385986328</v>
       </c>
       <c r="H210" t="n">
         <v>2902413</v>
@@ -6517,7 +6517,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G212" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H212" t="n">
         <v>3931503</v>
@@ -6720,7 +6720,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G219" t="n">
-        <v>8.38429164886475</v>
+        <v>8.38429260253906</v>
       </c>
       <c r="H219" t="n">
         <v>2139887</v>
@@ -6749,7 +6749,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G220" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H220" t="n">
         <v>2461590</v>
@@ -6778,7 +6778,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G221" t="n">
-        <v>8.73373031616211</v>
+        <v>8.73373126983643</v>
       </c>
       <c r="H221" t="n">
         <v>7014824</v>
@@ -6865,7 +6865,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H224" t="n">
         <v>2930403</v>
@@ -6894,7 +6894,7 @@
         <v>10.2240142822266</v>
       </c>
       <c r="G225" t="n">
-        <v>9.06536293029785</v>
+        <v>9.06536388397217</v>
       </c>
       <c r="H225" t="n">
         <v>2711291</v>
@@ -7068,7 +7068,7 @@
         <v>10.2215042114258</v>
       </c>
       <c r="G231" t="n">
-        <v>9.06313800811768</v>
+        <v>9.06313705444336</v>
       </c>
       <c r="H231" t="n">
         <v>2430715</v>
@@ -7097,7 +7097,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G232" t="n">
-        <v>9.16329479217529</v>
+        <v>9.16329383850098</v>
       </c>
       <c r="H232" t="n">
         <v>2155204</v>
@@ -7155,7 +7155,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G234" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H234" t="n">
         <v>2193109</v>
@@ -7242,7 +7242,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640228271484</v>
+        <v>9.72640323638916</v>
       </c>
       <c r="H237" t="n">
         <v>6656648</v>
@@ -7329,7 +7329,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.182674407959</v>
+        <v>10.1826753616333</v>
       </c>
       <c r="H240" t="n">
         <v>4126096</v>
@@ -7387,7 +7387,7 @@
         <v>11.4088249206543</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1159038543701</v>
+        <v>10.1159029006958</v>
       </c>
       <c r="H242" t="n">
         <v>4919856</v>
@@ -7474,7 +7474,7 @@
         <v>11.8230066299438</v>
       </c>
       <c r="G245" t="n">
-        <v>10.4831476211548</v>
+        <v>10.4831466674805</v>
       </c>
       <c r="H245" t="n">
         <v>7748349</v>
@@ -7532,7 +7532,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788536071777</v>
+        <v>10.5788545608521</v>
       </c>
       <c r="H247" t="n">
         <v>3112020</v>
@@ -7561,7 +7561,7 @@
         <v>12.2748422622681</v>
       </c>
       <c r="G248" t="n">
-        <v>10.8837785720825</v>
+        <v>10.8837776184082</v>
       </c>
       <c r="H248" t="n">
         <v>3278242</v>
@@ -7619,7 +7619,7 @@
         <v>12.8019819259644</v>
       </c>
       <c r="G250" t="n">
-        <v>11.3511791229248</v>
+        <v>11.3511781692505</v>
       </c>
       <c r="H250" t="n">
         <v>3391155</v>
@@ -7648,7 +7648,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G251" t="n">
-        <v>10.9883871078491</v>
+        <v>10.9883861541748</v>
       </c>
       <c r="H251" t="n">
         <v>3493539</v>
@@ -7706,7 +7706,7 @@
         <v>12.8772878646851</v>
       </c>
       <c r="G253" t="n">
-        <v>11.417950630188</v>
+        <v>11.4179496765137</v>
       </c>
       <c r="H253" t="n">
         <v>1908982</v>
@@ -7764,7 +7764,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295513153076</v>
+        <v>11.7295522689819</v>
       </c>
       <c r="H255" t="n">
         <v>2571001</v>
@@ -8054,7 +8054,7 @@
         <v>13.1032047271729</v>
       </c>
       <c r="G265" t="n">
-        <v>11.6182661056519</v>
+        <v>11.6182651519775</v>
       </c>
       <c r="H265" t="n">
         <v>3089766</v>
@@ -8112,7 +8112,7 @@
         <v>12.8647365570068</v>
       </c>
       <c r="G267" t="n">
-        <v>11.4068212509155</v>
+        <v>11.4068222045898</v>
       </c>
       <c r="H267" t="n">
         <v>2415292</v>
@@ -8141,7 +8141,7 @@
         <v>12.2999439239502</v>
       </c>
       <c r="G268" t="n">
-        <v>10.9060344696045</v>
+        <v>10.9060354232788</v>
       </c>
       <c r="H268" t="n">
         <v>3796302</v>
@@ -8170,7 +8170,7 @@
         <v>12.5635137557983</v>
       </c>
       <c r="G269" t="n">
-        <v>11.1397342681885</v>
+        <v>11.1397352218628</v>
       </c>
       <c r="H269" t="n">
         <v>3707353</v>
@@ -8228,7 +8228,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619930267334</v>
+        <v>11.1619920730591</v>
       </c>
       <c r="H271" t="n">
         <v>2083536</v>
@@ -8257,7 +8257,7 @@
         <v>12.6011667251587</v>
       </c>
       <c r="G272" t="n">
-        <v>11.1731204986572</v>
+        <v>11.1731214523315</v>
       </c>
       <c r="H272" t="n">
         <v>2804708</v>
@@ -8286,7 +8286,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351257324219</v>
+        <v>11.0351266860962</v>
       </c>
       <c r="H273" t="n">
         <v>2426178</v>
@@ -8315,7 +8315,7 @@
         <v>12.5007591247559</v>
       </c>
       <c r="G274" t="n">
-        <v>11.0840921401978</v>
+        <v>11.0840930938721</v>
       </c>
       <c r="H274" t="n">
         <v>2614176</v>
@@ -8344,7 +8344,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963228225708</v>
+        <v>11.7963237762451</v>
       </c>
       <c r="H275" t="n">
         <v>5968291</v>
@@ -8373,7 +8373,7 @@
         <v>13.1283073425293</v>
       </c>
       <c r="G276" t="n">
-        <v>11.6405220031738</v>
+        <v>11.6405229568481</v>
       </c>
       <c r="H276" t="n">
         <v>2868878</v>
@@ -8402,7 +8402,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960092544556</v>
+        <v>11.5960083007812</v>
       </c>
       <c r="H277" t="n">
         <v>1743449</v>
@@ -8518,7 +8518,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G281" t="n">
-        <v>10.2383193969727</v>
+        <v>10.2383184432983</v>
       </c>
       <c r="H281" t="n">
         <v>3878344</v>
@@ -8547,7 +8547,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141502380371</v>
+        <v>10.4141492843628</v>
       </c>
       <c r="H282" t="n">
         <v>2834757</v>
@@ -8663,7 +8663,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.3985710144043</v>
+        <v>10.39857006073</v>
       </c>
       <c r="H286" t="n">
         <v>2660739</v>
@@ -8692,7 +8692,7 @@
         <v>11.707537651062</v>
       </c>
       <c r="G287" t="n">
-        <v>10.3807640075684</v>
+        <v>10.3807649612427</v>
       </c>
       <c r="H287" t="n">
         <v>2250311</v>
@@ -8895,7 +8895,7 @@
         <v>11.6874570846558</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3629589080811</v>
+        <v>10.3629579544067</v>
       </c>
       <c r="H294" t="n">
         <v>2084853</v>
@@ -8953,7 +8953,7 @@
         <v>11.3310089111328</v>
       </c>
       <c r="G296" t="n">
-        <v>10.0469064712524</v>
+        <v>10.0469055175781</v>
       </c>
       <c r="H296" t="n">
         <v>2645855</v>
@@ -9011,7 +9011,7 @@
         <v>10.5754413604736</v>
       </c>
       <c r="G298" t="n">
-        <v>9.37696361541748</v>
+        <v>9.3769645690918</v>
       </c>
       <c r="H298" t="n">
         <v>3692492</v>
@@ -9185,7 +9185,7 @@
         <v>10.4675025939941</v>
       </c>
       <c r="G304" t="n">
-        <v>9.28125858306885</v>
+        <v>9.28125762939453</v>
       </c>
       <c r="H304" t="n">
         <v>3507793</v>
@@ -9243,7 +9243,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G306" t="n">
-        <v>9.007493019104</v>
+        <v>9.00749397277832</v>
       </c>
       <c r="H306" t="n">
         <v>4803773</v>
@@ -9272,7 +9272,7 @@
         <v>10.1386680603027</v>
       </c>
       <c r="G307" t="n">
-        <v>8.98968887329102</v>
+        <v>8.9896879196167</v>
       </c>
       <c r="H307" t="n">
         <v>3615164</v>
@@ -9330,7 +9330,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520614624023</v>
+        <v>8.96520709991455</v>
       </c>
       <c r="H309" t="n">
         <v>3858069</v>
@@ -9359,7 +9359,7 @@
         <v>10.218994140625</v>
       </c>
       <c r="G310" t="n">
-        <v>9.06091117858887</v>
+        <v>9.06091213226318</v>
       </c>
       <c r="H310" t="n">
         <v>3308377</v>
@@ -9388,7 +9388,7 @@
         <v>10.3244218826294</v>
       </c>
       <c r="G311" t="n">
-        <v>9.15439224243164</v>
+        <v>9.15439128875732</v>
       </c>
       <c r="H311" t="n">
         <v>3767044</v>
@@ -9562,7 +9562,7 @@
         <v>10.1562385559082</v>
       </c>
       <c r="G317" t="n">
-        <v>9.00526809692383</v>
+        <v>9.00526714324951</v>
       </c>
       <c r="H317" t="n">
         <v>2490908</v>
@@ -9620,7 +9620,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G319" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H319" t="n">
         <v>5837585</v>
@@ -9707,7 +9707,7 @@
         <v>10.6808700561523</v>
       </c>
       <c r="G322" t="n">
-        <v>9.47044467926025</v>
+        <v>9.47044563293457</v>
       </c>
       <c r="H322" t="n">
         <v>3003542</v>
@@ -9765,7 +9765,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G324" t="n">
-        <v>9.49047470092773</v>
+        <v>9.49047565460205</v>
       </c>
       <c r="H324" t="n">
         <v>4124738</v>
@@ -9794,7 +9794,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G325" t="n">
-        <v>9.51050853729248</v>
+        <v>9.51050662994385</v>
       </c>
       <c r="H325" t="n">
         <v>3181766</v>
@@ -9823,7 +9823,7 @@
         <v>10.7310733795166</v>
       </c>
       <c r="G326" t="n">
-        <v>9.51495933532715</v>
+        <v>9.51495838165283</v>
       </c>
       <c r="H326" t="n">
         <v>2539231</v>
@@ -9968,7 +9968,7 @@
         <v>10.2691984176636</v>
       </c>
       <c r="G331" t="n">
-        <v>9.10542678833008</v>
+        <v>9.10542583465576</v>
       </c>
       <c r="H331" t="n">
         <v>2262671</v>
@@ -10084,7 +10084,7 @@
         <v>9.7671594619751</v>
       </c>
       <c r="G335" t="n">
-        <v>8.66028213500977</v>
+        <v>8.66028118133545</v>
       </c>
       <c r="H335" t="n">
         <v>6899556</v>
@@ -10287,7 +10287,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837078094482</v>
+        <v>8.85837173461914</v>
       </c>
       <c r="H342" t="n">
         <v>3153124</v>
@@ -10316,7 +10316,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H343" t="n">
         <v>4027196</v>
@@ -10345,7 +10345,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G344" t="n">
-        <v>8.87840175628662</v>
+        <v>8.87840270996094</v>
       </c>
       <c r="H344" t="n">
         <v>4939603</v>
@@ -10432,7 +10432,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G347" t="n">
-        <v>8.87840175628662</v>
+        <v>8.87840270996094</v>
       </c>
       <c r="H347" t="n">
         <v>4232992</v>
@@ -10606,7 +10606,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G353" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H353" t="n">
         <v>3851850</v>
@@ -10635,7 +10635,7 @@
         <v>9.80481243133545</v>
       </c>
       <c r="G354" t="n">
-        <v>8.69366836547852</v>
+        <v>8.6936674118042</v>
       </c>
       <c r="H354" t="n">
         <v>2634747</v>
@@ -10664,7 +10664,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G355" t="n">
-        <v>8.86282253265381</v>
+        <v>8.86282348632812</v>
       </c>
       <c r="H355" t="n">
         <v>4334969</v>
@@ -10722,7 +10722,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G357" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H357" t="n">
         <v>2035124</v>
@@ -10780,7 +10780,7 @@
         <v>9.36301803588867</v>
       </c>
       <c r="G359" t="n">
-        <v>8.30194091796875</v>
+        <v>8.30193996429443</v>
       </c>
       <c r="H359" t="n">
         <v>3581572</v>
@@ -10896,7 +10896,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033880233765</v>
+        <v>7.9903392791748</v>
       </c>
       <c r="H363" t="n">
         <v>4201110</v>
@@ -11012,7 +11012,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215675354004</v>
+        <v>7.73215627670288</v>
       </c>
       <c r="H367" t="n">
         <v>4573774</v>
@@ -11041,7 +11041,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209337234497</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H368" t="n">
         <v>4145288</v>
@@ -11099,7 +11099,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G370" t="n">
-        <v>8.0571117401123</v>
+        <v>8.05711078643799</v>
       </c>
       <c r="H370" t="n">
         <v>5171240</v>
@@ -11157,7 +11157,7 @@
         <v>8.88106060028076</v>
       </c>
       <c r="G372" t="n">
-        <v>7.8746018409729</v>
+        <v>7.87460136413574</v>
       </c>
       <c r="H372" t="n">
         <v>3226298</v>
@@ -11186,7 +11186,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H373" t="n">
         <v>5046714</v>
@@ -11244,7 +11244,7 @@
         <v>8.27861499786377</v>
       </c>
       <c r="G375" t="n">
-        <v>7.34042930603027</v>
+        <v>7.34042882919312</v>
       </c>
       <c r="H375" t="n">
         <v>3956309</v>
@@ -11273,7 +11273,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G376" t="n">
-        <v>7.19798278808594</v>
+        <v>7.1979832649231</v>
       </c>
       <c r="H376" t="n">
         <v>3156325</v>
@@ -11331,7 +11331,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G378" t="n">
-        <v>7.18017673492432</v>
+        <v>7.18017721176147</v>
       </c>
       <c r="H378" t="n">
         <v>2433304</v>
@@ -11389,7 +11389,7 @@
         <v>8.07779979705811</v>
       </c>
       <c r="G380" t="n">
-        <v>7.16237115859985</v>
+        <v>7.16237163543701</v>
       </c>
       <c r="H380" t="n">
         <v>2966514</v>
@@ -11418,7 +11418,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914266586304</v>
+        <v>7.22914218902588</v>
       </c>
       <c r="H381" t="n">
         <v>2924827</v>
@@ -11447,7 +11447,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817197799683</v>
+        <v>7.31817150115967</v>
       </c>
       <c r="H382" t="n">
         <v>2594435</v>
@@ -11476,7 +11476,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H383" t="n">
         <v>2583014</v>
@@ -11505,7 +11505,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G384" t="n">
-        <v>7.19798278808594</v>
+        <v>7.1979832649231</v>
       </c>
       <c r="H384" t="n">
         <v>2069812</v>
@@ -11534,7 +11534,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055463790894</v>
+        <v>7.42055559158325</v>
       </c>
       <c r="H385" t="n">
         <v>3239198</v>
@@ -11563,7 +11563,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.69654560089111</v>
+        <v>7.69654512405396</v>
       </c>
       <c r="H386" t="n">
         <v>4250748</v>
@@ -11592,7 +11592,7 @@
         <v>8.44428825378418</v>
       </c>
       <c r="G387" t="n">
-        <v>7.48732662200928</v>
+        <v>7.48732709884644</v>
       </c>
       <c r="H387" t="n">
         <v>4117666</v>
@@ -11708,7 +11708,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390941619873</v>
+        <v>7.43390893936157</v>
       </c>
       <c r="H391" t="n">
         <v>1190917</v>
@@ -11737,7 +11737,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H392" t="n">
         <v>4462543</v>
@@ -11766,7 +11766,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G393" t="n">
-        <v>7.7455096244812</v>
+        <v>7.74551010131836</v>
       </c>
       <c r="H393" t="n">
         <v>2051870</v>
@@ -11824,7 +11824,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.85679626464844</v>
+        <v>7.85679578781128</v>
       </c>
       <c r="H395" t="n">
         <v>2325966</v>
@@ -11853,7 +11853,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H396" t="n">
         <v>3714587</v>
@@ -11882,7 +11882,7 @@
         <v>8.52461433410645</v>
       </c>
       <c r="G397" t="n">
-        <v>7.55854940414429</v>
+        <v>7.55854988098145</v>
       </c>
       <c r="H397" t="n">
         <v>2332643</v>
@@ -11911,7 +11911,7 @@
         <v>8.514573097229</v>
       </c>
       <c r="G398" t="n">
-        <v>7.54964637756348</v>
+        <v>7.54964685440063</v>
       </c>
       <c r="H398" t="n">
         <v>1501586</v>
@@ -11969,7 +11969,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196660995483</v>
+        <v>7.61196708679199</v>
       </c>
       <c r="H400" t="n">
         <v>2662388</v>
@@ -12056,7 +12056,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416151046753</v>
+        <v>7.59416103363037</v>
       </c>
       <c r="H403" t="n">
         <v>2870111</v>
@@ -12085,7 +12085,7 @@
         <v>8.6953067779541</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70989847183228</v>
+        <v>7.70989894866943</v>
       </c>
       <c r="H404" t="n">
         <v>2592503</v>
@@ -12114,7 +12114,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G405" t="n">
-        <v>7.70099592208862</v>
+        <v>7.70099496841431</v>
       </c>
       <c r="H405" t="n">
         <v>3030024</v>
@@ -12143,7 +12143,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209337234497</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H406" t="n">
         <v>2779239</v>
@@ -12346,7 +12346,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G413" t="n">
-        <v>7.5051326751709</v>
+        <v>7.50513172149658</v>
       </c>
       <c r="H413" t="n">
         <v>2055106</v>
@@ -12433,7 +12433,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G416" t="n">
-        <v>7.26475477218628</v>
+        <v>7.26475429534912</v>
       </c>
       <c r="H416" t="n">
         <v>2058975</v>
@@ -12462,7 +12462,7 @@
         <v>8.15812587738037</v>
       </c>
       <c r="G417" t="n">
-        <v>7.23359394073486</v>
+        <v>7.23359441757202</v>
       </c>
       <c r="H417" t="n">
         <v>3351310</v>
@@ -12491,7 +12491,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G418" t="n">
-        <v>7.30036640167236</v>
+        <v>7.30036592483521</v>
       </c>
       <c r="H418" t="n">
         <v>1896151</v>
@@ -12607,7 +12607,7 @@
         <v>7.61592388153076</v>
       </c>
       <c r="G422" t="n">
-        <v>6.75283861160278</v>
+        <v>6.75283813476562</v>
       </c>
       <c r="H422" t="n">
         <v>5344638</v>
@@ -12723,7 +12723,7 @@
         <v>7.40004777908325</v>
       </c>
       <c r="G426" t="n">
-        <v>6.56142663955688</v>
+        <v>6.56142616271973</v>
       </c>
       <c r="H426" t="n">
         <v>1915267</v>
@@ -12752,7 +12752,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.93979930877686</v>
+        <v>6.93979835510254</v>
       </c>
       <c r="H427" t="n">
         <v>6403078</v>
@@ -12781,7 +12781,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857557296753</v>
+        <v>6.86857604980469</v>
       </c>
       <c r="H428" t="n">
         <v>3961179</v>
@@ -12868,7 +12868,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G431" t="n">
-        <v>7.30036640167236</v>
+        <v>7.30036592483521</v>
       </c>
       <c r="H431" t="n">
         <v>5992264</v>
@@ -12897,7 +12897,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469091415405</v>
+        <v>7.22469139099121</v>
       </c>
       <c r="H432" t="n">
         <v>2571750</v>
@@ -12955,7 +12955,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591464996338</v>
+        <v>7.29591417312622</v>
       </c>
       <c r="H434" t="n">
         <v>3040311</v>
@@ -13042,7 +13042,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409860610962</v>
+        <v>7.55409908294678</v>
       </c>
       <c r="H437" t="n">
         <v>2971867</v>
@@ -13071,7 +13071,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.47397184371948</v>
+        <v>7.47397232055664</v>
       </c>
       <c r="H438" t="n">
         <v>2774137</v>
@@ -13129,7 +13129,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H440" t="n">
         <v>3440039</v>
@@ -13158,7 +13158,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.66538381576538</v>
+        <v>7.66538429260254</v>
       </c>
       <c r="H441" t="n">
         <v>3163095</v>
@@ -13187,7 +13187,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G442" t="n">
-        <v>7.70099592208862</v>
+        <v>7.70099496841431</v>
       </c>
       <c r="H442" t="n">
         <v>2989271</v>
@@ -13216,7 +13216,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H443" t="n">
         <v>2311936</v>
@@ -13245,7 +13245,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491683959961</v>
+        <v>8.07491779327393</v>
       </c>
       <c r="H444" t="n">
         <v>9651321</v>
@@ -13448,7 +13448,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692255020142</v>
+        <v>7.93692302703857</v>
       </c>
       <c r="H451" t="n">
         <v>4589432</v>
@@ -13796,7 +13796,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.4294581413269</v>
+        <v>7.42945766448975</v>
       </c>
       <c r="H463" t="n">
         <v>3847044</v>
@@ -13825,7 +13825,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H464" t="n">
         <v>4793014</v>
@@ -13883,7 +13883,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H466" t="n">
         <v>9145143</v>
@@ -13912,7 +13912,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.66538381576538</v>
+        <v>7.66538429260254</v>
       </c>
       <c r="H467" t="n">
         <v>3470929</v>
@@ -13941,7 +13941,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G468" t="n">
-        <v>7.64312744140625</v>
+        <v>7.64312648773193</v>
       </c>
       <c r="H468" t="n">
         <v>2766448</v>
@@ -13970,7 +13970,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479198455811</v>
+        <v>7.99479103088379</v>
       </c>
       <c r="H469" t="n">
         <v>8252776</v>
@@ -14028,7 +14028,7 @@
         <v>9.53371143341064</v>
       </c>
       <c r="G471" t="n">
-        <v>8.45328903198242</v>
+        <v>8.45328998565674</v>
       </c>
       <c r="H471" t="n">
         <v>8570157</v>
@@ -14057,7 +14057,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.54677104949951</v>
+        <v>8.5467700958252</v>
       </c>
       <c r="H472" t="n">
         <v>5904097</v>
@@ -14173,7 +14173,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H476" t="n">
         <v>3307360</v>
@@ -14231,7 +14231,7 @@
         <v>9.49354839324951</v>
       </c>
       <c r="G478" t="n">
-        <v>8.4176778793335</v>
+        <v>8.41767883300781</v>
       </c>
       <c r="H478" t="n">
         <v>4520776</v>
@@ -14289,7 +14289,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G480" t="n">
-        <v>7.78557395935059</v>
+        <v>7.78557348251343</v>
       </c>
       <c r="H480" t="n">
         <v>11572956</v>
@@ -14347,7 +14347,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G482" t="n">
-        <v>7.62532234191895</v>
+        <v>7.62532186508179</v>
       </c>
       <c r="H482" t="n">
         <v>3509049</v>
@@ -14376,7 +14376,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G483" t="n">
-        <v>7.62532234191895</v>
+        <v>7.62532186508179</v>
       </c>
       <c r="H483" t="n">
         <v>4716149</v>
@@ -14405,7 +14405,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209337234497</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H484" t="n">
         <v>3256857</v>
@@ -14463,7 +14463,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576219558716</v>
       </c>
       <c r="H486" t="n">
         <v>2564414</v>
@@ -14521,7 +14521,7 @@
         <v>8.60494041442871</v>
       </c>
       <c r="G488" t="n">
-        <v>7.62977266311646</v>
+        <v>7.62977313995361</v>
       </c>
       <c r="H488" t="n">
         <v>3215714</v>
@@ -14579,7 +14579,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H490" t="n">
         <v>2757855</v>
@@ -14608,7 +14608,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G491" t="n">
-        <v>7.7455096244812</v>
+        <v>7.74551010131836</v>
       </c>
       <c r="H491" t="n">
         <v>3546514</v>
@@ -14637,7 +14637,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G492" t="n">
-        <v>7.5051326751709</v>
+        <v>7.50513172149658</v>
       </c>
       <c r="H492" t="n">
         <v>28943183</v>
@@ -14666,7 +14666,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G493" t="n">
-        <v>7.64312744140625</v>
+        <v>7.64312648773193</v>
       </c>
       <c r="H493" t="n">
         <v>7994237</v>
@@ -14695,7 +14695,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H494" t="n">
         <v>4714362</v>
@@ -14724,7 +14724,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H495" t="n">
         <v>2456311</v>
@@ -14840,7 +14840,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63422393798828</v>
+        <v>7.63422441482544</v>
       </c>
       <c r="H499" t="n">
         <v>4090789</v>
@@ -14898,7 +14898,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H501" t="n">
         <v>2766406</v>
@@ -14985,7 +14985,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996280670166</v>
+        <v>7.74996185302734</v>
       </c>
       <c r="H504" t="n">
         <v>4120969</v>
@@ -15072,7 +15072,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G507" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H507" t="n">
         <v>4480449</v>
@@ -15159,7 +15159,7 @@
         <v>9.61403846740723</v>
       </c>
       <c r="G510" t="n">
-        <v>8.52451324462891</v>
+        <v>8.52451419830322</v>
       </c>
       <c r="H510" t="n">
         <v>2445873</v>
@@ -15188,7 +15188,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109508514404</v>
+        <v>8.47109603881836</v>
       </c>
       <c r="H511" t="n">
         <v>3770392</v>
@@ -15217,7 +15217,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670623779297</v>
+        <v>8.50670719146729</v>
       </c>
       <c r="H512" t="n">
         <v>2875008</v>
@@ -15275,7 +15275,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G514" t="n">
-        <v>8.73373031616211</v>
+        <v>8.73373126983643</v>
       </c>
       <c r="H514" t="n">
         <v>6368024</v>
@@ -15362,7 +15362,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H517" t="n">
         <v>4311139</v>
@@ -15391,7 +15391,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805625915527</v>
+        <v>8.65805530548096</v>
       </c>
       <c r="H518" t="n">
         <v>3468959</v>
@@ -15420,7 +15420,7 @@
         <v>10.1210966110229</v>
       </c>
       <c r="G519" t="n">
-        <v>8.97410869598389</v>
+        <v>8.9741096496582</v>
       </c>
       <c r="H519" t="n">
         <v>7443734</v>
@@ -15449,7 +15449,7 @@
         <v>10.1763210296631</v>
       </c>
       <c r="G520" t="n">
-        <v>9.02307415008545</v>
+        <v>9.02307510375977</v>
       </c>
       <c r="H520" t="n">
         <v>5305812</v>
@@ -15565,7 +15565,7 @@
         <v>10.1813411712646</v>
       </c>
       <c r="G524" t="n">
-        <v>9.02752590179443</v>
+        <v>9.02752685546875</v>
       </c>
       <c r="H524" t="n">
         <v>2378154</v>
@@ -15652,7 +15652,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G527" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H527" t="n">
         <v>5274403</v>
@@ -15681,7 +15681,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G528" t="n">
-        <v>9.16551971435547</v>
+        <v>9.1655216217041</v>
       </c>
       <c r="H528" t="n">
         <v>3314321</v>
@@ -15826,7 +15826,7 @@
         <v>9.46593570709229</v>
       </c>
       <c r="G533" t="n">
-        <v>8.39319515228271</v>
+        <v>8.3931941986084</v>
       </c>
       <c r="H533" t="n">
         <v>3664518</v>
@@ -15855,7 +15855,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.4199047088623</v>
+        <v>8.41990566253662</v>
       </c>
       <c r="H534" t="n">
         <v>2981971</v>
@@ -15884,7 +15884,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.24852466583252</v>
+        <v>8.2485237121582</v>
       </c>
       <c r="H535" t="n">
         <v>4093310</v>
@@ -15913,7 +15913,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H536" t="n">
         <v>4347986</v>
@@ -15942,7 +15942,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G537" t="n">
-        <v>7.82341146469116</v>
+        <v>7.82341051101685</v>
       </c>
       <c r="H537" t="n">
         <v>8270004</v>
@@ -16000,7 +16000,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660612106323</v>
       </c>
       <c r="H539" t="n">
         <v>5267752</v>
@@ -16029,7 +16029,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196660995483</v>
+        <v>7.61196708679199</v>
       </c>
       <c r="H540" t="n">
         <v>7866114</v>
@@ -16058,7 +16058,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519510269165</v>
+        <v>7.54519605636597</v>
       </c>
       <c r="H541" t="n">
         <v>2933056</v>
@@ -16116,7 +16116,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49622917175293</v>
+        <v>7.49622964859009</v>
       </c>
       <c r="H543" t="n">
         <v>5612249</v>
@@ -16232,7 +16232,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H547" t="n">
         <v>2390591</v>
@@ -16348,7 +16348,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.76331663131714</v>
+        <v>7.7633171081543</v>
       </c>
       <c r="H551" t="n">
         <v>3521552</v>
@@ -16377,7 +16377,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H552" t="n">
         <v>3398436</v>
@@ -16406,7 +16406,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G553" t="n">
-        <v>7.50068044662476</v>
+        <v>7.50068092346191</v>
       </c>
       <c r="H553" t="n">
         <v>4181215</v>
@@ -16435,7 +16435,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.5229377746582</v>
+        <v>7.52293872833252</v>
       </c>
       <c r="H554" t="n">
         <v>2585190</v>
@@ -16493,7 +16493,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G556" t="n">
-        <v>7.30036640167236</v>
+        <v>7.30036592483521</v>
       </c>
       <c r="H556" t="n">
         <v>4331827</v>
@@ -16522,7 +16522,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G557" t="n">
-        <v>7.50068044662476</v>
+        <v>7.50068092346191</v>
       </c>
       <c r="H557" t="n">
         <v>7379464</v>
@@ -16551,7 +16551,7 @@
         <v>8.56979656219482</v>
       </c>
       <c r="G558" t="n">
-        <v>7.59861183166504</v>
+        <v>7.5986123085022</v>
       </c>
       <c r="H558" t="n">
         <v>4269884</v>
@@ -16580,7 +16580,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.7566385269165</v>
+        <v>7.75663805007935</v>
       </c>
       <c r="H559" t="n">
         <v>3729295</v>
@@ -16609,7 +16609,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218820571899</v>
+        <v>7.75218725204468</v>
       </c>
       <c r="H560" t="n">
         <v>2796916</v>
@@ -16696,7 +16696,7 @@
         <v>8.32379913330078</v>
       </c>
       <c r="G563" t="n">
-        <v>7.38049221038818</v>
+        <v>7.38049268722534</v>
       </c>
       <c r="H563" t="n">
         <v>3760036</v>
@@ -16725,7 +16725,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936330795288</v>
+        <v>7.36936378479004</v>
       </c>
       <c r="H564" t="n">
         <v>2801339</v>
@@ -16754,7 +16754,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613386154175</v>
+        <v>7.43613433837891</v>
       </c>
       <c r="H565" t="n">
         <v>3258776</v>
@@ -16783,7 +16783,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585174560547</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H566" t="n">
         <v>4081106</v>
@@ -16812,7 +16812,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826633453369</v>
+        <v>7.37826585769653</v>
       </c>
       <c r="H567" t="n">
         <v>3350760</v>
@@ -16899,7 +16899,7 @@
         <v>8.17820739746094</v>
       </c>
       <c r="G570" t="n">
-        <v>7.25139999389648</v>
+        <v>7.25140047073364</v>
       </c>
       <c r="H570" t="n">
         <v>3395514</v>
@@ -16986,7 +16986,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111692428589</v>
+        <v>7.07111740112305</v>
       </c>
       <c r="H573" t="n">
         <v>3487395</v>
@@ -17131,7 +17131,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G578" t="n">
-        <v>6.98876571655273</v>
+        <v>6.98876523971558</v>
       </c>
       <c r="H578" t="n">
         <v>2910934</v>
@@ -17160,7 +17160,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744762420654</v>
+        <v>6.85744667053223</v>
       </c>
       <c r="H579" t="n">
         <v>4059831</v>
@@ -17218,7 +17218,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G581" t="n">
-        <v>7.08892250061035</v>
+        <v>7.08892202377319</v>
       </c>
       <c r="H581" t="n">
         <v>8326804</v>
@@ -17276,7 +17276,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469091415405</v>
+        <v>7.22469139099121</v>
       </c>
       <c r="H583" t="n">
         <v>5007935</v>
@@ -17334,7 +17334,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G585" t="n">
-        <v>7.18017673492432</v>
+        <v>7.18017721176147</v>
       </c>
       <c r="H585" t="n">
         <v>3344302</v>
@@ -17421,7 +17421,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610336303711</v>
+        <v>7.41610383987427</v>
       </c>
       <c r="H588" t="n">
         <v>4009682</v>
@@ -17479,7 +17479,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G590" t="n">
-        <v>7.26475477218628</v>
+        <v>7.26475429534912</v>
       </c>
       <c r="H590" t="n">
         <v>7182347</v>
@@ -17508,7 +17508,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G591" t="n">
-        <v>6.98876571655273</v>
+        <v>6.98876523971558</v>
       </c>
       <c r="H591" t="n">
         <v>9716283</v>
@@ -17595,7 +17595,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443977355957</v>
+        <v>7.06443881988525</v>
       </c>
       <c r="H594" t="n">
         <v>3740621</v>
@@ -17769,7 +17769,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H600" t="n">
         <v>11169423</v>
@@ -17827,7 +17827,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G602" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H602" t="n">
         <v>3638485</v>
@@ -17914,7 +17914,7 @@
         <v>9.83242416381836</v>
       </c>
       <c r="G605" t="n">
-        <v>8.71815013885498</v>
+        <v>8.7181510925293</v>
       </c>
       <c r="H605" t="n">
         <v>23153988</v>
@@ -17972,7 +17972,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G607" t="n">
-        <v>8.54009246826172</v>
+        <v>8.54009342193604</v>
       </c>
       <c r="H607" t="n">
         <v>5543597</v>
@@ -18030,7 +18030,7 @@
         <v>10.0909738540649</v>
       </c>
       <c r="G609" t="n">
-        <v>8.94740009307861</v>
+        <v>8.9473991394043</v>
       </c>
       <c r="H609" t="n">
         <v>8237079</v>
@@ -18117,7 +18117,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065475463867</v>
+        <v>8.19065380096436</v>
       </c>
       <c r="H612" t="n">
         <v>4712315</v>
@@ -18146,7 +18146,7 @@
         <v>8.79822540283203</v>
       </c>
       <c r="G613" t="n">
-        <v>7.80115413665771</v>
+        <v>7.80115365982056</v>
       </c>
       <c r="H613" t="n">
         <v>4731371</v>
@@ -18320,7 +18320,7 @@
         <v>9.42326259613037</v>
       </c>
       <c r="G619" t="n">
-        <v>8.3553581237793</v>
+        <v>8.35535717010498</v>
       </c>
       <c r="H619" t="n">
         <v>6500575</v>
@@ -18349,7 +18349,7 @@
         <v>9.31783485412598</v>
       </c>
       <c r="G620" t="n">
-        <v>8.26187705993652</v>
+        <v>8.26187896728516</v>
       </c>
       <c r="H620" t="n">
         <v>3046319</v>
@@ -18378,7 +18378,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H621" t="n">
         <v>4359962</v>
@@ -18436,7 +18436,7 @@
         <v>9.85250568389893</v>
       </c>
       <c r="G623" t="n">
-        <v>8.73595523834229</v>
+        <v>8.7359561920166</v>
       </c>
       <c r="H623" t="n">
         <v>3059274</v>
@@ -18494,7 +18494,7 @@
         <v>9.47848701477051</v>
       </c>
       <c r="G625" t="n">
-        <v>8.40432453155518</v>
+        <v>8.40432357788086</v>
       </c>
       <c r="H625" t="n">
         <v>3369292</v>
@@ -18610,7 +18610,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G629" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H629" t="n">
         <v>1664123</v>
@@ -18813,7 +18813,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G636" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H636" t="n">
         <v>6312564</v>
@@ -18900,7 +18900,7 @@
         <v>9.86254692077637</v>
       </c>
       <c r="G639" t="n">
-        <v>8.74485969543457</v>
+        <v>8.74485874176025</v>
       </c>
       <c r="H639" t="n">
         <v>2222101</v>
@@ -18929,7 +18929,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G640" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H640" t="n">
         <v>1067132</v>
@@ -18958,7 +18958,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.71147441864014</v>
+        <v>8.7114725112915</v>
       </c>
       <c r="H641" t="n">
         <v>2154097</v>
@@ -19045,7 +19045,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G644" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H644" t="n">
         <v>5210482</v>
@@ -19074,7 +19074,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009822845459</v>
+        <v>9.25009632110596</v>
       </c>
       <c r="H645" t="n">
         <v>6365259</v>
@@ -19103,7 +19103,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G646" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H646" t="n">
         <v>3391737</v>
@@ -19190,7 +19190,7 @@
         <v>10.0608520507812</v>
       </c>
       <c r="G649" t="n">
-        <v>8.92069053649902</v>
+        <v>8.92069149017334</v>
       </c>
       <c r="H649" t="n">
         <v>3535639</v>
@@ -19335,7 +19335,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G654" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H654" t="n">
         <v>2782854</v>
@@ -19509,7 +19509,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G660" t="n">
-        <v>9.84659099578857</v>
+        <v>9.84659194946289</v>
       </c>
       <c r="H660" t="n">
         <v>3631961</v>
@@ -19538,7 +19538,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G661" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H661" t="n">
         <v>5649923</v>
@@ -19683,7 +19683,7 @@
         <v>11.2331123352051</v>
       </c>
       <c r="G666" t="n">
-        <v>9.96010398864746</v>
+        <v>9.96010303497314</v>
       </c>
       <c r="H666" t="n">
         <v>2694360</v>
@@ -19712,7 +19712,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G667" t="n">
-        <v>9.87107467651367</v>
+        <v>9.87107372283936</v>
       </c>
       <c r="H667" t="n">
         <v>3825674</v>
@@ -19799,7 +19799,7 @@
         <v>11.4414577484131</v>
       </c>
       <c r="G670" t="n">
-        <v>10.1448373794556</v>
+        <v>10.1448383331299</v>
       </c>
       <c r="H670" t="n">
         <v>4154794</v>
@@ -19973,7 +19973,7 @@
         <v>11.6046199798584</v>
       </c>
       <c r="G676" t="n">
-        <v>10.2895088195801</v>
+        <v>10.2895097732544</v>
       </c>
       <c r="H676" t="n">
         <v>1818429</v>
@@ -20031,7 +20031,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G678" t="n">
-        <v>10.0157461166382</v>
+        <v>10.0157451629639</v>
       </c>
       <c r="H678" t="n">
         <v>2115163</v>
@@ -20176,7 +20176,7 @@
         <v>11.700008392334</v>
       </c>
       <c r="G683" t="n">
-        <v>10.3740873336792</v>
+        <v>10.3740882873535</v>
       </c>
       <c r="H683" t="n">
         <v>3804319</v>
@@ -20234,7 +20234,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99349021911621</v>
+        <v>9.99348926544189</v>
       </c>
       <c r="H685" t="n">
         <v>2940239</v>
@@ -20292,7 +20292,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694787979126</v>
+        <v>10.2694797515869</v>
       </c>
       <c r="H687" t="n">
         <v>2357662</v>
@@ -20321,7 +20321,7 @@
         <v>11.5017032623291</v>
       </c>
       <c r="G688" t="n">
-        <v>10.1982555389404</v>
+        <v>10.1982564926147</v>
       </c>
       <c r="H688" t="n">
         <v>1979022</v>
@@ -20379,7 +20379,7 @@
         <v>11.328498840332</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0446805953979</v>
+        <v>10.0446796417236</v>
       </c>
       <c r="H690" t="n">
         <v>5499203</v>
@@ -20437,7 +20437,7 @@
         <v>12.0489253997803</v>
       </c>
       <c r="G692" t="n">
-        <v>10.6834630966187</v>
+        <v>10.683464050293</v>
       </c>
       <c r="H692" t="n">
         <v>2537540</v>
@@ -20582,7 +20582,7 @@
         <v>12.4580860137939</v>
       </c>
       <c r="G697" t="n">
-        <v>11.0462560653687</v>
+        <v>11.0462551116943</v>
       </c>
       <c r="H697" t="n">
         <v>11143856</v>
@@ -20611,7 +20611,7 @@
         <v>13.1232872009277</v>
       </c>
       <c r="G698" t="n">
-        <v>11.6360712051392</v>
+        <v>11.6360721588135</v>
       </c>
       <c r="H698" t="n">
         <v>8601699</v>
@@ -20727,7 +20727,7 @@
         <v>13.5500202178955</v>
       </c>
       <c r="G702" t="n">
-        <v>12.0144443511963</v>
+        <v>12.014443397522</v>
       </c>
       <c r="H702" t="n">
         <v>7155972</v>
@@ -20814,7 +20814,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856676101685</v>
+        <v>12.0856685638428</v>
       </c>
       <c r="H705" t="n">
         <v>4491851</v>
@@ -21017,7 +21017,7 @@
         <v>12.7065954208374</v>
       </c>
       <c r="G712" t="n">
-        <v>11.2666025161743</v>
+        <v>11.2666015625</v>
       </c>
       <c r="H712" t="n">
         <v>5559737</v>
@@ -21046,7 +21046,7 @@
         <v>12.7015752792358</v>
       </c>
       <c r="G713" t="n">
-        <v>11.262149810791</v>
+        <v>11.2621507644653</v>
       </c>
       <c r="H713" t="n">
         <v>2952425</v>
@@ -21278,7 +21278,7 @@
         <v>11.7979049682617</v>
       </c>
       <c r="G721" t="n">
-        <v>10.4608907699585</v>
+        <v>10.4608898162842</v>
       </c>
       <c r="H721" t="n">
         <v>10788083</v>
@@ -21336,7 +21336,7 @@
         <v>11.8857622146606</v>
       </c>
       <c r="G723" t="n">
-        <v>10.5387907028198</v>
+        <v>10.5387916564941</v>
       </c>
       <c r="H723" t="n">
         <v>2694375</v>
@@ -21365,7 +21365,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H724" t="n">
         <v>4731058</v>
@@ -21452,7 +21452,7 @@
         <v>11.7025184631348</v>
       </c>
       <c r="G727" t="n">
-        <v>10.3763132095337</v>
+        <v>10.376314163208</v>
       </c>
       <c r="H727" t="n">
         <v>2777725</v>
@@ -21481,7 +21481,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H728" t="n">
         <v>6325209</v>
@@ -21539,7 +21539,7 @@
         <v>11.7251100540161</v>
       </c>
       <c r="G730" t="n">
-        <v>10.3963451385498</v>
+        <v>10.3963441848755</v>
       </c>
       <c r="H730" t="n">
         <v>2649841</v>
@@ -21597,7 +21597,7 @@
         <v>11.1377248764038</v>
       </c>
       <c r="G732" t="n">
-        <v>9.87552547454834</v>
+        <v>9.87552642822266</v>
       </c>
       <c r="H732" t="n">
         <v>3029135</v>
@@ -21655,7 +21655,7 @@
         <v>10.6607875823975</v>
       </c>
       <c r="G734" t="n">
-        <v>9.45263862609863</v>
+        <v>9.45263767242432</v>
       </c>
       <c r="H734" t="n">
         <v>4394592</v>
@@ -21713,7 +21713,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G736" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H736" t="n">
         <v>2599002</v>
@@ -21771,7 +21771,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G738" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H738" t="n">
         <v>10323921</v>
@@ -21858,7 +21858,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889585494995</v>
+        <v>7.77889633178711</v>
       </c>
       <c r="H741" t="n">
         <v>8894223</v>
@@ -21945,7 +21945,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H744" t="n">
         <v>2830649</v>
@@ -21974,7 +21974,7 @@
         <v>9.65922069549561</v>
       </c>
       <c r="G745" t="n">
-        <v>8.5645751953125</v>
+        <v>8.56457614898682</v>
       </c>
       <c r="H745" t="n">
         <v>3590690</v>
@@ -22003,7 +22003,7 @@
         <v>9.69938373565674</v>
       </c>
       <c r="G746" t="n">
-        <v>8.60018730163574</v>
+        <v>8.60018634796143</v>
       </c>
       <c r="H746" t="n">
         <v>4899103</v>
@@ -22090,7 +22090,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G749" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H749" t="n">
         <v>3226454</v>
@@ -22148,7 +22148,7 @@
         <v>9.75209808349609</v>
       </c>
       <c r="G751" t="n">
-        <v>8.64692687988281</v>
+        <v>8.64692783355713</v>
       </c>
       <c r="H751" t="n">
         <v>7331392</v>
@@ -22177,7 +22177,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G752" t="n">
-        <v>8.25520038604736</v>
+        <v>8.25519943237305</v>
       </c>
       <c r="H752" t="n">
         <v>4141957</v>
@@ -22264,7 +22264,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466522216797</v>
+        <v>7.91466569900513</v>
       </c>
       <c r="H755" t="n">
         <v>4636928</v>
@@ -22293,7 +22293,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.81228160858154</v>
+        <v>7.81228256225586</v>
       </c>
       <c r="H756" t="n">
         <v>3199541</v>
@@ -22322,7 +22322,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G757" t="n">
-        <v>7.30036640167236</v>
+        <v>7.30036592483521</v>
       </c>
       <c r="H757" t="n">
         <v>6552833</v>
@@ -22351,7 +22351,7 @@
         <v>8.25602340698242</v>
       </c>
       <c r="G758" t="n">
-        <v>7.32039737701416</v>
+        <v>7.32039785385132</v>
       </c>
       <c r="H758" t="n">
         <v>7880235</v>
@@ -22380,7 +22380,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416151046753</v>
+        <v>7.59416103363037</v>
       </c>
       <c r="H759" t="n">
         <v>5059632</v>
@@ -22409,7 +22409,7 @@
         <v>8.17318725585938</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24694871902466</v>
+        <v>7.24694919586182</v>
       </c>
       <c r="H760" t="n">
         <v>5578537</v>
@@ -22438,7 +22438,7 @@
         <v>8.12800407409668</v>
       </c>
       <c r="G761" t="n">
-        <v>7.20688581466675</v>
+        <v>7.20688629150391</v>
       </c>
       <c r="H761" t="n">
         <v>4333423</v>
@@ -22496,7 +22496,7 @@
         <v>8.19577884674072</v>
       </c>
       <c r="G763" t="n">
-        <v>7.26698064804077</v>
+        <v>7.26698017120361</v>
       </c>
       <c r="H763" t="n">
         <v>4297434</v>
@@ -22525,7 +22525,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G764" t="n">
-        <v>7.30036640167236</v>
+        <v>7.30036592483521</v>
       </c>
       <c r="H764" t="n">
         <v>3809859</v>
@@ -22583,7 +22583,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576219558716</v>
       </c>
       <c r="H766" t="n">
         <v>6705143</v>
@@ -22728,7 +22728,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G771" t="n">
-        <v>8.3976469039917</v>
+        <v>8.39764595031738</v>
       </c>
       <c r="H771" t="n">
         <v>5244277</v>
@@ -22757,7 +22757,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G772" t="n">
-        <v>8.25520038604736</v>
+        <v>8.25519943237305</v>
       </c>
       <c r="H772" t="n">
         <v>3230113</v>
@@ -22931,7 +22931,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G778" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H778" t="n">
         <v>3928570</v>
@@ -22960,7 +22960,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G779" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H779" t="n">
         <v>5108708</v>
@@ -23047,7 +23047,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G782" t="n">
-        <v>8.86282253265381</v>
+        <v>8.86282348632812</v>
       </c>
       <c r="H782" t="n">
         <v>3274045</v>
@@ -23105,7 +23105,7 @@
         <v>10.1763210296631</v>
       </c>
       <c r="G784" t="n">
-        <v>9.02307415008545</v>
+        <v>9.02307510375977</v>
       </c>
       <c r="H784" t="n">
         <v>2474098</v>
@@ -23192,7 +23192,7 @@
         <v>10.3445043563843</v>
       </c>
       <c r="G787" t="n">
-        <v>9.17219829559326</v>
+        <v>9.17219924926758</v>
       </c>
       <c r="H787" t="n">
         <v>3191829</v>
@@ -23221,7 +23221,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G788" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H788" t="n">
         <v>2462687</v>
@@ -23250,7 +23250,7 @@
         <v>10.4298496246338</v>
       </c>
       <c r="G789" t="n">
-        <v>9.2478723526001</v>
+        <v>9.24787139892578</v>
       </c>
       <c r="H789" t="n">
         <v>2010428</v>
@@ -23424,7 +23424,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G795" t="n">
-        <v>9.08094310760498</v>
+        <v>9.0809440612793</v>
       </c>
       <c r="H795" t="n">
         <v>2539926</v>
@@ -23453,7 +23453,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G796" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H796" t="n">
         <v>5910919</v>
@@ -23540,7 +23540,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H799" t="n">
         <v>2749374</v>
@@ -23656,7 +23656,7 @@
         <v>10.8440322875977</v>
       </c>
       <c r="G803" t="n">
-        <v>9.61511707305908</v>
+        <v>9.61511611938477</v>
       </c>
       <c r="H803" t="n">
         <v>5049854</v>
@@ -23714,7 +23714,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H805" t="n">
         <v>7839193</v>
@@ -24004,7 +24004,7 @@
         <v>12.3150053024292</v>
       </c>
       <c r="G815" t="n">
-        <v>10.9193897247314</v>
+        <v>10.9193887710571</v>
       </c>
       <c r="H815" t="n">
         <v>3038261</v>
@@ -24033,7 +24033,7 @@
         <v>12.1091690063477</v>
       </c>
       <c r="G816" t="n">
-        <v>10.7368793487549</v>
+        <v>10.7368803024292</v>
       </c>
       <c r="H816" t="n">
         <v>3221057</v>
@@ -24062,7 +24062,7 @@
         <v>12.2145967483521</v>
       </c>
       <c r="G817" t="n">
-        <v>10.8303604125977</v>
+        <v>10.8303594589233</v>
       </c>
       <c r="H817" t="n">
         <v>2672807</v>
@@ -24091,7 +24091,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371957778931</v>
+        <v>10.9371948242188</v>
       </c>
       <c r="H818" t="n">
         <v>2377360</v>
@@ -24120,7 +24120,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G819" t="n">
-        <v>10.9883871078491</v>
+        <v>10.9883861541748</v>
       </c>
       <c r="H819" t="n">
         <v>2021022</v>
@@ -24323,7 +24323,7 @@
         <v>11.8355579376221</v>
       </c>
       <c r="G826" t="n">
-        <v>10.4942770004272</v>
+        <v>10.4942760467529</v>
       </c>
       <c r="H826" t="n">
         <v>1876163</v>
@@ -24352,7 +24352,7 @@
         <v>12.1116790771484</v>
       </c>
       <c r="G827" t="n">
-        <v>10.7391061782837</v>
+        <v>10.7391052246094</v>
       </c>
       <c r="H827" t="n">
         <v>3457397</v>
@@ -24381,7 +24381,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147811889648</v>
+        <v>10.8147802352905</v>
       </c>
       <c r="H828" t="n">
         <v>2456179</v>
@@ -24410,7 +24410,7 @@
         <v>12.2522497177124</v>
       </c>
       <c r="G829" t="n">
-        <v>10.8637456893921</v>
+        <v>10.8637447357178</v>
       </c>
       <c r="H829" t="n">
         <v>3054118</v>
@@ -24439,7 +24439,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H830" t="n">
         <v>3008620</v>
@@ -24497,7 +24497,7 @@
         <v>12.6312885284424</v>
       </c>
       <c r="G832" t="n">
-        <v>11.1998291015625</v>
+        <v>11.1998300552368</v>
       </c>
       <c r="H832" t="n">
         <v>2539989</v>
@@ -24555,7 +24555,7 @@
         <v>12.0991277694702</v>
       </c>
       <c r="G834" t="n">
-        <v>10.7279767990112</v>
+        <v>10.7279777526855</v>
       </c>
       <c r="H834" t="n">
         <v>3226626</v>
@@ -24584,7 +24584,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G835" t="n">
-        <v>10.4386329650879</v>
+        <v>10.4386339187622</v>
       </c>
       <c r="H835" t="n">
         <v>4190619</v>
@@ -24671,7 +24671,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271900177002</v>
+        <v>10.2271909713745</v>
       </c>
       <c r="H838" t="n">
         <v>2776794</v>
@@ -24700,7 +24700,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G839" t="n">
-        <v>10.4386329650879</v>
+        <v>10.4386339187622</v>
       </c>
       <c r="H839" t="n">
         <v>3240942</v>
@@ -24729,7 +24729,7 @@
         <v>11.7150688171387</v>
       </c>
       <c r="G840" t="n">
-        <v>10.3874425888062</v>
+        <v>10.3874416351318</v>
       </c>
       <c r="H840" t="n">
         <v>7174346</v>
@@ -24758,7 +24758,7 @@
         <v>12.0564546585083</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6901397705078</v>
+        <v>10.6901388168335</v>
       </c>
       <c r="H841" t="n">
         <v>5047664</v>
@@ -24845,7 +24845,7 @@
         <v>11.3912544250488</v>
       </c>
       <c r="G844" t="n">
-        <v>10.1003246307373</v>
+        <v>10.100323677063</v>
       </c>
       <c r="H844" t="n">
         <v>5169154</v>
@@ -24874,7 +24874,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G845" t="n">
-        <v>10.2383193969727</v>
+        <v>10.2383184432983</v>
       </c>
       <c r="H845" t="n">
         <v>2752665</v>
@@ -25048,7 +25048,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G851" t="n">
-        <v>9.33912658691406</v>
+        <v>9.33912754058838</v>
       </c>
       <c r="H851" t="n">
         <v>2781028</v>
@@ -25135,7 +25135,7 @@
         <v>10.203932762146</v>
       </c>
       <c r="G854" t="n">
-        <v>9.04755783081055</v>
+        <v>9.04755687713623</v>
       </c>
       <c r="H854" t="n">
         <v>3132004</v>
@@ -25164,7 +25164,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G855" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H855" t="n">
         <v>2818749</v>
@@ -25251,7 +25251,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G858" t="n">
-        <v>9.27012920379639</v>
+        <v>9.2701301574707</v>
       </c>
       <c r="H858" t="n">
         <v>2728302</v>
@@ -25280,7 +25280,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G859" t="n">
-        <v>9.16329479217529</v>
+        <v>9.16329383850098</v>
       </c>
       <c r="H859" t="n">
         <v>1906242</v>
@@ -25309,7 +25309,7 @@
         <v>10.5101757049561</v>
       </c>
       <c r="G860" t="n">
-        <v>9.31909561157227</v>
+        <v>9.31909465789795</v>
       </c>
       <c r="H860" t="n">
         <v>1842259</v>
@@ -25338,7 +25338,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G861" t="n">
-        <v>9.25232315063477</v>
+        <v>9.25232410430908</v>
       </c>
       <c r="H861" t="n">
         <v>2313809</v>
@@ -25512,7 +25512,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H867" t="n">
         <v>1477729</v>
@@ -25686,7 +25686,7 @@
         <v>10.582971572876</v>
       </c>
       <c r="G873" t="n">
-        <v>9.38364028930664</v>
+        <v>9.38364124298096</v>
       </c>
       <c r="H873" t="n">
         <v>4424197</v>
@@ -25715,7 +25715,7 @@
         <v>10.768726348877</v>
       </c>
       <c r="G874" t="n">
-        <v>9.5483455657959</v>
+        <v>9.54834461212158</v>
       </c>
       <c r="H874" t="n">
         <v>1898679</v>
@@ -25773,7 +25773,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G876" t="n">
-        <v>9.23451805114746</v>
+        <v>9.23451900482178</v>
       </c>
       <c r="H876" t="n">
         <v>3483538</v>
@@ -25802,7 +25802,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G877" t="n">
-        <v>9.33912658691406</v>
+        <v>9.33912754058838</v>
       </c>
       <c r="H877" t="n">
         <v>2554085</v>
@@ -25831,7 +25831,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G878" t="n">
-        <v>9.27012920379639</v>
+        <v>9.2701301574707</v>
       </c>
       <c r="H878" t="n">
         <v>1207602</v>
@@ -25918,7 +25918,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G881" t="n">
-        <v>9.60621452331543</v>
+        <v>9.6062126159668</v>
       </c>
       <c r="H881" t="n">
         <v>3879724</v>
@@ -26034,7 +26034,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G885" t="n">
-        <v>9.49047470092773</v>
+        <v>9.49047565460205</v>
       </c>
       <c r="H885" t="n">
         <v>1721405</v>
@@ -26121,7 +26121,7 @@
         <v>10.9820928573608</v>
       </c>
       <c r="G888" t="n">
-        <v>9.7375316619873</v>
+        <v>9.73753070831299</v>
       </c>
       <c r="H888" t="n">
         <v>1257161</v>
@@ -26150,7 +26150,7 @@
         <v>11.2431526184082</v>
       </c>
       <c r="G889" t="n">
-        <v>9.9690055847168</v>
+        <v>9.96900653839111</v>
       </c>
       <c r="H889" t="n">
         <v>2480426</v>
@@ -26266,7 +26266,7 @@
         <v>11.0272760391235</v>
       </c>
       <c r="G893" t="n">
-        <v>9.7775936126709</v>
+        <v>9.77759456634521</v>
       </c>
       <c r="H893" t="n">
         <v>2592934</v>
@@ -26295,7 +26295,7 @@
         <v>11.2130298614502</v>
       </c>
       <c r="G894" t="n">
-        <v>9.94229793548584</v>
+        <v>9.94229698181152</v>
       </c>
       <c r="H894" t="n">
         <v>2717697</v>
@@ -26411,7 +26411,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070013046265</v>
+        <v>10.1070003509521</v>
       </c>
       <c r="H898" t="n">
         <v>2738861</v>
@@ -26440,7 +26440,7 @@
         <v>11.2381324768066</v>
       </c>
       <c r="G899" t="n">
-        <v>9.96455383300781</v>
+        <v>9.96455478668213</v>
       </c>
       <c r="H899" t="n">
         <v>2760288</v>
@@ -26469,7 +26469,7 @@
         <v>11.4715795516968</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1715459823608</v>
+        <v>10.1715469360352</v>
       </c>
       <c r="H900" t="n">
         <v>3265887</v>
@@ -26527,7 +26527,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304893493652</v>
+        <v>9.71304798126221</v>
       </c>
       <c r="H902" t="n">
         <v>2481185</v>
@@ -26643,7 +26643,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G906" t="n">
-        <v>10.0157461166382</v>
+        <v>10.0157451629639</v>
       </c>
       <c r="H906" t="n">
         <v>2792394</v>
@@ -26817,7 +26817,7 @@
         <v>11.1829080581665</v>
       </c>
       <c r="G912" t="n">
-        <v>9.91558933258057</v>
+        <v>9.91558837890625</v>
       </c>
       <c r="H912" t="n">
         <v>2387048</v>
@@ -26846,7 +26846,7 @@
         <v>10.7411136627197</v>
       </c>
       <c r="G913" t="n">
-        <v>9.52386093139648</v>
+        <v>9.5238618850708</v>
       </c>
       <c r="H913" t="n">
         <v>4157164</v>
@@ -26875,7 +26875,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G914" t="n">
-        <v>9.2078104019165</v>
+        <v>9.20780944824219</v>
       </c>
       <c r="H914" t="n">
         <v>3497415</v>
@@ -27049,7 +27049,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G920" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H920" t="n">
         <v>3210453</v>
@@ -27107,7 +27107,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.9518518447876</v>
+        <v>8.95185089111328</v>
       </c>
       <c r="H922" t="n">
         <v>2394616</v>
@@ -27223,7 +27223,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G926" t="n">
-        <v>9.31464290618896</v>
+        <v>9.31464385986328</v>
       </c>
       <c r="H926" t="n">
         <v>1774533</v>
@@ -27252,7 +27252,7 @@
         <v>10.2842588424683</v>
       </c>
       <c r="G927" t="n">
-        <v>9.1187801361084</v>
+        <v>9.11878108978271</v>
       </c>
       <c r="H927" t="n">
         <v>2220798</v>
@@ -27281,7 +27281,7 @@
         <v>10.3545436859131</v>
       </c>
       <c r="G928" t="n">
-        <v>9.1810998916626</v>
+        <v>9.18110084533691</v>
       </c>
       <c r="H928" t="n">
         <v>1304029</v>
@@ -27310,7 +27310,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H929" t="n">
         <v>2564513</v>
@@ -27368,7 +27368,7 @@
         <v>10.9092969894409</v>
       </c>
       <c r="G931" t="n">
-        <v>9.6729850769043</v>
+        <v>9.67298603057861</v>
       </c>
       <c r="H931" t="n">
         <v>2301134</v>
@@ -27455,7 +27455,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G934" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H934" t="n">
         <v>1857397</v>
@@ -27687,7 +27687,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403856277466</v>
+        <v>10.1403875350952</v>
       </c>
       <c r="H942" t="n">
         <v>2004685</v>
@@ -27774,7 +27774,7 @@
         <v>11.1854181289673</v>
       </c>
       <c r="G945" t="n">
-        <v>9.91781425476074</v>
+        <v>9.91781520843506</v>
       </c>
       <c r="H945" t="n">
         <v>2493319</v>
@@ -27803,7 +27803,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G946" t="n">
-        <v>9.87107467651367</v>
+        <v>9.87107372283936</v>
       </c>
       <c r="H946" t="n">
         <v>2839086</v>
@@ -27832,7 +27832,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G947" t="n">
-        <v>9.84659099578857</v>
+        <v>9.84659194946289</v>
       </c>
       <c r="H947" t="n">
         <v>2212266</v>
@@ -27890,7 +27890,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392574310303</v>
+        <v>9.56392383575439</v>
       </c>
       <c r="H949" t="n">
         <v>2157126</v>
@@ -27948,7 +27948,7 @@
         <v>10.4524421691895</v>
       </c>
       <c r="G951" t="n">
-        <v>9.26790332794189</v>
+        <v>9.26790428161621</v>
       </c>
       <c r="H951" t="n">
         <v>2009025</v>
@@ -27977,7 +27977,7 @@
         <v>10.4499320983887</v>
       </c>
       <c r="G952" t="n">
-        <v>9.26567935943604</v>
+        <v>9.26567840576172</v>
       </c>
       <c r="H952" t="n">
         <v>2896071</v>
@@ -28035,7 +28035,7 @@
         <v>10.2164840698242</v>
       </c>
       <c r="G954" t="n">
-        <v>9.05868625640869</v>
+        <v>9.05868530273438</v>
       </c>
       <c r="H954" t="n">
         <v>3488046</v>
@@ -28151,7 +28151,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G958" t="n">
-        <v>9.16551971435547</v>
+        <v>9.1655216217041</v>
       </c>
       <c r="H958" t="n">
         <v>3044501</v>
@@ -28209,7 +28209,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00972080230713</v>
+        <v>9.00971984863281</v>
       </c>
       <c r="H960" t="n">
         <v>3059945</v>
@@ -28267,7 +28267,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G962" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H962" t="n">
         <v>3934669</v>
@@ -28325,7 +28325,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G964" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H964" t="n">
         <v>4071910</v>
@@ -28441,7 +28441,7 @@
         <v>10.3294429779053</v>
       </c>
       <c r="G968" t="n">
-        <v>9.15884399414062</v>
+        <v>9.15884304046631</v>
       </c>
       <c r="H968" t="n">
         <v>2590661</v>
@@ -28470,7 +28470,7 @@
         <v>10.2792387008667</v>
       </c>
       <c r="G969" t="n">
-        <v>9.11432933807373</v>
+        <v>9.11433029174805</v>
       </c>
       <c r="H969" t="n">
         <v>2928089</v>
@@ -28586,7 +28586,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65963172912598</v>
+        <v>9.65962982177734</v>
       </c>
       <c r="H973" t="n">
         <v>3880597</v>
@@ -28615,7 +28615,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G974" t="n">
-        <v>9.51050853729248</v>
+        <v>9.51050662994385</v>
       </c>
       <c r="H974" t="n">
         <v>4349124</v>
@@ -28731,7 +28731,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G978" t="n">
-        <v>9.60621452331543</v>
+        <v>9.6062126159668</v>
       </c>
       <c r="H978" t="n">
         <v>5460186</v>
@@ -28818,7 +28818,7 @@
         <v>11.2306022644043</v>
       </c>
       <c r="G981" t="n">
-        <v>9.95787906646729</v>
+        <v>9.95787715911865</v>
       </c>
       <c r="H981" t="n">
         <v>2713471</v>
@@ -28847,7 +28847,7 @@
         <v>11.1402349472046</v>
       </c>
       <c r="G982" t="n">
-        <v>9.87775135040283</v>
+        <v>9.87775230407715</v>
       </c>
       <c r="H982" t="n">
         <v>2778291</v>
@@ -28992,7 +28992,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H987" t="n">
         <v>8182251</v>
@@ -29021,7 +29021,7 @@
         <v>10.7536649703979</v>
       </c>
       <c r="G988" t="n">
-        <v>9.53498935699463</v>
+        <v>9.53499031066895</v>
       </c>
       <c r="H988" t="n">
         <v>3248486</v>
@@ -29137,7 +29137,7 @@
         <v>10.7536649703979</v>
       </c>
       <c r="G992" t="n">
-        <v>9.53498935699463</v>
+        <v>9.53499031066895</v>
       </c>
       <c r="H992" t="n">
         <v>3374594</v>
@@ -29195,7 +29195,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G994" t="n">
-        <v>9.45931625366211</v>
+        <v>9.45931529998779</v>
       </c>
       <c r="H994" t="n">
         <v>2914765</v>
@@ -29253,7 +29253,7 @@
         <v>10.7135019302368</v>
       </c>
       <c r="G996" t="n">
-        <v>9.4993782043457</v>
+        <v>9.49937915802002</v>
       </c>
       <c r="H996" t="n">
         <v>2076226</v>
@@ -29282,7 +29282,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G997" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H997" t="n">
         <v>4136816</v>
@@ -29369,7 +29369,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.25232315063477</v>
+        <v>9.25232410430908</v>
       </c>
       <c r="H1000" t="n">
         <v>2435099</v>
@@ -29398,7 +29398,7 @@
         <v>10.427339553833</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.24564647674561</v>
+        <v>9.24564552307129</v>
       </c>
       <c r="H1001" t="n">
         <v>2310864</v>
@@ -29427,7 +29427,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H1002" t="n">
         <v>2942968</v>
@@ -29543,7 +29543,7 @@
         <v>10.582971572876</v>
       </c>
       <c r="G1006" t="n">
-        <v>9.38364028930664</v>
+        <v>9.38364124298096</v>
       </c>
       <c r="H1006" t="n">
         <v>2721399</v>
@@ -29572,7 +29572,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467674255371</v>
+        <v>9.33467578887939</v>
       </c>
       <c r="H1007" t="n">
         <v>3861795</v>
@@ -29601,7 +29601,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.45931625366211</v>
+        <v>9.45931529998779</v>
       </c>
       <c r="H1008" t="n">
         <v>2116813</v>
@@ -29630,7 +29630,7 @@
         <v>10.7938280105591</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.57060146331787</v>
+        <v>9.57060241699219</v>
       </c>
       <c r="H1009" t="n">
         <v>3043149</v>
@@ -29746,7 +29746,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.56169891357422</v>
+        <v>9.5616979598999</v>
       </c>
       <c r="H1013" t="n">
         <v>1635593</v>
@@ -29804,7 +29804,7 @@
         <v>10.934398651123</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.6952428817749</v>
+        <v>9.69524192810059</v>
       </c>
       <c r="H1015" t="n">
         <v>2311969</v>
@@ -29862,7 +29862,7 @@
         <v>11.0925407409668</v>
       </c>
       <c r="G1017" t="n">
-        <v>9.83546352386475</v>
+        <v>9.83546257019043</v>
       </c>
       <c r="H1017" t="n">
         <v>3772987</v>
@@ -29920,7 +29920,7 @@
         <v>11.1728668212891</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.9066858291626</v>
+        <v>9.90668487548828</v>
       </c>
       <c r="H1019" t="n">
         <v>3341541</v>
@@ -30036,7 +30036,7 @@
         <v>11.120153427124</v>
       </c>
       <c r="G1023" t="n">
-        <v>9.85994529724121</v>
+        <v>9.85994625091553</v>
       </c>
       <c r="H1023" t="n">
         <v>2013478</v>
@@ -30152,7 +30152,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H1027" t="n">
         <v>2223593</v>
@@ -30210,7 +30210,7 @@
         <v>11.1126232147217</v>
       </c>
       <c r="G1029" t="n">
-        <v>9.85326957702637</v>
+        <v>9.85326862335205</v>
       </c>
       <c r="H1029" t="n">
         <v>1959789</v>
@@ -30471,7 +30471,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H1038" t="n">
         <v>4452658</v>
@@ -30500,7 +30500,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.31974601745605</v>
+        <v>8.31974697113037</v>
       </c>
       <c r="H1039" t="n">
         <v>4814559</v>
@@ -30529,7 +30529,7 @@
         <v>9.75962924957275</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.65360546112061</v>
+        <v>8.65360450744629</v>
       </c>
       <c r="H1040" t="n">
         <v>7621307</v>
@@ -30674,7 +30674,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H1045" t="n">
         <v>5766485</v>
@@ -30732,7 +30732,7 @@
         <v>9.51613998413086</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.43770885467529</v>
+        <v>8.43770980834961</v>
       </c>
       <c r="H1047" t="n">
         <v>3892374</v>
@@ -30761,7 +30761,7 @@
         <v>9.55630302429199</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.47332096099854</v>
+        <v>8.47332191467285</v>
       </c>
       <c r="H1048" t="n">
         <v>2650515</v>
@@ -30790,7 +30790,7 @@
         <v>9.41573238372803</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.34868049621582</v>
+        <v>8.34868144989014</v>
       </c>
       <c r="H1049" t="n">
         <v>4412760</v>
@@ -30819,7 +30819,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.43548393249512</v>
+        <v>8.43548488616943</v>
       </c>
       <c r="H1050" t="n">
         <v>4171244</v>
@@ -30935,7 +30935,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754821777344</v>
+        <v>7.62754774093628</v>
       </c>
       <c r="H1054" t="n">
         <v>5328087</v>
@@ -31051,7 +31051,7 @@
         <v>8.3037166595459</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.36268663406372</v>
+        <v>7.36268615722656</v>
       </c>
       <c r="H1058" t="n">
         <v>5909074</v>
@@ -31080,7 +31080,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585174560547</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H1059" t="n">
         <v>5991896</v>
@@ -31109,7 +31109,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111692428589</v>
+        <v>7.07111740112305</v>
       </c>
       <c r="H1060" t="n">
         <v>4984381</v>
@@ -31138,7 +31138,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.70832443237305</v>
+        <v>6.70832347869873</v>
       </c>
       <c r="H1061" t="n">
         <v>5838598</v>
@@ -31196,7 +31196,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.9500036239624</v>
+        <v>4.95000410079956</v>
       </c>
       <c r="H1063" t="n">
         <v>15725169</v>
@@ -31225,7 +31225,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.9500036239624</v>
+        <v>4.95000410079956</v>
       </c>
       <c r="H1064" t="n">
         <v>14702152</v>
@@ -31283,7 +31283,7 @@
         <v>4.89613008499146</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.34126853942871</v>
+        <v>4.34126901626587</v>
       </c>
       <c r="H1066" t="n">
         <v>10214235</v>
@@ -31312,7 +31312,7 @@
         <v>5.16848611831665</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.58275938034058</v>
+        <v>4.58276033401489</v>
       </c>
       <c r="H1067" t="n">
         <v>9831037</v>
@@ -31515,7 +31515,7 @@
         <v>5.85627889633179</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.19260740280151</v>
+        <v>5.19260787963867</v>
       </c>
       <c r="H1074" t="n">
         <v>6147761</v>
@@ -31544,7 +31544,7 @@
         <v>5.8261570930481</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.1658992767334</v>
+        <v>5.16589975357056</v>
       </c>
       <c r="H1075" t="n">
         <v>7136455</v>
@@ -31631,7 +31631,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.98561525344849</v>
+        <v>4.98561573028564</v>
       </c>
       <c r="H1078" t="n">
         <v>2485771</v>
@@ -31660,7 +31660,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1079" t="n">
-        <v>4.98561525344849</v>
+        <v>4.98561573028564</v>
       </c>
       <c r="H1079" t="n">
         <v>4812027</v>
@@ -31718,7 +31718,7 @@
         <v>6.06713485717773</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.37956809997559</v>
+        <v>5.37956762313843</v>
       </c>
       <c r="H1081" t="n">
         <v>8617110</v>
@@ -31747,7 +31747,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386259078979</v>
+        <v>5.28386211395264</v>
       </c>
       <c r="H1082" t="n">
         <v>6987858</v>
@@ -31776,7 +31776,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950567245483</v>
+        <v>5.33950614929199</v>
       </c>
       <c r="H1083" t="n">
         <v>4088673</v>
@@ -31863,7 +31863,7 @@
         <v>6.04956388473511</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.36398839950562</v>
+        <v>5.36398887634277</v>
       </c>
       <c r="H1086" t="n">
         <v>5596784</v>
@@ -31892,7 +31892,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.29276561737061</v>
+        <v>5.29276514053345</v>
       </c>
       <c r="H1087" t="n">
         <v>3514754</v>
@@ -32037,7 +32037,7 @@
         <v>5.28395509719849</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.68514347076416</v>
+        <v>4.685142993927</v>
       </c>
       <c r="H1092" t="n">
         <v>4658214</v>
@@ -32066,7 +32066,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445537567139</v>
+        <v>4.95445489883423</v>
       </c>
       <c r="H1093" t="n">
         <v>3686235</v>
@@ -32211,7 +32211,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928550720215</v>
+        <v>5.19928503036499</v>
       </c>
       <c r="H1098" t="n">
         <v>4783125</v>
@@ -32298,7 +32298,7 @@
         <v>5.79101419448853</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.13473892211914</v>
+        <v>5.1347393989563</v>
       </c>
       <c r="H1101" t="n">
         <v>3599923</v>
@@ -32356,7 +32356,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470794677734</v>
+        <v>5.11470746994019</v>
       </c>
       <c r="H1103" t="n">
         <v>2616491</v>
@@ -32385,7 +32385,7 @@
         <v>5.80858516693115</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15031909942627</v>
+        <v>5.15031862258911</v>
       </c>
       <c r="H1104" t="n">
         <v>2378841</v>
@@ -32414,7 +32414,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248159408569</v>
+        <v>5.11248207092285</v>
       </c>
       <c r="H1105" t="n">
         <v>2051727</v>
@@ -32472,7 +32472,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.92329549789429</v>
+        <v>4.92329597473145</v>
       </c>
       <c r="H1107" t="n">
         <v>1872366</v>
@@ -32646,7 +32646,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.79800081253052</v>
+        <v>4.79800033569336</v>
       </c>
       <c r="H1113" t="n">
         <v>3350805</v>
@@ -32733,7 +32733,7 @@
         <v>5.46217918395996</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.865074634552</v>
+        <v>4.86507511138916</v>
       </c>
       <c r="H1116" t="n">
         <v>3829378</v>
@@ -32762,7 +32762,7 @@
         <v>5.30905723571777</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.72869110107422</v>
+        <v>4.72869157791138</v>
       </c>
       <c r="H1117" t="n">
         <v>7700374</v>
@@ -32907,7 +32907,7 @@
         <v>5.79854488372803</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.16466999053955</v>
+        <v>5.16467046737671</v>
       </c>
       <c r="H1122" t="n">
         <v>12491580</v>
@@ -32965,7 +32965,7 @@
         <v>6.46876621246338</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.76162576675415</v>
+        <v>5.76162528991699</v>
       </c>
       <c r="H1124" t="n">
         <v>11268120</v>
@@ -32994,7 +32994,7 @@
         <v>6.59176588058472</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.87117910385132</v>
+        <v>5.87117958068848</v>
       </c>
       <c r="H1125" t="n">
         <v>10577677</v>
@@ -33023,7 +33023,7 @@
         <v>6.41354179382324</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.71243762969971</v>
+        <v>5.71243810653687</v>
       </c>
       <c r="H1126" t="n">
         <v>6490655</v>
@@ -33139,7 +33139,7 @@
         <v>5.99182987213135</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33682584762573</v>
+        <v>5.33682632446289</v>
       </c>
       <c r="H1130" t="n">
         <v>5065402</v>
@@ -33197,7 +33197,7 @@
         <v>5.98680877685547</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.3323540687561</v>
+        <v>5.33235359191895</v>
       </c>
       <c r="H1132" t="n">
         <v>5119610</v>
@@ -33342,7 +33342,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.0841817855835</v>
+        <v>5.08418226242065</v>
       </c>
       <c r="H1137" t="n">
         <v>3931365</v>
@@ -33429,7 +33429,7 @@
         <v>5.61530113220215</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.00145816802979</v>
+        <v>5.00145769119263</v>
       </c>
       <c r="H1140" t="n">
         <v>4272132</v>
@@ -33487,7 +33487,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.97686338424683</v>
+        <v>4.97686290740967</v>
       </c>
       <c r="H1142" t="n">
         <v>3387639</v>
@@ -33574,7 +33574,7 @@
         <v>5.68558597564697</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.06405973434448</v>
+        <v>5.06405925750732</v>
       </c>
       <c r="H1145" t="n">
         <v>3689754</v>
@@ -33661,7 +33661,7 @@
         <v>5.27642488479614</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.69962596893311</v>
+        <v>4.69962644577026</v>
       </c>
       <c r="H1148" t="n">
         <v>5584746</v>
@@ -33748,7 +33748,7 @@
         <v>5.28897619247437</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.71080541610718</v>
+        <v>4.71080589294434</v>
       </c>
       <c r="H1151" t="n">
         <v>6369097</v>
@@ -33777,7 +33777,7 @@
         <v>5.36679220199585</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.78011465072632</v>
+        <v>4.78011512756348</v>
       </c>
       <c r="H1152" t="n">
         <v>6019418</v>
@@ -33806,7 +33806,7 @@
         <v>5.47724008560181</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.87848949432373</v>
+        <v>4.87848901748657</v>
       </c>
       <c r="H1153" t="n">
         <v>3853871</v>
@@ -34067,7 +34067,7 @@
         <v>4.92123222351074</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.38326215744019</v>
+        <v>4.38326168060303</v>
       </c>
       <c r="H1162" t="n">
         <v>24661467</v>
@@ -34154,7 +34154,7 @@
         <v>4.57357120513916</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.07360553741455</v>
+        <v>4.07360601425171</v>
       </c>
       <c r="H1165" t="n">
         <v>7438646</v>
@@ -34299,7 +34299,7 @@
         <v>4.96892595291138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.42574214935303</v>
+        <v>4.42574167251587</v>
       </c>
       <c r="H1170" t="n">
         <v>3451603</v>
@@ -34415,7 +34415,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1174" t="n">
-        <v>4.34189987182617</v>
+        <v>4.34190034866333</v>
       </c>
       <c r="H1174" t="n">
         <v>4695442</v>
@@ -34589,7 +34589,7 @@
         <v>4.66895818710327</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.15856552124023</v>
+        <v>4.15856599807739</v>
       </c>
       <c r="H1180" t="n">
         <v>6557504</v>
@@ -34734,7 +34734,7 @@
         <v>4.50579500198364</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.01323843002319</v>
+        <v>4.01323890686035</v>
       </c>
       <c r="H1185" t="n">
         <v>4155094</v>
@@ -34821,7 +34821,7 @@
         <v>4.39032697677612</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.91039347648621</v>
+        <v>3.91039323806763</v>
       </c>
       <c r="H1188" t="n">
         <v>4258438</v>
@@ -34850,7 +34850,7 @@
         <v>4.29242897033691</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.82319736480713</v>
+        <v>3.82319688796997</v>
       </c>
       <c r="H1189" t="n">
         <v>7837081</v>
@@ -34937,7 +34937,7 @@
         <v>4.19327592849731</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.73488283157349</v>
+        <v>3.73488306999207</v>
       </c>
       <c r="H1192" t="n">
         <v>4846298</v>
@@ -34995,7 +34995,7 @@
         <v>4.07906293869019</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.63315534591675</v>
+        <v>3.63315558433533</v>
       </c>
       <c r="H1194" t="n">
         <v>8280016</v>
@@ -35111,7 +35111,7 @@
         <v>4.22465419769287</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.76283097267151</v>
+        <v>3.76283121109009</v>
       </c>
       <c r="H1198" t="n">
         <v>5589044</v>
@@ -35401,7 +35401,7 @@
         <v>3.56321811676025</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.17370080947876</v>
+        <v>3.17370057106018</v>
       </c>
       <c r="H1208" t="n">
         <v>6464136</v>
@@ -35459,7 +35459,7 @@
         <v>3.86444091796875</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.4419949054718</v>
+        <v>3.44199514389038</v>
       </c>
       <c r="H1210" t="n">
         <v>7063864</v>
@@ -35604,7 +35604,7 @@
         <v>3.79415607452393</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.3793933391571</v>
+        <v>3.37939357757568</v>
       </c>
       <c r="H1215" t="n">
         <v>3909509</v>
@@ -35633,7 +35633,7 @@
         <v>3.65609502792358</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.25642466545105</v>
+        <v>3.25642490386963</v>
       </c>
       <c r="H1216" t="n">
         <v>4082735</v>
@@ -35807,7 +35807,7 @@
         <v>3.59585094451904</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.20276641845703</v>
+        <v>3.20276618003845</v>
       </c>
       <c r="H1222" t="n">
         <v>5346240</v>
@@ -35836,7 +35836,7 @@
         <v>3.62597298622131</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.22959566116333</v>
+        <v>3.22959542274475</v>
       </c>
       <c r="H1223" t="n">
         <v>3204692</v>
@@ -35865,7 +35865,7 @@
         <v>3.68496203422546</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.28213620185852</v>
+        <v>3.28213596343994</v>
       </c>
       <c r="H1224" t="n">
         <v>4139377</v>
@@ -36010,7 +36010,7 @@
         <v>3.78411507606506</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.37045001983643</v>
+        <v>3.370450258255</v>
       </c>
       <c r="H1229" t="n">
         <v>8618018</v>
@@ -36184,7 +36184,7 @@
         <v>4.6940598487854</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.18092346191406</v>
+        <v>4.1809229850769</v>
       </c>
       <c r="H1235" t="n">
         <v>15804964</v>
@@ -36387,7 +36387,7 @@
         <v>4.89487504959106</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.35978651046753</v>
+        <v>4.35978603363037</v>
       </c>
       <c r="H1242" t="n">
         <v>6079967</v>
@@ -36445,7 +36445,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.27706241607666</v>
+        <v>4.2770619392395</v>
       </c>
       <c r="H1244" t="n">
         <v>4685519</v>
@@ -36474,7 +36474,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.47157573699951</v>
+        <v>4.47157526016235</v>
       </c>
       <c r="H1245" t="n">
         <v>7739906</v>
@@ -36532,7 +36532,7 @@
         <v>5.42201614379883</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.8293023109436</v>
+        <v>4.82930183410645</v>
       </c>
       <c r="H1247" t="n">
         <v>8336834</v>
@@ -36561,7 +36561,7 @@
         <v>5.30654716491699</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.72645568847656</v>
+        <v>4.72645616531372</v>
       </c>
       <c r="H1248" t="n">
         <v>6460441</v>
@@ -36619,7 +36619,7 @@
         <v>5.1333441734314</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.5721869468689</v>
+        <v>4.57218647003174</v>
       </c>
       <c r="H1250" t="n">
         <v>5110006</v>
@@ -36706,7 +36706,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.62584495544434</v>
+        <v>4.62584447860718</v>
       </c>
       <c r="H1253" t="n">
         <v>2827257</v>
@@ -36735,7 +36735,7 @@
         <v>5.35675096511841</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.77117109298706</v>
+        <v>4.77117156982422</v>
       </c>
       <c r="H1254" t="n">
         <v>5955094</v>
@@ -36793,7 +36793,7 @@
         <v>5.37683200836182</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.78905773162842</v>
+        <v>4.78905725479126</v>
       </c>
       <c r="H1256" t="n">
         <v>1840506</v>
@@ -36880,7 +36880,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1259" t="n">
         <v>4061775</v>
@@ -36938,7 +36938,7 @@
         <v>5.46719884872437</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.86954593658447</v>
+        <v>4.86954545974731</v>
       </c>
       <c r="H1261" t="n">
         <v>2064399</v>
@@ -36967,7 +36967,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1262" t="n">
         <v>5407097</v>
@@ -36996,7 +36996,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.86060285568237</v>
+        <v>4.86060237884521</v>
       </c>
       <c r="H1263" t="n">
         <v>3511782</v>
@@ -37112,7 +37112,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1267" t="n">
         <v>3396789</v>
@@ -37257,7 +37257,7 @@
         <v>5.82364702224731</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.18702840805054</v>
+        <v>5.18702793121338</v>
       </c>
       <c r="H1272" t="n">
         <v>7105248</v>
@@ -37315,7 +37315,7 @@
         <v>6.17256307601929</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.49780178070068</v>
+        <v>5.49780225753784</v>
       </c>
       <c r="H1274" t="n">
         <v>7287173</v>
@@ -37344,7 +37344,7 @@
         <v>6.10729789733887</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.43967151641846</v>
+        <v>5.4396710395813</v>
       </c>
       <c r="H1275" t="n">
         <v>6169237</v>
@@ -37431,7 +37431,7 @@
         <v>6.08721685409546</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.42178583145142</v>
+        <v>5.42178535461426</v>
       </c>
       <c r="H1278" t="n">
         <v>4068724</v>
@@ -37460,7 +37460,7 @@
         <v>6.00689077377319</v>
       </c>
       <c r="G1279" t="n">
-        <v>5.35024070739746</v>
+        <v>5.3502402305603</v>
       </c>
       <c r="H1279" t="n">
         <v>3024433</v>
@@ -37547,7 +37547,7 @@
         <v>5.85878896713257</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.21832895278931</v>
+        <v>5.21832847595215</v>
       </c>
       <c r="H1282" t="n">
         <v>3059439</v>
@@ -37692,7 +37692,7 @@
         <v>5.34169006347656</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.75775718688965</v>
+        <v>4.75775671005249</v>
       </c>
       <c r="H1287" t="n">
         <v>4046294</v>
@@ -37721,7 +37721,7 @@
         <v>5.59019899368286</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.9790997505188</v>
+        <v>4.97910022735596</v>
       </c>
       <c r="H1288" t="n">
         <v>7589590</v>
@@ -37924,7 +37924,7 @@
         <v>5.98178911209106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.32788276672363</v>
+        <v>5.32788324356079</v>
       </c>
       <c r="H1295" t="n">
         <v>5483636</v>
@@ -38098,7 +38098,7 @@
         <v>6.55160188674927</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.83540630340576</v>
+        <v>5.8354058265686</v>
       </c>
       <c r="H1301" t="n">
         <v>9385518</v>
@@ -38156,7 +38156,7 @@
         <v>6.3457670211792</v>
       </c>
       <c r="G1303" t="n">
-        <v>5.65207195281982</v>
+        <v>5.65207242965698</v>
       </c>
       <c r="H1303" t="n">
         <v>6157528</v>
@@ -38185,7 +38185,7 @@
         <v>6.35078716278076</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.65654373168945</v>
+        <v>5.65654325485229</v>
       </c>
       <c r="H1304" t="n">
         <v>5745479</v>
@@ -38214,7 +38214,7 @@
         <v>6.40852212905884</v>
       </c>
       <c r="G1305" t="n">
-        <v>5.70796728134155</v>
+        <v>5.70796680450439</v>
       </c>
       <c r="H1305" t="n">
         <v>3560044</v>
@@ -38243,7 +38243,7 @@
         <v>6.63192892074585</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.90695142745972</v>
+        <v>5.90695190429688</v>
       </c>
       <c r="H1306" t="n">
         <v>7874391</v>
@@ -38330,7 +38330,7 @@
         <v>6.00940084457397</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.35247659683228</v>
+        <v>5.35247611999512</v>
       </c>
       <c r="H1309" t="n">
         <v>24228663</v>
@@ -38388,7 +38388,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.0841817855835</v>
+        <v>5.08418226242065</v>
       </c>
       <c r="H1311" t="n">
         <v>8961866</v>
@@ -38417,7 +38417,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1312" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1312" t="n">
         <v>9655227</v>
@@ -38504,7 +38504,7 @@
         <v>5.91652393341064</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.26975250244141</v>
+        <v>5.26975202560425</v>
       </c>
       <c r="H1315" t="n">
         <v>12797834</v>
@@ -38533,7 +38533,7 @@
         <v>6.07215595245361</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.40837097167969</v>
+        <v>5.40837144851685</v>
       </c>
       <c r="H1316" t="n">
         <v>9400118</v>
@@ -38591,7 +38591,7 @@
         <v>6.07717609405518</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.41284275054932</v>
+        <v>5.41284227371216</v>
       </c>
       <c r="H1318" t="n">
         <v>4627496</v>
@@ -38649,7 +38649,7 @@
         <v>6.12486982345581</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.45532274246216</v>
+        <v>5.455322265625</v>
       </c>
       <c r="H1320" t="n">
         <v>2675208</v>
@@ -38707,7 +38707,7 @@
         <v>5.97174787521362</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.31893920898438</v>
+        <v>5.31893968582153</v>
       </c>
       <c r="H1322" t="n">
         <v>5171781</v>
@@ -38765,7 +38765,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.31670379638672</v>
+        <v>5.31670331954956</v>
       </c>
       <c r="H1324" t="n">
         <v>4027905</v>
@@ -38852,7 +38852,7 @@
         <v>5.69060611724854</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.06853055953979</v>
+        <v>5.06853103637695</v>
       </c>
       <c r="H1327" t="n">
         <v>7314312</v>
@@ -39055,7 +39055,7 @@
         <v>5.87887096405029</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.23621559143066</v>
+        <v>5.23621511459351</v>
       </c>
       <c r="H1334" t="n">
         <v>3164034</v>
@@ -39287,7 +39287,7 @@
         <v>5.83870792388916</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.20044231414795</v>
+        <v>5.20044279098511</v>
       </c>
       <c r="H1342" t="n">
         <v>4486409</v>
@@ -39374,7 +39374,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.97686338424683</v>
+        <v>4.97686290740967</v>
       </c>
       <c r="H1345" t="n">
         <v>5024234</v>
@@ -39490,7 +39490,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.94556283950806</v>
+        <v>4.94556331634521</v>
       </c>
       <c r="H1349" t="n">
         <v>4621291</v>
@@ -39577,7 +39577,7 @@
         <v>4.87855911254883</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.34525346755981</v>
+        <v>4.34525394439697</v>
       </c>
       <c r="H1352" t="n">
         <v>14868855</v>
@@ -39606,7 +39606,7 @@
         <v>4.82333517074585</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.29606676101685</v>
+        <v>4.29606628417969</v>
       </c>
       <c r="H1353" t="n">
         <v>10990037</v>
@@ -39751,7 +39751,7 @@
         <v>5.06054782867432</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.50734806060791</v>
+        <v>4.50734853744507</v>
       </c>
       <c r="H1358" t="n">
         <v>3316325</v>
@@ -39954,7 +39954,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.69068288803101</v>
+        <v>4.69068336486816</v>
       </c>
       <c r="H1365" t="n">
         <v>9046399</v>
@@ -40012,7 +40012,7 @@
         <v>5.1383638381958</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.57665729522705</v>
+        <v>4.57665777206421</v>
       </c>
       <c r="H1367" t="n">
         <v>2528599</v>
@@ -40070,7 +40070,7 @@
         <v>5.12832307815552</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.56771421432495</v>
+        <v>4.56771469116211</v>
       </c>
       <c r="H1369" t="n">
         <v>2605182</v>
@@ -40186,7 +40186,7 @@
         <v>5.11828184127808</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.55877065658569</v>
+        <v>4.55877113342285</v>
       </c>
       <c r="H1373" t="n">
         <v>4133342</v>
@@ -40244,7 +40244,7 @@
         <v>5.3793420791626</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.79129266738892</v>
+        <v>4.79129314422607</v>
       </c>
       <c r="H1375" t="n">
         <v>10178926</v>
@@ -40273,7 +40273,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1376" t="n">
         <v>5287449</v>
@@ -40389,7 +40389,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1380" t="n">
         <v>6843942</v>
@@ -40476,7 +40476,7 @@
         <v>5.56760692596436</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.95897769927979</v>
+        <v>4.95897722244263</v>
       </c>
       <c r="H1383" t="n">
         <v>4282870</v>
@@ -40679,7 +40679,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.72422027587891</v>
+        <v>4.72421979904175</v>
       </c>
       <c r="H1390" t="n">
         <v>3701384</v>
@@ -40737,7 +40737,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.72422027587891</v>
+        <v>4.72421979904175</v>
       </c>
       <c r="H1392" t="n">
         <v>2649454</v>
@@ -40766,7 +40766,7 @@
         <v>5.29901599884033</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.71974754333496</v>
+        <v>4.71974802017212</v>
       </c>
       <c r="H1393" t="n">
         <v>2108129</v>
@@ -40853,7 +40853,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1396" t="n">
-        <v>4.56324338912964</v>
+        <v>4.56324291229248</v>
       </c>
       <c r="H1396" t="n">
         <v>3303148</v>
@@ -40882,7 +40882,7 @@
         <v>5.22873115539551</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.65714597702026</v>
+        <v>4.65714645385742</v>
       </c>
       <c r="H1397" t="n">
         <v>3565887</v>
@@ -40911,7 +40911,7 @@
         <v>5.21868991851807</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.64820241928101</v>
+        <v>4.64820289611816</v>
       </c>
       <c r="H1398" t="n">
         <v>2418474</v>
@@ -41027,7 +41027,7 @@
         <v>4.90617084503174</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.3698468208313</v>
+        <v>4.36984729766846</v>
       </c>
       <c r="H1402" t="n">
         <v>5231002</v>
@@ -41056,7 +41056,7 @@
         <v>4.97143602371216</v>
       </c>
       <c r="G1403" t="n">
-        <v>4.42797756195068</v>
+        <v>4.42797803878784</v>
       </c>
       <c r="H1403" t="n">
         <v>3203342</v>
@@ -41114,7 +41114,7 @@
         <v>4.88483476638794</v>
       </c>
       <c r="G1405" t="n">
-        <v>4.35084295272827</v>
+        <v>4.35084342956543</v>
       </c>
       <c r="H1405" t="n">
         <v>3408367</v>
@@ -41172,7 +41172,7 @@
         <v>4.90240621566772</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.36649417877197</v>
+        <v>4.36649370193481</v>
       </c>
       <c r="H1407" t="n">
         <v>3512290</v>
@@ -41288,7 +41288,7 @@
         <v>4.75681495666504</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.23681783676147</v>
+        <v>4.23681831359863</v>
       </c>
       <c r="H1411" t="n">
         <v>4771701</v>
@@ -41462,7 +41462,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1417" t="n">
-        <v>4.5297064781189</v>
+        <v>4.52970600128174</v>
       </c>
       <c r="H1417" t="n">
         <v>3747890</v>
@@ -41549,7 +41549,7 @@
         <v>4.91119194030762</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.37431955337524</v>
+        <v>4.37431907653809</v>
       </c>
       <c r="H1420" t="n">
         <v>4386657</v>
@@ -41636,7 +41636,7 @@
         <v>4.92499780654907</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.38661575317383</v>
+        <v>4.38661623001099</v>
       </c>
       <c r="H1423" t="n">
         <v>3890806</v>
@@ -41694,7 +41694,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.56324338912964</v>
+        <v>4.56324291229248</v>
       </c>
       <c r="H1425" t="n">
         <v>5305491</v>
@@ -41723,7 +41723,7 @@
         <v>5.16597604751587</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.60125160217285</v>
+        <v>4.60125112533569</v>
       </c>
       <c r="H1426" t="n">
         <v>3581797</v>
@@ -41868,7 +41868,7 @@
         <v>4.98147678375244</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.43692064285278</v>
+        <v>4.43692111968994</v>
       </c>
       <c r="H1431" t="n">
         <v>1848823</v>
@@ -41926,7 +41926,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.27706241607666</v>
+        <v>4.2770619392395</v>
       </c>
       <c r="H1433" t="n">
         <v>3356625</v>
@@ -42013,7 +42013,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.47157573699951</v>
+        <v>4.47157526016235</v>
       </c>
       <c r="H1436" t="n">
         <v>3876966</v>
@@ -42216,7 +42216,7 @@
         <v>4.96139478683472</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41903400421143</v>
+        <v>4.41903448104858</v>
       </c>
       <c r="H1443" t="n">
         <v>3045903</v>
@@ -42332,7 +42332,7 @@
         <v>5.01662015914917</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.46822214126587</v>
+        <v>4.46822261810303</v>
       </c>
       <c r="H1447" t="n">
         <v>5734258</v>
@@ -42390,7 +42390,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.62584495544434</v>
+        <v>4.62584447860718</v>
       </c>
       <c r="H1449" t="n">
         <v>7048976</v>
@@ -42419,7 +42419,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.5297064781189</v>
+        <v>4.52970600128174</v>
       </c>
       <c r="H1450" t="n">
         <v>6506615</v>
@@ -42506,7 +42506,7 @@
         <v>4.99151802062988</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.4458646774292</v>
+        <v>4.44586420059204</v>
       </c>
       <c r="H1453" t="n">
         <v>2739262</v>
@@ -42535,7 +42535,7 @@
         <v>4.91244697570801</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.37543725967407</v>
+        <v>4.37543678283691</v>
       </c>
       <c r="H1454" t="n">
         <v>3529674</v>
@@ -42564,7 +42564,7 @@
         <v>5.07058906555176</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.51629161834717</v>
+        <v>4.51629209518433</v>
       </c>
       <c r="H1455" t="n">
         <v>5222595</v>
@@ -42825,7 +42825,7 @@
         <v>5.55003595352173</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.9433274269104</v>
+        <v>4.94332695007324</v>
       </c>
       <c r="H1464" t="n">
         <v>6413047</v>
@@ -42883,7 +42883,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.69068288803101</v>
+        <v>4.69068336486816</v>
       </c>
       <c r="H1466" t="n">
         <v>7328705</v>
@@ -42941,7 +42941,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.79800081253052</v>
+        <v>4.79800033569336</v>
       </c>
       <c r="H1468" t="n">
         <v>8090619</v>
@@ -42999,7 +42999,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1470" t="n">
         <v>6942701</v>
@@ -43144,7 +43144,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.91202640533447</v>
+        <v>4.91202592849731</v>
       </c>
       <c r="H1475" t="n">
         <v>2995584</v>
@@ -43202,7 +43202,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1477" t="n">
         <v>4075860</v>
@@ -43289,7 +43289,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.94556283950806</v>
+        <v>4.94556331634521</v>
       </c>
       <c r="H1480" t="n">
         <v>5065969</v>
@@ -43347,7 +43347,7 @@
         <v>4.87353897094727</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.3407826423645</v>
+        <v>4.34078216552734</v>
       </c>
       <c r="H1482" t="n">
         <v>28990116</v>
@@ -43492,7 +43492,7 @@
         <v>4.81203889846802</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.28600549697876</v>
+        <v>4.2860050201416</v>
       </c>
       <c r="H1487" t="n">
         <v>5381782</v>
@@ -43521,7 +43521,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.34189987182617</v>
+        <v>4.34190034866333</v>
       </c>
       <c r="H1488" t="n">
         <v>5511409</v>
@@ -43666,7 +43666,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.39220523834229</v>
+        <v>4.39220476150513</v>
       </c>
       <c r="H1493" t="n">
         <v>2167743</v>
@@ -43956,7 +43956,7 @@
         <v>4.46563196182251</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.97746610641479</v>
+        <v>3.97746634483337</v>
       </c>
       <c r="H1503" t="n">
         <v>7272410</v>
@@ -43985,7 +43985,7 @@
         <v>4.50328493118286</v>
       </c>
       <c r="G1504" t="n">
-        <v>4.0110034942627</v>
+        <v>4.01100301742554</v>
       </c>
       <c r="H1504" t="n">
         <v>4367193</v>
@@ -44014,7 +44014,7 @@
         <v>4.42170381546021</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.93834018707275</v>
+        <v>3.93833994865417</v>
       </c>
       <c r="H1505" t="n">
         <v>3362331</v>
@@ -44130,7 +44130,7 @@
         <v>4.59365177154541</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.09149169921875</v>
+        <v>4.09149122238159</v>
       </c>
       <c r="H1509" t="n">
         <v>4350486</v>
@@ -44188,7 +44188,7 @@
         <v>4.56729507446289</v>
       </c>
       <c r="G1511" t="n">
-        <v>4.06801605224609</v>
+        <v>4.06801557540894</v>
       </c>
       <c r="H1511" t="n">
         <v>4359136</v>
@@ -44275,7 +44275,7 @@
         <v>4.41040802001953</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.92827916145325</v>
+        <v>3.92827892303467</v>
       </c>
       <c r="H1514" t="n">
         <v>3179388</v>
@@ -44304,7 +44304,7 @@
         <v>4.4455509185791</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.95958018302917</v>
+        <v>3.95958042144775</v>
       </c>
       <c r="H1515" t="n">
         <v>2325197</v>
@@ -44333,7 +44333,7 @@
         <v>4.37275505065918</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.89474248886108</v>
+        <v>3.89474201202393</v>
       </c>
       <c r="H1516" t="n">
         <v>3004717</v>
@@ -44507,7 +44507,7 @@
         <v>4.55097913742065</v>
       </c>
       <c r="G1522" t="n">
-        <v>4.05348348617554</v>
+        <v>4.0534839630127</v>
       </c>
       <c r="H1522" t="n">
         <v>1502529</v>
@@ -44652,7 +44652,7 @@
         <v>4.78317213058472</v>
       </c>
       <c r="G1527" t="n">
-        <v>4.26029443740845</v>
+        <v>4.26029396057129</v>
       </c>
       <c r="H1527" t="n">
         <v>2970018</v>
@@ -44768,7 +44768,7 @@
         <v>4.91495704650879</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.37767267227173</v>
+        <v>4.37767314910889</v>
       </c>
       <c r="H1531" t="n">
         <v>2759069</v>
@@ -44913,7 +44913,7 @@
         <v>5.03042602539062</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.48051929473877</v>
+        <v>4.48051881790161</v>
       </c>
       <c r="H1536" t="n">
         <v>2349535</v>
@@ -44971,7 +44971,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.39220523834229</v>
+        <v>4.39220476150513</v>
       </c>
       <c r="H1538" t="n">
         <v>3995107</v>
@@ -45058,7 +45058,7 @@
         <v>5.01410913467407</v>
       </c>
       <c r="G1541" t="n">
-        <v>4.46598625183105</v>
+        <v>4.4659857749939</v>
       </c>
       <c r="H1541" t="n">
         <v>2334898</v>
@@ -45348,7 +45348,7 @@
         <v>2.99591493606567</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.66841292381287</v>
+        <v>2.66841316223145</v>
       </c>
       <c r="H1551" t="n">
         <v>17072505</v>
@@ -45377,7 +45377,7 @@
         <v>3.02854704856873</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.69747805595398</v>
+        <v>2.6974778175354</v>
       </c>
       <c r="H1552" t="n">
         <v>16828629</v>
@@ -45522,7 +45522,7 @@
         <v>2.8616189956665</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.54879784584045</v>
+        <v>2.54879760742188</v>
       </c>
       <c r="H1557" t="n">
         <v>12600027</v>
@@ -45551,7 +45551,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.56221222877502</v>
+        <v>2.5622124671936</v>
       </c>
       <c r="H1558" t="n">
         <v>9318354</v>
@@ -45725,7 +45725,7 @@
         <v>2.51521301269531</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.24025964736938</v>
+        <v>2.24025940895081</v>
       </c>
       <c r="H1564" t="n">
         <v>6732142</v>
@@ -45754,7 +45754,7 @@
         <v>2.56165099143982</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.28162121772766</v>
+        <v>2.28162097930908</v>
       </c>
       <c r="H1565" t="n">
         <v>16777908</v>
@@ -45899,7 +45899,7 @@
         <v>2.56792688369751</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.28721117973328</v>
+        <v>2.2872109413147</v>
       </c>
       <c r="H1570" t="n">
         <v>5399583</v>
@@ -45928,7 +45928,7 @@
         <v>2.37715196609497</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.11729097366333</v>
+        <v>2.11729073524475</v>
       </c>
       <c r="H1571" t="n">
         <v>6070659</v>
@@ -46015,7 +46015,7 @@
         <v>2.58047795295715</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.29838991165161</v>
+        <v>2.29839015007019</v>
       </c>
       <c r="H1574" t="n">
         <v>9240163</v>
@@ -46131,7 +46131,7 @@
         <v>2.46450710296631</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.19509673118591</v>
+        <v>2.19509649276733</v>
       </c>
       <c r="H1578" t="n">
         <v>4819541</v>
@@ -46247,7 +46247,7 @@
         <v>2.67335510253906</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.38111400604248</v>
+        <v>2.38111424446106</v>
       </c>
       <c r="H1582" t="n">
         <v>3911764</v>
@@ -46392,7 +46392,7 @@
         <v>2.86287403106689</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.54991555213928</v>
+        <v>2.54991579055786</v>
       </c>
       <c r="H1587" t="n">
         <v>13747439</v>
@@ -46479,7 +46479,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.56221222877502</v>
+        <v>2.5622124671936</v>
       </c>
       <c r="H1590" t="n">
         <v>10760896</v>
@@ -46508,7 +46508,7 @@
         <v>2.93943500518799</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.61810731887817</v>
+        <v>2.61810708045959</v>
       </c>
       <c r="H1591" t="n">
         <v>7063060</v>
@@ -46537,7 +46537,7 @@
         <v>2.87919092178345</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.564448595047</v>
+        <v>2.56444883346558</v>
       </c>
       <c r="H1592" t="n">
         <v>10358249</v>
@@ -46566,7 +46566,7 @@
         <v>2.84404802322388</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.53314781188965</v>
+        <v>2.53314757347107</v>
       </c>
       <c r="H1593" t="n">
         <v>5883247</v>
@@ -46595,7 +46595,7 @@
         <v>2.77878308296204</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.47501730918884</v>
+        <v>2.47501707077026</v>
       </c>
       <c r="H1594" t="n">
         <v>7471517</v>
@@ -46653,7 +46653,7 @@
         <v>2.80262994766235</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.49625730514526</v>
+        <v>2.49625706672668</v>
       </c>
       <c r="H1596" t="n">
         <v>3079893</v>
@@ -46711,7 +46711,7 @@
         <v>2.79384398460388</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.48843169212341</v>
+        <v>2.48843145370483</v>
       </c>
       <c r="H1598" t="n">
         <v>2912676</v>
@@ -46740,7 +46740,7 @@
         <v>2.75744605064392</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.45601272583008</v>
+        <v>2.4560124874115</v>
       </c>
       <c r="H1599" t="n">
         <v>3637078</v>
@@ -46769,7 +46769,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.43700885772705</v>
+        <v>2.43700909614563</v>
       </c>
       <c r="H1600" t="n">
         <v>2248107</v>
@@ -46798,7 +46798,7 @@
         <v>2.84028291702271</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.52979397773743</v>
+        <v>2.52979421615601</v>
       </c>
       <c r="H1601" t="n">
         <v>4359715</v>
@@ -46885,7 +46885,7 @@
         <v>2.92437410354614</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.6046929359436</v>
+        <v>2.60469269752502</v>
       </c>
       <c r="H1604" t="n">
         <v>10127429</v>
@@ -46914,7 +46914,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.43700885772705</v>
+        <v>2.43700909614563</v>
       </c>
       <c r="H1605" t="n">
         <v>8650581</v>
@@ -47233,7 +47233,7 @@
         <v>2.48509001731873</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.21342945098877</v>
+        <v>2.21342968940735</v>
       </c>
       <c r="H1616" t="n">
         <v>11509858</v>
@@ -47262,7 +47262,7 @@
         <v>2.53780388832092</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.26038098335266</v>
+        <v>2.26038074493408</v>
       </c>
       <c r="H1617" t="n">
         <v>13634558</v>
@@ -47320,7 +47320,7 @@
         <v>2.68841600418091</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.39452886581421</v>
+        <v>2.39452862739563</v>
       </c>
       <c r="H1619" t="n">
         <v>6670481</v>
@@ -47349,7 +47349,7 @@
         <v>2.90680289268494</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.58904242515564</v>
+        <v>2.58904218673706</v>
       </c>
       <c r="H1620" t="n">
         <v>11371682</v>
@@ -47581,7 +47581,7 @@
         <v>2.97517991065979</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.6499445438385</v>
+        <v>2.64994478225708</v>
       </c>
       <c r="H1628" t="n">
         <v>9786163</v>
@@ -47755,7 +47755,7 @@
         <v>2.72426104545593</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.42645525932312</v>
+        <v>2.4264554977417</v>
       </c>
       <c r="H1634" t="n">
         <v>3222869</v>
@@ -47900,7 +47900,7 @@
         <v>2.37423992156982</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.11469721794128</v>
+        <v>2.11469697952271</v>
       </c>
       <c r="H1639" t="n">
         <v>5658326</v>
@@ -47987,7 +47987,7 @@
         <v>1.96649694442749</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.75152707099915</v>
+        <v>1.75152695178986</v>
       </c>
       <c r="H1642" t="n">
         <v>12639154</v>
@@ -48016,7 +48016,7 @@
         <v>2.01657509803772</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.79613077640533</v>
+        <v>1.79613089561462</v>
       </c>
       <c r="H1643" t="n">
         <v>25382152</v>
@@ -48103,7 +48103,7 @@
         <v>2.21557092666626</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.97337329387665</v>
+        <v>1.97337317466736</v>
       </c>
       <c r="H1646" t="n">
         <v>8434013</v>
@@ -48132,7 +48132,7 @@
         <v>1.73798203468323</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.54799246788025</v>
+        <v>1.54799258708954</v>
       </c>
       <c r="H1647" t="n">
         <v>26496542</v>
@@ -48161,7 +48161,7 @@
         <v>1.59776198863983</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.42310070991516</v>
+        <v>1.42310082912445</v>
       </c>
       <c r="H1648" t="n">
         <v>48720201</v>
@@ -48190,7 +48190,7 @@
         <v>1.24932205677032</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.11275100708008</v>
+        <v>1.11275088787079</v>
       </c>
       <c r="H1649" t="n">
         <v>56877192</v>
@@ -48451,7 +48451,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98913478851318</v>
+        <v>2.98913502693176</v>
       </c>
       <c r="H1658" t="n">
         <v>6899464</v>
@@ -48538,7 +48538,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.73594284057617</v>
+        <v>1.73594272136688</v>
       </c>
       <c r="H1661" t="n">
         <v>7745580</v>
@@ -48567,7 +48567,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.985986948013306</v>
+        <v>0.98598700761795</v>
       </c>
       <c r="H1662" t="n">
         <v>25986719</v>
@@ -48596,7 +48596,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.04209995269775</v>
+        <v>1.04210007190704</v>
       </c>
       <c r="H1663" t="n">
         <v>15517197</v>
@@ -48625,7 +48625,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.730360686779022</v>
+        <v>0.730360746383667</v>
       </c>
       <c r="H1664" t="n">
         <v>50412931</v>
@@ -48770,7 +48770,7 @@
         <v>0.71340000629425</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.635413825511932</v>
+        <v>0.635413885116577</v>
       </c>
       <c r="H1669" t="n">
         <v>28781555</v>
@@ -48828,7 +48828,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.659106075763702</v>
+        <v>0.659106016159058</v>
       </c>
       <c r="H1671" t="n">
         <v>27445946</v>
@@ -48857,7 +48857,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.692061364650726</v>
+        <v>0.692061305046082</v>
       </c>
       <c r="H1672" t="n">
         <v>35674340</v>
@@ -48944,7 +48944,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.751737177371979</v>
+        <v>0.751737117767334</v>
       </c>
       <c r="H1675" t="n">
         <v>37326895</v>
@@ -49002,7 +49002,7 @@
         <v>0.833599984645844</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.74247407913208</v>
+        <v>0.742474019527435</v>
       </c>
       <c r="H1677" t="n">
         <v>19689110</v>
@@ -49205,7 +49205,7 @@
         <v>0.821799993515015</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.731963992118835</v>
+        <v>0.731963932514191</v>
       </c>
       <c r="H1684" t="n">
         <v>16957436</v>
@@ -49292,7 +49292,7 @@
         <v>0.762199997901917</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.678879261016846</v>
+        <v>0.678879201412201</v>
       </c>
       <c r="H1687" t="n">
         <v>13487789</v>
@@ -49524,7 +49524,7 @@
         <v>0.716400027275085</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.638085901737213</v>
+        <v>0.638085961341858</v>
       </c>
       <c r="H1695" t="n">
         <v>20717644</v>
@@ -49756,7 +49756,7 @@
         <v>0.674600005149841</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.60085529088974</v>
+        <v>0.600855350494385</v>
       </c>
       <c r="H1703" t="n">
         <v>12648147</v>
@@ -49785,7 +49785,7 @@
         <v>0.697399973869324</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.621162891387939</v>
+        <v>0.621162831783295</v>
       </c>
       <c r="H1704" t="n">
         <v>26443104</v>
@@ -49843,7 +49843,7 @@
         <v>0.683200001716614</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.608515202999115</v>
+        <v>0.60851514339447</v>
       </c>
       <c r="H1706" t="n">
         <v>9988795</v>
@@ -49872,7 +49872,7 @@
         <v>0.662199974060059</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589810848236084</v>
+        <v>0.589810788631439</v>
       </c>
       <c r="H1707" t="n">
         <v>13712596</v>
@@ -49901,7 +49901,7 @@
         <v>0.64300000667572</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.572709739208221</v>
+        <v>0.572709679603577</v>
       </c>
       <c r="H1708" t="n">
         <v>58766149</v>
@@ -49930,7 +49930,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.540645062923431</v>
+        <v>0.540645122528076</v>
       </c>
       <c r="H1709" t="n">
         <v>28764901</v>
@@ -49959,7 +49959,7 @@
         <v>0.584800004959106</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.520871937274933</v>
+        <v>0.520871877670288</v>
       </c>
       <c r="H1710" t="n">
         <v>20980769</v>
@@ -49988,7 +49988,7 @@
         <v>0.59280002117157</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.527997374534607</v>
+        <v>0.527997434139252</v>
       </c>
       <c r="H1711" t="n">
         <v>21540866</v>
@@ -50075,7 +50075,7 @@
         <v>0.597199976444244</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.531916320323944</v>
+        <v>0.531916379928589</v>
       </c>
       <c r="H1714" t="n">
         <v>19250857</v>
@@ -50191,7 +50191,7 @@
         <v>0.637600004673004</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.567900002002716</v>
+        <v>0.567900061607361</v>
       </c>
       <c r="H1718" t="n">
         <v>20242520</v>
@@ -50336,7 +50336,7 @@
         <v>0.72759997844696</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.648061513900757</v>
+        <v>0.648061573505402</v>
       </c>
       <c r="H1723" t="n">
         <v>11884557</v>
@@ -50365,7 +50365,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.620806694030762</v>
+        <v>0.620806634426117</v>
       </c>
       <c r="H1724" t="n">
         <v>15320781</v>
@@ -50626,7 +50626,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.658215343952179</v>
+        <v>0.658215403556824</v>
       </c>
       <c r="H1733" t="n">
         <v>21488740</v>
@@ -50655,7 +50655,7 @@
         <v>0.758199989795685</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.675316452980042</v>
+        <v>0.675316512584686</v>
       </c>
       <c r="H1734" t="n">
         <v>33917790</v>
@@ -50713,7 +50713,7 @@
         <v>0.828599989414215</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.738020598888397</v>
+        <v>0.738020658493042</v>
       </c>
       <c r="H1736" t="n">
         <v>35628898</v>
@@ -50742,7 +50742,7 @@
         <v>0.958599984645844</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.853809535503387</v>
+        <v>0.853809475898743</v>
       </c>
       <c r="H1737" t="n">
         <v>99646498</v>
@@ -50800,7 +50800,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.8764328956604</v>
+        <v>0.876432955265045</v>
       </c>
       <c r="H1739" t="n">
         <v>39414006</v>
@@ -50829,7 +50829,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.87376081943512</v>
+        <v>0.873760879039764</v>
       </c>
       <c r="H1740" t="n">
         <v>36774205</v>
@@ -51003,7 +51003,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.882667660713196</v>
+        <v>0.882667720317841</v>
       </c>
       <c r="H1746" t="n">
         <v>44222060</v>
@@ -51061,7 +51061,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.919185698032379</v>
+        <v>0.919185638427734</v>
       </c>
       <c r="H1748" t="n">
         <v>60743048</v>
@@ -51090,7 +51090,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.957485198974609</v>
+        <v>0.957485139369965</v>
       </c>
       <c r="H1749" t="n">
         <v>38369686</v>
@@ -51148,7 +51148,7 @@
         <v>1.09650003910065</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.976634860038757</v>
+        <v>0.976634919643402</v>
       </c>
       <c r="H1751" t="n">
         <v>33789817</v>
@@ -51177,7 +51177,7 @@
         <v>1.03250002861023</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.919631063938141</v>
+        <v>0.919631123542786</v>
       </c>
       <c r="H1752" t="n">
         <v>95803812</v>
@@ -51206,7 +51206,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.921857714653015</v>
+        <v>0.92185777425766</v>
       </c>
       <c r="H1753" t="n">
         <v>44395351</v>
@@ -51322,7 +51322,7 @@
         <v>1.04649996757507</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.932100653648376</v>
+        <v>0.932100594043732</v>
       </c>
       <c r="H1757" t="n">
         <v>32064633</v>
@@ -51351,7 +51351,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.926311135292053</v>
+        <v>0.926311194896698</v>
       </c>
       <c r="H1758" t="n">
         <v>21110965</v>
@@ -51409,7 +51409,7 @@
         <v>1.04750001430511</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.93299126625061</v>
+        <v>0.932991325855255</v>
       </c>
       <c r="H1760" t="n">
         <v>40631058</v>
@@ -51438,7 +51438,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.912950873374939</v>
+        <v>0.912950932979584</v>
       </c>
       <c r="H1761" t="n">
         <v>26582079</v>
@@ -51467,7 +51467,7 @@
         <v>1.01950001716614</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.908052146434784</v>
+        <v>0.908052206039429</v>
       </c>
       <c r="H1762" t="n">
         <v>27481158</v>
@@ -51525,7 +51525,7 @@
         <v>1.04449999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.93031919002533</v>
+        <v>0.930319249629974</v>
       </c>
       <c r="H1764" t="n">
         <v>52512389</v>
@@ -51786,7 +51786,7 @@
         <v>1.00650000572205</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.896473228931427</v>
+        <v>0.896473288536072</v>
       </c>
       <c r="H1773" t="n">
         <v>22532469</v>
@@ -51844,7 +51844,7 @@
         <v>1.04949998855591</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.934772729873657</v>
+        <v>0.934772670269012</v>
       </c>
       <c r="H1775" t="n">
         <v>27222601</v>
@@ -51931,7 +51931,7 @@
         <v>1.10950005054474</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.988213777542114</v>
+        <v>0.988213717937469</v>
       </c>
       <c r="H1778" t="n">
         <v>33156068</v>
@@ -51989,7 +51989,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.977970957756042</v>
+        <v>0.977970898151398</v>
       </c>
       <c r="H1780" t="n">
         <v>82522322</v>
@@ -52047,7 +52047,7 @@
         <v>1.12750005722046</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.00424599647522</v>
+        <v>1.00424611568451</v>
       </c>
       <c r="H1782" t="n">
         <v>38953976</v>
@@ -52076,7 +52076,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.05456960201263</v>
+        <v>1.05456972122192</v>
       </c>
       <c r="H1783" t="n">
         <v>44539150</v>
@@ -52424,7 +52424,7 @@
         <v>1.31149995326996</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.16813182830811</v>
+        <v>1.16813170909882</v>
       </c>
       <c r="H1795" t="n">
         <v>88039189</v>
@@ -52685,7 +52685,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.25141072273254</v>
+        <v>1.25141084194183</v>
       </c>
       <c r="H1804" t="n">
         <v>50505371</v>
@@ -52772,7 +52772,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.2309250831604</v>
+        <v>1.23092496395111</v>
       </c>
       <c r="H1807" t="n">
         <v>27498297</v>
@@ -52801,7 +52801,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.21845555305481</v>
+        <v>1.21845543384552</v>
       </c>
       <c r="H1808" t="n">
         <v>27228579</v>
@@ -52946,7 +52946,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H1813" t="n">
         <v>201277103</v>
@@ -53062,7 +53062,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.25586414337158</v>
+        <v>1.25586426258087</v>
       </c>
       <c r="H1817" t="n">
         <v>26785082</v>
@@ -53149,7 +53149,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.24962949752808</v>
+        <v>1.24962937831879</v>
       </c>
       <c r="H1820" t="n">
         <v>28478257</v>
@@ -53236,7 +53236,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.3146493434906</v>
+        <v>1.31464922428131</v>
       </c>
       <c r="H1823" t="n">
         <v>73649010</v>
@@ -53265,7 +53265,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.35116744041443</v>
+        <v>1.35116732120514</v>
       </c>
       <c r="H1824" t="n">
         <v>173226691</v>
@@ -53294,7 +53294,7 @@
         <v>1.53450000286102</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.36675429344177</v>
+        <v>1.36675441265106</v>
       </c>
       <c r="H1825" t="n">
         <v>147696002</v>
@@ -53381,7 +53381,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.31643068790436</v>
+        <v>1.31643080711365</v>
       </c>
       <c r="H1828" t="n">
         <v>36445476</v>
@@ -53497,7 +53497,7 @@
         <v>1.35749995708466</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.20910334587097</v>
+        <v>1.20910322666168</v>
       </c>
       <c r="H1832" t="n">
         <v>30266079</v>
@@ -53555,7 +53555,7 @@
         <v>1.26549994945526</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.12716031074524</v>
+        <v>1.12716042995453</v>
       </c>
       <c r="H1834" t="n">
         <v>56083977</v>
@@ -53584,7 +53584,7 @@
         <v>1.14049994945526</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.01582491397858</v>
+        <v>1.01582479476929</v>
       </c>
       <c r="H1835" t="n">
         <v>70991471</v>
@@ -53671,7 +53671,7 @@
         <v>1.23450005054474</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.09954929351807</v>
+        <v>1.09954917430878</v>
       </c>
       <c r="H1838" t="n">
         <v>44048652</v>
@@ -53729,7 +53729,7 @@
         <v>1.32550001144409</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.18060147762299</v>
+        <v>1.1806013584137</v>
       </c>
       <c r="H1840" t="n">
         <v>26361553</v>
@@ -53758,7 +53758,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.14007532596588</v>
+        <v>1.14007520675659</v>
       </c>
       <c r="H1841" t="n">
         <v>30477091</v>
@@ -53932,7 +53932,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23181581497192</v>
+        <v>1.23181569576263</v>
       </c>
       <c r="H1847" t="n">
         <v>23160786</v>
@@ -53990,7 +53990,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1849" t="n">
         <v>61303523</v>
@@ -54512,7 +54512,7 @@
         <v>1.25049996376038</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.11380004882812</v>
+        <v>1.11380016803741</v>
       </c>
       <c r="H1867" t="n">
         <v>30080800</v>
@@ -54628,7 +54628,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.15076351165771</v>
+        <v>1.150763630867</v>
       </c>
       <c r="H1871" t="n">
         <v>24313190</v>
@@ -54715,7 +54715,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.13473129272461</v>
+        <v>1.13473117351532</v>
       </c>
       <c r="H1874" t="n">
         <v>17632468</v>
@@ -54802,7 +54802,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.12048017978668</v>
+        <v>1.12048029899597</v>
       </c>
       <c r="H1877" t="n">
         <v>12144067</v>
@@ -54831,7 +54831,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.15788900852203</v>
+        <v>1.15788888931274</v>
       </c>
       <c r="H1878" t="n">
         <v>28606803</v>
@@ -54976,7 +54976,7 @@
         <v>1.25750005245209</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.1200350522995</v>
+        <v>1.12003493309021</v>
       </c>
       <c r="H1883" t="n">
         <v>22657079</v>
@@ -55005,7 +55005,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.12226164340973</v>
+        <v>1.12226152420044</v>
       </c>
       <c r="H1884" t="n">
         <v>17046265</v>
@@ -55121,7 +55121,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.07416474819183</v>
+        <v>1.07416462898254</v>
       </c>
       <c r="H1888" t="n">
         <v>25051867</v>
@@ -55150,7 +55150,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.13473129272461</v>
+        <v>1.13473117351532</v>
       </c>
       <c r="H1889" t="n">
         <v>28793517</v>
@@ -55440,7 +55440,7 @@
         <v>1.25450003147125</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.11736297607422</v>
+        <v>1.11736285686493</v>
       </c>
       <c r="H1899" t="n">
         <v>19379185</v>
@@ -55498,7 +55498,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.08663427829742</v>
+        <v>1.08663439750671</v>
       </c>
       <c r="H1901" t="n">
         <v>20926564</v>
@@ -55585,7 +55585,7 @@
         <v>1.16250002384186</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.03541994094849</v>
+        <v>1.03542006015778</v>
       </c>
       <c r="H1904" t="n">
         <v>44264066</v>
@@ -55643,7 +55643,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.04833495616913</v>
+        <v>1.04833483695984</v>
       </c>
       <c r="H1906" t="n">
         <v>29040859</v>
@@ -55672,7 +55672,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.07772743701935</v>
+        <v>1.07772755622864</v>
       </c>
       <c r="H1907" t="n">
         <v>35754602</v>
@@ -55875,7 +55875,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.30039846897125</v>
+        <v>1.30039834976196</v>
       </c>
       <c r="H1914" t="n">
         <v>60137225</v>
@@ -55904,7 +55904,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.3110865354538</v>
+        <v>1.31108665466309</v>
       </c>
       <c r="H1915" t="n">
         <v>40402535</v>
@@ -55933,7 +55933,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.32266557216644</v>
+        <v>1.32266545295715</v>
       </c>
       <c r="H1916" t="n">
         <v>40030022</v>
@@ -56020,7 +56020,7 @@
         <v>1.43949997425079</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.28213942050934</v>
+        <v>1.28213930130005</v>
       </c>
       <c r="H1919" t="n">
         <v>27592628</v>
@@ -56049,7 +56049,7 @@
         <v>1.43250000476837</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.27590453624725</v>
+        <v>1.27590465545654</v>
       </c>
       <c r="H1920" t="n">
         <v>21395530</v>
@@ -56078,7 +56078,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.30039846897125</v>
+        <v>1.30039834976196</v>
       </c>
       <c r="H1921" t="n">
         <v>18806426</v>
@@ -56194,7 +56194,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.328009724617</v>
+        <v>1.32800960540771</v>
       </c>
       <c r="H1925" t="n">
         <v>26562115</v>
@@ -56281,7 +56281,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1928" t="n">
         <v>65561642</v>
@@ -56310,7 +56310,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1929" t="n">
         <v>29757990</v>
@@ -56339,7 +56339,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1930" t="n">
-        <v>1.29683566093445</v>
+        <v>1.29683554172516</v>
       </c>
       <c r="H1930" t="n">
         <v>46308940</v>
@@ -56368,7 +56368,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.29327285289764</v>
+        <v>1.29327297210693</v>
       </c>
       <c r="H1931" t="n">
         <v>26931723</v>
@@ -56426,7 +56426,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.25586414337158</v>
+        <v>1.25586426258087</v>
       </c>
       <c r="H1933" t="n">
         <v>26197753</v>
@@ -56484,7 +56484,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.24339461326599</v>
+        <v>1.24339473247528</v>
       </c>
       <c r="H1935" t="n">
         <v>23656707</v>
@@ -56658,7 +56658,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.30485188961029</v>
+        <v>1.304851770401</v>
       </c>
       <c r="H1941" t="n">
         <v>36097664</v>
@@ -56687,7 +56687,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H1942" t="n">
         <v>21886700</v>
@@ -56774,7 +56774,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.33869779109955</v>
+        <v>1.33869791030884</v>
       </c>
       <c r="H1945" t="n">
         <v>21109505</v>
@@ -56861,7 +56861,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.32266557216644</v>
+        <v>1.32266545295715</v>
       </c>
       <c r="H1948" t="n">
         <v>24397332</v>
@@ -56948,7 +56948,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1951" t="n">
-        <v>1.4019364118576</v>
+        <v>1.40193629264832</v>
       </c>
       <c r="H1951" t="n">
         <v>45002851</v>
@@ -56977,7 +56977,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.328009724617</v>
+        <v>1.32800960540771</v>
       </c>
       <c r="H1952" t="n">
         <v>124985920</v>
@@ -57093,7 +57093,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H1956" t="n">
         <v>39334965</v>
@@ -57151,7 +57151,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.37566113471985</v>
+        <v>1.37566125392914</v>
       </c>
       <c r="H1958" t="n">
         <v>66425360</v>
@@ -57238,7 +57238,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.41975009441376</v>
+        <v>1.41974997520447</v>
       </c>
       <c r="H1961" t="n">
         <v>31281838</v>
@@ -57325,7 +57325,7 @@
         <v>1.60950005054474</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.43355572223663</v>
+        <v>1.43355560302734</v>
       </c>
       <c r="H1964" t="n">
         <v>26138694</v>
@@ -57383,7 +57383,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.40104568004608</v>
+        <v>1.40104556083679</v>
       </c>
       <c r="H1966" t="n">
         <v>153129411</v>
@@ -57470,7 +57470,7 @@
         <v>1.46249997615814</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.30262517929077</v>
+        <v>1.30262506008148</v>
       </c>
       <c r="H1969" t="n">
         <v>26919423</v>
@@ -57499,7 +57499,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.27679538726807</v>
+        <v>1.27679526805878</v>
       </c>
       <c r="H1970" t="n">
         <v>26802260</v>
@@ -57528,7 +57528,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.29683566093445</v>
+        <v>1.29683554172516</v>
       </c>
       <c r="H1971" t="n">
         <v>25191162</v>
@@ -57731,7 +57731,7 @@
         <v>1.41849994659424</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.26343500614166</v>
+        <v>1.26343488693237</v>
       </c>
       <c r="H1978" t="n">
         <v>88712511</v>
@@ -57934,7 +57934,7 @@
         <v>1.5275000333786</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.36051964759827</v>
+        <v>1.36051952838898</v>
       </c>
       <c r="H1985" t="n">
         <v>16749025</v>
@@ -57992,7 +57992,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.37566113471985</v>
+        <v>1.37566125392914</v>
       </c>
       <c r="H1987" t="n">
         <v>51105926</v>
@@ -58021,7 +58021,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.29015564918518</v>
+        <v>1.29015552997589</v>
       </c>
       <c r="H1988" t="n">
         <v>67066172</v>
@@ -58079,7 +58079,7 @@
         <v>1.41449999809265</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.25987231731415</v>
+        <v>1.25987219810486</v>
       </c>
       <c r="H1990" t="n">
         <v>29949971</v>
@@ -58166,7 +58166,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.23626923561096</v>
+        <v>1.23626911640167</v>
       </c>
       <c r="H1993" t="n">
         <v>49894794</v>
@@ -58427,7 +58427,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H2002" t="n">
         <v>21379601</v>
@@ -58456,7 +58456,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.23805046081543</v>
+        <v>1.23805058002472</v>
       </c>
       <c r="H2003" t="n">
         <v>18744870</v>
@@ -58572,7 +58572,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H2007" t="n">
         <v>40689470</v>
@@ -58717,7 +58717,7 @@
         <v>1.44749999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>1.28926479816437</v>
+        <v>1.28926491737366</v>
       </c>
       <c r="H2012" t="n">
         <v>13752928</v>
@@ -58862,7 +58862,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H2017" t="n">
         <v>79262449</v>
@@ -58978,7 +58978,7 @@
         <v>1.46150004863739</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.30173444747925</v>
+        <v>1.30173456668854</v>
       </c>
       <c r="H2021" t="n">
         <v>32246011</v>
@@ -59007,7 +59007,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.24784803390503</v>
+        <v>1.24784815311432</v>
       </c>
       <c r="H2022" t="n">
         <v>61474648</v>
@@ -59036,7 +59036,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.24784803390503</v>
+        <v>1.24784815311432</v>
       </c>
       <c r="H2023" t="n">
         <v>34906238</v>
@@ -59123,7 +59123,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.22647166252136</v>
+        <v>1.22647154331207</v>
       </c>
       <c r="H2026" t="n">
         <v>31335128</v>
@@ -59210,7 +59210,7 @@
         <v>1.42050004005432</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.26521635055542</v>
+        <v>1.26521646976471</v>
       </c>
       <c r="H2029" t="n">
         <v>35969343</v>
@@ -59268,7 +59268,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.29015564918518</v>
+        <v>1.29015552997589</v>
       </c>
       <c r="H2031" t="n">
         <v>21961584</v>
@@ -59326,7 +59326,7 @@
         <v>1.44649994373322</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.28837406635284</v>
+        <v>1.28837418556213</v>
       </c>
       <c r="H2033" t="n">
         <v>15340362</v>
@@ -59384,7 +59384,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.3208841085434</v>
+        <v>1.32088422775269</v>
       </c>
       <c r="H2035" t="n">
         <v>16248522</v>
@@ -59413,7 +59413,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.30930531024933</v>
+        <v>1.30930519104004</v>
       </c>
       <c r="H2036" t="n">
         <v>16596498</v>
@@ -59471,7 +59471,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.32622814178467</v>
+        <v>1.32622826099396</v>
       </c>
       <c r="H2038" t="n">
         <v>31598891</v>
@@ -59558,7 +59558,7 @@
         <v>1.50650000572205</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.34181523323059</v>
+        <v>1.3418151140213</v>
       </c>
       <c r="H2041" t="n">
         <v>49175369</v>
@@ -59790,7 +59790,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.27679538726807</v>
+        <v>1.27679526805878</v>
       </c>
       <c r="H2049" t="n">
         <v>35782956</v>
@@ -59877,7 +59877,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31643068790436</v>
+        <v>1.31643080711365</v>
       </c>
       <c r="H2052" t="n">
         <v>70363678</v>
@@ -59964,7 +59964,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.34315121173859</v>
+        <v>1.34315133094788</v>
       </c>
       <c r="H2055" t="n">
         <v>21291896</v>
@@ -60399,7 +60399,7 @@
         <v>1.375</v>
       </c>
       <c r="G2070" t="n">
-        <v>1.22469019889832</v>
+        <v>1.2246903181076</v>
       </c>
       <c r="H2070" t="n">
         <v>37201230</v>
@@ -60486,7 +60486,7 @@
         <v>1.38100004196167</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.23003435134888</v>
+        <v>1.23003447055817</v>
       </c>
       <c r="H2073" t="n">
         <v>23884244</v>
@@ -60602,7 +60602,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.32979094982147</v>
+        <v>1.32979106903076</v>
       </c>
       <c r="H2077" t="n">
         <v>97981694</v>
@@ -60689,7 +60689,7 @@
         <v>1.82149994373322</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.6223806142807</v>
+        <v>1.62238049507141</v>
       </c>
       <c r="H2080" t="n">
         <v>170004032</v>
@@ -60776,7 +60776,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.72347319126129</v>
+        <v>1.723473072052</v>
       </c>
       <c r="H2083" t="n">
         <v>102058873</v>
@@ -60863,7 +60863,7 @@
         <v>1.97650003433228</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.76043665409088</v>
+        <v>1.76043653488159</v>
       </c>
       <c r="H2086" t="n">
         <v>36852781</v>
@@ -60979,7 +60979,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.87488961219788</v>
+        <v>1.87488949298859</v>
       </c>
       <c r="H2090" t="n">
         <v>47381130</v>
@@ -61008,7 +61008,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.88112413883209</v>
+        <v>1.88112425804138</v>
       </c>
       <c r="H2091" t="n">
         <v>28755854</v>
@@ -61037,7 +61037,7 @@
         <v>2.08699989318848</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.85885715484619</v>
+        <v>1.8588570356369</v>
       </c>
       <c r="H2092" t="n">
         <v>29642492</v>
@@ -61153,7 +61153,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.91318881511688</v>
+        <v>1.91318893432617</v>
       </c>
       <c r="H2096" t="n">
         <v>51280827</v>
@@ -61356,7 +61356,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.98889696598053</v>
+        <v>1.98889708518982</v>
       </c>
       <c r="H2103" t="n">
         <v>20444616</v>
@@ -61385,7 +61385,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2104" t="n">
-        <v>2.00760126113892</v>
+        <v>2.0076014995575</v>
       </c>
       <c r="H2104" t="n">
         <v>25187040</v>
@@ -61414,7 +61414,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G2105" t="n">
-        <v>2.00849199295044</v>
+        <v>2.00849223136902</v>
       </c>
       <c r="H2105" t="n">
         <v>29639951</v>
@@ -61472,7 +61472,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.06994915008545</v>
+        <v>2.06994891166687</v>
       </c>
       <c r="H2107" t="n">
         <v>41532484</v>
@@ -61530,7 +61530,7 @@
         <v>2.3970000743866</v>
       </c>
       <c r="G2109" t="n">
-        <v>2.13496923446655</v>
+        <v>2.13496899604797</v>
       </c>
       <c r="H2109" t="n">
         <v>81592175</v>
@@ -61559,7 +61559,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2110" t="n">
-        <v>2.08419990539551</v>
+        <v>2.08420014381409</v>
       </c>
       <c r="H2110" t="n">
         <v>42505018</v>
@@ -61646,7 +61646,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.99513185024261</v>
+        <v>1.99513173103333</v>
       </c>
       <c r="H2113" t="n">
         <v>34419597</v>
@@ -61675,7 +61675,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2114" t="n">
         <v>27318033</v>
@@ -61733,7 +61733,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.94258141517639</v>
+        <v>1.94258153438568</v>
       </c>
       <c r="H2116" t="n">
         <v>46811721</v>
@@ -61820,7 +61820,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.97197389602661</v>
+        <v>1.9719740152359</v>
       </c>
       <c r="H2119" t="n">
         <v>18487545</v>
@@ -61878,7 +61878,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.9523788690567</v>
+        <v>1.95237898826599</v>
       </c>
       <c r="H2121" t="n">
         <v>27702781</v>
@@ -61936,7 +61936,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.94080007076263</v>
+        <v>1.94079983234406</v>
       </c>
       <c r="H2123" t="n">
         <v>20243345</v>
@@ -62023,7 +62023,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2126" t="n">
-        <v>1.91318881511688</v>
+        <v>1.91318893432617</v>
       </c>
       <c r="H2126" t="n">
         <v>16042180</v>
@@ -62081,7 +62081,7 @@
         <v>2.13100004196167</v>
       </c>
       <c r="G2128" t="n">
-        <v>1.8980473279953</v>
+        <v>1.89804720878601</v>
       </c>
       <c r="H2128" t="n">
         <v>22011055</v>
@@ -62110,7 +62110,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2129" t="n">
         <v>19775385</v>
@@ -62168,7 +62168,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G2131" t="n">
-        <v>1.97019255161285</v>
+        <v>1.97019267082214</v>
       </c>
       <c r="H2131" t="n">
         <v>19971385</v>
@@ -62197,7 +62197,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2132" t="n">
-        <v>2.02541494369507</v>
+        <v>2.02541518211365</v>
       </c>
       <c r="H2132" t="n">
         <v>39975168</v>
@@ -62255,7 +62255,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2134" t="n">
-        <v>2.11359286308289</v>
+        <v>2.11359262466431</v>
       </c>
       <c r="H2134" t="n">
         <v>44554345</v>
@@ -62371,7 +62371,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2138" t="n">
-        <v>2.12160897254944</v>
+        <v>2.12160873413086</v>
       </c>
       <c r="H2138" t="n">
         <v>27147448</v>
@@ -62400,7 +62400,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2139" t="n">
-        <v>2.11359286308289</v>
+        <v>2.11359262466431</v>
       </c>
       <c r="H2139" t="n">
         <v>18307723</v>
@@ -62458,7 +62458,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2141" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2141" t="n">
         <v>13550932</v>
@@ -62516,7 +62516,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2143" t="n">
-        <v>1.98889696598053</v>
+        <v>1.98889708518982</v>
       </c>
       <c r="H2143" t="n">
         <v>26661132</v>
@@ -62574,7 +62574,7 @@
         <v>2.15300011634827</v>
       </c>
       <c r="G2145" t="n">
-        <v>1.91764235496521</v>
+        <v>1.9176424741745</v>
       </c>
       <c r="H2145" t="n">
         <v>22296682</v>
@@ -62603,7 +62603,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.9203143119812</v>
+        <v>1.92031419277191</v>
       </c>
       <c r="H2146" t="n">
         <v>35218310</v>
@@ -62632,7 +62632,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.93367457389832</v>
+        <v>1.9336746931076</v>
       </c>
       <c r="H2147" t="n">
         <v>17467441</v>
@@ -62661,7 +62661,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2148" t="n">
         <v>28506448</v>
@@ -62690,7 +62690,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.83926212787628</v>
+        <v>1.83926224708557</v>
       </c>
       <c r="H2149" t="n">
         <v>27905894</v>
@@ -62748,7 +62748,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2151" t="n">
         <v>33021803</v>
@@ -62835,7 +62835,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.86152911186218</v>
+        <v>1.86152923107147</v>
       </c>
       <c r="H2154" t="n">
         <v>35977989</v>
@@ -62864,7 +62864,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.86152911186218</v>
+        <v>1.86152923107147</v>
       </c>
       <c r="H2155" t="n">
         <v>22290014</v>
@@ -62893,7 +62893,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2156" t="n">
-        <v>1.89626574516296</v>
+        <v>1.89626586437225</v>
       </c>
       <c r="H2156" t="n">
         <v>21085975</v>
@@ -62922,7 +62922,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2157" t="n">
         <v>35756797</v>
@@ -62951,7 +62951,7 @@
         <v>2.15899991989136</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.92298626899719</v>
+        <v>1.92298638820648</v>
       </c>
       <c r="H2158" t="n">
         <v>16359113</v>
@@ -62980,7 +62980,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.99245965480804</v>
+        <v>1.99245977401733</v>
       </c>
       <c r="H2159" t="n">
         <v>39248301</v>
@@ -63096,7 +63096,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.1358597278595</v>
+        <v>2.13585996627808</v>
       </c>
       <c r="H2163" t="n">
         <v>33746318</v>
@@ -63212,7 +63212,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2167" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2167" t="n">
         <v>25601227</v>
@@ -63299,7 +63299,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G2170" t="n">
-        <v>2.07351183891296</v>
+        <v>2.07351207733154</v>
       </c>
       <c r="H2170" t="n">
         <v>26440425</v>
@@ -63328,7 +63328,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.06371426582336</v>
+        <v>2.06371450424194</v>
       </c>
       <c r="H2171" t="n">
         <v>26757191</v>
@@ -63357,7 +63357,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G2172" t="n">
-        <v>2.09666991233826</v>
+        <v>2.09666967391968</v>
       </c>
       <c r="H2172" t="n">
         <v>24912702</v>
@@ -63415,7 +63415,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2174" t="n">
-        <v>2.10913920402527</v>
+        <v>2.10913944244385</v>
       </c>
       <c r="H2174" t="n">
         <v>19724218</v>
@@ -63444,7 +63444,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.12339043617249</v>
+        <v>2.12339019775391</v>
       </c>
       <c r="H2175" t="n">
         <v>29130431</v>
@@ -63473,7 +63473,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.14476656913757</v>
+        <v>2.14476680755615</v>
       </c>
       <c r="H2176" t="n">
         <v>16678363</v>
@@ -63560,7 +63560,7 @@
         <v>2.41899991035461</v>
       </c>
       <c r="G2179" t="n">
-        <v>2.15456390380859</v>
+        <v>2.15456414222717</v>
       </c>
       <c r="H2179" t="n">
         <v>23246952</v>
@@ -63618,7 +63618,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2181" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2181" t="n">
         <v>45523587</v>
@@ -63647,7 +63647,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G2182" t="n">
-        <v>1.98444354534149</v>
+        <v>1.9844434261322</v>
       </c>
       <c r="H2182" t="n">
         <v>44868347</v>
@@ -63705,7 +63705,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.9461442232132</v>
+        <v>1.94614410400391</v>
       </c>
       <c r="H2184" t="n">
         <v>18067908</v>
@@ -63734,7 +63734,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2185" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2185" t="n">
         <v>20351307</v>
@@ -63763,7 +63763,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.94080007076263</v>
+        <v>1.94079983234406</v>
       </c>
       <c r="H2186" t="n">
         <v>18512647</v>
@@ -63879,7 +63879,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G2190" t="n">
-        <v>1.79294645786285</v>
+        <v>1.79294657707214</v>
       </c>
       <c r="H2190" t="n">
         <v>24047004</v>
@@ -63995,7 +63995,7 @@
         <v>1.98450005054474</v>
       </c>
       <c r="G2194" t="n">
-        <v>1.76756203174591</v>
+        <v>1.7675621509552</v>
       </c>
       <c r="H2194" t="n">
         <v>23362020</v>
@@ -64140,7 +64140,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G2199" t="n">
-        <v>1.84282493591309</v>
+        <v>1.8428248167038</v>
       </c>
       <c r="H2199" t="n">
         <v>32985049</v>
@@ -64227,7 +64227,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.84549701213837</v>
+        <v>1.84549689292908</v>
       </c>
       <c r="H2202" t="n">
         <v>16439030</v>
@@ -64256,7 +64256,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.81521379947662</v>
+        <v>1.81521368026733</v>
       </c>
       <c r="H2203" t="n">
         <v>23581831</v>
@@ -64343,7 +64343,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2206" t="n">
         <v>19255054</v>
@@ -64372,7 +64372,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2207" t="n">
-        <v>1.80185341835022</v>
+        <v>1.80185329914093</v>
       </c>
       <c r="H2207" t="n">
         <v>12789945</v>
@@ -64401,7 +64401,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.67448556423187</v>
+        <v>1.67448568344116</v>
       </c>
       <c r="H2208" t="n">
         <v>53900944</v>
@@ -64430,7 +64430,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.71189427375793</v>
+        <v>1.71189439296722</v>
       </c>
       <c r="H2209" t="n">
         <v>35189302</v>
@@ -64546,7 +64546,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G2213" t="n">
-        <v>1.60055887699127</v>
+        <v>1.60055899620056</v>
       </c>
       <c r="H2213" t="n">
         <v>37765591</v>
@@ -64575,7 +64575,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.6272794008255</v>
+        <v>1.62727928161621</v>
       </c>
       <c r="H2214" t="n">
         <v>22594695</v>
@@ -64865,7 +64865,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.81343221664429</v>
+        <v>1.81343233585358</v>
       </c>
       <c r="H2224" t="n">
         <v>24725349</v>
@@ -65097,7 +65097,7 @@
         <v>2.05699992179871</v>
       </c>
       <c r="G2232" t="n">
-        <v>1.83213663101196</v>
+        <v>1.83213651180267</v>
       </c>
       <c r="H2232" t="n">
         <v>29472348</v>
@@ -65155,7 +65155,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2234" t="n">
-        <v>1.79027438163757</v>
+        <v>1.79027450084686</v>
       </c>
       <c r="H2234" t="n">
         <v>16876658</v>
@@ -65184,7 +65184,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.80185341835022</v>
+        <v>1.80185329914093</v>
       </c>
       <c r="H2235" t="n">
         <v>20529123</v>
@@ -65358,7 +65358,7 @@
         <v>1.99150002002716</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.773796916008</v>
+        <v>1.77379679679871</v>
       </c>
       <c r="H2241" t="n">
         <v>46698722</v>
@@ -65416,7 +65416,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2243" t="n">
-        <v>1.83926212787628</v>
+        <v>1.83926224708557</v>
       </c>
       <c r="H2243" t="n">
         <v>48994310</v>
@@ -65445,7 +65445,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G2244" t="n">
-        <v>1.80630695819855</v>
+        <v>1.80630683898926</v>
       </c>
       <c r="H2244" t="n">
         <v>29352657</v>
@@ -65474,7 +65474,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G2245" t="n">
-        <v>1.89003121852875</v>
+        <v>1.89003109931946</v>
       </c>
       <c r="H2245" t="n">
         <v>81646961</v>
@@ -65503,7 +65503,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.94970679283142</v>
+        <v>1.94970667362213</v>
       </c>
       <c r="H2246" t="n">
         <v>74141845</v>
@@ -65561,7 +65561,7 @@
         <v>2.16300010681152</v>
       </c>
       <c r="G2248" t="n">
-        <v>1.92654919624329</v>
+        <v>1.92654931545258</v>
       </c>
       <c r="H2248" t="n">
         <v>30842480</v>
@@ -65590,7 +65590,7 @@
         <v>2.16700005531311</v>
       </c>
       <c r="G2249" t="n">
-        <v>1.93011200428009</v>
+        <v>1.9301118850708</v>
       </c>
       <c r="H2249" t="n">
         <v>30050128</v>
@@ -65619,7 +65619,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2250" t="n">
-        <v>1.94525361061096</v>
+        <v>1.94525349140167</v>
       </c>
       <c r="H2250" t="n">
         <v>26979522</v>
@@ -65648,7 +65648,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2251" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2251" t="n">
         <v>53288446</v>
@@ -65677,7 +65677,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2252" t="n">
         <v>41701778</v>
@@ -65735,7 +65735,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2254" t="n">
-        <v>2.00314784049988</v>
+        <v>2.00314807891846</v>
       </c>
       <c r="H2254" t="n">
         <v>44091922</v>
@@ -65793,7 +65793,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2256" t="n">
-        <v>2.06994915008545</v>
+        <v>2.06994891166687</v>
       </c>
       <c r="H2256" t="n">
         <v>54666411</v>
@@ -65880,7 +65880,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2259" t="n">
-        <v>2.05302619934082</v>
+        <v>2.0530264377594</v>
       </c>
       <c r="H2259" t="n">
         <v>24934085</v>
@@ -65909,7 +65909,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2260" t="n">
-        <v>2.06371426582336</v>
+        <v>2.06371450424194</v>
       </c>
       <c r="H2260" t="n">
         <v>40038315</v>
@@ -65938,7 +65938,7 @@
         <v>2.33299994468689</v>
       </c>
       <c r="G2261" t="n">
-        <v>2.07796549797058</v>
+        <v>2.077965259552</v>
       </c>
       <c r="H2261" t="n">
         <v>34552742</v>
@@ -65967,7 +65967,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2262" t="n">
-        <v>2.10913920402527</v>
+        <v>2.10913944244385</v>
       </c>
       <c r="H2262" t="n">
         <v>21092827</v>
@@ -66170,7 +66170,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G2269" t="n">
-        <v>2.16525220870972</v>
+        <v>2.1652524471283</v>
       </c>
       <c r="H2269" t="n">
         <v>38389055</v>
@@ -66315,7 +66315,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G2274" t="n">
-        <v>2.26768088340759</v>
+        <v>2.26768112182617</v>
       </c>
       <c r="H2274" t="n">
         <v>31890329</v>
@@ -66431,7 +66431,7 @@
         <v>2.48699998855591</v>
       </c>
       <c r="G2278" t="n">
-        <v>2.21513080596924</v>
+        <v>2.21513056755066</v>
       </c>
       <c r="H2278" t="n">
         <v>18431422</v>
@@ -66518,7 +66518,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2281" t="n">
-        <v>2.29261994361877</v>
+        <v>2.29262018203735</v>
       </c>
       <c r="H2281" t="n">
         <v>22696347</v>
@@ -66547,7 +66547,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2282" t="n">
-        <v>2.31577801704407</v>
+        <v>2.31577777862549</v>
       </c>
       <c r="H2282" t="n">
         <v>26132220</v>
@@ -66634,7 +66634,7 @@
         <v>2.64299988746643</v>
       </c>
       <c r="G2285" t="n">
-        <v>2.35407733917236</v>
+        <v>2.35407710075378</v>
       </c>
       <c r="H2285" t="n">
         <v>60652789</v>
@@ -66721,7 +66721,7 @@
         <v>2.51099991798401</v>
       </c>
       <c r="G2288" t="n">
-        <v>2.23650693893433</v>
+        <v>2.23650717735291</v>
       </c>
       <c r="H2288" t="n">
         <v>15785363</v>
@@ -66750,7 +66750,7 @@
         <v>2.5090000629425</v>
       </c>
       <c r="G2289" t="n">
-        <v>2.23472595214844</v>
+        <v>2.23472571372986</v>
       </c>
       <c r="H2289" t="n">
         <v>11480911</v>
@@ -66924,7 +66924,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G2295" t="n">
-        <v>2.45294332504272</v>
+        <v>2.45294308662415</v>
       </c>
       <c r="H2295" t="n">
         <v>20214762</v>
@@ -67040,7 +67040,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G2299" t="n">
-        <v>2.31221508979797</v>
+        <v>2.31221532821655</v>
       </c>
       <c r="H2299" t="n">
         <v>74870654</v>
@@ -67098,7 +67098,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G2301" t="n">
-        <v>2.27658772468567</v>
+        <v>2.27658796310425</v>
       </c>
       <c r="H2301" t="n">
         <v>30195449</v>
@@ -67127,7 +67127,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G2302" t="n">
-        <v>2.25164866447449</v>
+        <v>2.25164890289307</v>
       </c>
       <c r="H2302" t="n">
         <v>24626119</v>
@@ -67156,7 +67156,7 @@
         <v>2.51300001144409</v>
       </c>
       <c r="G2303" t="n">
-        <v>2.23828840255737</v>
+        <v>2.23828864097595</v>
       </c>
       <c r="H2303" t="n">
         <v>20104873</v>
@@ -67214,7 +67214,7 @@
         <v>2.48300004005432</v>
       </c>
       <c r="G2305" t="n">
-        <v>2.21156787872314</v>
+        <v>2.21156811714172</v>
       </c>
       <c r="H2305" t="n">
         <v>27751479</v>
@@ -67243,7 +67243,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G2306" t="n">
-        <v>2.14832949638367</v>
+        <v>2.14832925796509</v>
       </c>
       <c r="H2306" t="n">
         <v>43140551</v>
@@ -67272,7 +67272,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2307" t="n">
-        <v>2.12160897254944</v>
+        <v>2.12160873413086</v>
       </c>
       <c r="H2307" t="n">
         <v>24111895</v>
@@ -67504,7 +67504,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2315" t="n">
-        <v>2.04411935806274</v>
+        <v>2.04411959648132</v>
       </c>
       <c r="H2315" t="n">
         <v>24791375</v>
@@ -67562,7 +67562,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G2317" t="n">
-        <v>2.04768228530884</v>
+        <v>2.04768204689026</v>
       </c>
       <c r="H2317" t="n">
         <v>21357944</v>
@@ -67707,7 +67707,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G2322" t="n">
-        <v>2.05658912658691</v>
+        <v>2.05658888816833</v>
       </c>
       <c r="H2322" t="n">
         <v>15248097</v>
@@ -67794,7 +67794,7 @@
         <v>2.28099989891052</v>
       </c>
       <c r="G2325" t="n">
-        <v>2.03164982795715</v>
+        <v>2.03164958953857</v>
       </c>
       <c r="H2325" t="n">
         <v>20004250</v>
@@ -67823,7 +67823,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G2326" t="n">
-        <v>2.0681676864624</v>
+        <v>2.06816792488098</v>
       </c>
       <c r="H2326" t="n">
         <v>27029721</v>
@@ -67910,7 +67910,7 @@
         <v>2.20300006866455</v>
       </c>
       <c r="G2329" t="n">
-        <v>1.9621764421463</v>
+        <v>1.96217656135559</v>
       </c>
       <c r="H2329" t="n">
         <v>165427959</v>
@@ -67939,7 +67939,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2330" t="n">
-        <v>2.00314784049988</v>
+        <v>2.00314807891846</v>
       </c>
       <c r="H2330" t="n">
         <v>90357314</v>
@@ -67997,7 +67997,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2332" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2332" t="n">
         <v>49106059</v>
@@ -68055,7 +68055,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2334" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2334" t="n">
         <v>47390121</v>
@@ -68200,7 +68200,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G2339" t="n">
-        <v>1.85440385341644</v>
+        <v>1.85440373420715</v>
       </c>
       <c r="H2339" t="n">
         <v>52881442</v>
@@ -68287,7 +68287,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2342" t="n">
-        <v>1.89626574516296</v>
+        <v>1.89626586437225</v>
       </c>
       <c r="H2342" t="n">
         <v>54335801</v>
@@ -68316,7 +68316,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.93278396129608</v>
+        <v>1.93278384208679</v>
       </c>
       <c r="H2343" t="n">
         <v>54028041</v>
@@ -68345,7 +68345,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2344" t="n">
         <v>32171346</v>
@@ -68432,7 +68432,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2347" t="n">
-        <v>1.96841132640839</v>
+        <v>1.9684112071991</v>
       </c>
       <c r="H2347" t="n">
         <v>31365241</v>
@@ -68461,7 +68461,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2348" t="n">
-        <v>1.94525361061096</v>
+        <v>1.94525349140167</v>
       </c>
       <c r="H2348" t="n">
         <v>43704455</v>
@@ -68519,7 +68519,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G2350" t="n">
-        <v>1.9586136341095</v>
+        <v>1.95861351490021</v>
       </c>
       <c r="H2350" t="n">
         <v>35346168</v>
@@ -68548,7 +68548,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2351" t="n">
-        <v>1.93367457389832</v>
+        <v>1.9336746931076</v>
       </c>
       <c r="H2351" t="n">
         <v>29069827</v>
@@ -68635,7 +68635,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2354" t="n">
-        <v>1.89537537097931</v>
+        <v>1.89537525177002</v>
       </c>
       <c r="H2354" t="n">
         <v>33627039</v>
@@ -68664,7 +68664,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.72436380386353</v>
+        <v>1.72436392307281</v>
       </c>
       <c r="H2355" t="n">
         <v>85443225</v>
@@ -68838,7 +68838,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G2361" t="n">
-        <v>1.52128803730011</v>
+        <v>1.52128791809082</v>
       </c>
       <c r="H2361" t="n">
         <v>38867170</v>
@@ -68867,7 +68867,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G2362" t="n">
-        <v>1.56493139266968</v>
+        <v>1.56493151187897</v>
       </c>
       <c r="H2362" t="n">
         <v>50829326</v>
@@ -69041,7 +69041,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G2368" t="n">
-        <v>1.74930310249329</v>
+        <v>1.749302983284</v>
       </c>
       <c r="H2368" t="n">
         <v>65053471</v>
@@ -69128,7 +69128,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.82590174674988</v>
+        <v>1.82590186595917</v>
       </c>
       <c r="H2371" t="n">
         <v>29975796</v>
@@ -69186,7 +69186,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2373" t="n">
-        <v>1.85262227058411</v>
+        <v>1.8526223897934</v>
       </c>
       <c r="H2373" t="n">
         <v>37413416</v>
@@ -69215,7 +69215,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G2374" t="n">
-        <v>1.83302748203278</v>
+        <v>1.83302736282349</v>
       </c>
       <c r="H2374" t="n">
         <v>32042896</v>
@@ -69244,7 +69244,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G2375" t="n">
-        <v>1.82768332958221</v>
+        <v>1.82768321037292</v>
       </c>
       <c r="H2375" t="n">
         <v>38839501</v>
@@ -69273,7 +69273,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G2376" t="n">
-        <v>1.83837139606476</v>
+        <v>1.83837127685547</v>
       </c>
       <c r="H2376" t="n">
         <v>30420999</v>
@@ -69331,7 +69331,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G2378" t="n">
-        <v>1.9399094581604</v>
+        <v>1.93990933895111</v>
       </c>
       <c r="H2378" t="n">
         <v>64329397</v>
@@ -80154,6 +80154,35 @@
         <v>10959746</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>4.55000019073486</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>4.52099990844727</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>4.55100011825562</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>4.55100011825562</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>9820077</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -485,7 +485,7 @@
         <v>22.3245735168457</v>
       </c>
       <c r="G4" t="n">
-        <v>19.7946071624756</v>
+        <v>19.7946090698242</v>
       </c>
       <c r="H4" t="n">
         <v>808293</v>
@@ -601,7 +601,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.878662109375</v>
+        <v>19.8786602020264</v>
       </c>
       <c r="H8" t="n">
         <v>1620392</v>
@@ -630,7 +630,7 @@
         <v>22.1665782928467</v>
       </c>
       <c r="G9" t="n">
-        <v>19.6545181274414</v>
+        <v>19.65452003479</v>
       </c>
       <c r="H9" t="n">
         <v>916025</v>
@@ -659,7 +659,7 @@
         <v>22.1823787689209</v>
       </c>
       <c r="G10" t="n">
-        <v>19.668529510498</v>
+        <v>19.6685276031494</v>
       </c>
       <c r="H10" t="n">
         <v>887518</v>
@@ -688,7 +688,7 @@
         <v>20.9184246063232</v>
       </c>
       <c r="G11" t="n">
-        <v>18.5478134155273</v>
+        <v>18.547815322876</v>
       </c>
       <c r="H11" t="n">
         <v>1339292</v>
@@ -717,7 +717,7 @@
         <v>19.8440647125244</v>
       </c>
       <c r="G12" t="n">
-        <v>17.5952091217041</v>
+        <v>17.5952072143555</v>
       </c>
       <c r="H12" t="n">
         <v>1467001</v>
@@ -746,7 +746,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811958312988</v>
+        <v>17.5811977386475</v>
       </c>
       <c r="H13" t="n">
         <v>989105</v>
@@ -775,7 +775,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460289001465</v>
+        <v>15.7460279464722</v>
       </c>
       <c r="H14" t="n">
         <v>2077512</v>
@@ -804,7 +804,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.821439743042</v>
+        <v>14.8214406967163</v>
       </c>
       <c r="H15" t="n">
         <v>2435960</v>
@@ -862,7 +862,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552726745605</v>
+        <v>13.9552736282349</v>
       </c>
       <c r="H17" t="n">
         <v>354113</v>
@@ -949,7 +949,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087112426758</v>
+        <v>12.6087121963501</v>
       </c>
       <c r="H20" t="n">
         <v>1225889</v>
@@ -1123,7 +1123,7 @@
         <v>13.0530023574829</v>
       </c>
       <c r="G26" t="n">
-        <v>11.573751449585</v>
+        <v>11.5737524032593</v>
       </c>
       <c r="H26" t="n">
         <v>1877083</v>
@@ -1181,7 +1181,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H28" t="n">
         <v>1981662</v>
@@ -1239,7 +1239,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G30" t="n">
-        <v>7.08892202377319</v>
+        <v>7.08892250061035</v>
       </c>
       <c r="H30" t="n">
         <v>5755429</v>
@@ -1268,7 +1268,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G31" t="n">
-        <v>6.70832347869873</v>
+        <v>6.70832395553589</v>
       </c>
       <c r="H31" t="n">
         <v>7709298</v>
@@ -1297,7 +1297,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393558502197</v>
+        <v>6.74393510818481</v>
       </c>
       <c r="H32" t="n">
         <v>7100655</v>
@@ -1326,7 +1326,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.8774790763855</v>
+        <v>6.87747859954834</v>
       </c>
       <c r="H33" t="n">
         <v>7581026</v>
@@ -1355,7 +1355,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51180982589722</v>
+        <v>7.51181030273438</v>
       </c>
       <c r="H34" t="n">
         <v>6329665</v>
@@ -1413,7 +1413,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36046028137207</v>
+        <v>7.36045980453491</v>
       </c>
       <c r="H36" t="n">
         <v>4978216</v>
@@ -1471,7 +1471,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243934631348</v>
+        <v>7.91243886947632</v>
       </c>
       <c r="H38" t="n">
         <v>4762357</v>
@@ -1529,7 +1529,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H40" t="n">
         <v>5230684</v>
@@ -1587,7 +1587,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H42" t="n">
         <v>8046415</v>
@@ -1616,7 +1616,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H43" t="n">
         <v>5632607</v>
@@ -1732,7 +1732,7 @@
         <v>10.6884002685547</v>
       </c>
       <c r="G47" t="n">
-        <v>9.47712135314941</v>
+        <v>9.47712230682373</v>
       </c>
       <c r="H47" t="n">
         <v>6263628</v>
@@ -1761,7 +1761,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.07714366912842</v>
+        <v>8.0771427154541</v>
       </c>
       <c r="H48" t="n">
         <v>18012438</v>
@@ -1819,7 +1819,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811388015747</v>
+        <v>7.98811340332031</v>
       </c>
       <c r="H50" t="n">
         <v>5464353</v>
@@ -1877,7 +1877,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683300018311</v>
+        <v>8.58683204650879</v>
       </c>
       <c r="H52" t="n">
         <v>4362352</v>
@@ -1935,7 +1935,7 @@
         <v>9.26261138916016</v>
       </c>
       <c r="G54" t="n">
-        <v>8.21291351318359</v>
+        <v>8.21291255950928</v>
       </c>
       <c r="H54" t="n">
         <v>3721362</v>
@@ -1964,7 +1964,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.3175220489502</v>
+        <v>8.31752109527588</v>
       </c>
       <c r="H55" t="n">
         <v>4485559</v>
@@ -2080,7 +2080,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G59" t="n">
-        <v>8.20623397827148</v>
+        <v>8.2062349319458</v>
       </c>
       <c r="H59" t="n">
         <v>2418203</v>
@@ -2109,7 +2109,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218725204468</v>
+        <v>7.75218820571899</v>
       </c>
       <c r="H60" t="n">
         <v>3776976</v>
@@ -2138,7 +2138,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.3448805809021</v>
+        <v>7.34488010406494</v>
       </c>
       <c r="H61" t="n">
         <v>3010233</v>
@@ -2225,7 +2225,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870809555054</v>
+        <v>7.65870714187622</v>
       </c>
       <c r="H64" t="n">
         <v>2688899</v>
@@ -2283,7 +2283,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973640441895</v>
+        <v>6.89973592758179</v>
       </c>
       <c r="H66" t="n">
         <v>4271134</v>
@@ -2341,7 +2341,7 @@
         <v>7.61341381072998</v>
       </c>
       <c r="G68" t="n">
-        <v>6.75061273574829</v>
+        <v>6.75061225891113</v>
       </c>
       <c r="H68" t="n">
         <v>2618453</v>
@@ -2370,7 +2370,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365732192993</v>
+        <v>7.27365779876709</v>
       </c>
       <c r="H69" t="n">
         <v>3294930</v>
@@ -2399,7 +2399,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H70" t="n">
         <v>3239759</v>
@@ -2428,7 +2428,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G71" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H71" t="n">
         <v>3489116</v>
@@ -2457,7 +2457,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.86347436904907</v>
+        <v>7.8634729385376</v>
       </c>
       <c r="H72" t="n">
         <v>3751875</v>
@@ -2486,7 +2486,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09939956665039</v>
+        <v>8.09940052032471</v>
       </c>
       <c r="H73" t="n">
         <v>4017372</v>
@@ -2515,7 +2515,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86570072174072</v>
+        <v>7.86569976806641</v>
       </c>
       <c r="H74" t="n">
         <v>2931733</v>
@@ -2573,7 +2573,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H76" t="n">
         <v>3700496</v>
@@ -2689,7 +2689,7 @@
         <v>9.39816093444824</v>
       </c>
       <c r="G80" t="n">
-        <v>8.33310127258301</v>
+        <v>8.33310031890869</v>
       </c>
       <c r="H80" t="n">
         <v>1866023</v>
@@ -2747,7 +2747,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912178039551</v>
+        <v>8.62912082672119</v>
       </c>
       <c r="H82" t="n">
         <v>3841073</v>
@@ -2805,7 +2805,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H84" t="n">
         <v>6156371</v>
@@ -2834,7 +2834,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H85" t="n">
         <v>3915352</v>
@@ -2863,7 +2863,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G86" t="n">
-        <v>8.54009342193604</v>
+        <v>8.54009246826172</v>
       </c>
       <c r="H86" t="n">
         <v>4877613</v>
@@ -2892,7 +2892,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H87" t="n">
         <v>3783755</v>
@@ -2921,7 +2921,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G88" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H88" t="n">
         <v>2952497</v>
@@ -2950,7 +2950,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G89" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H89" t="n">
         <v>2726335</v>
@@ -2979,7 +2979,7 @@
         <v>9.36803913116455</v>
       </c>
       <c r="G90" t="n">
-        <v>8.30639171600342</v>
+        <v>8.30639266967773</v>
       </c>
       <c r="H90" t="n">
         <v>2595903</v>
@@ -3066,7 +3066,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H93" t="n">
         <v>3351378</v>
@@ -3095,7 +3095,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.2685546875</v>
+        <v>8.26855373382568</v>
       </c>
       <c r="H94" t="n">
         <v>2791506</v>
@@ -3124,7 +3124,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542007446289</v>
+        <v>8.39542102813721</v>
       </c>
       <c r="H95" t="n">
         <v>1782012</v>
@@ -3182,7 +3182,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G97" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H97" t="n">
         <v>1772130</v>
@@ -3211,7 +3211,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588848114014</v>
+        <v>7.98588752746582</v>
       </c>
       <c r="H98" t="n">
         <v>4712589</v>
@@ -3240,7 +3240,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701642990112</v>
+        <v>7.99701690673828</v>
       </c>
       <c r="H99" t="n">
         <v>2418605</v>
@@ -3327,7 +3327,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H102" t="n">
         <v>3679752</v>
@@ -3356,7 +3356,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G103" t="n">
-        <v>8.39764595031738</v>
+        <v>8.3976469039917</v>
       </c>
       <c r="H103" t="n">
         <v>2642334</v>
@@ -3530,7 +3530,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889633178711</v>
+        <v>7.77889585494995</v>
       </c>
       <c r="H109" t="n">
         <v>2101522</v>
@@ -3559,7 +3559,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701642990112</v>
+        <v>7.99701690673828</v>
       </c>
       <c r="H110" t="n">
         <v>2370853</v>
@@ -3646,7 +3646,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G113" t="n">
-        <v>8.6736364364624</v>
+        <v>8.67363548278809</v>
       </c>
       <c r="H113" t="n">
         <v>2693817</v>
@@ -3704,7 +3704,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325372695923</v>
+        <v>7.72325325012207</v>
       </c>
       <c r="H115" t="n">
         <v>4121823</v>
@@ -3733,7 +3733,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660612106323</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H116" t="n">
         <v>3931446</v>
@@ -3762,7 +3762,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808290481567</v>
+        <v>7.96808242797852</v>
       </c>
       <c r="H117" t="n">
         <v>3606977</v>
@@ -3820,7 +3820,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G119" t="n">
-        <v>8.20623397827148</v>
+        <v>8.2062349319458</v>
       </c>
       <c r="H119" t="n">
         <v>6157104</v>
@@ -3907,7 +3907,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76489067077637</v>
+        <v>8.76488971710205</v>
       </c>
       <c r="H122" t="n">
         <v>3417145</v>
@@ -3965,7 +3965,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.0593376159668</v>
+        <v>8.05933666229248</v>
       </c>
       <c r="H124" t="n">
         <v>4551998</v>
@@ -3994,7 +3994,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.59193563461304</v>
+        <v>7.5919361114502</v>
       </c>
       <c r="H125" t="n">
         <v>3711164</v>
@@ -4023,7 +4023,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78557348251343</v>
+        <v>7.78557395935059</v>
       </c>
       <c r="H126" t="n">
         <v>3269289</v>
@@ -4052,7 +4052,7 @@
         <v>8.86349010467529</v>
       </c>
       <c r="G127" t="n">
-        <v>7.85902214050293</v>
+        <v>7.85902261734009</v>
       </c>
       <c r="H127" t="n">
         <v>3013097</v>
@@ -4139,7 +4139,7 @@
         <v>9.60650730133057</v>
       </c>
       <c r="G130" t="n">
-        <v>8.51783561706543</v>
+        <v>8.51783657073975</v>
       </c>
       <c r="H130" t="n">
         <v>3045817</v>
@@ -4284,7 +4284,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.7114725112915</v>
+        <v>8.71147441864014</v>
       </c>
       <c r="H135" t="n">
         <v>4380711</v>
@@ -4313,7 +4313,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420352935791</v>
+        <v>9.03420257568359</v>
       </c>
       <c r="H136" t="n">
         <v>5039193</v>
@@ -4400,7 +4400,7 @@
         <v>10.3771362304688</v>
       </c>
       <c r="G139" t="n">
-        <v>9.20113277435303</v>
+        <v>9.20113182067871</v>
       </c>
       <c r="H139" t="n">
         <v>1660292</v>
@@ -4429,7 +4429,7 @@
         <v>10.5679111480713</v>
       </c>
       <c r="G140" t="n">
-        <v>9.37028694152832</v>
+        <v>9.37028789520264</v>
       </c>
       <c r="H140" t="n">
         <v>1710004</v>
@@ -4458,7 +4458,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G141" t="n">
-        <v>9.55947208404541</v>
+        <v>9.55947303771973</v>
       </c>
       <c r="H141" t="n">
         <v>3718667</v>
@@ -4603,7 +4603,7 @@
         <v>10.6934204101562</v>
       </c>
       <c r="G146" t="n">
-        <v>9.4815731048584</v>
+        <v>9.48157215118408</v>
       </c>
       <c r="H146" t="n">
         <v>2462145</v>
@@ -4632,7 +4632,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427124023438</v>
+        <v>9.78427219390869</v>
       </c>
       <c r="H147" t="n">
         <v>3288854</v>
@@ -4661,7 +4661,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G148" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H148" t="n">
         <v>11514563</v>
@@ -4690,7 +4690,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G149" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H149" t="n">
         <v>5327998</v>
@@ -4806,7 +4806,7 @@
         <v>9.37807941436768</v>
       </c>
       <c r="G153" t="n">
-        <v>8.31529521942139</v>
+        <v>8.31529426574707</v>
       </c>
       <c r="H153" t="n">
         <v>2495200</v>
@@ -4835,7 +4835,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228832244873</v>
+        <v>8.52228736877441</v>
       </c>
       <c r="H154" t="n">
         <v>2111524</v>
@@ -5009,7 +5009,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H160" t="n">
         <v>2723125</v>
@@ -5096,7 +5096,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H163" t="n">
         <v>1929655</v>
@@ -5125,7 +5125,7 @@
         <v>9.98303604125977</v>
       </c>
       <c r="G164" t="n">
-        <v>8.85169315338135</v>
+        <v>8.85169410705566</v>
       </c>
       <c r="H164" t="n">
         <v>1474788</v>
@@ -5154,7 +5154,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122570037842</v>
+        <v>9.26122665405273</v>
       </c>
       <c r="H165" t="n">
         <v>1784826</v>
@@ -5183,7 +5183,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G166" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H166" t="n">
         <v>2357597</v>
@@ -5241,7 +5241,7 @@
         <v>10.442400932312</v>
       </c>
       <c r="G168" t="n">
-        <v>9.25900077819824</v>
+        <v>9.25899982452393</v>
       </c>
       <c r="H168" t="n">
         <v>1567170</v>
@@ -5328,7 +5328,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548778533936</v>
+        <v>9.14548873901367</v>
       </c>
       <c r="H171" t="n">
         <v>1904678</v>
@@ -5386,7 +5386,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H173" t="n">
         <v>2380805</v>
@@ -5415,7 +5415,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.2723560333252</v>
+        <v>9.27235507965088</v>
       </c>
       <c r="H174" t="n">
         <v>1895264</v>
@@ -5502,7 +5502,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G177" t="n">
-        <v>9.23451900482178</v>
+        <v>9.23451805114746</v>
       </c>
       <c r="H177" t="n">
         <v>2950107</v>
@@ -5531,7 +5531,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G178" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H178" t="n">
         <v>1678053</v>
@@ -5647,7 +5647,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G182" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H182" t="n">
         <v>2932072</v>
@@ -5676,7 +5676,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359827041626</v>
+        <v>7.94359874725342</v>
       </c>
       <c r="H183" t="n">
         <v>4194583</v>
@@ -5763,7 +5763,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463329315186</v>
+        <v>7.89463376998901</v>
       </c>
       <c r="H186" t="n">
         <v>1967156</v>
@@ -5850,7 +5850,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798664093018</v>
+        <v>7.90798759460449</v>
       </c>
       <c r="H189" t="n">
         <v>3574353</v>
@@ -5908,7 +5908,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.73883247375488</v>
+        <v>7.7388334274292</v>
       </c>
       <c r="H191" t="n">
         <v>2882632</v>
@@ -5966,7 +5966,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G193" t="n">
-        <v>8.38429260253906</v>
+        <v>8.38429164886475</v>
       </c>
       <c r="H193" t="n">
         <v>3268951</v>
@@ -6024,7 +6024,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H195" t="n">
         <v>3058208</v>
@@ -6053,7 +6053,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G196" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H196" t="n">
         <v>2921152</v>
@@ -6111,7 +6111,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473388671875</v>
+        <v>8.66473293304443</v>
       </c>
       <c r="H198" t="n">
         <v>3635783</v>
@@ -6256,7 +6256,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H203" t="n">
         <v>2739605</v>
@@ -6285,7 +6285,7 @@
         <v>10.3696060180664</v>
       </c>
       <c r="G204" t="n">
-        <v>9.19445514678955</v>
+        <v>9.19445610046387</v>
       </c>
       <c r="H204" t="n">
         <v>2291727</v>
@@ -6314,7 +6314,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H205" t="n">
         <v>2047802</v>
@@ -6459,7 +6459,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G210" t="n">
-        <v>9.31464385986328</v>
+        <v>9.31464290618896</v>
       </c>
       <c r="H210" t="n">
         <v>2902413</v>
@@ -6488,7 +6488,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H211" t="n">
         <v>10102433</v>
@@ -6546,7 +6546,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H213" t="n">
         <v>3655602</v>
@@ -6720,7 +6720,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G219" t="n">
-        <v>8.38429260253906</v>
+        <v>8.38429164886475</v>
       </c>
       <c r="H219" t="n">
         <v>2139887</v>
@@ -6749,7 +6749,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G220" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H220" t="n">
         <v>2461590</v>
@@ -6778,7 +6778,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G221" t="n">
-        <v>8.73373126983643</v>
+        <v>8.73373031616211</v>
       </c>
       <c r="H221" t="n">
         <v>7014824</v>
@@ -6865,7 +6865,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H224" t="n">
         <v>2930403</v>
@@ -6923,7 +6923,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072341918945</v>
+        <v>8.94072246551514</v>
       </c>
       <c r="H226" t="n">
         <v>2515113</v>
@@ -6981,7 +6981,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G228" t="n">
-        <v>8.6736364364624</v>
+        <v>8.67363548278809</v>
       </c>
       <c r="H228" t="n">
         <v>3095637</v>
@@ -7039,7 +7039,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G230" t="n">
-        <v>8.94517421722412</v>
+        <v>8.9451732635498</v>
       </c>
       <c r="H230" t="n">
         <v>2705648</v>
@@ -7097,7 +7097,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G232" t="n">
-        <v>9.16329383850098</v>
+        <v>9.16329479217529</v>
       </c>
       <c r="H232" t="n">
         <v>2155204</v>
@@ -7126,7 +7126,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G233" t="n">
-        <v>8.92514324188232</v>
+        <v>8.92514228820801</v>
       </c>
       <c r="H233" t="n">
         <v>1340077</v>
@@ -7155,7 +7155,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G234" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H234" t="n">
         <v>2193109</v>
@@ -7242,7 +7242,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640323638916</v>
+        <v>9.72640228271484</v>
       </c>
       <c r="H237" t="n">
         <v>6656648</v>
@@ -7329,7 +7329,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1826753616333</v>
+        <v>10.182674407959</v>
       </c>
       <c r="H240" t="n">
         <v>4126096</v>
@@ -7387,7 +7387,7 @@
         <v>11.4088249206543</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1159029006958</v>
+        <v>10.1159038543701</v>
       </c>
       <c r="H242" t="n">
         <v>4919856</v>
@@ -7474,7 +7474,7 @@
         <v>11.8230066299438</v>
       </c>
       <c r="G245" t="n">
-        <v>10.4831466674805</v>
+        <v>10.4831476211548</v>
       </c>
       <c r="H245" t="n">
         <v>7748349</v>
@@ -7532,7 +7532,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788545608521</v>
+        <v>10.5788536071777</v>
       </c>
       <c r="H247" t="n">
         <v>3112020</v>
@@ -7648,7 +7648,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G251" t="n">
-        <v>10.9883861541748</v>
+        <v>10.9883871078491</v>
       </c>
       <c r="H251" t="n">
         <v>3493539</v>
@@ -7677,7 +7677,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G252" t="n">
-        <v>11.2844076156616</v>
+        <v>11.2844085693359</v>
       </c>
       <c r="H252" t="n">
         <v>3211844</v>
@@ -7706,7 +7706,7 @@
         <v>12.8772878646851</v>
       </c>
       <c r="G253" t="n">
-        <v>11.4179496765137</v>
+        <v>11.417950630188</v>
       </c>
       <c r="H253" t="n">
         <v>1908982</v>
@@ -7764,7 +7764,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295522689819</v>
+        <v>11.7295513153076</v>
       </c>
       <c r="H255" t="n">
         <v>2571001</v>
@@ -7822,7 +7822,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076099395752</v>
+        <v>11.9076108932495</v>
       </c>
       <c r="H257" t="n">
         <v>1775884</v>
@@ -7909,7 +7909,7 @@
         <v>13.9817733764648</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3972692489624</v>
+        <v>12.3972682952881</v>
       </c>
       <c r="H260" t="n">
         <v>3761116</v>
@@ -7938,7 +7938,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195251464844</v>
+        <v>12.4195261001587</v>
       </c>
       <c r="H261" t="n">
         <v>2771934</v>
@@ -7967,7 +7967,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858253479004</v>
+        <v>12.1858243942261</v>
       </c>
       <c r="H262" t="n">
         <v>2214682</v>
@@ -8112,7 +8112,7 @@
         <v>12.8647365570068</v>
       </c>
       <c r="G267" t="n">
-        <v>11.4068222045898</v>
+        <v>11.4068212509155</v>
       </c>
       <c r="H267" t="n">
         <v>2415292</v>
@@ -8199,7 +8199,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G270" t="n">
-        <v>11.2844076156616</v>
+        <v>11.2844085693359</v>
       </c>
       <c r="H270" t="n">
         <v>3414444</v>
@@ -8228,7 +8228,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619920730591</v>
+        <v>11.1619939804077</v>
       </c>
       <c r="H271" t="n">
         <v>2083536</v>
@@ -8286,7 +8286,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351266860962</v>
+        <v>11.0351257324219</v>
       </c>
       <c r="H273" t="n">
         <v>2426178</v>
@@ -8344,7 +8344,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963237762451</v>
+        <v>11.7963228225708</v>
       </c>
       <c r="H275" t="n">
         <v>5968291</v>
@@ -8402,7 +8402,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960083007812</v>
+        <v>11.5960092544556</v>
       </c>
       <c r="H277" t="n">
         <v>1743449</v>
@@ -8518,7 +8518,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G281" t="n">
-        <v>10.2383184432983</v>
+        <v>10.2383193969727</v>
       </c>
       <c r="H281" t="n">
         <v>3878344</v>
@@ -8547,7 +8547,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141492843628</v>
+        <v>10.4141502380371</v>
       </c>
       <c r="H282" t="n">
         <v>2834757</v>
@@ -8576,7 +8576,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.2516717910767</v>
+        <v>10.251672744751</v>
       </c>
       <c r="H283" t="n">
         <v>3104757</v>
@@ -8663,7 +8663,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.39857006073</v>
+        <v>10.3985710144043</v>
       </c>
       <c r="H286" t="n">
         <v>2660739</v>
@@ -8750,7 +8750,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651847839355</v>
+        <v>10.3651838302612</v>
       </c>
       <c r="H289" t="n">
         <v>3308303</v>
@@ -8837,7 +8837,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H292" t="n">
         <v>2600664</v>
@@ -8895,7 +8895,7 @@
         <v>11.6874570846558</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3629579544067</v>
+        <v>10.3629589080811</v>
       </c>
       <c r="H294" t="n">
         <v>2084853</v>
@@ -9011,7 +9011,7 @@
         <v>10.5754413604736</v>
       </c>
       <c r="G298" t="n">
-        <v>9.3769645690918</v>
+        <v>9.37696361541748</v>
       </c>
       <c r="H298" t="n">
         <v>3692492</v>
@@ -9098,7 +9098,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486354827881</v>
+        <v>9.45486450195312</v>
       </c>
       <c r="H301" t="n">
         <v>3459059</v>
@@ -9127,7 +9127,7 @@
         <v>10.6984405517578</v>
       </c>
       <c r="G302" t="n">
-        <v>9.48602390289307</v>
+        <v>9.48602485656738</v>
       </c>
       <c r="H302" t="n">
         <v>2707699</v>
@@ -9185,7 +9185,7 @@
         <v>10.4675025939941</v>
       </c>
       <c r="G304" t="n">
-        <v>9.28125762939453</v>
+        <v>9.28125858306885</v>
       </c>
       <c r="H304" t="n">
         <v>3507793</v>
@@ -9330,7 +9330,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520709991455</v>
+        <v>8.96520614624023</v>
       </c>
       <c r="H309" t="n">
         <v>3858069</v>
@@ -9359,7 +9359,7 @@
         <v>10.218994140625</v>
       </c>
       <c r="G310" t="n">
-        <v>9.06091213226318</v>
+        <v>9.06091117858887</v>
       </c>
       <c r="H310" t="n">
         <v>3308377</v>
@@ -9446,7 +9446,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G313" t="n">
-        <v>9.01639747619629</v>
+        <v>9.01639652252197</v>
       </c>
       <c r="H313" t="n">
         <v>2624769</v>
@@ -9475,7 +9475,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539485931396</v>
+        <v>9.08539390563965</v>
       </c>
       <c r="H314" t="n">
         <v>3039918</v>
@@ -9504,7 +9504,7 @@
         <v>10.1336479187012</v>
       </c>
       <c r="G315" t="n">
-        <v>8.98523712158203</v>
+        <v>8.98523807525635</v>
       </c>
       <c r="H315" t="n">
         <v>3230495</v>
@@ -9591,7 +9591,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H318" t="n">
         <v>3081207</v>
@@ -9620,7 +9620,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G319" t="n">
-        <v>9.39254474639893</v>
+        <v>9.39254379272461</v>
       </c>
       <c r="H319" t="n">
         <v>5837585</v>
@@ -9649,7 +9649,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G320" t="n">
-        <v>9.4615421295166</v>
+        <v>9.46154117584229</v>
       </c>
       <c r="H320" t="n">
         <v>4855845</v>
@@ -9736,7 +9736,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981948852539</v>
+        <v>9.77981853485107</v>
       </c>
       <c r="H323" t="n">
         <v>5715259</v>
@@ -9765,7 +9765,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G324" t="n">
-        <v>9.49047565460205</v>
+        <v>9.49047470092773</v>
       </c>
       <c r="H324" t="n">
         <v>4124738</v>
@@ -9794,7 +9794,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G325" t="n">
-        <v>9.51050662994385</v>
+        <v>9.51050758361816</v>
       </c>
       <c r="H325" t="n">
         <v>3181766</v>
@@ -9823,7 +9823,7 @@
         <v>10.7310733795166</v>
       </c>
       <c r="G326" t="n">
-        <v>9.51495838165283</v>
+        <v>9.51495933532715</v>
       </c>
       <c r="H326" t="n">
         <v>2539231</v>
@@ -9881,7 +9881,7 @@
         <v>10.5227270126343</v>
       </c>
       <c r="G328" t="n">
-        <v>9.33022403717041</v>
+        <v>9.33022308349609</v>
       </c>
       <c r="H328" t="n">
         <v>2488647</v>
@@ -9910,7 +9910,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H329" t="n">
         <v>3030394</v>
@@ -9939,7 +9939,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G330" t="n">
-        <v>9.12990856170654</v>
+        <v>9.12990951538086</v>
       </c>
       <c r="H330" t="n">
         <v>3092166</v>
@@ -10084,7 +10084,7 @@
         <v>9.7671594619751</v>
       </c>
       <c r="G335" t="n">
-        <v>8.66028118133545</v>
+        <v>8.66028213500977</v>
       </c>
       <c r="H335" t="n">
         <v>6899556</v>
@@ -10171,7 +10171,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.2033576965332</v>
+        <v>9.20335865020752</v>
       </c>
       <c r="H338" t="n">
         <v>3676909</v>
@@ -10316,7 +10316,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H343" t="n">
         <v>4027196</v>
@@ -10606,7 +10606,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G353" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H353" t="n">
         <v>3851850</v>
@@ -10635,7 +10635,7 @@
         <v>9.80481243133545</v>
       </c>
       <c r="G354" t="n">
-        <v>8.6936674118042</v>
+        <v>8.69366836547852</v>
       </c>
       <c r="H354" t="n">
         <v>2634747</v>
@@ -10693,7 +10693,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H356" t="n">
         <v>1939986</v>
@@ -10722,7 +10722,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G357" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H357" t="n">
         <v>2035124</v>
@@ -10809,7 +10809,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H360" t="n">
         <v>1852849</v>
@@ -10896,7 +10896,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.9903392791748</v>
+        <v>7.99033975601196</v>
       </c>
       <c r="H363" t="n">
         <v>4201110</v>
@@ -11012,7 +11012,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215627670288</v>
+        <v>7.73215579986572</v>
       </c>
       <c r="H367" t="n">
         <v>4573774</v>
@@ -11041,7 +11041,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H368" t="n">
         <v>4145288</v>
@@ -11157,7 +11157,7 @@
         <v>8.88106060028076</v>
       </c>
       <c r="G372" t="n">
-        <v>7.87460136413574</v>
+        <v>7.8746018409729</v>
       </c>
       <c r="H372" t="n">
         <v>3226298</v>
@@ -11186,7 +11186,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H373" t="n">
         <v>5046714</v>
@@ -11331,7 +11331,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G378" t="n">
-        <v>7.18017721176147</v>
+        <v>7.18017673492432</v>
       </c>
       <c r="H378" t="n">
         <v>2433304</v>
@@ -11360,7 +11360,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H379" t="n">
         <v>2182310</v>
@@ -11389,7 +11389,7 @@
         <v>8.07779979705811</v>
       </c>
       <c r="G380" t="n">
-        <v>7.16237163543701</v>
+        <v>7.16237115859985</v>
       </c>
       <c r="H380" t="n">
         <v>2966514</v>
@@ -11418,7 +11418,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914218902588</v>
+        <v>7.22914266586304</v>
       </c>
       <c r="H381" t="n">
         <v>2924827</v>
@@ -11447,7 +11447,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817150115967</v>
+        <v>7.31817245483398</v>
       </c>
       <c r="H382" t="n">
         <v>2594435</v>
@@ -11476,7 +11476,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804521560669</v>
+        <v>7.23804569244385</v>
       </c>
       <c r="H383" t="n">
         <v>2583014</v>
@@ -11534,7 +11534,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055559158325</v>
+        <v>7.42055463790894</v>
       </c>
       <c r="H385" t="n">
         <v>3239198</v>
@@ -11563,7 +11563,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.69654512405396</v>
+        <v>7.6965446472168</v>
       </c>
       <c r="H386" t="n">
         <v>4250748</v>
@@ -11592,7 +11592,7 @@
         <v>8.44428825378418</v>
       </c>
       <c r="G387" t="n">
-        <v>7.48732709884644</v>
+        <v>7.48732662200928</v>
       </c>
       <c r="H387" t="n">
         <v>4117666</v>
@@ -11708,7 +11708,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390893936157</v>
+        <v>7.43390846252441</v>
       </c>
       <c r="H391" t="n">
         <v>1190917</v>
@@ -11737,7 +11737,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H392" t="n">
         <v>4462543</v>
@@ -11766,7 +11766,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G393" t="n">
-        <v>7.74551010131836</v>
+        <v>7.7455096244812</v>
       </c>
       <c r="H393" t="n">
         <v>2051870</v>
@@ -11824,7 +11824,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.85679578781128</v>
+        <v>7.85679721832275</v>
       </c>
       <c r="H395" t="n">
         <v>2325966</v>
@@ -11853,7 +11853,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H396" t="n">
         <v>3714587</v>
@@ -11911,7 +11911,7 @@
         <v>8.514573097229</v>
       </c>
       <c r="G398" t="n">
-        <v>7.54964685440063</v>
+        <v>7.54964637756348</v>
       </c>
       <c r="H398" t="n">
         <v>1501586</v>
@@ -11940,7 +11940,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842311859131</v>
       </c>
       <c r="H399" t="n">
         <v>1479093</v>
@@ -11969,7 +11969,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196708679199</v>
+        <v>7.61196756362915</v>
       </c>
       <c r="H400" t="n">
         <v>2662388</v>
@@ -12056,7 +12056,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H403" t="n">
         <v>2870111</v>
@@ -12085,7 +12085,7 @@
         <v>8.6953067779541</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70989894866943</v>
+        <v>7.70989847183228</v>
       </c>
       <c r="H404" t="n">
         <v>2592503</v>
@@ -12143,7 +12143,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H406" t="n">
         <v>2779239</v>
@@ -12172,7 +12172,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757871627808</v>
+        <v>7.64757966995239</v>
       </c>
       <c r="H407" t="n">
         <v>1870136</v>
@@ -12259,7 +12259,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428731918335</v>
+        <v>7.67428636550903</v>
       </c>
       <c r="H410" t="n">
         <v>1678906</v>
@@ -12375,7 +12375,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249744415283</v>
+        <v>7.24249792098999</v>
       </c>
       <c r="H414" t="n">
         <v>3391728</v>
@@ -12404,7 +12404,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701162338257</v>
+        <v>7.28701210021973</v>
       </c>
       <c r="H415" t="n">
         <v>1909890</v>
@@ -12433,7 +12433,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G416" t="n">
-        <v>7.26475429534912</v>
+        <v>7.26475477218628</v>
       </c>
       <c r="H416" t="n">
         <v>2058975</v>
@@ -12520,7 +12520,7 @@
         <v>8.08281993865967</v>
       </c>
       <c r="G419" t="n">
-        <v>7.16682243347168</v>
+        <v>7.16682195663452</v>
       </c>
       <c r="H419" t="n">
         <v>1874275</v>
@@ -12578,7 +12578,7 @@
         <v>7.84184217453003</v>
       </c>
       <c r="G421" t="n">
-        <v>6.95315408706665</v>
+        <v>6.95315361022949</v>
       </c>
       <c r="H421" t="n">
         <v>2449535</v>
@@ -12607,7 +12607,7 @@
         <v>7.61592388153076</v>
       </c>
       <c r="G422" t="n">
-        <v>6.75283813476562</v>
+        <v>6.75283861160278</v>
       </c>
       <c r="H422" t="n">
         <v>5344638</v>
@@ -12636,7 +12636,7 @@
         <v>7.70127105712891</v>
       </c>
       <c r="G423" t="n">
-        <v>6.82851314544678</v>
+        <v>6.82851362228394</v>
       </c>
       <c r="H423" t="n">
         <v>3972357</v>
@@ -12665,7 +12665,7 @@
         <v>7.68621015548706</v>
       </c>
       <c r="G424" t="n">
-        <v>6.81515884399414</v>
+        <v>6.8151593208313</v>
       </c>
       <c r="H424" t="n">
         <v>2199628</v>
@@ -12723,7 +12723,7 @@
         <v>7.40004777908325</v>
       </c>
       <c r="G426" t="n">
-        <v>6.56142616271973</v>
+        <v>6.56142663955688</v>
       </c>
       <c r="H426" t="n">
         <v>1915267</v>
@@ -12752,7 +12752,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.93979835510254</v>
+        <v>6.9397988319397</v>
       </c>
       <c r="H427" t="n">
         <v>6403078</v>
@@ -12781,7 +12781,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857604980469</v>
+        <v>6.86857557296753</v>
       </c>
       <c r="H428" t="n">
         <v>3961179</v>
@@ -12897,7 +12897,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H432" t="n">
         <v>2571750</v>
@@ -12926,7 +12926,7 @@
         <v>7.96233081817627</v>
       </c>
       <c r="G433" t="n">
-        <v>7.05998802185059</v>
+        <v>7.05998849868774</v>
       </c>
       <c r="H433" t="n">
         <v>2066064</v>
@@ -13042,7 +13042,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409908294678</v>
+        <v>7.55409860610962</v>
       </c>
       <c r="H437" t="n">
         <v>2971867</v>
@@ -13071,7 +13071,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.47397232055664</v>
+        <v>7.4739727973938</v>
       </c>
       <c r="H438" t="n">
         <v>2774137</v>
@@ -13129,7 +13129,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H440" t="n">
         <v>3440039</v>
@@ -13158,7 +13158,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.66538429260254</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H441" t="n">
         <v>3163095</v>
@@ -13216,7 +13216,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H443" t="n">
         <v>2311936</v>
@@ -13448,7 +13448,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692302703857</v>
+        <v>7.93692350387573</v>
       </c>
       <c r="H451" t="n">
         <v>4589432</v>
@@ -13477,7 +13477,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504264831543</v>
+        <v>8.15504360198975</v>
       </c>
       <c r="H452" t="n">
         <v>4598808</v>
@@ -13767,7 +13767,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939523696899</v>
+        <v>7.38939476013184</v>
       </c>
       <c r="H462" t="n">
         <v>5765617</v>
@@ -13796,7 +13796,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.42945766448975</v>
+        <v>7.42945718765259</v>
       </c>
       <c r="H463" t="n">
         <v>3847044</v>
@@ -13825,7 +13825,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804521560669</v>
+        <v>7.23804569244385</v>
       </c>
       <c r="H464" t="n">
         <v>4793014</v>
@@ -13883,7 +13883,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H466" t="n">
         <v>9145143</v>
@@ -13912,7 +13912,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.66538429260254</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H467" t="n">
         <v>3470929</v>
@@ -13970,7 +13970,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479103088379</v>
+        <v>7.99479198455811</v>
       </c>
       <c r="H469" t="n">
         <v>8252776</v>
@@ -14057,7 +14057,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.5467700958252</v>
+        <v>8.54677104949951</v>
       </c>
       <c r="H472" t="n">
         <v>5904097</v>
@@ -14115,7 +14115,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H474" t="n">
         <v>5603952</v>
@@ -14144,7 +14144,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H475" t="n">
         <v>5013333</v>
@@ -14173,7 +14173,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H476" t="n">
         <v>3307360</v>
@@ -14231,7 +14231,7 @@
         <v>9.49354839324951</v>
       </c>
       <c r="G478" t="n">
-        <v>8.41767883300781</v>
+        <v>8.4176778793335</v>
       </c>
       <c r="H478" t="n">
         <v>4520776</v>
@@ -14289,7 +14289,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G480" t="n">
-        <v>7.78557348251343</v>
+        <v>7.78557395935059</v>
       </c>
       <c r="H480" t="n">
         <v>11572956</v>
@@ -14318,7 +14318,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757871627808</v>
+        <v>7.64757966995239</v>
       </c>
       <c r="H481" t="n">
         <v>6391732</v>
@@ -14347,7 +14347,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G482" t="n">
-        <v>7.62532186508179</v>
+        <v>7.62532234191895</v>
       </c>
       <c r="H482" t="n">
         <v>3509049</v>
@@ -14376,7 +14376,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G483" t="n">
-        <v>7.62532186508179</v>
+        <v>7.62532234191895</v>
       </c>
       <c r="H483" t="n">
         <v>4716149</v>
@@ -14405,7 +14405,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H484" t="n">
         <v>3256857</v>
@@ -14463,7 +14463,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576219558716</v>
+        <v>7.90576267242432</v>
       </c>
       <c r="H486" t="n">
         <v>2564414</v>
@@ -14492,7 +14492,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344148635864</v>
+        <v>7.84344244003296</v>
       </c>
       <c r="H487" t="n">
         <v>2436747</v>
@@ -14521,7 +14521,7 @@
         <v>8.60494041442871</v>
       </c>
       <c r="G488" t="n">
-        <v>7.62977313995361</v>
+        <v>7.62977266311646</v>
       </c>
       <c r="H488" t="n">
         <v>3215714</v>
@@ -14579,7 +14579,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H490" t="n">
         <v>2757855</v>
@@ -14608,7 +14608,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G491" t="n">
-        <v>7.74551010131836</v>
+        <v>7.7455096244812</v>
       </c>
       <c r="H491" t="n">
         <v>3546514</v>
@@ -14695,7 +14695,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H494" t="n">
         <v>4714362</v>
@@ -14724,7 +14724,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H495" t="n">
         <v>2456311</v>
@@ -14840,7 +14840,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63422441482544</v>
+        <v>7.6342248916626</v>
       </c>
       <c r="H499" t="n">
         <v>4090789</v>
@@ -14898,7 +14898,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H501" t="n">
         <v>2766406</v>
@@ -14985,7 +14985,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996185302734</v>
+        <v>7.74996280670166</v>
       </c>
       <c r="H504" t="n">
         <v>4120969</v>
@@ -15072,7 +15072,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G507" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H507" t="n">
         <v>4480449</v>
@@ -15130,7 +15130,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H509" t="n">
         <v>5719334</v>
@@ -15159,7 +15159,7 @@
         <v>9.61403846740723</v>
       </c>
       <c r="G510" t="n">
-        <v>8.52451419830322</v>
+        <v>8.52451324462891</v>
       </c>
       <c r="H510" t="n">
         <v>2445873</v>
@@ -15188,7 +15188,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109603881836</v>
+        <v>8.47109508514404</v>
       </c>
       <c r="H511" t="n">
         <v>3770392</v>
@@ -15217,7 +15217,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670719146729</v>
+        <v>8.50670623779297</v>
       </c>
       <c r="H512" t="n">
         <v>2875008</v>
@@ -15246,7 +15246,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.5022554397583</v>
+        <v>8.50225639343262</v>
       </c>
       <c r="H513" t="n">
         <v>2779890</v>
@@ -15275,7 +15275,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G514" t="n">
-        <v>8.73373126983643</v>
+        <v>8.73373031616211</v>
       </c>
       <c r="H514" t="n">
         <v>6368024</v>
@@ -15304,7 +15304,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H515" t="n">
         <v>3023534</v>
@@ -15391,7 +15391,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805530548096</v>
+        <v>8.65805625915527</v>
       </c>
       <c r="H518" t="n">
         <v>3468959</v>
@@ -15420,7 +15420,7 @@
         <v>10.1210966110229</v>
       </c>
       <c r="G519" t="n">
-        <v>8.9741096496582</v>
+        <v>8.97410869598389</v>
       </c>
       <c r="H519" t="n">
         <v>7443734</v>
@@ -15507,7 +15507,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G522" t="n">
-        <v>9.12990856170654</v>
+        <v>9.12990951538086</v>
       </c>
       <c r="H522" t="n">
         <v>5817803</v>
@@ -15536,7 +15536,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H523" t="n">
         <v>4786463</v>
@@ -15565,7 +15565,7 @@
         <v>10.1813411712646</v>
       </c>
       <c r="G524" t="n">
-        <v>9.02752685546875</v>
+        <v>9.02752590179443</v>
       </c>
       <c r="H524" t="n">
         <v>2378154</v>
@@ -15652,7 +15652,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G527" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H527" t="n">
         <v>5274403</v>
@@ -15681,7 +15681,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G528" t="n">
-        <v>9.1655216217041</v>
+        <v>9.16552066802979</v>
       </c>
       <c r="H528" t="n">
         <v>3314321</v>
@@ -15768,7 +15768,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833980560303</v>
+        <v>8.83833885192871</v>
       </c>
       <c r="H531" t="n">
         <v>2823997</v>
@@ -15826,7 +15826,7 @@
         <v>9.46593570709229</v>
       </c>
       <c r="G533" t="n">
-        <v>8.3931941986084</v>
+        <v>8.39319515228271</v>
       </c>
       <c r="H533" t="n">
         <v>3664518</v>
@@ -15855,7 +15855,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.41990566253662</v>
+        <v>8.41990375518799</v>
       </c>
       <c r="H534" t="n">
         <v>2981971</v>
@@ -15884,7 +15884,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.2485237121582</v>
+        <v>8.24852466583252</v>
       </c>
       <c r="H535" t="n">
         <v>4093310</v>
@@ -15913,7 +15913,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H536" t="n">
         <v>4347986</v>
@@ -16000,7 +16000,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660612106323</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H539" t="n">
         <v>5267752</v>
@@ -16029,7 +16029,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196708679199</v>
+        <v>7.61196756362915</v>
       </c>
       <c r="H540" t="n">
         <v>7866114</v>
@@ -16058,7 +16058,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519605636597</v>
+        <v>7.54519510269165</v>
       </c>
       <c r="H541" t="n">
         <v>2933056</v>
@@ -16116,7 +16116,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49622964859009</v>
+        <v>7.49623012542725</v>
       </c>
       <c r="H543" t="n">
         <v>5612249</v>
@@ -16232,7 +16232,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H547" t="n">
         <v>2390591</v>
@@ -16319,7 +16319,7 @@
         <v>8.83587837219238</v>
       </c>
       <c r="G550" t="n">
-        <v>7.83453989028931</v>
+        <v>7.83453893661499</v>
       </c>
       <c r="H550" t="n">
         <v>5628339</v>
@@ -16348,7 +16348,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.7633171081543</v>
+        <v>7.76331663131714</v>
       </c>
       <c r="H551" t="n">
         <v>3521552</v>
@@ -16377,7 +16377,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H552" t="n">
         <v>3398436</v>
@@ -16406,7 +16406,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G553" t="n">
-        <v>7.50068092346191</v>
+        <v>7.50068044662476</v>
       </c>
       <c r="H553" t="n">
         <v>4181215</v>
@@ -16435,7 +16435,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.52293872833252</v>
+        <v>7.5229377746582</v>
       </c>
       <c r="H554" t="n">
         <v>2585190</v>
@@ -16464,7 +16464,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368877410889</v>
+        <v>7.29368829727173</v>
       </c>
       <c r="H555" t="n">
         <v>4043829</v>
@@ -16522,7 +16522,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G557" t="n">
-        <v>7.50068092346191</v>
+        <v>7.50068044662476</v>
       </c>
       <c r="H557" t="n">
         <v>7379464</v>
@@ -16551,7 +16551,7 @@
         <v>8.56979656219482</v>
       </c>
       <c r="G558" t="n">
-        <v>7.5986123085022</v>
+        <v>7.59861183166504</v>
       </c>
       <c r="H558" t="n">
         <v>4269884</v>
@@ -16580,7 +16580,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663805007935</v>
+        <v>7.75663948059082</v>
       </c>
       <c r="H559" t="n">
         <v>3729295</v>
@@ -16609,7 +16609,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218725204468</v>
+        <v>7.75218820571899</v>
       </c>
       <c r="H560" t="n">
         <v>2796916</v>
@@ -16725,7 +16725,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936378479004</v>
+        <v>7.36936330795288</v>
       </c>
       <c r="H564" t="n">
         <v>2801339</v>
@@ -16754,7 +16754,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613433837891</v>
+        <v>7.43613481521606</v>
       </c>
       <c r="H565" t="n">
         <v>3258776</v>
@@ -16812,7 +16812,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826585769653</v>
+        <v>7.37826633453369</v>
       </c>
       <c r="H567" t="n">
         <v>3350760</v>
@@ -16899,7 +16899,7 @@
         <v>8.17820739746094</v>
       </c>
       <c r="G570" t="n">
-        <v>7.25140047073364</v>
+        <v>7.25139999389648</v>
       </c>
       <c r="H570" t="n">
         <v>3395514</v>
@@ -16986,7 +16986,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H573" t="n">
         <v>3487395</v>
@@ -17015,7 +17015,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H574" t="n">
         <v>1774619</v>
@@ -17131,7 +17131,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G578" t="n">
-        <v>6.98876523971558</v>
+        <v>6.98876571655273</v>
       </c>
       <c r="H578" t="n">
         <v>2910934</v>
@@ -17160,7 +17160,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744667053223</v>
+        <v>6.85744762420654</v>
       </c>
       <c r="H579" t="n">
         <v>4059831</v>
@@ -17218,7 +17218,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G581" t="n">
-        <v>7.08892202377319</v>
+        <v>7.08892250061035</v>
       </c>
       <c r="H581" t="n">
         <v>8326804</v>
@@ -17276,7 +17276,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H583" t="n">
         <v>5007935</v>
@@ -17305,7 +17305,7 @@
         <v>8.1079216003418</v>
       </c>
       <c r="G584" t="n">
-        <v>7.18907976150513</v>
+        <v>7.18907928466797</v>
       </c>
       <c r="H584" t="n">
         <v>3472564</v>
@@ -17334,7 +17334,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G585" t="n">
-        <v>7.18017721176147</v>
+        <v>7.18017673492432</v>
       </c>
       <c r="H585" t="n">
         <v>3344302</v>
@@ -17392,7 +17392,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842311859131</v>
       </c>
       <c r="H587" t="n">
         <v>5249327</v>
@@ -17421,7 +17421,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610383987427</v>
+        <v>7.41610431671143</v>
       </c>
       <c r="H588" t="n">
         <v>4009682</v>
@@ -17479,7 +17479,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G590" t="n">
-        <v>7.26475429534912</v>
+        <v>7.26475477218628</v>
       </c>
       <c r="H590" t="n">
         <v>7182347</v>
@@ -17508,7 +17508,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G591" t="n">
-        <v>6.98876523971558</v>
+        <v>6.98876571655273</v>
       </c>
       <c r="H591" t="n">
         <v>9716283</v>
@@ -17537,7 +17537,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766778945923</v>
+        <v>6.99766731262207</v>
       </c>
       <c r="H592" t="n">
         <v>4887233</v>
@@ -17595,7 +17595,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443881988525</v>
+        <v>7.06443929672241</v>
       </c>
       <c r="H594" t="n">
         <v>3740621</v>
@@ -17653,7 +17653,7 @@
         <v>7.92969799041748</v>
       </c>
       <c r="G596" t="n">
-        <v>7.03105306625366</v>
+        <v>7.03105354309082</v>
       </c>
       <c r="H596" t="n">
         <v>3230176</v>
@@ -17769,7 +17769,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G600" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H600" t="n">
         <v>11169423</v>
@@ -17798,7 +17798,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939523696899</v>
+        <v>7.38939476013184</v>
       </c>
       <c r="H601" t="n">
         <v>4478703</v>
@@ -17827,7 +17827,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G602" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H602" t="n">
         <v>3638485</v>
@@ -17914,7 +17914,7 @@
         <v>9.83242416381836</v>
       </c>
       <c r="G605" t="n">
-        <v>8.7181510925293</v>
+        <v>8.71815013885498</v>
       </c>
       <c r="H605" t="n">
         <v>23153988</v>
@@ -17943,7 +17943,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H606" t="n">
         <v>9737590</v>
@@ -17972,7 +17972,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G607" t="n">
-        <v>8.54009342193604</v>
+        <v>8.54009246826172</v>
       </c>
       <c r="H607" t="n">
         <v>5543597</v>
@@ -18001,7 +18001,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G608" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H608" t="n">
         <v>4747845</v>
@@ -18030,7 +18030,7 @@
         <v>10.0909738540649</v>
       </c>
       <c r="G609" t="n">
-        <v>8.9473991394043</v>
+        <v>8.94740009307861</v>
       </c>
       <c r="H609" t="n">
         <v>8237079</v>
@@ -18088,7 +18088,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37539005279541</v>
+        <v>8.37538909912109</v>
       </c>
       <c r="H611" t="n">
         <v>5678009</v>
@@ -18117,7 +18117,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065380096436</v>
+        <v>8.19065475463867</v>
       </c>
       <c r="H612" t="n">
         <v>4712315</v>
@@ -18146,7 +18146,7 @@
         <v>8.79822540283203</v>
       </c>
       <c r="G613" t="n">
-        <v>7.80115365982056</v>
+        <v>7.80115413665771</v>
       </c>
       <c r="H613" t="n">
         <v>4731371</v>
@@ -18262,7 +18262,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H617" t="n">
         <v>5676159</v>
@@ -18349,7 +18349,7 @@
         <v>9.31783485412598</v>
       </c>
       <c r="G620" t="n">
-        <v>8.26187896728516</v>
+        <v>8.26187801361084</v>
       </c>
       <c r="H620" t="n">
         <v>3046319</v>
@@ -18378,7 +18378,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H621" t="n">
         <v>4359962</v>
@@ -18407,7 +18407,7 @@
         <v>9.72448635101318</v>
       </c>
       <c r="G622" t="n">
-        <v>8.62244510650635</v>
+        <v>8.62244415283203</v>
       </c>
       <c r="H622" t="n">
         <v>5253374</v>
@@ -18436,7 +18436,7 @@
         <v>9.85250568389893</v>
       </c>
       <c r="G623" t="n">
-        <v>8.7359561920166</v>
+        <v>8.73595523834229</v>
       </c>
       <c r="H623" t="n">
         <v>3059274</v>
@@ -18465,7 +18465,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902694702148</v>
+        <v>8.56902599334717</v>
       </c>
       <c r="H624" t="n">
         <v>3124054</v>
@@ -18610,7 +18610,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G629" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H629" t="n">
         <v>1664123</v>
@@ -18813,7 +18813,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G636" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H636" t="n">
         <v>6312564</v>
@@ -18871,7 +18871,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H638" t="n">
         <v>2970699</v>
@@ -18929,7 +18929,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G640" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H640" t="n">
         <v>1067132</v>
@@ -18958,7 +18958,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.7114725112915</v>
+        <v>8.71147441864014</v>
       </c>
       <c r="H641" t="n">
         <v>2154097</v>
@@ -19045,7 +19045,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G644" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H644" t="n">
         <v>5210482</v>
@@ -19074,7 +19074,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009632110596</v>
+        <v>9.25009727478027</v>
       </c>
       <c r="H645" t="n">
         <v>6365259</v>
@@ -19103,7 +19103,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G646" t="n">
-        <v>9.39254474639893</v>
+        <v>9.39254379272461</v>
       </c>
       <c r="H646" t="n">
         <v>3391737</v>
@@ -19161,7 +19161,7 @@
         <v>10.0181789398193</v>
       </c>
       <c r="G648" t="n">
-        <v>8.88285446166992</v>
+        <v>8.88285350799561</v>
       </c>
       <c r="H648" t="n">
         <v>3244003</v>
@@ -19219,7 +19219,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G650" t="n">
-        <v>9.01639747619629</v>
+        <v>9.01639652252197</v>
       </c>
       <c r="H650" t="n">
         <v>2301830</v>
@@ -19277,7 +19277,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100601196289</v>
+        <v>9.12100505828857</v>
       </c>
       <c r="H652" t="n">
         <v>2816086</v>
@@ -19335,7 +19335,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G654" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H654" t="n">
         <v>2782854</v>
@@ -19422,7 +19422,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H657" t="n">
         <v>3819447</v>
@@ -19567,7 +19567,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686973571777</v>
+        <v>9.31686878204346</v>
       </c>
       <c r="H662" t="n">
         <v>5059956</v>
@@ -19625,7 +19625,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317378997803</v>
+        <v>9.79317283630371</v>
       </c>
       <c r="H664" t="n">
         <v>4580403</v>
@@ -19741,7 +19741,7 @@
         <v>11.200478553772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.93116855621338</v>
+        <v>9.93116760253906</v>
       </c>
       <c r="H668" t="n">
         <v>2563518</v>
@@ -19770,7 +19770,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139934539795</v>
+        <v>10.3139925003052</v>
       </c>
       <c r="H669" t="n">
         <v>8750009</v>
@@ -19973,7 +19973,7 @@
         <v>11.6046199798584</v>
       </c>
       <c r="G676" t="n">
-        <v>10.2895097732544</v>
+        <v>10.2895088195801</v>
       </c>
       <c r="H676" t="n">
         <v>1818429</v>
@@ -20002,7 +20002,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H677" t="n">
         <v>2314476</v>
@@ -20031,7 +20031,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G678" t="n">
-        <v>10.0157451629639</v>
+        <v>10.0157461166382</v>
       </c>
       <c r="H678" t="n">
         <v>2115163</v>
@@ -20118,7 +20118,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H681" t="n">
         <v>2245212</v>
@@ -20234,7 +20234,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99348926544189</v>
+        <v>9.99349021911621</v>
       </c>
       <c r="H685" t="n">
         <v>2940239</v>
@@ -20292,7 +20292,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694797515869</v>
+        <v>10.2694787979126</v>
       </c>
       <c r="H687" t="n">
         <v>2357662</v>
@@ -20321,7 +20321,7 @@
         <v>11.5017032623291</v>
       </c>
       <c r="G688" t="n">
-        <v>10.1982564926147</v>
+        <v>10.1982555389404</v>
       </c>
       <c r="H688" t="n">
         <v>1979022</v>
@@ -20350,7 +20350,7 @@
         <v>11.9259252548218</v>
       </c>
       <c r="G689" t="n">
-        <v>10.5744028091431</v>
+        <v>10.5744018554688</v>
       </c>
       <c r="H689" t="n">
         <v>2992968</v>
@@ -20379,7 +20379,7 @@
         <v>11.328498840332</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0446796417236</v>
+        <v>10.0446805953979</v>
       </c>
       <c r="H690" t="n">
         <v>5499203</v>
@@ -20408,7 +20408,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.3941192626953</v>
+        <v>10.394118309021</v>
       </c>
       <c r="H691" t="n">
         <v>4155413</v>
@@ -20437,7 +20437,7 @@
         <v>12.0489253997803</v>
       </c>
       <c r="G692" t="n">
-        <v>10.683464050293</v>
+        <v>10.6834630966187</v>
       </c>
       <c r="H692" t="n">
         <v>2537540</v>
@@ -20524,7 +20524,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.756911277771</v>
+        <v>10.7569122314453</v>
       </c>
       <c r="H695" t="n">
         <v>4827551</v>
@@ -20582,7 +20582,7 @@
         <v>12.4580860137939</v>
       </c>
       <c r="G697" t="n">
-        <v>11.0462551116943</v>
+        <v>11.0462560653687</v>
       </c>
       <c r="H697" t="n">
         <v>11143856</v>
@@ -20640,7 +20640,7 @@
         <v>13.2086343765259</v>
       </c>
       <c r="G699" t="n">
-        <v>11.7117462158203</v>
+        <v>11.7117471694946</v>
       </c>
       <c r="H699" t="n">
         <v>7959306</v>
@@ -20727,7 +20727,7 @@
         <v>13.5500202178955</v>
       </c>
       <c r="G702" t="n">
-        <v>12.014443397522</v>
+        <v>12.0144443511963</v>
       </c>
       <c r="H702" t="n">
         <v>7155972</v>
@@ -20814,7 +20814,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856685638428</v>
+        <v>12.0856676101685</v>
       </c>
       <c r="H705" t="n">
         <v>4491851</v>
@@ -20988,7 +20988,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395774841309</v>
+        <v>11.0395784378052</v>
       </c>
       <c r="H711" t="n">
         <v>3266745</v>
@@ -21017,7 +21017,7 @@
         <v>12.7065954208374</v>
       </c>
       <c r="G712" t="n">
-        <v>11.2666015625</v>
+        <v>11.2666025161743</v>
       </c>
       <c r="H712" t="n">
         <v>5559737</v>
@@ -21046,7 +21046,7 @@
         <v>12.7015752792358</v>
       </c>
       <c r="G713" t="n">
-        <v>11.2621507644653</v>
+        <v>11.262149810791</v>
       </c>
       <c r="H713" t="n">
         <v>2952425</v>
@@ -21162,7 +21162,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364080429077</v>
+        <v>10.4364070892334</v>
       </c>
       <c r="H717" t="n">
         <v>3926528</v>
@@ -21278,7 +21278,7 @@
         <v>11.7979049682617</v>
       </c>
       <c r="G721" t="n">
-        <v>10.4608898162842</v>
+        <v>10.4608907699585</v>
       </c>
       <c r="H721" t="n">
         <v>10788083</v>
@@ -21336,7 +21336,7 @@
         <v>11.8857622146606</v>
       </c>
       <c r="G723" t="n">
-        <v>10.5387916564941</v>
+        <v>10.5387907028198</v>
       </c>
       <c r="H723" t="n">
         <v>2694375</v>
@@ -21394,7 +21394,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.3941192626953</v>
+        <v>10.394118309021</v>
       </c>
       <c r="H725" t="n">
         <v>5437862</v>
@@ -21423,7 +21423,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H726" t="n">
         <v>2638902</v>
@@ -21452,7 +21452,7 @@
         <v>11.7025184631348</v>
       </c>
       <c r="G727" t="n">
-        <v>10.376314163208</v>
+        <v>10.3763132095337</v>
       </c>
       <c r="H727" t="n">
         <v>2777725</v>
@@ -21481,7 +21481,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H728" t="n">
         <v>6325209</v>
@@ -21510,7 +21510,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006381988525</v>
+        <v>10.3006391525269</v>
       </c>
       <c r="H729" t="n">
         <v>3047850</v>
@@ -21539,7 +21539,7 @@
         <v>11.7251100540161</v>
       </c>
       <c r="G730" t="n">
-        <v>10.3963441848755</v>
+        <v>10.3963451385498</v>
       </c>
       <c r="H730" t="n">
         <v>2649841</v>
@@ -21684,7 +21684,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580516815186</v>
+        <v>9.34580421447754</v>
       </c>
       <c r="H735" t="n">
         <v>2646670</v>
@@ -21713,7 +21713,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G736" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H736" t="n">
         <v>2599002</v>
@@ -21771,7 +21771,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G738" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H738" t="n">
         <v>10323921</v>
@@ -21800,7 +21800,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081153869629</v>
+        <v>8.29081249237061</v>
       </c>
       <c r="H739" t="n">
         <v>8509660</v>
@@ -21858,7 +21858,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889633178711</v>
+        <v>7.77889585494995</v>
       </c>
       <c r="H741" t="n">
         <v>8894223</v>
@@ -21916,7 +21916,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219253540039</v>
+        <v>8.46219158172607</v>
       </c>
       <c r="H743" t="n">
         <v>3711740</v>
@@ -21945,7 +21945,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H744" t="n">
         <v>2830649</v>
@@ -21974,7 +21974,7 @@
         <v>9.65922069549561</v>
       </c>
       <c r="G745" t="n">
-        <v>8.56457614898682</v>
+        <v>8.5645751953125</v>
       </c>
       <c r="H745" t="n">
         <v>3590690</v>
@@ -22090,7 +22090,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G749" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H749" t="n">
         <v>3226454</v>
@@ -22177,7 +22177,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G752" t="n">
-        <v>8.25519943237305</v>
+        <v>8.25520038604736</v>
       </c>
       <c r="H752" t="n">
         <v>4141957</v>
@@ -22206,7 +22206,7 @@
         <v>9.33540630340576</v>
       </c>
       <c r="G753" t="n">
-        <v>8.27745723724365</v>
+        <v>8.27745819091797</v>
       </c>
       <c r="H753" t="n">
         <v>2716829</v>
@@ -22264,7 +22264,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466569900513</v>
+        <v>7.91466617584229</v>
       </c>
       <c r="H755" t="n">
         <v>4636928</v>
@@ -22293,7 +22293,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.81228256225586</v>
+        <v>7.81228160858154</v>
       </c>
       <c r="H756" t="n">
         <v>3199541</v>
@@ -22380,7 +22380,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H759" t="n">
         <v>5059632</v>
@@ -22409,7 +22409,7 @@
         <v>8.17318725585938</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24694919586182</v>
+        <v>7.24694871902466</v>
       </c>
       <c r="H760" t="n">
         <v>5578537</v>
@@ -22438,7 +22438,7 @@
         <v>8.12800407409668</v>
       </c>
       <c r="G761" t="n">
-        <v>7.20688629150391</v>
+        <v>7.20688581466675</v>
       </c>
       <c r="H761" t="n">
         <v>4333423</v>
@@ -22467,7 +22467,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873378753662</v>
+        <v>6.96873331069946</v>
       </c>
       <c r="H762" t="n">
         <v>4541420</v>
@@ -22583,7 +22583,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576219558716</v>
+        <v>7.90576267242432</v>
       </c>
       <c r="H766" t="n">
         <v>6705143</v>
@@ -22728,7 +22728,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G771" t="n">
-        <v>8.39764595031738</v>
+        <v>8.3976469039917</v>
       </c>
       <c r="H771" t="n">
         <v>5244277</v>
@@ -22757,7 +22757,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G772" t="n">
-        <v>8.25519943237305</v>
+        <v>8.25520038604736</v>
       </c>
       <c r="H772" t="n">
         <v>3230113</v>
@@ -22786,7 +22786,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096927642822</v>
+        <v>8.39096832275391</v>
       </c>
       <c r="H773" t="n">
         <v>2691134</v>
@@ -22815,7 +22815,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H774" t="n">
         <v>4518486</v>
@@ -22931,7 +22931,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G778" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H778" t="n">
         <v>3928570</v>
@@ -22960,7 +22960,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G779" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H779" t="n">
         <v>5108708</v>
@@ -23018,7 +23018,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G781" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H781" t="n">
         <v>3452225</v>
@@ -23076,7 +23076,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G783" t="n">
-        <v>8.94517421722412</v>
+        <v>8.9451732635498</v>
       </c>
       <c r="H783" t="n">
         <v>2493851</v>
@@ -23192,7 +23192,7 @@
         <v>10.3445043563843</v>
       </c>
       <c r="G787" t="n">
-        <v>9.17219924926758</v>
+        <v>9.17219829559326</v>
       </c>
       <c r="H787" t="n">
         <v>3191829</v>
@@ -23221,7 +23221,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G788" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H788" t="n">
         <v>2462687</v>
@@ -23250,7 +23250,7 @@
         <v>10.4298496246338</v>
       </c>
       <c r="G789" t="n">
-        <v>9.24787139892578</v>
+        <v>9.2478723526001</v>
       </c>
       <c r="H789" t="n">
         <v>2010428</v>
@@ -23337,7 +23337,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G792" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H792" t="n">
         <v>1988992</v>
@@ -23453,7 +23453,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G796" t="n">
-        <v>9.43705940246582</v>
+        <v>9.4370584487915</v>
       </c>
       <c r="H796" t="n">
         <v>5910919</v>
@@ -23540,7 +23540,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H799" t="n">
         <v>2749374</v>
@@ -23656,7 +23656,7 @@
         <v>10.8440322875977</v>
       </c>
       <c r="G803" t="n">
-        <v>9.61511611938477</v>
+        <v>9.61511707305908</v>
       </c>
       <c r="H803" t="n">
         <v>5049854</v>
@@ -23714,7 +23714,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H805" t="n">
         <v>7839193</v>
@@ -23743,7 +23743,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232891082764</v>
+        <v>9.96232986450195</v>
       </c>
       <c r="H806" t="n">
         <v>5597634</v>
@@ -23801,7 +23801,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496046066284</v>
+        <v>10.3496036529541</v>
       </c>
       <c r="H808" t="n">
         <v>2858722</v>
@@ -24004,7 +24004,7 @@
         <v>12.3150053024292</v>
       </c>
       <c r="G815" t="n">
-        <v>10.9193887710571</v>
+        <v>10.9193897247314</v>
       </c>
       <c r="H815" t="n">
         <v>3038261</v>
@@ -24033,7 +24033,7 @@
         <v>12.1091690063477</v>
       </c>
       <c r="G816" t="n">
-        <v>10.7368803024292</v>
+        <v>10.7368793487549</v>
       </c>
       <c r="H816" t="n">
         <v>3221057</v>
@@ -24062,7 +24062,7 @@
         <v>12.2145967483521</v>
       </c>
       <c r="G817" t="n">
-        <v>10.8303594589233</v>
+        <v>10.8303604125977</v>
       </c>
       <c r="H817" t="n">
         <v>2672807</v>
@@ -24120,7 +24120,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G819" t="n">
-        <v>10.9883861541748</v>
+        <v>10.9883871078491</v>
       </c>
       <c r="H819" t="n">
         <v>2021022</v>
@@ -24381,7 +24381,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147802352905</v>
+        <v>10.8147811889648</v>
       </c>
       <c r="H828" t="n">
         <v>2456179</v>
@@ -24410,7 +24410,7 @@
         <v>12.2522497177124</v>
       </c>
       <c r="G829" t="n">
-        <v>10.8637447357178</v>
+        <v>10.8637456893921</v>
       </c>
       <c r="H829" t="n">
         <v>3054118</v>
@@ -24468,7 +24468,7 @@
         <v>12.4856977462769</v>
       </c>
       <c r="G831" t="n">
-        <v>11.0707368850708</v>
+        <v>11.0707378387451</v>
       </c>
       <c r="H831" t="n">
         <v>5821659</v>
@@ -24497,7 +24497,7 @@
         <v>12.6312885284424</v>
       </c>
       <c r="G832" t="n">
-        <v>11.1998300552368</v>
+        <v>11.1998291015625</v>
       </c>
       <c r="H832" t="n">
         <v>2539989</v>
@@ -24555,7 +24555,7 @@
         <v>12.0991277694702</v>
       </c>
       <c r="G834" t="n">
-        <v>10.7279777526855</v>
+        <v>10.7279767990112</v>
       </c>
       <c r="H834" t="n">
         <v>3226626</v>
@@ -24584,7 +24584,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G835" t="n">
-        <v>10.4386339187622</v>
+        <v>10.4386329650879</v>
       </c>
       <c r="H835" t="n">
         <v>4190619</v>
@@ -24642,7 +24642,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295736312866</v>
+        <v>10.3295726776123</v>
       </c>
       <c r="H837" t="n">
         <v>2609971</v>
@@ -24671,7 +24671,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271909713745</v>
+        <v>10.2271890640259</v>
       </c>
       <c r="H838" t="n">
         <v>2776794</v>
@@ -24700,7 +24700,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G839" t="n">
-        <v>10.4386339187622</v>
+        <v>10.4386329650879</v>
       </c>
       <c r="H839" t="n">
         <v>3240942</v>
@@ -24845,7 +24845,7 @@
         <v>11.3912544250488</v>
       </c>
       <c r="G844" t="n">
-        <v>10.100323677063</v>
+        <v>10.1003246307373</v>
       </c>
       <c r="H844" t="n">
         <v>5169154</v>
@@ -24874,7 +24874,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G845" t="n">
-        <v>10.2383184432983</v>
+        <v>10.2383193969727</v>
       </c>
       <c r="H845" t="n">
         <v>2752665</v>
@@ -24990,7 +24990,7 @@
         <v>10.836501121521</v>
       </c>
       <c r="G849" t="n">
-        <v>9.60843849182129</v>
+        <v>9.60843944549561</v>
       </c>
       <c r="H849" t="n">
         <v>2642683</v>
@@ -25019,7 +25019,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H850" t="n">
         <v>3580640</v>
@@ -25193,7 +25193,7 @@
         <v>10.4072589874268</v>
       </c>
       <c r="G856" t="n">
-        <v>9.2278413772583</v>
+        <v>9.22784042358398</v>
       </c>
       <c r="H856" t="n">
         <v>2374666</v>
@@ -25251,7 +25251,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G858" t="n">
-        <v>9.2701301574707</v>
+        <v>9.27012920379639</v>
       </c>
       <c r="H858" t="n">
         <v>2728302</v>
@@ -25280,7 +25280,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G859" t="n">
-        <v>9.16329383850098</v>
+        <v>9.16329479217529</v>
       </c>
       <c r="H859" t="n">
         <v>1906242</v>
@@ -25425,7 +25425,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G864" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H864" t="n">
         <v>1703266</v>
@@ -25570,7 +25570,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G869" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H869" t="n">
         <v>2768616</v>
@@ -25628,7 +25628,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G871" t="n">
-        <v>9.07204055786133</v>
+        <v>9.07204151153564</v>
       </c>
       <c r="H871" t="n">
         <v>6949172</v>
@@ -25744,7 +25744,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395671844482</v>
+        <v>9.58395576477051</v>
       </c>
       <c r="H875" t="n">
         <v>2681902</v>
@@ -25773,7 +25773,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G876" t="n">
-        <v>9.23451900482178</v>
+        <v>9.23451805114746</v>
       </c>
       <c r="H876" t="n">
         <v>3483538</v>
@@ -25831,7 +25831,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G878" t="n">
-        <v>9.2701301574707</v>
+        <v>9.27012920379639</v>
       </c>
       <c r="H878" t="n">
         <v>1207602</v>
@@ -25860,7 +25860,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G879" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H879" t="n">
         <v>2123211</v>
@@ -25889,7 +25889,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G880" t="n">
-        <v>9.55947208404541</v>
+        <v>9.55947303771973</v>
       </c>
       <c r="H880" t="n">
         <v>2840452</v>
@@ -25918,7 +25918,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G881" t="n">
-        <v>9.6062126159668</v>
+        <v>9.60621356964111</v>
       </c>
       <c r="H881" t="n">
         <v>3879724</v>
@@ -26005,7 +26005,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079208374023</v>
+        <v>9.69079113006592</v>
       </c>
       <c r="H884" t="n">
         <v>1520396</v>
@@ -26034,7 +26034,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G885" t="n">
-        <v>9.49047565460205</v>
+        <v>9.49047470092773</v>
       </c>
       <c r="H885" t="n">
         <v>1721405</v>
@@ -26121,7 +26121,7 @@
         <v>10.9820928573608</v>
       </c>
       <c r="G888" t="n">
-        <v>9.73753070831299</v>
+        <v>9.7375316619873</v>
       </c>
       <c r="H888" t="n">
         <v>1257161</v>
@@ -26266,7 +26266,7 @@
         <v>11.0272760391235</v>
       </c>
       <c r="G893" t="n">
-        <v>9.77759456634521</v>
+        <v>9.7775936126709</v>
       </c>
       <c r="H893" t="n">
         <v>2592934</v>
@@ -26353,7 +26353,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H896" t="n">
         <v>5491999</v>
@@ -26411,7 +26411,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070003509521</v>
+        <v>10.1070013046265</v>
       </c>
       <c r="H898" t="n">
         <v>2738861</v>
@@ -26527,7 +26527,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304798126221</v>
+        <v>9.71304893493652</v>
       </c>
       <c r="H902" t="n">
         <v>2481185</v>
@@ -26556,7 +26556,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H903" t="n">
         <v>2794057</v>
@@ -26643,7 +26643,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G906" t="n">
-        <v>10.0157451629639</v>
+        <v>10.0157461166382</v>
       </c>
       <c r="H906" t="n">
         <v>2792394</v>
@@ -26672,7 +26672,7 @@
         <v>11.4941720962524</v>
       </c>
       <c r="G907" t="n">
-        <v>10.1915788650513</v>
+        <v>10.191577911377</v>
       </c>
       <c r="H907" t="n">
         <v>5764525</v>
@@ -26701,7 +26701,7 @@
         <v>11.5845394134521</v>
       </c>
       <c r="G908" t="n">
-        <v>10.2717046737671</v>
+        <v>10.2717037200928</v>
       </c>
       <c r="H908" t="n">
         <v>2267960</v>
@@ -26788,7 +26788,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794006347656</v>
+        <v>9.99794101715088</v>
       </c>
       <c r="H911" t="n">
         <v>3280881</v>
@@ -26846,7 +26846,7 @@
         <v>10.7411136627197</v>
       </c>
       <c r="G913" t="n">
-        <v>9.5238618850708</v>
+        <v>9.52386093139648</v>
       </c>
       <c r="H913" t="n">
         <v>4157164</v>
@@ -26904,7 +26904,7 @@
         <v>10.4248304367065</v>
       </c>
       <c r="G915" t="n">
-        <v>9.24342155456543</v>
+        <v>9.24342060089111</v>
       </c>
       <c r="H915" t="n">
         <v>2417247</v>
@@ -26933,7 +26933,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G916" t="n">
-        <v>8.92514324188232</v>
+        <v>8.92514228820801</v>
       </c>
       <c r="H916" t="n">
         <v>4019358</v>
@@ -26991,7 +26991,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G918" t="n">
-        <v>9.12545776367188</v>
+        <v>9.12545871734619</v>
       </c>
       <c r="H918" t="n">
         <v>3054696</v>
@@ -27049,7 +27049,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G920" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H920" t="n">
         <v>3210453</v>
@@ -27107,7 +27107,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.95185089111328</v>
+        <v>8.9518518447876</v>
       </c>
       <c r="H922" t="n">
         <v>2394616</v>
@@ -27223,7 +27223,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G926" t="n">
-        <v>9.31464385986328</v>
+        <v>9.31464290618896</v>
       </c>
       <c r="H926" t="n">
         <v>1774533</v>
@@ -27252,7 +27252,7 @@
         <v>10.2842588424683</v>
       </c>
       <c r="G927" t="n">
-        <v>9.11878108978271</v>
+        <v>9.1187801361084</v>
       </c>
       <c r="H927" t="n">
         <v>2220798</v>
@@ -27281,7 +27281,7 @@
         <v>10.3545436859131</v>
       </c>
       <c r="G928" t="n">
-        <v>9.18110084533691</v>
+        <v>9.1810998916626</v>
       </c>
       <c r="H928" t="n">
         <v>1304029</v>
@@ -27310,7 +27310,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H929" t="n">
         <v>2564513</v>
@@ -27368,7 +27368,7 @@
         <v>10.9092969894409</v>
       </c>
       <c r="G931" t="n">
-        <v>9.67298603057861</v>
+        <v>9.6729850769043</v>
       </c>
       <c r="H931" t="n">
         <v>2301134</v>
@@ -27426,7 +27426,7 @@
         <v>10.9067869186401</v>
       </c>
       <c r="G933" t="n">
-        <v>9.67076015472412</v>
+        <v>9.6707592010498</v>
       </c>
       <c r="H933" t="n">
         <v>1044571</v>
@@ -27455,7 +27455,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G934" t="n">
-        <v>9.43705940246582</v>
+        <v>9.4370584487915</v>
       </c>
       <c r="H934" t="n">
         <v>1857397</v>
@@ -27629,7 +27629,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.1047744750977</v>
+        <v>10.1047735214233</v>
       </c>
       <c r="H940" t="n">
         <v>3374955</v>
@@ -27658,7 +27658,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136770248413</v>
+        <v>10.1136779785156</v>
       </c>
       <c r="H941" t="n">
         <v>3120641</v>
@@ -27687,7 +27687,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403875350952</v>
+        <v>10.1403856277466</v>
       </c>
       <c r="H942" t="n">
         <v>2004685</v>
@@ -27716,7 +27716,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230537414551</v>
+        <v>10.4230527877808</v>
       </c>
       <c r="H943" t="n">
         <v>5842648</v>
@@ -27890,7 +27890,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392383575439</v>
+        <v>9.56392574310303</v>
       </c>
       <c r="H949" t="n">
         <v>2157126</v>
@@ -28035,7 +28035,7 @@
         <v>10.2164840698242</v>
       </c>
       <c r="G954" t="n">
-        <v>9.05868530273438</v>
+        <v>9.05868625640869</v>
       </c>
       <c r="H954" t="n">
         <v>3488046</v>
@@ -28151,7 +28151,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G958" t="n">
-        <v>9.1655216217041</v>
+        <v>9.16552066802979</v>
       </c>
       <c r="H958" t="n">
         <v>3044501</v>
@@ -28209,7 +28209,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00971984863281</v>
+        <v>9.00972080230713</v>
       </c>
       <c r="H960" t="n">
         <v>3059945</v>
@@ -28267,7 +28267,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G962" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H962" t="n">
         <v>3934669</v>
@@ -28325,7 +28325,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G964" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H964" t="n">
         <v>4071910</v>
@@ -28354,7 +28354,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686973571777</v>
+        <v>9.31686878204346</v>
       </c>
       <c r="H965" t="n">
         <v>2851396</v>
@@ -28441,7 +28441,7 @@
         <v>10.3294429779053</v>
       </c>
       <c r="G968" t="n">
-        <v>9.15884304046631</v>
+        <v>9.15884399414062</v>
       </c>
       <c r="H968" t="n">
         <v>2590661</v>
@@ -28470,7 +28470,7 @@
         <v>10.2792387008667</v>
       </c>
       <c r="G969" t="n">
-        <v>9.11433029174805</v>
+        <v>9.11432933807373</v>
       </c>
       <c r="H969" t="n">
         <v>2928089</v>
@@ -28586,7 +28586,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65962982177734</v>
+        <v>9.65963077545166</v>
       </c>
       <c r="H973" t="n">
         <v>3880597</v>
@@ -28615,7 +28615,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G974" t="n">
-        <v>9.51050662994385</v>
+        <v>9.51050758361816</v>
       </c>
       <c r="H974" t="n">
         <v>4349124</v>
@@ -28673,7 +28673,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H976" t="n">
         <v>4961745</v>
@@ -28731,7 +28731,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G978" t="n">
-        <v>9.6062126159668</v>
+        <v>9.60621356964111</v>
       </c>
       <c r="H978" t="n">
         <v>5460186</v>
@@ -28789,7 +28789,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H980" t="n">
         <v>4874447</v>
@@ -28818,7 +28818,7 @@
         <v>11.2306022644043</v>
       </c>
       <c r="G981" t="n">
-        <v>9.95787715911865</v>
+        <v>9.95787811279297</v>
       </c>
       <c r="H981" t="n">
         <v>2713471</v>
@@ -28847,7 +28847,7 @@
         <v>11.1402349472046</v>
       </c>
       <c r="G982" t="n">
-        <v>9.87775230407715</v>
+        <v>9.87775135040283</v>
       </c>
       <c r="H982" t="n">
         <v>2778291</v>
@@ -28876,7 +28876,7 @@
         <v>11.0573978424072</v>
       </c>
       <c r="G983" t="n">
-        <v>9.80430126190186</v>
+        <v>9.80430221557617</v>
       </c>
       <c r="H983" t="n">
         <v>2502883</v>
@@ -28992,7 +28992,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H987" t="n">
         <v>8182251</v>
@@ -29050,7 +29050,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812492370605</v>
+        <v>9.40812397003174</v>
       </c>
       <c r="H989" t="n">
         <v>2714951</v>
@@ -29195,7 +29195,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G994" t="n">
-        <v>9.45931529998779</v>
+        <v>9.45931625366211</v>
       </c>
       <c r="H994" t="n">
         <v>2914765</v>
@@ -29282,7 +29282,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G997" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H997" t="n">
         <v>4136816</v>
@@ -29311,7 +29311,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G998" t="n">
-        <v>9.07204055786133</v>
+        <v>9.07204151153564</v>
       </c>
       <c r="H998" t="n">
         <v>3580666</v>
@@ -29398,7 +29398,7 @@
         <v>10.427339553833</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.24564552307129</v>
+        <v>9.24564647674561</v>
       </c>
       <c r="H1001" t="n">
         <v>2310864</v>
@@ -29427,7 +29427,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.39254474639893</v>
+        <v>9.39254379272461</v>
       </c>
       <c r="H1002" t="n">
         <v>2942968</v>
@@ -29514,7 +29514,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H1005" t="n">
         <v>2212645</v>
@@ -29572,7 +29572,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467578887939</v>
+        <v>9.33467674255371</v>
       </c>
       <c r="H1007" t="n">
         <v>3861795</v>
@@ -29601,7 +29601,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.45931529998779</v>
+        <v>9.45931625366211</v>
       </c>
       <c r="H1008" t="n">
         <v>2116813</v>
@@ -29630,7 +29630,7 @@
         <v>10.7938280105591</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.57060241699219</v>
+        <v>9.57060146331787</v>
       </c>
       <c r="H1009" t="n">
         <v>3043149</v>
@@ -29717,7 +29717,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H1012" t="n">
         <v>3418112</v>
@@ -29746,7 +29746,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.5616979598999</v>
+        <v>9.56169891357422</v>
       </c>
       <c r="H1013" t="n">
         <v>1635593</v>
@@ -29804,7 +29804,7 @@
         <v>10.934398651123</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.69524192810059</v>
+        <v>9.6952428817749</v>
       </c>
       <c r="H1015" t="n">
         <v>2311969</v>
@@ -29891,7 +29891,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H1018" t="n">
         <v>2839366</v>
@@ -29920,7 +29920,7 @@
         <v>11.1728668212891</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.90668487548828</v>
+        <v>9.9066858291626</v>
       </c>
       <c r="H1019" t="n">
         <v>3341541</v>
@@ -30065,7 +30065,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317378997803</v>
+        <v>9.79317283630371</v>
       </c>
       <c r="H1024" t="n">
         <v>1781897</v>
@@ -30152,7 +30152,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H1027" t="n">
         <v>2223593</v>
@@ -30210,7 +30210,7 @@
         <v>11.1126232147217</v>
       </c>
       <c r="G1029" t="n">
-        <v>9.85326862335205</v>
+        <v>9.85326957702637</v>
       </c>
       <c r="H1029" t="n">
         <v>1959789</v>
@@ -30239,7 +30239,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G1030" t="n">
-        <v>9.4615421295166</v>
+        <v>9.46154117584229</v>
       </c>
       <c r="H1030" t="n">
         <v>7606013</v>
@@ -30297,7 +30297,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G1032" t="n">
-        <v>9.12545776367188</v>
+        <v>9.12545871734619</v>
       </c>
       <c r="H1032" t="n">
         <v>2852190</v>
@@ -30471,7 +30471,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.20623397827148</v>
+        <v>8.2062349319458</v>
       </c>
       <c r="H1038" t="n">
         <v>4452658</v>
@@ -30529,7 +30529,7 @@
         <v>9.75962924957275</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.65360450744629</v>
+        <v>8.65360546112061</v>
       </c>
       <c r="H1040" t="n">
         <v>7621307</v>
@@ -30558,7 +30558,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H1041" t="n">
         <v>4707102</v>
@@ -30674,7 +30674,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H1045" t="n">
         <v>5766485</v>
@@ -30761,7 +30761,7 @@
         <v>9.55630302429199</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.47332191467285</v>
+        <v>8.47332096099854</v>
       </c>
       <c r="H1048" t="n">
         <v>2650515</v>
@@ -30819,7 +30819,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.43548488616943</v>
+        <v>8.43548393249512</v>
       </c>
       <c r="H1050" t="n">
         <v>4171244</v>
@@ -30906,7 +30906,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657657623291</v>
+        <v>7.71657609939575</v>
       </c>
       <c r="H1053" t="n">
         <v>7295256</v>
@@ -30935,7 +30935,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754774093628</v>
+        <v>7.62754726409912</v>
       </c>
       <c r="H1054" t="n">
         <v>5328087</v>
@@ -31109,7 +31109,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H1060" t="n">
         <v>4984381</v>
@@ -31138,7 +31138,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.70832347869873</v>
+        <v>6.70832395553589</v>
       </c>
       <c r="H1061" t="n">
         <v>5838598</v>
@@ -31196,7 +31196,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.95000410079956</v>
+        <v>4.9500036239624</v>
       </c>
       <c r="H1063" t="n">
         <v>15725169</v>
@@ -31225,7 +31225,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.95000410079956</v>
+        <v>4.9500036239624</v>
       </c>
       <c r="H1064" t="n">
         <v>14702152</v>
@@ -31312,7 +31312,7 @@
         <v>5.16848611831665</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.58276033401489</v>
+        <v>4.58275985717773</v>
       </c>
       <c r="H1067" t="n">
         <v>9831037</v>
@@ -31457,7 +31457,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342130661011</v>
+        <v>5.00342178344727</v>
       </c>
       <c r="H1072" t="n">
         <v>6911923</v>
@@ -31486,7 +31486,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.8899097442627</v>
+        <v>4.88990926742554</v>
       </c>
       <c r="H1073" t="n">
         <v>3925543</v>
@@ -31515,7 +31515,7 @@
         <v>5.85627889633179</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.19260787963867</v>
+        <v>5.19260740280151</v>
       </c>
       <c r="H1074" t="n">
         <v>6147761</v>
@@ -31544,7 +31544,7 @@
         <v>5.8261570930481</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.16589975357056</v>
+        <v>5.1658992767334</v>
       </c>
       <c r="H1075" t="n">
         <v>7136455</v>
@@ -31573,7 +31573,7 @@
         <v>5.89393186569214</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.22599363327026</v>
+        <v>5.22599315643311</v>
       </c>
       <c r="H1076" t="n">
         <v>4232448</v>
@@ -31631,7 +31631,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.98561573028564</v>
+        <v>4.98561525344849</v>
       </c>
       <c r="H1078" t="n">
         <v>2485771</v>
@@ -31660,7 +31660,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1079" t="n">
-        <v>4.98561573028564</v>
+        <v>4.98561525344849</v>
       </c>
       <c r="H1079" t="n">
         <v>4812027</v>
@@ -31718,7 +31718,7 @@
         <v>6.06713485717773</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.37956762313843</v>
+        <v>5.37956809997559</v>
       </c>
       <c r="H1081" t="n">
         <v>8617110</v>
@@ -31776,7 +31776,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950614929199</v>
+        <v>5.33950567245483</v>
       </c>
       <c r="H1083" t="n">
         <v>4088673</v>
@@ -31863,7 +31863,7 @@
         <v>6.04956388473511</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.36398887634277</v>
+        <v>5.36398839950562</v>
       </c>
       <c r="H1086" t="n">
         <v>5596784</v>
@@ -31921,7 +31921,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1088" t="n">
         <v>5337056</v>
@@ -31950,7 +31950,7 @@
         <v>5.47473001480103</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.85429811477661</v>
+        <v>4.85429859161377</v>
       </c>
       <c r="H1089" t="n">
         <v>3542169</v>
@@ -32037,7 +32037,7 @@
         <v>5.28395509719849</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.685142993927</v>
+        <v>4.68514347076416</v>
       </c>
       <c r="H1092" t="n">
         <v>4658214</v>
@@ -32124,7 +32124,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1095" t="n">
         <v>3476797</v>
@@ -32182,7 +32182,7 @@
         <v>5.55505609512329</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.92552137374878</v>
+        <v>4.92552089691162</v>
       </c>
       <c r="H1097" t="n">
         <v>3776492</v>
@@ -32211,7 +32211,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928503036499</v>
+        <v>5.19928550720215</v>
       </c>
       <c r="H1098" t="n">
         <v>4783125</v>
@@ -32240,7 +32240,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041393280029</v>
+        <v>5.21041345596313</v>
       </c>
       <c r="H1099" t="n">
         <v>4870688</v>
@@ -32298,7 +32298,7 @@
         <v>5.79101419448853</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.1347393989563</v>
+        <v>5.13473892211914</v>
       </c>
       <c r="H1101" t="n">
         <v>3599923</v>
@@ -32385,7 +32385,7 @@
         <v>5.80858516693115</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15031862258911</v>
+        <v>5.15031909942627</v>
       </c>
       <c r="H1104" t="n">
         <v>2378841</v>
@@ -32414,7 +32414,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248207092285</v>
+        <v>5.11248159408569</v>
       </c>
       <c r="H1105" t="n">
         <v>2051727</v>
@@ -32646,7 +32646,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.79800033569336</v>
+        <v>4.79800081253052</v>
       </c>
       <c r="H1113" t="n">
         <v>3350805</v>
@@ -32733,7 +32733,7 @@
         <v>5.46217918395996</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.86507511138916</v>
+        <v>4.865074634552</v>
       </c>
       <c r="H1116" t="n">
         <v>3829378</v>
@@ -32762,7 +32762,7 @@
         <v>5.30905723571777</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.72869157791138</v>
+        <v>4.72869110107422</v>
       </c>
       <c r="H1117" t="n">
         <v>7700374</v>
@@ -32907,7 +32907,7 @@
         <v>5.79854488372803</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.16467046737671</v>
+        <v>5.16466999053955</v>
       </c>
       <c r="H1122" t="n">
         <v>12491580</v>
@@ -32965,7 +32965,7 @@
         <v>6.46876621246338</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.76162528991699</v>
+        <v>5.76162576675415</v>
       </c>
       <c r="H1124" t="n">
         <v>11268120</v>
@@ -32994,7 +32994,7 @@
         <v>6.59176588058472</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.87117958068848</v>
+        <v>5.87117910385132</v>
       </c>
       <c r="H1125" t="n">
         <v>10577677</v>
@@ -33023,7 +33023,7 @@
         <v>6.41354179382324</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.71243810653687</v>
+        <v>5.71243762969971</v>
       </c>
       <c r="H1126" t="n">
         <v>6490655</v>
@@ -33139,7 +33139,7 @@
         <v>5.99182987213135</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33682632446289</v>
+        <v>5.33682584762573</v>
       </c>
       <c r="H1130" t="n">
         <v>5065402</v>
@@ -33197,7 +33197,7 @@
         <v>5.98680877685547</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.33235359191895</v>
+        <v>5.3323540687561</v>
       </c>
       <c r="H1132" t="n">
         <v>5119610</v>
@@ -33342,7 +33342,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.08418226242065</v>
+        <v>5.0841817855835</v>
       </c>
       <c r="H1137" t="n">
         <v>3931365</v>
@@ -33429,7 +33429,7 @@
         <v>5.61530113220215</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.00145769119263</v>
+        <v>5.00145816802979</v>
       </c>
       <c r="H1140" t="n">
         <v>4272132</v>
@@ -33487,7 +33487,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.97686290740967</v>
+        <v>4.97686338424683</v>
       </c>
       <c r="H1142" t="n">
         <v>3387639</v>
@@ -33574,7 +33574,7 @@
         <v>5.68558597564697</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.06405925750732</v>
+        <v>5.06405973434448</v>
       </c>
       <c r="H1145" t="n">
         <v>3689754</v>
@@ -33661,7 +33661,7 @@
         <v>5.27642488479614</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.69962644577026</v>
+        <v>4.69962596893311</v>
       </c>
       <c r="H1148" t="n">
         <v>5584746</v>
@@ -33748,7 +33748,7 @@
         <v>5.28897619247437</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.71080589294434</v>
+        <v>4.71080541610718</v>
       </c>
       <c r="H1151" t="n">
         <v>6369097</v>
@@ -33777,7 +33777,7 @@
         <v>5.36679220199585</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.78011512756348</v>
+        <v>4.78011465072632</v>
       </c>
       <c r="H1152" t="n">
         <v>6019418</v>
@@ -33806,7 +33806,7 @@
         <v>5.47724008560181</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.87848901748657</v>
+        <v>4.87848949432373</v>
       </c>
       <c r="H1153" t="n">
         <v>3853871</v>
@@ -34067,7 +34067,7 @@
         <v>4.92123222351074</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.38326168060303</v>
+        <v>4.38326215744019</v>
       </c>
       <c r="H1162" t="n">
         <v>24661467</v>
@@ -34154,7 +34154,7 @@
         <v>4.57357120513916</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.07360601425171</v>
+        <v>4.07360553741455</v>
       </c>
       <c r="H1165" t="n">
         <v>7438646</v>
@@ -34299,7 +34299,7 @@
         <v>4.96892595291138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.42574167251587</v>
+        <v>4.42574214935303</v>
       </c>
       <c r="H1170" t="n">
         <v>3451603</v>
@@ -34415,7 +34415,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1174" t="n">
-        <v>4.34190034866333</v>
+        <v>4.34189987182617</v>
       </c>
       <c r="H1174" t="n">
         <v>4695442</v>
@@ -34589,7 +34589,7 @@
         <v>4.66895818710327</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.15856599807739</v>
+        <v>4.15856552124023</v>
       </c>
       <c r="H1180" t="n">
         <v>6557504</v>
@@ -34734,7 +34734,7 @@
         <v>4.50579500198364</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.01323890686035</v>
+        <v>4.01323843002319</v>
       </c>
       <c r="H1185" t="n">
         <v>4155094</v>
@@ -34821,7 +34821,7 @@
         <v>4.39032697677612</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.91039323806763</v>
+        <v>3.91039347648621</v>
       </c>
       <c r="H1188" t="n">
         <v>4258438</v>
@@ -34850,7 +34850,7 @@
         <v>4.29242897033691</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.82319688796997</v>
+        <v>3.82319736480713</v>
       </c>
       <c r="H1189" t="n">
         <v>7837081</v>
@@ -34937,7 +34937,7 @@
         <v>4.19327592849731</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.73488306999207</v>
+        <v>3.73488283157349</v>
       </c>
       <c r="H1192" t="n">
         <v>4846298</v>
@@ -34995,7 +34995,7 @@
         <v>4.07906293869019</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.63315558433533</v>
+        <v>3.63315534591675</v>
       </c>
       <c r="H1194" t="n">
         <v>8280016</v>
@@ -35111,7 +35111,7 @@
         <v>4.22465419769287</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.76283121109009</v>
+        <v>3.76283097267151</v>
       </c>
       <c r="H1198" t="n">
         <v>5589044</v>
@@ -35401,7 +35401,7 @@
         <v>3.56321811676025</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.17370057106018</v>
+        <v>3.17370080947876</v>
       </c>
       <c r="H1208" t="n">
         <v>6464136</v>
@@ -35459,7 +35459,7 @@
         <v>3.86444091796875</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.44199514389038</v>
+        <v>3.4419949054718</v>
       </c>
       <c r="H1210" t="n">
         <v>7063864</v>
@@ -35604,7 +35604,7 @@
         <v>3.79415607452393</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.37939357757568</v>
+        <v>3.3793933391571</v>
       </c>
       <c r="H1215" t="n">
         <v>3909509</v>
@@ -35633,7 +35633,7 @@
         <v>3.65609502792358</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.25642490386963</v>
+        <v>3.25642466545105</v>
       </c>
       <c r="H1216" t="n">
         <v>4082735</v>
@@ -35807,7 +35807,7 @@
         <v>3.59585094451904</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.20276618003845</v>
+        <v>3.20276641845703</v>
       </c>
       <c r="H1222" t="n">
         <v>5346240</v>
@@ -35836,7 +35836,7 @@
         <v>3.62597298622131</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.22959542274475</v>
+        <v>3.22959566116333</v>
       </c>
       <c r="H1223" t="n">
         <v>3204692</v>
@@ -35865,7 +35865,7 @@
         <v>3.68496203422546</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.28213596343994</v>
+        <v>3.28213620185852</v>
       </c>
       <c r="H1224" t="n">
         <v>4139377</v>
@@ -36010,7 +36010,7 @@
         <v>3.78411507606506</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.370450258255</v>
+        <v>3.37045001983643</v>
       </c>
       <c r="H1229" t="n">
         <v>8618018</v>
@@ -36184,7 +36184,7 @@
         <v>4.6940598487854</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.1809229850769</v>
+        <v>4.18092346191406</v>
       </c>
       <c r="H1235" t="n">
         <v>15804964</v>
@@ -36387,7 +36387,7 @@
         <v>4.89487504959106</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.35978603363037</v>
+        <v>4.35978651046753</v>
       </c>
       <c r="H1242" t="n">
         <v>6079967</v>
@@ -36445,7 +36445,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.2770619392395</v>
+        <v>4.27706241607666</v>
       </c>
       <c r="H1244" t="n">
         <v>4685519</v>
@@ -36474,7 +36474,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.47157526016235</v>
+        <v>4.47157573699951</v>
       </c>
       <c r="H1245" t="n">
         <v>7739906</v>
@@ -36532,7 +36532,7 @@
         <v>5.42201614379883</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.82930183410645</v>
+        <v>4.8293023109436</v>
       </c>
       <c r="H1247" t="n">
         <v>8336834</v>
@@ -36561,7 +36561,7 @@
         <v>5.30654716491699</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.72645616531372</v>
+        <v>4.72645568847656</v>
       </c>
       <c r="H1248" t="n">
         <v>6460441</v>
@@ -36619,7 +36619,7 @@
         <v>5.1333441734314</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.57218647003174</v>
+        <v>4.5721869468689</v>
       </c>
       <c r="H1250" t="n">
         <v>5110006</v>
@@ -36706,7 +36706,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.62584447860718</v>
+        <v>4.62584495544434</v>
       </c>
       <c r="H1253" t="n">
         <v>2827257</v>
@@ -36735,7 +36735,7 @@
         <v>5.35675096511841</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.77117156982422</v>
+        <v>4.77117109298706</v>
       </c>
       <c r="H1254" t="n">
         <v>5955094</v>
@@ -36793,7 +36793,7 @@
         <v>5.37683200836182</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.78905725479126</v>
+        <v>4.78905773162842</v>
       </c>
       <c r="H1256" t="n">
         <v>1840506</v>
@@ -36880,7 +36880,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1259" t="n">
         <v>4061775</v>
@@ -36938,7 +36938,7 @@
         <v>5.46719884872437</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.86954545974731</v>
+        <v>4.86954593658447</v>
       </c>
       <c r="H1261" t="n">
         <v>2064399</v>
@@ -36967,7 +36967,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1262" t="n">
         <v>5407097</v>
@@ -36996,7 +36996,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.86060237884521</v>
+        <v>4.86060285568237</v>
       </c>
       <c r="H1263" t="n">
         <v>3511782</v>
@@ -37112,7 +37112,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1267" t="n">
         <v>3396789</v>
@@ -37257,7 +37257,7 @@
         <v>5.82364702224731</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.18702793121338</v>
+        <v>5.18702840805054</v>
       </c>
       <c r="H1272" t="n">
         <v>7105248</v>
@@ -37315,7 +37315,7 @@
         <v>6.17256307601929</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.49780225753784</v>
+        <v>5.49780178070068</v>
       </c>
       <c r="H1274" t="n">
         <v>7287173</v>
@@ -37344,7 +37344,7 @@
         <v>6.10729789733887</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.4396710395813</v>
+        <v>5.43967151641846</v>
       </c>
       <c r="H1275" t="n">
         <v>6169237</v>
@@ -37431,7 +37431,7 @@
         <v>6.08721685409546</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.42178535461426</v>
+        <v>5.42178583145142</v>
       </c>
       <c r="H1278" t="n">
         <v>4068724</v>
@@ -37460,7 +37460,7 @@
         <v>6.00689077377319</v>
       </c>
       <c r="G1279" t="n">
-        <v>5.3502402305603</v>
+        <v>5.35024070739746</v>
       </c>
       <c r="H1279" t="n">
         <v>3024433</v>
@@ -37547,7 +37547,7 @@
         <v>5.85878896713257</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.21832847595215</v>
+        <v>5.21832895278931</v>
       </c>
       <c r="H1282" t="n">
         <v>3059439</v>
@@ -37692,7 +37692,7 @@
         <v>5.34169006347656</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.75775671005249</v>
+        <v>4.75775718688965</v>
       </c>
       <c r="H1287" t="n">
         <v>4046294</v>
@@ -37721,7 +37721,7 @@
         <v>5.59019899368286</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.97910022735596</v>
+        <v>4.9790997505188</v>
       </c>
       <c r="H1288" t="n">
         <v>7589590</v>
@@ -37924,7 +37924,7 @@
         <v>5.98178911209106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.32788324356079</v>
+        <v>5.32788276672363</v>
       </c>
       <c r="H1295" t="n">
         <v>5483636</v>
@@ -38098,7 +38098,7 @@
         <v>6.55160188674927</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.8354058265686</v>
+        <v>5.83540630340576</v>
       </c>
       <c r="H1301" t="n">
         <v>9385518</v>
@@ -38156,7 +38156,7 @@
         <v>6.3457670211792</v>
       </c>
       <c r="G1303" t="n">
-        <v>5.65207242965698</v>
+        <v>5.65207195281982</v>
       </c>
       <c r="H1303" t="n">
         <v>6157528</v>
@@ -38185,7 +38185,7 @@
         <v>6.35078716278076</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.65654325485229</v>
+        <v>5.65654373168945</v>
       </c>
       <c r="H1304" t="n">
         <v>5745479</v>
@@ -38214,7 +38214,7 @@
         <v>6.40852212905884</v>
       </c>
       <c r="G1305" t="n">
-        <v>5.70796680450439</v>
+        <v>5.70796728134155</v>
       </c>
       <c r="H1305" t="n">
         <v>3560044</v>
@@ -38243,7 +38243,7 @@
         <v>6.63192892074585</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.90695190429688</v>
+        <v>5.90695142745972</v>
       </c>
       <c r="H1306" t="n">
         <v>7874391</v>
@@ -38330,7 +38330,7 @@
         <v>6.00940084457397</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.35247611999512</v>
+        <v>5.35247659683228</v>
       </c>
       <c r="H1309" t="n">
         <v>24228663</v>
@@ -38388,7 +38388,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.08418226242065</v>
+        <v>5.0841817855835</v>
       </c>
       <c r="H1311" t="n">
         <v>8961866</v>
@@ -38417,7 +38417,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1312" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1312" t="n">
         <v>9655227</v>
@@ -38504,7 +38504,7 @@
         <v>5.91652393341064</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.26975202560425</v>
+        <v>5.26975250244141</v>
       </c>
       <c r="H1315" t="n">
         <v>12797834</v>
@@ -38533,7 +38533,7 @@
         <v>6.07215595245361</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.40837144851685</v>
+        <v>5.40837097167969</v>
       </c>
       <c r="H1316" t="n">
         <v>9400118</v>
@@ -38591,7 +38591,7 @@
         <v>6.07717609405518</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.41284227371216</v>
+        <v>5.41284275054932</v>
       </c>
       <c r="H1318" t="n">
         <v>4627496</v>
@@ -38649,7 +38649,7 @@
         <v>6.12486982345581</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.455322265625</v>
+        <v>5.45532274246216</v>
       </c>
       <c r="H1320" t="n">
         <v>2675208</v>
@@ -38707,7 +38707,7 @@
         <v>5.97174787521362</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.31893968582153</v>
+        <v>5.31893920898438</v>
       </c>
       <c r="H1322" t="n">
         <v>5171781</v>
@@ -38765,7 +38765,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.31670331954956</v>
+        <v>5.31670379638672</v>
       </c>
       <c r="H1324" t="n">
         <v>4027905</v>
@@ -38852,7 +38852,7 @@
         <v>5.69060611724854</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.06853103637695</v>
+        <v>5.06853055953979</v>
       </c>
       <c r="H1327" t="n">
         <v>7314312</v>
@@ -39055,7 +39055,7 @@
         <v>5.87887096405029</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.23621511459351</v>
+        <v>5.23621559143066</v>
       </c>
       <c r="H1334" t="n">
         <v>3164034</v>
@@ -39287,7 +39287,7 @@
         <v>5.83870792388916</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.20044279098511</v>
+        <v>5.20044231414795</v>
       </c>
       <c r="H1342" t="n">
         <v>4486409</v>
@@ -39374,7 +39374,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.97686290740967</v>
+        <v>4.97686338424683</v>
       </c>
       <c r="H1345" t="n">
         <v>5024234</v>
@@ -39490,7 +39490,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.94556331634521</v>
+        <v>4.94556283950806</v>
       </c>
       <c r="H1349" t="n">
         <v>4621291</v>
@@ -39577,7 +39577,7 @@
         <v>4.87855911254883</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.34525394439697</v>
+        <v>4.34525346755981</v>
       </c>
       <c r="H1352" t="n">
         <v>14868855</v>
@@ -39606,7 +39606,7 @@
         <v>4.82333517074585</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.29606628417969</v>
+        <v>4.29606676101685</v>
       </c>
       <c r="H1353" t="n">
         <v>10990037</v>
@@ -39751,7 +39751,7 @@
         <v>5.06054782867432</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.50734853744507</v>
+        <v>4.50734806060791</v>
       </c>
       <c r="H1358" t="n">
         <v>3316325</v>
@@ -39954,7 +39954,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.69068336486816</v>
+        <v>4.69068288803101</v>
       </c>
       <c r="H1365" t="n">
         <v>9046399</v>
@@ -40012,7 +40012,7 @@
         <v>5.1383638381958</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.57665777206421</v>
+        <v>4.57665729522705</v>
       </c>
       <c r="H1367" t="n">
         <v>2528599</v>
@@ -40070,7 +40070,7 @@
         <v>5.12832307815552</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.56771469116211</v>
+        <v>4.56771421432495</v>
       </c>
       <c r="H1369" t="n">
         <v>2605182</v>
@@ -40186,7 +40186,7 @@
         <v>5.11828184127808</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.55877113342285</v>
+        <v>4.55877065658569</v>
       </c>
       <c r="H1373" t="n">
         <v>4133342</v>
@@ -40244,7 +40244,7 @@
         <v>5.3793420791626</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.79129314422607</v>
+        <v>4.79129266738892</v>
       </c>
       <c r="H1375" t="n">
         <v>10178926</v>
@@ -40273,7 +40273,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1376" t="n">
         <v>5287449</v>
@@ -40389,7 +40389,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1380" t="n">
         <v>6843942</v>
@@ -40476,7 +40476,7 @@
         <v>5.56760692596436</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.95897722244263</v>
+        <v>4.95897769927979</v>
       </c>
       <c r="H1383" t="n">
         <v>4282870</v>
@@ -40679,7 +40679,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.72421979904175</v>
+        <v>4.72422027587891</v>
       </c>
       <c r="H1390" t="n">
         <v>3701384</v>
@@ -40737,7 +40737,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.72421979904175</v>
+        <v>4.72422027587891</v>
       </c>
       <c r="H1392" t="n">
         <v>2649454</v>
@@ -40766,7 +40766,7 @@
         <v>5.29901599884033</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.71974802017212</v>
+        <v>4.71974754333496</v>
       </c>
       <c r="H1393" t="n">
         <v>2108129</v>
@@ -40853,7 +40853,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1396" t="n">
-        <v>4.56324291229248</v>
+        <v>4.56324338912964</v>
       </c>
       <c r="H1396" t="n">
         <v>3303148</v>
@@ -40882,7 +40882,7 @@
         <v>5.22873115539551</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.65714645385742</v>
+        <v>4.65714597702026</v>
       </c>
       <c r="H1397" t="n">
         <v>3565887</v>
@@ -40911,7 +40911,7 @@
         <v>5.21868991851807</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.64820289611816</v>
+        <v>4.64820241928101</v>
       </c>
       <c r="H1398" t="n">
         <v>2418474</v>
@@ -41027,7 +41027,7 @@
         <v>4.90617084503174</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.36984729766846</v>
+        <v>4.3698468208313</v>
       </c>
       <c r="H1402" t="n">
         <v>5231002</v>
@@ -41056,7 +41056,7 @@
         <v>4.97143602371216</v>
       </c>
       <c r="G1403" t="n">
-        <v>4.42797803878784</v>
+        <v>4.42797756195068</v>
       </c>
       <c r="H1403" t="n">
         <v>3203342</v>
@@ -41114,7 +41114,7 @@
         <v>4.88483476638794</v>
       </c>
       <c r="G1405" t="n">
-        <v>4.35084342956543</v>
+        <v>4.35084295272827</v>
       </c>
       <c r="H1405" t="n">
         <v>3408367</v>
@@ -41172,7 +41172,7 @@
         <v>4.90240621566772</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.36649370193481</v>
+        <v>4.36649417877197</v>
       </c>
       <c r="H1407" t="n">
         <v>3512290</v>
@@ -41288,7 +41288,7 @@
         <v>4.75681495666504</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.23681831359863</v>
+        <v>4.23681783676147</v>
       </c>
       <c r="H1411" t="n">
         <v>4771701</v>
@@ -41462,7 +41462,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1417" t="n">
-        <v>4.52970600128174</v>
+        <v>4.5297064781189</v>
       </c>
       <c r="H1417" t="n">
         <v>3747890</v>
@@ -41549,7 +41549,7 @@
         <v>4.91119194030762</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.37431907653809</v>
+        <v>4.37431955337524</v>
       </c>
       <c r="H1420" t="n">
         <v>4386657</v>
@@ -41636,7 +41636,7 @@
         <v>4.92499780654907</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.38661623001099</v>
+        <v>4.38661575317383</v>
       </c>
       <c r="H1423" t="n">
         <v>3890806</v>
@@ -41694,7 +41694,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.56324291229248</v>
+        <v>4.56324338912964</v>
       </c>
       <c r="H1425" t="n">
         <v>5305491</v>
@@ -41723,7 +41723,7 @@
         <v>5.16597604751587</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.60125112533569</v>
+        <v>4.60125160217285</v>
       </c>
       <c r="H1426" t="n">
         <v>3581797</v>
@@ -41868,7 +41868,7 @@
         <v>4.98147678375244</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.43692111968994</v>
+        <v>4.43692064285278</v>
       </c>
       <c r="H1431" t="n">
         <v>1848823</v>
@@ -41926,7 +41926,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.2770619392395</v>
+        <v>4.27706241607666</v>
       </c>
       <c r="H1433" t="n">
         <v>3356625</v>
@@ -42013,7 +42013,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.47157526016235</v>
+        <v>4.47157573699951</v>
       </c>
       <c r="H1436" t="n">
         <v>3876966</v>
@@ -42216,7 +42216,7 @@
         <v>4.96139478683472</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41903448104858</v>
+        <v>4.41903400421143</v>
       </c>
       <c r="H1443" t="n">
         <v>3045903</v>
@@ -42332,7 +42332,7 @@
         <v>5.01662015914917</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.46822261810303</v>
+        <v>4.46822214126587</v>
       </c>
       <c r="H1447" t="n">
         <v>5734258</v>
@@ -42390,7 +42390,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.62584447860718</v>
+        <v>4.62584495544434</v>
       </c>
       <c r="H1449" t="n">
         <v>7048976</v>
@@ -42419,7 +42419,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.52970600128174</v>
+        <v>4.5297064781189</v>
       </c>
       <c r="H1450" t="n">
         <v>6506615</v>
@@ -42506,7 +42506,7 @@
         <v>4.99151802062988</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.44586420059204</v>
+        <v>4.4458646774292</v>
       </c>
       <c r="H1453" t="n">
         <v>2739262</v>
@@ -42535,7 +42535,7 @@
         <v>4.91244697570801</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.37543678283691</v>
+        <v>4.37543725967407</v>
       </c>
       <c r="H1454" t="n">
         <v>3529674</v>
@@ -42564,7 +42564,7 @@
         <v>5.07058906555176</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.51629209518433</v>
+        <v>4.51629161834717</v>
       </c>
       <c r="H1455" t="n">
         <v>5222595</v>
@@ -42825,7 +42825,7 @@
         <v>5.55003595352173</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.94332695007324</v>
+        <v>4.9433274269104</v>
       </c>
       <c r="H1464" t="n">
         <v>6413047</v>
@@ -42883,7 +42883,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.69068336486816</v>
+        <v>4.69068288803101</v>
       </c>
       <c r="H1466" t="n">
         <v>7328705</v>
@@ -42941,7 +42941,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.79800033569336</v>
+        <v>4.79800081253052</v>
       </c>
       <c r="H1468" t="n">
         <v>8090619</v>
@@ -42999,7 +42999,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1470" t="n">
         <v>6942701</v>
@@ -43144,7 +43144,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.91202592849731</v>
+        <v>4.91202640533447</v>
       </c>
       <c r="H1475" t="n">
         <v>2995584</v>
@@ -43202,7 +43202,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1477" t="n">
         <v>4075860</v>
@@ -43289,7 +43289,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.94556331634521</v>
+        <v>4.94556283950806</v>
       </c>
       <c r="H1480" t="n">
         <v>5065969</v>
@@ -43347,7 +43347,7 @@
         <v>4.87353897094727</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.34078216552734</v>
+        <v>4.3407826423645</v>
       </c>
       <c r="H1482" t="n">
         <v>28990116</v>
@@ -43492,7 +43492,7 @@
         <v>4.81203889846802</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.2860050201416</v>
+        <v>4.28600549697876</v>
       </c>
       <c r="H1487" t="n">
         <v>5381782</v>
@@ -43521,7 +43521,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.34190034866333</v>
+        <v>4.34189987182617</v>
       </c>
       <c r="H1488" t="n">
         <v>5511409</v>
@@ -43666,7 +43666,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.39220476150513</v>
+        <v>4.39220523834229</v>
       </c>
       <c r="H1493" t="n">
         <v>2167743</v>
@@ -43956,7 +43956,7 @@
         <v>4.46563196182251</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.97746634483337</v>
+        <v>3.97746610641479</v>
       </c>
       <c r="H1503" t="n">
         <v>7272410</v>
@@ -43985,7 +43985,7 @@
         <v>4.50328493118286</v>
       </c>
       <c r="G1504" t="n">
-        <v>4.01100301742554</v>
+        <v>4.0110034942627</v>
       </c>
       <c r="H1504" t="n">
         <v>4367193</v>
@@ -44014,7 +44014,7 @@
         <v>4.42170381546021</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.93833994865417</v>
+        <v>3.93834018707275</v>
       </c>
       <c r="H1505" t="n">
         <v>3362331</v>
@@ -44130,7 +44130,7 @@
         <v>4.59365177154541</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.09149122238159</v>
+        <v>4.09149169921875</v>
       </c>
       <c r="H1509" t="n">
         <v>4350486</v>
@@ -44188,7 +44188,7 @@
         <v>4.56729507446289</v>
       </c>
       <c r="G1511" t="n">
-        <v>4.06801557540894</v>
+        <v>4.06801605224609</v>
       </c>
       <c r="H1511" t="n">
         <v>4359136</v>
@@ -44275,7 +44275,7 @@
         <v>4.41040802001953</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.92827892303467</v>
+        <v>3.92827916145325</v>
       </c>
       <c r="H1514" t="n">
         <v>3179388</v>
@@ -44304,7 +44304,7 @@
         <v>4.4455509185791</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.95958042144775</v>
+        <v>3.95958018302917</v>
       </c>
       <c r="H1515" t="n">
         <v>2325197</v>
@@ -44333,7 +44333,7 @@
         <v>4.37275505065918</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.89474201202393</v>
+        <v>3.89474248886108</v>
       </c>
       <c r="H1516" t="n">
         <v>3004717</v>
@@ -44507,7 +44507,7 @@
         <v>4.55097913742065</v>
       </c>
       <c r="G1522" t="n">
-        <v>4.0534839630127</v>
+        <v>4.05348348617554</v>
       </c>
       <c r="H1522" t="n">
         <v>1502529</v>
@@ -44652,7 +44652,7 @@
         <v>4.78317213058472</v>
       </c>
       <c r="G1527" t="n">
-        <v>4.26029396057129</v>
+        <v>4.26029443740845</v>
       </c>
       <c r="H1527" t="n">
         <v>2970018</v>
@@ -44768,7 +44768,7 @@
         <v>4.91495704650879</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.37767314910889</v>
+        <v>4.37767267227173</v>
       </c>
       <c r="H1531" t="n">
         <v>2759069</v>
@@ -44913,7 +44913,7 @@
         <v>5.03042602539062</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.48051881790161</v>
+        <v>4.48051929473877</v>
       </c>
       <c r="H1536" t="n">
         <v>2349535</v>
@@ -44971,7 +44971,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.39220476150513</v>
+        <v>4.39220523834229</v>
       </c>
       <c r="H1538" t="n">
         <v>3995107</v>
@@ -45058,7 +45058,7 @@
         <v>5.01410913467407</v>
       </c>
       <c r="G1541" t="n">
-        <v>4.4659857749939</v>
+        <v>4.46598625183105</v>
       </c>
       <c r="H1541" t="n">
         <v>2334898</v>
@@ -45348,7 +45348,7 @@
         <v>2.99591493606567</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.66841316223145</v>
+        <v>2.66841292381287</v>
       </c>
       <c r="H1551" t="n">
         <v>17072505</v>
@@ -45377,7 +45377,7 @@
         <v>3.02854704856873</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.6974778175354</v>
+        <v>2.69747805595398</v>
       </c>
       <c r="H1552" t="n">
         <v>16828629</v>
@@ -45522,7 +45522,7 @@
         <v>2.8616189956665</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.54879760742188</v>
+        <v>2.54879784584045</v>
       </c>
       <c r="H1557" t="n">
         <v>12600027</v>
@@ -45551,7 +45551,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.5622124671936</v>
+        <v>2.56221222877502</v>
       </c>
       <c r="H1558" t="n">
         <v>9318354</v>
@@ -45725,7 +45725,7 @@
         <v>2.51521301269531</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.24025940895081</v>
+        <v>2.24025964736938</v>
       </c>
       <c r="H1564" t="n">
         <v>6732142</v>
@@ -45754,7 +45754,7 @@
         <v>2.56165099143982</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.28162097930908</v>
+        <v>2.28162121772766</v>
       </c>
       <c r="H1565" t="n">
         <v>16777908</v>
@@ -45899,7 +45899,7 @@
         <v>2.56792688369751</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.2872109413147</v>
+        <v>2.28721117973328</v>
       </c>
       <c r="H1570" t="n">
         <v>5399583</v>
@@ -45928,7 +45928,7 @@
         <v>2.37715196609497</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.11729073524475</v>
+        <v>2.11729097366333</v>
       </c>
       <c r="H1571" t="n">
         <v>6070659</v>
@@ -46015,7 +46015,7 @@
         <v>2.58047795295715</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.29839015007019</v>
+        <v>2.29838991165161</v>
       </c>
       <c r="H1574" t="n">
         <v>9240163</v>
@@ -46131,7 +46131,7 @@
         <v>2.46450710296631</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.19509649276733</v>
+        <v>2.19509673118591</v>
       </c>
       <c r="H1578" t="n">
         <v>4819541</v>
@@ -46247,7 +46247,7 @@
         <v>2.67335510253906</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.38111424446106</v>
+        <v>2.38111400604248</v>
       </c>
       <c r="H1582" t="n">
         <v>3911764</v>
@@ -46392,7 +46392,7 @@
         <v>2.86287403106689</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.54991579055786</v>
+        <v>2.54991555213928</v>
       </c>
       <c r="H1587" t="n">
         <v>13747439</v>
@@ -46479,7 +46479,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.5622124671936</v>
+        <v>2.56221222877502</v>
       </c>
       <c r="H1590" t="n">
         <v>10760896</v>
@@ -46508,7 +46508,7 @@
         <v>2.93943500518799</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.61810708045959</v>
+        <v>2.61810731887817</v>
       </c>
       <c r="H1591" t="n">
         <v>7063060</v>
@@ -46537,7 +46537,7 @@
         <v>2.87919092178345</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.56444883346558</v>
+        <v>2.564448595047</v>
       </c>
       <c r="H1592" t="n">
         <v>10358249</v>
@@ -46566,7 +46566,7 @@
         <v>2.84404802322388</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.53314757347107</v>
+        <v>2.53314781188965</v>
       </c>
       <c r="H1593" t="n">
         <v>5883247</v>
@@ -46595,7 +46595,7 @@
         <v>2.77878308296204</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.47501707077026</v>
+        <v>2.47501730918884</v>
       </c>
       <c r="H1594" t="n">
         <v>7471517</v>
@@ -46653,7 +46653,7 @@
         <v>2.80262994766235</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.49625706672668</v>
+        <v>2.49625730514526</v>
       </c>
       <c r="H1596" t="n">
         <v>3079893</v>
@@ -46711,7 +46711,7 @@
         <v>2.79384398460388</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.48843145370483</v>
+        <v>2.48843169212341</v>
       </c>
       <c r="H1598" t="n">
         <v>2912676</v>
@@ -46740,7 +46740,7 @@
         <v>2.75744605064392</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.4560124874115</v>
+        <v>2.45601272583008</v>
       </c>
       <c r="H1599" t="n">
         <v>3637078</v>
@@ -46769,7 +46769,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.43700909614563</v>
+        <v>2.43700885772705</v>
       </c>
       <c r="H1600" t="n">
         <v>2248107</v>
@@ -46798,7 +46798,7 @@
         <v>2.84028291702271</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.52979421615601</v>
+        <v>2.52979397773743</v>
       </c>
       <c r="H1601" t="n">
         <v>4359715</v>
@@ -46885,7 +46885,7 @@
         <v>2.92437410354614</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.60469269752502</v>
+        <v>2.6046929359436</v>
       </c>
       <c r="H1604" t="n">
         <v>10127429</v>
@@ -46914,7 +46914,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.43700909614563</v>
+        <v>2.43700885772705</v>
       </c>
       <c r="H1605" t="n">
         <v>8650581</v>
@@ -47233,7 +47233,7 @@
         <v>2.48509001731873</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.21342968940735</v>
+        <v>2.21342945098877</v>
       </c>
       <c r="H1616" t="n">
         <v>11509858</v>
@@ -47262,7 +47262,7 @@
         <v>2.53780388832092</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.26038074493408</v>
+        <v>2.26038098335266</v>
       </c>
       <c r="H1617" t="n">
         <v>13634558</v>
@@ -47320,7 +47320,7 @@
         <v>2.68841600418091</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.39452862739563</v>
+        <v>2.39452886581421</v>
       </c>
       <c r="H1619" t="n">
         <v>6670481</v>
@@ -47349,7 +47349,7 @@
         <v>2.90680289268494</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.58904218673706</v>
+        <v>2.58904242515564</v>
       </c>
       <c r="H1620" t="n">
         <v>11371682</v>
@@ -47581,7 +47581,7 @@
         <v>2.97517991065979</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.64994478225708</v>
+        <v>2.6499445438385</v>
       </c>
       <c r="H1628" t="n">
         <v>9786163</v>
@@ -47755,7 +47755,7 @@
         <v>2.72426104545593</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.4264554977417</v>
+        <v>2.42645525932312</v>
       </c>
       <c r="H1634" t="n">
         <v>3222869</v>
@@ -47900,7 +47900,7 @@
         <v>2.37423992156982</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.11469697952271</v>
+        <v>2.11469721794128</v>
       </c>
       <c r="H1639" t="n">
         <v>5658326</v>
@@ -47987,7 +47987,7 @@
         <v>1.96649694442749</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.75152695178986</v>
+        <v>1.75152707099915</v>
       </c>
       <c r="H1642" t="n">
         <v>12639154</v>
@@ -48016,7 +48016,7 @@
         <v>2.01657509803772</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.79613089561462</v>
+        <v>1.79613077640533</v>
       </c>
       <c r="H1643" t="n">
         <v>25382152</v>
@@ -48103,7 +48103,7 @@
         <v>2.21557092666626</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.97337317466736</v>
+        <v>1.97337329387665</v>
       </c>
       <c r="H1646" t="n">
         <v>8434013</v>
@@ -48132,7 +48132,7 @@
         <v>1.73798203468323</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.54799258708954</v>
+        <v>1.54799246788025</v>
       </c>
       <c r="H1647" t="n">
         <v>26496542</v>
@@ -48161,7 +48161,7 @@
         <v>1.59776198863983</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.42310082912445</v>
+        <v>1.42310070991516</v>
       </c>
       <c r="H1648" t="n">
         <v>48720201</v>
@@ -48190,7 +48190,7 @@
         <v>1.24932205677032</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.11275088787079</v>
+        <v>1.11275100708008</v>
       </c>
       <c r="H1649" t="n">
         <v>56877192</v>
@@ -48451,7 +48451,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98913502693176</v>
+        <v>2.98913478851318</v>
       </c>
       <c r="H1658" t="n">
         <v>6899464</v>
@@ -48538,7 +48538,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.73594272136688</v>
+        <v>1.73594284057617</v>
       </c>
       <c r="H1661" t="n">
         <v>7745580</v>
@@ -48567,7 +48567,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.98598700761795</v>
+        <v>0.985986948013306</v>
       </c>
       <c r="H1662" t="n">
         <v>25986719</v>
@@ -48596,7 +48596,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.04210007190704</v>
+        <v>1.04209995269775</v>
       </c>
       <c r="H1663" t="n">
         <v>15517197</v>
@@ -48625,7 +48625,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.730360746383667</v>
+        <v>0.730360686779022</v>
       </c>
       <c r="H1664" t="n">
         <v>50412931</v>
@@ -48770,7 +48770,7 @@
         <v>0.71340000629425</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.635413885116577</v>
+        <v>0.635413825511932</v>
       </c>
       <c r="H1669" t="n">
         <v>28781555</v>
@@ -48828,7 +48828,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.659106016159058</v>
+        <v>0.659106075763702</v>
       </c>
       <c r="H1671" t="n">
         <v>27445946</v>
@@ -48857,7 +48857,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.692061305046082</v>
+        <v>0.692061364650726</v>
       </c>
       <c r="H1672" t="n">
         <v>35674340</v>
@@ -48944,7 +48944,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.751737117767334</v>
+        <v>0.751737177371979</v>
       </c>
       <c r="H1675" t="n">
         <v>37326895</v>
@@ -49002,7 +49002,7 @@
         <v>0.833599984645844</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.742474019527435</v>
+        <v>0.74247407913208</v>
       </c>
       <c r="H1677" t="n">
         <v>19689110</v>
@@ -49205,7 +49205,7 @@
         <v>0.821799993515015</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.731963932514191</v>
+        <v>0.731963992118835</v>
       </c>
       <c r="H1684" t="n">
         <v>16957436</v>
@@ -49292,7 +49292,7 @@
         <v>0.762199997901917</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.678879201412201</v>
+        <v>0.678879261016846</v>
       </c>
       <c r="H1687" t="n">
         <v>13487789</v>
@@ -49524,7 +49524,7 @@
         <v>0.716400027275085</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.638085961341858</v>
+        <v>0.638085901737213</v>
       </c>
       <c r="H1695" t="n">
         <v>20717644</v>
@@ -49756,7 +49756,7 @@
         <v>0.674600005149841</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.600855350494385</v>
+        <v>0.60085529088974</v>
       </c>
       <c r="H1703" t="n">
         <v>12648147</v>
@@ -49785,7 +49785,7 @@
         <v>0.697399973869324</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.621162831783295</v>
+        <v>0.621162891387939</v>
       </c>
       <c r="H1704" t="n">
         <v>26443104</v>
@@ -49843,7 +49843,7 @@
         <v>0.683200001716614</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.60851514339447</v>
+        <v>0.608515202999115</v>
       </c>
       <c r="H1706" t="n">
         <v>9988795</v>
@@ -49872,7 +49872,7 @@
         <v>0.662199974060059</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589810788631439</v>
+        <v>0.589810848236084</v>
       </c>
       <c r="H1707" t="n">
         <v>13712596</v>
@@ -49901,7 +49901,7 @@
         <v>0.64300000667572</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.572709679603577</v>
+        <v>0.572709739208221</v>
       </c>
       <c r="H1708" t="n">
         <v>58766149</v>
@@ -49930,7 +49930,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.540645122528076</v>
+        <v>0.540645062923431</v>
       </c>
       <c r="H1709" t="n">
         <v>28764901</v>
@@ -49959,7 +49959,7 @@
         <v>0.584800004959106</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.520871877670288</v>
+        <v>0.520871937274933</v>
       </c>
       <c r="H1710" t="n">
         <v>20980769</v>
@@ -49988,7 +49988,7 @@
         <v>0.59280002117157</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.527997434139252</v>
+        <v>0.527997374534607</v>
       </c>
       <c r="H1711" t="n">
         <v>21540866</v>
@@ -50075,7 +50075,7 @@
         <v>0.597199976444244</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.531916379928589</v>
+        <v>0.531916320323944</v>
       </c>
       <c r="H1714" t="n">
         <v>19250857</v>
@@ -50191,7 +50191,7 @@
         <v>0.637600004673004</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.567900061607361</v>
+        <v>0.567900002002716</v>
       </c>
       <c r="H1718" t="n">
         <v>20242520</v>
@@ -50336,7 +50336,7 @@
         <v>0.72759997844696</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.648061573505402</v>
+        <v>0.648061513900757</v>
       </c>
       <c r="H1723" t="n">
         <v>11884557</v>
@@ -50365,7 +50365,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.620806634426117</v>
+        <v>0.620806694030762</v>
       </c>
       <c r="H1724" t="n">
         <v>15320781</v>
@@ -50626,7 +50626,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.658215403556824</v>
+        <v>0.658215343952179</v>
       </c>
       <c r="H1733" t="n">
         <v>21488740</v>
@@ -50655,7 +50655,7 @@
         <v>0.758199989795685</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.675316512584686</v>
+        <v>0.675316452980042</v>
       </c>
       <c r="H1734" t="n">
         <v>33917790</v>
@@ -50713,7 +50713,7 @@
         <v>0.828599989414215</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.738020658493042</v>
+        <v>0.738020598888397</v>
       </c>
       <c r="H1736" t="n">
         <v>35628898</v>
@@ -50742,7 +50742,7 @@
         <v>0.958599984645844</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.853809475898743</v>
+        <v>0.853809535503387</v>
       </c>
       <c r="H1737" t="n">
         <v>99646498</v>
@@ -50800,7 +50800,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.876432955265045</v>
+        <v>0.8764328956604</v>
       </c>
       <c r="H1739" t="n">
         <v>39414006</v>
@@ -50829,7 +50829,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.873760879039764</v>
+        <v>0.87376081943512</v>
       </c>
       <c r="H1740" t="n">
         <v>36774205</v>
@@ -51003,7 +51003,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.882667720317841</v>
+        <v>0.882667660713196</v>
       </c>
       <c r="H1746" t="n">
         <v>44222060</v>
@@ -51061,7 +51061,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.919185638427734</v>
+        <v>0.919185698032379</v>
       </c>
       <c r="H1748" t="n">
         <v>60743048</v>
@@ -51090,7 +51090,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.957485139369965</v>
+        <v>0.957485198974609</v>
       </c>
       <c r="H1749" t="n">
         <v>38369686</v>
@@ -51148,7 +51148,7 @@
         <v>1.09650003910065</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.976634919643402</v>
+        <v>0.976634860038757</v>
       </c>
       <c r="H1751" t="n">
         <v>33789817</v>
@@ -51177,7 +51177,7 @@
         <v>1.03250002861023</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.919631123542786</v>
+        <v>0.919631063938141</v>
       </c>
       <c r="H1752" t="n">
         <v>95803812</v>
@@ -51206,7 +51206,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.92185777425766</v>
+        <v>0.921857714653015</v>
       </c>
       <c r="H1753" t="n">
         <v>44395351</v>
@@ -51322,7 +51322,7 @@
         <v>1.04649996757507</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.932100594043732</v>
+        <v>0.932100653648376</v>
       </c>
       <c r="H1757" t="n">
         <v>32064633</v>
@@ -51351,7 +51351,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.926311194896698</v>
+        <v>0.926311135292053</v>
       </c>
       <c r="H1758" t="n">
         <v>21110965</v>
@@ -51409,7 +51409,7 @@
         <v>1.04750001430511</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.932991325855255</v>
+        <v>0.93299126625061</v>
       </c>
       <c r="H1760" t="n">
         <v>40631058</v>
@@ -51438,7 +51438,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.912950932979584</v>
+        <v>0.912950873374939</v>
       </c>
       <c r="H1761" t="n">
         <v>26582079</v>
@@ -51467,7 +51467,7 @@
         <v>1.01950001716614</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.908052206039429</v>
+        <v>0.908052146434784</v>
       </c>
       <c r="H1762" t="n">
         <v>27481158</v>
@@ -51525,7 +51525,7 @@
         <v>1.04449999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.930319249629974</v>
+        <v>0.93031919002533</v>
       </c>
       <c r="H1764" t="n">
         <v>52512389</v>
@@ -51786,7 +51786,7 @@
         <v>1.00650000572205</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.896473288536072</v>
+        <v>0.896473228931427</v>
       </c>
       <c r="H1773" t="n">
         <v>22532469</v>
@@ -51844,7 +51844,7 @@
         <v>1.04949998855591</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.934772670269012</v>
+        <v>0.934772729873657</v>
       </c>
       <c r="H1775" t="n">
         <v>27222601</v>
@@ -51931,7 +51931,7 @@
         <v>1.10950005054474</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.988213717937469</v>
+        <v>0.988213777542114</v>
       </c>
       <c r="H1778" t="n">
         <v>33156068</v>
@@ -51989,7 +51989,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.977970898151398</v>
+        <v>0.977970957756042</v>
       </c>
       <c r="H1780" t="n">
         <v>82522322</v>
@@ -52047,7 +52047,7 @@
         <v>1.12750005722046</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.00424611568451</v>
+        <v>1.00424599647522</v>
       </c>
       <c r="H1782" t="n">
         <v>38953976</v>
@@ -52076,7 +52076,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.05456972122192</v>
+        <v>1.05456960201263</v>
       </c>
       <c r="H1783" t="n">
         <v>44539150</v>
@@ -52424,7 +52424,7 @@
         <v>1.31149995326996</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.16813170909882</v>
+        <v>1.16813182830811</v>
       </c>
       <c r="H1795" t="n">
         <v>88039189</v>
@@ -52685,7 +52685,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.25141084194183</v>
+        <v>1.25141072273254</v>
       </c>
       <c r="H1804" t="n">
         <v>50505371</v>
@@ -52772,7 +52772,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.23092496395111</v>
+        <v>1.2309250831604</v>
       </c>
       <c r="H1807" t="n">
         <v>27498297</v>
@@ -52801,7 +52801,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.21845543384552</v>
+        <v>1.21845555305481</v>
       </c>
       <c r="H1808" t="n">
         <v>27228579</v>
@@ -52946,7 +52946,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H1813" t="n">
         <v>201277103</v>
@@ -53062,7 +53062,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.25586426258087</v>
+        <v>1.25586414337158</v>
       </c>
       <c r="H1817" t="n">
         <v>26785082</v>
@@ -53149,7 +53149,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.24962937831879</v>
+        <v>1.24962949752808</v>
       </c>
       <c r="H1820" t="n">
         <v>28478257</v>
@@ -53236,7 +53236,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.31464922428131</v>
+        <v>1.3146493434906</v>
       </c>
       <c r="H1823" t="n">
         <v>73649010</v>
@@ -53265,7 +53265,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.35116732120514</v>
+        <v>1.35116744041443</v>
       </c>
       <c r="H1824" t="n">
         <v>173226691</v>
@@ -53294,7 +53294,7 @@
         <v>1.53450000286102</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.36675441265106</v>
+        <v>1.36675429344177</v>
       </c>
       <c r="H1825" t="n">
         <v>147696002</v>
@@ -53381,7 +53381,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.31643080711365</v>
+        <v>1.31643068790436</v>
       </c>
       <c r="H1828" t="n">
         <v>36445476</v>
@@ -53497,7 +53497,7 @@
         <v>1.35749995708466</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.20910322666168</v>
+        <v>1.20910334587097</v>
       </c>
       <c r="H1832" t="n">
         <v>30266079</v>
@@ -53555,7 +53555,7 @@
         <v>1.26549994945526</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.12716042995453</v>
+        <v>1.12716031074524</v>
       </c>
       <c r="H1834" t="n">
         <v>56083977</v>
@@ -53584,7 +53584,7 @@
         <v>1.14049994945526</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.01582479476929</v>
+        <v>1.01582491397858</v>
       </c>
       <c r="H1835" t="n">
         <v>70991471</v>
@@ -53671,7 +53671,7 @@
         <v>1.23450005054474</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.09954917430878</v>
+        <v>1.09954929351807</v>
       </c>
       <c r="H1838" t="n">
         <v>44048652</v>
@@ -53729,7 +53729,7 @@
         <v>1.32550001144409</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.1806013584137</v>
+        <v>1.18060147762299</v>
       </c>
       <c r="H1840" t="n">
         <v>26361553</v>
@@ -53758,7 +53758,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.14007520675659</v>
+        <v>1.14007532596588</v>
       </c>
       <c r="H1841" t="n">
         <v>30477091</v>
@@ -53932,7 +53932,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23181569576263</v>
+        <v>1.23181581497192</v>
       </c>
       <c r="H1847" t="n">
         <v>23160786</v>
@@ -53990,7 +53990,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1849" t="n">
         <v>61303523</v>
@@ -54512,7 +54512,7 @@
         <v>1.25049996376038</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.11380016803741</v>
+        <v>1.11380004882812</v>
       </c>
       <c r="H1867" t="n">
         <v>30080800</v>
@@ -54628,7 +54628,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.150763630867</v>
+        <v>1.15076351165771</v>
       </c>
       <c r="H1871" t="n">
         <v>24313190</v>
@@ -54715,7 +54715,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.13473117351532</v>
+        <v>1.13473129272461</v>
       </c>
       <c r="H1874" t="n">
         <v>17632468</v>
@@ -54802,7 +54802,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.12048029899597</v>
+        <v>1.12048017978668</v>
       </c>
       <c r="H1877" t="n">
         <v>12144067</v>
@@ -54831,7 +54831,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.15788888931274</v>
+        <v>1.15788900852203</v>
       </c>
       <c r="H1878" t="n">
         <v>28606803</v>
@@ -54976,7 +54976,7 @@
         <v>1.25750005245209</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.12003493309021</v>
+        <v>1.1200350522995</v>
       </c>
       <c r="H1883" t="n">
         <v>22657079</v>
@@ -55005,7 +55005,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.12226152420044</v>
+        <v>1.12226164340973</v>
       </c>
       <c r="H1884" t="n">
         <v>17046265</v>
@@ -55121,7 +55121,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.07416462898254</v>
+        <v>1.07416474819183</v>
       </c>
       <c r="H1888" t="n">
         <v>25051867</v>
@@ -55150,7 +55150,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.13473117351532</v>
+        <v>1.13473129272461</v>
       </c>
       <c r="H1889" t="n">
         <v>28793517</v>
@@ -55440,7 +55440,7 @@
         <v>1.25450003147125</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.11736285686493</v>
+        <v>1.11736297607422</v>
       </c>
       <c r="H1899" t="n">
         <v>19379185</v>
@@ -55498,7 +55498,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.08663439750671</v>
+        <v>1.08663427829742</v>
       </c>
       <c r="H1901" t="n">
         <v>20926564</v>
@@ -55585,7 +55585,7 @@
         <v>1.16250002384186</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.03542006015778</v>
+        <v>1.03541994094849</v>
       </c>
       <c r="H1904" t="n">
         <v>44264066</v>
@@ -55643,7 +55643,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.04833483695984</v>
+        <v>1.04833495616913</v>
       </c>
       <c r="H1906" t="n">
         <v>29040859</v>
@@ -55672,7 +55672,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.07772755622864</v>
+        <v>1.07772743701935</v>
       </c>
       <c r="H1907" t="n">
         <v>35754602</v>
@@ -55875,7 +55875,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.30039834976196</v>
+        <v>1.30039846897125</v>
       </c>
       <c r="H1914" t="n">
         <v>60137225</v>
@@ -55904,7 +55904,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.31108665466309</v>
+        <v>1.3110865354538</v>
       </c>
       <c r="H1915" t="n">
         <v>40402535</v>
@@ -55933,7 +55933,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.32266545295715</v>
+        <v>1.32266557216644</v>
       </c>
       <c r="H1916" t="n">
         <v>40030022</v>
@@ -56020,7 +56020,7 @@
         <v>1.43949997425079</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.28213930130005</v>
+        <v>1.28213942050934</v>
       </c>
       <c r="H1919" t="n">
         <v>27592628</v>
@@ -56049,7 +56049,7 @@
         <v>1.43250000476837</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.27590465545654</v>
+        <v>1.27590453624725</v>
       </c>
       <c r="H1920" t="n">
         <v>21395530</v>
@@ -56078,7 +56078,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.30039834976196</v>
+        <v>1.30039846897125</v>
       </c>
       <c r="H1921" t="n">
         <v>18806426</v>
@@ -56194,7 +56194,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.32800960540771</v>
+        <v>1.328009724617</v>
       </c>
       <c r="H1925" t="n">
         <v>26562115</v>
@@ -56281,7 +56281,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1928" t="n">
         <v>65561642</v>
@@ -56310,7 +56310,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1929" t="n">
         <v>29757990</v>
@@ -56339,7 +56339,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1930" t="n">
-        <v>1.29683554172516</v>
+        <v>1.29683566093445</v>
       </c>
       <c r="H1930" t="n">
         <v>46308940</v>
@@ -56368,7 +56368,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.29327297210693</v>
+        <v>1.29327285289764</v>
       </c>
       <c r="H1931" t="n">
         <v>26931723</v>
@@ -56426,7 +56426,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.25586426258087</v>
+        <v>1.25586414337158</v>
       </c>
       <c r="H1933" t="n">
         <v>26197753</v>
@@ -56484,7 +56484,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.24339473247528</v>
+        <v>1.24339461326599</v>
       </c>
       <c r="H1935" t="n">
         <v>23656707</v>
@@ -56658,7 +56658,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.304851770401</v>
+        <v>1.30485188961029</v>
       </c>
       <c r="H1941" t="n">
         <v>36097664</v>
@@ -56687,7 +56687,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H1942" t="n">
         <v>21886700</v>
@@ -56774,7 +56774,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.33869791030884</v>
+        <v>1.33869779109955</v>
       </c>
       <c r="H1945" t="n">
         <v>21109505</v>
@@ -56861,7 +56861,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.32266545295715</v>
+        <v>1.32266557216644</v>
       </c>
       <c r="H1948" t="n">
         <v>24397332</v>
@@ -56948,7 +56948,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1951" t="n">
-        <v>1.40193629264832</v>
+        <v>1.4019364118576</v>
       </c>
       <c r="H1951" t="n">
         <v>45002851</v>
@@ -56977,7 +56977,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.32800960540771</v>
+        <v>1.328009724617</v>
       </c>
       <c r="H1952" t="n">
         <v>124985920</v>
@@ -57093,7 +57093,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H1956" t="n">
         <v>39334965</v>
@@ -57151,7 +57151,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.37566125392914</v>
+        <v>1.37566113471985</v>
       </c>
       <c r="H1958" t="n">
         <v>66425360</v>
@@ -57238,7 +57238,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.41974997520447</v>
+        <v>1.41975009441376</v>
       </c>
       <c r="H1961" t="n">
         <v>31281838</v>
@@ -57325,7 +57325,7 @@
         <v>1.60950005054474</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.43355560302734</v>
+        <v>1.43355572223663</v>
       </c>
       <c r="H1964" t="n">
         <v>26138694</v>
@@ -57383,7 +57383,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.40104556083679</v>
+        <v>1.40104568004608</v>
       </c>
       <c r="H1966" t="n">
         <v>153129411</v>
@@ -57470,7 +57470,7 @@
         <v>1.46249997615814</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.30262506008148</v>
+        <v>1.30262517929077</v>
       </c>
       <c r="H1969" t="n">
         <v>26919423</v>
@@ -57499,7 +57499,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.27679526805878</v>
+        <v>1.27679538726807</v>
       </c>
       <c r="H1970" t="n">
         <v>26802260</v>
@@ -57528,7 +57528,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.29683554172516</v>
+        <v>1.29683566093445</v>
       </c>
       <c r="H1971" t="n">
         <v>25191162</v>
@@ -57731,7 +57731,7 @@
         <v>1.41849994659424</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.26343488693237</v>
+        <v>1.26343500614166</v>
       </c>
       <c r="H1978" t="n">
         <v>88712511</v>
@@ -57934,7 +57934,7 @@
         <v>1.5275000333786</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.36051952838898</v>
+        <v>1.36051964759827</v>
       </c>
       <c r="H1985" t="n">
         <v>16749025</v>
@@ -57992,7 +57992,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.37566125392914</v>
+        <v>1.37566113471985</v>
       </c>
       <c r="H1987" t="n">
         <v>51105926</v>
@@ -58021,7 +58021,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.29015552997589</v>
+        <v>1.29015564918518</v>
       </c>
       <c r="H1988" t="n">
         <v>67066172</v>
@@ -58079,7 +58079,7 @@
         <v>1.41449999809265</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.25987219810486</v>
+        <v>1.25987231731415</v>
       </c>
       <c r="H1990" t="n">
         <v>29949971</v>
@@ -58166,7 +58166,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.23626911640167</v>
+        <v>1.23626923561096</v>
       </c>
       <c r="H1993" t="n">
         <v>49894794</v>
@@ -58427,7 +58427,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H2002" t="n">
         <v>21379601</v>
@@ -58456,7 +58456,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.23805058002472</v>
+        <v>1.23805046081543</v>
       </c>
       <c r="H2003" t="n">
         <v>18744870</v>
@@ -58572,7 +58572,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H2007" t="n">
         <v>40689470</v>
@@ -58717,7 +58717,7 @@
         <v>1.44749999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>1.28926491737366</v>
+        <v>1.28926479816437</v>
       </c>
       <c r="H2012" t="n">
         <v>13752928</v>
@@ -58862,7 +58862,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H2017" t="n">
         <v>79262449</v>
@@ -58978,7 +58978,7 @@
         <v>1.46150004863739</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.30173456668854</v>
+        <v>1.30173444747925</v>
       </c>
       <c r="H2021" t="n">
         <v>32246011</v>
@@ -59007,7 +59007,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.24784815311432</v>
+        <v>1.24784803390503</v>
       </c>
       <c r="H2022" t="n">
         <v>61474648</v>
@@ -59036,7 +59036,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.24784815311432</v>
+        <v>1.24784803390503</v>
       </c>
       <c r="H2023" t="n">
         <v>34906238</v>
@@ -59123,7 +59123,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.22647154331207</v>
+        <v>1.22647166252136</v>
       </c>
       <c r="H2026" t="n">
         <v>31335128</v>
@@ -59210,7 +59210,7 @@
         <v>1.42050004005432</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.26521646976471</v>
+        <v>1.26521635055542</v>
       </c>
       <c r="H2029" t="n">
         <v>35969343</v>
@@ -59268,7 +59268,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.29015552997589</v>
+        <v>1.29015564918518</v>
       </c>
       <c r="H2031" t="n">
         <v>21961584</v>
@@ -59326,7 +59326,7 @@
         <v>1.44649994373322</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.28837418556213</v>
+        <v>1.28837406635284</v>
       </c>
       <c r="H2033" t="n">
         <v>15340362</v>
@@ -59384,7 +59384,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.32088422775269</v>
+        <v>1.3208841085434</v>
       </c>
       <c r="H2035" t="n">
         <v>16248522</v>
@@ -59413,7 +59413,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.30930519104004</v>
+        <v>1.30930531024933</v>
       </c>
       <c r="H2036" t="n">
         <v>16596498</v>
@@ -59471,7 +59471,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.32622826099396</v>
+        <v>1.32622814178467</v>
       </c>
       <c r="H2038" t="n">
         <v>31598891</v>
@@ -59558,7 +59558,7 @@
         <v>1.50650000572205</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.3418151140213</v>
+        <v>1.34181523323059</v>
       </c>
       <c r="H2041" t="n">
         <v>49175369</v>
@@ -59790,7 +59790,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.27679526805878</v>
+        <v>1.27679538726807</v>
       </c>
       <c r="H2049" t="n">
         <v>35782956</v>
@@ -59877,7 +59877,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31643080711365</v>
+        <v>1.31643068790436</v>
       </c>
       <c r="H2052" t="n">
         <v>70363678</v>
@@ -59964,7 +59964,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.34315133094788</v>
+        <v>1.34315121173859</v>
       </c>
       <c r="H2055" t="n">
         <v>21291896</v>
@@ -60399,7 +60399,7 @@
         <v>1.375</v>
       </c>
       <c r="G2070" t="n">
-        <v>1.2246903181076</v>
+        <v>1.22469019889832</v>
       </c>
       <c r="H2070" t="n">
         <v>37201230</v>
@@ -60486,7 +60486,7 @@
         <v>1.38100004196167</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.23003447055817</v>
+        <v>1.23003435134888</v>
       </c>
       <c r="H2073" t="n">
         <v>23884244</v>
@@ -60602,7 +60602,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.32979106903076</v>
+        <v>1.32979094982147</v>
       </c>
       <c r="H2077" t="n">
         <v>97981694</v>
@@ -60689,7 +60689,7 @@
         <v>1.82149994373322</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.62238049507141</v>
+        <v>1.6223806142807</v>
       </c>
       <c r="H2080" t="n">
         <v>170004032</v>
@@ -60776,7 +60776,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.723473072052</v>
+        <v>1.72347319126129</v>
       </c>
       <c r="H2083" t="n">
         <v>102058873</v>
@@ -60863,7 +60863,7 @@
         <v>1.97650003433228</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.76043653488159</v>
+        <v>1.76043665409088</v>
       </c>
       <c r="H2086" t="n">
         <v>36852781</v>
@@ -60979,7 +60979,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.87488949298859</v>
+        <v>1.87488961219788</v>
       </c>
       <c r="H2090" t="n">
         <v>47381130</v>
@@ -61008,7 +61008,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.88112425804138</v>
+        <v>1.88112413883209</v>
       </c>
       <c r="H2091" t="n">
         <v>28755854</v>
@@ -61037,7 +61037,7 @@
         <v>2.08699989318848</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.8588570356369</v>
+        <v>1.85885715484619</v>
       </c>
       <c r="H2092" t="n">
         <v>29642492</v>
@@ -61153,7 +61153,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.91318893432617</v>
+        <v>1.91318881511688</v>
       </c>
       <c r="H2096" t="n">
         <v>51280827</v>
@@ -61356,7 +61356,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.98889708518982</v>
+        <v>1.98889696598053</v>
       </c>
       <c r="H2103" t="n">
         <v>20444616</v>
@@ -61385,7 +61385,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2104" t="n">
-        <v>2.0076014995575</v>
+        <v>2.00760126113892</v>
       </c>
       <c r="H2104" t="n">
         <v>25187040</v>
@@ -61414,7 +61414,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G2105" t="n">
-        <v>2.00849223136902</v>
+        <v>2.00849199295044</v>
       </c>
       <c r="H2105" t="n">
         <v>29639951</v>
@@ -61472,7 +61472,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.06994891166687</v>
+        <v>2.06994915008545</v>
       </c>
       <c r="H2107" t="n">
         <v>41532484</v>
@@ -61530,7 +61530,7 @@
         <v>2.3970000743866</v>
       </c>
       <c r="G2109" t="n">
-        <v>2.13496899604797</v>
+        <v>2.13496923446655</v>
       </c>
       <c r="H2109" t="n">
         <v>81592175</v>
@@ -61559,7 +61559,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2110" t="n">
-        <v>2.08420014381409</v>
+        <v>2.08419990539551</v>
       </c>
       <c r="H2110" t="n">
         <v>42505018</v>
@@ -61646,7 +61646,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.99513173103333</v>
+        <v>1.99513185024261</v>
       </c>
       <c r="H2113" t="n">
         <v>34419597</v>
@@ -61675,7 +61675,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2114" t="n">
         <v>27318033</v>
@@ -61733,7 +61733,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.94258153438568</v>
+        <v>1.94258141517639</v>
       </c>
       <c r="H2116" t="n">
         <v>46811721</v>
@@ -61820,7 +61820,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.9719740152359</v>
+        <v>1.97197389602661</v>
       </c>
       <c r="H2119" t="n">
         <v>18487545</v>
@@ -61878,7 +61878,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.95237898826599</v>
+        <v>1.9523788690567</v>
       </c>
       <c r="H2121" t="n">
         <v>27702781</v>
@@ -61936,7 +61936,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.94079983234406</v>
+        <v>1.94080007076263</v>
       </c>
       <c r="H2123" t="n">
         <v>20243345</v>
@@ -62023,7 +62023,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2126" t="n">
-        <v>1.91318893432617</v>
+        <v>1.91318881511688</v>
       </c>
       <c r="H2126" t="n">
         <v>16042180</v>
@@ -62081,7 +62081,7 @@
         <v>2.13100004196167</v>
       </c>
       <c r="G2128" t="n">
-        <v>1.89804720878601</v>
+        <v>1.8980473279953</v>
       </c>
       <c r="H2128" t="n">
         <v>22011055</v>
@@ -62110,7 +62110,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2129" t="n">
         <v>19775385</v>
@@ -62168,7 +62168,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G2131" t="n">
-        <v>1.97019267082214</v>
+        <v>1.97019255161285</v>
       </c>
       <c r="H2131" t="n">
         <v>19971385</v>
@@ -62197,7 +62197,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2132" t="n">
-        <v>2.02541518211365</v>
+        <v>2.02541494369507</v>
       </c>
       <c r="H2132" t="n">
         <v>39975168</v>
@@ -62255,7 +62255,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2134" t="n">
-        <v>2.11359262466431</v>
+        <v>2.11359286308289</v>
       </c>
       <c r="H2134" t="n">
         <v>44554345</v>
@@ -62371,7 +62371,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2138" t="n">
-        <v>2.12160873413086</v>
+        <v>2.12160897254944</v>
       </c>
       <c r="H2138" t="n">
         <v>27147448</v>
@@ -62400,7 +62400,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2139" t="n">
-        <v>2.11359262466431</v>
+        <v>2.11359286308289</v>
       </c>
       <c r="H2139" t="n">
         <v>18307723</v>
@@ -62458,7 +62458,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2141" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2141" t="n">
         <v>13550932</v>
@@ -62516,7 +62516,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2143" t="n">
-        <v>1.98889708518982</v>
+        <v>1.98889696598053</v>
       </c>
       <c r="H2143" t="n">
         <v>26661132</v>
@@ -62574,7 +62574,7 @@
         <v>2.15300011634827</v>
       </c>
       <c r="G2145" t="n">
-        <v>1.9176424741745</v>
+        <v>1.91764235496521</v>
       </c>
       <c r="H2145" t="n">
         <v>22296682</v>
@@ -62603,7 +62603,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.92031419277191</v>
+        <v>1.9203143119812</v>
       </c>
       <c r="H2146" t="n">
         <v>35218310</v>
@@ -62632,7 +62632,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.9336746931076</v>
+        <v>1.93367457389832</v>
       </c>
       <c r="H2147" t="n">
         <v>17467441</v>
@@ -62661,7 +62661,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2148" t="n">
         <v>28506448</v>
@@ -62690,7 +62690,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.83926224708557</v>
+        <v>1.83926212787628</v>
       </c>
       <c r="H2149" t="n">
         <v>27905894</v>
@@ -62748,7 +62748,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2151" t="n">
         <v>33021803</v>
@@ -62835,7 +62835,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.86152923107147</v>
+        <v>1.86152911186218</v>
       </c>
       <c r="H2154" t="n">
         <v>35977989</v>
@@ -62864,7 +62864,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.86152923107147</v>
+        <v>1.86152911186218</v>
       </c>
       <c r="H2155" t="n">
         <v>22290014</v>
@@ -62893,7 +62893,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2156" t="n">
-        <v>1.89626586437225</v>
+        <v>1.89626574516296</v>
       </c>
       <c r="H2156" t="n">
         <v>21085975</v>
@@ -62922,7 +62922,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2157" t="n">
         <v>35756797</v>
@@ -62951,7 +62951,7 @@
         <v>2.15899991989136</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.92298638820648</v>
+        <v>1.92298626899719</v>
       </c>
       <c r="H2158" t="n">
         <v>16359113</v>
@@ -62980,7 +62980,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.99245977401733</v>
+        <v>1.99245965480804</v>
       </c>
       <c r="H2159" t="n">
         <v>39248301</v>
@@ -63096,7 +63096,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.13585996627808</v>
+        <v>2.1358597278595</v>
       </c>
       <c r="H2163" t="n">
         <v>33746318</v>
@@ -63212,7 +63212,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2167" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2167" t="n">
         <v>25601227</v>
@@ -63299,7 +63299,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G2170" t="n">
-        <v>2.07351207733154</v>
+        <v>2.07351183891296</v>
       </c>
       <c r="H2170" t="n">
         <v>26440425</v>
@@ -63328,7 +63328,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.06371450424194</v>
+        <v>2.06371426582336</v>
       </c>
       <c r="H2171" t="n">
         <v>26757191</v>
@@ -63357,7 +63357,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G2172" t="n">
-        <v>2.09666967391968</v>
+        <v>2.09666991233826</v>
       </c>
       <c r="H2172" t="n">
         <v>24912702</v>
@@ -63415,7 +63415,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2174" t="n">
-        <v>2.10913944244385</v>
+        <v>2.10913920402527</v>
       </c>
       <c r="H2174" t="n">
         <v>19724218</v>
@@ -63444,7 +63444,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.12339019775391</v>
+        <v>2.12339043617249</v>
       </c>
       <c r="H2175" t="n">
         <v>29130431</v>
@@ -63473,7 +63473,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.14476680755615</v>
+        <v>2.14476656913757</v>
       </c>
       <c r="H2176" t="n">
         <v>16678363</v>
@@ -63560,7 +63560,7 @@
         <v>2.41899991035461</v>
       </c>
       <c r="G2179" t="n">
-        <v>2.15456414222717</v>
+        <v>2.15456390380859</v>
       </c>
       <c r="H2179" t="n">
         <v>23246952</v>
@@ -63618,7 +63618,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2181" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2181" t="n">
         <v>45523587</v>
@@ -63647,7 +63647,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G2182" t="n">
-        <v>1.9844434261322</v>
+        <v>1.98444354534149</v>
       </c>
       <c r="H2182" t="n">
         <v>44868347</v>
@@ -63705,7 +63705,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.94614410400391</v>
+        <v>1.9461442232132</v>
       </c>
       <c r="H2184" t="n">
         <v>18067908</v>
@@ -63734,7 +63734,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2185" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2185" t="n">
         <v>20351307</v>
@@ -63763,7 +63763,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.94079983234406</v>
+        <v>1.94080007076263</v>
       </c>
       <c r="H2186" t="n">
         <v>18512647</v>
@@ -63879,7 +63879,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G2190" t="n">
-        <v>1.79294657707214</v>
+        <v>1.79294645786285</v>
       </c>
       <c r="H2190" t="n">
         <v>24047004</v>
@@ -63995,7 +63995,7 @@
         <v>1.98450005054474</v>
       </c>
       <c r="G2194" t="n">
-        <v>1.7675621509552</v>
+        <v>1.76756203174591</v>
       </c>
       <c r="H2194" t="n">
         <v>23362020</v>
@@ -64140,7 +64140,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G2199" t="n">
-        <v>1.8428248167038</v>
+        <v>1.84282493591309</v>
       </c>
       <c r="H2199" t="n">
         <v>32985049</v>
@@ -64227,7 +64227,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.84549689292908</v>
+        <v>1.84549701213837</v>
       </c>
       <c r="H2202" t="n">
         <v>16439030</v>
@@ -64256,7 +64256,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.81521368026733</v>
+        <v>1.81521379947662</v>
       </c>
       <c r="H2203" t="n">
         <v>23581831</v>
@@ -64343,7 +64343,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2206" t="n">
         <v>19255054</v>
@@ -64372,7 +64372,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2207" t="n">
-        <v>1.80185329914093</v>
+        <v>1.80185341835022</v>
       </c>
       <c r="H2207" t="n">
         <v>12789945</v>
@@ -64401,7 +64401,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.67448568344116</v>
+        <v>1.67448556423187</v>
       </c>
       <c r="H2208" t="n">
         <v>53900944</v>
@@ -64430,7 +64430,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.71189439296722</v>
+        <v>1.71189427375793</v>
       </c>
       <c r="H2209" t="n">
         <v>35189302</v>
@@ -64546,7 +64546,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G2213" t="n">
-        <v>1.60055899620056</v>
+        <v>1.60055887699127</v>
       </c>
       <c r="H2213" t="n">
         <v>37765591</v>
@@ -64575,7 +64575,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.62727928161621</v>
+        <v>1.6272794008255</v>
       </c>
       <c r="H2214" t="n">
         <v>22594695</v>
@@ -64865,7 +64865,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.81343233585358</v>
+        <v>1.81343221664429</v>
       </c>
       <c r="H2224" t="n">
         <v>24725349</v>
@@ -65097,7 +65097,7 @@
         <v>2.05699992179871</v>
       </c>
       <c r="G2232" t="n">
-        <v>1.83213651180267</v>
+        <v>1.83213663101196</v>
       </c>
       <c r="H2232" t="n">
         <v>29472348</v>
@@ -65155,7 +65155,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2234" t="n">
-        <v>1.79027450084686</v>
+        <v>1.79027438163757</v>
       </c>
       <c r="H2234" t="n">
         <v>16876658</v>
@@ -65184,7 +65184,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.80185329914093</v>
+        <v>1.80185341835022</v>
       </c>
       <c r="H2235" t="n">
         <v>20529123</v>
@@ -65358,7 +65358,7 @@
         <v>1.99150002002716</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.77379679679871</v>
+        <v>1.773796916008</v>
       </c>
       <c r="H2241" t="n">
         <v>46698722</v>
@@ -65416,7 +65416,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2243" t="n">
-        <v>1.83926224708557</v>
+        <v>1.83926212787628</v>
       </c>
       <c r="H2243" t="n">
         <v>48994310</v>
@@ -65445,7 +65445,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G2244" t="n">
-        <v>1.80630683898926</v>
+        <v>1.80630695819855</v>
       </c>
       <c r="H2244" t="n">
         <v>29352657</v>
@@ -65474,7 +65474,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G2245" t="n">
-        <v>1.89003109931946</v>
+        <v>1.89003121852875</v>
       </c>
       <c r="H2245" t="n">
         <v>81646961</v>
@@ -65503,7 +65503,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.94970667362213</v>
+        <v>1.94970679283142</v>
       </c>
       <c r="H2246" t="n">
         <v>74141845</v>
@@ -65561,7 +65561,7 @@
         <v>2.16300010681152</v>
       </c>
       <c r="G2248" t="n">
-        <v>1.92654931545258</v>
+        <v>1.92654919624329</v>
       </c>
       <c r="H2248" t="n">
         <v>30842480</v>
@@ -65590,7 +65590,7 @@
         <v>2.16700005531311</v>
       </c>
       <c r="G2249" t="n">
-        <v>1.9301118850708</v>
+        <v>1.93011200428009</v>
       </c>
       <c r="H2249" t="n">
         <v>30050128</v>
@@ -65619,7 +65619,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2250" t="n">
-        <v>1.94525349140167</v>
+        <v>1.94525361061096</v>
       </c>
       <c r="H2250" t="n">
         <v>26979522</v>
@@ -65648,7 +65648,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2251" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2251" t="n">
         <v>53288446</v>
@@ -65677,7 +65677,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2252" t="n">
         <v>41701778</v>
@@ -65735,7 +65735,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2254" t="n">
-        <v>2.00314807891846</v>
+        <v>2.00314784049988</v>
       </c>
       <c r="H2254" t="n">
         <v>44091922</v>
@@ -65793,7 +65793,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2256" t="n">
-        <v>2.06994891166687</v>
+        <v>2.06994915008545</v>
       </c>
       <c r="H2256" t="n">
         <v>54666411</v>
@@ -65880,7 +65880,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2259" t="n">
-        <v>2.0530264377594</v>
+        <v>2.05302619934082</v>
       </c>
       <c r="H2259" t="n">
         <v>24934085</v>
@@ -65909,7 +65909,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2260" t="n">
-        <v>2.06371450424194</v>
+        <v>2.06371426582336</v>
       </c>
       <c r="H2260" t="n">
         <v>40038315</v>
@@ -65938,7 +65938,7 @@
         <v>2.33299994468689</v>
       </c>
       <c r="G2261" t="n">
-        <v>2.077965259552</v>
+        <v>2.07796549797058</v>
       </c>
       <c r="H2261" t="n">
         <v>34552742</v>
@@ -65967,7 +65967,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2262" t="n">
-        <v>2.10913944244385</v>
+        <v>2.10913920402527</v>
       </c>
       <c r="H2262" t="n">
         <v>21092827</v>
@@ -66170,7 +66170,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G2269" t="n">
-        <v>2.1652524471283</v>
+        <v>2.16525220870972</v>
       </c>
       <c r="H2269" t="n">
         <v>38389055</v>
@@ -66315,7 +66315,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G2274" t="n">
-        <v>2.26768112182617</v>
+        <v>2.26768088340759</v>
       </c>
       <c r="H2274" t="n">
         <v>31890329</v>
@@ -66431,7 +66431,7 @@
         <v>2.48699998855591</v>
       </c>
       <c r="G2278" t="n">
-        <v>2.21513056755066</v>
+        <v>2.21513080596924</v>
       </c>
       <c r="H2278" t="n">
         <v>18431422</v>
@@ -66518,7 +66518,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2281" t="n">
-        <v>2.29262018203735</v>
+        <v>2.29261994361877</v>
       </c>
       <c r="H2281" t="n">
         <v>22696347</v>
@@ -66547,7 +66547,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2282" t="n">
-        <v>2.31577777862549</v>
+        <v>2.31577801704407</v>
       </c>
       <c r="H2282" t="n">
         <v>26132220</v>
@@ -66634,7 +66634,7 @@
         <v>2.64299988746643</v>
       </c>
       <c r="G2285" t="n">
-        <v>2.35407710075378</v>
+        <v>2.35407733917236</v>
       </c>
       <c r="H2285" t="n">
         <v>60652789</v>
@@ -66721,7 +66721,7 @@
         <v>2.51099991798401</v>
       </c>
       <c r="G2288" t="n">
-        <v>2.23650717735291</v>
+        <v>2.23650693893433</v>
       </c>
       <c r="H2288" t="n">
         <v>15785363</v>
@@ -66750,7 +66750,7 @@
         <v>2.5090000629425</v>
       </c>
       <c r="G2289" t="n">
-        <v>2.23472571372986</v>
+        <v>2.23472595214844</v>
       </c>
       <c r="H2289" t="n">
         <v>11480911</v>
@@ -66924,7 +66924,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G2295" t="n">
-        <v>2.45294308662415</v>
+        <v>2.45294332504272</v>
       </c>
       <c r="H2295" t="n">
         <v>20214762</v>
@@ -67040,7 +67040,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G2299" t="n">
-        <v>2.31221532821655</v>
+        <v>2.31221508979797</v>
       </c>
       <c r="H2299" t="n">
         <v>74870654</v>
@@ -67098,7 +67098,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G2301" t="n">
-        <v>2.27658796310425</v>
+        <v>2.27658772468567</v>
       </c>
       <c r="H2301" t="n">
         <v>30195449</v>
@@ -67127,7 +67127,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G2302" t="n">
-        <v>2.25164890289307</v>
+        <v>2.25164866447449</v>
       </c>
       <c r="H2302" t="n">
         <v>24626119</v>
@@ -67156,7 +67156,7 @@
         <v>2.51300001144409</v>
       </c>
       <c r="G2303" t="n">
-        <v>2.23828864097595</v>
+        <v>2.23828840255737</v>
       </c>
       <c r="H2303" t="n">
         <v>20104873</v>
@@ -67214,7 +67214,7 @@
         <v>2.48300004005432</v>
       </c>
       <c r="G2305" t="n">
-        <v>2.21156811714172</v>
+        <v>2.21156787872314</v>
       </c>
       <c r="H2305" t="n">
         <v>27751479</v>
@@ -67243,7 +67243,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G2306" t="n">
-        <v>2.14832925796509</v>
+        <v>2.14832949638367</v>
       </c>
       <c r="H2306" t="n">
         <v>43140551</v>
@@ -67272,7 +67272,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2307" t="n">
-        <v>2.12160873413086</v>
+        <v>2.12160897254944</v>
       </c>
       <c r="H2307" t="n">
         <v>24111895</v>
@@ -67504,7 +67504,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2315" t="n">
-        <v>2.04411959648132</v>
+        <v>2.04411935806274</v>
       </c>
       <c r="H2315" t="n">
         <v>24791375</v>
@@ -67562,7 +67562,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G2317" t="n">
-        <v>2.04768204689026</v>
+        <v>2.04768228530884</v>
       </c>
       <c r="H2317" t="n">
         <v>21357944</v>
@@ -67707,7 +67707,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G2322" t="n">
-        <v>2.05658888816833</v>
+        <v>2.05658912658691</v>
       </c>
       <c r="H2322" t="n">
         <v>15248097</v>
@@ -67794,7 +67794,7 @@
         <v>2.28099989891052</v>
       </c>
       <c r="G2325" t="n">
-        <v>2.03164958953857</v>
+        <v>2.03164982795715</v>
       </c>
       <c r="H2325" t="n">
         <v>20004250</v>
@@ -67823,7 +67823,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G2326" t="n">
-        <v>2.06816792488098</v>
+        <v>2.0681676864624</v>
       </c>
       <c r="H2326" t="n">
         <v>27029721</v>
@@ -67910,7 +67910,7 @@
         <v>2.20300006866455</v>
       </c>
       <c r="G2329" t="n">
-        <v>1.96217656135559</v>
+        <v>1.9621764421463</v>
       </c>
       <c r="H2329" t="n">
         <v>165427959</v>
@@ -67939,7 +67939,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2330" t="n">
-        <v>2.00314807891846</v>
+        <v>2.00314784049988</v>
       </c>
       <c r="H2330" t="n">
         <v>90357314</v>
@@ -67997,7 +67997,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2332" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2332" t="n">
         <v>49106059</v>
@@ -68055,7 +68055,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2334" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2334" t="n">
         <v>47390121</v>
@@ -68200,7 +68200,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G2339" t="n">
-        <v>1.85440373420715</v>
+        <v>1.85440385341644</v>
       </c>
       <c r="H2339" t="n">
         <v>52881442</v>
@@ -68287,7 +68287,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2342" t="n">
-        <v>1.89626586437225</v>
+        <v>1.89626574516296</v>
       </c>
       <c r="H2342" t="n">
         <v>54335801</v>
@@ -68316,7 +68316,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.93278384208679</v>
+        <v>1.93278396129608</v>
       </c>
       <c r="H2343" t="n">
         <v>54028041</v>
@@ -68345,7 +68345,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2344" t="n">
         <v>32171346</v>
@@ -68432,7 +68432,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2347" t="n">
-        <v>1.9684112071991</v>
+        <v>1.96841132640839</v>
       </c>
       <c r="H2347" t="n">
         <v>31365241</v>
@@ -68461,7 +68461,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2348" t="n">
-        <v>1.94525349140167</v>
+        <v>1.94525361061096</v>
       </c>
       <c r="H2348" t="n">
         <v>43704455</v>
@@ -68519,7 +68519,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G2350" t="n">
-        <v>1.95861351490021</v>
+        <v>1.9586136341095</v>
       </c>
       <c r="H2350" t="n">
         <v>35346168</v>
@@ -68548,7 +68548,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2351" t="n">
-        <v>1.9336746931076</v>
+        <v>1.93367457389832</v>
       </c>
       <c r="H2351" t="n">
         <v>29069827</v>
@@ -68635,7 +68635,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2354" t="n">
-        <v>1.89537525177002</v>
+        <v>1.89537537097931</v>
       </c>
       <c r="H2354" t="n">
         <v>33627039</v>
@@ -68664,7 +68664,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.72436392307281</v>
+        <v>1.72436380386353</v>
       </c>
       <c r="H2355" t="n">
         <v>85443225</v>
@@ -68838,7 +68838,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G2361" t="n">
-        <v>1.52128791809082</v>
+        <v>1.52128803730011</v>
       </c>
       <c r="H2361" t="n">
         <v>38867170</v>
@@ -68867,7 +68867,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G2362" t="n">
-        <v>1.56493151187897</v>
+        <v>1.56493139266968</v>
       </c>
       <c r="H2362" t="n">
         <v>50829326</v>
@@ -69041,7 +69041,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G2368" t="n">
-        <v>1.749302983284</v>
+        <v>1.74930310249329</v>
       </c>
       <c r="H2368" t="n">
         <v>65053471</v>
@@ -69128,7 +69128,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.82590186595917</v>
+        <v>1.82590174674988</v>
       </c>
       <c r="H2371" t="n">
         <v>29975796</v>
@@ -69186,7 +69186,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2373" t="n">
-        <v>1.8526223897934</v>
+        <v>1.85262227058411</v>
       </c>
       <c r="H2373" t="n">
         <v>37413416</v>
@@ -69215,7 +69215,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G2374" t="n">
-        <v>1.83302736282349</v>
+        <v>1.83302748203278</v>
       </c>
       <c r="H2374" t="n">
         <v>32042896</v>
@@ -69244,7 +69244,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G2375" t="n">
-        <v>1.82768321037292</v>
+        <v>1.82768332958221</v>
       </c>
       <c r="H2375" t="n">
         <v>38839501</v>
@@ -69273,7 +69273,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G2376" t="n">
-        <v>1.83837127685547</v>
+        <v>1.83837139606476</v>
       </c>
       <c r="H2376" t="n">
         <v>30420999</v>
@@ -69331,7 +69331,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G2378" t="n">
-        <v>1.93990933895111</v>
+        <v>1.9399094581604</v>
       </c>
       <c r="H2378" t="n">
         <v>64329397</v>
@@ -80183,6 +80183,35 @@
         <v>9820077</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>4.55100011825562</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>4.58599996566772</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>4.52299976348877</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>4.53700017929077</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>4.53700017929077</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>10131136</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -485,7 +485,7 @@
         <v>22.3245735168457</v>
       </c>
       <c r="G4" t="n">
-        <v>19.7946090698242</v>
+        <v>19.7946071624756</v>
       </c>
       <c r="H4" t="n">
         <v>808293</v>
@@ -601,7 +601,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.8786602020264</v>
+        <v>19.878662109375</v>
       </c>
       <c r="H8" t="n">
         <v>1620392</v>
@@ -630,7 +630,7 @@
         <v>22.1665782928467</v>
       </c>
       <c r="G9" t="n">
-        <v>19.65452003479</v>
+        <v>19.6545181274414</v>
       </c>
       <c r="H9" t="n">
         <v>916025</v>
@@ -659,7 +659,7 @@
         <v>22.1823787689209</v>
       </c>
       <c r="G10" t="n">
-        <v>19.6685276031494</v>
+        <v>19.668529510498</v>
       </c>
       <c r="H10" t="n">
         <v>887518</v>
@@ -688,7 +688,7 @@
         <v>20.9184246063232</v>
       </c>
       <c r="G11" t="n">
-        <v>18.547815322876</v>
+        <v>18.5478134155273</v>
       </c>
       <c r="H11" t="n">
         <v>1339292</v>
@@ -717,7 +717,7 @@
         <v>19.8440647125244</v>
       </c>
       <c r="G12" t="n">
-        <v>17.5952072143555</v>
+        <v>17.5952091217041</v>
       </c>
       <c r="H12" t="n">
         <v>1467001</v>
@@ -746,7 +746,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811977386475</v>
+        <v>17.5811958312988</v>
       </c>
       <c r="H13" t="n">
         <v>989105</v>
@@ -775,7 +775,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460279464722</v>
+        <v>15.7460289001465</v>
       </c>
       <c r="H14" t="n">
         <v>2077512</v>
@@ -804,7 +804,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.8214406967163</v>
+        <v>14.821439743042</v>
       </c>
       <c r="H15" t="n">
         <v>2435960</v>
@@ -862,7 +862,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552736282349</v>
+        <v>13.9552726745605</v>
       </c>
       <c r="H17" t="n">
         <v>354113</v>
@@ -949,7 +949,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087121963501</v>
+        <v>12.6087112426758</v>
       </c>
       <c r="H20" t="n">
         <v>1225889</v>
@@ -1123,7 +1123,7 @@
         <v>13.0530023574829</v>
       </c>
       <c r="G26" t="n">
-        <v>11.5737524032593</v>
+        <v>11.573751449585</v>
       </c>
       <c r="H26" t="n">
         <v>1877083</v>
@@ -1181,7 +1181,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H28" t="n">
         <v>1981662</v>
@@ -1239,7 +1239,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G30" t="n">
-        <v>7.08892250061035</v>
+        <v>7.08892202377319</v>
       </c>
       <c r="H30" t="n">
         <v>5755429</v>
@@ -1268,7 +1268,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G31" t="n">
-        <v>6.70832395553589</v>
+        <v>6.70832347869873</v>
       </c>
       <c r="H31" t="n">
         <v>7709298</v>
@@ -1297,7 +1297,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393510818481</v>
+        <v>6.74393558502197</v>
       </c>
       <c r="H32" t="n">
         <v>7100655</v>
@@ -1326,7 +1326,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.87747859954834</v>
+        <v>6.8774790763855</v>
       </c>
       <c r="H33" t="n">
         <v>7581026</v>
@@ -1355,7 +1355,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51181030273438</v>
+        <v>7.51180982589722</v>
       </c>
       <c r="H34" t="n">
         <v>6329665</v>
@@ -1413,7 +1413,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36045980453491</v>
+        <v>7.36046028137207</v>
       </c>
       <c r="H36" t="n">
         <v>4978216</v>
@@ -1471,7 +1471,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243886947632</v>
+        <v>7.91243934631348</v>
       </c>
       <c r="H38" t="n">
         <v>4762357</v>
@@ -1529,7 +1529,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H40" t="n">
         <v>5230684</v>
@@ -1587,7 +1587,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H42" t="n">
         <v>8046415</v>
@@ -1616,7 +1616,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H43" t="n">
         <v>5632607</v>
@@ -1732,7 +1732,7 @@
         <v>10.6884002685547</v>
       </c>
       <c r="G47" t="n">
-        <v>9.47712230682373</v>
+        <v>9.47712135314941</v>
       </c>
       <c r="H47" t="n">
         <v>6263628</v>
@@ -1761,7 +1761,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.0771427154541</v>
+        <v>8.07714366912842</v>
       </c>
       <c r="H48" t="n">
         <v>18012438</v>
@@ -1819,7 +1819,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811340332031</v>
+        <v>7.98811388015747</v>
       </c>
       <c r="H50" t="n">
         <v>5464353</v>
@@ -1877,7 +1877,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683204650879</v>
+        <v>8.58683300018311</v>
       </c>
       <c r="H52" t="n">
         <v>4362352</v>
@@ -1935,7 +1935,7 @@
         <v>9.26261138916016</v>
       </c>
       <c r="G54" t="n">
-        <v>8.21291255950928</v>
+        <v>8.21291351318359</v>
       </c>
       <c r="H54" t="n">
         <v>3721362</v>
@@ -1964,7 +1964,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.31752109527588</v>
+        <v>8.3175220489502</v>
       </c>
       <c r="H55" t="n">
         <v>4485559</v>
@@ -2080,7 +2080,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G59" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H59" t="n">
         <v>2418203</v>
@@ -2109,7 +2109,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218820571899</v>
+        <v>7.75218725204468</v>
       </c>
       <c r="H60" t="n">
         <v>3776976</v>
@@ -2138,7 +2138,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.34488010406494</v>
+        <v>7.3448805809021</v>
       </c>
       <c r="H61" t="n">
         <v>3010233</v>
@@ -2225,7 +2225,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870714187622</v>
+        <v>7.65870809555054</v>
       </c>
       <c r="H64" t="n">
         <v>2688899</v>
@@ -2283,7 +2283,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973592758179</v>
+        <v>6.89973640441895</v>
       </c>
       <c r="H66" t="n">
         <v>4271134</v>
@@ -2341,7 +2341,7 @@
         <v>7.61341381072998</v>
       </c>
       <c r="G68" t="n">
-        <v>6.75061225891113</v>
+        <v>6.75061273574829</v>
       </c>
       <c r="H68" t="n">
         <v>2618453</v>
@@ -2370,7 +2370,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365779876709</v>
+        <v>7.27365732192993</v>
       </c>
       <c r="H69" t="n">
         <v>3294930</v>
@@ -2399,7 +2399,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H70" t="n">
         <v>3239759</v>
@@ -2428,7 +2428,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G71" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H71" t="n">
         <v>3489116</v>
@@ -2457,7 +2457,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.8634729385376</v>
+        <v>7.86347436904907</v>
       </c>
       <c r="H72" t="n">
         <v>3751875</v>
@@ -2486,7 +2486,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09940052032471</v>
+        <v>8.09939956665039</v>
       </c>
       <c r="H73" t="n">
         <v>4017372</v>
@@ -2515,7 +2515,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86569976806641</v>
+        <v>7.86570072174072</v>
       </c>
       <c r="H74" t="n">
         <v>2931733</v>
@@ -2573,7 +2573,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H76" t="n">
         <v>3700496</v>
@@ -2689,7 +2689,7 @@
         <v>9.39816093444824</v>
       </c>
       <c r="G80" t="n">
-        <v>8.33310031890869</v>
+        <v>8.33310127258301</v>
       </c>
       <c r="H80" t="n">
         <v>1866023</v>
@@ -2747,7 +2747,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912082672119</v>
+        <v>8.62912178039551</v>
       </c>
       <c r="H82" t="n">
         <v>3841073</v>
@@ -2805,7 +2805,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H84" t="n">
         <v>6156371</v>
@@ -2834,7 +2834,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H85" t="n">
         <v>3915352</v>
@@ -2863,7 +2863,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G86" t="n">
-        <v>8.54009246826172</v>
+        <v>8.54009342193604</v>
       </c>
       <c r="H86" t="n">
         <v>4877613</v>
@@ -2892,7 +2892,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H87" t="n">
         <v>3783755</v>
@@ -2921,7 +2921,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G88" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H88" t="n">
         <v>2952497</v>
@@ -2950,7 +2950,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G89" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H89" t="n">
         <v>2726335</v>
@@ -2979,7 +2979,7 @@
         <v>9.36803913116455</v>
       </c>
       <c r="G90" t="n">
-        <v>8.30639266967773</v>
+        <v>8.30639171600342</v>
       </c>
       <c r="H90" t="n">
         <v>2595903</v>
@@ -3066,7 +3066,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H93" t="n">
         <v>3351378</v>
@@ -3095,7 +3095,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.26855373382568</v>
+        <v>8.2685546875</v>
       </c>
       <c r="H94" t="n">
         <v>2791506</v>
@@ -3124,7 +3124,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542102813721</v>
+        <v>8.39542007446289</v>
       </c>
       <c r="H95" t="n">
         <v>1782012</v>
@@ -3182,7 +3182,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G97" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H97" t="n">
         <v>1772130</v>
@@ -3211,7 +3211,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588752746582</v>
+        <v>7.98588848114014</v>
       </c>
       <c r="H98" t="n">
         <v>4712589</v>
@@ -3240,7 +3240,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701642990112</v>
       </c>
       <c r="H99" t="n">
         <v>2418605</v>
@@ -3327,7 +3327,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H102" t="n">
         <v>3679752</v>
@@ -3356,7 +3356,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G103" t="n">
-        <v>8.3976469039917</v>
+        <v>8.39764595031738</v>
       </c>
       <c r="H103" t="n">
         <v>2642334</v>
@@ -3530,7 +3530,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889585494995</v>
+        <v>7.77889633178711</v>
       </c>
       <c r="H109" t="n">
         <v>2101522</v>
@@ -3559,7 +3559,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701642990112</v>
       </c>
       <c r="H110" t="n">
         <v>2370853</v>
@@ -3646,7 +3646,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G113" t="n">
-        <v>8.67363548278809</v>
+        <v>8.6736364364624</v>
       </c>
       <c r="H113" t="n">
         <v>2693817</v>
@@ -3704,7 +3704,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325325012207</v>
+        <v>7.72325372695923</v>
       </c>
       <c r="H115" t="n">
         <v>4121823</v>
@@ -3733,7 +3733,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660612106323</v>
       </c>
       <c r="H116" t="n">
         <v>3931446</v>
@@ -3762,7 +3762,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808242797852</v>
+        <v>7.96808290481567</v>
       </c>
       <c r="H117" t="n">
         <v>3606977</v>
@@ -3820,7 +3820,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G119" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H119" t="n">
         <v>6157104</v>
@@ -3907,7 +3907,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76488971710205</v>
+        <v>8.76489067077637</v>
       </c>
       <c r="H122" t="n">
         <v>3417145</v>
@@ -3965,7 +3965,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933666229248</v>
+        <v>8.0593376159668</v>
       </c>
       <c r="H124" t="n">
         <v>4551998</v>
@@ -3994,7 +3994,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.5919361114502</v>
+        <v>7.59193563461304</v>
       </c>
       <c r="H125" t="n">
         <v>3711164</v>
@@ -4023,7 +4023,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78557395935059</v>
+        <v>7.78557348251343</v>
       </c>
       <c r="H126" t="n">
         <v>3269289</v>
@@ -4052,7 +4052,7 @@
         <v>8.86349010467529</v>
       </c>
       <c r="G127" t="n">
-        <v>7.85902261734009</v>
+        <v>7.85902214050293</v>
       </c>
       <c r="H127" t="n">
         <v>3013097</v>
@@ -4139,7 +4139,7 @@
         <v>9.60650730133057</v>
       </c>
       <c r="G130" t="n">
-        <v>8.51783657073975</v>
+        <v>8.51783561706543</v>
       </c>
       <c r="H130" t="n">
         <v>3045817</v>
@@ -4284,7 +4284,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.71147441864014</v>
+        <v>8.7114725112915</v>
       </c>
       <c r="H135" t="n">
         <v>4380711</v>
@@ -4313,7 +4313,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420257568359</v>
+        <v>9.03420352935791</v>
       </c>
       <c r="H136" t="n">
         <v>5039193</v>
@@ -4400,7 +4400,7 @@
         <v>10.3771362304688</v>
       </c>
       <c r="G139" t="n">
-        <v>9.20113182067871</v>
+        <v>9.20113277435303</v>
       </c>
       <c r="H139" t="n">
         <v>1660292</v>
@@ -4429,7 +4429,7 @@
         <v>10.5679111480713</v>
       </c>
       <c r="G140" t="n">
-        <v>9.37028789520264</v>
+        <v>9.37028694152832</v>
       </c>
       <c r="H140" t="n">
         <v>1710004</v>
@@ -4458,7 +4458,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G141" t="n">
-        <v>9.55947303771973</v>
+        <v>9.55947208404541</v>
       </c>
       <c r="H141" t="n">
         <v>3718667</v>
@@ -4603,7 +4603,7 @@
         <v>10.6934204101562</v>
       </c>
       <c r="G146" t="n">
-        <v>9.48157215118408</v>
+        <v>9.4815731048584</v>
       </c>
       <c r="H146" t="n">
         <v>2462145</v>
@@ -4632,7 +4632,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427219390869</v>
+        <v>9.78427124023438</v>
       </c>
       <c r="H147" t="n">
         <v>3288854</v>
@@ -4661,7 +4661,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G148" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H148" t="n">
         <v>11514563</v>
@@ -4690,7 +4690,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G149" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H149" t="n">
         <v>5327998</v>
@@ -4806,7 +4806,7 @@
         <v>9.37807941436768</v>
       </c>
       <c r="G153" t="n">
-        <v>8.31529426574707</v>
+        <v>8.31529521942139</v>
       </c>
       <c r="H153" t="n">
         <v>2495200</v>
@@ -4835,7 +4835,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228736877441</v>
+        <v>8.52228832244873</v>
       </c>
       <c r="H154" t="n">
         <v>2111524</v>
@@ -5009,7 +5009,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H160" t="n">
         <v>2723125</v>
@@ -5096,7 +5096,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H163" t="n">
         <v>1929655</v>
@@ -5125,7 +5125,7 @@
         <v>9.98303604125977</v>
       </c>
       <c r="G164" t="n">
-        <v>8.85169410705566</v>
+        <v>8.85169315338135</v>
       </c>
       <c r="H164" t="n">
         <v>1474788</v>
@@ -5154,7 +5154,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122665405273</v>
+        <v>9.26122570037842</v>
       </c>
       <c r="H165" t="n">
         <v>1784826</v>
@@ -5183,7 +5183,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G166" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H166" t="n">
         <v>2357597</v>
@@ -5241,7 +5241,7 @@
         <v>10.442400932312</v>
       </c>
       <c r="G168" t="n">
-        <v>9.25899982452393</v>
+        <v>9.25900077819824</v>
       </c>
       <c r="H168" t="n">
         <v>1567170</v>
@@ -5328,7 +5328,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548873901367</v>
+        <v>9.14548778533936</v>
       </c>
       <c r="H171" t="n">
         <v>1904678</v>
@@ -5386,7 +5386,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H173" t="n">
         <v>2380805</v>
@@ -5415,7 +5415,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.27235507965088</v>
+        <v>9.2723560333252</v>
       </c>
       <c r="H174" t="n">
         <v>1895264</v>
@@ -5502,7 +5502,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G177" t="n">
-        <v>9.23451805114746</v>
+        <v>9.23451900482178</v>
       </c>
       <c r="H177" t="n">
         <v>2950107</v>
@@ -5531,7 +5531,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G178" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H178" t="n">
         <v>1678053</v>
@@ -5647,7 +5647,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G182" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H182" t="n">
         <v>2932072</v>
@@ -5676,7 +5676,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359874725342</v>
+        <v>7.94359827041626</v>
       </c>
       <c r="H183" t="n">
         <v>4194583</v>
@@ -5763,7 +5763,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463376998901</v>
+        <v>7.89463329315186</v>
       </c>
       <c r="H186" t="n">
         <v>1967156</v>
@@ -5850,7 +5850,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798759460449</v>
+        <v>7.90798664093018</v>
       </c>
       <c r="H189" t="n">
         <v>3574353</v>
@@ -5908,7 +5908,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.7388334274292</v>
+        <v>7.73883247375488</v>
       </c>
       <c r="H191" t="n">
         <v>2882632</v>
@@ -5966,7 +5966,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G193" t="n">
-        <v>8.38429164886475</v>
+        <v>8.38429260253906</v>
       </c>
       <c r="H193" t="n">
         <v>3268951</v>
@@ -6024,7 +6024,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H195" t="n">
         <v>3058208</v>
@@ -6053,7 +6053,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G196" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H196" t="n">
         <v>2921152</v>
@@ -6111,7 +6111,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473293304443</v>
+        <v>8.66473388671875</v>
       </c>
       <c r="H198" t="n">
         <v>3635783</v>
@@ -6256,7 +6256,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H203" t="n">
         <v>2739605</v>
@@ -6285,7 +6285,7 @@
         <v>10.3696060180664</v>
       </c>
       <c r="G204" t="n">
-        <v>9.19445610046387</v>
+        <v>9.19445514678955</v>
       </c>
       <c r="H204" t="n">
         <v>2291727</v>
@@ -6314,7 +6314,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H205" t="n">
         <v>2047802</v>
@@ -6459,7 +6459,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G210" t="n">
-        <v>9.31464290618896</v>
+        <v>9.31464385986328</v>
       </c>
       <c r="H210" t="n">
         <v>2902413</v>
@@ -6488,7 +6488,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H211" t="n">
         <v>10102433</v>
@@ -6546,7 +6546,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H213" t="n">
         <v>3655602</v>
@@ -6720,7 +6720,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G219" t="n">
-        <v>8.38429164886475</v>
+        <v>8.38429260253906</v>
       </c>
       <c r="H219" t="n">
         <v>2139887</v>
@@ -6749,7 +6749,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G220" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H220" t="n">
         <v>2461590</v>
@@ -6778,7 +6778,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G221" t="n">
-        <v>8.73373031616211</v>
+        <v>8.73373126983643</v>
       </c>
       <c r="H221" t="n">
         <v>7014824</v>
@@ -6865,7 +6865,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H224" t="n">
         <v>2930403</v>
@@ -6923,7 +6923,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072246551514</v>
+        <v>8.94072341918945</v>
       </c>
       <c r="H226" t="n">
         <v>2515113</v>
@@ -6981,7 +6981,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G228" t="n">
-        <v>8.67363548278809</v>
+        <v>8.6736364364624</v>
       </c>
       <c r="H228" t="n">
         <v>3095637</v>
@@ -7039,7 +7039,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G230" t="n">
-        <v>8.9451732635498</v>
+        <v>8.94517421722412</v>
       </c>
       <c r="H230" t="n">
         <v>2705648</v>
@@ -7097,7 +7097,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G232" t="n">
-        <v>9.16329479217529</v>
+        <v>9.16329383850098</v>
       </c>
       <c r="H232" t="n">
         <v>2155204</v>
@@ -7126,7 +7126,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G233" t="n">
-        <v>8.92514228820801</v>
+        <v>8.92514324188232</v>
       </c>
       <c r="H233" t="n">
         <v>1340077</v>
@@ -7155,7 +7155,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G234" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H234" t="n">
         <v>2193109</v>
@@ -7242,7 +7242,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640228271484</v>
+        <v>9.72640323638916</v>
       </c>
       <c r="H237" t="n">
         <v>6656648</v>
@@ -7329,7 +7329,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.182674407959</v>
+        <v>10.1826753616333</v>
       </c>
       <c r="H240" t="n">
         <v>4126096</v>
@@ -7387,7 +7387,7 @@
         <v>11.4088249206543</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1159038543701</v>
+        <v>10.1159029006958</v>
       </c>
       <c r="H242" t="n">
         <v>4919856</v>
@@ -7474,7 +7474,7 @@
         <v>11.8230066299438</v>
       </c>
       <c r="G245" t="n">
-        <v>10.4831476211548</v>
+        <v>10.4831466674805</v>
       </c>
       <c r="H245" t="n">
         <v>7748349</v>
@@ -7532,7 +7532,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788536071777</v>
+        <v>10.5788545608521</v>
       </c>
       <c r="H247" t="n">
         <v>3112020</v>
@@ -7648,7 +7648,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G251" t="n">
-        <v>10.9883871078491</v>
+        <v>10.9883861541748</v>
       </c>
       <c r="H251" t="n">
         <v>3493539</v>
@@ -7677,7 +7677,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G252" t="n">
-        <v>11.2844085693359</v>
+        <v>11.2844076156616</v>
       </c>
       <c r="H252" t="n">
         <v>3211844</v>
@@ -7706,7 +7706,7 @@
         <v>12.8772878646851</v>
       </c>
       <c r="G253" t="n">
-        <v>11.417950630188</v>
+        <v>11.4179496765137</v>
       </c>
       <c r="H253" t="n">
         <v>1908982</v>
@@ -7764,7 +7764,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295513153076</v>
+        <v>11.7295522689819</v>
       </c>
       <c r="H255" t="n">
         <v>2571001</v>
@@ -7822,7 +7822,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076108932495</v>
+        <v>11.9076099395752</v>
       </c>
       <c r="H257" t="n">
         <v>1775884</v>
@@ -7909,7 +7909,7 @@
         <v>13.9817733764648</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3972682952881</v>
+        <v>12.3972692489624</v>
       </c>
       <c r="H260" t="n">
         <v>3761116</v>
@@ -7938,7 +7938,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195261001587</v>
+        <v>12.4195251464844</v>
       </c>
       <c r="H261" t="n">
         <v>2771934</v>
@@ -7967,7 +7967,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858243942261</v>
+        <v>12.1858253479004</v>
       </c>
       <c r="H262" t="n">
         <v>2214682</v>
@@ -8112,7 +8112,7 @@
         <v>12.8647365570068</v>
       </c>
       <c r="G267" t="n">
-        <v>11.4068212509155</v>
+        <v>11.4068222045898</v>
       </c>
       <c r="H267" t="n">
         <v>2415292</v>
@@ -8199,7 +8199,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G270" t="n">
-        <v>11.2844085693359</v>
+        <v>11.2844076156616</v>
       </c>
       <c r="H270" t="n">
         <v>3414444</v>
@@ -8228,7 +8228,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619939804077</v>
+        <v>11.1619920730591</v>
       </c>
       <c r="H271" t="n">
         <v>2083536</v>
@@ -8286,7 +8286,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351257324219</v>
+        <v>11.0351266860962</v>
       </c>
       <c r="H273" t="n">
         <v>2426178</v>
@@ -8344,7 +8344,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963228225708</v>
+        <v>11.7963237762451</v>
       </c>
       <c r="H275" t="n">
         <v>5968291</v>
@@ -8402,7 +8402,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960092544556</v>
+        <v>11.5960083007812</v>
       </c>
       <c r="H277" t="n">
         <v>1743449</v>
@@ -8518,7 +8518,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G281" t="n">
-        <v>10.2383193969727</v>
+        <v>10.2383184432983</v>
       </c>
       <c r="H281" t="n">
         <v>3878344</v>
@@ -8547,7 +8547,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141502380371</v>
+        <v>10.4141492843628</v>
       </c>
       <c r="H282" t="n">
         <v>2834757</v>
@@ -8576,7 +8576,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.251672744751</v>
+        <v>10.2516717910767</v>
       </c>
       <c r="H283" t="n">
         <v>3104757</v>
@@ -8663,7 +8663,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.3985710144043</v>
+        <v>10.39857006073</v>
       </c>
       <c r="H286" t="n">
         <v>2660739</v>
@@ -8750,7 +8750,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651838302612</v>
+        <v>10.3651847839355</v>
       </c>
       <c r="H289" t="n">
         <v>3308303</v>
@@ -8837,7 +8837,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H292" t="n">
         <v>2600664</v>
@@ -8895,7 +8895,7 @@
         <v>11.6874570846558</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3629589080811</v>
+        <v>10.3629579544067</v>
       </c>
       <c r="H294" t="n">
         <v>2084853</v>
@@ -9011,7 +9011,7 @@
         <v>10.5754413604736</v>
       </c>
       <c r="G298" t="n">
-        <v>9.37696361541748</v>
+        <v>9.3769645690918</v>
       </c>
       <c r="H298" t="n">
         <v>3692492</v>
@@ -9098,7 +9098,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486450195312</v>
+        <v>9.45486354827881</v>
       </c>
       <c r="H301" t="n">
         <v>3459059</v>
@@ -9127,7 +9127,7 @@
         <v>10.6984405517578</v>
       </c>
       <c r="G302" t="n">
-        <v>9.48602485656738</v>
+        <v>9.48602390289307</v>
       </c>
       <c r="H302" t="n">
         <v>2707699</v>
@@ -9185,7 +9185,7 @@
         <v>10.4675025939941</v>
       </c>
       <c r="G304" t="n">
-        <v>9.28125858306885</v>
+        <v>9.28125762939453</v>
       </c>
       <c r="H304" t="n">
         <v>3507793</v>
@@ -9330,7 +9330,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520614624023</v>
+        <v>8.96520709991455</v>
       </c>
       <c r="H309" t="n">
         <v>3858069</v>
@@ -9359,7 +9359,7 @@
         <v>10.218994140625</v>
       </c>
       <c r="G310" t="n">
-        <v>9.06091117858887</v>
+        <v>9.06091213226318</v>
       </c>
       <c r="H310" t="n">
         <v>3308377</v>
@@ -9446,7 +9446,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G313" t="n">
-        <v>9.01639652252197</v>
+        <v>9.01639747619629</v>
       </c>
       <c r="H313" t="n">
         <v>2624769</v>
@@ -9475,7 +9475,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539390563965</v>
+        <v>9.08539485931396</v>
       </c>
       <c r="H314" t="n">
         <v>3039918</v>
@@ -9504,7 +9504,7 @@
         <v>10.1336479187012</v>
       </c>
       <c r="G315" t="n">
-        <v>8.98523807525635</v>
+        <v>8.98523712158203</v>
       </c>
       <c r="H315" t="n">
         <v>3230495</v>
@@ -9591,7 +9591,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H318" t="n">
         <v>3081207</v>
@@ -9620,7 +9620,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G319" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H319" t="n">
         <v>5837585</v>
@@ -9649,7 +9649,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G320" t="n">
-        <v>9.46154117584229</v>
+        <v>9.4615421295166</v>
       </c>
       <c r="H320" t="n">
         <v>4855845</v>
@@ -9736,7 +9736,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981853485107</v>
+        <v>9.77981948852539</v>
       </c>
       <c r="H323" t="n">
         <v>5715259</v>
@@ -9765,7 +9765,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G324" t="n">
-        <v>9.49047470092773</v>
+        <v>9.49047565460205</v>
       </c>
       <c r="H324" t="n">
         <v>4124738</v>
@@ -9794,7 +9794,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G325" t="n">
-        <v>9.51050758361816</v>
+        <v>9.51050662994385</v>
       </c>
       <c r="H325" t="n">
         <v>3181766</v>
@@ -9823,7 +9823,7 @@
         <v>10.7310733795166</v>
       </c>
       <c r="G326" t="n">
-        <v>9.51495933532715</v>
+        <v>9.51495838165283</v>
       </c>
       <c r="H326" t="n">
         <v>2539231</v>
@@ -9881,7 +9881,7 @@
         <v>10.5227270126343</v>
       </c>
       <c r="G328" t="n">
-        <v>9.33022308349609</v>
+        <v>9.33022403717041</v>
       </c>
       <c r="H328" t="n">
         <v>2488647</v>
@@ -9910,7 +9910,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H329" t="n">
         <v>3030394</v>
@@ -9939,7 +9939,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G330" t="n">
-        <v>9.12990951538086</v>
+        <v>9.12990856170654</v>
       </c>
       <c r="H330" t="n">
         <v>3092166</v>
@@ -10084,7 +10084,7 @@
         <v>9.7671594619751</v>
       </c>
       <c r="G335" t="n">
-        <v>8.66028213500977</v>
+        <v>8.66028118133545</v>
       </c>
       <c r="H335" t="n">
         <v>6899556</v>
@@ -10171,7 +10171,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.20335865020752</v>
+        <v>9.2033576965332</v>
       </c>
       <c r="H338" t="n">
         <v>3676909</v>
@@ -10316,7 +10316,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H343" t="n">
         <v>4027196</v>
@@ -10606,7 +10606,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G353" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H353" t="n">
         <v>3851850</v>
@@ -10635,7 +10635,7 @@
         <v>9.80481243133545</v>
       </c>
       <c r="G354" t="n">
-        <v>8.69366836547852</v>
+        <v>8.6936674118042</v>
       </c>
       <c r="H354" t="n">
         <v>2634747</v>
@@ -10693,7 +10693,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H356" t="n">
         <v>1939986</v>
@@ -10722,7 +10722,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G357" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H357" t="n">
         <v>2035124</v>
@@ -10809,7 +10809,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H360" t="n">
         <v>1852849</v>
@@ -10896,7 +10896,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033975601196</v>
+        <v>7.9903392791748</v>
       </c>
       <c r="H363" t="n">
         <v>4201110</v>
@@ -11012,7 +11012,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215579986572</v>
+        <v>7.73215627670288</v>
       </c>
       <c r="H367" t="n">
         <v>4573774</v>
@@ -11041,7 +11041,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H368" t="n">
         <v>4145288</v>
@@ -11157,7 +11157,7 @@
         <v>8.88106060028076</v>
       </c>
       <c r="G372" t="n">
-        <v>7.8746018409729</v>
+        <v>7.87460136413574</v>
       </c>
       <c r="H372" t="n">
         <v>3226298</v>
@@ -11186,7 +11186,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H373" t="n">
         <v>5046714</v>
@@ -11331,7 +11331,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G378" t="n">
-        <v>7.18017673492432</v>
+        <v>7.18017721176147</v>
       </c>
       <c r="H378" t="n">
         <v>2433304</v>
@@ -11360,7 +11360,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H379" t="n">
         <v>2182310</v>
@@ -11389,7 +11389,7 @@
         <v>8.07779979705811</v>
       </c>
       <c r="G380" t="n">
-        <v>7.16237115859985</v>
+        <v>7.16237163543701</v>
       </c>
       <c r="H380" t="n">
         <v>2966514</v>
@@ -11418,7 +11418,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914266586304</v>
+        <v>7.22914218902588</v>
       </c>
       <c r="H381" t="n">
         <v>2924827</v>
@@ -11447,7 +11447,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817245483398</v>
+        <v>7.31817150115967</v>
       </c>
       <c r="H382" t="n">
         <v>2594435</v>
@@ -11476,7 +11476,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H383" t="n">
         <v>2583014</v>
@@ -11534,7 +11534,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055463790894</v>
+        <v>7.42055559158325</v>
       </c>
       <c r="H385" t="n">
         <v>3239198</v>
@@ -11563,7 +11563,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.6965446472168</v>
+        <v>7.69654512405396</v>
       </c>
       <c r="H386" t="n">
         <v>4250748</v>
@@ -11592,7 +11592,7 @@
         <v>8.44428825378418</v>
       </c>
       <c r="G387" t="n">
-        <v>7.48732662200928</v>
+        <v>7.48732709884644</v>
       </c>
       <c r="H387" t="n">
         <v>4117666</v>
@@ -11708,7 +11708,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390846252441</v>
+        <v>7.43390893936157</v>
       </c>
       <c r="H391" t="n">
         <v>1190917</v>
@@ -11737,7 +11737,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H392" t="n">
         <v>4462543</v>
@@ -11766,7 +11766,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G393" t="n">
-        <v>7.7455096244812</v>
+        <v>7.74551010131836</v>
       </c>
       <c r="H393" t="n">
         <v>2051870</v>
@@ -11824,7 +11824,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.85679721832275</v>
+        <v>7.85679578781128</v>
       </c>
       <c r="H395" t="n">
         <v>2325966</v>
@@ -11853,7 +11853,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H396" t="n">
         <v>3714587</v>
@@ -11911,7 +11911,7 @@
         <v>8.514573097229</v>
       </c>
       <c r="G398" t="n">
-        <v>7.54964637756348</v>
+        <v>7.54964685440063</v>
       </c>
       <c r="H398" t="n">
         <v>1501586</v>
@@ -11940,7 +11940,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842311859131</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H399" t="n">
         <v>1479093</v>
@@ -11969,7 +11969,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196756362915</v>
+        <v>7.61196708679199</v>
       </c>
       <c r="H400" t="n">
         <v>2662388</v>
@@ -12056,7 +12056,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416151046753</v>
+        <v>7.59416103363037</v>
       </c>
       <c r="H403" t="n">
         <v>2870111</v>
@@ -12085,7 +12085,7 @@
         <v>8.6953067779541</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70989847183228</v>
+        <v>7.70989894866943</v>
       </c>
       <c r="H404" t="n">
         <v>2592503</v>
@@ -12143,7 +12143,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H406" t="n">
         <v>2779239</v>
@@ -12172,7 +12172,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757966995239</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H407" t="n">
         <v>1870136</v>
@@ -12259,7 +12259,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428636550903</v>
+        <v>7.67428731918335</v>
       </c>
       <c r="H410" t="n">
         <v>1678906</v>
@@ -12375,7 +12375,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249792098999</v>
+        <v>7.24249744415283</v>
       </c>
       <c r="H414" t="n">
         <v>3391728</v>
@@ -12404,7 +12404,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701210021973</v>
+        <v>7.28701162338257</v>
       </c>
       <c r="H415" t="n">
         <v>1909890</v>
@@ -12433,7 +12433,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G416" t="n">
-        <v>7.26475477218628</v>
+        <v>7.26475429534912</v>
       </c>
       <c r="H416" t="n">
         <v>2058975</v>
@@ -12520,7 +12520,7 @@
         <v>8.08281993865967</v>
       </c>
       <c r="G419" t="n">
-        <v>7.16682195663452</v>
+        <v>7.16682243347168</v>
       </c>
       <c r="H419" t="n">
         <v>1874275</v>
@@ -12578,7 +12578,7 @@
         <v>7.84184217453003</v>
       </c>
       <c r="G421" t="n">
-        <v>6.95315361022949</v>
+        <v>6.95315408706665</v>
       </c>
       <c r="H421" t="n">
         <v>2449535</v>
@@ -12607,7 +12607,7 @@
         <v>7.61592388153076</v>
       </c>
       <c r="G422" t="n">
-        <v>6.75283861160278</v>
+        <v>6.75283813476562</v>
       </c>
       <c r="H422" t="n">
         <v>5344638</v>
@@ -12636,7 +12636,7 @@
         <v>7.70127105712891</v>
       </c>
       <c r="G423" t="n">
-        <v>6.82851362228394</v>
+        <v>6.82851314544678</v>
       </c>
       <c r="H423" t="n">
         <v>3972357</v>
@@ -12665,7 +12665,7 @@
         <v>7.68621015548706</v>
       </c>
       <c r="G424" t="n">
-        <v>6.8151593208313</v>
+        <v>6.81515884399414</v>
       </c>
       <c r="H424" t="n">
         <v>2199628</v>
@@ -12723,7 +12723,7 @@
         <v>7.40004777908325</v>
       </c>
       <c r="G426" t="n">
-        <v>6.56142663955688</v>
+        <v>6.56142616271973</v>
       </c>
       <c r="H426" t="n">
         <v>1915267</v>
@@ -12752,7 +12752,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.9397988319397</v>
+        <v>6.93979835510254</v>
       </c>
       <c r="H427" t="n">
         <v>6403078</v>
@@ -12781,7 +12781,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857557296753</v>
+        <v>6.86857604980469</v>
       </c>
       <c r="H428" t="n">
         <v>3961179</v>
@@ -12897,7 +12897,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469091415405</v>
+        <v>7.22469139099121</v>
       </c>
       <c r="H432" t="n">
         <v>2571750</v>
@@ -12926,7 +12926,7 @@
         <v>7.96233081817627</v>
       </c>
       <c r="G433" t="n">
-        <v>7.05998849868774</v>
+        <v>7.05998802185059</v>
       </c>
       <c r="H433" t="n">
         <v>2066064</v>
@@ -13042,7 +13042,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409860610962</v>
+        <v>7.55409908294678</v>
       </c>
       <c r="H437" t="n">
         <v>2971867</v>
@@ -13071,7 +13071,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.4739727973938</v>
+        <v>7.47397232055664</v>
       </c>
       <c r="H438" t="n">
         <v>2774137</v>
@@ -13129,7 +13129,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H440" t="n">
         <v>3440039</v>
@@ -13158,7 +13158,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538429260254</v>
       </c>
       <c r="H441" t="n">
         <v>3163095</v>
@@ -13216,7 +13216,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H443" t="n">
         <v>2311936</v>
@@ -13448,7 +13448,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692350387573</v>
+        <v>7.93692302703857</v>
       </c>
       <c r="H451" t="n">
         <v>4589432</v>
@@ -13477,7 +13477,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504360198975</v>
+        <v>8.15504264831543</v>
       </c>
       <c r="H452" t="n">
         <v>4598808</v>
@@ -13767,7 +13767,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H462" t="n">
         <v>5765617</v>
@@ -13796,7 +13796,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.42945718765259</v>
+        <v>7.42945766448975</v>
       </c>
       <c r="H463" t="n">
         <v>3847044</v>
@@ -13825,7 +13825,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H464" t="n">
         <v>4793014</v>
@@ -13883,7 +13883,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H466" t="n">
         <v>9145143</v>
@@ -13912,7 +13912,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538429260254</v>
       </c>
       <c r="H467" t="n">
         <v>3470929</v>
@@ -13970,7 +13970,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479198455811</v>
+        <v>7.99479103088379</v>
       </c>
       <c r="H469" t="n">
         <v>8252776</v>
@@ -14057,7 +14057,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.54677104949951</v>
+        <v>8.5467700958252</v>
       </c>
       <c r="H472" t="n">
         <v>5904097</v>
@@ -14115,7 +14115,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H474" t="n">
         <v>5603952</v>
@@ -14144,7 +14144,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H475" t="n">
         <v>5013333</v>
@@ -14173,7 +14173,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H476" t="n">
         <v>3307360</v>
@@ -14231,7 +14231,7 @@
         <v>9.49354839324951</v>
       </c>
       <c r="G478" t="n">
-        <v>8.4176778793335</v>
+        <v>8.41767883300781</v>
       </c>
       <c r="H478" t="n">
         <v>4520776</v>
@@ -14289,7 +14289,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G480" t="n">
-        <v>7.78557395935059</v>
+        <v>7.78557348251343</v>
       </c>
       <c r="H480" t="n">
         <v>11572956</v>
@@ -14318,7 +14318,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757966995239</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H481" t="n">
         <v>6391732</v>
@@ -14347,7 +14347,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G482" t="n">
-        <v>7.62532234191895</v>
+        <v>7.62532186508179</v>
       </c>
       <c r="H482" t="n">
         <v>3509049</v>
@@ -14376,7 +14376,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G483" t="n">
-        <v>7.62532234191895</v>
+        <v>7.62532186508179</v>
       </c>
       <c r="H483" t="n">
         <v>4716149</v>
@@ -14405,7 +14405,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H484" t="n">
         <v>3256857</v>
@@ -14463,7 +14463,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576219558716</v>
       </c>
       <c r="H486" t="n">
         <v>2564414</v>
@@ -14492,7 +14492,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344244003296</v>
+        <v>7.84344148635864</v>
       </c>
       <c r="H487" t="n">
         <v>2436747</v>
@@ -14521,7 +14521,7 @@
         <v>8.60494041442871</v>
       </c>
       <c r="G488" t="n">
-        <v>7.62977266311646</v>
+        <v>7.62977313995361</v>
       </c>
       <c r="H488" t="n">
         <v>3215714</v>
@@ -14579,7 +14579,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H490" t="n">
         <v>2757855</v>
@@ -14608,7 +14608,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G491" t="n">
-        <v>7.7455096244812</v>
+        <v>7.74551010131836</v>
       </c>
       <c r="H491" t="n">
         <v>3546514</v>
@@ -14695,7 +14695,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H494" t="n">
         <v>4714362</v>
@@ -14724,7 +14724,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H495" t="n">
         <v>2456311</v>
@@ -14840,7 +14840,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.6342248916626</v>
+        <v>7.63422441482544</v>
       </c>
       <c r="H499" t="n">
         <v>4090789</v>
@@ -14898,7 +14898,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H501" t="n">
         <v>2766406</v>
@@ -14985,7 +14985,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996280670166</v>
+        <v>7.74996185302734</v>
       </c>
       <c r="H504" t="n">
         <v>4120969</v>
@@ -15072,7 +15072,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G507" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H507" t="n">
         <v>4480449</v>
@@ -15130,7 +15130,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H509" t="n">
         <v>5719334</v>
@@ -15159,7 +15159,7 @@
         <v>9.61403846740723</v>
       </c>
       <c r="G510" t="n">
-        <v>8.52451324462891</v>
+        <v>8.52451419830322</v>
       </c>
       <c r="H510" t="n">
         <v>2445873</v>
@@ -15188,7 +15188,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109508514404</v>
+        <v>8.47109603881836</v>
       </c>
       <c r="H511" t="n">
         <v>3770392</v>
@@ -15217,7 +15217,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670623779297</v>
+        <v>8.50670719146729</v>
       </c>
       <c r="H512" t="n">
         <v>2875008</v>
@@ -15246,7 +15246,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.50225639343262</v>
+        <v>8.5022554397583</v>
       </c>
       <c r="H513" t="n">
         <v>2779890</v>
@@ -15275,7 +15275,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G514" t="n">
-        <v>8.73373031616211</v>
+        <v>8.73373126983643</v>
       </c>
       <c r="H514" t="n">
         <v>6368024</v>
@@ -15304,7 +15304,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H515" t="n">
         <v>3023534</v>
@@ -15391,7 +15391,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805625915527</v>
+        <v>8.65805530548096</v>
       </c>
       <c r="H518" t="n">
         <v>3468959</v>
@@ -15420,7 +15420,7 @@
         <v>10.1210966110229</v>
       </c>
       <c r="G519" t="n">
-        <v>8.97410869598389</v>
+        <v>8.9741096496582</v>
       </c>
       <c r="H519" t="n">
         <v>7443734</v>
@@ -15507,7 +15507,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G522" t="n">
-        <v>9.12990951538086</v>
+        <v>9.12990856170654</v>
       </c>
       <c r="H522" t="n">
         <v>5817803</v>
@@ -15536,7 +15536,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H523" t="n">
         <v>4786463</v>
@@ -15565,7 +15565,7 @@
         <v>10.1813411712646</v>
       </c>
       <c r="G524" t="n">
-        <v>9.02752590179443</v>
+        <v>9.02752685546875</v>
       </c>
       <c r="H524" t="n">
         <v>2378154</v>
@@ -15652,7 +15652,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G527" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H527" t="n">
         <v>5274403</v>
@@ -15681,7 +15681,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G528" t="n">
-        <v>9.16552066802979</v>
+        <v>9.1655216217041</v>
       </c>
       <c r="H528" t="n">
         <v>3314321</v>
@@ -15768,7 +15768,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833885192871</v>
+        <v>8.83833980560303</v>
       </c>
       <c r="H531" t="n">
         <v>2823997</v>
@@ -15826,7 +15826,7 @@
         <v>9.46593570709229</v>
       </c>
       <c r="G533" t="n">
-        <v>8.39319515228271</v>
+        <v>8.3931941986084</v>
       </c>
       <c r="H533" t="n">
         <v>3664518</v>
@@ -15855,7 +15855,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.41990375518799</v>
+        <v>8.41990566253662</v>
       </c>
       <c r="H534" t="n">
         <v>2981971</v>
@@ -15884,7 +15884,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.24852466583252</v>
+        <v>8.2485237121582</v>
       </c>
       <c r="H535" t="n">
         <v>4093310</v>
@@ -15913,7 +15913,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H536" t="n">
         <v>4347986</v>
@@ -16000,7 +16000,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660612106323</v>
       </c>
       <c r="H539" t="n">
         <v>5267752</v>
@@ -16029,7 +16029,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196756362915</v>
+        <v>7.61196708679199</v>
       </c>
       <c r="H540" t="n">
         <v>7866114</v>
@@ -16058,7 +16058,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519510269165</v>
+        <v>7.54519605636597</v>
       </c>
       <c r="H541" t="n">
         <v>2933056</v>
@@ -16116,7 +16116,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49623012542725</v>
+        <v>7.49622964859009</v>
       </c>
       <c r="H543" t="n">
         <v>5612249</v>
@@ -16232,7 +16232,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H547" t="n">
         <v>2390591</v>
@@ -16319,7 +16319,7 @@
         <v>8.83587837219238</v>
       </c>
       <c r="G550" t="n">
-        <v>7.83453893661499</v>
+        <v>7.83453989028931</v>
       </c>
       <c r="H550" t="n">
         <v>5628339</v>
@@ -16348,7 +16348,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.76331663131714</v>
+        <v>7.7633171081543</v>
       </c>
       <c r="H551" t="n">
         <v>3521552</v>
@@ -16377,7 +16377,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H552" t="n">
         <v>3398436</v>
@@ -16406,7 +16406,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G553" t="n">
-        <v>7.50068044662476</v>
+        <v>7.50068092346191</v>
       </c>
       <c r="H553" t="n">
         <v>4181215</v>
@@ -16435,7 +16435,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.5229377746582</v>
+        <v>7.52293872833252</v>
       </c>
       <c r="H554" t="n">
         <v>2585190</v>
@@ -16464,7 +16464,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368829727173</v>
+        <v>7.29368877410889</v>
       </c>
       <c r="H555" t="n">
         <v>4043829</v>
@@ -16522,7 +16522,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G557" t="n">
-        <v>7.50068044662476</v>
+        <v>7.50068092346191</v>
       </c>
       <c r="H557" t="n">
         <v>7379464</v>
@@ -16551,7 +16551,7 @@
         <v>8.56979656219482</v>
       </c>
       <c r="G558" t="n">
-        <v>7.59861183166504</v>
+        <v>7.5986123085022</v>
       </c>
       <c r="H558" t="n">
         <v>4269884</v>
@@ -16580,7 +16580,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663948059082</v>
+        <v>7.75663805007935</v>
       </c>
       <c r="H559" t="n">
         <v>3729295</v>
@@ -16609,7 +16609,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218820571899</v>
+        <v>7.75218725204468</v>
       </c>
       <c r="H560" t="n">
         <v>2796916</v>
@@ -16725,7 +16725,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936330795288</v>
+        <v>7.36936378479004</v>
       </c>
       <c r="H564" t="n">
         <v>2801339</v>
@@ -16754,7 +16754,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613481521606</v>
+        <v>7.43613433837891</v>
       </c>
       <c r="H565" t="n">
         <v>3258776</v>
@@ -16812,7 +16812,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826633453369</v>
+        <v>7.37826585769653</v>
       </c>
       <c r="H567" t="n">
         <v>3350760</v>
@@ -16899,7 +16899,7 @@
         <v>8.17820739746094</v>
       </c>
       <c r="G570" t="n">
-        <v>7.25139999389648</v>
+        <v>7.25140047073364</v>
       </c>
       <c r="H570" t="n">
         <v>3395514</v>
@@ -16986,7 +16986,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111692428589</v>
+        <v>7.07111740112305</v>
       </c>
       <c r="H573" t="n">
         <v>3487395</v>
@@ -17015,7 +17015,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H574" t="n">
         <v>1774619</v>
@@ -17131,7 +17131,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G578" t="n">
-        <v>6.98876571655273</v>
+        <v>6.98876523971558</v>
       </c>
       <c r="H578" t="n">
         <v>2910934</v>
@@ -17160,7 +17160,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744762420654</v>
+        <v>6.85744667053223</v>
       </c>
       <c r="H579" t="n">
         <v>4059831</v>
@@ -17218,7 +17218,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G581" t="n">
-        <v>7.08892250061035</v>
+        <v>7.08892202377319</v>
       </c>
       <c r="H581" t="n">
         <v>8326804</v>
@@ -17276,7 +17276,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469091415405</v>
+        <v>7.22469139099121</v>
       </c>
       <c r="H583" t="n">
         <v>5007935</v>
@@ -17305,7 +17305,7 @@
         <v>8.1079216003418</v>
       </c>
       <c r="G584" t="n">
-        <v>7.18907928466797</v>
+        <v>7.18907976150513</v>
       </c>
       <c r="H584" t="n">
         <v>3472564</v>
@@ -17334,7 +17334,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G585" t="n">
-        <v>7.18017673492432</v>
+        <v>7.18017721176147</v>
       </c>
       <c r="H585" t="n">
         <v>3344302</v>
@@ -17392,7 +17392,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842311859131</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H587" t="n">
         <v>5249327</v>
@@ -17421,7 +17421,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610431671143</v>
+        <v>7.41610383987427</v>
       </c>
       <c r="H588" t="n">
         <v>4009682</v>
@@ -17479,7 +17479,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G590" t="n">
-        <v>7.26475477218628</v>
+        <v>7.26475429534912</v>
       </c>
       <c r="H590" t="n">
         <v>7182347</v>
@@ -17508,7 +17508,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G591" t="n">
-        <v>6.98876571655273</v>
+        <v>6.98876523971558</v>
       </c>
       <c r="H591" t="n">
         <v>9716283</v>
@@ -17537,7 +17537,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766731262207</v>
+        <v>6.99766778945923</v>
       </c>
       <c r="H592" t="n">
         <v>4887233</v>
@@ -17595,7 +17595,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443929672241</v>
+        <v>7.06443881988525</v>
       </c>
       <c r="H594" t="n">
         <v>3740621</v>
@@ -17653,7 +17653,7 @@
         <v>7.92969799041748</v>
       </c>
       <c r="G596" t="n">
-        <v>7.03105354309082</v>
+        <v>7.03105306625366</v>
       </c>
       <c r="H596" t="n">
         <v>3230176</v>
@@ -17769,7 +17769,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H600" t="n">
         <v>11169423</v>
@@ -17798,7 +17798,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H601" t="n">
         <v>4478703</v>
@@ -17827,7 +17827,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G602" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H602" t="n">
         <v>3638485</v>
@@ -17914,7 +17914,7 @@
         <v>9.83242416381836</v>
       </c>
       <c r="G605" t="n">
-        <v>8.71815013885498</v>
+        <v>8.7181510925293</v>
       </c>
       <c r="H605" t="n">
         <v>23153988</v>
@@ -17943,7 +17943,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H606" t="n">
         <v>9737590</v>
@@ -17972,7 +17972,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G607" t="n">
-        <v>8.54009246826172</v>
+        <v>8.54009342193604</v>
       </c>
       <c r="H607" t="n">
         <v>5543597</v>
@@ -18001,7 +18001,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G608" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H608" t="n">
         <v>4747845</v>
@@ -18030,7 +18030,7 @@
         <v>10.0909738540649</v>
       </c>
       <c r="G609" t="n">
-        <v>8.94740009307861</v>
+        <v>8.9473991394043</v>
       </c>
       <c r="H609" t="n">
         <v>8237079</v>
@@ -18088,7 +18088,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37538909912109</v>
+        <v>8.37539005279541</v>
       </c>
       <c r="H611" t="n">
         <v>5678009</v>
@@ -18117,7 +18117,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065475463867</v>
+        <v>8.19065380096436</v>
       </c>
       <c r="H612" t="n">
         <v>4712315</v>
@@ -18146,7 +18146,7 @@
         <v>8.79822540283203</v>
       </c>
       <c r="G613" t="n">
-        <v>7.80115413665771</v>
+        <v>7.80115365982056</v>
       </c>
       <c r="H613" t="n">
         <v>4731371</v>
@@ -18262,7 +18262,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H617" t="n">
         <v>5676159</v>
@@ -18349,7 +18349,7 @@
         <v>9.31783485412598</v>
       </c>
       <c r="G620" t="n">
-        <v>8.26187801361084</v>
+        <v>8.26187896728516</v>
       </c>
       <c r="H620" t="n">
         <v>3046319</v>
@@ -18378,7 +18378,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H621" t="n">
         <v>4359962</v>
@@ -18407,7 +18407,7 @@
         <v>9.72448635101318</v>
       </c>
       <c r="G622" t="n">
-        <v>8.62244415283203</v>
+        <v>8.62244510650635</v>
       </c>
       <c r="H622" t="n">
         <v>5253374</v>
@@ -18436,7 +18436,7 @@
         <v>9.85250568389893</v>
       </c>
       <c r="G623" t="n">
-        <v>8.73595523834229</v>
+        <v>8.7359561920166</v>
       </c>
       <c r="H623" t="n">
         <v>3059274</v>
@@ -18465,7 +18465,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902599334717</v>
+        <v>8.56902694702148</v>
       </c>
       <c r="H624" t="n">
         <v>3124054</v>
@@ -18610,7 +18610,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G629" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H629" t="n">
         <v>1664123</v>
@@ -18813,7 +18813,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G636" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H636" t="n">
         <v>6312564</v>
@@ -18871,7 +18871,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H638" t="n">
         <v>2970699</v>
@@ -18929,7 +18929,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G640" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H640" t="n">
         <v>1067132</v>
@@ -18958,7 +18958,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.71147441864014</v>
+        <v>8.7114725112915</v>
       </c>
       <c r="H641" t="n">
         <v>2154097</v>
@@ -19045,7 +19045,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G644" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H644" t="n">
         <v>5210482</v>
@@ -19074,7 +19074,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009727478027</v>
+        <v>9.25009632110596</v>
       </c>
       <c r="H645" t="n">
         <v>6365259</v>
@@ -19103,7 +19103,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G646" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H646" t="n">
         <v>3391737</v>
@@ -19161,7 +19161,7 @@
         <v>10.0181789398193</v>
       </c>
       <c r="G648" t="n">
-        <v>8.88285350799561</v>
+        <v>8.88285446166992</v>
       </c>
       <c r="H648" t="n">
         <v>3244003</v>
@@ -19219,7 +19219,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G650" t="n">
-        <v>9.01639652252197</v>
+        <v>9.01639747619629</v>
       </c>
       <c r="H650" t="n">
         <v>2301830</v>
@@ -19277,7 +19277,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100505828857</v>
+        <v>9.12100601196289</v>
       </c>
       <c r="H652" t="n">
         <v>2816086</v>
@@ -19335,7 +19335,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G654" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H654" t="n">
         <v>2782854</v>
@@ -19422,7 +19422,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H657" t="n">
         <v>3819447</v>
@@ -19567,7 +19567,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H662" t="n">
         <v>5059956</v>
@@ -19625,7 +19625,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H664" t="n">
         <v>4580403</v>
@@ -19741,7 +19741,7 @@
         <v>11.200478553772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.93116760253906</v>
+        <v>9.93116855621338</v>
       </c>
       <c r="H668" t="n">
         <v>2563518</v>
@@ -19770,7 +19770,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139925003052</v>
+        <v>10.3139934539795</v>
       </c>
       <c r="H669" t="n">
         <v>8750009</v>
@@ -19973,7 +19973,7 @@
         <v>11.6046199798584</v>
       </c>
       <c r="G676" t="n">
-        <v>10.2895088195801</v>
+        <v>10.2895097732544</v>
       </c>
       <c r="H676" t="n">
         <v>1818429</v>
@@ -20002,7 +20002,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H677" t="n">
         <v>2314476</v>
@@ -20031,7 +20031,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G678" t="n">
-        <v>10.0157461166382</v>
+        <v>10.0157451629639</v>
       </c>
       <c r="H678" t="n">
         <v>2115163</v>
@@ -20118,7 +20118,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H681" t="n">
         <v>2245212</v>
@@ -20234,7 +20234,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99349021911621</v>
+        <v>9.99348926544189</v>
       </c>
       <c r="H685" t="n">
         <v>2940239</v>
@@ -20292,7 +20292,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694787979126</v>
+        <v>10.2694797515869</v>
       </c>
       <c r="H687" t="n">
         <v>2357662</v>
@@ -20321,7 +20321,7 @@
         <v>11.5017032623291</v>
       </c>
       <c r="G688" t="n">
-        <v>10.1982555389404</v>
+        <v>10.1982564926147</v>
       </c>
       <c r="H688" t="n">
         <v>1979022</v>
@@ -20350,7 +20350,7 @@
         <v>11.9259252548218</v>
       </c>
       <c r="G689" t="n">
-        <v>10.5744018554688</v>
+        <v>10.5744028091431</v>
       </c>
       <c r="H689" t="n">
         <v>2992968</v>
@@ -20379,7 +20379,7 @@
         <v>11.328498840332</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0446805953979</v>
+        <v>10.0446796417236</v>
       </c>
       <c r="H690" t="n">
         <v>5499203</v>
@@ -20408,7 +20408,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H691" t="n">
         <v>4155413</v>
@@ -20437,7 +20437,7 @@
         <v>12.0489253997803</v>
       </c>
       <c r="G692" t="n">
-        <v>10.6834630966187</v>
+        <v>10.683464050293</v>
       </c>
       <c r="H692" t="n">
         <v>2537540</v>
@@ -20524,7 +20524,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.7569122314453</v>
+        <v>10.756911277771</v>
       </c>
       <c r="H695" t="n">
         <v>4827551</v>
@@ -20582,7 +20582,7 @@
         <v>12.4580860137939</v>
       </c>
       <c r="G697" t="n">
-        <v>11.0462560653687</v>
+        <v>11.0462551116943</v>
       </c>
       <c r="H697" t="n">
         <v>11143856</v>
@@ -20640,7 +20640,7 @@
         <v>13.2086343765259</v>
       </c>
       <c r="G699" t="n">
-        <v>11.7117471694946</v>
+        <v>11.7117462158203</v>
       </c>
       <c r="H699" t="n">
         <v>7959306</v>
@@ -20727,7 +20727,7 @@
         <v>13.5500202178955</v>
       </c>
       <c r="G702" t="n">
-        <v>12.0144443511963</v>
+        <v>12.014443397522</v>
       </c>
       <c r="H702" t="n">
         <v>7155972</v>
@@ -20814,7 +20814,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856676101685</v>
+        <v>12.0856685638428</v>
       </c>
       <c r="H705" t="n">
         <v>4491851</v>
@@ -20988,7 +20988,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395784378052</v>
+        <v>11.0395774841309</v>
       </c>
       <c r="H711" t="n">
         <v>3266745</v>
@@ -21017,7 +21017,7 @@
         <v>12.7065954208374</v>
       </c>
       <c r="G712" t="n">
-        <v>11.2666025161743</v>
+        <v>11.2666015625</v>
       </c>
       <c r="H712" t="n">
         <v>5559737</v>
@@ -21046,7 +21046,7 @@
         <v>12.7015752792358</v>
       </c>
       <c r="G713" t="n">
-        <v>11.262149810791</v>
+        <v>11.2621507644653</v>
       </c>
       <c r="H713" t="n">
         <v>2952425</v>
@@ -21162,7 +21162,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364070892334</v>
+        <v>10.4364080429077</v>
       </c>
       <c r="H717" t="n">
         <v>3926528</v>
@@ -21278,7 +21278,7 @@
         <v>11.7979049682617</v>
       </c>
       <c r="G721" t="n">
-        <v>10.4608907699585</v>
+        <v>10.4608898162842</v>
       </c>
       <c r="H721" t="n">
         <v>10788083</v>
@@ -21336,7 +21336,7 @@
         <v>11.8857622146606</v>
       </c>
       <c r="G723" t="n">
-        <v>10.5387907028198</v>
+        <v>10.5387916564941</v>
       </c>
       <c r="H723" t="n">
         <v>2694375</v>
@@ -21394,7 +21394,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H725" t="n">
         <v>5437862</v>
@@ -21423,7 +21423,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H726" t="n">
         <v>2638902</v>
@@ -21452,7 +21452,7 @@
         <v>11.7025184631348</v>
       </c>
       <c r="G727" t="n">
-        <v>10.3763132095337</v>
+        <v>10.376314163208</v>
       </c>
       <c r="H727" t="n">
         <v>2777725</v>
@@ -21481,7 +21481,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H728" t="n">
         <v>6325209</v>
@@ -21510,7 +21510,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006391525269</v>
+        <v>10.3006381988525</v>
       </c>
       <c r="H729" t="n">
         <v>3047850</v>
@@ -21539,7 +21539,7 @@
         <v>11.7251100540161</v>
       </c>
       <c r="G730" t="n">
-        <v>10.3963451385498</v>
+        <v>10.3963441848755</v>
       </c>
       <c r="H730" t="n">
         <v>2649841</v>
@@ -21684,7 +21684,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580421447754</v>
+        <v>9.34580516815186</v>
       </c>
       <c r="H735" t="n">
         <v>2646670</v>
@@ -21713,7 +21713,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G736" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H736" t="n">
         <v>2599002</v>
@@ -21771,7 +21771,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G738" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H738" t="n">
         <v>10323921</v>
@@ -21800,7 +21800,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081249237061</v>
+        <v>8.29081153869629</v>
       </c>
       <c r="H739" t="n">
         <v>8509660</v>
@@ -21858,7 +21858,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889585494995</v>
+        <v>7.77889633178711</v>
       </c>
       <c r="H741" t="n">
         <v>8894223</v>
@@ -21916,7 +21916,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219158172607</v>
+        <v>8.46219253540039</v>
       </c>
       <c r="H743" t="n">
         <v>3711740</v>
@@ -21945,7 +21945,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H744" t="n">
         <v>2830649</v>
@@ -21974,7 +21974,7 @@
         <v>9.65922069549561</v>
       </c>
       <c r="G745" t="n">
-        <v>8.5645751953125</v>
+        <v>8.56457614898682</v>
       </c>
       <c r="H745" t="n">
         <v>3590690</v>
@@ -22090,7 +22090,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G749" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H749" t="n">
         <v>3226454</v>
@@ -22177,7 +22177,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G752" t="n">
-        <v>8.25520038604736</v>
+        <v>8.25519943237305</v>
       </c>
       <c r="H752" t="n">
         <v>4141957</v>
@@ -22206,7 +22206,7 @@
         <v>9.33540630340576</v>
       </c>
       <c r="G753" t="n">
-        <v>8.27745819091797</v>
+        <v>8.27745723724365</v>
       </c>
       <c r="H753" t="n">
         <v>2716829</v>
@@ -22264,7 +22264,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466617584229</v>
+        <v>7.91466569900513</v>
       </c>
       <c r="H755" t="n">
         <v>4636928</v>
@@ -22293,7 +22293,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.81228160858154</v>
+        <v>7.81228256225586</v>
       </c>
       <c r="H756" t="n">
         <v>3199541</v>
@@ -22380,7 +22380,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416151046753</v>
+        <v>7.59416103363037</v>
       </c>
       <c r="H759" t="n">
         <v>5059632</v>
@@ -22409,7 +22409,7 @@
         <v>8.17318725585938</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24694871902466</v>
+        <v>7.24694919586182</v>
       </c>
       <c r="H760" t="n">
         <v>5578537</v>
@@ -22438,7 +22438,7 @@
         <v>8.12800407409668</v>
       </c>
       <c r="G761" t="n">
-        <v>7.20688581466675</v>
+        <v>7.20688629150391</v>
       </c>
       <c r="H761" t="n">
         <v>4333423</v>
@@ -22467,7 +22467,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873331069946</v>
+        <v>6.96873378753662</v>
       </c>
       <c r="H762" t="n">
         <v>4541420</v>
@@ -22583,7 +22583,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576219558716</v>
       </c>
       <c r="H766" t="n">
         <v>6705143</v>
@@ -22728,7 +22728,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G771" t="n">
-        <v>8.3976469039917</v>
+        <v>8.39764595031738</v>
       </c>
       <c r="H771" t="n">
         <v>5244277</v>
@@ -22757,7 +22757,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G772" t="n">
-        <v>8.25520038604736</v>
+        <v>8.25519943237305</v>
       </c>
       <c r="H772" t="n">
         <v>3230113</v>
@@ -22786,7 +22786,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096832275391</v>
+        <v>8.39096927642822</v>
       </c>
       <c r="H773" t="n">
         <v>2691134</v>
@@ -22815,7 +22815,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H774" t="n">
         <v>4518486</v>
@@ -22931,7 +22931,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G778" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H778" t="n">
         <v>3928570</v>
@@ -22960,7 +22960,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G779" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H779" t="n">
         <v>5108708</v>
@@ -23018,7 +23018,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G781" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H781" t="n">
         <v>3452225</v>
@@ -23076,7 +23076,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G783" t="n">
-        <v>8.9451732635498</v>
+        <v>8.94517421722412</v>
       </c>
       <c r="H783" t="n">
         <v>2493851</v>
@@ -23192,7 +23192,7 @@
         <v>10.3445043563843</v>
       </c>
       <c r="G787" t="n">
-        <v>9.17219829559326</v>
+        <v>9.17219924926758</v>
       </c>
       <c r="H787" t="n">
         <v>3191829</v>
@@ -23221,7 +23221,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G788" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H788" t="n">
         <v>2462687</v>
@@ -23250,7 +23250,7 @@
         <v>10.4298496246338</v>
       </c>
       <c r="G789" t="n">
-        <v>9.2478723526001</v>
+        <v>9.24787139892578</v>
       </c>
       <c r="H789" t="n">
         <v>2010428</v>
@@ -23337,7 +23337,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G792" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H792" t="n">
         <v>1988992</v>
@@ -23453,7 +23453,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G796" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H796" t="n">
         <v>5910919</v>
@@ -23540,7 +23540,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H799" t="n">
         <v>2749374</v>
@@ -23656,7 +23656,7 @@
         <v>10.8440322875977</v>
       </c>
       <c r="G803" t="n">
-        <v>9.61511707305908</v>
+        <v>9.61511611938477</v>
       </c>
       <c r="H803" t="n">
         <v>5049854</v>
@@ -23714,7 +23714,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H805" t="n">
         <v>7839193</v>
@@ -23743,7 +23743,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232986450195</v>
+        <v>9.96232891082764</v>
       </c>
       <c r="H806" t="n">
         <v>5597634</v>
@@ -23801,7 +23801,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496036529541</v>
+        <v>10.3496046066284</v>
       </c>
       <c r="H808" t="n">
         <v>2858722</v>
@@ -24004,7 +24004,7 @@
         <v>12.3150053024292</v>
       </c>
       <c r="G815" t="n">
-        <v>10.9193897247314</v>
+        <v>10.9193887710571</v>
       </c>
       <c r="H815" t="n">
         <v>3038261</v>
@@ -24033,7 +24033,7 @@
         <v>12.1091690063477</v>
       </c>
       <c r="G816" t="n">
-        <v>10.7368793487549</v>
+        <v>10.7368803024292</v>
       </c>
       <c r="H816" t="n">
         <v>3221057</v>
@@ -24062,7 +24062,7 @@
         <v>12.2145967483521</v>
       </c>
       <c r="G817" t="n">
-        <v>10.8303604125977</v>
+        <v>10.8303594589233</v>
       </c>
       <c r="H817" t="n">
         <v>2672807</v>
@@ -24120,7 +24120,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G819" t="n">
-        <v>10.9883871078491</v>
+        <v>10.9883861541748</v>
       </c>
       <c r="H819" t="n">
         <v>2021022</v>
@@ -24381,7 +24381,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147811889648</v>
+        <v>10.8147802352905</v>
       </c>
       <c r="H828" t="n">
         <v>2456179</v>
@@ -24410,7 +24410,7 @@
         <v>12.2522497177124</v>
       </c>
       <c r="G829" t="n">
-        <v>10.8637456893921</v>
+        <v>10.8637447357178</v>
       </c>
       <c r="H829" t="n">
         <v>3054118</v>
@@ -24468,7 +24468,7 @@
         <v>12.4856977462769</v>
       </c>
       <c r="G831" t="n">
-        <v>11.0707378387451</v>
+        <v>11.0707368850708</v>
       </c>
       <c r="H831" t="n">
         <v>5821659</v>
@@ -24497,7 +24497,7 @@
         <v>12.6312885284424</v>
       </c>
       <c r="G832" t="n">
-        <v>11.1998291015625</v>
+        <v>11.1998300552368</v>
       </c>
       <c r="H832" t="n">
         <v>2539989</v>
@@ -24555,7 +24555,7 @@
         <v>12.0991277694702</v>
       </c>
       <c r="G834" t="n">
-        <v>10.7279767990112</v>
+        <v>10.7279777526855</v>
       </c>
       <c r="H834" t="n">
         <v>3226626</v>
@@ -24584,7 +24584,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G835" t="n">
-        <v>10.4386329650879</v>
+        <v>10.4386339187622</v>
       </c>
       <c r="H835" t="n">
         <v>4190619</v>
@@ -24642,7 +24642,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295726776123</v>
+        <v>10.3295736312866</v>
       </c>
       <c r="H837" t="n">
         <v>2609971</v>
@@ -24671,7 +24671,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271890640259</v>
+        <v>10.2271909713745</v>
       </c>
       <c r="H838" t="n">
         <v>2776794</v>
@@ -24700,7 +24700,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G839" t="n">
-        <v>10.4386329650879</v>
+        <v>10.4386339187622</v>
       </c>
       <c r="H839" t="n">
         <v>3240942</v>
@@ -24845,7 +24845,7 @@
         <v>11.3912544250488</v>
       </c>
       <c r="G844" t="n">
-        <v>10.1003246307373</v>
+        <v>10.100323677063</v>
       </c>
       <c r="H844" t="n">
         <v>5169154</v>
@@ -24874,7 +24874,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G845" t="n">
-        <v>10.2383193969727</v>
+        <v>10.2383184432983</v>
       </c>
       <c r="H845" t="n">
         <v>2752665</v>
@@ -24990,7 +24990,7 @@
         <v>10.836501121521</v>
       </c>
       <c r="G849" t="n">
-        <v>9.60843944549561</v>
+        <v>9.60843849182129</v>
       </c>
       <c r="H849" t="n">
         <v>2642683</v>
@@ -25019,7 +25019,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H850" t="n">
         <v>3580640</v>
@@ -25193,7 +25193,7 @@
         <v>10.4072589874268</v>
       </c>
       <c r="G856" t="n">
-        <v>9.22784042358398</v>
+        <v>9.2278413772583</v>
       </c>
       <c r="H856" t="n">
         <v>2374666</v>
@@ -25251,7 +25251,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G858" t="n">
-        <v>9.27012920379639</v>
+        <v>9.2701301574707</v>
       </c>
       <c r="H858" t="n">
         <v>2728302</v>
@@ -25280,7 +25280,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G859" t="n">
-        <v>9.16329479217529</v>
+        <v>9.16329383850098</v>
       </c>
       <c r="H859" t="n">
         <v>1906242</v>
@@ -25425,7 +25425,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G864" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H864" t="n">
         <v>1703266</v>
@@ -25570,7 +25570,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G869" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H869" t="n">
         <v>2768616</v>
@@ -25628,7 +25628,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G871" t="n">
-        <v>9.07204151153564</v>
+        <v>9.07204055786133</v>
       </c>
       <c r="H871" t="n">
         <v>6949172</v>
@@ -25744,7 +25744,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395576477051</v>
+        <v>9.58395671844482</v>
       </c>
       <c r="H875" t="n">
         <v>2681902</v>
@@ -25773,7 +25773,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G876" t="n">
-        <v>9.23451805114746</v>
+        <v>9.23451900482178</v>
       </c>
       <c r="H876" t="n">
         <v>3483538</v>
@@ -25831,7 +25831,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G878" t="n">
-        <v>9.27012920379639</v>
+        <v>9.2701301574707</v>
       </c>
       <c r="H878" t="n">
         <v>1207602</v>
@@ -25860,7 +25860,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G879" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H879" t="n">
         <v>2123211</v>
@@ -25889,7 +25889,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G880" t="n">
-        <v>9.55947303771973</v>
+        <v>9.55947208404541</v>
       </c>
       <c r="H880" t="n">
         <v>2840452</v>
@@ -25918,7 +25918,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G881" t="n">
-        <v>9.60621356964111</v>
+        <v>9.6062126159668</v>
       </c>
       <c r="H881" t="n">
         <v>3879724</v>
@@ -26005,7 +26005,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079113006592</v>
+        <v>9.69079208374023</v>
       </c>
       <c r="H884" t="n">
         <v>1520396</v>
@@ -26034,7 +26034,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G885" t="n">
-        <v>9.49047470092773</v>
+        <v>9.49047565460205</v>
       </c>
       <c r="H885" t="n">
         <v>1721405</v>
@@ -26121,7 +26121,7 @@
         <v>10.9820928573608</v>
       </c>
       <c r="G888" t="n">
-        <v>9.7375316619873</v>
+        <v>9.73753070831299</v>
       </c>
       <c r="H888" t="n">
         <v>1257161</v>
@@ -26266,7 +26266,7 @@
         <v>11.0272760391235</v>
       </c>
       <c r="G893" t="n">
-        <v>9.7775936126709</v>
+        <v>9.77759456634521</v>
       </c>
       <c r="H893" t="n">
         <v>2592934</v>
@@ -26353,7 +26353,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H896" t="n">
         <v>5491999</v>
@@ -26411,7 +26411,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070013046265</v>
+        <v>10.1070003509521</v>
       </c>
       <c r="H898" t="n">
         <v>2738861</v>
@@ -26527,7 +26527,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304893493652</v>
+        <v>9.71304798126221</v>
       </c>
       <c r="H902" t="n">
         <v>2481185</v>
@@ -26556,7 +26556,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H903" t="n">
         <v>2794057</v>
@@ -26643,7 +26643,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G906" t="n">
-        <v>10.0157461166382</v>
+        <v>10.0157451629639</v>
       </c>
       <c r="H906" t="n">
         <v>2792394</v>
@@ -26672,7 +26672,7 @@
         <v>11.4941720962524</v>
       </c>
       <c r="G907" t="n">
-        <v>10.191577911377</v>
+        <v>10.1915788650513</v>
       </c>
       <c r="H907" t="n">
         <v>5764525</v>
@@ -26701,7 +26701,7 @@
         <v>11.5845394134521</v>
       </c>
       <c r="G908" t="n">
-        <v>10.2717037200928</v>
+        <v>10.2717046737671</v>
       </c>
       <c r="H908" t="n">
         <v>2267960</v>
@@ -26788,7 +26788,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794101715088</v>
+        <v>9.99794006347656</v>
       </c>
       <c r="H911" t="n">
         <v>3280881</v>
@@ -26846,7 +26846,7 @@
         <v>10.7411136627197</v>
       </c>
       <c r="G913" t="n">
-        <v>9.52386093139648</v>
+        <v>9.5238618850708</v>
       </c>
       <c r="H913" t="n">
         <v>4157164</v>
@@ -26904,7 +26904,7 @@
         <v>10.4248304367065</v>
       </c>
       <c r="G915" t="n">
-        <v>9.24342060089111</v>
+        <v>9.24342155456543</v>
       </c>
       <c r="H915" t="n">
         <v>2417247</v>
@@ -26933,7 +26933,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G916" t="n">
-        <v>8.92514228820801</v>
+        <v>8.92514324188232</v>
       </c>
       <c r="H916" t="n">
         <v>4019358</v>
@@ -26991,7 +26991,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G918" t="n">
-        <v>9.12545871734619</v>
+        <v>9.12545776367188</v>
       </c>
       <c r="H918" t="n">
         <v>3054696</v>
@@ -27049,7 +27049,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G920" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H920" t="n">
         <v>3210453</v>
@@ -27107,7 +27107,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.9518518447876</v>
+        <v>8.95185089111328</v>
       </c>
       <c r="H922" t="n">
         <v>2394616</v>
@@ -27223,7 +27223,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G926" t="n">
-        <v>9.31464290618896</v>
+        <v>9.31464385986328</v>
       </c>
       <c r="H926" t="n">
         <v>1774533</v>
@@ -27252,7 +27252,7 @@
         <v>10.2842588424683</v>
       </c>
       <c r="G927" t="n">
-        <v>9.1187801361084</v>
+        <v>9.11878108978271</v>
       </c>
       <c r="H927" t="n">
         <v>2220798</v>
@@ -27281,7 +27281,7 @@
         <v>10.3545436859131</v>
       </c>
       <c r="G928" t="n">
-        <v>9.1810998916626</v>
+        <v>9.18110084533691</v>
       </c>
       <c r="H928" t="n">
         <v>1304029</v>
@@ -27310,7 +27310,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H929" t="n">
         <v>2564513</v>
@@ -27368,7 +27368,7 @@
         <v>10.9092969894409</v>
       </c>
       <c r="G931" t="n">
-        <v>9.6729850769043</v>
+        <v>9.67298603057861</v>
       </c>
       <c r="H931" t="n">
         <v>2301134</v>
@@ -27426,7 +27426,7 @@
         <v>10.9067869186401</v>
       </c>
       <c r="G933" t="n">
-        <v>9.6707592010498</v>
+        <v>9.67076015472412</v>
       </c>
       <c r="H933" t="n">
         <v>1044571</v>
@@ -27455,7 +27455,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G934" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H934" t="n">
         <v>1857397</v>
@@ -27629,7 +27629,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.1047735214233</v>
+        <v>10.1047744750977</v>
       </c>
       <c r="H940" t="n">
         <v>3374955</v>
@@ -27658,7 +27658,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136779785156</v>
+        <v>10.1136770248413</v>
       </c>
       <c r="H941" t="n">
         <v>3120641</v>
@@ -27687,7 +27687,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403856277466</v>
+        <v>10.1403875350952</v>
       </c>
       <c r="H942" t="n">
         <v>2004685</v>
@@ -27716,7 +27716,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230527877808</v>
+        <v>10.4230537414551</v>
       </c>
       <c r="H943" t="n">
         <v>5842648</v>
@@ -27890,7 +27890,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392574310303</v>
+        <v>9.56392383575439</v>
       </c>
       <c r="H949" t="n">
         <v>2157126</v>
@@ -28035,7 +28035,7 @@
         <v>10.2164840698242</v>
       </c>
       <c r="G954" t="n">
-        <v>9.05868625640869</v>
+        <v>9.05868530273438</v>
       </c>
       <c r="H954" t="n">
         <v>3488046</v>
@@ -28151,7 +28151,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G958" t="n">
-        <v>9.16552066802979</v>
+        <v>9.1655216217041</v>
       </c>
       <c r="H958" t="n">
         <v>3044501</v>
@@ -28209,7 +28209,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00972080230713</v>
+        <v>9.00971984863281</v>
       </c>
       <c r="H960" t="n">
         <v>3059945</v>
@@ -28267,7 +28267,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G962" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H962" t="n">
         <v>3934669</v>
@@ -28325,7 +28325,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G964" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H964" t="n">
         <v>4071910</v>
@@ -28354,7 +28354,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H965" t="n">
         <v>2851396</v>
@@ -28441,7 +28441,7 @@
         <v>10.3294429779053</v>
       </c>
       <c r="G968" t="n">
-        <v>9.15884399414062</v>
+        <v>9.15884304046631</v>
       </c>
       <c r="H968" t="n">
         <v>2590661</v>
@@ -28470,7 +28470,7 @@
         <v>10.2792387008667</v>
       </c>
       <c r="G969" t="n">
-        <v>9.11432933807373</v>
+        <v>9.11433029174805</v>
       </c>
       <c r="H969" t="n">
         <v>2928089</v>
@@ -28586,7 +28586,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65963077545166</v>
+        <v>9.65962982177734</v>
       </c>
       <c r="H973" t="n">
         <v>3880597</v>
@@ -28615,7 +28615,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G974" t="n">
-        <v>9.51050758361816</v>
+        <v>9.51050662994385</v>
       </c>
       <c r="H974" t="n">
         <v>4349124</v>
@@ -28673,7 +28673,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H976" t="n">
         <v>4961745</v>
@@ -28731,7 +28731,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G978" t="n">
-        <v>9.60621356964111</v>
+        <v>9.6062126159668</v>
       </c>
       <c r="H978" t="n">
         <v>5460186</v>
@@ -28789,7 +28789,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H980" t="n">
         <v>4874447</v>
@@ -28818,7 +28818,7 @@
         <v>11.2306022644043</v>
       </c>
       <c r="G981" t="n">
-        <v>9.95787811279297</v>
+        <v>9.95787715911865</v>
       </c>
       <c r="H981" t="n">
         <v>2713471</v>
@@ -28847,7 +28847,7 @@
         <v>11.1402349472046</v>
       </c>
       <c r="G982" t="n">
-        <v>9.87775135040283</v>
+        <v>9.87775230407715</v>
       </c>
       <c r="H982" t="n">
         <v>2778291</v>
@@ -28876,7 +28876,7 @@
         <v>11.0573978424072</v>
       </c>
       <c r="G983" t="n">
-        <v>9.80430221557617</v>
+        <v>9.80430126190186</v>
       </c>
       <c r="H983" t="n">
         <v>2502883</v>
@@ -28992,7 +28992,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H987" t="n">
         <v>8182251</v>
@@ -29050,7 +29050,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812397003174</v>
+        <v>9.40812492370605</v>
       </c>
       <c r="H989" t="n">
         <v>2714951</v>
@@ -29195,7 +29195,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G994" t="n">
-        <v>9.45931625366211</v>
+        <v>9.45931529998779</v>
       </c>
       <c r="H994" t="n">
         <v>2914765</v>
@@ -29282,7 +29282,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G997" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H997" t="n">
         <v>4136816</v>
@@ -29311,7 +29311,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G998" t="n">
-        <v>9.07204151153564</v>
+        <v>9.07204055786133</v>
       </c>
       <c r="H998" t="n">
         <v>3580666</v>
@@ -29398,7 +29398,7 @@
         <v>10.427339553833</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.24564647674561</v>
+        <v>9.24564552307129</v>
       </c>
       <c r="H1001" t="n">
         <v>2310864</v>
@@ -29427,7 +29427,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H1002" t="n">
         <v>2942968</v>
@@ -29514,7 +29514,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H1005" t="n">
         <v>2212645</v>
@@ -29572,7 +29572,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467674255371</v>
+        <v>9.33467578887939</v>
       </c>
       <c r="H1007" t="n">
         <v>3861795</v>
@@ -29601,7 +29601,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.45931625366211</v>
+        <v>9.45931529998779</v>
       </c>
       <c r="H1008" t="n">
         <v>2116813</v>
@@ -29630,7 +29630,7 @@
         <v>10.7938280105591</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.57060146331787</v>
+        <v>9.57060241699219</v>
       </c>
       <c r="H1009" t="n">
         <v>3043149</v>
@@ -29717,7 +29717,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H1012" t="n">
         <v>3418112</v>
@@ -29746,7 +29746,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.56169891357422</v>
+        <v>9.5616979598999</v>
       </c>
       <c r="H1013" t="n">
         <v>1635593</v>
@@ -29804,7 +29804,7 @@
         <v>10.934398651123</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.6952428817749</v>
+        <v>9.69524192810059</v>
       </c>
       <c r="H1015" t="n">
         <v>2311969</v>
@@ -29891,7 +29891,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H1018" t="n">
         <v>2839366</v>
@@ -29920,7 +29920,7 @@
         <v>11.1728668212891</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.9066858291626</v>
+        <v>9.90668487548828</v>
       </c>
       <c r="H1019" t="n">
         <v>3341541</v>
@@ -30065,7 +30065,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H1024" t="n">
         <v>1781897</v>
@@ -30152,7 +30152,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H1027" t="n">
         <v>2223593</v>
@@ -30210,7 +30210,7 @@
         <v>11.1126232147217</v>
       </c>
       <c r="G1029" t="n">
-        <v>9.85326957702637</v>
+        <v>9.85326862335205</v>
       </c>
       <c r="H1029" t="n">
         <v>1959789</v>
@@ -30239,7 +30239,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G1030" t="n">
-        <v>9.46154117584229</v>
+        <v>9.4615421295166</v>
       </c>
       <c r="H1030" t="n">
         <v>7606013</v>
@@ -30297,7 +30297,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G1032" t="n">
-        <v>9.12545871734619</v>
+        <v>9.12545776367188</v>
       </c>
       <c r="H1032" t="n">
         <v>2852190</v>
@@ -30471,7 +30471,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H1038" t="n">
         <v>4452658</v>
@@ -30529,7 +30529,7 @@
         <v>9.75962924957275</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.65360546112061</v>
+        <v>8.65360450744629</v>
       </c>
       <c r="H1040" t="n">
         <v>7621307</v>
@@ -30558,7 +30558,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H1041" t="n">
         <v>4707102</v>
@@ -30674,7 +30674,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H1045" t="n">
         <v>5766485</v>
@@ -30761,7 +30761,7 @@
         <v>9.55630302429199</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.47332096099854</v>
+        <v>8.47332191467285</v>
       </c>
       <c r="H1048" t="n">
         <v>2650515</v>
@@ -30819,7 +30819,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.43548393249512</v>
+        <v>8.43548488616943</v>
       </c>
       <c r="H1050" t="n">
         <v>4171244</v>
@@ -30906,7 +30906,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657609939575</v>
+        <v>7.71657657623291</v>
       </c>
       <c r="H1053" t="n">
         <v>7295256</v>
@@ -30935,7 +30935,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754726409912</v>
+        <v>7.62754774093628</v>
       </c>
       <c r="H1054" t="n">
         <v>5328087</v>
@@ -31109,7 +31109,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111692428589</v>
+        <v>7.07111740112305</v>
       </c>
       <c r="H1060" t="n">
         <v>4984381</v>
@@ -31138,7 +31138,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.70832395553589</v>
+        <v>6.70832347869873</v>
       </c>
       <c r="H1061" t="n">
         <v>5838598</v>
@@ -31196,7 +31196,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.9500036239624</v>
+        <v>4.95000410079956</v>
       </c>
       <c r="H1063" t="n">
         <v>15725169</v>
@@ -31225,7 +31225,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.9500036239624</v>
+        <v>4.95000410079956</v>
       </c>
       <c r="H1064" t="n">
         <v>14702152</v>
@@ -31312,7 +31312,7 @@
         <v>5.16848611831665</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.58275985717773</v>
+        <v>4.58276033401489</v>
       </c>
       <c r="H1067" t="n">
         <v>9831037</v>
@@ -31457,7 +31457,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342178344727</v>
+        <v>5.00342130661011</v>
       </c>
       <c r="H1072" t="n">
         <v>6911923</v>
@@ -31486,7 +31486,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.88990926742554</v>
+        <v>4.8899097442627</v>
       </c>
       <c r="H1073" t="n">
         <v>3925543</v>
@@ -31515,7 +31515,7 @@
         <v>5.85627889633179</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.19260740280151</v>
+        <v>5.19260787963867</v>
       </c>
       <c r="H1074" t="n">
         <v>6147761</v>
@@ -31544,7 +31544,7 @@
         <v>5.8261570930481</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.1658992767334</v>
+        <v>5.16589975357056</v>
       </c>
       <c r="H1075" t="n">
         <v>7136455</v>
@@ -31573,7 +31573,7 @@
         <v>5.89393186569214</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.22599315643311</v>
+        <v>5.22599363327026</v>
       </c>
       <c r="H1076" t="n">
         <v>4232448</v>
@@ -31631,7 +31631,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.98561525344849</v>
+        <v>4.98561573028564</v>
       </c>
       <c r="H1078" t="n">
         <v>2485771</v>
@@ -31660,7 +31660,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1079" t="n">
-        <v>4.98561525344849</v>
+        <v>4.98561573028564</v>
       </c>
       <c r="H1079" t="n">
         <v>4812027</v>
@@ -31718,7 +31718,7 @@
         <v>6.06713485717773</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.37956809997559</v>
+        <v>5.37956762313843</v>
       </c>
       <c r="H1081" t="n">
         <v>8617110</v>
@@ -31776,7 +31776,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950567245483</v>
+        <v>5.33950614929199</v>
       </c>
       <c r="H1083" t="n">
         <v>4088673</v>
@@ -31863,7 +31863,7 @@
         <v>6.04956388473511</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.36398839950562</v>
+        <v>5.36398887634277</v>
       </c>
       <c r="H1086" t="n">
         <v>5596784</v>
@@ -31921,7 +31921,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1088" t="n">
         <v>5337056</v>
@@ -31950,7 +31950,7 @@
         <v>5.47473001480103</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.85429859161377</v>
+        <v>4.85429811477661</v>
       </c>
       <c r="H1089" t="n">
         <v>3542169</v>
@@ -32037,7 +32037,7 @@
         <v>5.28395509719849</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.68514347076416</v>
+        <v>4.685142993927</v>
       </c>
       <c r="H1092" t="n">
         <v>4658214</v>
@@ -32124,7 +32124,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1095" t="n">
         <v>3476797</v>
@@ -32182,7 +32182,7 @@
         <v>5.55505609512329</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.92552089691162</v>
+        <v>4.92552137374878</v>
       </c>
       <c r="H1097" t="n">
         <v>3776492</v>
@@ -32211,7 +32211,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928550720215</v>
+        <v>5.19928503036499</v>
       </c>
       <c r="H1098" t="n">
         <v>4783125</v>
@@ -32240,7 +32240,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041345596313</v>
+        <v>5.21041393280029</v>
       </c>
       <c r="H1099" t="n">
         <v>4870688</v>
@@ -32298,7 +32298,7 @@
         <v>5.79101419448853</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.13473892211914</v>
+        <v>5.1347393989563</v>
       </c>
       <c r="H1101" t="n">
         <v>3599923</v>
@@ -32385,7 +32385,7 @@
         <v>5.80858516693115</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15031909942627</v>
+        <v>5.15031862258911</v>
       </c>
       <c r="H1104" t="n">
         <v>2378841</v>
@@ -32414,7 +32414,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248159408569</v>
+        <v>5.11248207092285</v>
       </c>
       <c r="H1105" t="n">
         <v>2051727</v>
@@ -32646,7 +32646,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.79800081253052</v>
+        <v>4.79800033569336</v>
       </c>
       <c r="H1113" t="n">
         <v>3350805</v>
@@ -32733,7 +32733,7 @@
         <v>5.46217918395996</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.865074634552</v>
+        <v>4.86507511138916</v>
       </c>
       <c r="H1116" t="n">
         <v>3829378</v>
@@ -32762,7 +32762,7 @@
         <v>5.30905723571777</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.72869110107422</v>
+        <v>4.72869157791138</v>
       </c>
       <c r="H1117" t="n">
         <v>7700374</v>
@@ -32907,7 +32907,7 @@
         <v>5.79854488372803</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.16466999053955</v>
+        <v>5.16467046737671</v>
       </c>
       <c r="H1122" t="n">
         <v>12491580</v>
@@ -32965,7 +32965,7 @@
         <v>6.46876621246338</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.76162576675415</v>
+        <v>5.76162528991699</v>
       </c>
       <c r="H1124" t="n">
         <v>11268120</v>
@@ -32994,7 +32994,7 @@
         <v>6.59176588058472</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.87117910385132</v>
+        <v>5.87117958068848</v>
       </c>
       <c r="H1125" t="n">
         <v>10577677</v>
@@ -33023,7 +33023,7 @@
         <v>6.41354179382324</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.71243762969971</v>
+        <v>5.71243810653687</v>
       </c>
       <c r="H1126" t="n">
         <v>6490655</v>
@@ -33139,7 +33139,7 @@
         <v>5.99182987213135</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33682584762573</v>
+        <v>5.33682632446289</v>
       </c>
       <c r="H1130" t="n">
         <v>5065402</v>
@@ -33197,7 +33197,7 @@
         <v>5.98680877685547</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.3323540687561</v>
+        <v>5.33235359191895</v>
       </c>
       <c r="H1132" t="n">
         <v>5119610</v>
@@ -33342,7 +33342,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.0841817855835</v>
+        <v>5.08418226242065</v>
       </c>
       <c r="H1137" t="n">
         <v>3931365</v>
@@ -33429,7 +33429,7 @@
         <v>5.61530113220215</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.00145816802979</v>
+        <v>5.00145769119263</v>
       </c>
       <c r="H1140" t="n">
         <v>4272132</v>
@@ -33487,7 +33487,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.97686338424683</v>
+        <v>4.97686290740967</v>
       </c>
       <c r="H1142" t="n">
         <v>3387639</v>
@@ -33574,7 +33574,7 @@
         <v>5.68558597564697</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.06405973434448</v>
+        <v>5.06405925750732</v>
       </c>
       <c r="H1145" t="n">
         <v>3689754</v>
@@ -33661,7 +33661,7 @@
         <v>5.27642488479614</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.69962596893311</v>
+        <v>4.69962644577026</v>
       </c>
       <c r="H1148" t="n">
         <v>5584746</v>
@@ -33748,7 +33748,7 @@
         <v>5.28897619247437</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.71080541610718</v>
+        <v>4.71080589294434</v>
       </c>
       <c r="H1151" t="n">
         <v>6369097</v>
@@ -33777,7 +33777,7 @@
         <v>5.36679220199585</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.78011465072632</v>
+        <v>4.78011512756348</v>
       </c>
       <c r="H1152" t="n">
         <v>6019418</v>
@@ -33806,7 +33806,7 @@
         <v>5.47724008560181</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.87848949432373</v>
+        <v>4.87848901748657</v>
       </c>
       <c r="H1153" t="n">
         <v>3853871</v>
@@ -34067,7 +34067,7 @@
         <v>4.92123222351074</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.38326215744019</v>
+        <v>4.38326168060303</v>
       </c>
       <c r="H1162" t="n">
         <v>24661467</v>
@@ -34154,7 +34154,7 @@
         <v>4.57357120513916</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.07360553741455</v>
+        <v>4.07360601425171</v>
       </c>
       <c r="H1165" t="n">
         <v>7438646</v>
@@ -34299,7 +34299,7 @@
         <v>4.96892595291138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.42574214935303</v>
+        <v>4.42574167251587</v>
       </c>
       <c r="H1170" t="n">
         <v>3451603</v>
@@ -34415,7 +34415,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1174" t="n">
-        <v>4.34189987182617</v>
+        <v>4.34190034866333</v>
       </c>
       <c r="H1174" t="n">
         <v>4695442</v>
@@ -34589,7 +34589,7 @@
         <v>4.66895818710327</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.15856552124023</v>
+        <v>4.15856599807739</v>
       </c>
       <c r="H1180" t="n">
         <v>6557504</v>
@@ -34734,7 +34734,7 @@
         <v>4.50579500198364</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.01323843002319</v>
+        <v>4.01323890686035</v>
       </c>
       <c r="H1185" t="n">
         <v>4155094</v>
@@ -34821,7 +34821,7 @@
         <v>4.39032697677612</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.91039347648621</v>
+        <v>3.91039323806763</v>
       </c>
       <c r="H1188" t="n">
         <v>4258438</v>
@@ -34850,7 +34850,7 @@
         <v>4.29242897033691</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.82319736480713</v>
+        <v>3.82319688796997</v>
       </c>
       <c r="H1189" t="n">
         <v>7837081</v>
@@ -34937,7 +34937,7 @@
         <v>4.19327592849731</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.73488283157349</v>
+        <v>3.73488306999207</v>
       </c>
       <c r="H1192" t="n">
         <v>4846298</v>
@@ -34995,7 +34995,7 @@
         <v>4.07906293869019</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.63315534591675</v>
+        <v>3.63315558433533</v>
       </c>
       <c r="H1194" t="n">
         <v>8280016</v>
@@ -35111,7 +35111,7 @@
         <v>4.22465419769287</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.76283097267151</v>
+        <v>3.76283121109009</v>
       </c>
       <c r="H1198" t="n">
         <v>5589044</v>
@@ -35401,7 +35401,7 @@
         <v>3.56321811676025</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.17370080947876</v>
+        <v>3.17370057106018</v>
       </c>
       <c r="H1208" t="n">
         <v>6464136</v>
@@ -35459,7 +35459,7 @@
         <v>3.86444091796875</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.4419949054718</v>
+        <v>3.44199514389038</v>
       </c>
       <c r="H1210" t="n">
         <v>7063864</v>
@@ -35604,7 +35604,7 @@
         <v>3.79415607452393</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.3793933391571</v>
+        <v>3.37939357757568</v>
       </c>
       <c r="H1215" t="n">
         <v>3909509</v>
@@ -35633,7 +35633,7 @@
         <v>3.65609502792358</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.25642466545105</v>
+        <v>3.25642490386963</v>
       </c>
       <c r="H1216" t="n">
         <v>4082735</v>
@@ -35807,7 +35807,7 @@
         <v>3.59585094451904</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.20276641845703</v>
+        <v>3.20276618003845</v>
       </c>
       <c r="H1222" t="n">
         <v>5346240</v>
@@ -35836,7 +35836,7 @@
         <v>3.62597298622131</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.22959566116333</v>
+        <v>3.22959542274475</v>
       </c>
       <c r="H1223" t="n">
         <v>3204692</v>
@@ -35865,7 +35865,7 @@
         <v>3.68496203422546</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.28213620185852</v>
+        <v>3.28213596343994</v>
       </c>
       <c r="H1224" t="n">
         <v>4139377</v>
@@ -36010,7 +36010,7 @@
         <v>3.78411507606506</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.37045001983643</v>
+        <v>3.370450258255</v>
       </c>
       <c r="H1229" t="n">
         <v>8618018</v>
@@ -36184,7 +36184,7 @@
         <v>4.6940598487854</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.18092346191406</v>
+        <v>4.1809229850769</v>
       </c>
       <c r="H1235" t="n">
         <v>15804964</v>
@@ -36387,7 +36387,7 @@
         <v>4.89487504959106</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.35978651046753</v>
+        <v>4.35978603363037</v>
       </c>
       <c r="H1242" t="n">
         <v>6079967</v>
@@ -36445,7 +36445,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.27706241607666</v>
+        <v>4.2770619392395</v>
       </c>
       <c r="H1244" t="n">
         <v>4685519</v>
@@ -36474,7 +36474,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.47157573699951</v>
+        <v>4.47157526016235</v>
       </c>
       <c r="H1245" t="n">
         <v>7739906</v>
@@ -36532,7 +36532,7 @@
         <v>5.42201614379883</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.8293023109436</v>
+        <v>4.82930183410645</v>
       </c>
       <c r="H1247" t="n">
         <v>8336834</v>
@@ -36561,7 +36561,7 @@
         <v>5.30654716491699</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.72645568847656</v>
+        <v>4.72645616531372</v>
       </c>
       <c r="H1248" t="n">
         <v>6460441</v>
@@ -36619,7 +36619,7 @@
         <v>5.1333441734314</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.5721869468689</v>
+        <v>4.57218647003174</v>
       </c>
       <c r="H1250" t="n">
         <v>5110006</v>
@@ -36706,7 +36706,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.62584495544434</v>
+        <v>4.62584447860718</v>
       </c>
       <c r="H1253" t="n">
         <v>2827257</v>
@@ -36735,7 +36735,7 @@
         <v>5.35675096511841</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.77117109298706</v>
+        <v>4.77117156982422</v>
       </c>
       <c r="H1254" t="n">
         <v>5955094</v>
@@ -36793,7 +36793,7 @@
         <v>5.37683200836182</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.78905773162842</v>
+        <v>4.78905725479126</v>
       </c>
       <c r="H1256" t="n">
         <v>1840506</v>
@@ -36880,7 +36880,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1259" t="n">
         <v>4061775</v>
@@ -36938,7 +36938,7 @@
         <v>5.46719884872437</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.86954593658447</v>
+        <v>4.86954545974731</v>
       </c>
       <c r="H1261" t="n">
         <v>2064399</v>
@@ -36967,7 +36967,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1262" t="n">
         <v>5407097</v>
@@ -36996,7 +36996,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.86060285568237</v>
+        <v>4.86060237884521</v>
       </c>
       <c r="H1263" t="n">
         <v>3511782</v>
@@ -37112,7 +37112,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1267" t="n">
         <v>3396789</v>
@@ -37257,7 +37257,7 @@
         <v>5.82364702224731</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.18702840805054</v>
+        <v>5.18702793121338</v>
       </c>
       <c r="H1272" t="n">
         <v>7105248</v>
@@ -37315,7 +37315,7 @@
         <v>6.17256307601929</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.49780178070068</v>
+        <v>5.49780225753784</v>
       </c>
       <c r="H1274" t="n">
         <v>7287173</v>
@@ -37344,7 +37344,7 @@
         <v>6.10729789733887</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.43967151641846</v>
+        <v>5.4396710395813</v>
       </c>
       <c r="H1275" t="n">
         <v>6169237</v>
@@ -37431,7 +37431,7 @@
         <v>6.08721685409546</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.42178583145142</v>
+        <v>5.42178535461426</v>
       </c>
       <c r="H1278" t="n">
         <v>4068724</v>
@@ -37460,7 +37460,7 @@
         <v>6.00689077377319</v>
       </c>
       <c r="G1279" t="n">
-        <v>5.35024070739746</v>
+        <v>5.3502402305603</v>
       </c>
       <c r="H1279" t="n">
         <v>3024433</v>
@@ -37547,7 +37547,7 @@
         <v>5.85878896713257</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.21832895278931</v>
+        <v>5.21832847595215</v>
       </c>
       <c r="H1282" t="n">
         <v>3059439</v>
@@ -37692,7 +37692,7 @@
         <v>5.34169006347656</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.75775718688965</v>
+        <v>4.75775671005249</v>
       </c>
       <c r="H1287" t="n">
         <v>4046294</v>
@@ -37721,7 +37721,7 @@
         <v>5.59019899368286</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.9790997505188</v>
+        <v>4.97910022735596</v>
       </c>
       <c r="H1288" t="n">
         <v>7589590</v>
@@ -37924,7 +37924,7 @@
         <v>5.98178911209106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.32788276672363</v>
+        <v>5.32788324356079</v>
       </c>
       <c r="H1295" t="n">
         <v>5483636</v>
@@ -38098,7 +38098,7 @@
         <v>6.55160188674927</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.83540630340576</v>
+        <v>5.8354058265686</v>
       </c>
       <c r="H1301" t="n">
         <v>9385518</v>
@@ -38156,7 +38156,7 @@
         <v>6.3457670211792</v>
       </c>
       <c r="G1303" t="n">
-        <v>5.65207195281982</v>
+        <v>5.65207242965698</v>
       </c>
       <c r="H1303" t="n">
         <v>6157528</v>
@@ -38185,7 +38185,7 @@
         <v>6.35078716278076</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.65654373168945</v>
+        <v>5.65654325485229</v>
       </c>
       <c r="H1304" t="n">
         <v>5745479</v>
@@ -38214,7 +38214,7 @@
         <v>6.40852212905884</v>
       </c>
       <c r="G1305" t="n">
-        <v>5.70796728134155</v>
+        <v>5.70796680450439</v>
       </c>
       <c r="H1305" t="n">
         <v>3560044</v>
@@ -38243,7 +38243,7 @@
         <v>6.63192892074585</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.90695142745972</v>
+        <v>5.90695190429688</v>
       </c>
       <c r="H1306" t="n">
         <v>7874391</v>
@@ -38330,7 +38330,7 @@
         <v>6.00940084457397</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.35247659683228</v>
+        <v>5.35247611999512</v>
       </c>
       <c r="H1309" t="n">
         <v>24228663</v>
@@ -38388,7 +38388,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.0841817855835</v>
+        <v>5.08418226242065</v>
       </c>
       <c r="H1311" t="n">
         <v>8961866</v>
@@ -38417,7 +38417,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1312" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1312" t="n">
         <v>9655227</v>
@@ -38504,7 +38504,7 @@
         <v>5.91652393341064</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.26975250244141</v>
+        <v>5.26975202560425</v>
       </c>
       <c r="H1315" t="n">
         <v>12797834</v>
@@ -38533,7 +38533,7 @@
         <v>6.07215595245361</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.40837097167969</v>
+        <v>5.40837144851685</v>
       </c>
       <c r="H1316" t="n">
         <v>9400118</v>
@@ -38591,7 +38591,7 @@
         <v>6.07717609405518</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.41284275054932</v>
+        <v>5.41284227371216</v>
       </c>
       <c r="H1318" t="n">
         <v>4627496</v>
@@ -38649,7 +38649,7 @@
         <v>6.12486982345581</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.45532274246216</v>
+        <v>5.455322265625</v>
       </c>
       <c r="H1320" t="n">
         <v>2675208</v>
@@ -38707,7 +38707,7 @@
         <v>5.97174787521362</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.31893920898438</v>
+        <v>5.31893968582153</v>
       </c>
       <c r="H1322" t="n">
         <v>5171781</v>
@@ -38765,7 +38765,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.31670379638672</v>
+        <v>5.31670331954956</v>
       </c>
       <c r="H1324" t="n">
         <v>4027905</v>
@@ -38852,7 +38852,7 @@
         <v>5.69060611724854</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.06853055953979</v>
+        <v>5.06853103637695</v>
       </c>
       <c r="H1327" t="n">
         <v>7314312</v>
@@ -39055,7 +39055,7 @@
         <v>5.87887096405029</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.23621559143066</v>
+        <v>5.23621511459351</v>
       </c>
       <c r="H1334" t="n">
         <v>3164034</v>
@@ -39287,7 +39287,7 @@
         <v>5.83870792388916</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.20044231414795</v>
+        <v>5.20044279098511</v>
       </c>
       <c r="H1342" t="n">
         <v>4486409</v>
@@ -39374,7 +39374,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.97686338424683</v>
+        <v>4.97686290740967</v>
       </c>
       <c r="H1345" t="n">
         <v>5024234</v>
@@ -39490,7 +39490,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.94556283950806</v>
+        <v>4.94556331634521</v>
       </c>
       <c r="H1349" t="n">
         <v>4621291</v>
@@ -39577,7 +39577,7 @@
         <v>4.87855911254883</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.34525346755981</v>
+        <v>4.34525394439697</v>
       </c>
       <c r="H1352" t="n">
         <v>14868855</v>
@@ -39606,7 +39606,7 @@
         <v>4.82333517074585</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.29606676101685</v>
+        <v>4.29606628417969</v>
       </c>
       <c r="H1353" t="n">
         <v>10990037</v>
@@ -39751,7 +39751,7 @@
         <v>5.06054782867432</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.50734806060791</v>
+        <v>4.50734853744507</v>
       </c>
       <c r="H1358" t="n">
         <v>3316325</v>
@@ -39954,7 +39954,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.69068288803101</v>
+        <v>4.69068336486816</v>
       </c>
       <c r="H1365" t="n">
         <v>9046399</v>
@@ -40012,7 +40012,7 @@
         <v>5.1383638381958</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.57665729522705</v>
+        <v>4.57665777206421</v>
       </c>
       <c r="H1367" t="n">
         <v>2528599</v>
@@ -40070,7 +40070,7 @@
         <v>5.12832307815552</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.56771421432495</v>
+        <v>4.56771469116211</v>
       </c>
       <c r="H1369" t="n">
         <v>2605182</v>
@@ -40186,7 +40186,7 @@
         <v>5.11828184127808</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.55877065658569</v>
+        <v>4.55877113342285</v>
       </c>
       <c r="H1373" t="n">
         <v>4133342</v>
@@ -40244,7 +40244,7 @@
         <v>5.3793420791626</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.79129266738892</v>
+        <v>4.79129314422607</v>
       </c>
       <c r="H1375" t="n">
         <v>10178926</v>
@@ -40273,7 +40273,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1376" t="n">
         <v>5287449</v>
@@ -40389,7 +40389,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1380" t="n">
         <v>6843942</v>
@@ -40476,7 +40476,7 @@
         <v>5.56760692596436</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.95897769927979</v>
+        <v>4.95897722244263</v>
       </c>
       <c r="H1383" t="n">
         <v>4282870</v>
@@ -40679,7 +40679,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.72422027587891</v>
+        <v>4.72421979904175</v>
       </c>
       <c r="H1390" t="n">
         <v>3701384</v>
@@ -40737,7 +40737,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.72422027587891</v>
+        <v>4.72421979904175</v>
       </c>
       <c r="H1392" t="n">
         <v>2649454</v>
@@ -40766,7 +40766,7 @@
         <v>5.29901599884033</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.71974754333496</v>
+        <v>4.71974802017212</v>
       </c>
       <c r="H1393" t="n">
         <v>2108129</v>
@@ -40853,7 +40853,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1396" t="n">
-        <v>4.56324338912964</v>
+        <v>4.56324291229248</v>
       </c>
       <c r="H1396" t="n">
         <v>3303148</v>
@@ -40882,7 +40882,7 @@
         <v>5.22873115539551</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.65714597702026</v>
+        <v>4.65714645385742</v>
       </c>
       <c r="H1397" t="n">
         <v>3565887</v>
@@ -40911,7 +40911,7 @@
         <v>5.21868991851807</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.64820241928101</v>
+        <v>4.64820289611816</v>
       </c>
       <c r="H1398" t="n">
         <v>2418474</v>
@@ -41027,7 +41027,7 @@
         <v>4.90617084503174</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.3698468208313</v>
+        <v>4.36984729766846</v>
       </c>
       <c r="H1402" t="n">
         <v>5231002</v>
@@ -41056,7 +41056,7 @@
         <v>4.97143602371216</v>
       </c>
       <c r="G1403" t="n">
-        <v>4.42797756195068</v>
+        <v>4.42797803878784</v>
       </c>
       <c r="H1403" t="n">
         <v>3203342</v>
@@ -41114,7 +41114,7 @@
         <v>4.88483476638794</v>
       </c>
       <c r="G1405" t="n">
-        <v>4.35084295272827</v>
+        <v>4.35084342956543</v>
       </c>
       <c r="H1405" t="n">
         <v>3408367</v>
@@ -41172,7 +41172,7 @@
         <v>4.90240621566772</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.36649417877197</v>
+        <v>4.36649370193481</v>
       </c>
       <c r="H1407" t="n">
         <v>3512290</v>
@@ -41288,7 +41288,7 @@
         <v>4.75681495666504</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.23681783676147</v>
+        <v>4.23681831359863</v>
       </c>
       <c r="H1411" t="n">
         <v>4771701</v>
@@ -41462,7 +41462,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1417" t="n">
-        <v>4.5297064781189</v>
+        <v>4.52970600128174</v>
       </c>
       <c r="H1417" t="n">
         <v>3747890</v>
@@ -41549,7 +41549,7 @@
         <v>4.91119194030762</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.37431955337524</v>
+        <v>4.37431907653809</v>
       </c>
       <c r="H1420" t="n">
         <v>4386657</v>
@@ -41636,7 +41636,7 @@
         <v>4.92499780654907</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.38661575317383</v>
+        <v>4.38661623001099</v>
       </c>
       <c r="H1423" t="n">
         <v>3890806</v>
@@ -41694,7 +41694,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.56324338912964</v>
+        <v>4.56324291229248</v>
       </c>
       <c r="H1425" t="n">
         <v>5305491</v>
@@ -41723,7 +41723,7 @@
         <v>5.16597604751587</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.60125160217285</v>
+        <v>4.60125112533569</v>
       </c>
       <c r="H1426" t="n">
         <v>3581797</v>
@@ -41868,7 +41868,7 @@
         <v>4.98147678375244</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.43692064285278</v>
+        <v>4.43692111968994</v>
       </c>
       <c r="H1431" t="n">
         <v>1848823</v>
@@ -41926,7 +41926,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.27706241607666</v>
+        <v>4.2770619392395</v>
       </c>
       <c r="H1433" t="n">
         <v>3356625</v>
@@ -42013,7 +42013,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.47157573699951</v>
+        <v>4.47157526016235</v>
       </c>
       <c r="H1436" t="n">
         <v>3876966</v>
@@ -42216,7 +42216,7 @@
         <v>4.96139478683472</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41903400421143</v>
+        <v>4.41903448104858</v>
       </c>
       <c r="H1443" t="n">
         <v>3045903</v>
@@ -42332,7 +42332,7 @@
         <v>5.01662015914917</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.46822214126587</v>
+        <v>4.46822261810303</v>
       </c>
       <c r="H1447" t="n">
         <v>5734258</v>
@@ -42390,7 +42390,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.62584495544434</v>
+        <v>4.62584447860718</v>
       </c>
       <c r="H1449" t="n">
         <v>7048976</v>
@@ -42419,7 +42419,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.5297064781189</v>
+        <v>4.52970600128174</v>
       </c>
       <c r="H1450" t="n">
         <v>6506615</v>
@@ -42506,7 +42506,7 @@
         <v>4.99151802062988</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.4458646774292</v>
+        <v>4.44586420059204</v>
       </c>
       <c r="H1453" t="n">
         <v>2739262</v>
@@ -42535,7 +42535,7 @@
         <v>4.91244697570801</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.37543725967407</v>
+        <v>4.37543678283691</v>
       </c>
       <c r="H1454" t="n">
         <v>3529674</v>
@@ -42564,7 +42564,7 @@
         <v>5.07058906555176</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.51629161834717</v>
+        <v>4.51629209518433</v>
       </c>
       <c r="H1455" t="n">
         <v>5222595</v>
@@ -42825,7 +42825,7 @@
         <v>5.55003595352173</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.9433274269104</v>
+        <v>4.94332695007324</v>
       </c>
       <c r="H1464" t="n">
         <v>6413047</v>
@@ -42883,7 +42883,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.69068288803101</v>
+        <v>4.69068336486816</v>
       </c>
       <c r="H1466" t="n">
         <v>7328705</v>
@@ -42941,7 +42941,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.79800081253052</v>
+        <v>4.79800033569336</v>
       </c>
       <c r="H1468" t="n">
         <v>8090619</v>
@@ -42999,7 +42999,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1470" t="n">
         <v>6942701</v>
@@ -43144,7 +43144,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.91202640533447</v>
+        <v>4.91202592849731</v>
       </c>
       <c r="H1475" t="n">
         <v>2995584</v>
@@ -43202,7 +43202,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1477" t="n">
         <v>4075860</v>
@@ -43289,7 +43289,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.94556283950806</v>
+        <v>4.94556331634521</v>
       </c>
       <c r="H1480" t="n">
         <v>5065969</v>
@@ -43347,7 +43347,7 @@
         <v>4.87353897094727</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.3407826423645</v>
+        <v>4.34078216552734</v>
       </c>
       <c r="H1482" t="n">
         <v>28990116</v>
@@ -43492,7 +43492,7 @@
         <v>4.81203889846802</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.28600549697876</v>
+        <v>4.2860050201416</v>
       </c>
       <c r="H1487" t="n">
         <v>5381782</v>
@@ -43521,7 +43521,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.34189987182617</v>
+        <v>4.34190034866333</v>
       </c>
       <c r="H1488" t="n">
         <v>5511409</v>
@@ -43666,7 +43666,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.39220523834229</v>
+        <v>4.39220476150513</v>
       </c>
       <c r="H1493" t="n">
         <v>2167743</v>
@@ -43956,7 +43956,7 @@
         <v>4.46563196182251</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.97746610641479</v>
+        <v>3.97746634483337</v>
       </c>
       <c r="H1503" t="n">
         <v>7272410</v>
@@ -43985,7 +43985,7 @@
         <v>4.50328493118286</v>
       </c>
       <c r="G1504" t="n">
-        <v>4.0110034942627</v>
+        <v>4.01100301742554</v>
       </c>
       <c r="H1504" t="n">
         <v>4367193</v>
@@ -44014,7 +44014,7 @@
         <v>4.42170381546021</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.93834018707275</v>
+        <v>3.93833994865417</v>
       </c>
       <c r="H1505" t="n">
         <v>3362331</v>
@@ -44130,7 +44130,7 @@
         <v>4.59365177154541</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.09149169921875</v>
+        <v>4.09149122238159</v>
       </c>
       <c r="H1509" t="n">
         <v>4350486</v>
@@ -44188,7 +44188,7 @@
         <v>4.56729507446289</v>
       </c>
       <c r="G1511" t="n">
-        <v>4.06801605224609</v>
+        <v>4.06801557540894</v>
       </c>
       <c r="H1511" t="n">
         <v>4359136</v>
@@ -44275,7 +44275,7 @@
         <v>4.41040802001953</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.92827916145325</v>
+        <v>3.92827892303467</v>
       </c>
       <c r="H1514" t="n">
         <v>3179388</v>
@@ -44304,7 +44304,7 @@
         <v>4.4455509185791</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.95958018302917</v>
+        <v>3.95958042144775</v>
       </c>
       <c r="H1515" t="n">
         <v>2325197</v>
@@ -44333,7 +44333,7 @@
         <v>4.37275505065918</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.89474248886108</v>
+        <v>3.89474201202393</v>
       </c>
       <c r="H1516" t="n">
         <v>3004717</v>
@@ -44507,7 +44507,7 @@
         <v>4.55097913742065</v>
       </c>
       <c r="G1522" t="n">
-        <v>4.05348348617554</v>
+        <v>4.0534839630127</v>
       </c>
       <c r="H1522" t="n">
         <v>1502529</v>
@@ -44652,7 +44652,7 @@
         <v>4.78317213058472</v>
       </c>
       <c r="G1527" t="n">
-        <v>4.26029443740845</v>
+        <v>4.26029396057129</v>
       </c>
       <c r="H1527" t="n">
         <v>2970018</v>
@@ -44768,7 +44768,7 @@
         <v>4.91495704650879</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.37767267227173</v>
+        <v>4.37767314910889</v>
       </c>
       <c r="H1531" t="n">
         <v>2759069</v>
@@ -44913,7 +44913,7 @@
         <v>5.03042602539062</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.48051929473877</v>
+        <v>4.48051881790161</v>
       </c>
       <c r="H1536" t="n">
         <v>2349535</v>
@@ -44971,7 +44971,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.39220523834229</v>
+        <v>4.39220476150513</v>
       </c>
       <c r="H1538" t="n">
         <v>3995107</v>
@@ -45058,7 +45058,7 @@
         <v>5.01410913467407</v>
       </c>
       <c r="G1541" t="n">
-        <v>4.46598625183105</v>
+        <v>4.4659857749939</v>
       </c>
       <c r="H1541" t="n">
         <v>2334898</v>
@@ -45348,7 +45348,7 @@
         <v>2.99591493606567</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.66841292381287</v>
+        <v>2.66841316223145</v>
       </c>
       <c r="H1551" t="n">
         <v>17072505</v>
@@ -45377,7 +45377,7 @@
         <v>3.02854704856873</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.69747805595398</v>
+        <v>2.6974778175354</v>
       </c>
       <c r="H1552" t="n">
         <v>16828629</v>
@@ -45522,7 +45522,7 @@
         <v>2.8616189956665</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.54879784584045</v>
+        <v>2.54879760742188</v>
       </c>
       <c r="H1557" t="n">
         <v>12600027</v>
@@ -45551,7 +45551,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.56221222877502</v>
+        <v>2.5622124671936</v>
       </c>
       <c r="H1558" t="n">
         <v>9318354</v>
@@ -45725,7 +45725,7 @@
         <v>2.51521301269531</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.24025964736938</v>
+        <v>2.24025940895081</v>
       </c>
       <c r="H1564" t="n">
         <v>6732142</v>
@@ -45754,7 +45754,7 @@
         <v>2.56165099143982</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.28162121772766</v>
+        <v>2.28162097930908</v>
       </c>
       <c r="H1565" t="n">
         <v>16777908</v>
@@ -45899,7 +45899,7 @@
         <v>2.56792688369751</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.28721117973328</v>
+        <v>2.2872109413147</v>
       </c>
       <c r="H1570" t="n">
         <v>5399583</v>
@@ -45928,7 +45928,7 @@
         <v>2.37715196609497</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.11729097366333</v>
+        <v>2.11729073524475</v>
       </c>
       <c r="H1571" t="n">
         <v>6070659</v>
@@ -46015,7 +46015,7 @@
         <v>2.58047795295715</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.29838991165161</v>
+        <v>2.29839015007019</v>
       </c>
       <c r="H1574" t="n">
         <v>9240163</v>
@@ -46131,7 +46131,7 @@
         <v>2.46450710296631</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.19509673118591</v>
+        <v>2.19509649276733</v>
       </c>
       <c r="H1578" t="n">
         <v>4819541</v>
@@ -46247,7 +46247,7 @@
         <v>2.67335510253906</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.38111400604248</v>
+        <v>2.38111424446106</v>
       </c>
       <c r="H1582" t="n">
         <v>3911764</v>
@@ -46392,7 +46392,7 @@
         <v>2.86287403106689</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.54991555213928</v>
+        <v>2.54991579055786</v>
       </c>
       <c r="H1587" t="n">
         <v>13747439</v>
@@ -46479,7 +46479,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.56221222877502</v>
+        <v>2.5622124671936</v>
       </c>
       <c r="H1590" t="n">
         <v>10760896</v>
@@ -46508,7 +46508,7 @@
         <v>2.93943500518799</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.61810731887817</v>
+        <v>2.61810708045959</v>
       </c>
       <c r="H1591" t="n">
         <v>7063060</v>
@@ -46537,7 +46537,7 @@
         <v>2.87919092178345</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.564448595047</v>
+        <v>2.56444883346558</v>
       </c>
       <c r="H1592" t="n">
         <v>10358249</v>
@@ -46566,7 +46566,7 @@
         <v>2.84404802322388</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.53314781188965</v>
+        <v>2.53314757347107</v>
       </c>
       <c r="H1593" t="n">
         <v>5883247</v>
@@ -46595,7 +46595,7 @@
         <v>2.77878308296204</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.47501730918884</v>
+        <v>2.47501707077026</v>
       </c>
       <c r="H1594" t="n">
         <v>7471517</v>
@@ -46653,7 +46653,7 @@
         <v>2.80262994766235</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.49625730514526</v>
+        <v>2.49625706672668</v>
       </c>
       <c r="H1596" t="n">
         <v>3079893</v>
@@ -46711,7 +46711,7 @@
         <v>2.79384398460388</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.48843169212341</v>
+        <v>2.48843145370483</v>
       </c>
       <c r="H1598" t="n">
         <v>2912676</v>
@@ -46740,7 +46740,7 @@
         <v>2.75744605064392</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.45601272583008</v>
+        <v>2.4560124874115</v>
       </c>
       <c r="H1599" t="n">
         <v>3637078</v>
@@ -46769,7 +46769,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.43700885772705</v>
+        <v>2.43700909614563</v>
       </c>
       <c r="H1600" t="n">
         <v>2248107</v>
@@ -46798,7 +46798,7 @@
         <v>2.84028291702271</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.52979397773743</v>
+        <v>2.52979421615601</v>
       </c>
       <c r="H1601" t="n">
         <v>4359715</v>
@@ -46885,7 +46885,7 @@
         <v>2.92437410354614</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.6046929359436</v>
+        <v>2.60469269752502</v>
       </c>
       <c r="H1604" t="n">
         <v>10127429</v>
@@ -46914,7 +46914,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.43700885772705</v>
+        <v>2.43700909614563</v>
       </c>
       <c r="H1605" t="n">
         <v>8650581</v>
@@ -47233,7 +47233,7 @@
         <v>2.48509001731873</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.21342945098877</v>
+        <v>2.21342968940735</v>
       </c>
       <c r="H1616" t="n">
         <v>11509858</v>
@@ -47262,7 +47262,7 @@
         <v>2.53780388832092</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.26038098335266</v>
+        <v>2.26038074493408</v>
       </c>
       <c r="H1617" t="n">
         <v>13634558</v>
@@ -47320,7 +47320,7 @@
         <v>2.68841600418091</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.39452886581421</v>
+        <v>2.39452862739563</v>
       </c>
       <c r="H1619" t="n">
         <v>6670481</v>
@@ -47349,7 +47349,7 @@
         <v>2.90680289268494</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.58904242515564</v>
+        <v>2.58904218673706</v>
       </c>
       <c r="H1620" t="n">
         <v>11371682</v>
@@ -47581,7 +47581,7 @@
         <v>2.97517991065979</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.6499445438385</v>
+        <v>2.64994478225708</v>
       </c>
       <c r="H1628" t="n">
         <v>9786163</v>
@@ -47755,7 +47755,7 @@
         <v>2.72426104545593</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.42645525932312</v>
+        <v>2.4264554977417</v>
       </c>
       <c r="H1634" t="n">
         <v>3222869</v>
@@ -47900,7 +47900,7 @@
         <v>2.37423992156982</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.11469721794128</v>
+        <v>2.11469697952271</v>
       </c>
       <c r="H1639" t="n">
         <v>5658326</v>
@@ -47987,7 +47987,7 @@
         <v>1.96649694442749</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.75152707099915</v>
+        <v>1.75152695178986</v>
       </c>
       <c r="H1642" t="n">
         <v>12639154</v>
@@ -48016,7 +48016,7 @@
         <v>2.01657509803772</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.79613077640533</v>
+        <v>1.79613089561462</v>
       </c>
       <c r="H1643" t="n">
         <v>25382152</v>
@@ -48103,7 +48103,7 @@
         <v>2.21557092666626</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.97337329387665</v>
+        <v>1.97337317466736</v>
       </c>
       <c r="H1646" t="n">
         <v>8434013</v>
@@ -48132,7 +48132,7 @@
         <v>1.73798203468323</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.54799246788025</v>
+        <v>1.54799258708954</v>
       </c>
       <c r="H1647" t="n">
         <v>26496542</v>
@@ -48161,7 +48161,7 @@
         <v>1.59776198863983</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.42310070991516</v>
+        <v>1.42310082912445</v>
       </c>
       <c r="H1648" t="n">
         <v>48720201</v>
@@ -48190,7 +48190,7 @@
         <v>1.24932205677032</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.11275100708008</v>
+        <v>1.11275088787079</v>
       </c>
       <c r="H1649" t="n">
         <v>56877192</v>
@@ -48451,7 +48451,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98913478851318</v>
+        <v>2.98913502693176</v>
       </c>
       <c r="H1658" t="n">
         <v>6899464</v>
@@ -48538,7 +48538,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.73594284057617</v>
+        <v>1.73594272136688</v>
       </c>
       <c r="H1661" t="n">
         <v>7745580</v>
@@ -48567,7 +48567,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.985986948013306</v>
+        <v>0.98598700761795</v>
       </c>
       <c r="H1662" t="n">
         <v>25986719</v>
@@ -48596,7 +48596,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.04209995269775</v>
+        <v>1.04210007190704</v>
       </c>
       <c r="H1663" t="n">
         <v>15517197</v>
@@ -48625,7 +48625,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.730360686779022</v>
+        <v>0.730360746383667</v>
       </c>
       <c r="H1664" t="n">
         <v>50412931</v>
@@ -48770,7 +48770,7 @@
         <v>0.71340000629425</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.635413825511932</v>
+        <v>0.635413885116577</v>
       </c>
       <c r="H1669" t="n">
         <v>28781555</v>
@@ -48828,7 +48828,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.659106075763702</v>
+        <v>0.659106016159058</v>
       </c>
       <c r="H1671" t="n">
         <v>27445946</v>
@@ -48857,7 +48857,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.692061364650726</v>
+        <v>0.692061305046082</v>
       </c>
       <c r="H1672" t="n">
         <v>35674340</v>
@@ -48944,7 +48944,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.751737177371979</v>
+        <v>0.751737117767334</v>
       </c>
       <c r="H1675" t="n">
         <v>37326895</v>
@@ -49002,7 +49002,7 @@
         <v>0.833599984645844</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.74247407913208</v>
+        <v>0.742474019527435</v>
       </c>
       <c r="H1677" t="n">
         <v>19689110</v>
@@ -49205,7 +49205,7 @@
         <v>0.821799993515015</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.731963992118835</v>
+        <v>0.731963932514191</v>
       </c>
       <c r="H1684" t="n">
         <v>16957436</v>
@@ -49292,7 +49292,7 @@
         <v>0.762199997901917</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.678879261016846</v>
+        <v>0.678879201412201</v>
       </c>
       <c r="H1687" t="n">
         <v>13487789</v>
@@ -49524,7 +49524,7 @@
         <v>0.716400027275085</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.638085901737213</v>
+        <v>0.638085961341858</v>
       </c>
       <c r="H1695" t="n">
         <v>20717644</v>
@@ -49756,7 +49756,7 @@
         <v>0.674600005149841</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.60085529088974</v>
+        <v>0.600855350494385</v>
       </c>
       <c r="H1703" t="n">
         <v>12648147</v>
@@ -49785,7 +49785,7 @@
         <v>0.697399973869324</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.621162891387939</v>
+        <v>0.621162831783295</v>
       </c>
       <c r="H1704" t="n">
         <v>26443104</v>
@@ -49843,7 +49843,7 @@
         <v>0.683200001716614</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.608515202999115</v>
+        <v>0.60851514339447</v>
       </c>
       <c r="H1706" t="n">
         <v>9988795</v>
@@ -49872,7 +49872,7 @@
         <v>0.662199974060059</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589810848236084</v>
+        <v>0.589810788631439</v>
       </c>
       <c r="H1707" t="n">
         <v>13712596</v>
@@ -49901,7 +49901,7 @@
         <v>0.64300000667572</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.572709739208221</v>
+        <v>0.572709679603577</v>
       </c>
       <c r="H1708" t="n">
         <v>58766149</v>
@@ -49930,7 +49930,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.540645062923431</v>
+        <v>0.540645122528076</v>
       </c>
       <c r="H1709" t="n">
         <v>28764901</v>
@@ -49959,7 +49959,7 @@
         <v>0.584800004959106</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.520871937274933</v>
+        <v>0.520871877670288</v>
       </c>
       <c r="H1710" t="n">
         <v>20980769</v>
@@ -49988,7 +49988,7 @@
         <v>0.59280002117157</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.527997374534607</v>
+        <v>0.527997434139252</v>
       </c>
       <c r="H1711" t="n">
         <v>21540866</v>
@@ -50075,7 +50075,7 @@
         <v>0.597199976444244</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.531916320323944</v>
+        <v>0.531916379928589</v>
       </c>
       <c r="H1714" t="n">
         <v>19250857</v>
@@ -50191,7 +50191,7 @@
         <v>0.637600004673004</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.567900002002716</v>
+        <v>0.567900061607361</v>
       </c>
       <c r="H1718" t="n">
         <v>20242520</v>
@@ -50336,7 +50336,7 @@
         <v>0.72759997844696</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.648061513900757</v>
+        <v>0.648061573505402</v>
       </c>
       <c r="H1723" t="n">
         <v>11884557</v>
@@ -50365,7 +50365,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.620806694030762</v>
+        <v>0.620806634426117</v>
       </c>
       <c r="H1724" t="n">
         <v>15320781</v>
@@ -50626,7 +50626,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.658215343952179</v>
+        <v>0.658215403556824</v>
       </c>
       <c r="H1733" t="n">
         <v>21488740</v>
@@ -50655,7 +50655,7 @@
         <v>0.758199989795685</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.675316452980042</v>
+        <v>0.675316512584686</v>
       </c>
       <c r="H1734" t="n">
         <v>33917790</v>
@@ -50713,7 +50713,7 @@
         <v>0.828599989414215</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.738020598888397</v>
+        <v>0.738020658493042</v>
       </c>
       <c r="H1736" t="n">
         <v>35628898</v>
@@ -50742,7 +50742,7 @@
         <v>0.958599984645844</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.853809535503387</v>
+        <v>0.853809475898743</v>
       </c>
       <c r="H1737" t="n">
         <v>99646498</v>
@@ -50800,7 +50800,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.8764328956604</v>
+        <v>0.876432955265045</v>
       </c>
       <c r="H1739" t="n">
         <v>39414006</v>
@@ -50829,7 +50829,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.87376081943512</v>
+        <v>0.873760879039764</v>
       </c>
       <c r="H1740" t="n">
         <v>36774205</v>
@@ -51003,7 +51003,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.882667660713196</v>
+        <v>0.882667720317841</v>
       </c>
       <c r="H1746" t="n">
         <v>44222060</v>
@@ -51061,7 +51061,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.919185698032379</v>
+        <v>0.919185638427734</v>
       </c>
       <c r="H1748" t="n">
         <v>60743048</v>
@@ -51090,7 +51090,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.957485198974609</v>
+        <v>0.957485139369965</v>
       </c>
       <c r="H1749" t="n">
         <v>38369686</v>
@@ -51148,7 +51148,7 @@
         <v>1.09650003910065</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.976634860038757</v>
+        <v>0.976634919643402</v>
       </c>
       <c r="H1751" t="n">
         <v>33789817</v>
@@ -51177,7 +51177,7 @@
         <v>1.03250002861023</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.919631063938141</v>
+        <v>0.919631123542786</v>
       </c>
       <c r="H1752" t="n">
         <v>95803812</v>
@@ -51206,7 +51206,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.921857714653015</v>
+        <v>0.92185777425766</v>
       </c>
       <c r="H1753" t="n">
         <v>44395351</v>
@@ -51322,7 +51322,7 @@
         <v>1.04649996757507</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.932100653648376</v>
+        <v>0.932100594043732</v>
       </c>
       <c r="H1757" t="n">
         <v>32064633</v>
@@ -51351,7 +51351,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.926311135292053</v>
+        <v>0.926311194896698</v>
       </c>
       <c r="H1758" t="n">
         <v>21110965</v>
@@ -51409,7 +51409,7 @@
         <v>1.04750001430511</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.93299126625061</v>
+        <v>0.932991325855255</v>
       </c>
       <c r="H1760" t="n">
         <v>40631058</v>
@@ -51438,7 +51438,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.912950873374939</v>
+        <v>0.912950932979584</v>
       </c>
       <c r="H1761" t="n">
         <v>26582079</v>
@@ -51467,7 +51467,7 @@
         <v>1.01950001716614</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.908052146434784</v>
+        <v>0.908052206039429</v>
       </c>
       <c r="H1762" t="n">
         <v>27481158</v>
@@ -51525,7 +51525,7 @@
         <v>1.04449999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.93031919002533</v>
+        <v>0.930319249629974</v>
       </c>
       <c r="H1764" t="n">
         <v>52512389</v>
@@ -51786,7 +51786,7 @@
         <v>1.00650000572205</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.896473228931427</v>
+        <v>0.896473288536072</v>
       </c>
       <c r="H1773" t="n">
         <v>22532469</v>
@@ -51844,7 +51844,7 @@
         <v>1.04949998855591</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.934772729873657</v>
+        <v>0.934772670269012</v>
       </c>
       <c r="H1775" t="n">
         <v>27222601</v>
@@ -51931,7 +51931,7 @@
         <v>1.10950005054474</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.988213777542114</v>
+        <v>0.988213717937469</v>
       </c>
       <c r="H1778" t="n">
         <v>33156068</v>
@@ -51989,7 +51989,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.977970957756042</v>
+        <v>0.977970898151398</v>
       </c>
       <c r="H1780" t="n">
         <v>82522322</v>
@@ -52047,7 +52047,7 @@
         <v>1.12750005722046</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.00424599647522</v>
+        <v>1.00424611568451</v>
       </c>
       <c r="H1782" t="n">
         <v>38953976</v>
@@ -52076,7 +52076,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.05456960201263</v>
+        <v>1.05456972122192</v>
       </c>
       <c r="H1783" t="n">
         <v>44539150</v>
@@ -52424,7 +52424,7 @@
         <v>1.31149995326996</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.16813182830811</v>
+        <v>1.16813170909882</v>
       </c>
       <c r="H1795" t="n">
         <v>88039189</v>
@@ -52685,7 +52685,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.25141072273254</v>
+        <v>1.25141084194183</v>
       </c>
       <c r="H1804" t="n">
         <v>50505371</v>
@@ -52772,7 +52772,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.2309250831604</v>
+        <v>1.23092496395111</v>
       </c>
       <c r="H1807" t="n">
         <v>27498297</v>
@@ -52801,7 +52801,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.21845555305481</v>
+        <v>1.21845543384552</v>
       </c>
       <c r="H1808" t="n">
         <v>27228579</v>
@@ -52946,7 +52946,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H1813" t="n">
         <v>201277103</v>
@@ -53062,7 +53062,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.25586414337158</v>
+        <v>1.25586426258087</v>
       </c>
       <c r="H1817" t="n">
         <v>26785082</v>
@@ -53149,7 +53149,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.24962949752808</v>
+        <v>1.24962937831879</v>
       </c>
       <c r="H1820" t="n">
         <v>28478257</v>
@@ -53236,7 +53236,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.3146493434906</v>
+        <v>1.31464922428131</v>
       </c>
       <c r="H1823" t="n">
         <v>73649010</v>
@@ -53265,7 +53265,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.35116744041443</v>
+        <v>1.35116732120514</v>
       </c>
       <c r="H1824" t="n">
         <v>173226691</v>
@@ -53294,7 +53294,7 @@
         <v>1.53450000286102</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.36675429344177</v>
+        <v>1.36675441265106</v>
       </c>
       <c r="H1825" t="n">
         <v>147696002</v>
@@ -53381,7 +53381,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.31643068790436</v>
+        <v>1.31643080711365</v>
       </c>
       <c r="H1828" t="n">
         <v>36445476</v>
@@ -53497,7 +53497,7 @@
         <v>1.35749995708466</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.20910334587097</v>
+        <v>1.20910322666168</v>
       </c>
       <c r="H1832" t="n">
         <v>30266079</v>
@@ -53555,7 +53555,7 @@
         <v>1.26549994945526</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.12716031074524</v>
+        <v>1.12716042995453</v>
       </c>
       <c r="H1834" t="n">
         <v>56083977</v>
@@ -53584,7 +53584,7 @@
         <v>1.14049994945526</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.01582491397858</v>
+        <v>1.01582479476929</v>
       </c>
       <c r="H1835" t="n">
         <v>70991471</v>
@@ -53671,7 +53671,7 @@
         <v>1.23450005054474</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.09954929351807</v>
+        <v>1.09954917430878</v>
       </c>
       <c r="H1838" t="n">
         <v>44048652</v>
@@ -53729,7 +53729,7 @@
         <v>1.32550001144409</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.18060147762299</v>
+        <v>1.1806013584137</v>
       </c>
       <c r="H1840" t="n">
         <v>26361553</v>
@@ -53758,7 +53758,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.14007532596588</v>
+        <v>1.14007520675659</v>
       </c>
       <c r="H1841" t="n">
         <v>30477091</v>
@@ -53932,7 +53932,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23181581497192</v>
+        <v>1.23181569576263</v>
       </c>
       <c r="H1847" t="n">
         <v>23160786</v>
@@ -53990,7 +53990,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1849" t="n">
         <v>61303523</v>
@@ -54512,7 +54512,7 @@
         <v>1.25049996376038</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.11380004882812</v>
+        <v>1.11380016803741</v>
       </c>
       <c r="H1867" t="n">
         <v>30080800</v>
@@ -54628,7 +54628,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.15076351165771</v>
+        <v>1.150763630867</v>
       </c>
       <c r="H1871" t="n">
         <v>24313190</v>
@@ -54715,7 +54715,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.13473129272461</v>
+        <v>1.13473117351532</v>
       </c>
       <c r="H1874" t="n">
         <v>17632468</v>
@@ -54802,7 +54802,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.12048017978668</v>
+        <v>1.12048029899597</v>
       </c>
       <c r="H1877" t="n">
         <v>12144067</v>
@@ -54831,7 +54831,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.15788900852203</v>
+        <v>1.15788888931274</v>
       </c>
       <c r="H1878" t="n">
         <v>28606803</v>
@@ -54976,7 +54976,7 @@
         <v>1.25750005245209</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.1200350522995</v>
+        <v>1.12003493309021</v>
       </c>
       <c r="H1883" t="n">
         <v>22657079</v>
@@ -55005,7 +55005,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.12226164340973</v>
+        <v>1.12226152420044</v>
       </c>
       <c r="H1884" t="n">
         <v>17046265</v>
@@ -55121,7 +55121,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.07416474819183</v>
+        <v>1.07416462898254</v>
       </c>
       <c r="H1888" t="n">
         <v>25051867</v>
@@ -55150,7 +55150,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.13473129272461</v>
+        <v>1.13473117351532</v>
       </c>
       <c r="H1889" t="n">
         <v>28793517</v>
@@ -55440,7 +55440,7 @@
         <v>1.25450003147125</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.11736297607422</v>
+        <v>1.11736285686493</v>
       </c>
       <c r="H1899" t="n">
         <v>19379185</v>
@@ -55498,7 +55498,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.08663427829742</v>
+        <v>1.08663439750671</v>
       </c>
       <c r="H1901" t="n">
         <v>20926564</v>
@@ -55585,7 +55585,7 @@
         <v>1.16250002384186</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.03541994094849</v>
+        <v>1.03542006015778</v>
       </c>
       <c r="H1904" t="n">
         <v>44264066</v>
@@ -55643,7 +55643,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.04833495616913</v>
+        <v>1.04833483695984</v>
       </c>
       <c r="H1906" t="n">
         <v>29040859</v>
@@ -55672,7 +55672,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.07772743701935</v>
+        <v>1.07772755622864</v>
       </c>
       <c r="H1907" t="n">
         <v>35754602</v>
@@ -55875,7 +55875,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.30039846897125</v>
+        <v>1.30039834976196</v>
       </c>
       <c r="H1914" t="n">
         <v>60137225</v>
@@ -55904,7 +55904,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.3110865354538</v>
+        <v>1.31108665466309</v>
       </c>
       <c r="H1915" t="n">
         <v>40402535</v>
@@ -55933,7 +55933,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.32266557216644</v>
+        <v>1.32266545295715</v>
       </c>
       <c r="H1916" t="n">
         <v>40030022</v>
@@ -56020,7 +56020,7 @@
         <v>1.43949997425079</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.28213942050934</v>
+        <v>1.28213930130005</v>
       </c>
       <c r="H1919" t="n">
         <v>27592628</v>
@@ -56049,7 +56049,7 @@
         <v>1.43250000476837</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.27590453624725</v>
+        <v>1.27590465545654</v>
       </c>
       <c r="H1920" t="n">
         <v>21395530</v>
@@ -56078,7 +56078,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.30039846897125</v>
+        <v>1.30039834976196</v>
       </c>
       <c r="H1921" t="n">
         <v>18806426</v>
@@ -56194,7 +56194,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.328009724617</v>
+        <v>1.32800960540771</v>
       </c>
       <c r="H1925" t="n">
         <v>26562115</v>
@@ -56281,7 +56281,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1928" t="n">
         <v>65561642</v>
@@ -56310,7 +56310,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1929" t="n">
         <v>29757990</v>
@@ -56339,7 +56339,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1930" t="n">
-        <v>1.29683566093445</v>
+        <v>1.29683554172516</v>
       </c>
       <c r="H1930" t="n">
         <v>46308940</v>
@@ -56368,7 +56368,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.29327285289764</v>
+        <v>1.29327297210693</v>
       </c>
       <c r="H1931" t="n">
         <v>26931723</v>
@@ -56426,7 +56426,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.25586414337158</v>
+        <v>1.25586426258087</v>
       </c>
       <c r="H1933" t="n">
         <v>26197753</v>
@@ -56484,7 +56484,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.24339461326599</v>
+        <v>1.24339473247528</v>
       </c>
       <c r="H1935" t="n">
         <v>23656707</v>
@@ -56658,7 +56658,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.30485188961029</v>
+        <v>1.304851770401</v>
       </c>
       <c r="H1941" t="n">
         <v>36097664</v>
@@ -56687,7 +56687,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H1942" t="n">
         <v>21886700</v>
@@ -56774,7 +56774,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.33869779109955</v>
+        <v>1.33869791030884</v>
       </c>
       <c r="H1945" t="n">
         <v>21109505</v>
@@ -56861,7 +56861,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.32266557216644</v>
+        <v>1.32266545295715</v>
       </c>
       <c r="H1948" t="n">
         <v>24397332</v>
@@ -56948,7 +56948,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1951" t="n">
-        <v>1.4019364118576</v>
+        <v>1.40193629264832</v>
       </c>
       <c r="H1951" t="n">
         <v>45002851</v>
@@ -56977,7 +56977,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.328009724617</v>
+        <v>1.32800960540771</v>
       </c>
       <c r="H1952" t="n">
         <v>124985920</v>
@@ -57093,7 +57093,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H1956" t="n">
         <v>39334965</v>
@@ -57151,7 +57151,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.37566113471985</v>
+        <v>1.37566125392914</v>
       </c>
       <c r="H1958" t="n">
         <v>66425360</v>
@@ -57238,7 +57238,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.41975009441376</v>
+        <v>1.41974997520447</v>
       </c>
       <c r="H1961" t="n">
         <v>31281838</v>
@@ -57325,7 +57325,7 @@
         <v>1.60950005054474</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.43355572223663</v>
+        <v>1.43355560302734</v>
       </c>
       <c r="H1964" t="n">
         <v>26138694</v>
@@ -57383,7 +57383,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.40104568004608</v>
+        <v>1.40104556083679</v>
       </c>
       <c r="H1966" t="n">
         <v>153129411</v>
@@ -57470,7 +57470,7 @@
         <v>1.46249997615814</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.30262517929077</v>
+        <v>1.30262506008148</v>
       </c>
       <c r="H1969" t="n">
         <v>26919423</v>
@@ -57499,7 +57499,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.27679538726807</v>
+        <v>1.27679526805878</v>
       </c>
       <c r="H1970" t="n">
         <v>26802260</v>
@@ -57528,7 +57528,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.29683566093445</v>
+        <v>1.29683554172516</v>
       </c>
       <c r="H1971" t="n">
         <v>25191162</v>
@@ -57731,7 +57731,7 @@
         <v>1.41849994659424</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.26343500614166</v>
+        <v>1.26343488693237</v>
       </c>
       <c r="H1978" t="n">
         <v>88712511</v>
@@ -57934,7 +57934,7 @@
         <v>1.5275000333786</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.36051964759827</v>
+        <v>1.36051952838898</v>
       </c>
       <c r="H1985" t="n">
         <v>16749025</v>
@@ -57992,7 +57992,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.37566113471985</v>
+        <v>1.37566125392914</v>
       </c>
       <c r="H1987" t="n">
         <v>51105926</v>
@@ -58021,7 +58021,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.29015564918518</v>
+        <v>1.29015552997589</v>
       </c>
       <c r="H1988" t="n">
         <v>67066172</v>
@@ -58079,7 +58079,7 @@
         <v>1.41449999809265</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.25987231731415</v>
+        <v>1.25987219810486</v>
       </c>
       <c r="H1990" t="n">
         <v>29949971</v>
@@ -58166,7 +58166,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.23626923561096</v>
+        <v>1.23626911640167</v>
       </c>
       <c r="H1993" t="n">
         <v>49894794</v>
@@ -58427,7 +58427,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H2002" t="n">
         <v>21379601</v>
@@ -58456,7 +58456,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.23805046081543</v>
+        <v>1.23805058002472</v>
       </c>
       <c r="H2003" t="n">
         <v>18744870</v>
@@ -58572,7 +58572,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H2007" t="n">
         <v>40689470</v>
@@ -58717,7 +58717,7 @@
         <v>1.44749999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>1.28926479816437</v>
+        <v>1.28926491737366</v>
       </c>
       <c r="H2012" t="n">
         <v>13752928</v>
@@ -58862,7 +58862,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H2017" t="n">
         <v>79262449</v>
@@ -58978,7 +58978,7 @@
         <v>1.46150004863739</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.30173444747925</v>
+        <v>1.30173456668854</v>
       </c>
       <c r="H2021" t="n">
         <v>32246011</v>
@@ -59007,7 +59007,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.24784803390503</v>
+        <v>1.24784815311432</v>
       </c>
       <c r="H2022" t="n">
         <v>61474648</v>
@@ -59036,7 +59036,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.24784803390503</v>
+        <v>1.24784815311432</v>
       </c>
       <c r="H2023" t="n">
         <v>34906238</v>
@@ -59123,7 +59123,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.22647166252136</v>
+        <v>1.22647154331207</v>
       </c>
       <c r="H2026" t="n">
         <v>31335128</v>
@@ -59210,7 +59210,7 @@
         <v>1.42050004005432</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.26521635055542</v>
+        <v>1.26521646976471</v>
       </c>
       <c r="H2029" t="n">
         <v>35969343</v>
@@ -59268,7 +59268,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.29015564918518</v>
+        <v>1.29015552997589</v>
       </c>
       <c r="H2031" t="n">
         <v>21961584</v>
@@ -59326,7 +59326,7 @@
         <v>1.44649994373322</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.28837406635284</v>
+        <v>1.28837418556213</v>
       </c>
       <c r="H2033" t="n">
         <v>15340362</v>
@@ -59384,7 +59384,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.3208841085434</v>
+        <v>1.32088422775269</v>
       </c>
       <c r="H2035" t="n">
         <v>16248522</v>
@@ -59413,7 +59413,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.30930531024933</v>
+        <v>1.30930519104004</v>
       </c>
       <c r="H2036" t="n">
         <v>16596498</v>
@@ -59471,7 +59471,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.32622814178467</v>
+        <v>1.32622826099396</v>
       </c>
       <c r="H2038" t="n">
         <v>31598891</v>
@@ -59558,7 +59558,7 @@
         <v>1.50650000572205</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.34181523323059</v>
+        <v>1.3418151140213</v>
       </c>
       <c r="H2041" t="n">
         <v>49175369</v>
@@ -59790,7 +59790,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.27679538726807</v>
+        <v>1.27679526805878</v>
       </c>
       <c r="H2049" t="n">
         <v>35782956</v>
@@ -59877,7 +59877,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31643068790436</v>
+        <v>1.31643080711365</v>
       </c>
       <c r="H2052" t="n">
         <v>70363678</v>
@@ -59964,7 +59964,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.34315121173859</v>
+        <v>1.34315133094788</v>
       </c>
       <c r="H2055" t="n">
         <v>21291896</v>
@@ -60399,7 +60399,7 @@
         <v>1.375</v>
       </c>
       <c r="G2070" t="n">
-        <v>1.22469019889832</v>
+        <v>1.2246903181076</v>
       </c>
       <c r="H2070" t="n">
         <v>37201230</v>
@@ -60486,7 +60486,7 @@
         <v>1.38100004196167</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.23003435134888</v>
+        <v>1.23003447055817</v>
       </c>
       <c r="H2073" t="n">
         <v>23884244</v>
@@ -60602,7 +60602,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.32979094982147</v>
+        <v>1.32979106903076</v>
       </c>
       <c r="H2077" t="n">
         <v>97981694</v>
@@ -60689,7 +60689,7 @@
         <v>1.82149994373322</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.6223806142807</v>
+        <v>1.62238049507141</v>
       </c>
       <c r="H2080" t="n">
         <v>170004032</v>
@@ -60776,7 +60776,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.72347319126129</v>
+        <v>1.723473072052</v>
       </c>
       <c r="H2083" t="n">
         <v>102058873</v>
@@ -60863,7 +60863,7 @@
         <v>1.97650003433228</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.76043665409088</v>
+        <v>1.76043653488159</v>
       </c>
       <c r="H2086" t="n">
         <v>36852781</v>
@@ -60979,7 +60979,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.87488961219788</v>
+        <v>1.87488949298859</v>
       </c>
       <c r="H2090" t="n">
         <v>47381130</v>
@@ -61008,7 +61008,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.88112413883209</v>
+        <v>1.88112425804138</v>
       </c>
       <c r="H2091" t="n">
         <v>28755854</v>
@@ -61037,7 +61037,7 @@
         <v>2.08699989318848</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.85885715484619</v>
+        <v>1.8588570356369</v>
       </c>
       <c r="H2092" t="n">
         <v>29642492</v>
@@ -61153,7 +61153,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.91318881511688</v>
+        <v>1.91318893432617</v>
       </c>
       <c r="H2096" t="n">
         <v>51280827</v>
@@ -61356,7 +61356,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.98889696598053</v>
+        <v>1.98889708518982</v>
       </c>
       <c r="H2103" t="n">
         <v>20444616</v>
@@ -61385,7 +61385,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2104" t="n">
-        <v>2.00760126113892</v>
+        <v>2.0076014995575</v>
       </c>
       <c r="H2104" t="n">
         <v>25187040</v>
@@ -61414,7 +61414,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G2105" t="n">
-        <v>2.00849199295044</v>
+        <v>2.00849223136902</v>
       </c>
       <c r="H2105" t="n">
         <v>29639951</v>
@@ -61472,7 +61472,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.06994915008545</v>
+        <v>2.06994891166687</v>
       </c>
       <c r="H2107" t="n">
         <v>41532484</v>
@@ -61530,7 +61530,7 @@
         <v>2.3970000743866</v>
       </c>
       <c r="G2109" t="n">
-        <v>2.13496923446655</v>
+        <v>2.13496899604797</v>
       </c>
       <c r="H2109" t="n">
         <v>81592175</v>
@@ -61559,7 +61559,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2110" t="n">
-        <v>2.08419990539551</v>
+        <v>2.08420014381409</v>
       </c>
       <c r="H2110" t="n">
         <v>42505018</v>
@@ -61646,7 +61646,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.99513185024261</v>
+        <v>1.99513173103333</v>
       </c>
       <c r="H2113" t="n">
         <v>34419597</v>
@@ -61675,7 +61675,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2114" t="n">
         <v>27318033</v>
@@ -61733,7 +61733,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.94258141517639</v>
+        <v>1.94258153438568</v>
       </c>
       <c r="H2116" t="n">
         <v>46811721</v>
@@ -61820,7 +61820,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.97197389602661</v>
+        <v>1.9719740152359</v>
       </c>
       <c r="H2119" t="n">
         <v>18487545</v>
@@ -61878,7 +61878,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.9523788690567</v>
+        <v>1.95237898826599</v>
       </c>
       <c r="H2121" t="n">
         <v>27702781</v>
@@ -61936,7 +61936,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.94080007076263</v>
+        <v>1.94079983234406</v>
       </c>
       <c r="H2123" t="n">
         <v>20243345</v>
@@ -62023,7 +62023,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2126" t="n">
-        <v>1.91318881511688</v>
+        <v>1.91318893432617</v>
       </c>
       <c r="H2126" t="n">
         <v>16042180</v>
@@ -62081,7 +62081,7 @@
         <v>2.13100004196167</v>
       </c>
       <c r="G2128" t="n">
-        <v>1.8980473279953</v>
+        <v>1.89804720878601</v>
       </c>
       <c r="H2128" t="n">
         <v>22011055</v>
@@ -62110,7 +62110,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2129" t="n">
         <v>19775385</v>
@@ -62168,7 +62168,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G2131" t="n">
-        <v>1.97019255161285</v>
+        <v>1.97019267082214</v>
       </c>
       <c r="H2131" t="n">
         <v>19971385</v>
@@ -62197,7 +62197,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2132" t="n">
-        <v>2.02541494369507</v>
+        <v>2.02541518211365</v>
       </c>
       <c r="H2132" t="n">
         <v>39975168</v>
@@ -62255,7 +62255,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2134" t="n">
-        <v>2.11359286308289</v>
+        <v>2.11359262466431</v>
       </c>
       <c r="H2134" t="n">
         <v>44554345</v>
@@ -62371,7 +62371,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2138" t="n">
-        <v>2.12160897254944</v>
+        <v>2.12160873413086</v>
       </c>
       <c r="H2138" t="n">
         <v>27147448</v>
@@ -62400,7 +62400,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2139" t="n">
-        <v>2.11359286308289</v>
+        <v>2.11359262466431</v>
       </c>
       <c r="H2139" t="n">
         <v>18307723</v>
@@ -62458,7 +62458,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2141" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2141" t="n">
         <v>13550932</v>
@@ -62516,7 +62516,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2143" t="n">
-        <v>1.98889696598053</v>
+        <v>1.98889708518982</v>
       </c>
       <c r="H2143" t="n">
         <v>26661132</v>
@@ -62574,7 +62574,7 @@
         <v>2.15300011634827</v>
       </c>
       <c r="G2145" t="n">
-        <v>1.91764235496521</v>
+        <v>1.9176424741745</v>
       </c>
       <c r="H2145" t="n">
         <v>22296682</v>
@@ -62603,7 +62603,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.9203143119812</v>
+        <v>1.92031419277191</v>
       </c>
       <c r="H2146" t="n">
         <v>35218310</v>
@@ -62632,7 +62632,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.93367457389832</v>
+        <v>1.9336746931076</v>
       </c>
       <c r="H2147" t="n">
         <v>17467441</v>
@@ -62661,7 +62661,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2148" t="n">
         <v>28506448</v>
@@ -62690,7 +62690,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.83926212787628</v>
+        <v>1.83926224708557</v>
       </c>
       <c r="H2149" t="n">
         <v>27905894</v>
@@ -62748,7 +62748,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2151" t="n">
         <v>33021803</v>
@@ -62835,7 +62835,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.86152911186218</v>
+        <v>1.86152923107147</v>
       </c>
       <c r="H2154" t="n">
         <v>35977989</v>
@@ -62864,7 +62864,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.86152911186218</v>
+        <v>1.86152923107147</v>
       </c>
       <c r="H2155" t="n">
         <v>22290014</v>
@@ -62893,7 +62893,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2156" t="n">
-        <v>1.89626574516296</v>
+        <v>1.89626586437225</v>
       </c>
       <c r="H2156" t="n">
         <v>21085975</v>
@@ -62922,7 +62922,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2157" t="n">
         <v>35756797</v>
@@ -62951,7 +62951,7 @@
         <v>2.15899991989136</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.92298626899719</v>
+        <v>1.92298638820648</v>
       </c>
       <c r="H2158" t="n">
         <v>16359113</v>
@@ -62980,7 +62980,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.99245965480804</v>
+        <v>1.99245977401733</v>
       </c>
       <c r="H2159" t="n">
         <v>39248301</v>
@@ -63096,7 +63096,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.1358597278595</v>
+        <v>2.13585996627808</v>
       </c>
       <c r="H2163" t="n">
         <v>33746318</v>
@@ -63212,7 +63212,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2167" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2167" t="n">
         <v>25601227</v>
@@ -63299,7 +63299,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G2170" t="n">
-        <v>2.07351183891296</v>
+        <v>2.07351207733154</v>
       </c>
       <c r="H2170" t="n">
         <v>26440425</v>
@@ -63328,7 +63328,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.06371426582336</v>
+        <v>2.06371450424194</v>
       </c>
       <c r="H2171" t="n">
         <v>26757191</v>
@@ -63357,7 +63357,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G2172" t="n">
-        <v>2.09666991233826</v>
+        <v>2.09666967391968</v>
       </c>
       <c r="H2172" t="n">
         <v>24912702</v>
@@ -63415,7 +63415,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2174" t="n">
-        <v>2.10913920402527</v>
+        <v>2.10913944244385</v>
       </c>
       <c r="H2174" t="n">
         <v>19724218</v>
@@ -63444,7 +63444,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.12339043617249</v>
+        <v>2.12339019775391</v>
       </c>
       <c r="H2175" t="n">
         <v>29130431</v>
@@ -63473,7 +63473,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.14476656913757</v>
+        <v>2.14476680755615</v>
       </c>
       <c r="H2176" t="n">
         <v>16678363</v>
@@ -63560,7 +63560,7 @@
         <v>2.41899991035461</v>
       </c>
       <c r="G2179" t="n">
-        <v>2.15456390380859</v>
+        <v>2.15456414222717</v>
       </c>
       <c r="H2179" t="n">
         <v>23246952</v>
@@ -63618,7 +63618,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2181" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2181" t="n">
         <v>45523587</v>
@@ -63647,7 +63647,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G2182" t="n">
-        <v>1.98444354534149</v>
+        <v>1.9844434261322</v>
       </c>
       <c r="H2182" t="n">
         <v>44868347</v>
@@ -63705,7 +63705,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.9461442232132</v>
+        <v>1.94614410400391</v>
       </c>
       <c r="H2184" t="n">
         <v>18067908</v>
@@ -63734,7 +63734,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2185" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2185" t="n">
         <v>20351307</v>
@@ -63763,7 +63763,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.94080007076263</v>
+        <v>1.94079983234406</v>
       </c>
       <c r="H2186" t="n">
         <v>18512647</v>
@@ -63879,7 +63879,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G2190" t="n">
-        <v>1.79294645786285</v>
+        <v>1.79294657707214</v>
       </c>
       <c r="H2190" t="n">
         <v>24047004</v>
@@ -63995,7 +63995,7 @@
         <v>1.98450005054474</v>
       </c>
       <c r="G2194" t="n">
-        <v>1.76756203174591</v>
+        <v>1.7675621509552</v>
       </c>
       <c r="H2194" t="n">
         <v>23362020</v>
@@ -64140,7 +64140,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G2199" t="n">
-        <v>1.84282493591309</v>
+        <v>1.8428248167038</v>
       </c>
       <c r="H2199" t="n">
         <v>32985049</v>
@@ -64227,7 +64227,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.84549701213837</v>
+        <v>1.84549689292908</v>
       </c>
       <c r="H2202" t="n">
         <v>16439030</v>
@@ -64256,7 +64256,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.81521379947662</v>
+        <v>1.81521368026733</v>
       </c>
       <c r="H2203" t="n">
         <v>23581831</v>
@@ -64343,7 +64343,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2206" t="n">
         <v>19255054</v>
@@ -64372,7 +64372,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2207" t="n">
-        <v>1.80185341835022</v>
+        <v>1.80185329914093</v>
       </c>
       <c r="H2207" t="n">
         <v>12789945</v>
@@ -64401,7 +64401,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.67448556423187</v>
+        <v>1.67448568344116</v>
       </c>
       <c r="H2208" t="n">
         <v>53900944</v>
@@ -64430,7 +64430,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.71189427375793</v>
+        <v>1.71189439296722</v>
       </c>
       <c r="H2209" t="n">
         <v>35189302</v>
@@ -64546,7 +64546,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G2213" t="n">
-        <v>1.60055887699127</v>
+        <v>1.60055899620056</v>
       </c>
       <c r="H2213" t="n">
         <v>37765591</v>
@@ -64575,7 +64575,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.6272794008255</v>
+        <v>1.62727928161621</v>
       </c>
       <c r="H2214" t="n">
         <v>22594695</v>
@@ -64865,7 +64865,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.81343221664429</v>
+        <v>1.81343233585358</v>
       </c>
       <c r="H2224" t="n">
         <v>24725349</v>
@@ -65097,7 +65097,7 @@
         <v>2.05699992179871</v>
       </c>
       <c r="G2232" t="n">
-        <v>1.83213663101196</v>
+        <v>1.83213651180267</v>
       </c>
       <c r="H2232" t="n">
         <v>29472348</v>
@@ -65155,7 +65155,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2234" t="n">
-        <v>1.79027438163757</v>
+        <v>1.79027450084686</v>
       </c>
       <c r="H2234" t="n">
         <v>16876658</v>
@@ -65184,7 +65184,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.80185341835022</v>
+        <v>1.80185329914093</v>
       </c>
       <c r="H2235" t="n">
         <v>20529123</v>
@@ -65358,7 +65358,7 @@
         <v>1.99150002002716</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.773796916008</v>
+        <v>1.77379679679871</v>
       </c>
       <c r="H2241" t="n">
         <v>46698722</v>
@@ -65416,7 +65416,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2243" t="n">
-        <v>1.83926212787628</v>
+        <v>1.83926224708557</v>
       </c>
       <c r="H2243" t="n">
         <v>48994310</v>
@@ -65445,7 +65445,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G2244" t="n">
-        <v>1.80630695819855</v>
+        <v>1.80630683898926</v>
       </c>
       <c r="H2244" t="n">
         <v>29352657</v>
@@ -65474,7 +65474,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G2245" t="n">
-        <v>1.89003121852875</v>
+        <v>1.89003109931946</v>
       </c>
       <c r="H2245" t="n">
         <v>81646961</v>
@@ -65503,7 +65503,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.94970679283142</v>
+        <v>1.94970667362213</v>
       </c>
       <c r="H2246" t="n">
         <v>74141845</v>
@@ -65561,7 +65561,7 @@
         <v>2.16300010681152</v>
       </c>
       <c r="G2248" t="n">
-        <v>1.92654919624329</v>
+        <v>1.92654931545258</v>
       </c>
       <c r="H2248" t="n">
         <v>30842480</v>
@@ -65590,7 +65590,7 @@
         <v>2.16700005531311</v>
       </c>
       <c r="G2249" t="n">
-        <v>1.93011200428009</v>
+        <v>1.9301118850708</v>
       </c>
       <c r="H2249" t="n">
         <v>30050128</v>
@@ -65619,7 +65619,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2250" t="n">
-        <v>1.94525361061096</v>
+        <v>1.94525349140167</v>
       </c>
       <c r="H2250" t="n">
         <v>26979522</v>
@@ -65648,7 +65648,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2251" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2251" t="n">
         <v>53288446</v>
@@ -65677,7 +65677,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2252" t="n">
         <v>41701778</v>
@@ -65735,7 +65735,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2254" t="n">
-        <v>2.00314784049988</v>
+        <v>2.00314807891846</v>
       </c>
       <c r="H2254" t="n">
         <v>44091922</v>
@@ -65793,7 +65793,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2256" t="n">
-        <v>2.06994915008545</v>
+        <v>2.06994891166687</v>
       </c>
       <c r="H2256" t="n">
         <v>54666411</v>
@@ -65880,7 +65880,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2259" t="n">
-        <v>2.05302619934082</v>
+        <v>2.0530264377594</v>
       </c>
       <c r="H2259" t="n">
         <v>24934085</v>
@@ -65909,7 +65909,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2260" t="n">
-        <v>2.06371426582336</v>
+        <v>2.06371450424194</v>
       </c>
       <c r="H2260" t="n">
         <v>40038315</v>
@@ -65938,7 +65938,7 @@
         <v>2.33299994468689</v>
       </c>
       <c r="G2261" t="n">
-        <v>2.07796549797058</v>
+        <v>2.077965259552</v>
       </c>
       <c r="H2261" t="n">
         <v>34552742</v>
@@ -65967,7 +65967,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2262" t="n">
-        <v>2.10913920402527</v>
+        <v>2.10913944244385</v>
       </c>
       <c r="H2262" t="n">
         <v>21092827</v>
@@ -66170,7 +66170,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G2269" t="n">
-        <v>2.16525220870972</v>
+        <v>2.1652524471283</v>
       </c>
       <c r="H2269" t="n">
         <v>38389055</v>
@@ -66315,7 +66315,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G2274" t="n">
-        <v>2.26768088340759</v>
+        <v>2.26768112182617</v>
       </c>
       <c r="H2274" t="n">
         <v>31890329</v>
@@ -66431,7 +66431,7 @@
         <v>2.48699998855591</v>
       </c>
       <c r="G2278" t="n">
-        <v>2.21513080596924</v>
+        <v>2.21513056755066</v>
       </c>
       <c r="H2278" t="n">
         <v>18431422</v>
@@ -66518,7 +66518,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2281" t="n">
-        <v>2.29261994361877</v>
+        <v>2.29262018203735</v>
       </c>
       <c r="H2281" t="n">
         <v>22696347</v>
@@ -66547,7 +66547,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2282" t="n">
-        <v>2.31577801704407</v>
+        <v>2.31577777862549</v>
       </c>
       <c r="H2282" t="n">
         <v>26132220</v>
@@ -66634,7 +66634,7 @@
         <v>2.64299988746643</v>
       </c>
       <c r="G2285" t="n">
-        <v>2.35407733917236</v>
+        <v>2.35407710075378</v>
       </c>
       <c r="H2285" t="n">
         <v>60652789</v>
@@ -66721,7 +66721,7 @@
         <v>2.51099991798401</v>
       </c>
       <c r="G2288" t="n">
-        <v>2.23650693893433</v>
+        <v>2.23650717735291</v>
       </c>
       <c r="H2288" t="n">
         <v>15785363</v>
@@ -66750,7 +66750,7 @@
         <v>2.5090000629425</v>
       </c>
       <c r="G2289" t="n">
-        <v>2.23472595214844</v>
+        <v>2.23472571372986</v>
       </c>
       <c r="H2289" t="n">
         <v>11480911</v>
@@ -66924,7 +66924,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G2295" t="n">
-        <v>2.45294332504272</v>
+        <v>2.45294308662415</v>
       </c>
       <c r="H2295" t="n">
         <v>20214762</v>
@@ -67040,7 +67040,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G2299" t="n">
-        <v>2.31221508979797</v>
+        <v>2.31221532821655</v>
       </c>
       <c r="H2299" t="n">
         <v>74870654</v>
@@ -67098,7 +67098,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G2301" t="n">
-        <v>2.27658772468567</v>
+        <v>2.27658796310425</v>
       </c>
       <c r="H2301" t="n">
         <v>30195449</v>
@@ -67127,7 +67127,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G2302" t="n">
-        <v>2.25164866447449</v>
+        <v>2.25164890289307</v>
       </c>
       <c r="H2302" t="n">
         <v>24626119</v>
@@ -67156,7 +67156,7 @@
         <v>2.51300001144409</v>
       </c>
       <c r="G2303" t="n">
-        <v>2.23828840255737</v>
+        <v>2.23828864097595</v>
       </c>
       <c r="H2303" t="n">
         <v>20104873</v>
@@ -67214,7 +67214,7 @@
         <v>2.48300004005432</v>
       </c>
       <c r="G2305" t="n">
-        <v>2.21156787872314</v>
+        <v>2.21156811714172</v>
       </c>
       <c r="H2305" t="n">
         <v>27751479</v>
@@ -67243,7 +67243,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G2306" t="n">
-        <v>2.14832949638367</v>
+        <v>2.14832925796509</v>
       </c>
       <c r="H2306" t="n">
         <v>43140551</v>
@@ -67272,7 +67272,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2307" t="n">
-        <v>2.12160897254944</v>
+        <v>2.12160873413086</v>
       </c>
       <c r="H2307" t="n">
         <v>24111895</v>
@@ -67504,7 +67504,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2315" t="n">
-        <v>2.04411935806274</v>
+        <v>2.04411959648132</v>
       </c>
       <c r="H2315" t="n">
         <v>24791375</v>
@@ -67562,7 +67562,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G2317" t="n">
-        <v>2.04768228530884</v>
+        <v>2.04768204689026</v>
       </c>
       <c r="H2317" t="n">
         <v>21357944</v>
@@ -67707,7 +67707,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G2322" t="n">
-        <v>2.05658912658691</v>
+        <v>2.05658888816833</v>
       </c>
       <c r="H2322" t="n">
         <v>15248097</v>
@@ -67794,7 +67794,7 @@
         <v>2.28099989891052</v>
       </c>
       <c r="G2325" t="n">
-        <v>2.03164982795715</v>
+        <v>2.03164958953857</v>
       </c>
       <c r="H2325" t="n">
         <v>20004250</v>
@@ -67823,7 +67823,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G2326" t="n">
-        <v>2.0681676864624</v>
+        <v>2.06816792488098</v>
       </c>
       <c r="H2326" t="n">
         <v>27029721</v>
@@ -67910,7 +67910,7 @@
         <v>2.20300006866455</v>
       </c>
       <c r="G2329" t="n">
-        <v>1.9621764421463</v>
+        <v>1.96217656135559</v>
       </c>
       <c r="H2329" t="n">
         <v>165427959</v>
@@ -67939,7 +67939,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2330" t="n">
-        <v>2.00314784049988</v>
+        <v>2.00314807891846</v>
       </c>
       <c r="H2330" t="n">
         <v>90357314</v>
@@ -67997,7 +67997,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2332" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2332" t="n">
         <v>49106059</v>
@@ -68055,7 +68055,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2334" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2334" t="n">
         <v>47390121</v>
@@ -68200,7 +68200,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G2339" t="n">
-        <v>1.85440385341644</v>
+        <v>1.85440373420715</v>
       </c>
       <c r="H2339" t="n">
         <v>52881442</v>
@@ -68287,7 +68287,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2342" t="n">
-        <v>1.89626574516296</v>
+        <v>1.89626586437225</v>
       </c>
       <c r="H2342" t="n">
         <v>54335801</v>
@@ -68316,7 +68316,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.93278396129608</v>
+        <v>1.93278384208679</v>
       </c>
       <c r="H2343" t="n">
         <v>54028041</v>
@@ -68345,7 +68345,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2344" t="n">
         <v>32171346</v>
@@ -68432,7 +68432,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2347" t="n">
-        <v>1.96841132640839</v>
+        <v>1.9684112071991</v>
       </c>
       <c r="H2347" t="n">
         <v>31365241</v>
@@ -68461,7 +68461,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2348" t="n">
-        <v>1.94525361061096</v>
+        <v>1.94525349140167</v>
       </c>
       <c r="H2348" t="n">
         <v>43704455</v>
@@ -68519,7 +68519,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G2350" t="n">
-        <v>1.9586136341095</v>
+        <v>1.95861351490021</v>
       </c>
       <c r="H2350" t="n">
         <v>35346168</v>
@@ -68548,7 +68548,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2351" t="n">
-        <v>1.93367457389832</v>
+        <v>1.9336746931076</v>
       </c>
       <c r="H2351" t="n">
         <v>29069827</v>
@@ -68635,7 +68635,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2354" t="n">
-        <v>1.89537537097931</v>
+        <v>1.89537525177002</v>
       </c>
       <c r="H2354" t="n">
         <v>33627039</v>
@@ -68664,7 +68664,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.72436380386353</v>
+        <v>1.72436392307281</v>
       </c>
       <c r="H2355" t="n">
         <v>85443225</v>
@@ -68838,7 +68838,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G2361" t="n">
-        <v>1.52128803730011</v>
+        <v>1.52128791809082</v>
       </c>
       <c r="H2361" t="n">
         <v>38867170</v>
@@ -68867,7 +68867,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G2362" t="n">
-        <v>1.56493139266968</v>
+        <v>1.56493151187897</v>
       </c>
       <c r="H2362" t="n">
         <v>50829326</v>
@@ -69041,7 +69041,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G2368" t="n">
-        <v>1.74930310249329</v>
+        <v>1.749302983284</v>
       </c>
       <c r="H2368" t="n">
         <v>65053471</v>
@@ -69128,7 +69128,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.82590174674988</v>
+        <v>1.82590186595917</v>
       </c>
       <c r="H2371" t="n">
         <v>29975796</v>
@@ -69186,7 +69186,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2373" t="n">
-        <v>1.85262227058411</v>
+        <v>1.8526223897934</v>
       </c>
       <c r="H2373" t="n">
         <v>37413416</v>
@@ -69215,7 +69215,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G2374" t="n">
-        <v>1.83302748203278</v>
+        <v>1.83302736282349</v>
       </c>
       <c r="H2374" t="n">
         <v>32042896</v>
@@ -69244,7 +69244,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G2375" t="n">
-        <v>1.82768332958221</v>
+        <v>1.82768321037292</v>
       </c>
       <c r="H2375" t="n">
         <v>38839501</v>
@@ -69273,7 +69273,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G2376" t="n">
-        <v>1.83837139606476</v>
+        <v>1.83837127685547</v>
       </c>
       <c r="H2376" t="n">
         <v>30420999</v>
@@ -69331,7 +69331,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G2378" t="n">
-        <v>1.9399094581604</v>
+        <v>1.93990933895111</v>
       </c>
       <c r="H2378" t="n">
         <v>64329397</v>
@@ -80212,6 +80212,35 @@
         <v>10131136</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>4.53700017929077</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>4.54699993133545</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>4.46099996566772</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>4.48099994659424</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>4.48099994659424</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>10790046</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
